--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,1145 +508,1145 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.75</v>
+        <v>17.51</v>
       </c>
       <c r="C2" t="n">
-        <v>17.77</v>
+        <v>17.53</v>
       </c>
       <c r="D2" t="n">
-        <v>17.74</v>
+        <v>17.51</v>
       </c>
       <c r="E2" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="F2" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>70.92</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>71.09999999999999</v>
+        <v>73.83</v>
       </c>
       <c r="J2" t="n">
-        <v>70.67</v>
+        <v>73.56</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.17</v>
+        <v>17.6</v>
       </c>
       <c r="C3" t="n">
-        <v>18.45</v>
+        <v>17.68</v>
       </c>
       <c r="D3" t="n">
-        <v>17.85</v>
+        <v>17.49</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="F3" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>67.5</v>
+        <v>72.5</v>
       </c>
       <c r="I3" t="n">
-        <v>70.09</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>65.53</v>
+        <v>71.78</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="N3" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.12</v>
+        <v>17.53</v>
       </c>
       <c r="C4" t="n">
-        <v>19.48</v>
+        <v>17.62</v>
       </c>
       <c r="D4" t="n">
-        <v>18.59</v>
+        <v>17.45</v>
       </c>
       <c r="E4" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="F4" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>62.25</v>
+        <v>72.33</v>
       </c>
       <c r="I4" t="n">
-        <v>64.8</v>
+        <v>72.88</v>
       </c>
       <c r="J4" t="n">
-        <v>60.27</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N4" t="n">
-        <v>6180</v>
+        <v>6152</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.89</v>
+        <v>17.64</v>
       </c>
       <c r="C5" t="n">
-        <v>20.2</v>
+        <v>17.9</v>
       </c>
       <c r="D5" t="n">
-        <v>19.54</v>
+        <v>17.44</v>
       </c>
       <c r="E5" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="F5" t="n">
-        <v>11.1</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>58.12</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>59.88</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>56.65</v>
+        <v>69.53</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N5" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.59</v>
+        <v>17.84</v>
       </c>
       <c r="C6" t="n">
-        <v>21.02</v>
+        <v>17.88</v>
       </c>
       <c r="D6" t="n">
-        <v>20.23</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>55.26</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>56.46</v>
+        <v>70.3</v>
       </c>
       <c r="J6" t="n">
-        <v>54.02</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="N6" t="n">
-        <v>6200</v>
+        <v>6162</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.34</v>
+        <v>17.9</v>
       </c>
       <c r="C7" t="n">
-        <v>21.65</v>
+        <v>17.97</v>
       </c>
       <c r="D7" t="n">
-        <v>20.98</v>
+        <v>17.82</v>
       </c>
       <c r="E7" t="n">
-        <v>11.1</v>
+        <v>12.1</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>52.89</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>53.97</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>51.51</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="N7" t="n">
-        <v>6220</v>
+        <v>6162</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.22</v>
+        <v>17.74</v>
       </c>
       <c r="C8" t="n">
-        <v>22.72</v>
+        <v>17.82</v>
       </c>
       <c r="D8" t="n">
-        <v>21.71</v>
+        <v>17.7</v>
       </c>
       <c r="E8" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="F8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G8" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>50.44</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>51.7</v>
+        <v>70.98</v>
       </c>
       <c r="J8" t="n">
-        <v>49.53</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="N8" t="n">
-        <v>6240</v>
+        <v>6162</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.94</v>
+        <v>17.68</v>
       </c>
       <c r="C9" t="n">
-        <v>23.82</v>
+        <v>17.71</v>
       </c>
       <c r="D9" t="n">
-        <v>22.29</v>
+        <v>17.64</v>
       </c>
       <c r="E9" t="n">
-        <v>10.6</v>
+        <v>12.3</v>
       </c>
       <c r="F9" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="G9" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>46.37</v>
+        <v>71.42</v>
       </c>
       <c r="I9" t="n">
-        <v>49.68</v>
+        <v>71.8</v>
       </c>
       <c r="J9" t="n">
-        <v>44.22</v>
+        <v>71.13</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>6250</v>
+        <v>6162</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.12</v>
+        <v>17.74</v>
       </c>
       <c r="C10" t="n">
-        <v>24.14</v>
+        <v>17.78</v>
       </c>
       <c r="D10" t="n">
-        <v>22.72</v>
+        <v>17.68</v>
       </c>
       <c r="E10" t="n">
-        <v>10.5</v>
+        <v>12.4</v>
       </c>
       <c r="F10" t="n">
-        <v>10.3</v>
+        <v>12.2</v>
       </c>
       <c r="G10" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>45.59</v>
+        <v>71.53</v>
       </c>
       <c r="I10" t="n">
-        <v>46.9</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>43.18</v>
+        <v>70.67</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>6240</v>
+        <v>6152</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.76</v>
+        <v>18.17</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63</v>
+        <v>18.45</v>
       </c>
       <c r="D11" t="n">
-        <v>22.08</v>
+        <v>17.85</v>
       </c>
       <c r="E11" t="n">
-        <v>10.8</v>
+        <v>11.9</v>
       </c>
       <c r="F11" t="n">
-        <v>10.5</v>
+        <v>11.7</v>
       </c>
       <c r="G11" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>47.51</v>
+        <v>67.5</v>
       </c>
       <c r="I11" t="n">
-        <v>49.36</v>
+        <v>70.09</v>
       </c>
       <c r="J11" t="n">
-        <v>46.08</v>
+        <v>65.53</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>6240</v>
+        <v>6152</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22.55</v>
+        <v>19.12</v>
       </c>
       <c r="C12" t="n">
-        <v>23.29</v>
+        <v>19.48</v>
       </c>
       <c r="D12" t="n">
-        <v>21.68</v>
+        <v>18.59</v>
       </c>
       <c r="E12" t="n">
-        <v>10.7</v>
+        <v>11.5</v>
       </c>
       <c r="F12" t="n">
-        <v>10.5</v>
+        <v>11.4</v>
       </c>
       <c r="G12" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>47.88</v>
+        <v>62.25</v>
       </c>
       <c r="I12" t="n">
-        <v>50.32</v>
+        <v>64.8</v>
       </c>
       <c r="J12" t="n">
-        <v>46.13</v>
+        <v>60.27</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="N12" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22.47</v>
+        <v>19.89</v>
       </c>
       <c r="C13" t="n">
-        <v>23.42</v>
+        <v>20.2</v>
       </c>
       <c r="D13" t="n">
-        <v>21.73</v>
+        <v>19.54</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="F13" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="G13" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>49.09</v>
+        <v>58.12</v>
       </c>
       <c r="I13" t="n">
-        <v>51.32</v>
+        <v>59.88</v>
       </c>
       <c r="J13" t="n">
-        <v>46.18</v>
+        <v>56.65</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="N13" t="n">
-        <v>6230</v>
+        <v>6190</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.72</v>
+        <v>20.59</v>
       </c>
       <c r="C14" t="n">
-        <v>23.46</v>
+        <v>21.02</v>
       </c>
       <c r="D14" t="n">
-        <v>20.79</v>
+        <v>20.23</v>
       </c>
       <c r="E14" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="F14" t="n">
         <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>616</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>52.51</v>
+        <v>55.26</v>
       </c>
       <c r="I14" t="n">
-        <v>55.76</v>
+        <v>56.46</v>
       </c>
       <c r="J14" t="n">
-        <v>47.65</v>
+        <v>54.02</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="N14" t="n">
-        <v>6220</v>
+        <v>6200</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20.86</v>
+        <v>21.34</v>
       </c>
       <c r="C15" t="n">
-        <v>21.56</v>
+        <v>21.65</v>
       </c>
       <c r="D15" t="n">
-        <v>20.25</v>
+        <v>20.98</v>
       </c>
       <c r="E15" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
       <c r="F15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>642</v>
+        <v>63</v>
       </c>
       <c r="H15" t="n">
-        <v>56.36</v>
+        <v>52.89</v>
       </c>
       <c r="I15" t="n">
-        <v>59</v>
+        <v>53.97</v>
       </c>
       <c r="J15" t="n">
-        <v>53.69</v>
+        <v>51.51</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="N15" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19.5</v>
+        <v>22.22</v>
       </c>
       <c r="C16" t="n">
-        <v>19.99</v>
+        <v>22.72</v>
       </c>
       <c r="D16" t="n">
-        <v>19.01</v>
+        <v>21.71</v>
       </c>
       <c r="E16" t="n">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
       <c r="F16" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="G16" t="n">
-        <v>341</v>
+        <v>210</v>
       </c>
       <c r="H16" t="n">
-        <v>61.31</v>
+        <v>50.44</v>
       </c>
       <c r="I16" t="n">
-        <v>62.89</v>
+        <v>51.7</v>
       </c>
       <c r="J16" t="n">
-        <v>59.57</v>
+        <v>49.53</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
         <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>6190</v>
+        <v>6240</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.96</v>
+        <v>22.94</v>
       </c>
       <c r="C17" t="n">
-        <v>18.97</v>
+        <v>23.82</v>
       </c>
       <c r="D17" t="n">
-        <v>17.06</v>
+        <v>22.29</v>
       </c>
       <c r="E17" t="n">
-        <v>12.1</v>
+        <v>10.6</v>
       </c>
       <c r="F17" t="n">
-        <v>11.8</v>
+        <v>10.3</v>
       </c>
       <c r="G17" t="n">
-        <v>158</v>
+        <v>355</v>
       </c>
       <c r="H17" t="n">
-        <v>69.53</v>
+        <v>46.37</v>
       </c>
       <c r="I17" t="n">
-        <v>74.66</v>
+        <v>49.68</v>
       </c>
       <c r="J17" t="n">
-        <v>64.09</v>
+        <v>44.22</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="M17" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>6180</v>
+        <v>6250</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.73</v>
+        <v>23.12</v>
       </c>
       <c r="C18" t="n">
-        <v>16.97</v>
+        <v>24.14</v>
       </c>
       <c r="D18" t="n">
-        <v>16.64</v>
+        <v>22.72</v>
       </c>
       <c r="E18" t="n">
-        <v>12.4</v>
+        <v>10.5</v>
       </c>
       <c r="F18" t="n">
-        <v>12.4</v>
+        <v>10.3</v>
       </c>
       <c r="G18" t="n">
-        <v>33</v>
+        <v>344</v>
       </c>
       <c r="H18" t="n">
-        <v>76.20999999999999</v>
+        <v>45.59</v>
       </c>
       <c r="I18" t="n">
-        <v>76.59999999999999</v>
+        <v>46.9</v>
       </c>
       <c r="J18" t="n">
-        <v>75.42</v>
+        <v>43.18</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>6162</v>
+        <v>6240</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16.74</v>
+        <v>22.76</v>
       </c>
       <c r="C19" t="n">
-        <v>16.83</v>
+        <v>23.63</v>
       </c>
       <c r="D19" t="n">
-        <v>16.69</v>
+        <v>22.08</v>
       </c>
       <c r="E19" t="n">
-        <v>12.4</v>
+        <v>10.8</v>
       </c>
       <c r="F19" t="n">
-        <v>12.3</v>
+        <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="H19" t="n">
-        <v>76.59</v>
+        <v>47.51</v>
       </c>
       <c r="I19" t="n">
-        <v>77.48</v>
+        <v>49.36</v>
       </c>
       <c r="J19" t="n">
-        <v>75.81999999999999</v>
+        <v>46.08</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6152</v>
+        <v>6240</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.74</v>
+        <v>22.55</v>
       </c>
       <c r="C20" t="n">
-        <v>16.81</v>
+        <v>23.29</v>
       </c>
       <c r="D20" t="n">
-        <v>16.65</v>
+        <v>21.68</v>
       </c>
       <c r="E20" t="n">
-        <v>12.6</v>
+        <v>10.7</v>
       </c>
       <c r="F20" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="H20" t="n">
-        <v>77.14</v>
+        <v>47.88</v>
       </c>
       <c r="I20" t="n">
-        <v>77.55</v>
+        <v>50.32</v>
       </c>
       <c r="J20" t="n">
-        <v>76.81999999999999</v>
+        <v>46.13</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>6162</v>
+        <v>6220</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.83</v>
+        <v>22.47</v>
       </c>
       <c r="C21" t="n">
-        <v>16.93</v>
+        <v>23.42</v>
       </c>
       <c r="D21" t="n">
-        <v>16.77</v>
+        <v>21.73</v>
       </c>
       <c r="E21" t="n">
-        <v>12.8</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>12.7</v>
+        <v>10.7</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="H21" t="n">
-        <v>77.89</v>
+        <v>49.09</v>
       </c>
       <c r="I21" t="n">
-        <v>78.14</v>
+        <v>51.32</v>
       </c>
       <c r="J21" t="n">
-        <v>77.23</v>
+        <v>46.18</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>6142</v>
+        <v>6230</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.08</v>
+        <v>21.72</v>
       </c>
       <c r="C22" t="n">
-        <v>17.24</v>
+        <v>23.46</v>
       </c>
       <c r="D22" t="n">
-        <v>16.95</v>
+        <v>20.79</v>
       </c>
       <c r="E22" t="n">
-        <v>12.9</v>
+        <v>11.3</v>
       </c>
       <c r="F22" t="n">
-        <v>12.8</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="H22" t="n">
-        <v>77.45999999999999</v>
+        <v>52.51</v>
       </c>
       <c r="I22" t="n">
-        <v>78.15000000000001</v>
+        <v>55.76</v>
       </c>
       <c r="J22" t="n">
-        <v>76.95</v>
+        <v>47.65</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>6142</v>
+        <v>6220</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.17</v>
+        <v>20.86</v>
       </c>
       <c r="C23" t="n">
-        <v>17.3</v>
+        <v>21.56</v>
       </c>
       <c r="D23" t="n">
-        <v>16.93</v>
+        <v>20.25</v>
       </c>
       <c r="E23" t="n">
-        <v>13.2</v>
+        <v>11.7</v>
       </c>
       <c r="F23" t="n">
-        <v>13.1</v>
+        <v>11.5</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="H23" t="n">
-        <v>78.43000000000001</v>
+        <v>56.36</v>
       </c>
       <c r="I23" t="n">
-        <v>81.27</v>
+        <v>59</v>
       </c>
       <c r="J23" t="n">
-        <v>77.08</v>
+        <v>53.69</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.59</v>
+        <v>19.5</v>
       </c>
       <c r="C24" t="n">
-        <v>17.86</v>
+        <v>19.99</v>
       </c>
       <c r="D24" t="n">
-        <v>17.28</v>
+        <v>19.01</v>
       </c>
       <c r="E24" t="n">
-        <v>12.9</v>
+        <v>11.7</v>
       </c>
       <c r="F24" t="n">
-        <v>12.8</v>
+        <v>11.4</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H24" t="n">
-        <v>75</v>
+        <v>61.31</v>
       </c>
       <c r="I24" t="n">
-        <v>77.95</v>
+        <v>62.89</v>
       </c>
       <c r="J24" t="n">
-        <v>73.39</v>
+        <v>59.57</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="M24" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18.2</v>
+        <v>17.96</v>
       </c>
       <c r="C25" t="n">
-        <v>18.41</v>
+        <v>18.97</v>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>17.06</v>
       </c>
       <c r="E25" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F25" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H25" t="n">
-        <v>69.83</v>
+        <v>69.53</v>
       </c>
       <c r="I25" t="n">
-        <v>72.37</v>
+        <v>74.66</v>
       </c>
       <c r="J25" t="n">
-        <v>68.34</v>
+        <v>64.09</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="N25" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18.56</v>
+        <v>16.73</v>
       </c>
       <c r="C26" t="n">
-        <v>18.7</v>
+        <v>16.97</v>
       </c>
       <c r="D26" t="n">
-        <v>18.41</v>
+        <v>16.64</v>
       </c>
       <c r="E26" t="n">
         <v>12.4</v>
@@ -1655,25 +1655,25 @@
         <v>12.4</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H26" t="n">
-        <v>67.93000000000001</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>68.55</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>67.33</v>
+        <v>75.42</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="M26" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="N26" t="n">
         <v>6162</v>
@@ -1683,928 +1683,930 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>18.92</v>
+        <v>16.74</v>
       </c>
       <c r="C27" t="n">
-        <v>19.04</v>
+        <v>16.83</v>
       </c>
       <c r="D27" t="n">
-        <v>18.74</v>
+        <v>16.69</v>
       </c>
       <c r="E27" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F27" t="n">
         <v>12.3</v>
       </c>
-      <c r="F27" t="n">
-        <v>12.2</v>
-      </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>66</v>
+        <v>76.59</v>
       </c>
       <c r="I27" t="n">
-        <v>67.08</v>
+        <v>77.48</v>
       </c>
       <c r="J27" t="n">
-        <v>65.19</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="M27" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="N27" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.98</v>
+        <v>16.74</v>
       </c>
       <c r="C28" t="n">
-        <v>19.02</v>
+        <v>16.81</v>
       </c>
       <c r="D28" t="n">
-        <v>18.95</v>
+        <v>16.65</v>
       </c>
       <c r="E28" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="F28" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>65.26000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="I28" t="n">
-        <v>65.51000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J28" t="n">
-        <v>65.09999999999999</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M28" t="n">
         <v>1.4</v>
       </c>
-      <c r="M28" t="n">
-        <v>1.7</v>
-      </c>
       <c r="N28" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.27</v>
+        <v>16.83</v>
       </c>
       <c r="C29" t="n">
-        <v>19.65</v>
+        <v>16.93</v>
       </c>
       <c r="D29" t="n">
-        <v>19.01</v>
+        <v>16.77</v>
       </c>
       <c r="E29" t="n">
-        <v>11.9</v>
+        <v>12.8</v>
       </c>
       <c r="F29" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>62.96</v>
+        <v>77.89</v>
       </c>
       <c r="I29" t="n">
-        <v>64.81</v>
+        <v>78.14</v>
       </c>
       <c r="J29" t="n">
-        <v>60.5</v>
+        <v>77.23</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="N29" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-14 19:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.98</v>
+        <v>17.08</v>
       </c>
       <c r="C30" t="n">
-        <v>20.21</v>
+        <v>17.24</v>
       </c>
       <c r="D30" t="n">
-        <v>19.72</v>
+        <v>16.95</v>
       </c>
       <c r="E30" t="n">
-        <v>11.5</v>
+        <v>12.9</v>
       </c>
       <c r="F30" t="n">
-        <v>11.3</v>
+        <v>12.8</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>58.7</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>59.99</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>57.42</v>
+        <v>76.95</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="N30" t="n">
-        <v>6180</v>
+        <v>6142</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20.51</v>
+        <v>17.17</v>
       </c>
       <c r="C31" t="n">
-        <v>20.87</v>
+        <v>17.3</v>
       </c>
       <c r="D31" t="n">
-        <v>20.26</v>
+        <v>16.93</v>
       </c>
       <c r="E31" t="n">
-        <v>11.3</v>
+        <v>13.2</v>
       </c>
       <c r="F31" t="n">
-        <v>11.2</v>
+        <v>13.1</v>
       </c>
       <c r="G31" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>56.48</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>57.91</v>
+        <v>81.27</v>
       </c>
       <c r="J31" t="n">
-        <v>55.61</v>
+        <v>77.08</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="N31" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>20.85</v>
+        <v>17.59</v>
       </c>
       <c r="C32" t="n">
-        <v>21.07</v>
+        <v>17.86</v>
       </c>
       <c r="D32" t="n">
-        <v>20.73</v>
+        <v>17.28</v>
       </c>
       <c r="E32" t="n">
-        <v>11.7</v>
+        <v>12.9</v>
       </c>
       <c r="F32" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="G32" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>56.48</v>
+        <v>75</v>
       </c>
       <c r="I32" t="n">
-        <v>57.04</v>
+        <v>77.95</v>
       </c>
       <c r="J32" t="n">
-        <v>56</v>
+        <v>73.39</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="N32" t="n">
-        <v>6210</v>
+        <v>6162</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.96</v>
+        <v>18.2</v>
       </c>
       <c r="C33" t="n">
-        <v>21.38</v>
+        <v>18.41</v>
       </c>
       <c r="D33" t="n">
-        <v>20.75</v>
+        <v>18</v>
       </c>
       <c r="E33" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="F33" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="G33" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>56.06</v>
+        <v>69.83</v>
       </c>
       <c r="I33" t="n">
-        <v>56.71</v>
+        <v>72.37</v>
       </c>
       <c r="J33" t="n">
-        <v>54.86</v>
+        <v>68.34</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="N33" t="n">
-        <v>6220</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21.55</v>
+        <v>18.56</v>
       </c>
       <c r="C34" t="n">
-        <v>21.81</v>
+        <v>18.7</v>
       </c>
       <c r="D34" t="n">
-        <v>21.14</v>
+        <v>18.41</v>
       </c>
       <c r="E34" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="F34" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
       <c r="G34" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>53.03</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>54.48</v>
+        <v>68.55</v>
       </c>
       <c r="J34" t="n">
-        <v>51.56</v>
+        <v>67.33</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="N34" t="n">
-        <v>6220</v>
+        <v>6162</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-14 14:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>21.25</v>
+        <v>18.92</v>
       </c>
       <c r="C35" t="n">
-        <v>21.62</v>
+        <v>19.04</v>
       </c>
       <c r="D35" t="n">
-        <v>20.57</v>
+        <v>18.74</v>
       </c>
       <c r="E35" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="F35" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="G35" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>55.82</v>
+        <v>66</v>
       </c>
       <c r="I35" t="n">
-        <v>57.91</v>
+        <v>67.08</v>
       </c>
       <c r="J35" t="n">
-        <v>54.45</v>
+        <v>65.19</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="N35" t="n">
-        <v>6230</v>
+        <v>6170</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-14 13:00:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>20.17</v>
+        <v>18.98</v>
       </c>
       <c r="C36" t="n">
-        <v>22.05</v>
+        <v>19.02</v>
       </c>
       <c r="D36" t="n">
-        <v>19.15</v>
+        <v>18.95</v>
       </c>
       <c r="E36" t="n">
         <v>12.2</v>
       </c>
       <c r="F36" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="G36" t="n">
-        <v>426</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>60.86</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>65.42</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>53.21</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="N36" t="n">
-        <v>6250</v>
+        <v>6170</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.06</v>
+        <v>19.27</v>
       </c>
       <c r="C37" t="n">
-        <v>20.31</v>
+        <v>19.65</v>
       </c>
       <c r="D37" t="n">
-        <v>18.02</v>
+        <v>19.01</v>
       </c>
       <c r="E37" t="n">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="F37" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="G37" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>67.37</v>
+        <v>62.96</v>
       </c>
       <c r="I37" t="n">
-        <v>72.42</v>
+        <v>64.81</v>
       </c>
       <c r="J37" t="n">
-        <v>61.34</v>
+        <v>60.5</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="M37" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="N37" t="n">
-        <v>6210</v>
+        <v>6170</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00:00</t>
+          <t>2026-10-14 19:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.91</v>
+        <v>19.98</v>
       </c>
       <c r="C38" t="n">
-        <v>18.13</v>
+        <v>20.21</v>
       </c>
       <c r="D38" t="n">
-        <v>17.79</v>
+        <v>19.72</v>
       </c>
       <c r="E38" t="n">
-        <v>12.8</v>
+        <v>11.5</v>
       </c>
       <c r="F38" t="n">
-        <v>12.6</v>
+        <v>11.3</v>
       </c>
       <c r="G38" t="n">
-        <v>139</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
-        <v>72.75</v>
+        <v>58.7</v>
       </c>
       <c r="I38" t="n">
-        <v>73.73999999999999</v>
+        <v>59.99</v>
       </c>
       <c r="J38" t="n">
-        <v>71.81</v>
+        <v>57.42</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="M38" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="N38" t="n">
-        <v>6200</v>
+        <v>6180</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14 10:00:00</t>
+          <t>2026-10-14 18:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.23</v>
+        <v>20.51</v>
       </c>
       <c r="C39" t="n">
-        <v>17.93</v>
+        <v>20.87</v>
       </c>
       <c r="D39" t="n">
-        <v>16.74</v>
+        <v>20.26</v>
       </c>
       <c r="E39" t="n">
-        <v>13</v>
+        <v>11.3</v>
       </c>
       <c r="F39" t="n">
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="G39" t="n">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="H39" t="n">
-        <v>76.95999999999999</v>
+        <v>56.48</v>
       </c>
       <c r="I39" t="n">
-        <v>79.36</v>
+        <v>57.91</v>
       </c>
       <c r="J39" t="n">
-        <v>73.15000000000001</v>
+        <v>55.61</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14 09:00:00</t>
+          <t>2026-10-14 17:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.12</v>
+        <v>20.85</v>
       </c>
       <c r="C40" t="n">
-        <v>17.33</v>
+        <v>21.07</v>
       </c>
       <c r="D40" t="n">
-        <v>16.81</v>
+        <v>20.73</v>
       </c>
       <c r="E40" t="n">
-        <v>13.1</v>
+        <v>11.7</v>
       </c>
       <c r="F40" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="G40" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="H40" t="n">
-        <v>78.23999999999999</v>
+        <v>56.48</v>
       </c>
       <c r="I40" t="n">
-        <v>80.20999999999999</v>
+        <v>57.04</v>
       </c>
       <c r="J40" t="n">
-        <v>76.95999999999999</v>
+        <v>56</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>6180</v>
+        <v>6210</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14 08:00:00</t>
+          <t>2026-10-14 16:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.38</v>
+        <v>20.96</v>
       </c>
       <c r="C41" t="n">
-        <v>17.11</v>
+        <v>21.38</v>
       </c>
       <c r="D41" t="n">
-        <v>15.9</v>
+        <v>20.75</v>
       </c>
       <c r="E41" t="n">
-        <v>13.4</v>
+        <v>11.6</v>
       </c>
       <c r="F41" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="G41" t="n">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="H41" t="n">
-        <v>83.54000000000001</v>
+        <v>56.06</v>
       </c>
       <c r="I41" t="n">
-        <v>87.8</v>
+        <v>56.71</v>
       </c>
       <c r="J41" t="n">
-        <v>79.43000000000001</v>
+        <v>54.86</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="N41" t="n">
-        <v>6180</v>
+        <v>6220</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 07:00:00</t>
+          <t>2026-10-14 15:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.72</v>
+        <v>21.55</v>
       </c>
       <c r="C42" t="n">
-        <v>15.84</v>
+        <v>21.81</v>
       </c>
       <c r="D42" t="n">
-        <v>15.66</v>
+        <v>21.14</v>
       </c>
       <c r="E42" t="n">
-        <v>13.9</v>
+        <v>11.3</v>
       </c>
       <c r="F42" t="n">
-        <v>13.7</v>
+        <v>11.1</v>
       </c>
       <c r="G42" t="n">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="H42" t="n">
-        <v>89.95999999999999</v>
+        <v>53.03</v>
       </c>
       <c r="I42" t="n">
-        <v>91.70999999999999</v>
+        <v>54.48</v>
       </c>
       <c r="J42" t="n">
-        <v>88.26000000000001</v>
+        <v>51.56</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="M42" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>6170</v>
+        <v>6220</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 06:00:00</t>
+          <t>2026-10-14 14:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15.84</v>
+        <v>21.25</v>
       </c>
       <c r="C43" t="n">
-        <v>16.18</v>
+        <v>21.62</v>
       </c>
       <c r="D43" t="n">
-        <v>15.68</v>
+        <v>20.57</v>
       </c>
       <c r="E43" t="n">
-        <v>14.1</v>
+        <v>11.9</v>
       </c>
       <c r="F43" t="n">
-        <v>13.8</v>
+        <v>11.7</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="H43" t="n">
-        <v>90.09</v>
+        <v>55.82</v>
       </c>
       <c r="I43" t="n">
-        <v>91.78</v>
+        <v>57.91</v>
       </c>
       <c r="J43" t="n">
-        <v>86.43000000000001</v>
+        <v>54.45</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>6162</v>
+        <v>6230</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 05:00:00</t>
+          <t>2026-10-14 13:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.41</v>
+        <v>20.17</v>
       </c>
       <c r="C44" t="n">
-        <v>16.5</v>
+        <v>22.05</v>
       </c>
       <c r="D44" t="n">
-        <v>16.29</v>
+        <v>19.15</v>
       </c>
       <c r="E44" t="n">
-        <v>14.1</v>
+        <v>12.2</v>
       </c>
       <c r="F44" t="n">
-        <v>13.7</v>
+        <v>11.9</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="H44" t="n">
-        <v>86.45999999999999</v>
+        <v>60.86</v>
       </c>
       <c r="I44" t="n">
-        <v>87.2</v>
+        <v>65.42</v>
       </c>
       <c r="J44" t="n">
-        <v>85.92</v>
+        <v>53.21</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="M44" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>6162</v>
+        <v>6250</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 04:00:00</t>
+          <t>2026-10-14 12:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.47</v>
+        <v>19.06</v>
       </c>
       <c r="C45" t="n">
-        <v>16.54</v>
+        <v>20.31</v>
       </c>
       <c r="D45" t="n">
-        <v>16.42</v>
+        <v>18.02</v>
       </c>
       <c r="E45" t="n">
-        <v>13.9</v>
+        <v>12.6</v>
       </c>
       <c r="F45" t="n">
-        <v>13.9</v>
+        <v>11.9</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="H45" t="n">
-        <v>85.78</v>
+        <v>67.37</v>
       </c>
       <c r="I45" t="n">
-        <v>86.31</v>
+        <v>72.42</v>
       </c>
       <c r="J45" t="n">
-        <v>85.06999999999999</v>
+        <v>61.34</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="N45" t="n">
-        <v>6170</v>
+        <v>6210</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 03:00:00</t>
+          <t>2026-10-14 11:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16.86</v>
+        <v>17.91</v>
       </c>
       <c r="C46" t="n">
-        <v>17.03</v>
+        <v>18.13</v>
       </c>
       <c r="D46" t="n">
-        <v>16.59</v>
+        <v>17.79</v>
       </c>
       <c r="E46" t="n">
-        <v>13.5</v>
+        <v>12.8</v>
       </c>
       <c r="F46" t="n">
-        <v>13.4</v>
+        <v>12.6</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="H46" t="n">
-        <v>81.77</v>
+        <v>72.75</v>
       </c>
       <c r="I46" t="n">
-        <v>84.56</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>80.16</v>
+        <v>71.81</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2613,203 +2615,201 @@
         <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="N46" t="n">
-        <v>6152</v>
+        <v>6200</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 02:00:00</t>
+          <t>2026-10-14 10:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>17.23</v>
       </c>
       <c r="C47" t="n">
-        <v>17.36</v>
+        <v>17.93</v>
       </c>
       <c r="D47" t="n">
-        <v>17.07</v>
+        <v>16.74</v>
       </c>
       <c r="E47" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F47" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="H47" t="n">
-        <v>77.90000000000001</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>79.65000000000001</v>
+        <v>79.36</v>
       </c>
       <c r="J47" t="n">
-        <v>76.63</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M47" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N47" t="n">
-        <v>6162</v>
+        <v>6200</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:00</t>
+          <t>2026-10-14 09:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.5</v>
+        <v>17.12</v>
       </c>
       <c r="C48" t="n">
-        <v>17.63</v>
+        <v>17.33</v>
       </c>
       <c r="D48" t="n">
-        <v>17.35</v>
+        <v>16.81</v>
       </c>
       <c r="E48" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="F48" t="n">
         <v>12.8</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="H48" t="n">
-        <v>75.40000000000001</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>76.48</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>74.15000000000001</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="M48" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-14 08:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.86</v>
+        <v>16.38</v>
       </c>
       <c r="C49" t="n">
-        <v>18.06</v>
+        <v>17.11</v>
       </c>
       <c r="D49" t="n">
-        <v>17.7</v>
+        <v>15.9</v>
       </c>
       <c r="E49" t="n">
-        <v>12.7</v>
+        <v>13.4</v>
       </c>
       <c r="F49" t="n">
-        <v>12.6</v>
+        <v>13.2</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="H49" t="n">
-        <v>72.56</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>73.86</v>
+        <v>87.8</v>
       </c>
       <c r="J49" t="n">
-        <v>71.53</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>6170</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.5</v>
-      </c>
+        <v>6180</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-13 23:00:00</t>
+          <t>2026-10-14 07:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>18.21</v>
+        <v>15.72</v>
       </c>
       <c r="C50" t="n">
-        <v>18.34</v>
+        <v>15.84</v>
       </c>
       <c r="D50" t="n">
-        <v>18.08</v>
+        <v>15.66</v>
       </c>
       <c r="E50" t="n">
-        <v>12.6</v>
+        <v>13.9</v>
       </c>
       <c r="F50" t="n">
-        <v>12.5</v>
+        <v>13.7</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>70.86</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>71.23999999999999</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>70.38</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="M50" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="N50" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O50" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,279 +508,279 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.51</v>
+        <v>21.99</v>
       </c>
       <c r="C2" t="n">
-        <v>17.53</v>
+        <v>22.22</v>
       </c>
       <c r="D2" t="n">
-        <v>17.51</v>
+        <v>21.61</v>
       </c>
       <c r="E2" t="n">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="F2" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="H2" t="n">
-        <v>73.70999999999999</v>
+        <v>53.11</v>
       </c>
       <c r="I2" t="n">
-        <v>73.83</v>
+        <v>54.1</v>
       </c>
       <c r="J2" t="n">
-        <v>73.56</v>
+        <v>52.16</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="N2" t="n">
-        <v>6152</v>
+        <v>6210</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.6</v>
+        <v>21.1</v>
       </c>
       <c r="C3" t="n">
-        <v>17.68</v>
+        <v>21.69</v>
       </c>
       <c r="D3" t="n">
-        <v>17.49</v>
+        <v>20.51</v>
       </c>
       <c r="E3" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F3" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="H3" t="n">
-        <v>72.5</v>
+        <v>55.96</v>
       </c>
       <c r="I3" t="n">
-        <v>73.76000000000001</v>
+        <v>58.01</v>
       </c>
       <c r="J3" t="n">
-        <v>71.78</v>
+        <v>53.81</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>6142</v>
+        <v>6210</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.53</v>
+        <v>20.15</v>
       </c>
       <c r="C4" t="n">
-        <v>17.62</v>
+        <v>20.85</v>
       </c>
       <c r="D4" t="n">
-        <v>17.45</v>
+        <v>19.57</v>
       </c>
       <c r="E4" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F4" t="n">
-        <v>12.2</v>
+        <v>11.6</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="H4" t="n">
-        <v>72.33</v>
+        <v>60.77</v>
       </c>
       <c r="I4" t="n">
-        <v>72.88</v>
+        <v>64.81</v>
       </c>
       <c r="J4" t="n">
-        <v>71.93000000000001</v>
+        <v>56.73</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="N4" t="n">
-        <v>6152</v>
+        <v>6200</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.64</v>
+        <v>19.37</v>
       </c>
       <c r="C5" t="n">
-        <v>17.9</v>
+        <v>19.79</v>
       </c>
       <c r="D5" t="n">
-        <v>17.44</v>
+        <v>18.91</v>
       </c>
       <c r="E5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F5" t="n">
         <v>12.3</v>
       </c>
-      <c r="F5" t="n">
-        <v>12</v>
-      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="H5" t="n">
-        <v>71.73999999999999</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>73.59999999999999</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>69.53</v>
+        <v>63.19</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="N5" t="n">
-        <v>6152</v>
+        <v>6180</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.84</v>
+        <v>18.41</v>
       </c>
       <c r="C6" t="n">
-        <v>17.88</v>
+        <v>18.85</v>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>18.05</v>
       </c>
       <c r="E6" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H6" t="n">
-        <v>70.06999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="I6" t="n">
-        <v>70.3</v>
+        <v>71.67</v>
       </c>
       <c r="J6" t="n">
-        <v>69.65000000000001</v>
+        <v>67.22</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="N6" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.9</v>
+        <v>17.66</v>
       </c>
       <c r="C7" t="n">
-        <v>17.97</v>
+        <v>17.95</v>
       </c>
       <c r="D7" t="n">
-        <v>17.82</v>
+        <v>17.51</v>
       </c>
       <c r="E7" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>69.79000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="I7" t="n">
-        <v>70.48999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="J7" t="n">
-        <v>69.43000000000001</v>
+        <v>72.19</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="N7" t="n">
         <v>6162</v>
@@ -790,138 +790,138 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.74</v>
+        <v>17.6</v>
       </c>
       <c r="C8" t="n">
-        <v>17.82</v>
+        <v>17.68</v>
       </c>
       <c r="D8" t="n">
-        <v>17.7</v>
+        <v>17.49</v>
       </c>
       <c r="E8" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F8" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>70.81999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I8" t="n">
-        <v>70.98</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>70.54000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="N8" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.68</v>
+        <v>17.53</v>
       </c>
       <c r="C9" t="n">
-        <v>17.71</v>
+        <v>17.62</v>
       </c>
       <c r="D9" t="n">
-        <v>17.64</v>
+        <v>17.45</v>
       </c>
       <c r="E9" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F9" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>71.42</v>
+        <v>72.33</v>
       </c>
       <c r="I9" t="n">
-        <v>71.8</v>
+        <v>72.88</v>
       </c>
       <c r="J9" t="n">
-        <v>71.13</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N9" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.74</v>
+        <v>17.64</v>
       </c>
       <c r="C10" t="n">
-        <v>17.78</v>
+        <v>17.9</v>
       </c>
       <c r="D10" t="n">
-        <v>17.68</v>
+        <v>17.44</v>
       </c>
       <c r="E10" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F10" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>71.53</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>72.06999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>70.67</v>
+        <v>69.53</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N10" t="n">
         <v>6152</v>
@@ -931,467 +931,467 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18.17</v>
+        <v>17.84</v>
       </c>
       <c r="C11" t="n">
-        <v>18.45</v>
+        <v>17.88</v>
       </c>
       <c r="D11" t="n">
-        <v>17.85</v>
+        <v>17.8</v>
       </c>
       <c r="E11" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="F11" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>67.5</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>70.09</v>
+        <v>70.3</v>
       </c>
       <c r="J11" t="n">
-        <v>65.53</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N11" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.12</v>
+        <v>17.9</v>
       </c>
       <c r="C12" t="n">
-        <v>19.48</v>
+        <v>17.97</v>
       </c>
       <c r="D12" t="n">
-        <v>18.59</v>
+        <v>17.82</v>
       </c>
       <c r="E12" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="F12" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>62.25</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>64.8</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>60.27</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>1.5</v>
       </c>
       <c r="N12" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19.89</v>
+        <v>17.74</v>
       </c>
       <c r="C13" t="n">
-        <v>20.2</v>
+        <v>17.82</v>
       </c>
       <c r="D13" t="n">
-        <v>19.54</v>
+        <v>17.7</v>
       </c>
       <c r="E13" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="F13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>58.12</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>59.88</v>
+        <v>70.98</v>
       </c>
       <c r="J13" t="n">
-        <v>56.65</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N13" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20.59</v>
+        <v>17.68</v>
       </c>
       <c r="C14" t="n">
-        <v>21.02</v>
+        <v>17.71</v>
       </c>
       <c r="D14" t="n">
-        <v>20.23</v>
+        <v>17.64</v>
       </c>
       <c r="E14" t="n">
-        <v>11.1</v>
+        <v>12.3</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>55.26</v>
+        <v>71.42</v>
       </c>
       <c r="I14" t="n">
-        <v>56.46</v>
+        <v>71.8</v>
       </c>
       <c r="J14" t="n">
-        <v>54.02</v>
+        <v>71.13</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M14" t="n">
         <v>2</v>
       </c>
-      <c r="M14" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N14" t="n">
-        <v>6200</v>
+        <v>6162</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21.34</v>
+        <v>17.74</v>
       </c>
       <c r="C15" t="n">
-        <v>21.65</v>
+        <v>17.78</v>
       </c>
       <c r="D15" t="n">
-        <v>20.98</v>
+        <v>17.68</v>
       </c>
       <c r="E15" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="G15" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>52.89</v>
+        <v>71.53</v>
       </c>
       <c r="I15" t="n">
-        <v>53.97</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>51.51</v>
+        <v>70.67</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>6220</v>
+        <v>6152</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22.22</v>
+        <v>18.17</v>
       </c>
       <c r="C16" t="n">
-        <v>22.72</v>
+        <v>18.45</v>
       </c>
       <c r="D16" t="n">
-        <v>21.71</v>
+        <v>17.85</v>
       </c>
       <c r="E16" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="F16" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="G16" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>50.44</v>
+        <v>67.5</v>
       </c>
       <c r="I16" t="n">
-        <v>51.7</v>
+        <v>70.09</v>
       </c>
       <c r="J16" t="n">
-        <v>49.53</v>
+        <v>65.53</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>6240</v>
+        <v>6152</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22.94</v>
+        <v>19.12</v>
       </c>
       <c r="C17" t="n">
-        <v>23.82</v>
+        <v>19.48</v>
       </c>
       <c r="D17" t="n">
-        <v>22.29</v>
+        <v>18.59</v>
       </c>
       <c r="E17" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="F17" t="n">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="G17" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>46.37</v>
+        <v>62.25</v>
       </c>
       <c r="I17" t="n">
-        <v>49.68</v>
+        <v>64.8</v>
       </c>
       <c r="J17" t="n">
-        <v>44.22</v>
+        <v>60.27</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="N17" t="n">
-        <v>6250</v>
+        <v>6180</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23.12</v>
+        <v>19.89</v>
       </c>
       <c r="C18" t="n">
-        <v>24.14</v>
+        <v>20.2</v>
       </c>
       <c r="D18" t="n">
-        <v>22.72</v>
+        <v>19.54</v>
       </c>
       <c r="E18" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="F18" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="G18" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>45.59</v>
+        <v>58.12</v>
       </c>
       <c r="I18" t="n">
-        <v>46.9</v>
+        <v>59.88</v>
       </c>
       <c r="J18" t="n">
-        <v>43.18</v>
+        <v>56.65</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="N18" t="n">
-        <v>6240</v>
+        <v>6190</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.76</v>
+        <v>20.59</v>
       </c>
       <c r="C19" t="n">
-        <v>23.63</v>
+        <v>21.02</v>
       </c>
       <c r="D19" t="n">
-        <v>22.08</v>
+        <v>20.23</v>
       </c>
       <c r="E19" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>462</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>47.51</v>
+        <v>55.26</v>
       </c>
       <c r="I19" t="n">
-        <v>49.36</v>
+        <v>56.46</v>
       </c>
       <c r="J19" t="n">
-        <v>46.08</v>
+        <v>54.02</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="N19" t="n">
-        <v>6240</v>
+        <v>6200</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.55</v>
+        <v>21.34</v>
       </c>
       <c r="C20" t="n">
-        <v>23.29</v>
+        <v>21.65</v>
       </c>
       <c r="D20" t="n">
-        <v>21.68</v>
+        <v>20.98</v>
       </c>
       <c r="E20" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="F20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>364</v>
+        <v>63</v>
       </c>
       <c r="H20" t="n">
-        <v>47.88</v>
+        <v>52.89</v>
       </c>
       <c r="I20" t="n">
-        <v>50.32</v>
+        <v>53.97</v>
       </c>
       <c r="J20" t="n">
-        <v>46.13</v>
+        <v>51.51</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="N20" t="n">
         <v>6220</v>
@@ -1401,742 +1401,740 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.47</v>
+        <v>22.22</v>
       </c>
       <c r="C21" t="n">
-        <v>23.42</v>
+        <v>22.72</v>
       </c>
       <c r="D21" t="n">
-        <v>21.73</v>
+        <v>21.71</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="F21" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="G21" t="n">
-        <v>531</v>
+        <v>210</v>
       </c>
       <c r="H21" t="n">
-        <v>49.09</v>
+        <v>50.44</v>
       </c>
       <c r="I21" t="n">
-        <v>51.32</v>
+        <v>51.7</v>
       </c>
       <c r="J21" t="n">
-        <v>46.18</v>
+        <v>49.53</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
         <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>6230</v>
+        <v>6240</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21.72</v>
+        <v>22.94</v>
       </c>
       <c r="C22" t="n">
-        <v>23.46</v>
+        <v>23.82</v>
       </c>
       <c r="D22" t="n">
-        <v>20.79</v>
+        <v>22.29</v>
       </c>
       <c r="E22" t="n">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="G22" t="n">
-        <v>616</v>
+        <v>355</v>
       </c>
       <c r="H22" t="n">
-        <v>52.51</v>
+        <v>46.37</v>
       </c>
       <c r="I22" t="n">
-        <v>55.76</v>
+        <v>49.68</v>
       </c>
       <c r="J22" t="n">
-        <v>47.65</v>
+        <v>44.22</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>6220</v>
+        <v>6250</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20.86</v>
+        <v>23.12</v>
       </c>
       <c r="C23" t="n">
-        <v>21.56</v>
+        <v>24.14</v>
       </c>
       <c r="D23" t="n">
-        <v>20.25</v>
+        <v>22.72</v>
       </c>
       <c r="E23" t="n">
-        <v>11.7</v>
+        <v>10.5</v>
       </c>
       <c r="F23" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="G23" t="n">
-        <v>642</v>
+        <v>344</v>
       </c>
       <c r="H23" t="n">
-        <v>56.36</v>
+        <v>45.59</v>
       </c>
       <c r="I23" t="n">
-        <v>59</v>
+        <v>46.9</v>
       </c>
       <c r="J23" t="n">
-        <v>53.69</v>
+        <v>43.18</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>6190</v>
+        <v>6240</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.5</v>
+        <v>22.76</v>
       </c>
       <c r="C24" t="n">
-        <v>19.99</v>
+        <v>23.63</v>
       </c>
       <c r="D24" t="n">
-        <v>19.01</v>
+        <v>22.08</v>
       </c>
       <c r="E24" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
       </c>
       <c r="F24" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="G24" t="n">
-        <v>341</v>
+        <v>462</v>
       </c>
       <c r="H24" t="n">
-        <v>61.31</v>
+        <v>47.51</v>
       </c>
       <c r="I24" t="n">
-        <v>62.89</v>
+        <v>49.36</v>
       </c>
       <c r="J24" t="n">
-        <v>59.57</v>
+        <v>46.08</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6190</v>
+        <v>6240</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.96</v>
+        <v>22.55</v>
       </c>
       <c r="C25" t="n">
-        <v>18.97</v>
+        <v>23.29</v>
       </c>
       <c r="D25" t="n">
-        <v>17.06</v>
+        <v>21.68</v>
       </c>
       <c r="E25" t="n">
-        <v>12.1</v>
+        <v>10.7</v>
       </c>
       <c r="F25" t="n">
-        <v>11.8</v>
+        <v>10.5</v>
       </c>
       <c r="G25" t="n">
-        <v>158</v>
+        <v>364</v>
       </c>
       <c r="H25" t="n">
-        <v>69.53</v>
+        <v>47.88</v>
       </c>
       <c r="I25" t="n">
-        <v>74.66</v>
+        <v>50.32</v>
       </c>
       <c r="J25" t="n">
-        <v>64.09</v>
+        <v>46.13</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M25" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>6180</v>
+        <v>6220</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16.73</v>
+        <v>22.47</v>
       </c>
       <c r="C26" t="n">
-        <v>16.97</v>
+        <v>23.42</v>
       </c>
       <c r="D26" t="n">
-        <v>16.64</v>
+        <v>21.73</v>
       </c>
       <c r="E26" t="n">
-        <v>12.4</v>
+        <v>11</v>
       </c>
       <c r="F26" t="n">
-        <v>12.4</v>
+        <v>10.7</v>
       </c>
       <c r="G26" t="n">
-        <v>33</v>
+        <v>531</v>
       </c>
       <c r="H26" t="n">
-        <v>76.20999999999999</v>
+        <v>49.09</v>
       </c>
       <c r="I26" t="n">
-        <v>76.59999999999999</v>
+        <v>51.32</v>
       </c>
       <c r="J26" t="n">
-        <v>75.42</v>
+        <v>46.18</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>6162</v>
+        <v>6230</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.74</v>
+        <v>21.72</v>
       </c>
       <c r="C27" t="n">
-        <v>16.83</v>
+        <v>23.46</v>
       </c>
       <c r="D27" t="n">
-        <v>16.69</v>
+        <v>20.79</v>
       </c>
       <c r="E27" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
       <c r="F27" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="H27" t="n">
-        <v>76.59</v>
+        <v>52.51</v>
       </c>
       <c r="I27" t="n">
-        <v>77.48</v>
+        <v>55.76</v>
       </c>
       <c r="J27" t="n">
-        <v>75.81999999999999</v>
+        <v>47.65</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="M27" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>6152</v>
+        <v>6220</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16.74</v>
+        <v>20.86</v>
       </c>
       <c r="C28" t="n">
-        <v>16.81</v>
+        <v>21.56</v>
       </c>
       <c r="D28" t="n">
-        <v>16.65</v>
+        <v>20.25</v>
       </c>
       <c r="E28" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="F28" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="H28" t="n">
-        <v>77.14</v>
+        <v>56.36</v>
       </c>
       <c r="I28" t="n">
-        <v>77.55</v>
+        <v>59</v>
       </c>
       <c r="J28" t="n">
-        <v>76.81999999999999</v>
+        <v>53.69</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>16.83</v>
+        <v>19.5</v>
       </c>
       <c r="C29" t="n">
-        <v>16.93</v>
+        <v>19.99</v>
       </c>
       <c r="D29" t="n">
-        <v>16.77</v>
+        <v>19.01</v>
       </c>
       <c r="E29" t="n">
-        <v>12.8</v>
+        <v>11.7</v>
       </c>
       <c r="F29" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H29" t="n">
-        <v>77.89</v>
+        <v>61.31</v>
       </c>
       <c r="I29" t="n">
-        <v>78.14</v>
+        <v>62.89</v>
       </c>
       <c r="J29" t="n">
-        <v>77.23</v>
+        <v>59.57</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="M29" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>6142</v>
+        <v>6190</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.08</v>
+        <v>17.96</v>
       </c>
       <c r="C30" t="n">
-        <v>17.24</v>
+        <v>18.97</v>
       </c>
       <c r="D30" t="n">
-        <v>16.95</v>
+        <v>17.06</v>
       </c>
       <c r="E30" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="F30" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H30" t="n">
-        <v>77.45999999999999</v>
+        <v>69.53</v>
       </c>
       <c r="I30" t="n">
-        <v>78.15000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="J30" t="n">
-        <v>76.95</v>
+        <v>64.09</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="N30" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.17</v>
+        <v>16.73</v>
       </c>
       <c r="C31" t="n">
-        <v>17.3</v>
+        <v>16.97</v>
       </c>
       <c r="D31" t="n">
-        <v>16.93</v>
+        <v>16.64</v>
       </c>
       <c r="E31" t="n">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="F31" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H31" t="n">
-        <v>78.43000000000001</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>81.27</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>77.08</v>
+        <v>75.42</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M31" t="n">
         <v>1.4</v>
       </c>
-      <c r="M31" t="n">
-        <v>1.7</v>
-      </c>
       <c r="N31" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.59</v>
+        <v>16.74</v>
       </c>
       <c r="C32" t="n">
-        <v>17.86</v>
+        <v>16.83</v>
       </c>
       <c r="D32" t="n">
-        <v>17.28</v>
+        <v>16.69</v>
       </c>
       <c r="E32" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="F32" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>75</v>
+        <v>76.59</v>
       </c>
       <c r="I32" t="n">
-        <v>77.95</v>
+        <v>77.48</v>
       </c>
       <c r="J32" t="n">
-        <v>73.39</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="M32" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="N32" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>18.2</v>
+        <v>16.74</v>
       </c>
       <c r="C33" t="n">
-        <v>18.41</v>
+        <v>16.81</v>
       </c>
       <c r="D33" t="n">
-        <v>18</v>
+        <v>16.65</v>
       </c>
       <c r="E33" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="F33" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>69.83</v>
+        <v>77.14</v>
       </c>
       <c r="I33" t="n">
-        <v>72.37</v>
+        <v>77.55</v>
       </c>
       <c r="J33" t="n">
-        <v>68.34</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="M33" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="N33" t="n">
         <v>6162</v>
       </c>
-      <c r="O33" t="n">
-        <v>3.7</v>
-      </c>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18.56</v>
+        <v>16.83</v>
       </c>
       <c r="C34" t="n">
-        <v>18.7</v>
+        <v>16.93</v>
       </c>
       <c r="D34" t="n">
-        <v>18.41</v>
+        <v>16.77</v>
       </c>
       <c r="E34" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="F34" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>67.93000000000001</v>
+        <v>77.89</v>
       </c>
       <c r="I34" t="n">
-        <v>68.55</v>
+        <v>78.14</v>
       </c>
       <c r="J34" t="n">
-        <v>67.33</v>
+        <v>77.23</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="N34" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>18.92</v>
+        <v>17.08</v>
       </c>
       <c r="C35" t="n">
-        <v>19.04</v>
+        <v>17.24</v>
       </c>
       <c r="D35" t="n">
-        <v>18.74</v>
+        <v>16.95</v>
       </c>
       <c r="E35" t="n">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="F35" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>66</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>67.08</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>65.19</v>
+        <v>76.95</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="M35" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="N35" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>18.98</v>
+        <v>17.17</v>
       </c>
       <c r="C36" t="n">
-        <v>19.02</v>
+        <v>17.3</v>
       </c>
       <c r="D36" t="n">
-        <v>18.95</v>
+        <v>16.93</v>
       </c>
       <c r="E36" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F36" t="n">
-        <v>12.2</v>
+        <v>13.1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>65.26000000000001</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>65.51000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="J36" t="n">
-        <v>65.09999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2148,427 +2146,429 @@
         <v>1.7</v>
       </c>
       <c r="N36" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.27</v>
+        <v>17.59</v>
       </c>
       <c r="C37" t="n">
-        <v>19.65</v>
+        <v>17.86</v>
       </c>
       <c r="D37" t="n">
-        <v>19.01</v>
+        <v>17.28</v>
       </c>
       <c r="E37" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="F37" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>62.96</v>
+        <v>75</v>
       </c>
       <c r="I37" t="n">
-        <v>64.81</v>
+        <v>77.95</v>
       </c>
       <c r="J37" t="n">
-        <v>60.5</v>
+        <v>73.39</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="M37" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="N37" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-14 19:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>19.98</v>
+        <v>18.2</v>
       </c>
       <c r="C38" t="n">
-        <v>20.21</v>
+        <v>18.41</v>
       </c>
       <c r="D38" t="n">
-        <v>19.72</v>
+        <v>18</v>
       </c>
       <c r="E38" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="F38" t="n">
-        <v>11.3</v>
+        <v>12.2</v>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>58.7</v>
+        <v>69.83</v>
       </c>
       <c r="I38" t="n">
-        <v>59.99</v>
+        <v>72.37</v>
       </c>
       <c r="J38" t="n">
-        <v>57.42</v>
+        <v>68.34</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="N38" t="n">
-        <v>6180</v>
-      </c>
-      <c r="O38" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20.51</v>
+        <v>18.56</v>
       </c>
       <c r="C39" t="n">
-        <v>20.87</v>
+        <v>18.7</v>
       </c>
       <c r="D39" t="n">
-        <v>20.26</v>
+        <v>18.41</v>
       </c>
       <c r="E39" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="F39" t="n">
-        <v>11.2</v>
+        <v>12.4</v>
       </c>
       <c r="G39" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>56.48</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>57.91</v>
+        <v>68.55</v>
       </c>
       <c r="J39" t="n">
-        <v>55.61</v>
+        <v>67.33</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M39" t="n">
         <v>2.6</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.4</v>
-      </c>
       <c r="N39" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20.85</v>
+        <v>18.92</v>
       </c>
       <c r="C40" t="n">
-        <v>21.07</v>
+        <v>19.04</v>
       </c>
       <c r="D40" t="n">
-        <v>20.73</v>
+        <v>18.74</v>
       </c>
       <c r="E40" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="F40" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="G40" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>56.48</v>
+        <v>66</v>
       </c>
       <c r="I40" t="n">
-        <v>57.04</v>
+        <v>67.08</v>
       </c>
       <c r="J40" t="n">
-        <v>56</v>
+        <v>65.19</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="N40" t="n">
-        <v>6210</v>
+        <v>6170</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20.96</v>
+        <v>18.98</v>
       </c>
       <c r="C41" t="n">
-        <v>21.38</v>
+        <v>19.02</v>
       </c>
       <c r="D41" t="n">
-        <v>20.75</v>
+        <v>18.95</v>
       </c>
       <c r="E41" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="F41" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="G41" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>56.06</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>56.71</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>54.86</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="M41" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="N41" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>21.55</v>
+        <v>19.27</v>
       </c>
       <c r="C42" t="n">
-        <v>21.81</v>
+        <v>19.65</v>
       </c>
       <c r="D42" t="n">
-        <v>21.14</v>
+        <v>19.01</v>
       </c>
       <c r="E42" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="F42" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="G42" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>53.03</v>
+        <v>62.96</v>
       </c>
       <c r="I42" t="n">
-        <v>54.48</v>
+        <v>64.81</v>
       </c>
       <c r="J42" t="n">
-        <v>51.56</v>
+        <v>60.5</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="N42" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 14:00:00</t>
+          <t>2026-10-14 19:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>21.25</v>
+        <v>19.98</v>
       </c>
       <c r="C43" t="n">
-        <v>21.62</v>
+        <v>20.21</v>
       </c>
       <c r="D43" t="n">
-        <v>20.57</v>
+        <v>19.72</v>
       </c>
       <c r="E43" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="F43" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="G43" t="n">
-        <v>285</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
-        <v>55.82</v>
+        <v>58.7</v>
       </c>
       <c r="I43" t="n">
-        <v>57.91</v>
+        <v>59.99</v>
       </c>
       <c r="J43" t="n">
-        <v>54.45</v>
+        <v>57.42</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="N43" t="n">
-        <v>6230</v>
+        <v>6180</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 13:00:00</t>
+          <t>2026-10-14 18:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20.17</v>
+        <v>20.51</v>
       </c>
       <c r="C44" t="n">
-        <v>22.05</v>
+        <v>20.87</v>
       </c>
       <c r="D44" t="n">
-        <v>19.15</v>
+        <v>20.26</v>
       </c>
       <c r="E44" t="n">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
       <c r="F44" t="n">
-        <v>11.9</v>
+        <v>11.2</v>
       </c>
       <c r="G44" t="n">
-        <v>426</v>
+        <v>47</v>
       </c>
       <c r="H44" t="n">
-        <v>60.86</v>
+        <v>56.48</v>
       </c>
       <c r="I44" t="n">
-        <v>65.42</v>
+        <v>57.91</v>
       </c>
       <c r="J44" t="n">
-        <v>53.21</v>
+        <v>55.61</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>6250</v>
+        <v>6190</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00:00</t>
+          <t>2026-10-14 17:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.06</v>
+        <v>20.85</v>
       </c>
       <c r="C45" t="n">
-        <v>20.31</v>
+        <v>21.07</v>
       </c>
       <c r="D45" t="n">
-        <v>18.02</v>
+        <v>20.73</v>
       </c>
       <c r="E45" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="F45" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="G45" t="n">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="H45" t="n">
-        <v>67.37</v>
+        <v>56.48</v>
       </c>
       <c r="I45" t="n">
-        <v>72.42</v>
+        <v>57.04</v>
       </c>
       <c r="J45" t="n">
-        <v>61.34</v>
+        <v>56</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="M45" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
         <v>6210</v>
@@ -2578,235 +2578,235 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00:00</t>
+          <t>2026-10-14 16:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.91</v>
+        <v>20.96</v>
       </c>
       <c r="C46" t="n">
-        <v>18.13</v>
+        <v>21.38</v>
       </c>
       <c r="D46" t="n">
-        <v>17.79</v>
+        <v>20.75</v>
       </c>
       <c r="E46" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="F46" t="n">
-        <v>12.6</v>
+        <v>11.4</v>
       </c>
       <c r="G46" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="H46" t="n">
-        <v>72.75</v>
+        <v>56.06</v>
       </c>
       <c r="I46" t="n">
-        <v>73.73999999999999</v>
+        <v>56.71</v>
       </c>
       <c r="J46" t="n">
-        <v>71.81</v>
+        <v>54.86</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="M46" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N46" t="n">
-        <v>6200</v>
+        <v>6220</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 10:00:00</t>
+          <t>2026-10-14 15:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.23</v>
+        <v>21.55</v>
       </c>
       <c r="C47" t="n">
-        <v>17.93</v>
+        <v>21.81</v>
       </c>
       <c r="D47" t="n">
-        <v>16.74</v>
+        <v>21.14</v>
       </c>
       <c r="E47" t="n">
-        <v>13</v>
+        <v>11.3</v>
       </c>
       <c r="F47" t="n">
-        <v>12.8</v>
+        <v>11.1</v>
       </c>
       <c r="G47" t="n">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="H47" t="n">
-        <v>76.95999999999999</v>
+        <v>53.03</v>
       </c>
       <c r="I47" t="n">
-        <v>79.36</v>
+        <v>54.48</v>
       </c>
       <c r="J47" t="n">
-        <v>73.15000000000001</v>
+        <v>51.56</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="M47" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>6200</v>
+        <v>6220</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 09:00:00</t>
+          <t>2026-10-14 14:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.12</v>
+        <v>21.25</v>
       </c>
       <c r="C48" t="n">
-        <v>17.33</v>
+        <v>21.62</v>
       </c>
       <c r="D48" t="n">
-        <v>16.81</v>
+        <v>20.57</v>
       </c>
       <c r="E48" t="n">
-        <v>13.1</v>
+        <v>11.9</v>
       </c>
       <c r="F48" t="n">
-        <v>12.8</v>
+        <v>11.7</v>
       </c>
       <c r="G48" t="n">
-        <v>132</v>
+        <v>285</v>
       </c>
       <c r="H48" t="n">
-        <v>78.23999999999999</v>
+        <v>55.82</v>
       </c>
       <c r="I48" t="n">
-        <v>80.20999999999999</v>
+        <v>57.91</v>
       </c>
       <c r="J48" t="n">
-        <v>76.95999999999999</v>
+        <v>54.45</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N48" t="n">
-        <v>6180</v>
+        <v>6230</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 08:00:00</t>
+          <t>2026-10-14 13:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16.38</v>
+        <v>20.17</v>
       </c>
       <c r="C49" t="n">
-        <v>17.11</v>
+        <v>22.05</v>
       </c>
       <c r="D49" t="n">
-        <v>15.9</v>
+        <v>19.15</v>
       </c>
       <c r="E49" t="n">
-        <v>13.4</v>
+        <v>12.2</v>
       </c>
       <c r="F49" t="n">
-        <v>13.2</v>
+        <v>11.9</v>
       </c>
       <c r="G49" t="n">
-        <v>107</v>
+        <v>426</v>
       </c>
       <c r="H49" t="n">
-        <v>83.54000000000001</v>
+        <v>60.86</v>
       </c>
       <c r="I49" t="n">
-        <v>87.8</v>
+        <v>65.42</v>
       </c>
       <c r="J49" t="n">
-        <v>79.43000000000001</v>
+        <v>53.21</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M49" t="n">
         <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>6180</v>
+        <v>6250</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14 07:00:00</t>
+          <t>2026-10-14 12:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>15.72</v>
+        <v>19.06</v>
       </c>
       <c r="C50" t="n">
-        <v>15.84</v>
+        <v>20.31</v>
       </c>
       <c r="D50" t="n">
-        <v>15.66</v>
+        <v>18.02</v>
       </c>
       <c r="E50" t="n">
-        <v>13.9</v>
+        <v>12.6</v>
       </c>
       <c r="F50" t="n">
-        <v>13.7</v>
+        <v>11.9</v>
       </c>
       <c r="G50" t="n">
-        <v>15</v>
+        <v>257</v>
       </c>
       <c r="H50" t="n">
-        <v>89.95999999999999</v>
+        <v>67.37</v>
       </c>
       <c r="I50" t="n">
-        <v>91.70999999999999</v>
+        <v>72.42</v>
       </c>
       <c r="J50" t="n">
-        <v>88.26000000000001</v>
+        <v>61.34</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="N50" t="n">
-        <v>6170</v>
+        <v>6210</v>
       </c>
       <c r="O50" t="n">
         <v>2.5</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,364 +508,364 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.99</v>
+        <v>21.72</v>
       </c>
       <c r="C2" t="n">
-        <v>22.22</v>
+        <v>21.84</v>
       </c>
       <c r="D2" t="n">
         <v>21.61</v>
       </c>
       <c r="E2" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="F2" t="n">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
       <c r="G2" t="n">
-        <v>525</v>
+        <v>204</v>
       </c>
       <c r="H2" t="n">
-        <v>53.11</v>
+        <v>52.83</v>
       </c>
       <c r="I2" t="n">
-        <v>54.1</v>
+        <v>53.09</v>
       </c>
       <c r="J2" t="n">
-        <v>52.16</v>
+        <v>52.51</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.1</v>
+        <v>21.42</v>
       </c>
       <c r="C3" t="n">
-        <v>21.69</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>20.51</v>
+        <v>20.92</v>
       </c>
       <c r="E3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F3" t="n">
         <v>11.5</v>
       </c>
       <c r="G3" t="n">
-        <v>480</v>
+        <v>218</v>
       </c>
       <c r="H3" t="n">
-        <v>55.96</v>
+        <v>54.49</v>
       </c>
       <c r="I3" t="n">
-        <v>58.01</v>
+        <v>56.38</v>
       </c>
       <c r="J3" t="n">
-        <v>53.81</v>
+        <v>52.2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.15</v>
+        <v>21.35</v>
       </c>
       <c r="C4" t="n">
-        <v>20.85</v>
+        <v>22.22</v>
       </c>
       <c r="D4" t="n">
-        <v>19.57</v>
+        <v>20.87</v>
       </c>
       <c r="E4" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="F4" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G4" t="n">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="H4" t="n">
-        <v>60.77</v>
+        <v>55.07</v>
       </c>
       <c r="I4" t="n">
-        <v>64.81</v>
+        <v>56.71</v>
       </c>
       <c r="J4" t="n">
-        <v>56.73</v>
+        <v>52.16</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="N4" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.37</v>
+        <v>21.1</v>
       </c>
       <c r="C5" t="n">
-        <v>19.79</v>
+        <v>21.69</v>
       </c>
       <c r="D5" t="n">
-        <v>18.91</v>
+        <v>20.51</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F5" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G5" t="n">
-        <v>174</v>
+        <v>480</v>
       </c>
       <c r="H5" t="n">
-        <v>65.04000000000001</v>
+        <v>55.96</v>
       </c>
       <c r="I5" t="n">
-        <v>66.98999999999999</v>
+        <v>58.01</v>
       </c>
       <c r="J5" t="n">
-        <v>63.19</v>
+        <v>53.81</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>6180</v>
+        <v>6210</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.41</v>
+        <v>20.15</v>
       </c>
       <c r="C6" t="n">
-        <v>18.85</v>
+        <v>20.85</v>
       </c>
       <c r="D6" t="n">
-        <v>18.05</v>
+        <v>19.57</v>
       </c>
       <c r="E6" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="F6" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="G6" t="n">
-        <v>76</v>
+        <v>266</v>
       </c>
       <c r="H6" t="n">
-        <v>69.37</v>
+        <v>60.77</v>
       </c>
       <c r="I6" t="n">
-        <v>71.67</v>
+        <v>64.81</v>
       </c>
       <c r="J6" t="n">
-        <v>67.22</v>
+        <v>56.73</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
         <v>2.3</v>
       </c>
       <c r="N6" t="n">
-        <v>6170</v>
+        <v>6200</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.66</v>
+        <v>19.37</v>
       </c>
       <c r="C7" t="n">
-        <v>17.95</v>
+        <v>19.79</v>
       </c>
       <c r="D7" t="n">
-        <v>17.51</v>
+        <v>18.91</v>
       </c>
       <c r="E7" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="F7" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="H7" t="n">
-        <v>73.31</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>74.14</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>72.19</v>
+        <v>63.19</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="N7" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.6</v>
+        <v>18.41</v>
       </c>
       <c r="C8" t="n">
-        <v>17.68</v>
+        <v>18.85</v>
       </c>
       <c r="D8" t="n">
-        <v>17.49</v>
+        <v>18.05</v>
       </c>
       <c r="E8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F8" t="n">
         <v>12.4</v>
       </c>
-      <c r="F8" t="n">
-        <v>12.3</v>
-      </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>72.5</v>
+        <v>69.37</v>
       </c>
       <c r="I8" t="n">
-        <v>73.76000000000001</v>
+        <v>71.67</v>
       </c>
       <c r="J8" t="n">
-        <v>71.78</v>
+        <v>67.22</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="N8" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.53</v>
+        <v>17.66</v>
       </c>
       <c r="C9" t="n">
-        <v>17.62</v>
+        <v>17.95</v>
       </c>
       <c r="D9" t="n">
-        <v>17.45</v>
+        <v>17.51</v>
       </c>
       <c r="E9" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="F9" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>72.33</v>
+        <v>73.31</v>
       </c>
       <c r="I9" t="n">
-        <v>72.88</v>
+        <v>74.14</v>
       </c>
       <c r="J9" t="n">
-        <v>71.93000000000001</v>
+        <v>72.19</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -874,124 +874,124 @@
         <v>0.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N9" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.64</v>
+        <v>17.6</v>
       </c>
       <c r="C10" t="n">
-        <v>17.9</v>
+        <v>17.68</v>
       </c>
       <c r="D10" t="n">
-        <v>17.44</v>
+        <v>17.49</v>
       </c>
       <c r="E10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F10" t="n">
         <v>12.3</v>
       </c>
-      <c r="F10" t="n">
-        <v>12</v>
-      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>71.73999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I10" t="n">
-        <v>73.59999999999999</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>69.53</v>
+        <v>71.78</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="N10" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.84</v>
+        <v>17.53</v>
       </c>
       <c r="C11" t="n">
-        <v>17.88</v>
+        <v>17.62</v>
       </c>
       <c r="D11" t="n">
-        <v>17.8</v>
+        <v>17.45</v>
       </c>
       <c r="E11" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F11" t="n">
         <v>12.2</v>
       </c>
-      <c r="F11" t="n">
-        <v>12</v>
-      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>70.06999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="I11" t="n">
-        <v>70.3</v>
+        <v>72.88</v>
       </c>
       <c r="J11" t="n">
-        <v>69.65000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M11" t="n">
         <v>0.8</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.3</v>
-      </c>
       <c r="N11" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="C12" t="n">
         <v>17.9</v>
       </c>
-      <c r="C12" t="n">
-        <v>17.97</v>
-      </c>
       <c r="D12" t="n">
-        <v>17.82</v>
+        <v>17.44</v>
       </c>
       <c r="E12" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="F12" t="n">
         <v>12</v>
@@ -1000,69 +1000,69 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>69.79000000000001</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>70.48999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>69.43000000000001</v>
+        <v>69.53</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="N12" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.74</v>
+        <v>17.84</v>
       </c>
       <c r="C13" t="n">
-        <v>17.82</v>
+        <v>17.88</v>
       </c>
       <c r="D13" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="E13" t="n">
         <v>12.2</v>
       </c>
       <c r="F13" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>70.81999999999999</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>70.98</v>
+        <v>70.3</v>
       </c>
       <c r="J13" t="n">
-        <v>70.54000000000001</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N13" t="n">
         <v>6162</v>
@@ -1072,44 +1072,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.68</v>
+        <v>17.9</v>
       </c>
       <c r="C14" t="n">
-        <v>17.71</v>
+        <v>17.97</v>
       </c>
       <c r="D14" t="n">
-        <v>17.64</v>
+        <v>17.82</v>
       </c>
       <c r="E14" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="F14" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>71.42</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>71.8</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>71.13</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2</v>
       </c>
       <c r="N14" t="n">
         <v>6162</v>
@@ -1119,20 +1119,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>17.74</v>
       </c>
       <c r="C15" t="n">
-        <v>17.78</v>
+        <v>17.82</v>
       </c>
       <c r="D15" t="n">
-        <v>17.68</v>
+        <v>17.7</v>
       </c>
       <c r="E15" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="F15" t="n">
         <v>12.2</v>
@@ -1141,60 +1141,60 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>71.53</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>72.06999999999999</v>
+        <v>70.98</v>
       </c>
       <c r="J15" t="n">
-        <v>70.67</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N15" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18.17</v>
+        <v>17.68</v>
       </c>
       <c r="C16" t="n">
-        <v>18.45</v>
+        <v>17.71</v>
       </c>
       <c r="D16" t="n">
-        <v>17.85</v>
+        <v>17.64</v>
       </c>
       <c r="E16" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="F16" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>67.5</v>
+        <v>71.42</v>
       </c>
       <c r="I16" t="n">
-        <v>70.09</v>
+        <v>71.8</v>
       </c>
       <c r="J16" t="n">
-        <v>65.53</v>
+        <v>71.13</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1206,333 +1206,333 @@
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.12</v>
+        <v>17.74</v>
       </c>
       <c r="C17" t="n">
-        <v>19.48</v>
+        <v>17.78</v>
       </c>
       <c r="D17" t="n">
-        <v>18.59</v>
+        <v>17.68</v>
       </c>
       <c r="E17" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="F17" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>62.25</v>
+        <v>71.53</v>
       </c>
       <c r="I17" t="n">
-        <v>64.8</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>60.27</v>
+        <v>70.67</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>6180</v>
+        <v>6152</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19.89</v>
+        <v>18.17</v>
       </c>
       <c r="C18" t="n">
-        <v>20.2</v>
+        <v>18.45</v>
       </c>
       <c r="D18" t="n">
-        <v>19.54</v>
+        <v>17.85</v>
       </c>
       <c r="E18" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="F18" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>58.12</v>
+        <v>67.5</v>
       </c>
       <c r="I18" t="n">
-        <v>59.88</v>
+        <v>70.09</v>
       </c>
       <c r="J18" t="n">
-        <v>56.65</v>
+        <v>65.53</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20.59</v>
+        <v>19.12</v>
       </c>
       <c r="C19" t="n">
-        <v>21.02</v>
+        <v>19.48</v>
       </c>
       <c r="D19" t="n">
-        <v>20.23</v>
+        <v>18.59</v>
       </c>
       <c r="E19" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>55.26</v>
+        <v>62.25</v>
       </c>
       <c r="I19" t="n">
-        <v>56.46</v>
+        <v>64.8</v>
       </c>
       <c r="J19" t="n">
-        <v>54.02</v>
+        <v>60.27</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="N19" t="n">
-        <v>6200</v>
+        <v>6180</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.34</v>
+        <v>19.89</v>
       </c>
       <c r="C20" t="n">
-        <v>21.65</v>
+        <v>20.2</v>
       </c>
       <c r="D20" t="n">
-        <v>20.98</v>
+        <v>19.54</v>
       </c>
       <c r="E20" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F20" t="n">
         <v>11.1</v>
       </c>
-      <c r="F20" t="n">
-        <v>11</v>
-      </c>
       <c r="G20" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>52.89</v>
+        <v>58.12</v>
       </c>
       <c r="I20" t="n">
-        <v>53.97</v>
+        <v>59.88</v>
       </c>
       <c r="J20" t="n">
-        <v>51.51</v>
+        <v>56.65</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="N20" t="n">
-        <v>6220</v>
+        <v>6190</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.22</v>
+        <v>20.59</v>
       </c>
       <c r="C21" t="n">
-        <v>22.72</v>
+        <v>21.02</v>
       </c>
       <c r="D21" t="n">
-        <v>21.71</v>
+        <v>20.23</v>
       </c>
       <c r="E21" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="F21" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>210</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>50.44</v>
+        <v>55.26</v>
       </c>
       <c r="I21" t="n">
-        <v>51.7</v>
+        <v>56.46</v>
       </c>
       <c r="J21" t="n">
-        <v>49.53</v>
+        <v>54.02</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N21" t="n">
-        <v>6240</v>
+        <v>6200</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.94</v>
+        <v>21.34</v>
       </c>
       <c r="C22" t="n">
-        <v>23.82</v>
+        <v>21.65</v>
       </c>
       <c r="D22" t="n">
-        <v>22.29</v>
+        <v>20.98</v>
       </c>
       <c r="E22" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="F22" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>355</v>
+        <v>63</v>
       </c>
       <c r="H22" t="n">
-        <v>46.37</v>
+        <v>52.89</v>
       </c>
       <c r="I22" t="n">
-        <v>49.68</v>
+        <v>53.97</v>
       </c>
       <c r="J22" t="n">
-        <v>44.22</v>
+        <v>51.51</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M22" t="n">
         <v>2.7</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.8</v>
-      </c>
       <c r="N22" t="n">
-        <v>6250</v>
+        <v>6220</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.12</v>
+        <v>22.22</v>
       </c>
       <c r="C23" t="n">
-        <v>24.14</v>
+        <v>22.72</v>
       </c>
       <c r="D23" t="n">
-        <v>22.72</v>
+        <v>21.71</v>
       </c>
       <c r="E23" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="F23" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="G23" t="n">
-        <v>344</v>
+        <v>210</v>
       </c>
       <c r="H23" t="n">
-        <v>45.59</v>
+        <v>50.44</v>
       </c>
       <c r="I23" t="n">
-        <v>46.9</v>
+        <v>51.7</v>
       </c>
       <c r="J23" t="n">
-        <v>43.18</v>
+        <v>49.53</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
         <v>6240</v>
@@ -1542,182 +1542,182 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22.76</v>
+        <v>22.94</v>
       </c>
       <c r="C24" t="n">
-        <v>23.63</v>
+        <v>23.82</v>
       </c>
       <c r="D24" t="n">
-        <v>22.08</v>
+        <v>22.29</v>
       </c>
       <c r="E24" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="F24" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="G24" t="n">
-        <v>462</v>
+        <v>355</v>
       </c>
       <c r="H24" t="n">
-        <v>47.51</v>
+        <v>46.37</v>
       </c>
       <c r="I24" t="n">
-        <v>49.36</v>
+        <v>49.68</v>
       </c>
       <c r="J24" t="n">
-        <v>46.08</v>
+        <v>44.22</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>6240</v>
+        <v>6250</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.55</v>
+        <v>23.12</v>
       </c>
       <c r="C25" t="n">
-        <v>23.29</v>
+        <v>24.14</v>
       </c>
       <c r="D25" t="n">
-        <v>21.68</v>
+        <v>22.72</v>
       </c>
       <c r="E25" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="F25" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="G25" t="n">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="H25" t="n">
-        <v>47.88</v>
+        <v>45.59</v>
       </c>
       <c r="I25" t="n">
-        <v>50.32</v>
+        <v>46.9</v>
       </c>
       <c r="J25" t="n">
-        <v>46.13</v>
+        <v>43.18</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>6220</v>
+        <v>6240</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22.47</v>
+        <v>22.76</v>
       </c>
       <c r="C26" t="n">
-        <v>23.42</v>
+        <v>23.63</v>
       </c>
       <c r="D26" t="n">
-        <v>21.73</v>
+        <v>22.08</v>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="F26" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="G26" t="n">
-        <v>531</v>
+        <v>462</v>
       </c>
       <c r="H26" t="n">
-        <v>49.09</v>
+        <v>47.51</v>
       </c>
       <c r="I26" t="n">
-        <v>51.32</v>
+        <v>49.36</v>
       </c>
       <c r="J26" t="n">
-        <v>46.18</v>
+        <v>46.08</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>6230</v>
+        <v>6240</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.72</v>
+        <v>22.55</v>
       </c>
       <c r="C27" t="n">
-        <v>23.46</v>
+        <v>23.29</v>
       </c>
       <c r="D27" t="n">
-        <v>20.79</v>
+        <v>21.68</v>
       </c>
       <c r="E27" t="n">
-        <v>11.3</v>
+        <v>10.7</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G27" t="n">
-        <v>616</v>
+        <v>364</v>
       </c>
       <c r="H27" t="n">
-        <v>52.51</v>
+        <v>47.88</v>
       </c>
       <c r="I27" t="n">
-        <v>55.76</v>
+        <v>50.32</v>
       </c>
       <c r="J27" t="n">
-        <v>47.65</v>
+        <v>46.13</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
         <v>3.5</v>
@@ -1730,276 +1730,276 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20.86</v>
+        <v>22.47</v>
       </c>
       <c r="C28" t="n">
-        <v>21.56</v>
+        <v>23.42</v>
       </c>
       <c r="D28" t="n">
-        <v>20.25</v>
+        <v>21.73</v>
       </c>
       <c r="E28" t="n">
-        <v>11.7</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>11.5</v>
+        <v>10.7</v>
       </c>
       <c r="G28" t="n">
-        <v>642</v>
+        <v>531</v>
       </c>
       <c r="H28" t="n">
-        <v>56.36</v>
+        <v>49.09</v>
       </c>
       <c r="I28" t="n">
-        <v>59</v>
+        <v>51.32</v>
       </c>
       <c r="J28" t="n">
-        <v>53.69</v>
+        <v>46.18</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>6190</v>
+        <v>6230</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.5</v>
+        <v>21.72</v>
       </c>
       <c r="C29" t="n">
-        <v>19.99</v>
+        <v>23.46</v>
       </c>
       <c r="D29" t="n">
-        <v>19.01</v>
+        <v>20.79</v>
       </c>
       <c r="E29" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="F29" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>341</v>
+        <v>616</v>
       </c>
       <c r="H29" t="n">
-        <v>61.31</v>
+        <v>52.51</v>
       </c>
       <c r="I29" t="n">
-        <v>62.89</v>
+        <v>55.76</v>
       </c>
       <c r="J29" t="n">
-        <v>59.57</v>
+        <v>47.65</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.96</v>
+        <v>20.86</v>
       </c>
       <c r="C30" t="n">
-        <v>18.97</v>
+        <v>21.56</v>
       </c>
       <c r="D30" t="n">
-        <v>17.06</v>
+        <v>20.25</v>
       </c>
       <c r="E30" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="F30" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="G30" t="n">
-        <v>158</v>
+        <v>642</v>
       </c>
       <c r="H30" t="n">
-        <v>69.53</v>
+        <v>56.36</v>
       </c>
       <c r="I30" t="n">
-        <v>74.66</v>
+        <v>59</v>
       </c>
       <c r="J30" t="n">
-        <v>64.09</v>
+        <v>53.69</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M30" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16.73</v>
+        <v>19.5</v>
       </c>
       <c r="C31" t="n">
-        <v>16.97</v>
+        <v>19.99</v>
       </c>
       <c r="D31" t="n">
-        <v>16.64</v>
+        <v>19.01</v>
       </c>
       <c r="E31" t="n">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="F31" t="n">
-        <v>12.4</v>
+        <v>11.4</v>
       </c>
       <c r="G31" t="n">
-        <v>33</v>
+        <v>341</v>
       </c>
       <c r="H31" t="n">
-        <v>76.20999999999999</v>
+        <v>61.31</v>
       </c>
       <c r="I31" t="n">
-        <v>76.59999999999999</v>
+        <v>62.89</v>
       </c>
       <c r="J31" t="n">
-        <v>75.42</v>
+        <v>59.57</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.74</v>
+        <v>17.96</v>
       </c>
       <c r="C32" t="n">
-        <v>16.83</v>
+        <v>18.97</v>
       </c>
       <c r="D32" t="n">
-        <v>16.69</v>
+        <v>17.06</v>
       </c>
       <c r="E32" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F32" t="n">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H32" t="n">
-        <v>76.59</v>
+        <v>69.53</v>
       </c>
       <c r="I32" t="n">
-        <v>77.48</v>
+        <v>74.66</v>
       </c>
       <c r="J32" t="n">
-        <v>75.81999999999999</v>
+        <v>64.09</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="N32" t="n">
-        <v>6152</v>
+        <v>6180</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.74</v>
+        <v>16.73</v>
       </c>
       <c r="C33" t="n">
-        <v>16.81</v>
+        <v>16.97</v>
       </c>
       <c r="D33" t="n">
-        <v>16.65</v>
+        <v>16.64</v>
       </c>
       <c r="E33" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="F33" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H33" t="n">
-        <v>77.14</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>77.55</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>76.81999999999999</v>
+        <v>75.42</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="M33" t="n">
         <v>1.4</v>
@@ -2012,158 +2012,158 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="C34" t="n">
         <v>16.83</v>
       </c>
-      <c r="C34" t="n">
-        <v>16.93</v>
-      </c>
       <c r="D34" t="n">
-        <v>16.77</v>
+        <v>16.69</v>
       </c>
       <c r="E34" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="F34" t="n">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>77.89</v>
+        <v>76.59</v>
       </c>
       <c r="I34" t="n">
-        <v>78.14</v>
+        <v>77.48</v>
       </c>
       <c r="J34" t="n">
-        <v>77.23</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M34" t="n">
         <v>1.5</v>
       </c>
-      <c r="M34" t="n">
-        <v>1.8</v>
-      </c>
       <c r="N34" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.08</v>
+        <v>16.74</v>
       </c>
       <c r="C35" t="n">
-        <v>17.24</v>
+        <v>16.81</v>
       </c>
       <c r="D35" t="n">
-        <v>16.95</v>
+        <v>16.65</v>
       </c>
       <c r="E35" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="F35" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>77.45999999999999</v>
+        <v>77.14</v>
       </c>
       <c r="I35" t="n">
-        <v>78.15000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J35" t="n">
-        <v>76.95</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M35" t="n">
         <v>1.4</v>
       </c>
-      <c r="M35" t="n">
-        <v>1.7</v>
-      </c>
       <c r="N35" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.17</v>
+        <v>16.83</v>
       </c>
       <c r="C36" t="n">
-        <v>17.3</v>
+        <v>16.93</v>
       </c>
       <c r="D36" t="n">
-        <v>16.93</v>
+        <v>16.77</v>
       </c>
       <c r="E36" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="F36" t="n">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>78.43000000000001</v>
+        <v>77.89</v>
       </c>
       <c r="I36" t="n">
-        <v>81.27</v>
+        <v>78.14</v>
       </c>
       <c r="J36" t="n">
-        <v>77.08</v>
+        <v>77.23</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M36" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N36" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.59</v>
+        <v>17.08</v>
       </c>
       <c r="C37" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="D37" t="n">
-        <v>17.28</v>
+        <v>16.95</v>
       </c>
       <c r="E37" t="n">
         <v>12.9</v>
@@ -2175,115 +2175,113 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>75</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>77.95</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>73.39</v>
+        <v>76.95</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="M37" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="N37" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18.2</v>
+        <v>17.17</v>
       </c>
       <c r="C38" t="n">
-        <v>18.41</v>
+        <v>17.3</v>
       </c>
       <c r="D38" t="n">
-        <v>18</v>
+        <v>16.93</v>
       </c>
       <c r="E38" t="n">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="F38" t="n">
-        <v>12.2</v>
+        <v>13.1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>69.83</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>72.37</v>
+        <v>81.27</v>
       </c>
       <c r="J38" t="n">
-        <v>68.34</v>
+        <v>77.08</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M38" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="N38" t="n">
-        <v>6162</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3.7</v>
-      </c>
+        <v>6152</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>18.56</v>
+        <v>17.59</v>
       </c>
       <c r="C39" t="n">
-        <v>18.7</v>
+        <v>17.86</v>
       </c>
       <c r="D39" t="n">
-        <v>18.41</v>
+        <v>17.28</v>
       </c>
       <c r="E39" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="F39" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>67.93000000000001</v>
+        <v>75</v>
       </c>
       <c r="I39" t="n">
-        <v>68.55</v>
+        <v>77.95</v>
       </c>
       <c r="J39" t="n">
-        <v>67.33</v>
+        <v>73.39</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M39" t="n">
         <v>2.6</v>
@@ -2296,20 +2294,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>18.92</v>
+        <v>18.2</v>
       </c>
       <c r="C40" t="n">
-        <v>19.04</v>
+        <v>18.41</v>
       </c>
       <c r="D40" t="n">
-        <v>18.74</v>
+        <v>18</v>
       </c>
       <c r="E40" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F40" t="n">
         <v>12.2</v>
@@ -2318,116 +2316,118 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>66</v>
+        <v>69.83</v>
       </c>
       <c r="I40" t="n">
-        <v>67.08</v>
+        <v>72.37</v>
       </c>
       <c r="J40" t="n">
-        <v>65.19</v>
+        <v>68.34</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="N40" t="n">
-        <v>6170</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>18.98</v>
+        <v>18.56</v>
       </c>
       <c r="C41" t="n">
-        <v>19.02</v>
+        <v>18.7</v>
       </c>
       <c r="D41" t="n">
-        <v>18.95</v>
+        <v>18.41</v>
       </c>
       <c r="E41" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F41" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>65.26000000000001</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>65.51000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="J41" t="n">
-        <v>65.09999999999999</v>
+        <v>67.33</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="M41" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="N41" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19.27</v>
+        <v>18.92</v>
       </c>
       <c r="C42" t="n">
-        <v>19.65</v>
+        <v>19.04</v>
       </c>
       <c r="D42" t="n">
-        <v>19.01</v>
+        <v>18.74</v>
       </c>
       <c r="E42" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="F42" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>62.96</v>
+        <v>66</v>
       </c>
       <c r="I42" t="n">
-        <v>64.81</v>
+        <v>67.08</v>
       </c>
       <c r="J42" t="n">
-        <v>60.5</v>
+        <v>65.19</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="M42" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="N42" t="n">
         <v>6170</v>
@@ -2437,376 +2437,376 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 19:00:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.98</v>
+        <v>18.98</v>
       </c>
       <c r="C43" t="n">
-        <v>20.21</v>
+        <v>19.02</v>
       </c>
       <c r="D43" t="n">
-        <v>19.72</v>
+        <v>18.95</v>
       </c>
       <c r="E43" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="F43" t="n">
-        <v>11.3</v>
+        <v>12.2</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>58.7</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>59.99</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>57.42</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="M43" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="N43" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20.51</v>
+        <v>19.27</v>
       </c>
       <c r="C44" t="n">
-        <v>20.87</v>
+        <v>19.65</v>
       </c>
       <c r="D44" t="n">
-        <v>20.26</v>
+        <v>19.01</v>
       </c>
       <c r="E44" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="F44" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="G44" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>56.48</v>
+        <v>62.96</v>
       </c>
       <c r="I44" t="n">
-        <v>57.91</v>
+        <v>64.81</v>
       </c>
       <c r="J44" t="n">
-        <v>55.61</v>
+        <v>60.5</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="N44" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-14 19:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>20.85</v>
+        <v>19.98</v>
       </c>
       <c r="C45" t="n">
-        <v>21.07</v>
+        <v>20.21</v>
       </c>
       <c r="D45" t="n">
-        <v>20.73</v>
+        <v>19.72</v>
       </c>
       <c r="E45" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="F45" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="G45" t="n">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>56.48</v>
+        <v>58.7</v>
       </c>
       <c r="I45" t="n">
-        <v>57.04</v>
+        <v>59.99</v>
       </c>
       <c r="J45" t="n">
-        <v>56</v>
+        <v>57.42</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="N45" t="n">
-        <v>6210</v>
+        <v>6180</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-14 18:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20.96</v>
+        <v>20.51</v>
       </c>
       <c r="C46" t="n">
-        <v>21.38</v>
+        <v>20.87</v>
       </c>
       <c r="D46" t="n">
-        <v>20.75</v>
+        <v>20.26</v>
       </c>
       <c r="E46" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="F46" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G46" t="n">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="H46" t="n">
-        <v>56.06</v>
+        <v>56.48</v>
       </c>
       <c r="I46" t="n">
-        <v>56.71</v>
+        <v>57.91</v>
       </c>
       <c r="J46" t="n">
-        <v>54.86</v>
+        <v>55.61</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="M46" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>6220</v>
+        <v>6190</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00:00</t>
+          <t>2026-10-14 17:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21.55</v>
+        <v>20.85</v>
       </c>
       <c r="C47" t="n">
-        <v>21.81</v>
+        <v>21.07</v>
       </c>
       <c r="D47" t="n">
-        <v>21.14</v>
+        <v>20.73</v>
       </c>
       <c r="E47" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="F47" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="G47" t="n">
-        <v>296</v>
+        <v>112</v>
       </c>
       <c r="H47" t="n">
-        <v>53.03</v>
+        <v>56.48</v>
       </c>
       <c r="I47" t="n">
-        <v>54.48</v>
+        <v>57.04</v>
       </c>
       <c r="J47" t="n">
-        <v>51.56</v>
+        <v>56</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
-        <v>6220</v>
+        <v>6210</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 14:00:00</t>
+          <t>2026-10-14 16:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.25</v>
+        <v>20.96</v>
       </c>
       <c r="C48" t="n">
-        <v>21.62</v>
+        <v>21.38</v>
       </c>
       <c r="D48" t="n">
-        <v>20.57</v>
+        <v>20.75</v>
       </c>
       <c r="E48" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="F48" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="G48" t="n">
-        <v>285</v>
+        <v>151</v>
       </c>
       <c r="H48" t="n">
-        <v>55.82</v>
+        <v>56.06</v>
       </c>
       <c r="I48" t="n">
-        <v>57.91</v>
+        <v>56.71</v>
       </c>
       <c r="J48" t="n">
-        <v>54.45</v>
+        <v>54.86</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="M48" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>6230</v>
+        <v>6220</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 13:00:00</t>
+          <t>2026-10-14 15:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.17</v>
+        <v>21.55</v>
       </c>
       <c r="C49" t="n">
-        <v>22.05</v>
+        <v>21.81</v>
       </c>
       <c r="D49" t="n">
-        <v>19.15</v>
+        <v>21.14</v>
       </c>
       <c r="E49" t="n">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
       <c r="F49" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="G49" t="n">
-        <v>426</v>
+        <v>296</v>
       </c>
       <c r="H49" t="n">
-        <v>60.86</v>
+        <v>53.03</v>
       </c>
       <c r="I49" t="n">
-        <v>65.42</v>
+        <v>54.48</v>
       </c>
       <c r="J49" t="n">
-        <v>53.21</v>
+        <v>51.56</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N49" t="n">
-        <v>6250</v>
+        <v>6220</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00:00</t>
+          <t>2026-10-14 14:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>19.06</v>
+        <v>21.25</v>
       </c>
       <c r="C50" t="n">
-        <v>20.31</v>
+        <v>21.62</v>
       </c>
       <c r="D50" t="n">
-        <v>18.02</v>
+        <v>20.57</v>
       </c>
       <c r="E50" t="n">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="F50" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="G50" t="n">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="H50" t="n">
-        <v>67.37</v>
+        <v>55.82</v>
       </c>
       <c r="I50" t="n">
-        <v>72.42</v>
+        <v>57.91</v>
       </c>
       <c r="J50" t="n">
-        <v>61.34</v>
+        <v>54.45</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="M50" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>6210</v>
+        <v>6230</v>
       </c>
       <c r="O50" t="n">
         <v>2.5</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,41 +508,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.72</v>
+        <v>21.8</v>
       </c>
       <c r="C2" t="n">
-        <v>21.84</v>
+        <v>21.85</v>
       </c>
       <c r="D2" t="n">
-        <v>21.61</v>
+        <v>21.73</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F2" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="G2" t="n">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="H2" t="n">
-        <v>52.83</v>
+        <v>52.66</v>
       </c>
       <c r="I2" t="n">
-        <v>53.09</v>
+        <v>52.78</v>
       </c>
       <c r="J2" t="n">
-        <v>52.51</v>
+        <v>52.56</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -555,44 +555,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.42</v>
+        <v>21.74</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>21.95</v>
       </c>
       <c r="D3" t="n">
-        <v>20.92</v>
+        <v>21.56</v>
       </c>
       <c r="E3" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G3" t="n">
-        <v>218</v>
+        <v>165</v>
       </c>
       <c r="H3" t="n">
-        <v>54.49</v>
+        <v>52.76</v>
       </c>
       <c r="I3" t="n">
-        <v>56.38</v>
+        <v>53.57</v>
       </c>
       <c r="J3" t="n">
-        <v>52.2</v>
+        <v>52.06</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="N3" t="n">
         <v>6190</v>
@@ -602,35 +602,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.35</v>
+        <v>21.42</v>
       </c>
       <c r="C4" t="n">
-        <v>22.22</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>20.87</v>
+        <v>20.92</v>
       </c>
       <c r="E4" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F4" t="n">
         <v>11.5</v>
       </c>
       <c r="G4" t="n">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="H4" t="n">
-        <v>55.07</v>
+        <v>54.49</v>
       </c>
       <c r="I4" t="n">
-        <v>56.71</v>
+        <v>56.38</v>
       </c>
       <c r="J4" t="n">
-        <v>52.16</v>
+        <v>52.2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>6190</v>
@@ -649,17 +649,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.1</v>
+        <v>21.35</v>
       </c>
       <c r="C5" t="n">
-        <v>21.69</v>
+        <v>22.22</v>
       </c>
       <c r="D5" t="n">
-        <v>20.51</v>
+        <v>20.87</v>
       </c>
       <c r="E5" t="n">
         <v>11.8</v>
@@ -668,110 +668,110 @@
         <v>11.5</v>
       </c>
       <c r="G5" t="n">
-        <v>480</v>
+        <v>238</v>
       </c>
       <c r="H5" t="n">
-        <v>55.96</v>
+        <v>55.07</v>
       </c>
       <c r="I5" t="n">
-        <v>58.01</v>
+        <v>56.71</v>
       </c>
       <c r="J5" t="n">
-        <v>53.81</v>
+        <v>52.16</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="N5" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.15</v>
+        <v>21.1</v>
       </c>
       <c r="C6" t="n">
-        <v>20.85</v>
+        <v>21.69</v>
       </c>
       <c r="D6" t="n">
-        <v>19.57</v>
+        <v>20.51</v>
       </c>
       <c r="E6" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="F6" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G6" t="n">
-        <v>266</v>
+        <v>480</v>
       </c>
       <c r="H6" t="n">
-        <v>60.77</v>
+        <v>55.96</v>
       </c>
       <c r="I6" t="n">
-        <v>64.81</v>
+        <v>58.01</v>
       </c>
       <c r="J6" t="n">
-        <v>56.73</v>
+        <v>53.81</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>6200</v>
+        <v>6210</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.37</v>
+        <v>20.15</v>
       </c>
       <c r="C7" t="n">
-        <v>19.79</v>
+        <v>20.85</v>
       </c>
       <c r="D7" t="n">
-        <v>18.91</v>
+        <v>19.57</v>
       </c>
       <c r="E7" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F7" t="n">
-        <v>12.3</v>
+        <v>11.6</v>
       </c>
       <c r="G7" t="n">
-        <v>174</v>
+        <v>266</v>
       </c>
       <c r="H7" t="n">
-        <v>65.04000000000001</v>
+        <v>60.77</v>
       </c>
       <c r="I7" t="n">
-        <v>66.98999999999999</v>
+        <v>64.81</v>
       </c>
       <c r="J7" t="n">
-        <v>63.19</v>
+        <v>56.73</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -780,233 +780,233 @@
         <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="N7" t="n">
-        <v>6180</v>
+        <v>6200</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.41</v>
+        <v>19.37</v>
       </c>
       <c r="C8" t="n">
-        <v>18.85</v>
+        <v>19.79</v>
       </c>
       <c r="D8" t="n">
-        <v>18.05</v>
+        <v>18.91</v>
       </c>
       <c r="E8" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="F8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="G8" t="n">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="H8" t="n">
-        <v>69.37</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>71.67</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>67.22</v>
+        <v>63.19</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="N8" t="n">
-        <v>6170</v>
+        <v>6180</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.66</v>
+        <v>18.41</v>
       </c>
       <c r="C9" t="n">
-        <v>17.95</v>
+        <v>18.85</v>
       </c>
       <c r="D9" t="n">
-        <v>17.51</v>
+        <v>18.05</v>
       </c>
       <c r="E9" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="F9" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>73.31</v>
+        <v>69.37</v>
       </c>
       <c r="I9" t="n">
-        <v>74.14</v>
+        <v>71.67</v>
       </c>
       <c r="J9" t="n">
-        <v>72.19</v>
+        <v>67.22</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="N9" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.6</v>
+        <v>17.66</v>
       </c>
       <c r="C10" t="n">
-        <v>17.68</v>
+        <v>17.95</v>
       </c>
       <c r="D10" t="n">
-        <v>17.49</v>
+        <v>17.51</v>
       </c>
       <c r="E10" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="F10" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>72.5</v>
+        <v>73.31</v>
       </c>
       <c r="I10" t="n">
-        <v>73.76000000000001</v>
+        <v>74.14</v>
       </c>
       <c r="J10" t="n">
-        <v>71.78</v>
+        <v>72.19</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="N10" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.53</v>
+        <v>17.6</v>
       </c>
       <c r="C11" t="n">
-        <v>17.62</v>
+        <v>17.68</v>
       </c>
       <c r="D11" t="n">
-        <v>17.45</v>
+        <v>17.49</v>
       </c>
       <c r="E11" t="n">
         <v>12.4</v>
       </c>
       <c r="F11" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>72.33</v>
+        <v>72.5</v>
       </c>
       <c r="I11" t="n">
-        <v>72.88</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>71.93000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="N11" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.64</v>
+        <v>17.53</v>
       </c>
       <c r="C12" t="n">
-        <v>17.9</v>
+        <v>17.62</v>
       </c>
       <c r="D12" t="n">
-        <v>17.44</v>
+        <v>17.45</v>
       </c>
       <c r="E12" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>71.73999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="I12" t="n">
-        <v>73.59999999999999</v>
+        <v>72.88</v>
       </c>
       <c r="J12" t="n">
-        <v>69.53</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="N12" t="n">
         <v>6152</v>
@@ -1025,20 +1025,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.84</v>
+        <v>17.64</v>
       </c>
       <c r="C13" t="n">
-        <v>17.88</v>
+        <v>17.9</v>
       </c>
       <c r="D13" t="n">
-        <v>17.8</v>
+        <v>17.44</v>
       </c>
       <c r="E13" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
@@ -1047,45 +1047,45 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>70.06999999999999</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>70.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>69.65000000000001</v>
+        <v>69.53</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N13" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.9</v>
+        <v>17.84</v>
       </c>
       <c r="C14" t="n">
-        <v>17.97</v>
+        <v>17.88</v>
       </c>
       <c r="D14" t="n">
-        <v>17.82</v>
+        <v>17.8</v>
       </c>
       <c r="E14" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F14" t="n">
         <v>12</v>
@@ -1094,22 +1094,22 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>69.79000000000001</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>70.48999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="J14" t="n">
-        <v>69.43000000000001</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="N14" t="n">
         <v>6162</v>
@@ -1119,35 +1119,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.74</v>
+        <v>17.9</v>
       </c>
       <c r="C15" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.82</v>
       </c>
-      <c r="D15" t="n">
-        <v>17.7</v>
-      </c>
       <c r="E15" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="F15" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>70.81999999999999</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>70.98</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>70.54000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="N15" t="n">
         <v>6162</v>
@@ -1166,44 +1166,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.68</v>
+        <v>17.74</v>
       </c>
       <c r="C16" t="n">
-        <v>17.71</v>
+        <v>17.82</v>
       </c>
       <c r="D16" t="n">
-        <v>17.64</v>
+        <v>17.7</v>
       </c>
       <c r="E16" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F16" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>71.42</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>71.8</v>
+        <v>70.98</v>
       </c>
       <c r="J16" t="n">
-        <v>71.13</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N16" t="n">
         <v>6162</v>
@@ -1213,88 +1213,88 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.74</v>
+        <v>17.68</v>
       </c>
       <c r="C17" t="n">
-        <v>17.78</v>
+        <v>17.71</v>
       </c>
       <c r="D17" t="n">
-        <v>17.68</v>
+        <v>17.64</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F17" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>71.53</v>
+        <v>71.42</v>
       </c>
       <c r="I17" t="n">
-        <v>72.06999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="J17" t="n">
-        <v>70.67</v>
+        <v>71.13</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18.17</v>
+        <v>17.74</v>
       </c>
       <c r="C18" t="n">
-        <v>18.45</v>
+        <v>17.78</v>
       </c>
       <c r="D18" t="n">
-        <v>17.85</v>
+        <v>17.68</v>
       </c>
       <c r="E18" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="F18" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>67.5</v>
+        <v>71.53</v>
       </c>
       <c r="I18" t="n">
-        <v>70.09</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>65.53</v>
+        <v>70.67</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="n">
         <v>2</v>
@@ -1307,158 +1307,158 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.12</v>
+        <v>18.17</v>
       </c>
       <c r="C19" t="n">
-        <v>19.48</v>
+        <v>18.45</v>
       </c>
       <c r="D19" t="n">
-        <v>18.59</v>
+        <v>17.85</v>
       </c>
       <c r="E19" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="F19" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>62.25</v>
+        <v>67.5</v>
       </c>
       <c r="I19" t="n">
-        <v>64.8</v>
+        <v>70.09</v>
       </c>
       <c r="J19" t="n">
-        <v>60.27</v>
+        <v>65.53</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>6180</v>
+        <v>6152</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.89</v>
+        <v>19.12</v>
       </c>
       <c r="C20" t="n">
-        <v>20.2</v>
+        <v>19.48</v>
       </c>
       <c r="D20" t="n">
-        <v>19.54</v>
+        <v>18.59</v>
       </c>
       <c r="E20" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="F20" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>58.12</v>
+        <v>62.25</v>
       </c>
       <c r="I20" t="n">
-        <v>59.88</v>
+        <v>64.8</v>
       </c>
       <c r="J20" t="n">
-        <v>56.65</v>
+        <v>60.27</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="N20" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.59</v>
+        <v>19.89</v>
       </c>
       <c r="C21" t="n">
-        <v>21.02</v>
+        <v>20.2</v>
       </c>
       <c r="D21" t="n">
-        <v>20.23</v>
+        <v>19.54</v>
       </c>
       <c r="E21" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F21" t="n">
         <v>11.1</v>
       </c>
-      <c r="F21" t="n">
-        <v>11</v>
-      </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>55.26</v>
+        <v>58.12</v>
       </c>
       <c r="I21" t="n">
-        <v>56.46</v>
+        <v>59.88</v>
       </c>
       <c r="J21" t="n">
-        <v>54.02</v>
+        <v>56.65</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="N21" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21.34</v>
+        <v>20.59</v>
       </c>
       <c r="C22" t="n">
-        <v>21.65</v>
+        <v>21.02</v>
       </c>
       <c r="D22" t="n">
-        <v>20.98</v>
+        <v>20.23</v>
       </c>
       <c r="E22" t="n">
         <v>11.1</v>
@@ -1467,213 +1467,213 @@
         <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>52.89</v>
+        <v>55.26</v>
       </c>
       <c r="I22" t="n">
-        <v>53.97</v>
+        <v>56.46</v>
       </c>
       <c r="J22" t="n">
-        <v>51.51</v>
+        <v>54.02</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="N22" t="n">
-        <v>6220</v>
+        <v>6200</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22.22</v>
+        <v>21.34</v>
       </c>
       <c r="C23" t="n">
-        <v>22.72</v>
+        <v>21.65</v>
       </c>
       <c r="D23" t="n">
-        <v>21.71</v>
+        <v>20.98</v>
       </c>
       <c r="E23" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="F23" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>210</v>
+        <v>63</v>
       </c>
       <c r="H23" t="n">
-        <v>50.44</v>
+        <v>52.89</v>
       </c>
       <c r="I23" t="n">
-        <v>51.7</v>
+        <v>53.97</v>
       </c>
       <c r="J23" t="n">
-        <v>49.53</v>
+        <v>51.51</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="N23" t="n">
-        <v>6240</v>
+        <v>6220</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22.94</v>
+        <v>22.22</v>
       </c>
       <c r="C24" t="n">
-        <v>23.82</v>
+        <v>22.72</v>
       </c>
       <c r="D24" t="n">
-        <v>22.29</v>
+        <v>21.71</v>
       </c>
       <c r="E24" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="F24" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="G24" t="n">
-        <v>355</v>
+        <v>210</v>
       </c>
       <c r="H24" t="n">
-        <v>46.37</v>
+        <v>50.44</v>
       </c>
       <c r="I24" t="n">
-        <v>49.68</v>
+        <v>51.7</v>
       </c>
       <c r="J24" t="n">
-        <v>44.22</v>
+        <v>49.53</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
         <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>6250</v>
+        <v>6240</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>23.12</v>
+        <v>22.94</v>
       </c>
       <c r="C25" t="n">
-        <v>24.14</v>
+        <v>23.82</v>
       </c>
       <c r="D25" t="n">
-        <v>22.72</v>
+        <v>22.29</v>
       </c>
       <c r="E25" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="F25" t="n">
         <v>10.3</v>
       </c>
       <c r="G25" t="n">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="H25" t="n">
-        <v>45.59</v>
+        <v>46.37</v>
       </c>
       <c r="I25" t="n">
-        <v>46.9</v>
+        <v>49.68</v>
       </c>
       <c r="J25" t="n">
-        <v>43.18</v>
+        <v>44.22</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>6240</v>
+        <v>6250</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22.76</v>
+        <v>23.12</v>
       </c>
       <c r="C26" t="n">
-        <v>23.63</v>
+        <v>24.14</v>
       </c>
       <c r="D26" t="n">
-        <v>22.08</v>
+        <v>22.72</v>
       </c>
       <c r="E26" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="F26" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="G26" t="n">
-        <v>462</v>
+        <v>344</v>
       </c>
       <c r="H26" t="n">
-        <v>47.51</v>
+        <v>45.59</v>
       </c>
       <c r="I26" t="n">
-        <v>49.36</v>
+        <v>46.9</v>
       </c>
       <c r="J26" t="n">
-        <v>46.08</v>
+        <v>43.18</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
         <v>6240</v>
@@ -1683,223 +1683,223 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22.55</v>
+        <v>22.76</v>
       </c>
       <c r="C27" t="n">
-        <v>23.29</v>
+        <v>23.63</v>
       </c>
       <c r="D27" t="n">
-        <v>21.68</v>
+        <v>22.08</v>
       </c>
       <c r="E27" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F27" t="n">
         <v>10.5</v>
       </c>
       <c r="G27" t="n">
-        <v>364</v>
+        <v>462</v>
       </c>
       <c r="H27" t="n">
-        <v>47.88</v>
+        <v>47.51</v>
       </c>
       <c r="I27" t="n">
-        <v>50.32</v>
+        <v>49.36</v>
       </c>
       <c r="J27" t="n">
-        <v>46.13</v>
+        <v>46.08</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>6220</v>
+        <v>6240</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22.47</v>
+        <v>22.55</v>
       </c>
       <c r="C28" t="n">
-        <v>23.42</v>
+        <v>23.29</v>
       </c>
       <c r="D28" t="n">
-        <v>21.73</v>
+        <v>21.68</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="F28" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>531</v>
+        <v>364</v>
       </c>
       <c r="H28" t="n">
-        <v>49.09</v>
+        <v>47.88</v>
       </c>
       <c r="I28" t="n">
-        <v>51.32</v>
+        <v>50.32</v>
       </c>
       <c r="J28" t="n">
-        <v>46.18</v>
+        <v>46.13</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>6230</v>
+        <v>6220</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21.72</v>
+        <v>22.47</v>
       </c>
       <c r="C29" t="n">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="D29" t="n">
-        <v>20.79</v>
+        <v>21.73</v>
       </c>
       <c r="E29" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="G29" t="n">
-        <v>616</v>
+        <v>531</v>
       </c>
       <c r="H29" t="n">
-        <v>52.51</v>
+        <v>49.09</v>
       </c>
       <c r="I29" t="n">
-        <v>55.76</v>
+        <v>51.32</v>
       </c>
       <c r="J29" t="n">
-        <v>47.65</v>
+        <v>46.18</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>6220</v>
+        <v>6230</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20.86</v>
+        <v>21.72</v>
       </c>
       <c r="C30" t="n">
-        <v>21.56</v>
+        <v>23.46</v>
       </c>
       <c r="D30" t="n">
-        <v>20.25</v>
+        <v>20.79</v>
       </c>
       <c r="E30" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="F30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>642</v>
+        <v>616</v>
       </c>
       <c r="H30" t="n">
-        <v>56.36</v>
+        <v>52.51</v>
       </c>
       <c r="I30" t="n">
-        <v>59</v>
+        <v>55.76</v>
       </c>
       <c r="J30" t="n">
-        <v>53.69</v>
+        <v>47.65</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.5</v>
+        <v>20.86</v>
       </c>
       <c r="C31" t="n">
-        <v>19.99</v>
+        <v>21.56</v>
       </c>
       <c r="D31" t="n">
-        <v>19.01</v>
+        <v>20.25</v>
       </c>
       <c r="E31" t="n">
         <v>11.7</v>
       </c>
       <c r="F31" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="G31" t="n">
-        <v>341</v>
+        <v>642</v>
       </c>
       <c r="H31" t="n">
-        <v>61.31</v>
+        <v>56.36</v>
       </c>
       <c r="I31" t="n">
-        <v>62.89</v>
+        <v>59</v>
       </c>
       <c r="J31" t="n">
-        <v>59.57</v>
+        <v>53.69</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>3.2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
         <v>6190</v>
@@ -1918,129 +1918,129 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.96</v>
+        <v>19.5</v>
       </c>
       <c r="C32" t="n">
-        <v>18.97</v>
+        <v>19.99</v>
       </c>
       <c r="D32" t="n">
-        <v>17.06</v>
+        <v>19.01</v>
       </c>
       <c r="E32" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="F32" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="G32" t="n">
-        <v>158</v>
+        <v>341</v>
       </c>
       <c r="H32" t="n">
-        <v>69.53</v>
+        <v>61.31</v>
       </c>
       <c r="I32" t="n">
-        <v>74.66</v>
+        <v>62.89</v>
       </c>
       <c r="J32" t="n">
-        <v>64.09</v>
+        <v>59.57</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M32" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.73</v>
+        <v>17.96</v>
       </c>
       <c r="C33" t="n">
-        <v>16.97</v>
+        <v>18.97</v>
       </c>
       <c r="D33" t="n">
-        <v>16.64</v>
+        <v>17.06</v>
       </c>
       <c r="E33" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F33" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="G33" t="n">
-        <v>33</v>
+        <v>158</v>
       </c>
       <c r="H33" t="n">
-        <v>76.20999999999999</v>
+        <v>69.53</v>
       </c>
       <c r="I33" t="n">
-        <v>76.59999999999999</v>
+        <v>74.66</v>
       </c>
       <c r="J33" t="n">
-        <v>75.42</v>
+        <v>64.09</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="N33" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.74</v>
+        <v>16.73</v>
       </c>
       <c r="C34" t="n">
-        <v>16.83</v>
+        <v>16.97</v>
       </c>
       <c r="D34" t="n">
-        <v>16.69</v>
+        <v>16.64</v>
       </c>
       <c r="E34" t="n">
         <v>12.4</v>
       </c>
       <c r="F34" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>76.59</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>77.48</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>75.81999999999999</v>
+        <v>75.42</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2049,148 +2049,148 @@
         <v>1.2</v>
       </c>
       <c r="M34" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="N34" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>16.74</v>
       </c>
       <c r="C35" t="n">
-        <v>16.81</v>
+        <v>16.83</v>
       </c>
       <c r="D35" t="n">
-        <v>16.65</v>
+        <v>16.69</v>
       </c>
       <c r="E35" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="F35" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>77.14</v>
+        <v>76.59</v>
       </c>
       <c r="I35" t="n">
-        <v>77.55</v>
+        <v>77.48</v>
       </c>
       <c r="J35" t="n">
-        <v>76.81999999999999</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="M35" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="N35" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16.83</v>
+        <v>16.74</v>
       </c>
       <c r="C36" t="n">
-        <v>16.93</v>
+        <v>16.81</v>
       </c>
       <c r="D36" t="n">
-        <v>16.77</v>
+        <v>16.65</v>
       </c>
       <c r="E36" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="F36" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>77.89</v>
+        <v>77.14</v>
       </c>
       <c r="I36" t="n">
-        <v>78.14</v>
+        <v>77.55</v>
       </c>
       <c r="J36" t="n">
-        <v>77.23</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="M36" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="N36" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.08</v>
+        <v>16.83</v>
       </c>
       <c r="C37" t="n">
-        <v>17.24</v>
+        <v>16.93</v>
       </c>
       <c r="D37" t="n">
-        <v>16.95</v>
+        <v>16.77</v>
       </c>
       <c r="E37" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="F37" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>77.45999999999999</v>
+        <v>77.89</v>
       </c>
       <c r="I37" t="n">
-        <v>78.15000000000001</v>
+        <v>78.14</v>
       </c>
       <c r="J37" t="n">
-        <v>76.95</v>
+        <v>77.23</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N37" t="n">
         <v>6142</v>
@@ -2200,35 +2200,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.17</v>
+        <v>17.08</v>
       </c>
       <c r="C38" t="n">
-        <v>17.3</v>
+        <v>17.24</v>
       </c>
       <c r="D38" t="n">
-        <v>16.93</v>
+        <v>16.95</v>
       </c>
       <c r="E38" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="F38" t="n">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>78.43000000000001</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>81.27</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>77.08</v>
+        <v>76.95</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2240,185 +2240,185 @@
         <v>1.7</v>
       </c>
       <c r="N38" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.59</v>
+        <v>17.17</v>
       </c>
       <c r="C39" t="n">
-        <v>17.86</v>
+        <v>17.3</v>
       </c>
       <c r="D39" t="n">
-        <v>17.28</v>
+        <v>16.93</v>
       </c>
       <c r="E39" t="n">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="F39" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>75</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>77.95</v>
+        <v>81.27</v>
       </c>
       <c r="J39" t="n">
-        <v>73.39</v>
+        <v>77.08</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="M39" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="N39" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>18.2</v>
+        <v>17.59</v>
       </c>
       <c r="C40" t="n">
-        <v>18.41</v>
+        <v>17.86</v>
       </c>
       <c r="D40" t="n">
-        <v>18</v>
+        <v>17.28</v>
       </c>
       <c r="E40" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="F40" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>69.83</v>
+        <v>75</v>
       </c>
       <c r="I40" t="n">
-        <v>72.37</v>
+        <v>77.95</v>
       </c>
       <c r="J40" t="n">
-        <v>68.34</v>
+        <v>73.39</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="M40" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="N40" t="n">
         <v>6162</v>
       </c>
-      <c r="O40" t="n">
-        <v>3.7</v>
-      </c>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>18.56</v>
+        <v>18.2</v>
       </c>
       <c r="C41" t="n">
-        <v>18.7</v>
+        <v>18.41</v>
       </c>
       <c r="D41" t="n">
-        <v>18.41</v>
+        <v>18</v>
       </c>
       <c r="E41" t="n">
         <v>12.4</v>
       </c>
       <c r="F41" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>67.93000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="I41" t="n">
-        <v>68.55</v>
+        <v>72.37</v>
       </c>
       <c r="J41" t="n">
-        <v>67.33</v>
+        <v>68.34</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="N41" t="n">
         <v>6162</v>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18.92</v>
+        <v>18.56</v>
       </c>
       <c r="C42" t="n">
-        <v>19.04</v>
+        <v>18.7</v>
       </c>
       <c r="D42" t="n">
-        <v>18.74</v>
+        <v>18.41</v>
       </c>
       <c r="E42" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F42" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>66</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>67.08</v>
+        <v>68.55</v>
       </c>
       <c r="J42" t="n">
-        <v>65.19</v>
+        <v>67.33</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2430,27 +2430,27 @@
         <v>2.6</v>
       </c>
       <c r="N42" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18.98</v>
+        <v>18.92</v>
       </c>
       <c r="C43" t="n">
-        <v>19.02</v>
+        <v>19.04</v>
       </c>
       <c r="D43" t="n">
-        <v>18.95</v>
+        <v>18.74</v>
       </c>
       <c r="E43" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F43" t="n">
         <v>12.2</v>
@@ -2459,22 +2459,22 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>65.26000000000001</v>
+        <v>66</v>
       </c>
       <c r="I43" t="n">
-        <v>65.51000000000001</v>
+        <v>67.08</v>
       </c>
       <c r="J43" t="n">
-        <v>65.09999999999999</v>
+        <v>65.19</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="M43" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="N43" t="n">
         <v>6170</v>
@@ -2484,44 +2484,44 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.27</v>
+        <v>18.98</v>
       </c>
       <c r="C44" t="n">
-        <v>19.65</v>
+        <v>19.02</v>
       </c>
       <c r="D44" t="n">
-        <v>19.01</v>
+        <v>18.95</v>
       </c>
       <c r="E44" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="F44" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>62.96</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>64.81</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>60.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="M44" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="N44" t="n">
         <v>6170</v>
@@ -2531,232 +2531,232 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 19:00:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.98</v>
+        <v>19.27</v>
       </c>
       <c r="C45" t="n">
-        <v>20.21</v>
+        <v>19.65</v>
       </c>
       <c r="D45" t="n">
-        <v>19.72</v>
+        <v>19.01</v>
       </c>
       <c r="E45" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="F45" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>58.7</v>
+        <v>62.96</v>
       </c>
       <c r="I45" t="n">
-        <v>59.99</v>
+        <v>64.81</v>
       </c>
       <c r="J45" t="n">
-        <v>57.42</v>
+        <v>60.5</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="M45" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="N45" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-14 19:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20.51</v>
+        <v>19.98</v>
       </c>
       <c r="C46" t="n">
-        <v>20.87</v>
+        <v>20.21</v>
       </c>
       <c r="D46" t="n">
-        <v>20.26</v>
+        <v>19.72</v>
       </c>
       <c r="E46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F46" t="n">
         <v>11.3</v>
       </c>
-      <c r="F46" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G46" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
-        <v>56.48</v>
+        <v>58.7</v>
       </c>
       <c r="I46" t="n">
-        <v>57.91</v>
+        <v>59.99</v>
       </c>
       <c r="J46" t="n">
-        <v>55.61</v>
+        <v>57.42</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="N46" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-14 18:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20.85</v>
+        <v>20.51</v>
       </c>
       <c r="C47" t="n">
-        <v>21.07</v>
+        <v>20.87</v>
       </c>
       <c r="D47" t="n">
-        <v>20.73</v>
+        <v>20.26</v>
       </c>
       <c r="E47" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="F47" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G47" t="n">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="H47" t="n">
         <v>56.48</v>
       </c>
       <c r="I47" t="n">
-        <v>57.04</v>
+        <v>57.91</v>
       </c>
       <c r="J47" t="n">
-        <v>56</v>
+        <v>55.61</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-14 17:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>20.96</v>
+        <v>20.85</v>
       </c>
       <c r="C48" t="n">
-        <v>21.38</v>
+        <v>21.07</v>
       </c>
       <c r="D48" t="n">
-        <v>20.75</v>
+        <v>20.73</v>
       </c>
       <c r="E48" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F48" t="n">
         <v>11.6</v>
       </c>
-      <c r="F48" t="n">
-        <v>11.4</v>
-      </c>
       <c r="G48" t="n">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="H48" t="n">
-        <v>56.06</v>
+        <v>56.48</v>
       </c>
       <c r="I48" t="n">
-        <v>56.71</v>
+        <v>57.04</v>
       </c>
       <c r="J48" t="n">
-        <v>54.86</v>
+        <v>56</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M48" t="n">
         <v>3.3</v>
       </c>
-      <c r="M48" t="n">
-        <v>4.2</v>
-      </c>
       <c r="N48" t="n">
-        <v>6220</v>
+        <v>6210</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00:00</t>
+          <t>2026-10-14 16:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>21.55</v>
+        <v>20.96</v>
       </c>
       <c r="C49" t="n">
-        <v>21.81</v>
+        <v>21.38</v>
       </c>
       <c r="D49" t="n">
-        <v>21.14</v>
+        <v>20.75</v>
       </c>
       <c r="E49" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F49" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="G49" t="n">
-        <v>296</v>
+        <v>151</v>
       </c>
       <c r="H49" t="n">
-        <v>53.03</v>
+        <v>56.06</v>
       </c>
       <c r="I49" t="n">
-        <v>54.48</v>
+        <v>56.71</v>
       </c>
       <c r="J49" t="n">
-        <v>51.56</v>
+        <v>54.86</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="M49" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
         <v>6220</v>
@@ -2766,47 +2766,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14 14:00:00</t>
+          <t>2026-10-14 15:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>21.25</v>
+        <v>21.55</v>
       </c>
       <c r="C50" t="n">
-        <v>21.62</v>
+        <v>21.81</v>
       </c>
       <c r="D50" t="n">
-        <v>20.57</v>
+        <v>21.14</v>
       </c>
       <c r="E50" t="n">
-        <v>11.9</v>
+        <v>11.3</v>
       </c>
       <c r="F50" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
       <c r="G50" t="n">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="H50" t="n">
-        <v>55.82</v>
+        <v>53.03</v>
       </c>
       <c r="I50" t="n">
-        <v>57.91</v>
+        <v>54.48</v>
       </c>
       <c r="J50" t="n">
-        <v>54.45</v>
+        <v>51.56</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="M50" t="n">
         <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>6230</v>
+        <v>6220</v>
       </c>
       <c r="O50" t="n">
         <v>2.5</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,185 +508,185 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.8</v>
+        <v>22.83</v>
       </c>
       <c r="C2" t="n">
-        <v>21.85</v>
+        <v>22.85</v>
       </c>
       <c r="D2" t="n">
-        <v>21.73</v>
+        <v>22.81</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F2" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G2" t="n">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="H2" t="n">
-        <v>52.66</v>
+        <v>48.9</v>
       </c>
       <c r="I2" t="n">
-        <v>52.78</v>
+        <v>48.98</v>
       </c>
       <c r="J2" t="n">
-        <v>52.56</v>
+        <v>48.79</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="N2" t="n">
-        <v>6190</v>
+        <v>6210</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.74</v>
+        <v>23.26</v>
       </c>
       <c r="C3" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>21.56</v>
+        <v>22.73</v>
       </c>
       <c r="E3" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="F3" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="G3" t="n">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="H3" t="n">
-        <v>52.76</v>
+        <v>47.55</v>
       </c>
       <c r="I3" t="n">
-        <v>53.57</v>
+        <v>48.93</v>
       </c>
       <c r="J3" t="n">
-        <v>52.06</v>
+        <v>45.68</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.42</v>
+        <v>22.81</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>20.92</v>
+        <v>21.97</v>
       </c>
       <c r="E4" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>218</v>
+        <v>373</v>
       </c>
       <c r="H4" t="n">
-        <v>54.49</v>
+        <v>49.12</v>
       </c>
       <c r="I4" t="n">
-        <v>56.38</v>
+        <v>52.45</v>
       </c>
       <c r="J4" t="n">
-        <v>52.2</v>
+        <v>45.39</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N4" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.35</v>
+        <v>21.82</v>
       </c>
       <c r="C5" t="n">
-        <v>22.22</v>
+        <v>21.95</v>
       </c>
       <c r="D5" t="n">
-        <v>20.87</v>
+        <v>21.73</v>
       </c>
       <c r="E5" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F5" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G5" t="n">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="H5" t="n">
-        <v>55.07</v>
+        <v>52.7</v>
       </c>
       <c r="I5" t="n">
-        <v>56.71</v>
+        <v>52.97</v>
       </c>
       <c r="J5" t="n">
-        <v>52.16</v>
+        <v>52.47</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="N5" t="n">
         <v>6190</v>
@@ -696,252 +696,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.1</v>
+        <v>21.74</v>
       </c>
       <c r="C6" t="n">
-        <v>21.69</v>
+        <v>21.95</v>
       </c>
       <c r="D6" t="n">
-        <v>20.51</v>
+        <v>21.56</v>
       </c>
       <c r="E6" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="F6" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G6" t="n">
-        <v>480</v>
+        <v>165</v>
       </c>
       <c r="H6" t="n">
-        <v>55.96</v>
+        <v>52.76</v>
       </c>
       <c r="I6" t="n">
-        <v>58.01</v>
+        <v>53.57</v>
       </c>
       <c r="J6" t="n">
-        <v>53.81</v>
+        <v>52.06</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="N6" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.15</v>
+        <v>21.42</v>
       </c>
       <c r="C7" t="n">
-        <v>20.85</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>19.57</v>
+        <v>20.92</v>
       </c>
       <c r="E7" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="F7" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G7" t="n">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="H7" t="n">
-        <v>60.77</v>
+        <v>54.49</v>
       </c>
       <c r="I7" t="n">
-        <v>64.81</v>
+        <v>56.38</v>
       </c>
       <c r="J7" t="n">
-        <v>56.73</v>
+        <v>52.2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.37</v>
+        <v>21.35</v>
       </c>
       <c r="C8" t="n">
-        <v>19.79</v>
+        <v>22.22</v>
       </c>
       <c r="D8" t="n">
-        <v>18.91</v>
+        <v>20.87</v>
       </c>
       <c r="E8" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F8" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G8" t="n">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="H8" t="n">
-        <v>65.04000000000001</v>
+        <v>55.07</v>
       </c>
       <c r="I8" t="n">
-        <v>66.98999999999999</v>
+        <v>56.71</v>
       </c>
       <c r="J8" t="n">
-        <v>63.19</v>
+        <v>52.16</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N8" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.41</v>
+        <v>21.1</v>
       </c>
       <c r="C9" t="n">
-        <v>18.85</v>
+        <v>21.69</v>
       </c>
       <c r="D9" t="n">
-        <v>18.05</v>
+        <v>20.51</v>
       </c>
       <c r="E9" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F9" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>480</v>
       </c>
       <c r="H9" t="n">
-        <v>69.37</v>
+        <v>55.96</v>
       </c>
       <c r="I9" t="n">
-        <v>71.67</v>
+        <v>58.01</v>
       </c>
       <c r="J9" t="n">
-        <v>67.22</v>
+        <v>53.81</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>6170</v>
+        <v>6210</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.66</v>
+        <v>20.15</v>
       </c>
       <c r="C10" t="n">
-        <v>17.95</v>
+        <v>20.85</v>
       </c>
       <c r="D10" t="n">
-        <v>17.51</v>
+        <v>19.57</v>
       </c>
       <c r="E10" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="F10" t="n">
-        <v>12.6</v>
+        <v>11.6</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>266</v>
       </c>
       <c r="H10" t="n">
-        <v>73.31</v>
+        <v>60.77</v>
       </c>
       <c r="I10" t="n">
-        <v>74.14</v>
+        <v>64.81</v>
       </c>
       <c r="J10" t="n">
-        <v>72.19</v>
+        <v>56.73</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="N10" t="n">
-        <v>6162</v>
+        <v>6200</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.6</v>
+        <v>19.37</v>
       </c>
       <c r="C11" t="n">
-        <v>17.68</v>
+        <v>19.79</v>
       </c>
       <c r="D11" t="n">
-        <v>17.49</v>
+        <v>18.91</v>
       </c>
       <c r="E11" t="n">
         <v>12.4</v>
@@ -950,110 +950,110 @@
         <v>12.3</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="H11" t="n">
-        <v>72.5</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>73.76000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>71.78</v>
+        <v>63.19</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="N11" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.53</v>
+        <v>18.41</v>
       </c>
       <c r="C12" t="n">
-        <v>17.62</v>
+        <v>18.85</v>
       </c>
       <c r="D12" t="n">
-        <v>17.45</v>
+        <v>18.05</v>
       </c>
       <c r="E12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F12" t="n">
         <v>12.4</v>
       </c>
-      <c r="F12" t="n">
-        <v>12.2</v>
-      </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H12" t="n">
-        <v>72.33</v>
+        <v>69.37</v>
       </c>
       <c r="I12" t="n">
-        <v>72.88</v>
+        <v>71.67</v>
       </c>
       <c r="J12" t="n">
-        <v>71.93000000000001</v>
+        <v>67.22</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="N12" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.64</v>
+        <v>17.66</v>
       </c>
       <c r="C13" t="n">
-        <v>17.9</v>
+        <v>17.95</v>
       </c>
       <c r="D13" t="n">
-        <v>17.44</v>
+        <v>17.51</v>
       </c>
       <c r="E13" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>71.73999999999999</v>
+        <v>73.31</v>
       </c>
       <c r="I13" t="n">
-        <v>73.59999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="J13" t="n">
-        <v>69.53</v>
+        <v>72.19</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1062,195 +1062,195 @@
         <v>0.3</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="N13" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.84</v>
+        <v>17.6</v>
       </c>
       <c r="C14" t="n">
-        <v>17.88</v>
+        <v>17.68</v>
       </c>
       <c r="D14" t="n">
-        <v>17.8</v>
+        <v>17.49</v>
       </c>
       <c r="E14" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>70.06999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I14" t="n">
-        <v>70.3</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>69.65000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="N14" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.9</v>
+        <v>17.53</v>
       </c>
       <c r="C15" t="n">
-        <v>17.97</v>
+        <v>17.62</v>
       </c>
       <c r="D15" t="n">
-        <v>17.82</v>
+        <v>17.45</v>
       </c>
       <c r="E15" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>69.79000000000001</v>
+        <v>72.33</v>
       </c>
       <c r="I15" t="n">
-        <v>70.48999999999999</v>
+        <v>72.88</v>
       </c>
       <c r="J15" t="n">
-        <v>69.43000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N15" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.74</v>
+        <v>17.64</v>
       </c>
       <c r="C16" t="n">
-        <v>17.82</v>
+        <v>17.9</v>
       </c>
       <c r="D16" t="n">
-        <v>17.7</v>
+        <v>17.44</v>
       </c>
       <c r="E16" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F16" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>70.81999999999999</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>70.98</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>70.54000000000001</v>
+        <v>69.53</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M16" t="n">
         <v>1.4</v>
       </c>
       <c r="N16" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.68</v>
+        <v>17.84</v>
       </c>
       <c r="C17" t="n">
-        <v>17.71</v>
+        <v>17.88</v>
       </c>
       <c r="D17" t="n">
-        <v>17.64</v>
+        <v>17.8</v>
       </c>
       <c r="E17" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F17" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>71.42</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>71.8</v>
+        <v>70.3</v>
       </c>
       <c r="J17" t="n">
-        <v>71.13</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N17" t="n">
         <v>6162</v>
@@ -1260,299 +1260,299 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.74</v>
+        <v>17.9</v>
       </c>
       <c r="C18" t="n">
-        <v>17.78</v>
+        <v>17.97</v>
       </c>
       <c r="D18" t="n">
-        <v>17.68</v>
+        <v>17.82</v>
       </c>
       <c r="E18" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F18" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>71.53</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>72.06999999999999</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>70.67</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N18" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18.17</v>
+        <v>17.74</v>
       </c>
       <c r="C19" t="n">
-        <v>18.45</v>
+        <v>17.82</v>
       </c>
       <c r="D19" t="n">
-        <v>17.85</v>
+        <v>17.7</v>
       </c>
       <c r="E19" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="F19" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>67.5</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>70.09</v>
+        <v>70.98</v>
       </c>
       <c r="J19" t="n">
-        <v>65.53</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.12</v>
+        <v>17.68</v>
       </c>
       <c r="C20" t="n">
-        <v>19.48</v>
+        <v>17.71</v>
       </c>
       <c r="D20" t="n">
-        <v>18.59</v>
+        <v>17.64</v>
       </c>
       <c r="E20" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="F20" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>62.25</v>
+        <v>71.42</v>
       </c>
       <c r="I20" t="n">
-        <v>64.8</v>
+        <v>71.8</v>
       </c>
       <c r="J20" t="n">
-        <v>60.27</v>
+        <v>71.13</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.89</v>
+        <v>17.74</v>
       </c>
       <c r="C21" t="n">
-        <v>20.2</v>
+        <v>17.78</v>
       </c>
       <c r="D21" t="n">
-        <v>19.54</v>
+        <v>17.68</v>
       </c>
       <c r="E21" t="n">
-        <v>11.2</v>
+        <v>12.4</v>
       </c>
       <c r="F21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>58.12</v>
+        <v>71.53</v>
       </c>
       <c r="I21" t="n">
-        <v>59.88</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>56.65</v>
+        <v>70.67</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20.59</v>
+        <v>18.17</v>
       </c>
       <c r="C22" t="n">
-        <v>21.02</v>
+        <v>18.45</v>
       </c>
       <c r="D22" t="n">
-        <v>20.23</v>
+        <v>17.85</v>
       </c>
       <c r="E22" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>55.26</v>
+        <v>67.5</v>
       </c>
       <c r="I22" t="n">
-        <v>56.46</v>
+        <v>70.09</v>
       </c>
       <c r="J22" t="n">
-        <v>54.02</v>
+        <v>65.53</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M22" t="n">
         <v>2</v>
       </c>
-      <c r="M22" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N22" t="n">
-        <v>6200</v>
+        <v>6152</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21.34</v>
+        <v>19.12</v>
       </c>
       <c r="C23" t="n">
-        <v>21.65</v>
+        <v>19.48</v>
       </c>
       <c r="D23" t="n">
-        <v>20.98</v>
+        <v>18.59</v>
       </c>
       <c r="E23" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="G23" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>52.89</v>
+        <v>62.25</v>
       </c>
       <c r="I23" t="n">
-        <v>53.97</v>
+        <v>64.8</v>
       </c>
       <c r="J23" t="n">
-        <v>51.51</v>
+        <v>60.27</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="N23" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22.22</v>
+        <v>19.89</v>
       </c>
       <c r="C24" t="n">
-        <v>22.72</v>
+        <v>20.2</v>
       </c>
       <c r="D24" t="n">
-        <v>21.71</v>
+        <v>19.54</v>
       </c>
       <c r="E24" t="n">
         <v>11.2</v>
@@ -1561,166 +1561,166 @@
         <v>11.1</v>
       </c>
       <c r="G24" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>50.44</v>
+        <v>58.12</v>
       </c>
       <c r="I24" t="n">
-        <v>51.7</v>
+        <v>59.88</v>
       </c>
       <c r="J24" t="n">
-        <v>49.53</v>
+        <v>56.65</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="N24" t="n">
-        <v>6240</v>
+        <v>6190</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.94</v>
+        <v>20.59</v>
       </c>
       <c r="C25" t="n">
-        <v>23.82</v>
+        <v>21.02</v>
       </c>
       <c r="D25" t="n">
-        <v>22.29</v>
+        <v>20.23</v>
       </c>
       <c r="E25" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="F25" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>355</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>46.37</v>
+        <v>55.26</v>
       </c>
       <c r="I25" t="n">
-        <v>49.68</v>
+        <v>56.46</v>
       </c>
       <c r="J25" t="n">
-        <v>44.22</v>
+        <v>54.02</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N25" t="n">
-        <v>6250</v>
+        <v>6200</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23.12</v>
+        <v>21.34</v>
       </c>
       <c r="C26" t="n">
-        <v>24.14</v>
+        <v>21.65</v>
       </c>
       <c r="D26" t="n">
-        <v>22.72</v>
+        <v>20.98</v>
       </c>
       <c r="E26" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F26" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>344</v>
+        <v>63</v>
       </c>
       <c r="H26" t="n">
-        <v>45.59</v>
+        <v>52.89</v>
       </c>
       <c r="I26" t="n">
-        <v>46.9</v>
+        <v>53.97</v>
       </c>
       <c r="J26" t="n">
-        <v>43.18</v>
+        <v>51.51</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="N26" t="n">
-        <v>6240</v>
+        <v>6220</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22.76</v>
+        <v>22.22</v>
       </c>
       <c r="C27" t="n">
-        <v>23.63</v>
+        <v>22.72</v>
       </c>
       <c r="D27" t="n">
-        <v>22.08</v>
+        <v>21.71</v>
       </c>
       <c r="E27" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="F27" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="G27" t="n">
-        <v>462</v>
+        <v>210</v>
       </c>
       <c r="H27" t="n">
-        <v>47.51</v>
+        <v>50.44</v>
       </c>
       <c r="I27" t="n">
-        <v>49.36</v>
+        <v>51.7</v>
       </c>
       <c r="J27" t="n">
-        <v>46.08</v>
+        <v>49.53</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
         <v>6240</v>
@@ -1730,774 +1730,772 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22.55</v>
+        <v>22.94</v>
       </c>
       <c r="C28" t="n">
-        <v>23.29</v>
+        <v>23.82</v>
       </c>
       <c r="D28" t="n">
-        <v>21.68</v>
+        <v>22.29</v>
       </c>
       <c r="E28" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="F28" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="G28" t="n">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H28" t="n">
-        <v>47.88</v>
+        <v>46.37</v>
       </c>
       <c r="I28" t="n">
-        <v>50.32</v>
+        <v>49.68</v>
       </c>
       <c r="J28" t="n">
-        <v>46.13</v>
+        <v>44.22</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>6220</v>
+        <v>6250</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22.47</v>
+        <v>23.12</v>
       </c>
       <c r="C29" t="n">
-        <v>23.42</v>
+        <v>24.14</v>
       </c>
       <c r="D29" t="n">
-        <v>21.73</v>
+        <v>22.72</v>
       </c>
       <c r="E29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="F29" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="G29" t="n">
-        <v>531</v>
+        <v>344</v>
       </c>
       <c r="H29" t="n">
-        <v>49.09</v>
+        <v>45.59</v>
       </c>
       <c r="I29" t="n">
-        <v>51.32</v>
+        <v>46.9</v>
       </c>
       <c r="J29" t="n">
-        <v>46.18</v>
+        <v>43.18</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>6230</v>
+        <v>6240</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21.72</v>
+        <v>22.76</v>
       </c>
       <c r="C30" t="n">
-        <v>23.46</v>
+        <v>23.63</v>
       </c>
       <c r="D30" t="n">
-        <v>20.79</v>
+        <v>22.08</v>
       </c>
       <c r="E30" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G30" t="n">
-        <v>616</v>
+        <v>462</v>
       </c>
       <c r="H30" t="n">
-        <v>52.51</v>
+        <v>47.51</v>
       </c>
       <c r="I30" t="n">
-        <v>55.76</v>
+        <v>49.36</v>
       </c>
       <c r="J30" t="n">
-        <v>47.65</v>
+        <v>46.08</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>6220</v>
+        <v>6240</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20.86</v>
+        <v>22.55</v>
       </c>
       <c r="C31" t="n">
-        <v>21.56</v>
+        <v>23.29</v>
       </c>
       <c r="D31" t="n">
-        <v>20.25</v>
+        <v>21.68</v>
       </c>
       <c r="E31" t="n">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="F31" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G31" t="n">
-        <v>642</v>
+        <v>364</v>
       </c>
       <c r="H31" t="n">
-        <v>56.36</v>
+        <v>47.88</v>
       </c>
       <c r="I31" t="n">
-        <v>59</v>
+        <v>50.32</v>
       </c>
       <c r="J31" t="n">
-        <v>53.69</v>
+        <v>46.13</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19.5</v>
+        <v>22.47</v>
       </c>
       <c r="C32" t="n">
-        <v>19.99</v>
+        <v>23.42</v>
       </c>
       <c r="D32" t="n">
-        <v>19.01</v>
+        <v>21.73</v>
       </c>
       <c r="E32" t="n">
-        <v>11.7</v>
+        <v>11</v>
       </c>
       <c r="F32" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="G32" t="n">
-        <v>341</v>
+        <v>531</v>
       </c>
       <c r="H32" t="n">
-        <v>61.31</v>
+        <v>49.09</v>
       </c>
       <c r="I32" t="n">
-        <v>62.89</v>
+        <v>51.32</v>
       </c>
       <c r="J32" t="n">
-        <v>59.57</v>
+        <v>46.18</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M32" t="n">
         <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>6190</v>
+        <v>6230</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.96</v>
+        <v>21.72</v>
       </c>
       <c r="C33" t="n">
-        <v>18.97</v>
+        <v>23.46</v>
       </c>
       <c r="D33" t="n">
-        <v>17.06</v>
+        <v>20.79</v>
       </c>
       <c r="E33" t="n">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="F33" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="G33" t="n">
-        <v>158</v>
+        <v>616</v>
       </c>
       <c r="H33" t="n">
-        <v>69.53</v>
+        <v>52.51</v>
       </c>
       <c r="I33" t="n">
-        <v>74.66</v>
+        <v>55.76</v>
       </c>
       <c r="J33" t="n">
-        <v>64.09</v>
+        <v>47.65</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="M33" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>6180</v>
+        <v>6220</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.73</v>
+        <v>20.86</v>
       </c>
       <c r="C34" t="n">
-        <v>16.97</v>
+        <v>21.56</v>
       </c>
       <c r="D34" t="n">
-        <v>16.64</v>
+        <v>20.25</v>
       </c>
       <c r="E34" t="n">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="F34" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G34" t="n">
-        <v>33</v>
+        <v>642</v>
       </c>
       <c r="H34" t="n">
-        <v>76.20999999999999</v>
+        <v>56.36</v>
       </c>
       <c r="I34" t="n">
-        <v>76.59999999999999</v>
+        <v>59</v>
       </c>
       <c r="J34" t="n">
-        <v>75.42</v>
+        <v>53.69</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16.74</v>
+        <v>19.5</v>
       </c>
       <c r="C35" t="n">
-        <v>16.83</v>
+        <v>19.99</v>
       </c>
       <c r="D35" t="n">
-        <v>16.69</v>
+        <v>19.01</v>
       </c>
       <c r="E35" t="n">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="F35" t="n">
-        <v>12.3</v>
+        <v>11.4</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H35" t="n">
-        <v>76.59</v>
+        <v>61.31</v>
       </c>
       <c r="I35" t="n">
-        <v>77.48</v>
+        <v>62.89</v>
       </c>
       <c r="J35" t="n">
-        <v>75.81999999999999</v>
+        <v>59.57</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="M35" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16.74</v>
+        <v>17.96</v>
       </c>
       <c r="C36" t="n">
-        <v>16.81</v>
+        <v>18.97</v>
       </c>
       <c r="D36" t="n">
-        <v>16.65</v>
+        <v>17.06</v>
       </c>
       <c r="E36" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="F36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H36" t="n">
-        <v>77.14</v>
+        <v>69.53</v>
       </c>
       <c r="I36" t="n">
-        <v>77.55</v>
+        <v>74.66</v>
       </c>
       <c r="J36" t="n">
-        <v>76.81999999999999</v>
+        <v>64.09</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="N36" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16.83</v>
+        <v>16.73</v>
       </c>
       <c r="C37" t="n">
-        <v>16.93</v>
+        <v>16.97</v>
       </c>
       <c r="D37" t="n">
-        <v>16.77</v>
+        <v>16.64</v>
       </c>
       <c r="E37" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="F37" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H37" t="n">
-        <v>77.89</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>78.14</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>77.23</v>
+        <v>75.42</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M37" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="N37" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.08</v>
+        <v>16.74</v>
       </c>
       <c r="C38" t="n">
-        <v>17.24</v>
+        <v>16.83</v>
       </c>
       <c r="D38" t="n">
-        <v>16.95</v>
+        <v>16.69</v>
       </c>
       <c r="E38" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="F38" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>77.45999999999999</v>
+        <v>76.59</v>
       </c>
       <c r="I38" t="n">
-        <v>78.15000000000001</v>
+        <v>77.48</v>
       </c>
       <c r="J38" t="n">
-        <v>76.95</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="M38" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="N38" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.17</v>
+        <v>16.74</v>
       </c>
       <c r="C39" t="n">
-        <v>17.3</v>
+        <v>16.81</v>
       </c>
       <c r="D39" t="n">
-        <v>16.93</v>
+        <v>16.65</v>
       </c>
       <c r="E39" t="n">
-        <v>13.2</v>
+        <v>12.6</v>
       </c>
       <c r="F39" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>78.43000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="I39" t="n">
-        <v>81.27</v>
+        <v>77.55</v>
       </c>
       <c r="J39" t="n">
-        <v>77.08</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M39" t="n">
         <v>1.4</v>
       </c>
-      <c r="M39" t="n">
-        <v>1.7</v>
-      </c>
       <c r="N39" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.59</v>
+        <v>16.83</v>
       </c>
       <c r="C40" t="n">
-        <v>17.86</v>
+        <v>16.93</v>
       </c>
       <c r="D40" t="n">
-        <v>17.28</v>
+        <v>16.77</v>
       </c>
       <c r="E40" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="F40" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>75</v>
+        <v>77.89</v>
       </c>
       <c r="I40" t="n">
-        <v>77.95</v>
+        <v>78.14</v>
       </c>
       <c r="J40" t="n">
-        <v>73.39</v>
+        <v>77.23</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M40" t="n">
         <v>1.8</v>
       </c>
-      <c r="M40" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N40" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>18.2</v>
+        <v>17.08</v>
       </c>
       <c r="C41" t="n">
-        <v>18.41</v>
+        <v>17.24</v>
       </c>
       <c r="D41" t="n">
-        <v>18</v>
+        <v>16.95</v>
       </c>
       <c r="E41" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="F41" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>69.83</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>72.37</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>68.34</v>
+        <v>76.95</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M41" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="N41" t="n">
-        <v>6162</v>
-      </c>
-      <c r="O41" t="n">
-        <v>3.7</v>
-      </c>
+        <v>6142</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18.56</v>
+        <v>17.17</v>
       </c>
       <c r="C42" t="n">
-        <v>18.7</v>
+        <v>17.3</v>
       </c>
       <c r="D42" t="n">
-        <v>18.41</v>
+        <v>16.93</v>
       </c>
       <c r="E42" t="n">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="F42" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>67.93000000000001</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>68.55</v>
+        <v>81.27</v>
       </c>
       <c r="J42" t="n">
-        <v>67.33</v>
+        <v>77.08</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="M42" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="N42" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18.92</v>
+        <v>17.59</v>
       </c>
       <c r="C43" t="n">
-        <v>19.04</v>
+        <v>17.86</v>
       </c>
       <c r="D43" t="n">
-        <v>18.74</v>
+        <v>17.28</v>
       </c>
       <c r="E43" t="n">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="F43" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I43" t="n">
-        <v>67.08</v>
+        <v>77.95</v>
       </c>
       <c r="J43" t="n">
-        <v>65.19</v>
+        <v>73.39</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
         <v>2.6</v>
       </c>
       <c r="N43" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.98</v>
+        <v>18.2</v>
       </c>
       <c r="C44" t="n">
-        <v>19.02</v>
+        <v>18.41</v>
       </c>
       <c r="D44" t="n">
-        <v>18.95</v>
+        <v>18</v>
       </c>
       <c r="E44" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F44" t="n">
         <v>12.2</v>
@@ -2506,307 +2504,309 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>65.26000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="I44" t="n">
-        <v>65.51000000000001</v>
+        <v>72.37</v>
       </c>
       <c r="J44" t="n">
-        <v>65.09999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="N44" t="n">
-        <v>6170</v>
-      </c>
-      <c r="O44" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.27</v>
+        <v>18.56</v>
       </c>
       <c r="C45" t="n">
-        <v>19.65</v>
+        <v>18.7</v>
       </c>
       <c r="D45" t="n">
-        <v>19.01</v>
+        <v>18.41</v>
       </c>
       <c r="E45" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="F45" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>62.96</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>64.81</v>
+        <v>68.55</v>
       </c>
       <c r="J45" t="n">
-        <v>60.5</v>
+        <v>67.33</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="M45" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="N45" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 19:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.98</v>
+        <v>18.92</v>
       </c>
       <c r="C46" t="n">
-        <v>20.21</v>
+        <v>19.04</v>
       </c>
       <c r="D46" t="n">
-        <v>19.72</v>
+        <v>18.74</v>
       </c>
       <c r="E46" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="F46" t="n">
-        <v>11.3</v>
+        <v>12.2</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>58.7</v>
+        <v>66</v>
       </c>
       <c r="I46" t="n">
-        <v>59.99</v>
+        <v>67.08</v>
       </c>
       <c r="J46" t="n">
-        <v>57.42</v>
+        <v>65.19</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="M46" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="N46" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20.51</v>
+        <v>18.98</v>
       </c>
       <c r="C47" t="n">
-        <v>20.87</v>
+        <v>19.02</v>
       </c>
       <c r="D47" t="n">
-        <v>20.26</v>
+        <v>18.95</v>
       </c>
       <c r="E47" t="n">
-        <v>11.3</v>
+        <v>12.2</v>
       </c>
       <c r="F47" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="G47" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>56.48</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>57.91</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>55.61</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="N47" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>20.85</v>
+        <v>19.27</v>
       </c>
       <c r="C48" t="n">
-        <v>21.07</v>
+        <v>19.65</v>
       </c>
       <c r="D48" t="n">
-        <v>20.73</v>
+        <v>19.01</v>
       </c>
       <c r="E48" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="F48" t="n">
         <v>11.6</v>
       </c>
       <c r="G48" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>56.48</v>
+        <v>62.96</v>
       </c>
       <c r="I48" t="n">
-        <v>57.04</v>
+        <v>64.81</v>
       </c>
       <c r="J48" t="n">
-        <v>56</v>
+        <v>60.5</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="N48" t="n">
-        <v>6210</v>
+        <v>6170</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-14 19:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.96</v>
+        <v>19.98</v>
       </c>
       <c r="C49" t="n">
-        <v>21.38</v>
+        <v>20.21</v>
       </c>
       <c r="D49" t="n">
-        <v>20.75</v>
+        <v>19.72</v>
       </c>
       <c r="E49" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F49" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G49" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>56.06</v>
+        <v>58.7</v>
       </c>
       <c r="I49" t="n">
-        <v>56.71</v>
+        <v>59.99</v>
       </c>
       <c r="J49" t="n">
-        <v>54.86</v>
+        <v>57.42</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="N49" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00:00</t>
+          <t>2026-10-14 18:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>21.55</v>
+        <v>20.51</v>
       </c>
       <c r="C50" t="n">
-        <v>21.81</v>
+        <v>20.87</v>
       </c>
       <c r="D50" t="n">
-        <v>21.14</v>
+        <v>20.26</v>
       </c>
       <c r="E50" t="n">
         <v>11.3</v>
       </c>
       <c r="F50" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="G50" t="n">
-        <v>296</v>
+        <v>47</v>
       </c>
       <c r="H50" t="n">
-        <v>53.03</v>
+        <v>56.48</v>
       </c>
       <c r="I50" t="n">
-        <v>54.48</v>
+        <v>57.91</v>
       </c>
       <c r="J50" t="n">
-        <v>51.56</v>
+        <v>55.61</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M50" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>6220</v>
+        <v>6190</v>
       </c>
       <c r="O50" t="n">
         <v>2.5</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,129 +508,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.83</v>
+        <v>20.55</v>
       </c>
       <c r="C2" t="n">
-        <v>22.85</v>
+        <v>20.64</v>
       </c>
       <c r="D2" t="n">
-        <v>22.81</v>
+        <v>20.48</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="F2" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="G2" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>48.9</v>
+        <v>57.78</v>
       </c>
       <c r="I2" t="n">
-        <v>48.98</v>
+        <v>58.1</v>
       </c>
       <c r="J2" t="n">
-        <v>48.79</v>
+        <v>57.52</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>6210</v>
+        <v>6162</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.26</v>
+        <v>20.99</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>21.3</v>
       </c>
       <c r="D3" t="n">
-        <v>22.73</v>
+        <v>20.64</v>
       </c>
       <c r="E3" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F3" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="G3" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>47.55</v>
+        <v>55.76</v>
       </c>
       <c r="I3" t="n">
-        <v>48.93</v>
+        <v>57.26</v>
       </c>
       <c r="J3" t="n">
-        <v>45.68</v>
+        <v>54.28</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N3" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.81</v>
+        <v>21.82</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>22.25</v>
       </c>
       <c r="D4" t="n">
-        <v>21.97</v>
+        <v>21.38</v>
       </c>
       <c r="E4" t="n">
         <v>11.4</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="G4" t="n">
-        <v>373</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>49.12</v>
+        <v>52.03</v>
       </c>
       <c r="I4" t="n">
-        <v>52.45</v>
+        <v>53.83</v>
       </c>
       <c r="J4" t="n">
-        <v>45.39</v>
+        <v>50.23</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -639,195 +639,195 @@
         <v>0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.82</v>
+        <v>22.61</v>
       </c>
       <c r="C5" t="n">
-        <v>21.95</v>
+        <v>22.85</v>
       </c>
       <c r="D5" t="n">
-        <v>21.73</v>
+        <v>22.34</v>
       </c>
       <c r="E5" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F5" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="H5" t="n">
-        <v>52.7</v>
+        <v>49.28</v>
       </c>
       <c r="I5" t="n">
-        <v>52.97</v>
+        <v>50.37</v>
       </c>
       <c r="J5" t="n">
-        <v>52.47</v>
+        <v>48.38</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="N5" t="n">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.74</v>
+        <v>23.26</v>
       </c>
       <c r="C6" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>21.56</v>
+        <v>22.73</v>
       </c>
       <c r="E6" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="F6" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="G6" t="n">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="H6" t="n">
-        <v>52.76</v>
+        <v>47.55</v>
       </c>
       <c r="I6" t="n">
-        <v>53.57</v>
+        <v>48.93</v>
       </c>
       <c r="J6" t="n">
-        <v>52.06</v>
+        <v>45.68</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.42</v>
+        <v>22.81</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>20.92</v>
+        <v>21.97</v>
       </c>
       <c r="E7" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>218</v>
+        <v>373</v>
       </c>
       <c r="H7" t="n">
-        <v>54.49</v>
+        <v>49.12</v>
       </c>
       <c r="I7" t="n">
-        <v>56.38</v>
+        <v>52.45</v>
       </c>
       <c r="J7" t="n">
-        <v>52.2</v>
+        <v>45.39</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N7" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.35</v>
+        <v>21.82</v>
       </c>
       <c r="C8" t="n">
-        <v>22.22</v>
+        <v>21.95</v>
       </c>
       <c r="D8" t="n">
-        <v>20.87</v>
+        <v>21.73</v>
       </c>
       <c r="E8" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F8" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G8" t="n">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="H8" t="n">
-        <v>55.07</v>
+        <v>52.7</v>
       </c>
       <c r="I8" t="n">
-        <v>56.71</v>
+        <v>52.97</v>
       </c>
       <c r="J8" t="n">
-        <v>52.16</v>
+        <v>52.47</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="N8" t="n">
         <v>6190</v>
@@ -837,252 +837,252 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.1</v>
+        <v>21.74</v>
       </c>
       <c r="C9" t="n">
-        <v>21.69</v>
+        <v>21.95</v>
       </c>
       <c r="D9" t="n">
-        <v>20.51</v>
+        <v>21.56</v>
       </c>
       <c r="E9" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="F9" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G9" t="n">
-        <v>480</v>
+        <v>165</v>
       </c>
       <c r="H9" t="n">
-        <v>55.96</v>
+        <v>52.76</v>
       </c>
       <c r="I9" t="n">
-        <v>58.01</v>
+        <v>53.57</v>
       </c>
       <c r="J9" t="n">
-        <v>53.81</v>
+        <v>52.06</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="N9" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20.15</v>
+        <v>21.42</v>
       </c>
       <c r="C10" t="n">
-        <v>20.85</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>19.57</v>
+        <v>20.92</v>
       </c>
       <c r="E10" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="F10" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G10" t="n">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="H10" t="n">
-        <v>60.77</v>
+        <v>54.49</v>
       </c>
       <c r="I10" t="n">
-        <v>64.81</v>
+        <v>56.38</v>
       </c>
       <c r="J10" t="n">
-        <v>56.73</v>
+        <v>52.2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.37</v>
+        <v>21.35</v>
       </c>
       <c r="C11" t="n">
-        <v>19.79</v>
+        <v>22.22</v>
       </c>
       <c r="D11" t="n">
-        <v>18.91</v>
+        <v>20.87</v>
       </c>
       <c r="E11" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F11" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G11" t="n">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="H11" t="n">
-        <v>65.04000000000001</v>
+        <v>55.07</v>
       </c>
       <c r="I11" t="n">
-        <v>66.98999999999999</v>
+        <v>56.71</v>
       </c>
       <c r="J11" t="n">
-        <v>63.19</v>
+        <v>52.16</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N11" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.41</v>
+        <v>21.1</v>
       </c>
       <c r="C12" t="n">
-        <v>18.85</v>
+        <v>21.69</v>
       </c>
       <c r="D12" t="n">
-        <v>18.05</v>
+        <v>20.51</v>
       </c>
       <c r="E12" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F12" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G12" t="n">
-        <v>76</v>
+        <v>480</v>
       </c>
       <c r="H12" t="n">
-        <v>69.37</v>
+        <v>55.96</v>
       </c>
       <c r="I12" t="n">
-        <v>71.67</v>
+        <v>58.01</v>
       </c>
       <c r="J12" t="n">
-        <v>67.22</v>
+        <v>53.81</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>6170</v>
+        <v>6210</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.66</v>
+        <v>20.15</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95</v>
+        <v>20.85</v>
       </c>
       <c r="D13" t="n">
-        <v>17.51</v>
+        <v>19.57</v>
       </c>
       <c r="E13" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="F13" t="n">
-        <v>12.6</v>
+        <v>11.6</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>266</v>
       </c>
       <c r="H13" t="n">
-        <v>73.31</v>
+        <v>60.77</v>
       </c>
       <c r="I13" t="n">
-        <v>74.14</v>
+        <v>64.81</v>
       </c>
       <c r="J13" t="n">
-        <v>72.19</v>
+        <v>56.73</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="N13" t="n">
-        <v>6162</v>
+        <v>6200</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.6</v>
+        <v>19.37</v>
       </c>
       <c r="C14" t="n">
-        <v>17.68</v>
+        <v>19.79</v>
       </c>
       <c r="D14" t="n">
-        <v>17.49</v>
+        <v>18.91</v>
       </c>
       <c r="E14" t="n">
         <v>12.4</v>
@@ -1091,110 +1091,110 @@
         <v>12.3</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="H14" t="n">
-        <v>72.5</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>73.76000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>71.78</v>
+        <v>63.19</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="N14" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.53</v>
+        <v>18.41</v>
       </c>
       <c r="C15" t="n">
-        <v>17.62</v>
+        <v>18.85</v>
       </c>
       <c r="D15" t="n">
-        <v>17.45</v>
+        <v>18.05</v>
       </c>
       <c r="E15" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F15" t="n">
         <v>12.4</v>
       </c>
-      <c r="F15" t="n">
-        <v>12.2</v>
-      </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H15" t="n">
-        <v>72.33</v>
+        <v>69.37</v>
       </c>
       <c r="I15" t="n">
-        <v>72.88</v>
+        <v>71.67</v>
       </c>
       <c r="J15" t="n">
-        <v>71.93000000000001</v>
+        <v>67.22</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="N15" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.64</v>
+        <v>17.66</v>
       </c>
       <c r="C16" t="n">
-        <v>17.9</v>
+        <v>17.95</v>
       </c>
       <c r="D16" t="n">
-        <v>17.44</v>
+        <v>17.51</v>
       </c>
       <c r="E16" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>71.73999999999999</v>
+        <v>73.31</v>
       </c>
       <c r="I16" t="n">
-        <v>73.59999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="J16" t="n">
-        <v>69.53</v>
+        <v>72.19</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1203,195 +1203,195 @@
         <v>0.3</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="N16" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.84</v>
+        <v>17.6</v>
       </c>
       <c r="C17" t="n">
-        <v>17.88</v>
+        <v>17.68</v>
       </c>
       <c r="D17" t="n">
-        <v>17.8</v>
+        <v>17.49</v>
       </c>
       <c r="E17" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>70.06999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I17" t="n">
-        <v>70.3</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>69.65000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="N17" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.9</v>
+        <v>17.53</v>
       </c>
       <c r="C18" t="n">
-        <v>17.97</v>
+        <v>17.62</v>
       </c>
       <c r="D18" t="n">
-        <v>17.82</v>
+        <v>17.45</v>
       </c>
       <c r="E18" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>69.79000000000001</v>
+        <v>72.33</v>
       </c>
       <c r="I18" t="n">
-        <v>70.48999999999999</v>
+        <v>72.88</v>
       </c>
       <c r="J18" t="n">
-        <v>69.43000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N18" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.74</v>
+        <v>17.64</v>
       </c>
       <c r="C19" t="n">
-        <v>17.82</v>
+        <v>17.9</v>
       </c>
       <c r="D19" t="n">
-        <v>17.7</v>
+        <v>17.44</v>
       </c>
       <c r="E19" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F19" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>70.81999999999999</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>70.98</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>70.54000000000001</v>
+        <v>69.53</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M19" t="n">
         <v>1.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.68</v>
+        <v>17.84</v>
       </c>
       <c r="C20" t="n">
-        <v>17.71</v>
+        <v>17.88</v>
       </c>
       <c r="D20" t="n">
-        <v>17.64</v>
+        <v>17.8</v>
       </c>
       <c r="E20" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F20" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>71.42</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>71.8</v>
+        <v>70.3</v>
       </c>
       <c r="J20" t="n">
-        <v>71.13</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N20" t="n">
         <v>6162</v>
@@ -1401,299 +1401,299 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.74</v>
+        <v>17.9</v>
       </c>
       <c r="C21" t="n">
-        <v>17.78</v>
+        <v>17.97</v>
       </c>
       <c r="D21" t="n">
-        <v>17.68</v>
+        <v>17.82</v>
       </c>
       <c r="E21" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F21" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>71.53</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>72.06999999999999</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>70.67</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N21" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18.17</v>
+        <v>17.74</v>
       </c>
       <c r="C22" t="n">
-        <v>18.45</v>
+        <v>17.82</v>
       </c>
       <c r="D22" t="n">
-        <v>17.85</v>
+        <v>17.7</v>
       </c>
       <c r="E22" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="F22" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>67.5</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>70.09</v>
+        <v>70.98</v>
       </c>
       <c r="J22" t="n">
-        <v>65.53</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N22" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.12</v>
+        <v>17.68</v>
       </c>
       <c r="C23" t="n">
-        <v>19.48</v>
+        <v>17.71</v>
       </c>
       <c r="D23" t="n">
-        <v>18.59</v>
+        <v>17.64</v>
       </c>
       <c r="E23" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="F23" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>62.25</v>
+        <v>71.42</v>
       </c>
       <c r="I23" t="n">
-        <v>64.8</v>
+        <v>71.8</v>
       </c>
       <c r="J23" t="n">
-        <v>60.27</v>
+        <v>71.13</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.89</v>
+        <v>17.74</v>
       </c>
       <c r="C24" t="n">
-        <v>20.2</v>
+        <v>17.78</v>
       </c>
       <c r="D24" t="n">
-        <v>19.54</v>
+        <v>17.68</v>
       </c>
       <c r="E24" t="n">
-        <v>11.2</v>
+        <v>12.4</v>
       </c>
       <c r="F24" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>58.12</v>
+        <v>71.53</v>
       </c>
       <c r="I24" t="n">
-        <v>59.88</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>56.65</v>
+        <v>70.67</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20.59</v>
+        <v>18.17</v>
       </c>
       <c r="C25" t="n">
-        <v>21.02</v>
+        <v>18.45</v>
       </c>
       <c r="D25" t="n">
-        <v>20.23</v>
+        <v>17.85</v>
       </c>
       <c r="E25" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>55.26</v>
+        <v>67.5</v>
       </c>
       <c r="I25" t="n">
-        <v>56.46</v>
+        <v>70.09</v>
       </c>
       <c r="J25" t="n">
-        <v>54.02</v>
+        <v>65.53</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M25" t="n">
         <v>2</v>
       </c>
-      <c r="M25" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N25" t="n">
-        <v>6200</v>
+        <v>6152</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21.34</v>
+        <v>19.12</v>
       </c>
       <c r="C26" t="n">
-        <v>21.65</v>
+        <v>19.48</v>
       </c>
       <c r="D26" t="n">
-        <v>20.98</v>
+        <v>18.59</v>
       </c>
       <c r="E26" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="G26" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>52.89</v>
+        <v>62.25</v>
       </c>
       <c r="I26" t="n">
-        <v>53.97</v>
+        <v>64.8</v>
       </c>
       <c r="J26" t="n">
-        <v>51.51</v>
+        <v>60.27</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="M26" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="N26" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22.22</v>
+        <v>19.89</v>
       </c>
       <c r="C27" t="n">
-        <v>22.72</v>
+        <v>20.2</v>
       </c>
       <c r="D27" t="n">
-        <v>21.71</v>
+        <v>19.54</v>
       </c>
       <c r="E27" t="n">
         <v>11.2</v>
@@ -1702,166 +1702,166 @@
         <v>11.1</v>
       </c>
       <c r="G27" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>50.44</v>
+        <v>58.12</v>
       </c>
       <c r="I27" t="n">
-        <v>51.7</v>
+        <v>59.88</v>
       </c>
       <c r="J27" t="n">
-        <v>49.53</v>
+        <v>56.65</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="N27" t="n">
-        <v>6240</v>
+        <v>6190</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22.94</v>
+        <v>20.59</v>
       </c>
       <c r="C28" t="n">
-        <v>23.82</v>
+        <v>21.02</v>
       </c>
       <c r="D28" t="n">
-        <v>22.29</v>
+        <v>20.23</v>
       </c>
       <c r="E28" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="F28" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>355</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>46.37</v>
+        <v>55.26</v>
       </c>
       <c r="I28" t="n">
-        <v>49.68</v>
+        <v>56.46</v>
       </c>
       <c r="J28" t="n">
-        <v>44.22</v>
+        <v>54.02</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N28" t="n">
-        <v>6250</v>
+        <v>6200</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23.12</v>
+        <v>21.34</v>
       </c>
       <c r="C29" t="n">
-        <v>24.14</v>
+        <v>21.65</v>
       </c>
       <c r="D29" t="n">
-        <v>22.72</v>
+        <v>20.98</v>
       </c>
       <c r="E29" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F29" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>344</v>
+        <v>63</v>
       </c>
       <c r="H29" t="n">
-        <v>45.59</v>
+        <v>52.89</v>
       </c>
       <c r="I29" t="n">
-        <v>46.9</v>
+        <v>53.97</v>
       </c>
       <c r="J29" t="n">
-        <v>43.18</v>
+        <v>51.51</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="N29" t="n">
-        <v>6240</v>
+        <v>6220</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.76</v>
+        <v>22.22</v>
       </c>
       <c r="C30" t="n">
-        <v>23.63</v>
+        <v>22.72</v>
       </c>
       <c r="D30" t="n">
-        <v>22.08</v>
+        <v>21.71</v>
       </c>
       <c r="E30" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="F30" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="G30" t="n">
-        <v>462</v>
+        <v>210</v>
       </c>
       <c r="H30" t="n">
-        <v>47.51</v>
+        <v>50.44</v>
       </c>
       <c r="I30" t="n">
-        <v>49.36</v>
+        <v>51.7</v>
       </c>
       <c r="J30" t="n">
-        <v>46.08</v>
+        <v>49.53</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
         <v>6240</v>
@@ -1871,774 +1871,772 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22.55</v>
+        <v>22.94</v>
       </c>
       <c r="C31" t="n">
-        <v>23.29</v>
+        <v>23.82</v>
       </c>
       <c r="D31" t="n">
-        <v>21.68</v>
+        <v>22.29</v>
       </c>
       <c r="E31" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="F31" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="G31" t="n">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H31" t="n">
-        <v>47.88</v>
+        <v>46.37</v>
       </c>
       <c r="I31" t="n">
-        <v>50.32</v>
+        <v>49.68</v>
       </c>
       <c r="J31" t="n">
-        <v>46.13</v>
+        <v>44.22</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>6220</v>
+        <v>6250</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22.47</v>
+        <v>23.12</v>
       </c>
       <c r="C32" t="n">
-        <v>23.42</v>
+        <v>24.14</v>
       </c>
       <c r="D32" t="n">
-        <v>21.73</v>
+        <v>22.72</v>
       </c>
       <c r="E32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="F32" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="G32" t="n">
-        <v>531</v>
+        <v>344</v>
       </c>
       <c r="H32" t="n">
-        <v>49.09</v>
+        <v>45.59</v>
       </c>
       <c r="I32" t="n">
-        <v>51.32</v>
+        <v>46.9</v>
       </c>
       <c r="J32" t="n">
-        <v>46.18</v>
+        <v>43.18</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>6230</v>
+        <v>6240</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21.72</v>
+        <v>22.76</v>
       </c>
       <c r="C33" t="n">
-        <v>23.46</v>
+        <v>23.63</v>
       </c>
       <c r="D33" t="n">
-        <v>20.79</v>
+        <v>22.08</v>
       </c>
       <c r="E33" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G33" t="n">
-        <v>616</v>
+        <v>462</v>
       </c>
       <c r="H33" t="n">
-        <v>52.51</v>
+        <v>47.51</v>
       </c>
       <c r="I33" t="n">
-        <v>55.76</v>
+        <v>49.36</v>
       </c>
       <c r="J33" t="n">
-        <v>47.65</v>
+        <v>46.08</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>6220</v>
+        <v>6240</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>20.86</v>
+        <v>22.55</v>
       </c>
       <c r="C34" t="n">
-        <v>21.56</v>
+        <v>23.29</v>
       </c>
       <c r="D34" t="n">
-        <v>20.25</v>
+        <v>21.68</v>
       </c>
       <c r="E34" t="n">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="F34" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G34" t="n">
-        <v>642</v>
+        <v>364</v>
       </c>
       <c r="H34" t="n">
-        <v>56.36</v>
+        <v>47.88</v>
       </c>
       <c r="I34" t="n">
-        <v>59</v>
+        <v>50.32</v>
       </c>
       <c r="J34" t="n">
-        <v>53.69</v>
+        <v>46.13</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.5</v>
+        <v>22.47</v>
       </c>
       <c r="C35" t="n">
-        <v>19.99</v>
+        <v>23.42</v>
       </c>
       <c r="D35" t="n">
-        <v>19.01</v>
+        <v>21.73</v>
       </c>
       <c r="E35" t="n">
-        <v>11.7</v>
+        <v>11</v>
       </c>
       <c r="F35" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="G35" t="n">
-        <v>341</v>
+        <v>531</v>
       </c>
       <c r="H35" t="n">
-        <v>61.31</v>
+        <v>49.09</v>
       </c>
       <c r="I35" t="n">
-        <v>62.89</v>
+        <v>51.32</v>
       </c>
       <c r="J35" t="n">
-        <v>59.57</v>
+        <v>46.18</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M35" t="n">
         <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>6190</v>
+        <v>6230</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.96</v>
+        <v>21.72</v>
       </c>
       <c r="C36" t="n">
-        <v>18.97</v>
+        <v>23.46</v>
       </c>
       <c r="D36" t="n">
-        <v>17.06</v>
+        <v>20.79</v>
       </c>
       <c r="E36" t="n">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="F36" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="G36" t="n">
-        <v>158</v>
+        <v>616</v>
       </c>
       <c r="H36" t="n">
-        <v>69.53</v>
+        <v>52.51</v>
       </c>
       <c r="I36" t="n">
-        <v>74.66</v>
+        <v>55.76</v>
       </c>
       <c r="J36" t="n">
-        <v>64.09</v>
+        <v>47.65</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="M36" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>6180</v>
+        <v>6220</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16.73</v>
+        <v>20.86</v>
       </c>
       <c r="C37" t="n">
-        <v>16.97</v>
+        <v>21.56</v>
       </c>
       <c r="D37" t="n">
-        <v>16.64</v>
+        <v>20.25</v>
       </c>
       <c r="E37" t="n">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="F37" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G37" t="n">
-        <v>33</v>
+        <v>642</v>
       </c>
       <c r="H37" t="n">
-        <v>76.20999999999999</v>
+        <v>56.36</v>
       </c>
       <c r="I37" t="n">
-        <v>76.59999999999999</v>
+        <v>59</v>
       </c>
       <c r="J37" t="n">
-        <v>75.42</v>
+        <v>53.69</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.74</v>
+        <v>19.5</v>
       </c>
       <c r="C38" t="n">
-        <v>16.83</v>
+        <v>19.99</v>
       </c>
       <c r="D38" t="n">
-        <v>16.69</v>
+        <v>19.01</v>
       </c>
       <c r="E38" t="n">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="F38" t="n">
-        <v>12.3</v>
+        <v>11.4</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H38" t="n">
-        <v>76.59</v>
+        <v>61.31</v>
       </c>
       <c r="I38" t="n">
-        <v>77.48</v>
+        <v>62.89</v>
       </c>
       <c r="J38" t="n">
-        <v>75.81999999999999</v>
+        <v>59.57</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="M38" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.74</v>
+        <v>17.96</v>
       </c>
       <c r="C39" t="n">
-        <v>16.81</v>
+        <v>18.97</v>
       </c>
       <c r="D39" t="n">
-        <v>16.65</v>
+        <v>17.06</v>
       </c>
       <c r="E39" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="F39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H39" t="n">
-        <v>77.14</v>
+        <v>69.53</v>
       </c>
       <c r="I39" t="n">
-        <v>77.55</v>
+        <v>74.66</v>
       </c>
       <c r="J39" t="n">
-        <v>76.81999999999999</v>
+        <v>64.09</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="N39" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.83</v>
+        <v>16.73</v>
       </c>
       <c r="C40" t="n">
-        <v>16.93</v>
+        <v>16.97</v>
       </c>
       <c r="D40" t="n">
-        <v>16.77</v>
+        <v>16.64</v>
       </c>
       <c r="E40" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="F40" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H40" t="n">
-        <v>77.89</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>78.14</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>77.23</v>
+        <v>75.42</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M40" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="N40" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.08</v>
+        <v>16.74</v>
       </c>
       <c r="C41" t="n">
-        <v>17.24</v>
+        <v>16.83</v>
       </c>
       <c r="D41" t="n">
-        <v>16.95</v>
+        <v>16.69</v>
       </c>
       <c r="E41" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="F41" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>77.45999999999999</v>
+        <v>76.59</v>
       </c>
       <c r="I41" t="n">
-        <v>78.15000000000001</v>
+        <v>77.48</v>
       </c>
       <c r="J41" t="n">
-        <v>76.95</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="M41" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="N41" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.17</v>
+        <v>16.74</v>
       </c>
       <c r="C42" t="n">
-        <v>17.3</v>
+        <v>16.81</v>
       </c>
       <c r="D42" t="n">
-        <v>16.93</v>
+        <v>16.65</v>
       </c>
       <c r="E42" t="n">
-        <v>13.2</v>
+        <v>12.6</v>
       </c>
       <c r="F42" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>78.43000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="I42" t="n">
-        <v>81.27</v>
+        <v>77.55</v>
       </c>
       <c r="J42" t="n">
-        <v>77.08</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M42" t="n">
         <v>1.4</v>
       </c>
-      <c r="M42" t="n">
-        <v>1.7</v>
-      </c>
       <c r="N42" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.59</v>
+        <v>16.83</v>
       </c>
       <c r="C43" t="n">
-        <v>17.86</v>
+        <v>16.93</v>
       </c>
       <c r="D43" t="n">
-        <v>17.28</v>
+        <v>16.77</v>
       </c>
       <c r="E43" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="F43" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>75</v>
+        <v>77.89</v>
       </c>
       <c r="I43" t="n">
-        <v>77.95</v>
+        <v>78.14</v>
       </c>
       <c r="J43" t="n">
-        <v>73.39</v>
+        <v>77.23</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M43" t="n">
         <v>1.8</v>
       </c>
-      <c r="M43" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N43" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.2</v>
+        <v>17.08</v>
       </c>
       <c r="C44" t="n">
-        <v>18.41</v>
+        <v>17.24</v>
       </c>
       <c r="D44" t="n">
-        <v>18</v>
+        <v>16.95</v>
       </c>
       <c r="E44" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="F44" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>69.83</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>72.37</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>68.34</v>
+        <v>76.95</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M44" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="N44" t="n">
-        <v>6162</v>
-      </c>
-      <c r="O44" t="n">
-        <v>3.7</v>
-      </c>
+        <v>6142</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>18.56</v>
+        <v>17.17</v>
       </c>
       <c r="C45" t="n">
-        <v>18.7</v>
+        <v>17.3</v>
       </c>
       <c r="D45" t="n">
-        <v>18.41</v>
+        <v>16.93</v>
       </c>
       <c r="E45" t="n">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="F45" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>67.93000000000001</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>68.55</v>
+        <v>81.27</v>
       </c>
       <c r="J45" t="n">
-        <v>67.33</v>
+        <v>77.08</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="M45" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="N45" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18.92</v>
+        <v>17.59</v>
       </c>
       <c r="C46" t="n">
-        <v>19.04</v>
+        <v>17.86</v>
       </c>
       <c r="D46" t="n">
-        <v>18.74</v>
+        <v>17.28</v>
       </c>
       <c r="E46" t="n">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="F46" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I46" t="n">
-        <v>67.08</v>
+        <v>77.95</v>
       </c>
       <c r="J46" t="n">
-        <v>65.19</v>
+        <v>73.39</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
         <v>2.6</v>
       </c>
       <c r="N46" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>18.98</v>
+        <v>18.2</v>
       </c>
       <c r="C47" t="n">
-        <v>19.02</v>
+        <v>18.41</v>
       </c>
       <c r="D47" t="n">
-        <v>18.95</v>
+        <v>18</v>
       </c>
       <c r="E47" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F47" t="n">
         <v>12.2</v>
@@ -2647,166 +2645,168 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>65.26000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="I47" t="n">
-        <v>65.51000000000001</v>
+        <v>72.37</v>
       </c>
       <c r="J47" t="n">
-        <v>65.09999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M47" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="N47" t="n">
-        <v>6170</v>
-      </c>
-      <c r="O47" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O47" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19.27</v>
+        <v>18.56</v>
       </c>
       <c r="C48" t="n">
-        <v>19.65</v>
+        <v>18.7</v>
       </c>
       <c r="D48" t="n">
-        <v>19.01</v>
+        <v>18.41</v>
       </c>
       <c r="E48" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="F48" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>62.96</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>64.81</v>
+        <v>68.55</v>
       </c>
       <c r="J48" t="n">
-        <v>60.5</v>
+        <v>67.33</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="M48" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="N48" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 19:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19.98</v>
+        <v>18.92</v>
       </c>
       <c r="C49" t="n">
-        <v>20.21</v>
+        <v>19.04</v>
       </c>
       <c r="D49" t="n">
-        <v>19.72</v>
+        <v>18.74</v>
       </c>
       <c r="E49" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="F49" t="n">
-        <v>11.3</v>
+        <v>12.2</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>58.7</v>
+        <v>66</v>
       </c>
       <c r="I49" t="n">
-        <v>59.99</v>
+        <v>67.08</v>
       </c>
       <c r="J49" t="n">
-        <v>57.42</v>
+        <v>65.19</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="N49" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>20.51</v>
+        <v>18.98</v>
       </c>
       <c r="C50" t="n">
-        <v>20.87</v>
+        <v>19.02</v>
       </c>
       <c r="D50" t="n">
-        <v>20.26</v>
+        <v>18.95</v>
       </c>
       <c r="E50" t="n">
-        <v>11.3</v>
+        <v>12.2</v>
       </c>
       <c r="F50" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="G50" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>56.48</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>57.91</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>55.61</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="N50" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O50" t="n">
         <v>2.5</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,35 +508,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.55</v>
+        <v>19.51</v>
       </c>
       <c r="C2" t="n">
-        <v>20.64</v>
+        <v>19.57</v>
       </c>
       <c r="D2" t="n">
-        <v>20.48</v>
+        <v>19.47</v>
       </c>
       <c r="E2" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F2" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>57.78</v>
+        <v>60.52</v>
       </c>
       <c r="I2" t="n">
-        <v>58.1</v>
+        <v>60.64</v>
       </c>
       <c r="J2" t="n">
-        <v>57.52</v>
+        <v>60.39</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -548,277 +548,277 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.99</v>
+        <v>19.62</v>
       </c>
       <c r="C3" t="n">
-        <v>21.3</v>
+        <v>19.71</v>
       </c>
       <c r="D3" t="n">
-        <v>20.64</v>
+        <v>19.49</v>
       </c>
       <c r="E3" t="n">
         <v>11.6</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>55.76</v>
+        <v>60.63</v>
       </c>
       <c r="I3" t="n">
-        <v>57.26</v>
+        <v>61.71</v>
       </c>
       <c r="J3" t="n">
-        <v>54.28</v>
+        <v>59.73</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.82</v>
+        <v>19.79</v>
       </c>
       <c r="C4" t="n">
-        <v>22.25</v>
+        <v>20.01</v>
       </c>
       <c r="D4" t="n">
-        <v>21.38</v>
+        <v>19.61</v>
       </c>
       <c r="E4" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="F4" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>52.03</v>
+        <v>60.18</v>
       </c>
       <c r="I4" t="n">
-        <v>53.83</v>
+        <v>61.23</v>
       </c>
       <c r="J4" t="n">
-        <v>50.23</v>
+        <v>59.04</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="N4" t="n">
-        <v>6180</v>
+        <v>6142</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.61</v>
+        <v>20.19</v>
       </c>
       <c r="C5" t="n">
-        <v>22.85</v>
+        <v>20.36</v>
       </c>
       <c r="D5" t="n">
-        <v>22.34</v>
+        <v>20.01</v>
       </c>
       <c r="E5" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>49.28</v>
+        <v>58.19</v>
       </c>
       <c r="I5" t="n">
-        <v>50.37</v>
+        <v>59.14</v>
       </c>
       <c r="J5" t="n">
-        <v>48.38</v>
+        <v>57.54</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="N5" t="n">
-        <v>6200</v>
+        <v>6132</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.26</v>
+        <v>20.44</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>20.64</v>
       </c>
       <c r="D6" t="n">
-        <v>22.73</v>
+        <v>20.37</v>
       </c>
       <c r="E6" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="F6" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="G6" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>47.55</v>
+        <v>57.96</v>
       </c>
       <c r="I6" t="n">
-        <v>48.93</v>
+        <v>58.31</v>
       </c>
       <c r="J6" t="n">
-        <v>45.68</v>
+        <v>57.52</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.81</v>
+        <v>20.99</v>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>21.3</v>
       </c>
       <c r="D7" t="n">
-        <v>21.97</v>
+        <v>20.64</v>
       </c>
       <c r="E7" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G7" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>49.12</v>
+        <v>55.76</v>
       </c>
       <c r="I7" t="n">
-        <v>52.45</v>
+        <v>57.26</v>
       </c>
       <c r="J7" t="n">
-        <v>45.39</v>
+        <v>54.28</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="N7" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>21.82</v>
       </c>
       <c r="C8" t="n">
-        <v>21.95</v>
+        <v>22.25</v>
       </c>
       <c r="D8" t="n">
-        <v>21.73</v>
+        <v>21.38</v>
       </c>
       <c r="E8" t="n">
         <v>11.4</v>
       </c>
       <c r="F8" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G8" t="n">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>52.7</v>
+        <v>52.03</v>
       </c>
       <c r="I8" t="n">
-        <v>52.97</v>
+        <v>53.83</v>
       </c>
       <c r="J8" t="n">
-        <v>52.47</v>
+        <v>50.23</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -827,571 +827,571 @@
         <v>0.7</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.74</v>
+        <v>22.61</v>
       </c>
       <c r="C9" t="n">
-        <v>21.95</v>
+        <v>22.85</v>
       </c>
       <c r="D9" t="n">
-        <v>21.56</v>
+        <v>22.34</v>
       </c>
       <c r="E9" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="F9" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="H9" t="n">
-        <v>52.76</v>
+        <v>49.28</v>
       </c>
       <c r="I9" t="n">
-        <v>53.57</v>
+        <v>50.37</v>
       </c>
       <c r="J9" t="n">
-        <v>52.06</v>
+        <v>48.38</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="N9" t="n">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.42</v>
+        <v>23.26</v>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>20.92</v>
+        <v>22.73</v>
       </c>
       <c r="E10" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="F10" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="G10" t="n">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="H10" t="n">
-        <v>54.49</v>
+        <v>47.55</v>
       </c>
       <c r="I10" t="n">
-        <v>56.38</v>
+        <v>48.93</v>
       </c>
       <c r="J10" t="n">
-        <v>52.2</v>
+        <v>45.68</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.35</v>
+        <v>22.81</v>
       </c>
       <c r="C11" t="n">
-        <v>22.22</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>20.87</v>
+        <v>21.97</v>
       </c>
       <c r="E11" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>238</v>
+        <v>373</v>
       </c>
       <c r="H11" t="n">
-        <v>55.07</v>
+        <v>49.12</v>
       </c>
       <c r="I11" t="n">
-        <v>56.71</v>
+        <v>52.45</v>
       </c>
       <c r="J11" t="n">
-        <v>52.16</v>
+        <v>45.39</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="N11" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21.1</v>
+        <v>21.82</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69</v>
+        <v>21.95</v>
       </c>
       <c r="D12" t="n">
-        <v>20.51</v>
+        <v>21.73</v>
       </c>
       <c r="E12" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F12" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G12" t="n">
-        <v>480</v>
+        <v>146</v>
       </c>
       <c r="H12" t="n">
-        <v>55.96</v>
+        <v>52.7</v>
       </c>
       <c r="I12" t="n">
-        <v>58.01</v>
+        <v>52.97</v>
       </c>
       <c r="J12" t="n">
-        <v>53.81</v>
+        <v>52.47</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="N12" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20.15</v>
+        <v>21.74</v>
       </c>
       <c r="C13" t="n">
-        <v>20.85</v>
+        <v>21.95</v>
       </c>
       <c r="D13" t="n">
-        <v>19.57</v>
+        <v>21.56</v>
       </c>
       <c r="E13" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="F13" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G13" t="n">
-        <v>266</v>
+        <v>165</v>
       </c>
       <c r="H13" t="n">
-        <v>60.77</v>
+        <v>52.76</v>
       </c>
       <c r="I13" t="n">
-        <v>64.81</v>
+        <v>53.57</v>
       </c>
       <c r="J13" t="n">
-        <v>56.73</v>
+        <v>52.06</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="N13" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19.37</v>
+        <v>21.42</v>
       </c>
       <c r="C14" t="n">
-        <v>19.79</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>18.91</v>
+        <v>20.92</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="F14" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G14" t="n">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="H14" t="n">
-        <v>65.04000000000001</v>
+        <v>54.49</v>
       </c>
       <c r="I14" t="n">
-        <v>66.98999999999999</v>
+        <v>56.38</v>
       </c>
       <c r="J14" t="n">
-        <v>63.19</v>
+        <v>52.2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18.41</v>
+        <v>21.35</v>
       </c>
       <c r="C15" t="n">
-        <v>18.85</v>
+        <v>22.22</v>
       </c>
       <c r="D15" t="n">
-        <v>18.05</v>
+        <v>20.87</v>
       </c>
       <c r="E15" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F15" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="H15" t="n">
-        <v>69.37</v>
+        <v>55.07</v>
       </c>
       <c r="I15" t="n">
-        <v>71.67</v>
+        <v>56.71</v>
       </c>
       <c r="J15" t="n">
-        <v>67.22</v>
+        <v>52.16</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="N15" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.66</v>
+        <v>21.1</v>
       </c>
       <c r="C16" t="n">
-        <v>17.95</v>
+        <v>21.69</v>
       </c>
       <c r="D16" t="n">
-        <v>17.51</v>
+        <v>20.51</v>
       </c>
       <c r="E16" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="F16" t="n">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>480</v>
       </c>
       <c r="H16" t="n">
-        <v>73.31</v>
+        <v>55.96</v>
       </c>
       <c r="I16" t="n">
-        <v>74.14</v>
+        <v>58.01</v>
       </c>
       <c r="J16" t="n">
-        <v>72.19</v>
+        <v>53.81</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>6162</v>
+        <v>6210</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.6</v>
+        <v>20.15</v>
       </c>
       <c r="C17" t="n">
-        <v>17.68</v>
+        <v>20.85</v>
       </c>
       <c r="D17" t="n">
-        <v>17.49</v>
+        <v>19.57</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F17" t="n">
-        <v>12.3</v>
+        <v>11.6</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="H17" t="n">
-        <v>72.5</v>
+        <v>60.77</v>
       </c>
       <c r="I17" t="n">
-        <v>73.76000000000001</v>
+        <v>64.81</v>
       </c>
       <c r="J17" t="n">
-        <v>71.78</v>
+        <v>56.73</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="N17" t="n">
-        <v>6142</v>
+        <v>6200</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.53</v>
+        <v>19.37</v>
       </c>
       <c r="C18" t="n">
-        <v>17.62</v>
+        <v>19.79</v>
       </c>
       <c r="D18" t="n">
-        <v>17.45</v>
+        <v>18.91</v>
       </c>
       <c r="E18" t="n">
         <v>12.4</v>
       </c>
       <c r="F18" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="H18" t="n">
-        <v>72.33</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>72.88</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>71.93000000000001</v>
+        <v>63.19</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="N18" t="n">
-        <v>6152</v>
+        <v>6180</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.64</v>
+        <v>18.41</v>
       </c>
       <c r="C19" t="n">
-        <v>17.9</v>
+        <v>18.85</v>
       </c>
       <c r="D19" t="n">
-        <v>17.44</v>
+        <v>18.05</v>
       </c>
       <c r="E19" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H19" t="n">
-        <v>71.73999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="I19" t="n">
-        <v>73.59999999999999</v>
+        <v>71.67</v>
       </c>
       <c r="J19" t="n">
-        <v>69.53</v>
+        <v>67.22</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="N19" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.84</v>
+        <v>17.66</v>
       </c>
       <c r="C20" t="n">
-        <v>17.88</v>
+        <v>17.95</v>
       </c>
       <c r="D20" t="n">
-        <v>17.8</v>
+        <v>17.51</v>
       </c>
       <c r="E20" t="n">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>70.06999999999999</v>
+        <v>73.31</v>
       </c>
       <c r="I20" t="n">
-        <v>70.3</v>
+        <v>74.14</v>
       </c>
       <c r="J20" t="n">
-        <v>69.65000000000001</v>
+        <v>72.19</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="N20" t="n">
         <v>6162</v>
@@ -1401,67 +1401,67 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.9</v>
+        <v>17.6</v>
       </c>
       <c r="C21" t="n">
-        <v>17.97</v>
+        <v>17.68</v>
       </c>
       <c r="D21" t="n">
-        <v>17.82</v>
+        <v>17.49</v>
       </c>
       <c r="E21" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>69.79000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="I21" t="n">
-        <v>70.48999999999999</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>69.43000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="N21" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.74</v>
+        <v>17.53</v>
       </c>
       <c r="C22" t="n">
-        <v>17.82</v>
+        <v>17.62</v>
       </c>
       <c r="D22" t="n">
-        <v>17.7</v>
+        <v>17.45</v>
       </c>
       <c r="E22" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F22" t="n">
         <v>12.2</v>
@@ -1470,1103 +1470,1105 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>70.81999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="I22" t="n">
-        <v>70.98</v>
+        <v>72.88</v>
       </c>
       <c r="J22" t="n">
-        <v>70.54000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="N22" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.68</v>
+        <v>17.64</v>
       </c>
       <c r="C23" t="n">
-        <v>17.71</v>
+        <v>17.9</v>
       </c>
       <c r="D23" t="n">
-        <v>17.64</v>
+        <v>17.44</v>
       </c>
       <c r="E23" t="n">
         <v>12.3</v>
       </c>
       <c r="F23" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>71.42</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>71.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>71.13</v>
+        <v>69.53</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N23" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.74</v>
+        <v>17.84</v>
       </c>
       <c r="C24" t="n">
-        <v>17.78</v>
+        <v>17.88</v>
       </c>
       <c r="D24" t="n">
-        <v>17.68</v>
+        <v>17.8</v>
       </c>
       <c r="E24" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="F24" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>71.53</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>72.06999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="J24" t="n">
-        <v>70.67</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N24" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18.17</v>
+        <v>17.9</v>
       </c>
       <c r="C25" t="n">
-        <v>18.45</v>
+        <v>17.97</v>
       </c>
       <c r="D25" t="n">
-        <v>17.85</v>
+        <v>17.82</v>
       </c>
       <c r="E25" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="F25" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>67.5</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>70.09</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>65.53</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
       <c r="N25" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19.12</v>
+        <v>17.74</v>
       </c>
       <c r="C26" t="n">
-        <v>19.48</v>
+        <v>17.82</v>
       </c>
       <c r="D26" t="n">
-        <v>18.59</v>
+        <v>17.7</v>
       </c>
       <c r="E26" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="F26" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>62.25</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>64.8</v>
+        <v>70.98</v>
       </c>
       <c r="J26" t="n">
-        <v>60.27</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="N26" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.89</v>
+        <v>17.68</v>
       </c>
       <c r="C27" t="n">
-        <v>20.2</v>
+        <v>17.71</v>
       </c>
       <c r="D27" t="n">
-        <v>19.54</v>
+        <v>17.64</v>
       </c>
       <c r="E27" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="F27" t="n">
-        <v>11.1</v>
+        <v>12.3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>58.12</v>
+        <v>71.42</v>
       </c>
       <c r="I27" t="n">
-        <v>59.88</v>
+        <v>71.8</v>
       </c>
       <c r="J27" t="n">
-        <v>56.65</v>
+        <v>71.13</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>6190</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20.59</v>
+        <v>17.74</v>
       </c>
       <c r="C28" t="n">
-        <v>21.02</v>
+        <v>17.78</v>
       </c>
       <c r="D28" t="n">
-        <v>20.23</v>
+        <v>17.68</v>
       </c>
       <c r="E28" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>55.26</v>
+        <v>71.53</v>
       </c>
       <c r="I28" t="n">
-        <v>56.46</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>54.02</v>
+        <v>70.67</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M28" t="n">
         <v>2</v>
       </c>
-      <c r="M28" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N28" t="n">
-        <v>6200</v>
+        <v>6152</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21.34</v>
+        <v>18.17</v>
       </c>
       <c r="C29" t="n">
-        <v>21.65</v>
+        <v>18.45</v>
       </c>
       <c r="D29" t="n">
-        <v>20.98</v>
+        <v>17.85</v>
       </c>
       <c r="E29" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="G29" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>52.89</v>
+        <v>67.5</v>
       </c>
       <c r="I29" t="n">
-        <v>53.97</v>
+        <v>70.09</v>
       </c>
       <c r="J29" t="n">
-        <v>51.51</v>
+        <v>65.53</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>6220</v>
+        <v>6152</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.22</v>
+        <v>19.12</v>
       </c>
       <c r="C30" t="n">
-        <v>22.72</v>
+        <v>19.48</v>
       </c>
       <c r="D30" t="n">
-        <v>21.71</v>
+        <v>18.59</v>
       </c>
       <c r="E30" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="F30" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="G30" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>50.44</v>
+        <v>62.25</v>
       </c>
       <c r="I30" t="n">
-        <v>51.7</v>
+        <v>64.8</v>
       </c>
       <c r="J30" t="n">
-        <v>49.53</v>
+        <v>60.27</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="N30" t="n">
-        <v>6240</v>
+        <v>6180</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22.94</v>
+        <v>19.89</v>
       </c>
       <c r="C31" t="n">
-        <v>23.82</v>
+        <v>20.2</v>
       </c>
       <c r="D31" t="n">
-        <v>22.29</v>
+        <v>19.54</v>
       </c>
       <c r="E31" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="F31" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="G31" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>46.37</v>
+        <v>58.12</v>
       </c>
       <c r="I31" t="n">
-        <v>49.68</v>
+        <v>59.88</v>
       </c>
       <c r="J31" t="n">
-        <v>44.22</v>
+        <v>56.65</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="N31" t="n">
-        <v>6250</v>
+        <v>6190</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23.12</v>
+        <v>20.59</v>
       </c>
       <c r="C32" t="n">
-        <v>24.14</v>
+        <v>21.02</v>
       </c>
       <c r="D32" t="n">
-        <v>22.72</v>
+        <v>20.23</v>
       </c>
       <c r="E32" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F32" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G32" t="n">
-        <v>344</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>45.59</v>
+        <v>55.26</v>
       </c>
       <c r="I32" t="n">
-        <v>46.9</v>
+        <v>56.46</v>
       </c>
       <c r="J32" t="n">
-        <v>43.18</v>
+        <v>54.02</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M32" t="n">
         <v>2.6</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.7</v>
-      </c>
       <c r="N32" t="n">
-        <v>6240</v>
+        <v>6200</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.76</v>
+        <v>21.34</v>
       </c>
       <c r="C33" t="n">
-        <v>23.63</v>
+        <v>21.65</v>
       </c>
       <c r="D33" t="n">
-        <v>22.08</v>
+        <v>20.98</v>
       </c>
       <c r="E33" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F33" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G33" t="n">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="H33" t="n">
-        <v>47.51</v>
+        <v>52.89</v>
       </c>
       <c r="I33" t="n">
-        <v>49.36</v>
+        <v>53.97</v>
       </c>
       <c r="J33" t="n">
-        <v>46.08</v>
+        <v>51.51</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="N33" t="n">
-        <v>6240</v>
+        <v>6220</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22.55</v>
+        <v>22.22</v>
       </c>
       <c r="C34" t="n">
-        <v>23.29</v>
+        <v>22.72</v>
       </c>
       <c r="D34" t="n">
-        <v>21.68</v>
+        <v>21.71</v>
       </c>
       <c r="E34" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="F34" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="G34" t="n">
-        <v>364</v>
+        <v>210</v>
       </c>
       <c r="H34" t="n">
-        <v>47.88</v>
+        <v>50.44</v>
       </c>
       <c r="I34" t="n">
-        <v>50.32</v>
+        <v>51.7</v>
       </c>
       <c r="J34" t="n">
-        <v>46.13</v>
+        <v>49.53</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>6220</v>
+        <v>6240</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.47</v>
+        <v>22.94</v>
       </c>
       <c r="C35" t="n">
-        <v>23.42</v>
+        <v>23.82</v>
       </c>
       <c r="D35" t="n">
-        <v>21.73</v>
+        <v>22.29</v>
       </c>
       <c r="E35" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="F35" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="G35" t="n">
-        <v>531</v>
+        <v>355</v>
       </c>
       <c r="H35" t="n">
-        <v>49.09</v>
+        <v>46.37</v>
       </c>
       <c r="I35" t="n">
-        <v>51.32</v>
+        <v>49.68</v>
       </c>
       <c r="J35" t="n">
-        <v>46.18</v>
+        <v>44.22</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
         <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>6230</v>
+        <v>6250</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21.72</v>
+        <v>23.12</v>
       </c>
       <c r="C36" t="n">
-        <v>23.46</v>
+        <v>24.14</v>
       </c>
       <c r="D36" t="n">
-        <v>20.79</v>
+        <v>22.72</v>
       </c>
       <c r="E36" t="n">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="G36" t="n">
-        <v>616</v>
+        <v>344</v>
       </c>
       <c r="H36" t="n">
-        <v>52.51</v>
+        <v>45.59</v>
       </c>
       <c r="I36" t="n">
-        <v>55.76</v>
+        <v>46.9</v>
       </c>
       <c r="J36" t="n">
-        <v>47.65</v>
+        <v>43.18</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>6220</v>
+        <v>6240</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>20.86</v>
+        <v>22.76</v>
       </c>
       <c r="C37" t="n">
-        <v>21.56</v>
+        <v>23.63</v>
       </c>
       <c r="D37" t="n">
-        <v>20.25</v>
+        <v>22.08</v>
       </c>
       <c r="E37" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
       </c>
       <c r="F37" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G37" t="n">
-        <v>642</v>
+        <v>462</v>
       </c>
       <c r="H37" t="n">
-        <v>56.36</v>
+        <v>47.51</v>
       </c>
       <c r="I37" t="n">
-        <v>59</v>
+        <v>49.36</v>
       </c>
       <c r="J37" t="n">
-        <v>53.69</v>
+        <v>46.08</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>6190</v>
+        <v>6240</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>19.5</v>
+        <v>22.55</v>
       </c>
       <c r="C38" t="n">
-        <v>19.99</v>
+        <v>23.29</v>
       </c>
       <c r="D38" t="n">
-        <v>19.01</v>
+        <v>21.68</v>
       </c>
       <c r="E38" t="n">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="F38" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="G38" t="n">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="H38" t="n">
-        <v>61.31</v>
+        <v>47.88</v>
       </c>
       <c r="I38" t="n">
-        <v>62.89</v>
+        <v>50.32</v>
       </c>
       <c r="J38" t="n">
-        <v>59.57</v>
+        <v>46.13</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.96</v>
+        <v>22.47</v>
       </c>
       <c r="C39" t="n">
-        <v>18.97</v>
+        <v>23.42</v>
       </c>
       <c r="D39" t="n">
-        <v>17.06</v>
+        <v>21.73</v>
       </c>
       <c r="E39" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="G39" t="n">
-        <v>158</v>
+        <v>531</v>
       </c>
       <c r="H39" t="n">
-        <v>69.53</v>
+        <v>49.09</v>
       </c>
       <c r="I39" t="n">
-        <v>74.66</v>
+        <v>51.32</v>
       </c>
       <c r="J39" t="n">
-        <v>64.09</v>
+        <v>46.18</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="M39" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>6180</v>
+        <v>6230</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.73</v>
+        <v>21.72</v>
       </c>
       <c r="C40" t="n">
-        <v>16.97</v>
+        <v>23.46</v>
       </c>
       <c r="D40" t="n">
-        <v>16.64</v>
+        <v>20.79</v>
       </c>
       <c r="E40" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
       <c r="F40" t="n">
-        <v>12.4</v>
+        <v>11</v>
       </c>
       <c r="G40" t="n">
-        <v>33</v>
+        <v>616</v>
       </c>
       <c r="H40" t="n">
-        <v>76.20999999999999</v>
+        <v>52.51</v>
       </c>
       <c r="I40" t="n">
-        <v>76.59999999999999</v>
+        <v>55.76</v>
       </c>
       <c r="J40" t="n">
-        <v>75.42</v>
+        <v>47.65</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="M40" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>6162</v>
+        <v>6220</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.74</v>
+        <v>20.86</v>
       </c>
       <c r="C41" t="n">
-        <v>16.83</v>
+        <v>21.56</v>
       </c>
       <c r="D41" t="n">
-        <v>16.69</v>
+        <v>20.25</v>
       </c>
       <c r="E41" t="n">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="F41" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="H41" t="n">
-        <v>76.59</v>
+        <v>56.36</v>
       </c>
       <c r="I41" t="n">
-        <v>77.48</v>
+        <v>59</v>
       </c>
       <c r="J41" t="n">
-        <v>75.81999999999999</v>
+        <v>53.69</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="M41" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16.74</v>
+        <v>19.5</v>
       </c>
       <c r="C42" t="n">
-        <v>16.81</v>
+        <v>19.99</v>
       </c>
       <c r="D42" t="n">
-        <v>16.65</v>
+        <v>19.01</v>
       </c>
       <c r="E42" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="F42" t="n">
-        <v>12.5</v>
+        <v>11.4</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H42" t="n">
-        <v>77.14</v>
+        <v>61.31</v>
       </c>
       <c r="I42" t="n">
-        <v>77.55</v>
+        <v>62.89</v>
       </c>
       <c r="J42" t="n">
-        <v>76.81999999999999</v>
+        <v>59.57</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="M42" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16.83</v>
+        <v>17.96</v>
       </c>
       <c r="C43" t="n">
-        <v>16.93</v>
+        <v>18.97</v>
       </c>
       <c r="D43" t="n">
-        <v>16.77</v>
+        <v>17.06</v>
       </c>
       <c r="E43" t="n">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="F43" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H43" t="n">
-        <v>77.89</v>
+        <v>69.53</v>
       </c>
       <c r="I43" t="n">
-        <v>78.14</v>
+        <v>74.66</v>
       </c>
       <c r="J43" t="n">
-        <v>77.23</v>
+        <v>64.09</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="N43" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17.08</v>
+        <v>16.73</v>
       </c>
       <c r="C44" t="n">
-        <v>17.24</v>
+        <v>16.97</v>
       </c>
       <c r="D44" t="n">
-        <v>16.95</v>
+        <v>16.64</v>
       </c>
       <c r="E44" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="F44" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H44" t="n">
-        <v>77.45999999999999</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>78.15000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>76.95</v>
+        <v>75.42</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M44" t="n">
         <v>1.4</v>
       </c>
-      <c r="M44" t="n">
-        <v>1.7</v>
-      </c>
       <c r="N44" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.17</v>
+        <v>16.74</v>
       </c>
       <c r="C45" t="n">
-        <v>17.3</v>
+        <v>16.83</v>
       </c>
       <c r="D45" t="n">
-        <v>16.93</v>
+        <v>16.69</v>
       </c>
       <c r="E45" t="n">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="F45" t="n">
-        <v>13.1</v>
+        <v>12.3</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>78.43000000000001</v>
+        <v>76.59</v>
       </c>
       <c r="I45" t="n">
-        <v>81.27</v>
+        <v>77.48</v>
       </c>
       <c r="J45" t="n">
-        <v>77.08</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="M45" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="N45" t="n">
         <v>6152</v>
@@ -2576,44 +2578,44 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.59</v>
+        <v>16.74</v>
       </c>
       <c r="C46" t="n">
-        <v>17.86</v>
+        <v>16.81</v>
       </c>
       <c r="D46" t="n">
-        <v>17.28</v>
+        <v>16.65</v>
       </c>
       <c r="E46" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="F46" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>75</v>
+        <v>77.14</v>
       </c>
       <c r="I46" t="n">
-        <v>77.95</v>
+        <v>77.55</v>
       </c>
       <c r="J46" t="n">
-        <v>73.39</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="M46" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="N46" t="n">
         <v>6162</v>
@@ -2623,35 +2625,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>18.2</v>
+        <v>16.83</v>
       </c>
       <c r="C47" t="n">
-        <v>18.41</v>
+        <v>16.93</v>
       </c>
       <c r="D47" t="n">
-        <v>18</v>
+        <v>16.77</v>
       </c>
       <c r="E47" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="F47" t="n">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>69.83</v>
+        <v>77.89</v>
       </c>
       <c r="I47" t="n">
-        <v>72.37</v>
+        <v>78.14</v>
       </c>
       <c r="J47" t="n">
-        <v>68.34</v>
+        <v>77.23</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2660,156 +2662,154 @@
         <v>1.5</v>
       </c>
       <c r="M47" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="N47" t="n">
-        <v>6162</v>
-      </c>
-      <c r="O47" t="n">
-        <v>3.7</v>
-      </c>
+        <v>6142</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18.56</v>
+        <v>17.08</v>
       </c>
       <c r="C48" t="n">
-        <v>18.7</v>
+        <v>17.24</v>
       </c>
       <c r="D48" t="n">
-        <v>18.41</v>
+        <v>16.95</v>
       </c>
       <c r="E48" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="F48" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>67.93000000000001</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>68.55</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>67.33</v>
+        <v>76.95</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="M48" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="N48" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>18.92</v>
+        <v>17.17</v>
       </c>
       <c r="C49" t="n">
-        <v>19.04</v>
+        <v>17.3</v>
       </c>
       <c r="D49" t="n">
-        <v>18.74</v>
+        <v>16.93</v>
       </c>
       <c r="E49" t="n">
-        <v>12.3</v>
+        <v>13.2</v>
       </c>
       <c r="F49" t="n">
-        <v>12.2</v>
+        <v>13.1</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>66</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>67.08</v>
+        <v>81.27</v>
       </c>
       <c r="J49" t="n">
-        <v>65.19</v>
+        <v>77.08</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="M49" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="N49" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>18.98</v>
+        <v>17.59</v>
       </c>
       <c r="C50" t="n">
-        <v>19.02</v>
+        <v>17.86</v>
       </c>
       <c r="D50" t="n">
-        <v>18.95</v>
+        <v>17.28</v>
       </c>
       <c r="E50" t="n">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="F50" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>65.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="I50" t="n">
-        <v>65.51000000000001</v>
+        <v>77.95</v>
       </c>
       <c r="J50" t="n">
-        <v>65.09999999999999</v>
+        <v>73.39</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="M50" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="N50" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O50" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
   </sheetData>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,35 +508,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.51</v>
+        <v>17.24</v>
       </c>
       <c r="C2" t="n">
-        <v>19.57</v>
+        <v>17.29</v>
       </c>
       <c r="D2" t="n">
-        <v>19.47</v>
+        <v>17.19</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4</v>
+        <v>13.2</v>
       </c>
       <c r="F2" t="n">
-        <v>11.4</v>
+        <v>13.1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>60.52</v>
+        <v>78.5</v>
       </c>
       <c r="I2" t="n">
-        <v>60.64</v>
+        <v>79.16</v>
       </c>
       <c r="J2" t="n">
-        <v>60.39</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -548,42 +548,42 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.62</v>
+        <v>17.62</v>
       </c>
       <c r="C3" t="n">
-        <v>19.71</v>
+        <v>17.85</v>
       </c>
       <c r="D3" t="n">
-        <v>19.49</v>
+        <v>17.33</v>
       </c>
       <c r="E3" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="F3" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>60.63</v>
+        <v>74.13</v>
       </c>
       <c r="I3" t="n">
-        <v>61.71</v>
+        <v>77.06</v>
       </c>
       <c r="J3" t="n">
-        <v>59.73</v>
+        <v>71.3</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -595,89 +595,89 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.79</v>
+        <v>17.72</v>
       </c>
       <c r="C4" t="n">
-        <v>20.01</v>
+        <v>18.84</v>
       </c>
       <c r="D4" t="n">
-        <v>19.61</v>
+        <v>17.46</v>
       </c>
       <c r="E4" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="F4" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>60.18</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>61.23</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>59.04</v>
+        <v>65.83</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.19</v>
+        <v>18.99</v>
       </c>
       <c r="C5" t="n">
-        <v>20.36</v>
+        <v>19.05</v>
       </c>
       <c r="D5" t="n">
-        <v>20.01</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="n">
         <v>11.5</v>
       </c>
       <c r="F5" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>58.19</v>
+        <v>62.56</v>
       </c>
       <c r="I5" t="n">
-        <v>59.14</v>
+        <v>63.18</v>
       </c>
       <c r="J5" t="n">
-        <v>57.54</v>
+        <v>61.89</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -686,45 +686,45 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.44</v>
+        <v>19.33</v>
       </c>
       <c r="C6" t="n">
-        <v>20.64</v>
+        <v>19.55</v>
       </c>
       <c r="D6" t="n">
-        <v>20.37</v>
+        <v>19.01</v>
       </c>
       <c r="E6" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F6" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>57.96</v>
+        <v>60.72</v>
       </c>
       <c r="I6" t="n">
-        <v>58.31</v>
+        <v>62.8</v>
       </c>
       <c r="J6" t="n">
-        <v>57.52</v>
+        <v>59.1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -733,900 +733,900 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N6" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.99</v>
+        <v>19.52</v>
       </c>
       <c r="C7" t="n">
-        <v>21.3</v>
+        <v>19.58</v>
       </c>
       <c r="D7" t="n">
-        <v>20.64</v>
+        <v>19.46</v>
       </c>
       <c r="E7" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F7" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>55.76</v>
+        <v>60.01</v>
       </c>
       <c r="I7" t="n">
-        <v>57.26</v>
+        <v>60.64</v>
       </c>
       <c r="J7" t="n">
-        <v>54.28</v>
+        <v>59.58</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.82</v>
+        <v>19.62</v>
       </c>
       <c r="C8" t="n">
-        <v>22.25</v>
+        <v>19.71</v>
       </c>
       <c r="D8" t="n">
-        <v>21.38</v>
+        <v>19.49</v>
       </c>
       <c r="E8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F8" t="n">
         <v>11.4</v>
       </c>
-      <c r="F8" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>52.03</v>
+        <v>60.63</v>
       </c>
       <c r="I8" t="n">
-        <v>53.83</v>
+        <v>61.71</v>
       </c>
       <c r="J8" t="n">
-        <v>50.23</v>
+        <v>59.73</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>6180</v>
+        <v>6152</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.61</v>
+        <v>19.79</v>
       </c>
       <c r="C9" t="n">
-        <v>22.85</v>
+        <v>20.01</v>
       </c>
       <c r="D9" t="n">
-        <v>22.34</v>
+        <v>19.61</v>
       </c>
       <c r="E9" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="G9" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>49.28</v>
+        <v>60.18</v>
       </c>
       <c r="I9" t="n">
-        <v>50.37</v>
+        <v>61.23</v>
       </c>
       <c r="J9" t="n">
-        <v>48.38</v>
+        <v>59.04</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="N9" t="n">
-        <v>6200</v>
+        <v>6142</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.26</v>
+        <v>20.19</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>20.36</v>
       </c>
       <c r="D10" t="n">
-        <v>22.73</v>
+        <v>20.01</v>
       </c>
       <c r="E10" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="F10" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="G10" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>47.55</v>
+        <v>58.19</v>
       </c>
       <c r="I10" t="n">
-        <v>48.93</v>
+        <v>59.14</v>
       </c>
       <c r="J10" t="n">
-        <v>45.68</v>
+        <v>57.54</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="N10" t="n">
-        <v>6220</v>
+        <v>6132</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.81</v>
+        <v>20.44</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>20.64</v>
       </c>
       <c r="D11" t="n">
-        <v>21.97</v>
+        <v>20.37</v>
       </c>
       <c r="E11" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G11" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>49.12</v>
+        <v>57.96</v>
       </c>
       <c r="I11" t="n">
-        <v>52.45</v>
+        <v>58.31</v>
       </c>
       <c r="J11" t="n">
-        <v>45.39</v>
+        <v>57.52</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21.82</v>
+        <v>20.99</v>
       </c>
       <c r="C12" t="n">
-        <v>21.95</v>
+        <v>21.3</v>
       </c>
       <c r="D12" t="n">
-        <v>21.73</v>
+        <v>20.64</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F12" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="G12" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>52.7</v>
+        <v>55.76</v>
       </c>
       <c r="I12" t="n">
-        <v>52.97</v>
+        <v>57.26</v>
       </c>
       <c r="J12" t="n">
-        <v>52.47</v>
+        <v>54.28</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="N12" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.74</v>
+        <v>21.82</v>
       </c>
       <c r="C13" t="n">
-        <v>21.95</v>
+        <v>22.25</v>
       </c>
       <c r="D13" t="n">
-        <v>21.56</v>
+        <v>21.38</v>
       </c>
       <c r="E13" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F13" t="n">
         <v>11.2</v>
       </c>
       <c r="G13" t="n">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>52.76</v>
+        <v>52.03</v>
       </c>
       <c r="I13" t="n">
-        <v>53.57</v>
+        <v>53.83</v>
       </c>
       <c r="J13" t="n">
-        <v>52.06</v>
+        <v>50.23</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.42</v>
+        <v>22.61</v>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>22.85</v>
       </c>
       <c r="D14" t="n">
-        <v>20.92</v>
+        <v>22.34</v>
       </c>
       <c r="E14" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="F14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="H14" t="n">
-        <v>54.49</v>
+        <v>49.28</v>
       </c>
       <c r="I14" t="n">
-        <v>56.38</v>
+        <v>50.37</v>
       </c>
       <c r="J14" t="n">
-        <v>52.2</v>
+        <v>48.38</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N14" t="n">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21.35</v>
+        <v>23.26</v>
       </c>
       <c r="C15" t="n">
-        <v>22.22</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>20.87</v>
+        <v>22.73</v>
       </c>
       <c r="E15" t="n">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
       <c r="F15" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="G15" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="H15" t="n">
-        <v>55.07</v>
+        <v>47.55</v>
       </c>
       <c r="I15" t="n">
-        <v>56.71</v>
+        <v>48.93</v>
       </c>
       <c r="J15" t="n">
-        <v>52.16</v>
+        <v>45.68</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21.1</v>
+        <v>22.81</v>
       </c>
       <c r="C16" t="n">
-        <v>21.69</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>20.51</v>
+        <v>21.97</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>480</v>
+        <v>373</v>
       </c>
       <c r="H16" t="n">
-        <v>55.96</v>
+        <v>49.12</v>
       </c>
       <c r="I16" t="n">
-        <v>58.01</v>
+        <v>52.45</v>
       </c>
       <c r="J16" t="n">
-        <v>53.81</v>
+        <v>45.39</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="N16" t="n">
-        <v>6210</v>
+        <v>6220</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.15</v>
+        <v>21.82</v>
       </c>
       <c r="C17" t="n">
-        <v>20.85</v>
+        <v>21.95</v>
       </c>
       <c r="D17" t="n">
-        <v>19.57</v>
+        <v>21.73</v>
       </c>
       <c r="E17" t="n">
-        <v>12.1</v>
+        <v>11.4</v>
       </c>
       <c r="F17" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="G17" t="n">
-        <v>266</v>
+        <v>146</v>
       </c>
       <c r="H17" t="n">
-        <v>60.77</v>
+        <v>52.7</v>
       </c>
       <c r="I17" t="n">
-        <v>64.81</v>
+        <v>52.97</v>
       </c>
       <c r="J17" t="n">
-        <v>56.73</v>
+        <v>52.47</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="N17" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19.37</v>
+        <v>21.74</v>
       </c>
       <c r="C18" t="n">
-        <v>19.79</v>
+        <v>21.95</v>
       </c>
       <c r="D18" t="n">
-        <v>18.91</v>
+        <v>21.56</v>
       </c>
       <c r="E18" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="F18" t="n">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
       <c r="G18" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="H18" t="n">
-        <v>65.04000000000001</v>
+        <v>52.76</v>
       </c>
       <c r="I18" t="n">
-        <v>66.98999999999999</v>
+        <v>53.57</v>
       </c>
       <c r="J18" t="n">
-        <v>63.19</v>
+        <v>52.06</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="N18" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18.41</v>
+        <v>21.42</v>
       </c>
       <c r="C19" t="n">
-        <v>18.85</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>18.05</v>
+        <v>20.92</v>
       </c>
       <c r="E19" t="n">
-        <v>12.6</v>
+        <v>11.6</v>
       </c>
       <c r="F19" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G19" t="n">
-        <v>76</v>
+        <v>218</v>
       </c>
       <c r="H19" t="n">
-        <v>69.37</v>
+        <v>54.49</v>
       </c>
       <c r="I19" t="n">
-        <v>71.67</v>
+        <v>56.38</v>
       </c>
       <c r="J19" t="n">
-        <v>67.22</v>
+        <v>52.2</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.66</v>
+        <v>21.35</v>
       </c>
       <c r="C20" t="n">
-        <v>17.95</v>
+        <v>22.22</v>
       </c>
       <c r="D20" t="n">
-        <v>17.51</v>
+        <v>20.87</v>
       </c>
       <c r="E20" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="F20" t="n">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>238</v>
       </c>
       <c r="H20" t="n">
-        <v>73.31</v>
+        <v>55.07</v>
       </c>
       <c r="I20" t="n">
-        <v>74.14</v>
+        <v>56.71</v>
       </c>
       <c r="J20" t="n">
-        <v>72.19</v>
+        <v>52.16</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="N20" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.6</v>
+        <v>21.1</v>
       </c>
       <c r="C21" t="n">
-        <v>17.68</v>
+        <v>21.69</v>
       </c>
       <c r="D21" t="n">
-        <v>17.49</v>
+        <v>20.51</v>
       </c>
       <c r="E21" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F21" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="H21" t="n">
-        <v>72.5</v>
+        <v>55.96</v>
       </c>
       <c r="I21" t="n">
-        <v>73.76000000000001</v>
+        <v>58.01</v>
       </c>
       <c r="J21" t="n">
-        <v>71.78</v>
+        <v>53.81</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>6142</v>
+        <v>6210</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.53</v>
+        <v>20.15</v>
       </c>
       <c r="C22" t="n">
-        <v>17.62</v>
+        <v>20.85</v>
       </c>
       <c r="D22" t="n">
-        <v>17.45</v>
+        <v>19.57</v>
       </c>
       <c r="E22" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F22" t="n">
-        <v>12.2</v>
+        <v>11.6</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="H22" t="n">
-        <v>72.33</v>
+        <v>60.77</v>
       </c>
       <c r="I22" t="n">
-        <v>72.88</v>
+        <v>64.81</v>
       </c>
       <c r="J22" t="n">
-        <v>71.93000000000001</v>
+        <v>56.73</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="N22" t="n">
-        <v>6152</v>
+        <v>6200</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.64</v>
+        <v>19.37</v>
       </c>
       <c r="C23" t="n">
-        <v>17.9</v>
+        <v>19.79</v>
       </c>
       <c r="D23" t="n">
-        <v>17.44</v>
+        <v>18.91</v>
       </c>
       <c r="E23" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F23" t="n">
         <v>12.3</v>
       </c>
-      <c r="F23" t="n">
-        <v>12</v>
-      </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="H23" t="n">
-        <v>71.73999999999999</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>73.59999999999999</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>69.53</v>
+        <v>63.19</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="N23" t="n">
-        <v>6152</v>
+        <v>6180</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.84</v>
+        <v>18.41</v>
       </c>
       <c r="C24" t="n">
-        <v>17.88</v>
+        <v>18.85</v>
       </c>
       <c r="D24" t="n">
-        <v>17.8</v>
+        <v>18.05</v>
       </c>
       <c r="E24" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H24" t="n">
-        <v>70.06999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="I24" t="n">
-        <v>70.3</v>
+        <v>71.67</v>
       </c>
       <c r="J24" t="n">
-        <v>69.65000000000001</v>
+        <v>67.22</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="N24" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.9</v>
+        <v>17.66</v>
       </c>
       <c r="C25" t="n">
-        <v>17.97</v>
+        <v>17.95</v>
       </c>
       <c r="D25" t="n">
-        <v>17.82</v>
+        <v>17.51</v>
       </c>
       <c r="E25" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
-        <v>69.79000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="I25" t="n">
-        <v>70.48999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="J25" t="n">
-        <v>69.43000000000001</v>
+        <v>72.19</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M25" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="N25" t="n">
         <v>6162</v>
@@ -1636,140 +1636,138 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17.74</v>
+        <v>17.6</v>
       </c>
       <c r="C26" t="n">
-        <v>17.82</v>
+        <v>17.68</v>
       </c>
       <c r="D26" t="n">
-        <v>17.7</v>
+        <v>17.49</v>
       </c>
       <c r="E26" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F26" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>70.81999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I26" t="n">
-        <v>70.98</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>70.54000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="N26" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.68</v>
+        <v>17.53</v>
       </c>
       <c r="C27" t="n">
-        <v>17.71</v>
+        <v>17.62</v>
       </c>
       <c r="D27" t="n">
-        <v>17.64</v>
+        <v>17.45</v>
       </c>
       <c r="E27" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F27" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>71.42</v>
+        <v>72.33</v>
       </c>
       <c r="I27" t="n">
-        <v>71.8</v>
+        <v>72.88</v>
       </c>
       <c r="J27" t="n">
-        <v>71.13</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N27" t="n">
-        <v>6162</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.4</v>
-      </c>
+        <v>6152</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17.74</v>
+        <v>17.64</v>
       </c>
       <c r="C28" t="n">
-        <v>17.78</v>
+        <v>17.9</v>
       </c>
       <c r="D28" t="n">
-        <v>17.68</v>
+        <v>17.44</v>
       </c>
       <c r="E28" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F28" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>71.53</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>72.06999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>70.67</v>
+        <v>69.53</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="M28" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N28" t="n">
         <v>6152</v>
@@ -1779,467 +1777,469 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18.17</v>
+        <v>17.84</v>
       </c>
       <c r="C29" t="n">
-        <v>18.45</v>
+        <v>17.88</v>
       </c>
       <c r="D29" t="n">
-        <v>17.85</v>
+        <v>17.8</v>
       </c>
       <c r="E29" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="F29" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>67.5</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>70.09</v>
+        <v>70.3</v>
       </c>
       <c r="J29" t="n">
-        <v>65.53</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N29" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.12</v>
+        <v>17.9</v>
       </c>
       <c r="C30" t="n">
-        <v>19.48</v>
+        <v>17.97</v>
       </c>
       <c r="D30" t="n">
-        <v>18.59</v>
+        <v>17.82</v>
       </c>
       <c r="E30" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="F30" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>62.25</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>64.8</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>60.27</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>1.5</v>
       </c>
       <c r="N30" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.89</v>
+        <v>17.74</v>
       </c>
       <c r="C31" t="n">
-        <v>20.2</v>
+        <v>17.82</v>
       </c>
       <c r="D31" t="n">
-        <v>19.54</v>
+        <v>17.7</v>
       </c>
       <c r="E31" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="F31" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>58.12</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>59.88</v>
+        <v>70.98</v>
       </c>
       <c r="J31" t="n">
-        <v>56.65</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N31" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>20.59</v>
+        <v>17.68</v>
       </c>
       <c r="C32" t="n">
-        <v>21.02</v>
+        <v>17.71</v>
       </c>
       <c r="D32" t="n">
-        <v>20.23</v>
+        <v>17.64</v>
       </c>
       <c r="E32" t="n">
-        <v>11.1</v>
+        <v>12.3</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>55.26</v>
+        <v>71.42</v>
       </c>
       <c r="I32" t="n">
-        <v>56.46</v>
+        <v>71.8</v>
       </c>
       <c r="J32" t="n">
-        <v>54.02</v>
+        <v>71.13</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M32" t="n">
         <v>2</v>
       </c>
-      <c r="M32" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N32" t="n">
-        <v>6200</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21.34</v>
+        <v>17.74</v>
       </c>
       <c r="C33" t="n">
-        <v>21.65</v>
+        <v>17.78</v>
       </c>
       <c r="D33" t="n">
-        <v>20.98</v>
+        <v>17.68</v>
       </c>
       <c r="E33" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="G33" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>52.89</v>
+        <v>71.53</v>
       </c>
       <c r="I33" t="n">
-        <v>53.97</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>51.51</v>
+        <v>70.67</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="M33" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>6220</v>
+        <v>6152</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22.22</v>
+        <v>18.17</v>
       </c>
       <c r="C34" t="n">
-        <v>22.72</v>
+        <v>18.45</v>
       </c>
       <c r="D34" t="n">
-        <v>21.71</v>
+        <v>17.85</v>
       </c>
       <c r="E34" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="F34" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="G34" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>50.44</v>
+        <v>67.5</v>
       </c>
       <c r="I34" t="n">
-        <v>51.7</v>
+        <v>70.09</v>
       </c>
       <c r="J34" t="n">
-        <v>49.53</v>
+        <v>65.53</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
-        <v>6240</v>
+        <v>6152</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.94</v>
+        <v>19.12</v>
       </c>
       <c r="C35" t="n">
-        <v>23.82</v>
+        <v>19.48</v>
       </c>
       <c r="D35" t="n">
-        <v>22.29</v>
+        <v>18.59</v>
       </c>
       <c r="E35" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="F35" t="n">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="G35" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>46.37</v>
+        <v>62.25</v>
       </c>
       <c r="I35" t="n">
-        <v>49.68</v>
+        <v>64.8</v>
       </c>
       <c r="J35" t="n">
-        <v>44.22</v>
+        <v>60.27</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="N35" t="n">
-        <v>6250</v>
+        <v>6180</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>23.12</v>
+        <v>19.89</v>
       </c>
       <c r="C36" t="n">
-        <v>24.14</v>
+        <v>20.2</v>
       </c>
       <c r="D36" t="n">
-        <v>22.72</v>
+        <v>19.54</v>
       </c>
       <c r="E36" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="F36" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="G36" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>45.59</v>
+        <v>58.12</v>
       </c>
       <c r="I36" t="n">
-        <v>46.9</v>
+        <v>59.88</v>
       </c>
       <c r="J36" t="n">
-        <v>43.18</v>
+        <v>56.65</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="N36" t="n">
-        <v>6240</v>
+        <v>6190</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22.76</v>
+        <v>20.59</v>
       </c>
       <c r="C37" t="n">
-        <v>23.63</v>
+        <v>21.02</v>
       </c>
       <c r="D37" t="n">
-        <v>22.08</v>
+        <v>20.23</v>
       </c>
       <c r="E37" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F37" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G37" t="n">
-        <v>462</v>
+        <v>6</v>
       </c>
       <c r="H37" t="n">
-        <v>47.51</v>
+        <v>55.26</v>
       </c>
       <c r="I37" t="n">
-        <v>49.36</v>
+        <v>56.46</v>
       </c>
       <c r="J37" t="n">
-        <v>46.08</v>
+        <v>54.02</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="N37" t="n">
-        <v>6240</v>
+        <v>6200</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>22.55</v>
+        <v>21.34</v>
       </c>
       <c r="C38" t="n">
-        <v>23.29</v>
+        <v>21.65</v>
       </c>
       <c r="D38" t="n">
-        <v>21.68</v>
+        <v>20.98</v>
       </c>
       <c r="E38" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="F38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G38" t="n">
-        <v>364</v>
+        <v>63</v>
       </c>
       <c r="H38" t="n">
-        <v>47.88</v>
+        <v>52.89</v>
       </c>
       <c r="I38" t="n">
-        <v>50.32</v>
+        <v>53.97</v>
       </c>
       <c r="J38" t="n">
-        <v>46.13</v>
+        <v>51.51</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="N38" t="n">
         <v>6220</v>
@@ -2249,564 +2249,564 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>22.47</v>
+        <v>22.22</v>
       </c>
       <c r="C39" t="n">
-        <v>23.42</v>
+        <v>22.72</v>
       </c>
       <c r="D39" t="n">
-        <v>21.73</v>
+        <v>21.71</v>
       </c>
       <c r="E39" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="F39" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="G39" t="n">
-        <v>531</v>
+        <v>210</v>
       </c>
       <c r="H39" t="n">
-        <v>49.09</v>
+        <v>50.44</v>
       </c>
       <c r="I39" t="n">
-        <v>51.32</v>
+        <v>51.7</v>
       </c>
       <c r="J39" t="n">
-        <v>46.18</v>
+        <v>49.53</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
         <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>6230</v>
+        <v>6240</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>21.72</v>
+        <v>22.94</v>
       </c>
       <c r="C40" t="n">
-        <v>23.46</v>
+        <v>23.82</v>
       </c>
       <c r="D40" t="n">
-        <v>20.79</v>
+        <v>22.29</v>
       </c>
       <c r="E40" t="n">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="G40" t="n">
-        <v>616</v>
+        <v>355</v>
       </c>
       <c r="H40" t="n">
-        <v>52.51</v>
+        <v>46.37</v>
       </c>
       <c r="I40" t="n">
-        <v>55.76</v>
+        <v>49.68</v>
       </c>
       <c r="J40" t="n">
-        <v>47.65</v>
+        <v>44.22</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>6220</v>
+        <v>6250</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20.86</v>
+        <v>23.12</v>
       </c>
       <c r="C41" t="n">
-        <v>21.56</v>
+        <v>24.14</v>
       </c>
       <c r="D41" t="n">
-        <v>20.25</v>
+        <v>22.72</v>
       </c>
       <c r="E41" t="n">
-        <v>11.7</v>
+        <v>10.5</v>
       </c>
       <c r="F41" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="G41" t="n">
-        <v>642</v>
+        <v>344</v>
       </c>
       <c r="H41" t="n">
-        <v>56.36</v>
+        <v>45.59</v>
       </c>
       <c r="I41" t="n">
-        <v>59</v>
+        <v>46.9</v>
       </c>
       <c r="J41" t="n">
-        <v>53.69</v>
+        <v>43.18</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>6190</v>
+        <v>6240</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19.5</v>
+        <v>22.76</v>
       </c>
       <c r="C42" t="n">
-        <v>19.99</v>
+        <v>23.63</v>
       </c>
       <c r="D42" t="n">
-        <v>19.01</v>
+        <v>22.08</v>
       </c>
       <c r="E42" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
       </c>
       <c r="F42" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="G42" t="n">
-        <v>341</v>
+        <v>462</v>
       </c>
       <c r="H42" t="n">
-        <v>61.31</v>
+        <v>47.51</v>
       </c>
       <c r="I42" t="n">
-        <v>62.89</v>
+        <v>49.36</v>
       </c>
       <c r="J42" t="n">
-        <v>59.57</v>
+        <v>46.08</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>6190</v>
+        <v>6240</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.96</v>
+        <v>22.55</v>
       </c>
       <c r="C43" t="n">
-        <v>18.97</v>
+        <v>23.29</v>
       </c>
       <c r="D43" t="n">
-        <v>17.06</v>
+        <v>21.68</v>
       </c>
       <c r="E43" t="n">
-        <v>12.1</v>
+        <v>10.7</v>
       </c>
       <c r="F43" t="n">
-        <v>11.8</v>
+        <v>10.5</v>
       </c>
       <c r="G43" t="n">
-        <v>158</v>
+        <v>364</v>
       </c>
       <c r="H43" t="n">
-        <v>69.53</v>
+        <v>47.88</v>
       </c>
       <c r="I43" t="n">
-        <v>74.66</v>
+        <v>50.32</v>
       </c>
       <c r="J43" t="n">
-        <v>64.09</v>
+        <v>46.13</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M43" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>6180</v>
+        <v>6220</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.73</v>
+        <v>22.47</v>
       </c>
       <c r="C44" t="n">
-        <v>16.97</v>
+        <v>23.42</v>
       </c>
       <c r="D44" t="n">
-        <v>16.64</v>
+        <v>21.73</v>
       </c>
       <c r="E44" t="n">
-        <v>12.4</v>
+        <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>12.4</v>
+        <v>10.7</v>
       </c>
       <c r="G44" t="n">
-        <v>33</v>
+        <v>531</v>
       </c>
       <c r="H44" t="n">
-        <v>76.20999999999999</v>
+        <v>49.09</v>
       </c>
       <c r="I44" t="n">
-        <v>76.59999999999999</v>
+        <v>51.32</v>
       </c>
       <c r="J44" t="n">
-        <v>75.42</v>
+        <v>46.18</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="M44" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="N44" t="n">
-        <v>6162</v>
+        <v>6230</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.74</v>
+        <v>21.72</v>
       </c>
       <c r="C45" t="n">
-        <v>16.83</v>
+        <v>23.46</v>
       </c>
       <c r="D45" t="n">
-        <v>16.69</v>
+        <v>20.79</v>
       </c>
       <c r="E45" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
       <c r="F45" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="H45" t="n">
-        <v>76.59</v>
+        <v>52.51</v>
       </c>
       <c r="I45" t="n">
-        <v>77.48</v>
+        <v>55.76</v>
       </c>
       <c r="J45" t="n">
-        <v>75.81999999999999</v>
+        <v>47.65</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="M45" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>6152</v>
+        <v>6220</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16.74</v>
+        <v>20.86</v>
       </c>
       <c r="C46" t="n">
-        <v>16.81</v>
+        <v>21.56</v>
       </c>
       <c r="D46" t="n">
-        <v>16.65</v>
+        <v>20.25</v>
       </c>
       <c r="E46" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="F46" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="H46" t="n">
-        <v>77.14</v>
+        <v>56.36</v>
       </c>
       <c r="I46" t="n">
-        <v>77.55</v>
+        <v>59</v>
       </c>
       <c r="J46" t="n">
-        <v>76.81999999999999</v>
+        <v>53.69</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="M46" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.83</v>
+        <v>19.5</v>
       </c>
       <c r="C47" t="n">
-        <v>16.93</v>
+        <v>19.99</v>
       </c>
       <c r="D47" t="n">
-        <v>16.77</v>
+        <v>19.01</v>
       </c>
       <c r="E47" t="n">
-        <v>12.8</v>
+        <v>11.7</v>
       </c>
       <c r="F47" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H47" t="n">
-        <v>77.89</v>
+        <v>61.31</v>
       </c>
       <c r="I47" t="n">
-        <v>78.14</v>
+        <v>62.89</v>
       </c>
       <c r="J47" t="n">
-        <v>77.23</v>
+        <v>59.57</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="M47" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="N47" t="n">
-        <v>6142</v>
+        <v>6190</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.08</v>
+        <v>17.96</v>
       </c>
       <c r="C48" t="n">
-        <v>17.24</v>
+        <v>18.97</v>
       </c>
       <c r="D48" t="n">
-        <v>16.95</v>
+        <v>17.06</v>
       </c>
       <c r="E48" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="F48" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H48" t="n">
-        <v>77.45999999999999</v>
+        <v>69.53</v>
       </c>
       <c r="I48" t="n">
-        <v>78.15000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="J48" t="n">
-        <v>76.95</v>
+        <v>64.09</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="N48" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.17</v>
+        <v>16.73</v>
       </c>
       <c r="C49" t="n">
-        <v>17.3</v>
+        <v>16.97</v>
       </c>
       <c r="D49" t="n">
-        <v>16.93</v>
+        <v>16.64</v>
       </c>
       <c r="E49" t="n">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="F49" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H49" t="n">
-        <v>78.43000000000001</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>81.27</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>77.08</v>
+        <v>75.42</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M49" t="n">
         <v>1.4</v>
       </c>
-      <c r="M49" t="n">
-        <v>1.7</v>
-      </c>
       <c r="N49" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>17.59</v>
+        <v>16.74</v>
       </c>
       <c r="C50" t="n">
-        <v>17.86</v>
+        <v>16.83</v>
       </c>
       <c r="D50" t="n">
-        <v>17.28</v>
+        <v>16.69</v>
       </c>
       <c r="E50" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="F50" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>75</v>
+        <v>76.59</v>
       </c>
       <c r="I50" t="n">
-        <v>77.95</v>
+        <v>77.48</v>
       </c>
       <c r="J50" t="n">
-        <v>73.39</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="M50" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="N50" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O50" t="n">
         <v>3.7</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,138 +508,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.24</v>
+        <v>19.93</v>
       </c>
       <c r="C2" t="n">
-        <v>17.29</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>17.19</v>
+        <v>19.87</v>
       </c>
       <c r="E2" t="n">
-        <v>13.2</v>
+        <v>10.5</v>
       </c>
       <c r="F2" t="n">
-        <v>13.1</v>
+        <v>10.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H2" t="n">
-        <v>78.5</v>
+        <v>54.82</v>
       </c>
       <c r="I2" t="n">
-        <v>79.16</v>
+        <v>56.41</v>
       </c>
       <c r="J2" t="n">
-        <v>77.70999999999999</v>
+        <v>54.01</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N2" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.62</v>
+        <v>19.38</v>
       </c>
       <c r="C3" t="n">
-        <v>17.85</v>
+        <v>19.85</v>
       </c>
       <c r="D3" t="n">
-        <v>17.33</v>
+        <v>18.89</v>
       </c>
       <c r="E3" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="F3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
-        <v>74.13</v>
+        <v>61.37</v>
       </c>
       <c r="I3" t="n">
-        <v>77.06</v>
+        <v>65.44</v>
       </c>
       <c r="J3" t="n">
-        <v>71.3</v>
+        <v>57.45</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.72</v>
+        <v>18.52</v>
       </c>
       <c r="C4" t="n">
-        <v>18.84</v>
+        <v>18.87</v>
       </c>
       <c r="D4" t="n">
-        <v>17.46</v>
+        <v>18.23</v>
       </c>
       <c r="E4" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="F4" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
-        <v>71.95999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="I4" t="n">
-        <v>74.59999999999999</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>65.83</v>
+        <v>65.33</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>6152</v>
@@ -649,91 +649,91 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.99</v>
+        <v>17.89</v>
       </c>
       <c r="C5" t="n">
-        <v>19.05</v>
+        <v>18.27</v>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>17.53</v>
       </c>
       <c r="E5" t="n">
-        <v>11.5</v>
+        <v>13.1</v>
       </c>
       <c r="F5" t="n">
-        <v>11.3</v>
+        <v>12.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>62.56</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>63.18</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>61.89</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.33</v>
+        <v>17.34</v>
       </c>
       <c r="C6" t="n">
-        <v>19.55</v>
+        <v>17.48</v>
       </c>
       <c r="D6" t="n">
-        <v>19.01</v>
+        <v>17.19</v>
       </c>
       <c r="E6" t="n">
-        <v>11.4</v>
+        <v>13.3</v>
       </c>
       <c r="F6" t="n">
-        <v>11.3</v>
+        <v>13.1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>60.72</v>
+        <v>78.27</v>
       </c>
       <c r="I6" t="n">
-        <v>62.8</v>
+        <v>79.16</v>
       </c>
       <c r="J6" t="n">
-        <v>59.1</v>
+        <v>77.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="N6" t="n">
         <v>6132</v>
@@ -743,82 +743,82 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.52</v>
+        <v>17.62</v>
       </c>
       <c r="C7" t="n">
-        <v>19.58</v>
+        <v>17.85</v>
       </c>
       <c r="D7" t="n">
-        <v>19.46</v>
+        <v>17.33</v>
       </c>
       <c r="E7" t="n">
-        <v>11.4</v>
+        <v>12.8</v>
       </c>
       <c r="F7" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>60.01</v>
+        <v>74.13</v>
       </c>
       <c r="I7" t="n">
-        <v>60.64</v>
+        <v>77.06</v>
       </c>
       <c r="J7" t="n">
-        <v>59.58</v>
+        <v>71.3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.62</v>
+        <v>17.72</v>
       </c>
       <c r="C8" t="n">
-        <v>19.71</v>
+        <v>18.84</v>
       </c>
       <c r="D8" t="n">
-        <v>19.49</v>
+        <v>17.46</v>
       </c>
       <c r="E8" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="F8" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>60.63</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>61.71</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>59.73</v>
+        <v>65.83</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -837,82 +837,82 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.79</v>
+        <v>18.99</v>
       </c>
       <c r="C9" t="n">
-        <v>20.01</v>
+        <v>19.05</v>
       </c>
       <c r="D9" t="n">
-        <v>19.61</v>
+        <v>18.9</v>
       </c>
       <c r="E9" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="F9" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>60.18</v>
+        <v>62.56</v>
       </c>
       <c r="I9" t="n">
-        <v>61.23</v>
+        <v>63.18</v>
       </c>
       <c r="J9" t="n">
-        <v>59.04</v>
+        <v>61.89</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20.19</v>
+        <v>19.33</v>
       </c>
       <c r="C10" t="n">
-        <v>20.36</v>
+        <v>19.55</v>
       </c>
       <c r="D10" t="n">
-        <v>20.01</v>
+        <v>19.01</v>
       </c>
       <c r="E10" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F10" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>58.19</v>
+        <v>60.72</v>
       </c>
       <c r="I10" t="n">
-        <v>59.14</v>
+        <v>62.8</v>
       </c>
       <c r="J10" t="n">
-        <v>57.54</v>
+        <v>59.1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="N10" t="n">
         <v>6132</v>
@@ -931,317 +931,317 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20.44</v>
+        <v>19.52</v>
       </c>
       <c r="C11" t="n">
-        <v>20.64</v>
+        <v>19.58</v>
       </c>
       <c r="D11" t="n">
-        <v>20.37</v>
+        <v>19.46</v>
       </c>
       <c r="E11" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F11" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>57.96</v>
+        <v>60.01</v>
       </c>
       <c r="I11" t="n">
-        <v>58.31</v>
+        <v>60.64</v>
       </c>
       <c r="J11" t="n">
-        <v>57.52</v>
+        <v>59.58</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N11" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.99</v>
+        <v>19.62</v>
       </c>
       <c r="C12" t="n">
-        <v>21.3</v>
+        <v>19.71</v>
       </c>
       <c r="D12" t="n">
-        <v>20.64</v>
+        <v>19.49</v>
       </c>
       <c r="E12" t="n">
         <v>11.6</v>
       </c>
       <c r="F12" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>55.76</v>
+        <v>60.63</v>
       </c>
       <c r="I12" t="n">
-        <v>57.26</v>
+        <v>61.71</v>
       </c>
       <c r="J12" t="n">
-        <v>54.28</v>
+        <v>59.73</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.82</v>
+        <v>19.79</v>
       </c>
       <c r="C13" t="n">
-        <v>22.25</v>
+        <v>20.01</v>
       </c>
       <c r="D13" t="n">
-        <v>21.38</v>
+        <v>19.61</v>
       </c>
       <c r="E13" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="F13" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>52.03</v>
+        <v>60.18</v>
       </c>
       <c r="I13" t="n">
-        <v>53.83</v>
+        <v>61.23</v>
       </c>
       <c r="J13" t="n">
-        <v>50.23</v>
+        <v>59.04</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="N13" t="n">
-        <v>6180</v>
+        <v>6142</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22.61</v>
+        <v>20.19</v>
       </c>
       <c r="C14" t="n">
-        <v>22.85</v>
+        <v>20.36</v>
       </c>
       <c r="D14" t="n">
-        <v>22.34</v>
+        <v>20.01</v>
       </c>
       <c r="E14" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="G14" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>49.28</v>
+        <v>58.19</v>
       </c>
       <c r="I14" t="n">
-        <v>50.37</v>
+        <v>59.14</v>
       </c>
       <c r="J14" t="n">
-        <v>48.38</v>
+        <v>57.54</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="N14" t="n">
-        <v>6200</v>
+        <v>6132</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23.26</v>
+        <v>20.44</v>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>20.64</v>
       </c>
       <c r="D15" t="n">
-        <v>22.73</v>
+        <v>20.37</v>
       </c>
       <c r="E15" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="F15" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>47.55</v>
+        <v>57.96</v>
       </c>
       <c r="I15" t="n">
-        <v>48.93</v>
+        <v>58.31</v>
       </c>
       <c r="J15" t="n">
-        <v>45.68</v>
+        <v>57.52</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22.81</v>
+        <v>20.99</v>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>21.3</v>
       </c>
       <c r="D16" t="n">
-        <v>21.97</v>
+        <v>20.64</v>
       </c>
       <c r="E16" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G16" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>49.12</v>
+        <v>55.76</v>
       </c>
       <c r="I16" t="n">
-        <v>52.45</v>
+        <v>57.26</v>
       </c>
       <c r="J16" t="n">
-        <v>45.39</v>
+        <v>54.28</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="N16" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>21.82</v>
       </c>
       <c r="C17" t="n">
-        <v>21.95</v>
+        <v>22.25</v>
       </c>
       <c r="D17" t="n">
-        <v>21.73</v>
+        <v>21.38</v>
       </c>
       <c r="E17" t="n">
         <v>11.4</v>
       </c>
       <c r="F17" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G17" t="n">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>52.7</v>
+        <v>52.03</v>
       </c>
       <c r="I17" t="n">
-        <v>52.97</v>
+        <v>53.83</v>
       </c>
       <c r="J17" t="n">
-        <v>52.47</v>
+        <v>50.23</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1250,571 +1250,571 @@
         <v>0.7</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21.74</v>
+        <v>22.61</v>
       </c>
       <c r="C18" t="n">
-        <v>21.95</v>
+        <v>22.85</v>
       </c>
       <c r="D18" t="n">
-        <v>21.56</v>
+        <v>22.34</v>
       </c>
       <c r="E18" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="F18" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="H18" t="n">
-        <v>52.76</v>
+        <v>49.28</v>
       </c>
       <c r="I18" t="n">
-        <v>53.57</v>
+        <v>50.37</v>
       </c>
       <c r="J18" t="n">
-        <v>52.06</v>
+        <v>48.38</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="N18" t="n">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21.42</v>
+        <v>23.26</v>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>20.92</v>
+        <v>22.73</v>
       </c>
       <c r="E19" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="F19" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="G19" t="n">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="H19" t="n">
-        <v>54.49</v>
+        <v>47.55</v>
       </c>
       <c r="I19" t="n">
-        <v>56.38</v>
+        <v>48.93</v>
       </c>
       <c r="J19" t="n">
-        <v>52.2</v>
+        <v>45.68</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.35</v>
+        <v>22.81</v>
       </c>
       <c r="C20" t="n">
-        <v>22.22</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>20.87</v>
+        <v>21.97</v>
       </c>
       <c r="E20" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>238</v>
+        <v>373</v>
       </c>
       <c r="H20" t="n">
-        <v>55.07</v>
+        <v>49.12</v>
       </c>
       <c r="I20" t="n">
-        <v>56.71</v>
+        <v>52.45</v>
       </c>
       <c r="J20" t="n">
-        <v>52.16</v>
+        <v>45.39</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="N20" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.1</v>
+        <v>21.82</v>
       </c>
       <c r="C21" t="n">
-        <v>21.69</v>
+        <v>21.95</v>
       </c>
       <c r="D21" t="n">
-        <v>20.51</v>
+        <v>21.73</v>
       </c>
       <c r="E21" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F21" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G21" t="n">
-        <v>480</v>
+        <v>146</v>
       </c>
       <c r="H21" t="n">
-        <v>55.96</v>
+        <v>52.7</v>
       </c>
       <c r="I21" t="n">
-        <v>58.01</v>
+        <v>52.97</v>
       </c>
       <c r="J21" t="n">
-        <v>53.81</v>
+        <v>52.47</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="N21" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20.15</v>
+        <v>21.74</v>
       </c>
       <c r="C22" t="n">
-        <v>20.85</v>
+        <v>21.95</v>
       </c>
       <c r="D22" t="n">
-        <v>19.57</v>
+        <v>21.56</v>
       </c>
       <c r="E22" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="F22" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G22" t="n">
-        <v>266</v>
+        <v>165</v>
       </c>
       <c r="H22" t="n">
-        <v>60.77</v>
+        <v>52.76</v>
       </c>
       <c r="I22" t="n">
-        <v>64.81</v>
+        <v>53.57</v>
       </c>
       <c r="J22" t="n">
-        <v>56.73</v>
+        <v>52.06</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="M22" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="N22" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.37</v>
+        <v>21.42</v>
       </c>
       <c r="C23" t="n">
-        <v>19.79</v>
+        <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>18.91</v>
+        <v>20.92</v>
       </c>
       <c r="E23" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="F23" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G23" t="n">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="H23" t="n">
-        <v>65.04000000000001</v>
+        <v>54.49</v>
       </c>
       <c r="I23" t="n">
-        <v>66.98999999999999</v>
+        <v>56.38</v>
       </c>
       <c r="J23" t="n">
-        <v>63.19</v>
+        <v>52.2</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18.41</v>
+        <v>21.35</v>
       </c>
       <c r="C24" t="n">
-        <v>18.85</v>
+        <v>22.22</v>
       </c>
       <c r="D24" t="n">
-        <v>18.05</v>
+        <v>20.87</v>
       </c>
       <c r="E24" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F24" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G24" t="n">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="H24" t="n">
-        <v>69.37</v>
+        <v>55.07</v>
       </c>
       <c r="I24" t="n">
-        <v>71.67</v>
+        <v>56.71</v>
       </c>
       <c r="J24" t="n">
-        <v>67.22</v>
+        <v>52.16</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="N24" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.66</v>
+        <v>21.1</v>
       </c>
       <c r="C25" t="n">
-        <v>17.95</v>
+        <v>21.69</v>
       </c>
       <c r="D25" t="n">
-        <v>17.51</v>
+        <v>20.51</v>
       </c>
       <c r="E25" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="F25" t="n">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>480</v>
       </c>
       <c r="H25" t="n">
-        <v>73.31</v>
+        <v>55.96</v>
       </c>
       <c r="I25" t="n">
-        <v>74.14</v>
+        <v>58.01</v>
       </c>
       <c r="J25" t="n">
-        <v>72.19</v>
+        <v>53.81</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>6162</v>
+        <v>6210</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17.6</v>
+        <v>20.15</v>
       </c>
       <c r="C26" t="n">
-        <v>17.68</v>
+        <v>20.85</v>
       </c>
       <c r="D26" t="n">
-        <v>17.49</v>
+        <v>19.57</v>
       </c>
       <c r="E26" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F26" t="n">
-        <v>12.3</v>
+        <v>11.6</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="H26" t="n">
-        <v>72.5</v>
+        <v>60.77</v>
       </c>
       <c r="I26" t="n">
-        <v>73.76000000000001</v>
+        <v>64.81</v>
       </c>
       <c r="J26" t="n">
-        <v>71.78</v>
+        <v>56.73</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="N26" t="n">
-        <v>6142</v>
+        <v>6200</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.53</v>
+        <v>19.37</v>
       </c>
       <c r="C27" t="n">
-        <v>17.62</v>
+        <v>19.79</v>
       </c>
       <c r="D27" t="n">
-        <v>17.45</v>
+        <v>18.91</v>
       </c>
       <c r="E27" t="n">
         <v>12.4</v>
       </c>
       <c r="F27" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="H27" t="n">
-        <v>72.33</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>72.88</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>71.93000000000001</v>
+        <v>63.19</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="N27" t="n">
-        <v>6152</v>
+        <v>6180</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17.64</v>
+        <v>18.41</v>
       </c>
       <c r="C28" t="n">
-        <v>17.9</v>
+        <v>18.85</v>
       </c>
       <c r="D28" t="n">
-        <v>17.44</v>
+        <v>18.05</v>
       </c>
       <c r="E28" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H28" t="n">
-        <v>71.73999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="I28" t="n">
-        <v>73.59999999999999</v>
+        <v>71.67</v>
       </c>
       <c r="J28" t="n">
-        <v>69.53</v>
+        <v>67.22</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.84</v>
+        <v>17.66</v>
       </c>
       <c r="C29" t="n">
-        <v>17.88</v>
+        <v>17.95</v>
       </c>
       <c r="D29" t="n">
-        <v>17.8</v>
+        <v>17.51</v>
       </c>
       <c r="E29" t="n">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H29" t="n">
-        <v>70.06999999999999</v>
+        <v>73.31</v>
       </c>
       <c r="I29" t="n">
-        <v>70.3</v>
+        <v>74.14</v>
       </c>
       <c r="J29" t="n">
-        <v>69.65000000000001</v>
+        <v>72.19</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="N29" t="n">
         <v>6162</v>
@@ -1824,67 +1824,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.9</v>
+        <v>17.6</v>
       </c>
       <c r="C30" t="n">
-        <v>17.97</v>
+        <v>17.68</v>
       </c>
       <c r="D30" t="n">
-        <v>17.82</v>
+        <v>17.49</v>
       </c>
       <c r="E30" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="F30" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>69.79000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="I30" t="n">
-        <v>70.48999999999999</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>69.43000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="N30" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.74</v>
+        <v>17.53</v>
       </c>
       <c r="C31" t="n">
-        <v>17.82</v>
+        <v>17.62</v>
       </c>
       <c r="D31" t="n">
-        <v>17.7</v>
+        <v>17.45</v>
       </c>
       <c r="E31" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F31" t="n">
         <v>12.2</v>
@@ -1893,920 +1893,920 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>70.81999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="I31" t="n">
-        <v>70.98</v>
+        <v>72.88</v>
       </c>
       <c r="J31" t="n">
-        <v>70.54000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="N31" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.68</v>
+        <v>17.64</v>
       </c>
       <c r="C32" t="n">
-        <v>17.71</v>
+        <v>17.9</v>
       </c>
       <c r="D32" t="n">
-        <v>17.64</v>
+        <v>17.44</v>
       </c>
       <c r="E32" t="n">
         <v>12.3</v>
       </c>
       <c r="F32" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>71.42</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>71.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>71.13</v>
+        <v>69.53</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N32" t="n">
-        <v>6162</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.4</v>
-      </c>
+        <v>6152</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.74</v>
+        <v>17.84</v>
       </c>
       <c r="C33" t="n">
-        <v>17.78</v>
+        <v>17.88</v>
       </c>
       <c r="D33" t="n">
-        <v>17.68</v>
+        <v>17.8</v>
       </c>
       <c r="E33" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="F33" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>71.53</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>72.06999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="J33" t="n">
-        <v>70.67</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N33" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18.17</v>
+        <v>17.9</v>
       </c>
       <c r="C34" t="n">
-        <v>18.45</v>
+        <v>17.97</v>
       </c>
       <c r="D34" t="n">
-        <v>17.85</v>
+        <v>17.82</v>
       </c>
       <c r="E34" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="F34" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>67.5</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>70.09</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>65.53</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
         <v>1.5</v>
       </c>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
       <c r="N34" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.12</v>
+        <v>17.74</v>
       </c>
       <c r="C35" t="n">
-        <v>19.48</v>
+        <v>17.82</v>
       </c>
       <c r="D35" t="n">
-        <v>18.59</v>
+        <v>17.7</v>
       </c>
       <c r="E35" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="F35" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>62.25</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>64.8</v>
+        <v>70.98</v>
       </c>
       <c r="J35" t="n">
-        <v>60.27</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="N35" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19.89</v>
+        <v>17.68</v>
       </c>
       <c r="C36" t="n">
-        <v>20.2</v>
+        <v>17.71</v>
       </c>
       <c r="D36" t="n">
-        <v>19.54</v>
+        <v>17.64</v>
       </c>
       <c r="E36" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="F36" t="n">
-        <v>11.1</v>
+        <v>12.3</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>58.12</v>
+        <v>71.42</v>
       </c>
       <c r="I36" t="n">
-        <v>59.88</v>
+        <v>71.8</v>
       </c>
       <c r="J36" t="n">
-        <v>56.65</v>
+        <v>71.13</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M36" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
-        <v>6190</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>20.59</v>
+        <v>17.74</v>
       </c>
       <c r="C37" t="n">
-        <v>21.02</v>
+        <v>17.78</v>
       </c>
       <c r="D37" t="n">
-        <v>20.23</v>
+        <v>17.68</v>
       </c>
       <c r="E37" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>55.26</v>
+        <v>71.53</v>
       </c>
       <c r="I37" t="n">
-        <v>56.46</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>54.02</v>
+        <v>70.67</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M37" t="n">
         <v>2</v>
       </c>
-      <c r="M37" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N37" t="n">
-        <v>6200</v>
+        <v>6152</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>21.34</v>
+        <v>18.17</v>
       </c>
       <c r="C38" t="n">
-        <v>21.65</v>
+        <v>18.45</v>
       </c>
       <c r="D38" t="n">
-        <v>20.98</v>
+        <v>17.85</v>
       </c>
       <c r="E38" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="F38" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="G38" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>52.89</v>
+        <v>67.5</v>
       </c>
       <c r="I38" t="n">
-        <v>53.97</v>
+        <v>70.09</v>
       </c>
       <c r="J38" t="n">
-        <v>51.51</v>
+        <v>65.53</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>6220</v>
+        <v>6152</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>22.22</v>
+        <v>19.12</v>
       </c>
       <c r="C39" t="n">
-        <v>22.72</v>
+        <v>19.48</v>
       </c>
       <c r="D39" t="n">
-        <v>21.71</v>
+        <v>18.59</v>
       </c>
       <c r="E39" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="F39" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="G39" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>50.44</v>
+        <v>62.25</v>
       </c>
       <c r="I39" t="n">
-        <v>51.7</v>
+        <v>64.8</v>
       </c>
       <c r="J39" t="n">
-        <v>49.53</v>
+        <v>60.27</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="N39" t="n">
-        <v>6240</v>
+        <v>6180</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>22.94</v>
+        <v>19.89</v>
       </c>
       <c r="C40" t="n">
-        <v>23.82</v>
+        <v>20.2</v>
       </c>
       <c r="D40" t="n">
-        <v>22.29</v>
+        <v>19.54</v>
       </c>
       <c r="E40" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="F40" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="G40" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>46.37</v>
+        <v>58.12</v>
       </c>
       <c r="I40" t="n">
-        <v>49.68</v>
+        <v>59.88</v>
       </c>
       <c r="J40" t="n">
-        <v>44.22</v>
+        <v>56.65</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="N40" t="n">
-        <v>6250</v>
+        <v>6190</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>23.12</v>
+        <v>20.59</v>
       </c>
       <c r="C41" t="n">
-        <v>24.14</v>
+        <v>21.02</v>
       </c>
       <c r="D41" t="n">
-        <v>22.72</v>
+        <v>20.23</v>
       </c>
       <c r="E41" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F41" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>344</v>
+        <v>6</v>
       </c>
       <c r="H41" t="n">
-        <v>45.59</v>
+        <v>55.26</v>
       </c>
       <c r="I41" t="n">
-        <v>46.9</v>
+        <v>56.46</v>
       </c>
       <c r="J41" t="n">
-        <v>43.18</v>
+        <v>54.02</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" t="n">
         <v>2.6</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.7</v>
-      </c>
       <c r="N41" t="n">
-        <v>6240</v>
+        <v>6200</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>22.76</v>
+        <v>21.34</v>
       </c>
       <c r="C42" t="n">
-        <v>23.63</v>
+        <v>21.65</v>
       </c>
       <c r="D42" t="n">
-        <v>22.08</v>
+        <v>20.98</v>
       </c>
       <c r="E42" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F42" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G42" t="n">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="H42" t="n">
-        <v>47.51</v>
+        <v>52.89</v>
       </c>
       <c r="I42" t="n">
-        <v>49.36</v>
+        <v>53.97</v>
       </c>
       <c r="J42" t="n">
-        <v>46.08</v>
+        <v>51.51</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="N42" t="n">
-        <v>6240</v>
+        <v>6220</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22.55</v>
+        <v>22.22</v>
       </c>
       <c r="C43" t="n">
-        <v>23.29</v>
+        <v>22.72</v>
       </c>
       <c r="D43" t="n">
-        <v>21.68</v>
+        <v>21.71</v>
       </c>
       <c r="E43" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="F43" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="G43" t="n">
-        <v>364</v>
+        <v>210</v>
       </c>
       <c r="H43" t="n">
-        <v>47.88</v>
+        <v>50.44</v>
       </c>
       <c r="I43" t="n">
-        <v>50.32</v>
+        <v>51.7</v>
       </c>
       <c r="J43" t="n">
-        <v>46.13</v>
+        <v>49.53</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N43" t="n">
-        <v>6220</v>
+        <v>6240</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>22.47</v>
+        <v>22.94</v>
       </c>
       <c r="C44" t="n">
-        <v>23.42</v>
+        <v>23.82</v>
       </c>
       <c r="D44" t="n">
-        <v>21.73</v>
+        <v>22.29</v>
       </c>
       <c r="E44" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="F44" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="G44" t="n">
-        <v>531</v>
+        <v>355</v>
       </c>
       <c r="H44" t="n">
-        <v>49.09</v>
+        <v>46.37</v>
       </c>
       <c r="I44" t="n">
-        <v>51.32</v>
+        <v>49.68</v>
       </c>
       <c r="J44" t="n">
-        <v>46.18</v>
+        <v>44.22</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="M44" t="n">
         <v>3.8</v>
       </c>
       <c r="N44" t="n">
-        <v>6230</v>
+        <v>6250</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21.72</v>
+        <v>23.12</v>
       </c>
       <c r="C45" t="n">
-        <v>23.46</v>
+        <v>24.14</v>
       </c>
       <c r="D45" t="n">
-        <v>20.79</v>
+        <v>22.72</v>
       </c>
       <c r="E45" t="n">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="F45" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="G45" t="n">
-        <v>616</v>
+        <v>344</v>
       </c>
       <c r="H45" t="n">
-        <v>52.51</v>
+        <v>45.59</v>
       </c>
       <c r="I45" t="n">
-        <v>55.76</v>
+        <v>46.9</v>
       </c>
       <c r="J45" t="n">
-        <v>47.65</v>
+        <v>43.18</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N45" t="n">
-        <v>6220</v>
+        <v>6240</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20.86</v>
+        <v>22.76</v>
       </c>
       <c r="C46" t="n">
-        <v>21.56</v>
+        <v>23.63</v>
       </c>
       <c r="D46" t="n">
-        <v>20.25</v>
+        <v>22.08</v>
       </c>
       <c r="E46" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
       </c>
       <c r="F46" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G46" t="n">
-        <v>642</v>
+        <v>462</v>
       </c>
       <c r="H46" t="n">
-        <v>56.36</v>
+        <v>47.51</v>
       </c>
       <c r="I46" t="n">
-        <v>59</v>
+        <v>49.36</v>
       </c>
       <c r="J46" t="n">
-        <v>53.69</v>
+        <v>46.08</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>6190</v>
+        <v>6240</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>19.5</v>
+        <v>22.55</v>
       </c>
       <c r="C47" t="n">
-        <v>19.99</v>
+        <v>23.29</v>
       </c>
       <c r="D47" t="n">
-        <v>19.01</v>
+        <v>21.68</v>
       </c>
       <c r="E47" t="n">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="F47" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="G47" t="n">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="H47" t="n">
-        <v>61.31</v>
+        <v>47.88</v>
       </c>
       <c r="I47" t="n">
-        <v>62.89</v>
+        <v>50.32</v>
       </c>
       <c r="J47" t="n">
-        <v>59.57</v>
+        <v>46.13</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.96</v>
+        <v>22.47</v>
       </c>
       <c r="C48" t="n">
-        <v>18.97</v>
+        <v>23.42</v>
       </c>
       <c r="D48" t="n">
-        <v>17.06</v>
+        <v>21.73</v>
       </c>
       <c r="E48" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="F48" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="G48" t="n">
-        <v>158</v>
+        <v>531</v>
       </c>
       <c r="H48" t="n">
-        <v>69.53</v>
+        <v>49.09</v>
       </c>
       <c r="I48" t="n">
-        <v>74.66</v>
+        <v>51.32</v>
       </c>
       <c r="J48" t="n">
-        <v>64.09</v>
+        <v>46.18</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="M48" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="N48" t="n">
-        <v>6180</v>
+        <v>6230</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16.73</v>
+        <v>21.72</v>
       </c>
       <c r="C49" t="n">
-        <v>16.97</v>
+        <v>23.46</v>
       </c>
       <c r="D49" t="n">
-        <v>16.64</v>
+        <v>20.79</v>
       </c>
       <c r="E49" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
       <c r="F49" t="n">
-        <v>12.4</v>
+        <v>11</v>
       </c>
       <c r="G49" t="n">
-        <v>33</v>
+        <v>616</v>
       </c>
       <c r="H49" t="n">
-        <v>76.20999999999999</v>
+        <v>52.51</v>
       </c>
       <c r="I49" t="n">
-        <v>76.59999999999999</v>
+        <v>55.76</v>
       </c>
       <c r="J49" t="n">
-        <v>75.42</v>
+        <v>47.65</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="M49" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="N49" t="n">
-        <v>6162</v>
+        <v>6220</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>16.74</v>
+        <v>20.86</v>
       </c>
       <c r="C50" t="n">
-        <v>16.83</v>
+        <v>21.56</v>
       </c>
       <c r="D50" t="n">
-        <v>16.69</v>
+        <v>20.25</v>
       </c>
       <c r="E50" t="n">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="F50" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="H50" t="n">
-        <v>76.59</v>
+        <v>56.36</v>
       </c>
       <c r="I50" t="n">
-        <v>77.48</v>
+        <v>59</v>
       </c>
       <c r="J50" t="n">
-        <v>75.81999999999999</v>
+        <v>53.69</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="M50" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O50" t="n">
         <v>3.7</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,82 +508,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.93</v>
+        <v>22.85</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>22.93</v>
       </c>
       <c r="D2" t="n">
-        <v>19.87</v>
+        <v>22.75</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="G2" t="n">
-        <v>218</v>
+        <v>416</v>
       </c>
       <c r="H2" t="n">
-        <v>54.82</v>
+        <v>43.45</v>
       </c>
       <c r="I2" t="n">
-        <v>56.41</v>
+        <v>44.07</v>
       </c>
       <c r="J2" t="n">
-        <v>54.01</v>
+        <v>43.12</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.38</v>
+        <v>22.23</v>
       </c>
       <c r="C3" t="n">
-        <v>19.85</v>
+        <v>22.76</v>
       </c>
       <c r="D3" t="n">
-        <v>18.89</v>
+        <v>21.86</v>
       </c>
       <c r="E3" t="n">
-        <v>11.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>383</v>
       </c>
       <c r="H3" t="n">
-        <v>61.37</v>
+        <v>45.63</v>
       </c>
       <c r="I3" t="n">
-        <v>65.44</v>
+        <v>47.01</v>
       </c>
       <c r="J3" t="n">
-        <v>57.45</v>
+        <v>44.24</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -592,327 +592,327 @@
         <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="N3" t="n">
-        <v>6152</v>
+        <v>6180</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.52</v>
+        <v>21.57</v>
       </c>
       <c r="C4" t="n">
-        <v>18.87</v>
+        <v>22.64</v>
       </c>
       <c r="D4" t="n">
-        <v>18.23</v>
+        <v>20.71</v>
       </c>
       <c r="E4" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>34</v>
+        <v>373</v>
       </c>
       <c r="H4" t="n">
-        <v>67.5</v>
+        <v>48.34</v>
       </c>
       <c r="I4" t="n">
-        <v>70.43000000000001</v>
+        <v>51.45</v>
       </c>
       <c r="J4" t="n">
-        <v>65.33</v>
+        <v>45.03</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N4" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.89</v>
+        <v>20.3</v>
       </c>
       <c r="C5" t="n">
-        <v>18.27</v>
+        <v>20.76</v>
       </c>
       <c r="D5" t="n">
-        <v>17.53</v>
+        <v>19.87</v>
       </c>
       <c r="E5" t="n">
-        <v>13.1</v>
+        <v>10.3</v>
       </c>
       <c r="F5" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>231</v>
       </c>
       <c r="H5" t="n">
-        <v>74.15000000000001</v>
+        <v>53.23</v>
       </c>
       <c r="I5" t="n">
-        <v>77.34999999999999</v>
+        <v>56.41</v>
       </c>
       <c r="J5" t="n">
-        <v>70.23999999999999</v>
+        <v>51.05</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N5" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.34</v>
+        <v>19.38</v>
       </c>
       <c r="C6" t="n">
-        <v>17.48</v>
+        <v>19.85</v>
       </c>
       <c r="D6" t="n">
-        <v>17.19</v>
+        <v>18.89</v>
       </c>
       <c r="E6" t="n">
-        <v>13.3</v>
+        <v>11.6</v>
       </c>
       <c r="F6" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H6" t="n">
-        <v>78.27</v>
+        <v>61.37</v>
       </c>
       <c r="I6" t="n">
-        <v>79.16</v>
+        <v>65.44</v>
       </c>
       <c r="J6" t="n">
-        <v>77.5</v>
+        <v>57.45</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.62</v>
+        <v>18.52</v>
       </c>
       <c r="C7" t="n">
-        <v>17.85</v>
+        <v>18.87</v>
       </c>
       <c r="D7" t="n">
-        <v>17.33</v>
+        <v>18.23</v>
       </c>
       <c r="E7" t="n">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="F7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H7" t="n">
-        <v>74.13</v>
+        <v>67.5</v>
       </c>
       <c r="I7" t="n">
-        <v>77.06</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>71.3</v>
+        <v>65.33</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.72</v>
+        <v>17.89</v>
       </c>
       <c r="C8" t="n">
-        <v>18.84</v>
+        <v>18.27</v>
       </c>
       <c r="D8" t="n">
-        <v>17.46</v>
+        <v>17.53</v>
       </c>
       <c r="E8" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="F8" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>71.95999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>74.59999999999999</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>65.83</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.99</v>
+        <v>17.34</v>
       </c>
       <c r="C9" t="n">
-        <v>19.05</v>
+        <v>17.48</v>
       </c>
       <c r="D9" t="n">
-        <v>18.9</v>
+        <v>17.19</v>
       </c>
       <c r="E9" t="n">
-        <v>11.5</v>
+        <v>13.3</v>
       </c>
       <c r="F9" t="n">
-        <v>11.3</v>
+        <v>13.1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>62.56</v>
+        <v>78.27</v>
       </c>
       <c r="I9" t="n">
-        <v>63.18</v>
+        <v>79.16</v>
       </c>
       <c r="J9" t="n">
-        <v>61.89</v>
+        <v>77.5</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N9" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19.33</v>
+        <v>17.62</v>
       </c>
       <c r="C10" t="n">
-        <v>19.55</v>
+        <v>17.85</v>
       </c>
       <c r="D10" t="n">
-        <v>19.01</v>
+        <v>17.33</v>
       </c>
       <c r="E10" t="n">
-        <v>11.4</v>
+        <v>12.8</v>
       </c>
       <c r="F10" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>60.72</v>
+        <v>74.13</v>
       </c>
       <c r="I10" t="n">
-        <v>62.8</v>
+        <v>77.06</v>
       </c>
       <c r="J10" t="n">
-        <v>59.1</v>
+        <v>71.3</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -921,54 +921,54 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.52</v>
+        <v>17.72</v>
       </c>
       <c r="C11" t="n">
-        <v>19.58</v>
+        <v>18.84</v>
       </c>
       <c r="D11" t="n">
-        <v>19.46</v>
+        <v>17.46</v>
       </c>
       <c r="E11" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F11" t="n">
-        <v>11.2</v>
+        <v>12.1</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>60.01</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>60.64</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>59.58</v>
+        <v>65.83</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>6152</v>
@@ -978,35 +978,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.62</v>
+        <v>18.99</v>
       </c>
       <c r="C12" t="n">
-        <v>19.71</v>
+        <v>19.05</v>
       </c>
       <c r="D12" t="n">
-        <v>19.49</v>
+        <v>18.9</v>
       </c>
       <c r="E12" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F12" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>60.63</v>
+        <v>62.56</v>
       </c>
       <c r="I12" t="n">
-        <v>61.71</v>
+        <v>63.18</v>
       </c>
       <c r="J12" t="n">
-        <v>59.73</v>
+        <v>61.89</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1025,129 +1025,129 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19.79</v>
+        <v>19.33</v>
       </c>
       <c r="C13" t="n">
-        <v>20.01</v>
+        <v>19.55</v>
       </c>
       <c r="D13" t="n">
-        <v>19.61</v>
+        <v>19.01</v>
       </c>
       <c r="E13" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F13" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>60.18</v>
+        <v>60.72</v>
       </c>
       <c r="I13" t="n">
-        <v>61.23</v>
+        <v>62.8</v>
       </c>
       <c r="J13" t="n">
-        <v>59.04</v>
+        <v>59.1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="N13" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20.19</v>
+        <v>19.52</v>
       </c>
       <c r="C14" t="n">
-        <v>20.36</v>
+        <v>19.58</v>
       </c>
       <c r="D14" t="n">
-        <v>20.01</v>
+        <v>19.46</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F14" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>58.19</v>
+        <v>60.01</v>
       </c>
       <c r="I14" t="n">
-        <v>59.14</v>
+        <v>60.64</v>
       </c>
       <c r="J14" t="n">
-        <v>57.54</v>
+        <v>59.58</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="N14" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20.44</v>
+        <v>19.62</v>
       </c>
       <c r="C15" t="n">
-        <v>20.64</v>
+        <v>19.71</v>
       </c>
       <c r="D15" t="n">
-        <v>20.37</v>
+        <v>19.49</v>
       </c>
       <c r="E15" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F15" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>57.96</v>
+        <v>60.63</v>
       </c>
       <c r="I15" t="n">
-        <v>58.31</v>
+        <v>61.71</v>
       </c>
       <c r="J15" t="n">
-        <v>57.52</v>
+        <v>59.73</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1159,42 +1159,42 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20.99</v>
+        <v>19.79</v>
       </c>
       <c r="C16" t="n">
-        <v>21.3</v>
+        <v>20.01</v>
       </c>
       <c r="D16" t="n">
-        <v>20.64</v>
+        <v>19.61</v>
       </c>
       <c r="E16" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F16" t="n">
         <v>11.6</v>
       </c>
-      <c r="F16" t="n">
-        <v>11.5</v>
-      </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>55.76</v>
+        <v>60.18</v>
       </c>
       <c r="I16" t="n">
-        <v>57.26</v>
+        <v>61.23</v>
       </c>
       <c r="J16" t="n">
-        <v>54.28</v>
+        <v>59.04</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1203,186 +1203,186 @@
         <v>0.2</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N16" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21.82</v>
+        <v>20.19</v>
       </c>
       <c r="C17" t="n">
-        <v>22.25</v>
+        <v>20.36</v>
       </c>
       <c r="D17" t="n">
-        <v>21.38</v>
+        <v>20.01</v>
       </c>
       <c r="E17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F17" t="n">
         <v>11.4</v>
       </c>
-      <c r="F17" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>52.03</v>
+        <v>58.19</v>
       </c>
       <c r="I17" t="n">
-        <v>53.83</v>
+        <v>59.14</v>
       </c>
       <c r="J17" t="n">
-        <v>50.23</v>
+        <v>57.54</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N17" t="n">
-        <v>6180</v>
+        <v>6132</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22.61</v>
+        <v>20.44</v>
       </c>
       <c r="C18" t="n">
-        <v>22.85</v>
+        <v>20.64</v>
       </c>
       <c r="D18" t="n">
-        <v>22.34</v>
+        <v>20.37</v>
       </c>
       <c r="E18" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G18" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>49.28</v>
+        <v>57.96</v>
       </c>
       <c r="I18" t="n">
-        <v>50.37</v>
+        <v>58.31</v>
       </c>
       <c r="J18" t="n">
-        <v>48.38</v>
+        <v>57.52</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.26</v>
+        <v>20.99</v>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>21.3</v>
       </c>
       <c r="D19" t="n">
-        <v>22.73</v>
+        <v>20.64</v>
       </c>
       <c r="E19" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F19" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="G19" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>47.55</v>
+        <v>55.76</v>
       </c>
       <c r="I19" t="n">
-        <v>48.93</v>
+        <v>57.26</v>
       </c>
       <c r="J19" t="n">
-        <v>45.68</v>
+        <v>54.28</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N19" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.81</v>
+        <v>21.82</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>22.25</v>
       </c>
       <c r="D20" t="n">
-        <v>21.97</v>
+        <v>21.38</v>
       </c>
       <c r="E20" t="n">
         <v>11.4</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="G20" t="n">
-        <v>373</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>49.12</v>
+        <v>52.03</v>
       </c>
       <c r="I20" t="n">
-        <v>52.45</v>
+        <v>53.83</v>
       </c>
       <c r="J20" t="n">
-        <v>45.39</v>
+        <v>50.23</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1391,195 +1391,195 @@
         <v>0.7</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.82</v>
+        <v>22.61</v>
       </c>
       <c r="C21" t="n">
-        <v>21.95</v>
+        <v>22.85</v>
       </c>
       <c r="D21" t="n">
-        <v>21.73</v>
+        <v>22.34</v>
       </c>
       <c r="E21" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F21" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="H21" t="n">
-        <v>52.7</v>
+        <v>49.28</v>
       </c>
       <c r="I21" t="n">
-        <v>52.97</v>
+        <v>50.37</v>
       </c>
       <c r="J21" t="n">
-        <v>52.47</v>
+        <v>48.38</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="N21" t="n">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21.74</v>
+        <v>23.26</v>
       </c>
       <c r="C22" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>21.56</v>
+        <v>22.73</v>
       </c>
       <c r="E22" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="F22" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="G22" t="n">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="H22" t="n">
-        <v>52.76</v>
+        <v>47.55</v>
       </c>
       <c r="I22" t="n">
-        <v>53.57</v>
+        <v>48.93</v>
       </c>
       <c r="J22" t="n">
-        <v>52.06</v>
+        <v>45.68</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21.42</v>
+        <v>22.81</v>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>20.92</v>
+        <v>21.97</v>
       </c>
       <c r="E23" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>218</v>
+        <v>373</v>
       </c>
       <c r="H23" t="n">
-        <v>54.49</v>
+        <v>49.12</v>
       </c>
       <c r="I23" t="n">
-        <v>56.38</v>
+        <v>52.45</v>
       </c>
       <c r="J23" t="n">
-        <v>52.2</v>
+        <v>45.39</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N23" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21.35</v>
+        <v>21.82</v>
       </c>
       <c r="C24" t="n">
-        <v>22.22</v>
+        <v>21.95</v>
       </c>
       <c r="D24" t="n">
-        <v>20.87</v>
+        <v>21.73</v>
       </c>
       <c r="E24" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F24" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G24" t="n">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="H24" t="n">
-        <v>55.07</v>
+        <v>52.7</v>
       </c>
       <c r="I24" t="n">
-        <v>56.71</v>
+        <v>52.97</v>
       </c>
       <c r="J24" t="n">
-        <v>52.16</v>
+        <v>52.47</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="N24" t="n">
         <v>6190</v>
@@ -1589,252 +1589,252 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21.1</v>
+        <v>21.74</v>
       </c>
       <c r="C25" t="n">
-        <v>21.69</v>
+        <v>21.95</v>
       </c>
       <c r="D25" t="n">
-        <v>20.51</v>
+        <v>21.56</v>
       </c>
       <c r="E25" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="F25" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G25" t="n">
-        <v>480</v>
+        <v>165</v>
       </c>
       <c r="H25" t="n">
-        <v>55.96</v>
+        <v>52.76</v>
       </c>
       <c r="I25" t="n">
-        <v>58.01</v>
+        <v>53.57</v>
       </c>
       <c r="J25" t="n">
-        <v>53.81</v>
+        <v>52.06</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="N25" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20.15</v>
+        <v>21.42</v>
       </c>
       <c r="C26" t="n">
-        <v>20.85</v>
+        <v>22</v>
       </c>
       <c r="D26" t="n">
-        <v>19.57</v>
+        <v>20.92</v>
       </c>
       <c r="E26" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="F26" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G26" t="n">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="H26" t="n">
-        <v>60.77</v>
+        <v>54.49</v>
       </c>
       <c r="I26" t="n">
-        <v>64.81</v>
+        <v>56.38</v>
       </c>
       <c r="J26" t="n">
-        <v>56.73</v>
+        <v>52.2</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.37</v>
+        <v>21.35</v>
       </c>
       <c r="C27" t="n">
-        <v>19.79</v>
+        <v>22.22</v>
       </c>
       <c r="D27" t="n">
-        <v>18.91</v>
+        <v>20.87</v>
       </c>
       <c r="E27" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F27" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G27" t="n">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="H27" t="n">
-        <v>65.04000000000001</v>
+        <v>55.07</v>
       </c>
       <c r="I27" t="n">
-        <v>66.98999999999999</v>
+        <v>56.71</v>
       </c>
       <c r="J27" t="n">
-        <v>63.19</v>
+        <v>52.16</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N27" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.41</v>
+        <v>21.1</v>
       </c>
       <c r="C28" t="n">
-        <v>18.85</v>
+        <v>21.69</v>
       </c>
       <c r="D28" t="n">
-        <v>18.05</v>
+        <v>20.51</v>
       </c>
       <c r="E28" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F28" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G28" t="n">
-        <v>76</v>
+        <v>480</v>
       </c>
       <c r="H28" t="n">
-        <v>69.37</v>
+        <v>55.96</v>
       </c>
       <c r="I28" t="n">
-        <v>71.67</v>
+        <v>58.01</v>
       </c>
       <c r="J28" t="n">
-        <v>67.22</v>
+        <v>53.81</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>6170</v>
+        <v>6210</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.66</v>
+        <v>20.15</v>
       </c>
       <c r="C29" t="n">
-        <v>17.95</v>
+        <v>20.85</v>
       </c>
       <c r="D29" t="n">
-        <v>17.51</v>
+        <v>19.57</v>
       </c>
       <c r="E29" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="F29" t="n">
-        <v>12.6</v>
+        <v>11.6</v>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
+        <v>266</v>
       </c>
       <c r="H29" t="n">
-        <v>73.31</v>
+        <v>60.77</v>
       </c>
       <c r="I29" t="n">
-        <v>74.14</v>
+        <v>64.81</v>
       </c>
       <c r="J29" t="n">
-        <v>72.19</v>
+        <v>56.73</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="N29" t="n">
-        <v>6162</v>
+        <v>6200</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.6</v>
+        <v>19.37</v>
       </c>
       <c r="C30" t="n">
-        <v>17.68</v>
+        <v>19.79</v>
       </c>
       <c r="D30" t="n">
-        <v>17.49</v>
+        <v>18.91</v>
       </c>
       <c r="E30" t="n">
         <v>12.4</v>
@@ -1843,110 +1843,110 @@
         <v>12.3</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="H30" t="n">
-        <v>72.5</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>73.76000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>71.78</v>
+        <v>63.19</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="N30" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.53</v>
+        <v>18.41</v>
       </c>
       <c r="C31" t="n">
-        <v>17.62</v>
+        <v>18.85</v>
       </c>
       <c r="D31" t="n">
-        <v>17.45</v>
+        <v>18.05</v>
       </c>
       <c r="E31" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F31" t="n">
         <v>12.4</v>
       </c>
-      <c r="F31" t="n">
-        <v>12.2</v>
-      </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H31" t="n">
-        <v>72.33</v>
+        <v>69.37</v>
       </c>
       <c r="I31" t="n">
-        <v>72.88</v>
+        <v>71.67</v>
       </c>
       <c r="J31" t="n">
-        <v>71.93000000000001</v>
+        <v>67.22</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="N31" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.64</v>
+        <v>17.66</v>
       </c>
       <c r="C32" t="n">
-        <v>17.9</v>
+        <v>17.95</v>
       </c>
       <c r="D32" t="n">
-        <v>17.44</v>
+        <v>17.51</v>
       </c>
       <c r="E32" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F32" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H32" t="n">
-        <v>71.73999999999999</v>
+        <v>73.31</v>
       </c>
       <c r="I32" t="n">
-        <v>73.59999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="J32" t="n">
-        <v>69.53</v>
+        <v>72.19</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1955,499 +1955,499 @@
         <v>0.3</v>
       </c>
       <c r="M32" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="N32" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.84</v>
+        <v>17.6</v>
       </c>
       <c r="C33" t="n">
-        <v>17.88</v>
+        <v>17.68</v>
       </c>
       <c r="D33" t="n">
-        <v>17.8</v>
+        <v>17.49</v>
       </c>
       <c r="E33" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F33" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>70.06999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I33" t="n">
-        <v>70.3</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>69.65000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="N33" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.9</v>
+        <v>17.53</v>
       </c>
       <c r="C34" t="n">
-        <v>17.97</v>
+        <v>17.62</v>
       </c>
       <c r="D34" t="n">
-        <v>17.82</v>
+        <v>17.45</v>
       </c>
       <c r="E34" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="F34" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>69.79000000000001</v>
+        <v>72.33</v>
       </c>
       <c r="I34" t="n">
-        <v>70.48999999999999</v>
+        <v>72.88</v>
       </c>
       <c r="J34" t="n">
-        <v>69.43000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M34" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N34" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.74</v>
+        <v>17.64</v>
       </c>
       <c r="C35" t="n">
-        <v>17.82</v>
+        <v>17.9</v>
       </c>
       <c r="D35" t="n">
-        <v>17.7</v>
+        <v>17.44</v>
       </c>
       <c r="E35" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F35" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>70.81999999999999</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>70.98</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>70.54000000000001</v>
+        <v>69.53</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M35" t="n">
         <v>1.4</v>
       </c>
       <c r="N35" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.68</v>
+        <v>17.84</v>
       </c>
       <c r="C36" t="n">
-        <v>17.71</v>
+        <v>17.88</v>
       </c>
       <c r="D36" t="n">
-        <v>17.64</v>
+        <v>17.8</v>
       </c>
       <c r="E36" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F36" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>71.42</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>71.8</v>
+        <v>70.3</v>
       </c>
       <c r="J36" t="n">
-        <v>71.13</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N36" t="n">
         <v>6162</v>
       </c>
-      <c r="O36" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.74</v>
+        <v>17.9</v>
       </c>
       <c r="C37" t="n">
-        <v>17.78</v>
+        <v>17.97</v>
       </c>
       <c r="D37" t="n">
-        <v>17.68</v>
+        <v>17.82</v>
       </c>
       <c r="E37" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F37" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>71.53</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>72.06999999999999</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>70.67</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N37" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18.17</v>
+        <v>17.74</v>
       </c>
       <c r="C38" t="n">
-        <v>18.45</v>
+        <v>17.82</v>
       </c>
       <c r="D38" t="n">
-        <v>17.85</v>
+        <v>17.7</v>
       </c>
       <c r="E38" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="F38" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>67.5</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>70.09</v>
+        <v>70.98</v>
       </c>
       <c r="J38" t="n">
-        <v>65.53</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N38" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>19.12</v>
+        <v>17.68</v>
       </c>
       <c r="C39" t="n">
-        <v>19.48</v>
+        <v>17.71</v>
       </c>
       <c r="D39" t="n">
-        <v>18.59</v>
+        <v>17.64</v>
       </c>
       <c r="E39" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="F39" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>62.25</v>
+        <v>71.42</v>
       </c>
       <c r="I39" t="n">
-        <v>64.8</v>
+        <v>71.8</v>
       </c>
       <c r="J39" t="n">
-        <v>60.27</v>
+        <v>71.13</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>6180</v>
-      </c>
-      <c r="O39" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19.89</v>
+        <v>17.74</v>
       </c>
       <c r="C40" t="n">
-        <v>20.2</v>
+        <v>17.78</v>
       </c>
       <c r="D40" t="n">
-        <v>19.54</v>
+        <v>17.68</v>
       </c>
       <c r="E40" t="n">
-        <v>11.2</v>
+        <v>12.4</v>
       </c>
       <c r="F40" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>58.12</v>
+        <v>71.53</v>
       </c>
       <c r="I40" t="n">
-        <v>59.88</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>56.65</v>
+        <v>70.67</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="M40" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N40" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20.59</v>
+        <v>18.17</v>
       </c>
       <c r="C41" t="n">
-        <v>21.02</v>
+        <v>18.45</v>
       </c>
       <c r="D41" t="n">
-        <v>20.23</v>
+        <v>17.85</v>
       </c>
       <c r="E41" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>55.26</v>
+        <v>67.5</v>
       </c>
       <c r="I41" t="n">
-        <v>56.46</v>
+        <v>70.09</v>
       </c>
       <c r="J41" t="n">
-        <v>54.02</v>
+        <v>65.53</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M41" t="n">
         <v>2</v>
       </c>
-      <c r="M41" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N41" t="n">
-        <v>6200</v>
+        <v>6152</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>21.34</v>
+        <v>19.12</v>
       </c>
       <c r="C42" t="n">
-        <v>21.65</v>
+        <v>19.48</v>
       </c>
       <c r="D42" t="n">
-        <v>20.98</v>
+        <v>18.59</v>
       </c>
       <c r="E42" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="F42" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="G42" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>52.89</v>
+        <v>62.25</v>
       </c>
       <c r="I42" t="n">
-        <v>53.97</v>
+        <v>64.8</v>
       </c>
       <c r="J42" t="n">
-        <v>51.51</v>
+        <v>60.27</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="M42" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="N42" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22.22</v>
+        <v>19.89</v>
       </c>
       <c r="C43" t="n">
-        <v>22.72</v>
+        <v>20.2</v>
       </c>
       <c r="D43" t="n">
-        <v>21.71</v>
+        <v>19.54</v>
       </c>
       <c r="E43" t="n">
         <v>11.2</v>
@@ -2456,166 +2456,166 @@
         <v>11.1</v>
       </c>
       <c r="G43" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>50.44</v>
+        <v>58.12</v>
       </c>
       <c r="I43" t="n">
-        <v>51.7</v>
+        <v>59.88</v>
       </c>
       <c r="J43" t="n">
-        <v>49.53</v>
+        <v>56.65</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="M43" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="N43" t="n">
-        <v>6240</v>
+        <v>6190</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>22.94</v>
+        <v>20.59</v>
       </c>
       <c r="C44" t="n">
-        <v>23.82</v>
+        <v>21.02</v>
       </c>
       <c r="D44" t="n">
-        <v>22.29</v>
+        <v>20.23</v>
       </c>
       <c r="E44" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="F44" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>355</v>
+        <v>6</v>
       </c>
       <c r="H44" t="n">
-        <v>46.37</v>
+        <v>55.26</v>
       </c>
       <c r="I44" t="n">
-        <v>49.68</v>
+        <v>56.46</v>
       </c>
       <c r="J44" t="n">
-        <v>44.22</v>
+        <v>54.02</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N44" t="n">
-        <v>6250</v>
+        <v>6200</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>23.12</v>
+        <v>21.34</v>
       </c>
       <c r="C45" t="n">
-        <v>24.14</v>
+        <v>21.65</v>
       </c>
       <c r="D45" t="n">
-        <v>22.72</v>
+        <v>20.98</v>
       </c>
       <c r="E45" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F45" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G45" t="n">
-        <v>344</v>
+        <v>63</v>
       </c>
       <c r="H45" t="n">
-        <v>45.59</v>
+        <v>52.89</v>
       </c>
       <c r="I45" t="n">
-        <v>46.9</v>
+        <v>53.97</v>
       </c>
       <c r="J45" t="n">
-        <v>43.18</v>
+        <v>51.51</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M45" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="N45" t="n">
-        <v>6240</v>
+        <v>6220</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22.76</v>
+        <v>22.22</v>
       </c>
       <c r="C46" t="n">
-        <v>23.63</v>
+        <v>22.72</v>
       </c>
       <c r="D46" t="n">
-        <v>22.08</v>
+        <v>21.71</v>
       </c>
       <c r="E46" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="F46" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="G46" t="n">
-        <v>462</v>
+        <v>210</v>
       </c>
       <c r="H46" t="n">
-        <v>47.51</v>
+        <v>50.44</v>
       </c>
       <c r="I46" t="n">
-        <v>49.36</v>
+        <v>51.7</v>
       </c>
       <c r="J46" t="n">
-        <v>46.08</v>
+        <v>49.53</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N46" t="n">
         <v>6240</v>
@@ -2625,188 +2625,188 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>22.55</v>
+        <v>22.94</v>
       </c>
       <c r="C47" t="n">
-        <v>23.29</v>
+        <v>23.82</v>
       </c>
       <c r="D47" t="n">
-        <v>21.68</v>
+        <v>22.29</v>
       </c>
       <c r="E47" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="F47" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="G47" t="n">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H47" t="n">
-        <v>47.88</v>
+        <v>46.37</v>
       </c>
       <c r="I47" t="n">
-        <v>50.32</v>
+        <v>49.68</v>
       </c>
       <c r="J47" t="n">
-        <v>46.13</v>
+        <v>44.22</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N47" t="n">
-        <v>6220</v>
+        <v>6250</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.47</v>
+        <v>23.12</v>
       </c>
       <c r="C48" t="n">
-        <v>23.42</v>
+        <v>24.14</v>
       </c>
       <c r="D48" t="n">
-        <v>21.73</v>
+        <v>22.72</v>
       </c>
       <c r="E48" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="F48" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="G48" t="n">
-        <v>531</v>
+        <v>344</v>
       </c>
       <c r="H48" t="n">
-        <v>49.09</v>
+        <v>45.59</v>
       </c>
       <c r="I48" t="n">
-        <v>51.32</v>
+        <v>46.9</v>
       </c>
       <c r="J48" t="n">
-        <v>46.18</v>
+        <v>43.18</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="M48" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N48" t="n">
-        <v>6230</v>
+        <v>6240</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>21.72</v>
+        <v>22.76</v>
       </c>
       <c r="C49" t="n">
-        <v>23.46</v>
+        <v>23.63</v>
       </c>
       <c r="D49" t="n">
-        <v>20.79</v>
+        <v>22.08</v>
       </c>
       <c r="E49" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G49" t="n">
-        <v>616</v>
+        <v>462</v>
       </c>
       <c r="H49" t="n">
-        <v>52.51</v>
+        <v>47.51</v>
       </c>
       <c r="I49" t="n">
-        <v>55.76</v>
+        <v>49.36</v>
       </c>
       <c r="J49" t="n">
-        <v>47.65</v>
+        <v>46.08</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M49" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>6220</v>
+        <v>6240</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>20.86</v>
+        <v>22.55</v>
       </c>
       <c r="C50" t="n">
-        <v>21.56</v>
+        <v>23.29</v>
       </c>
       <c r="D50" t="n">
-        <v>20.25</v>
+        <v>21.68</v>
       </c>
       <c r="E50" t="n">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="F50" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G50" t="n">
-        <v>642</v>
+        <v>364</v>
       </c>
       <c r="H50" t="n">
-        <v>56.36</v>
+        <v>47.88</v>
       </c>
       <c r="I50" t="n">
-        <v>59</v>
+        <v>50.32</v>
       </c>
       <c r="J50" t="n">
-        <v>53.69</v>
+        <v>46.13</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O50" t="n">
         <v>3.7</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,44 +508,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.85</v>
+        <v>23.63</v>
       </c>
       <c r="C2" t="n">
-        <v>22.93</v>
+        <v>23.93</v>
       </c>
       <c r="D2" t="n">
-        <v>22.75</v>
+        <v>23.26</v>
       </c>
       <c r="E2" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="G2" t="n">
-        <v>416</v>
+        <v>334</v>
       </c>
       <c r="H2" t="n">
-        <v>43.45</v>
+        <v>42.8</v>
       </c>
       <c r="I2" t="n">
-        <v>44.07</v>
+        <v>44.12</v>
       </c>
       <c r="J2" t="n">
-        <v>43.12</v>
+        <v>41.98</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="N2" t="n">
         <v>6190</v>
@@ -555,35 +555,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.23</v>
+        <v>23.27</v>
       </c>
       <c r="C3" t="n">
-        <v>22.76</v>
+        <v>23.64</v>
       </c>
       <c r="D3" t="n">
-        <v>21.86</v>
+        <v>22.89</v>
       </c>
       <c r="E3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="F3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="H3" t="n">
-        <v>45.63</v>
+        <v>42.52</v>
       </c>
       <c r="I3" t="n">
-        <v>47.01</v>
+        <v>43.12</v>
       </c>
       <c r="J3" t="n">
-        <v>44.24</v>
+        <v>41.91</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -592,336 +592,336 @@
         <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="N3" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.57</v>
+        <v>22.93</v>
       </c>
       <c r="C4" t="n">
-        <v>22.64</v>
+        <v>23.35</v>
       </c>
       <c r="D4" t="n">
-        <v>20.71</v>
+        <v>22.54</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G4" t="n">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="H4" t="n">
-        <v>48.34</v>
+        <v>43.56</v>
       </c>
       <c r="I4" t="n">
-        <v>51.45</v>
+        <v>44.91</v>
       </c>
       <c r="J4" t="n">
-        <v>45.03</v>
+        <v>42.28</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N4" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.3</v>
+        <v>22.23</v>
       </c>
       <c r="C5" t="n">
-        <v>20.76</v>
+        <v>22.76</v>
       </c>
       <c r="D5" t="n">
-        <v>19.87</v>
+        <v>21.86</v>
       </c>
       <c r="E5" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>231</v>
+        <v>383</v>
       </c>
       <c r="H5" t="n">
-        <v>53.23</v>
+        <v>45.63</v>
       </c>
       <c r="I5" t="n">
-        <v>56.41</v>
+        <v>47.01</v>
       </c>
       <c r="J5" t="n">
-        <v>51.05</v>
+        <v>44.24</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="N5" t="n">
-        <v>6170</v>
+        <v>6180</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.38</v>
+        <v>21.57</v>
       </c>
       <c r="C6" t="n">
-        <v>19.85</v>
+        <v>22.64</v>
       </c>
       <c r="D6" t="n">
-        <v>18.89</v>
+        <v>20.71</v>
       </c>
       <c r="E6" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>373</v>
       </c>
       <c r="H6" t="n">
-        <v>61.37</v>
+        <v>48.34</v>
       </c>
       <c r="I6" t="n">
-        <v>65.44</v>
+        <v>51.45</v>
       </c>
       <c r="J6" t="n">
-        <v>57.45</v>
+        <v>45.03</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="N6" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.52</v>
+        <v>20.3</v>
       </c>
       <c r="C7" t="n">
-        <v>18.87</v>
+        <v>20.76</v>
       </c>
       <c r="D7" t="n">
-        <v>18.23</v>
+        <v>19.87</v>
       </c>
       <c r="E7" t="n">
-        <v>12.2</v>
+        <v>10.3</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>34</v>
+        <v>231</v>
       </c>
       <c r="H7" t="n">
-        <v>67.5</v>
+        <v>53.23</v>
       </c>
       <c r="I7" t="n">
-        <v>70.43000000000001</v>
+        <v>56.41</v>
       </c>
       <c r="J7" t="n">
-        <v>65.33</v>
+        <v>51.05</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N7" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.89</v>
+        <v>19.38</v>
       </c>
       <c r="C8" t="n">
-        <v>18.27</v>
+        <v>19.85</v>
       </c>
       <c r="D8" t="n">
-        <v>17.53</v>
+        <v>18.89</v>
       </c>
       <c r="E8" t="n">
-        <v>13.1</v>
+        <v>11.6</v>
       </c>
       <c r="F8" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="H8" t="n">
-        <v>74.15000000000001</v>
+        <v>61.37</v>
       </c>
       <c r="I8" t="n">
-        <v>77.34999999999999</v>
+        <v>65.44</v>
       </c>
       <c r="J8" t="n">
-        <v>70.23999999999999</v>
+        <v>57.45</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.34</v>
+        <v>18.52</v>
       </c>
       <c r="C9" t="n">
-        <v>17.48</v>
+        <v>18.87</v>
       </c>
       <c r="D9" t="n">
-        <v>17.19</v>
+        <v>18.23</v>
       </c>
       <c r="E9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="F9" t="n">
-        <v>13.1</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H9" t="n">
-        <v>78.27</v>
+        <v>67.5</v>
       </c>
       <c r="I9" t="n">
-        <v>79.16</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>77.5</v>
+        <v>65.33</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.62</v>
+        <v>17.89</v>
       </c>
       <c r="C10" t="n">
-        <v>17.85</v>
+        <v>18.27</v>
       </c>
       <c r="D10" t="n">
-        <v>17.33</v>
+        <v>17.53</v>
       </c>
       <c r="E10" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="F10" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>74.13</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>77.06</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>71.3</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>6142</v>
@@ -931,82 +931,82 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.72</v>
+        <v>17.34</v>
       </c>
       <c r="C11" t="n">
-        <v>18.84</v>
+        <v>17.48</v>
       </c>
       <c r="D11" t="n">
-        <v>17.46</v>
+        <v>17.19</v>
       </c>
       <c r="E11" t="n">
-        <v>12.4</v>
+        <v>13.3</v>
       </c>
       <c r="F11" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>71.95999999999999</v>
+        <v>78.27</v>
       </c>
       <c r="I11" t="n">
-        <v>74.59999999999999</v>
+        <v>79.16</v>
       </c>
       <c r="J11" t="n">
-        <v>65.83</v>
+        <v>77.5</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N11" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.99</v>
+        <v>17.62</v>
       </c>
       <c r="C12" t="n">
-        <v>19.05</v>
+        <v>17.85</v>
       </c>
       <c r="D12" t="n">
-        <v>18.9</v>
+        <v>17.33</v>
       </c>
       <c r="E12" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="F12" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>62.56</v>
+        <v>74.13</v>
       </c>
       <c r="I12" t="n">
-        <v>63.18</v>
+        <v>77.06</v>
       </c>
       <c r="J12" t="n">
-        <v>61.89</v>
+        <v>71.3</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1018,42 +1018,42 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19.33</v>
+        <v>17.72</v>
       </c>
       <c r="C13" t="n">
-        <v>19.55</v>
+        <v>18.84</v>
       </c>
       <c r="D13" t="n">
-        <v>19.01</v>
+        <v>17.46</v>
       </c>
       <c r="E13" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F13" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>60.72</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>62.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>59.1</v>
+        <v>65.83</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1062,54 +1062,54 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19.52</v>
+        <v>18.99</v>
       </c>
       <c r="C14" t="n">
-        <v>19.58</v>
+        <v>19.05</v>
       </c>
       <c r="D14" t="n">
-        <v>19.46</v>
+        <v>18.9</v>
       </c>
       <c r="E14" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="F14" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>60.01</v>
+        <v>62.56</v>
       </c>
       <c r="I14" t="n">
-        <v>60.64</v>
+        <v>63.18</v>
       </c>
       <c r="J14" t="n">
-        <v>59.58</v>
+        <v>61.89</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>6152</v>
@@ -1119,35 +1119,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.62</v>
+        <v>19.33</v>
       </c>
       <c r="C15" t="n">
-        <v>19.71</v>
+        <v>19.55</v>
       </c>
       <c r="D15" t="n">
-        <v>19.49</v>
+        <v>19.01</v>
       </c>
       <c r="E15" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F15" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>60.63</v>
+        <v>60.72</v>
       </c>
       <c r="I15" t="n">
-        <v>61.71</v>
+        <v>62.8</v>
       </c>
       <c r="J15" t="n">
-        <v>59.73</v>
+        <v>59.1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1156,77 +1156,77 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N15" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19.79</v>
+        <v>19.52</v>
       </c>
       <c r="C16" t="n">
-        <v>20.01</v>
+        <v>19.58</v>
       </c>
       <c r="D16" t="n">
-        <v>19.61</v>
+        <v>19.46</v>
       </c>
       <c r="E16" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F16" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>60.18</v>
+        <v>60.01</v>
       </c>
       <c r="I16" t="n">
-        <v>61.23</v>
+        <v>60.64</v>
       </c>
       <c r="J16" t="n">
-        <v>59.04</v>
+        <v>59.58</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M16" t="n">
         <v>0.5</v>
       </c>
       <c r="N16" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.19</v>
+        <v>19.62</v>
       </c>
       <c r="C17" t="n">
-        <v>20.36</v>
+        <v>19.71</v>
       </c>
       <c r="D17" t="n">
-        <v>20.01</v>
+        <v>19.49</v>
       </c>
       <c r="E17" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F17" t="n">
         <v>11.4</v>
@@ -1235,13 +1235,13 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>58.19</v>
+        <v>60.63</v>
       </c>
       <c r="I17" t="n">
-        <v>59.14</v>
+        <v>61.71</v>
       </c>
       <c r="J17" t="n">
-        <v>57.54</v>
+        <v>59.73</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1250,430 +1250,430 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20.44</v>
+        <v>19.79</v>
       </c>
       <c r="C18" t="n">
-        <v>20.64</v>
+        <v>20.01</v>
       </c>
       <c r="D18" t="n">
-        <v>20.37</v>
+        <v>19.61</v>
       </c>
       <c r="E18" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F18" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>57.96</v>
+        <v>60.18</v>
       </c>
       <c r="I18" t="n">
-        <v>58.31</v>
+        <v>61.23</v>
       </c>
       <c r="J18" t="n">
-        <v>57.52</v>
+        <v>59.04</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N18" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20.99</v>
+        <v>20.19</v>
       </c>
       <c r="C19" t="n">
-        <v>21.3</v>
+        <v>20.36</v>
       </c>
       <c r="D19" t="n">
-        <v>20.64</v>
+        <v>20.01</v>
       </c>
       <c r="E19" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F19" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>55.76</v>
+        <v>58.19</v>
       </c>
       <c r="I19" t="n">
-        <v>57.26</v>
+        <v>59.14</v>
       </c>
       <c r="J19" t="n">
-        <v>54.28</v>
+        <v>57.54</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0.2</v>
       </c>
-      <c r="M19" t="n">
-        <v>0.8</v>
-      </c>
       <c r="N19" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.82</v>
+        <v>20.44</v>
       </c>
       <c r="C20" t="n">
-        <v>22.25</v>
+        <v>20.64</v>
       </c>
       <c r="D20" t="n">
-        <v>21.38</v>
+        <v>20.37</v>
       </c>
       <c r="E20" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="F20" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>52.03</v>
+        <v>57.96</v>
       </c>
       <c r="I20" t="n">
-        <v>53.83</v>
+        <v>58.31</v>
       </c>
       <c r="J20" t="n">
-        <v>50.23</v>
+        <v>57.52</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.61</v>
+        <v>20.99</v>
       </c>
       <c r="C21" t="n">
-        <v>22.85</v>
+        <v>21.3</v>
       </c>
       <c r="D21" t="n">
-        <v>22.34</v>
+        <v>20.64</v>
       </c>
       <c r="E21" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G21" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>49.28</v>
+        <v>55.76</v>
       </c>
       <c r="I21" t="n">
-        <v>50.37</v>
+        <v>57.26</v>
       </c>
       <c r="J21" t="n">
-        <v>48.38</v>
+        <v>54.28</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="N21" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23.26</v>
+        <v>21.82</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>22.25</v>
       </c>
       <c r="D22" t="n">
-        <v>22.73</v>
+        <v>21.38</v>
       </c>
       <c r="E22" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F22" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="G22" t="n">
-        <v>249</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>47.55</v>
+        <v>52.03</v>
       </c>
       <c r="I22" t="n">
-        <v>48.93</v>
+        <v>53.83</v>
       </c>
       <c r="J22" t="n">
-        <v>45.68</v>
+        <v>50.23</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M22" t="n">
         <v>1.1</v>
       </c>
-      <c r="M22" t="n">
-        <v>2</v>
-      </c>
       <c r="N22" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22.81</v>
+        <v>22.61</v>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>22.85</v>
       </c>
       <c r="D23" t="n">
-        <v>21.97</v>
+        <v>22.34</v>
       </c>
       <c r="E23" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="H23" t="n">
-        <v>49.12</v>
+        <v>49.28</v>
       </c>
       <c r="I23" t="n">
-        <v>52.45</v>
+        <v>50.37</v>
       </c>
       <c r="J23" t="n">
-        <v>45.39</v>
+        <v>48.38</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="N23" t="n">
-        <v>6220</v>
+        <v>6200</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21.82</v>
+        <v>23.26</v>
       </c>
       <c r="C24" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>21.73</v>
+        <v>22.73</v>
       </c>
       <c r="E24" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="F24" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="G24" t="n">
-        <v>146</v>
+        <v>249</v>
       </c>
       <c r="H24" t="n">
-        <v>52.7</v>
+        <v>47.55</v>
       </c>
       <c r="I24" t="n">
-        <v>52.97</v>
+        <v>48.93</v>
       </c>
       <c r="J24" t="n">
-        <v>52.47</v>
+        <v>45.68</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21.74</v>
+        <v>22.81</v>
       </c>
       <c r="C25" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>21.56</v>
+        <v>21.97</v>
       </c>
       <c r="E25" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F25" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>165</v>
+        <v>373</v>
       </c>
       <c r="H25" t="n">
-        <v>52.76</v>
+        <v>49.12</v>
       </c>
       <c r="I25" t="n">
-        <v>53.57</v>
+        <v>52.45</v>
       </c>
       <c r="J25" t="n">
-        <v>52.06</v>
+        <v>45.39</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M25" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N25" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21.42</v>
+        <v>21.82</v>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>21.95</v>
       </c>
       <c r="D26" t="n">
-        <v>20.92</v>
+        <v>21.73</v>
       </c>
       <c r="E26" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F26" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G26" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="H26" t="n">
-        <v>54.49</v>
+        <v>52.7</v>
       </c>
       <c r="I26" t="n">
-        <v>56.38</v>
+        <v>52.97</v>
       </c>
       <c r="J26" t="n">
-        <v>52.2</v>
+        <v>52.47</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N26" t="n">
         <v>6190</v>
@@ -1683,44 +1683,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.35</v>
+        <v>21.74</v>
       </c>
       <c r="C27" t="n">
-        <v>22.22</v>
+        <v>21.95</v>
       </c>
       <c r="D27" t="n">
-        <v>20.87</v>
+        <v>21.56</v>
       </c>
       <c r="E27" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="F27" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G27" t="n">
-        <v>238</v>
+        <v>165</v>
       </c>
       <c r="H27" t="n">
-        <v>55.07</v>
+        <v>52.76</v>
       </c>
       <c r="I27" t="n">
-        <v>56.71</v>
+        <v>53.57</v>
       </c>
       <c r="J27" t="n">
-        <v>52.16</v>
+        <v>52.06</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="M27" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="N27" t="n">
         <v>6190</v>
@@ -1730,317 +1730,317 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21.1</v>
+        <v>21.42</v>
       </c>
       <c r="C28" t="n">
-        <v>21.69</v>
+        <v>22</v>
       </c>
       <c r="D28" t="n">
-        <v>20.51</v>
+        <v>20.92</v>
       </c>
       <c r="E28" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F28" t="n">
         <v>11.5</v>
       </c>
       <c r="G28" t="n">
-        <v>480</v>
+        <v>218</v>
       </c>
       <c r="H28" t="n">
-        <v>55.96</v>
+        <v>54.49</v>
       </c>
       <c r="I28" t="n">
-        <v>58.01</v>
+        <v>56.38</v>
       </c>
       <c r="J28" t="n">
-        <v>53.81</v>
+        <v>52.2</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>20.15</v>
+        <v>21.35</v>
       </c>
       <c r="C29" t="n">
-        <v>20.85</v>
+        <v>22.22</v>
       </c>
       <c r="D29" t="n">
-        <v>19.57</v>
+        <v>20.87</v>
       </c>
       <c r="E29" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="F29" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G29" t="n">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="H29" t="n">
-        <v>60.77</v>
+        <v>55.07</v>
       </c>
       <c r="I29" t="n">
-        <v>64.81</v>
+        <v>56.71</v>
       </c>
       <c r="J29" t="n">
-        <v>56.73</v>
+        <v>52.16</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="N29" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.37</v>
+        <v>21.1</v>
       </c>
       <c r="C30" t="n">
-        <v>19.79</v>
+        <v>21.69</v>
       </c>
       <c r="D30" t="n">
-        <v>18.91</v>
+        <v>20.51</v>
       </c>
       <c r="E30" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F30" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G30" t="n">
-        <v>174</v>
+        <v>480</v>
       </c>
       <c r="H30" t="n">
-        <v>65.04000000000001</v>
+        <v>55.96</v>
       </c>
       <c r="I30" t="n">
-        <v>66.98999999999999</v>
+        <v>58.01</v>
       </c>
       <c r="J30" t="n">
-        <v>63.19</v>
+        <v>53.81</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>6180</v>
+        <v>6210</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18.41</v>
+        <v>20.15</v>
       </c>
       <c r="C31" t="n">
-        <v>18.85</v>
+        <v>20.85</v>
       </c>
       <c r="D31" t="n">
-        <v>18.05</v>
+        <v>19.57</v>
       </c>
       <c r="E31" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="F31" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="G31" t="n">
-        <v>76</v>
+        <v>266</v>
       </c>
       <c r="H31" t="n">
-        <v>69.37</v>
+        <v>60.77</v>
       </c>
       <c r="I31" t="n">
-        <v>71.67</v>
+        <v>64.81</v>
       </c>
       <c r="J31" t="n">
-        <v>67.22</v>
+        <v>56.73</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" t="n">
-        <v>6170</v>
+        <v>6200</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.66</v>
+        <v>19.37</v>
       </c>
       <c r="C32" t="n">
-        <v>17.95</v>
+        <v>19.79</v>
       </c>
       <c r="D32" t="n">
-        <v>17.51</v>
+        <v>18.91</v>
       </c>
       <c r="E32" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="F32" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="H32" t="n">
-        <v>73.31</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>74.14</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>72.19</v>
+        <v>63.19</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="N32" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.6</v>
+        <v>18.41</v>
       </c>
       <c r="C33" t="n">
-        <v>17.68</v>
+        <v>18.85</v>
       </c>
       <c r="D33" t="n">
-        <v>17.49</v>
+        <v>18.05</v>
       </c>
       <c r="E33" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F33" t="n">
         <v>12.4</v>
       </c>
-      <c r="F33" t="n">
-        <v>12.3</v>
-      </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H33" t="n">
-        <v>72.5</v>
+        <v>69.37</v>
       </c>
       <c r="I33" t="n">
-        <v>73.76000000000001</v>
+        <v>71.67</v>
       </c>
       <c r="J33" t="n">
-        <v>71.78</v>
+        <v>67.22</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="N33" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.53</v>
+        <v>17.66</v>
       </c>
       <c r="C34" t="n">
-        <v>17.62</v>
+        <v>17.95</v>
       </c>
       <c r="D34" t="n">
-        <v>17.45</v>
+        <v>17.51</v>
       </c>
       <c r="E34" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="F34" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H34" t="n">
-        <v>72.33</v>
+        <v>73.31</v>
       </c>
       <c r="I34" t="n">
-        <v>72.88</v>
+        <v>74.14</v>
       </c>
       <c r="J34" t="n">
-        <v>71.93000000000001</v>
+        <v>72.19</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2049,124 +2049,124 @@
         <v>0.3</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N34" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.64</v>
+        <v>17.6</v>
       </c>
       <c r="C35" t="n">
-        <v>17.9</v>
+        <v>17.68</v>
       </c>
       <c r="D35" t="n">
-        <v>17.44</v>
+        <v>17.49</v>
       </c>
       <c r="E35" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F35" t="n">
         <v>12.3</v>
       </c>
-      <c r="F35" t="n">
-        <v>12</v>
-      </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>71.73999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I35" t="n">
-        <v>73.59999999999999</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>69.53</v>
+        <v>71.78</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="N35" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.84</v>
+        <v>17.53</v>
       </c>
       <c r="C36" t="n">
-        <v>17.88</v>
+        <v>17.62</v>
       </c>
       <c r="D36" t="n">
-        <v>17.8</v>
+        <v>17.45</v>
       </c>
       <c r="E36" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F36" t="n">
         <v>12.2</v>
       </c>
-      <c r="F36" t="n">
-        <v>12</v>
-      </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>70.06999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="I36" t="n">
-        <v>70.3</v>
+        <v>72.88</v>
       </c>
       <c r="J36" t="n">
-        <v>69.65000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M36" t="n">
         <v>0.8</v>
       </c>
-      <c r="M36" t="n">
-        <v>1.3</v>
-      </c>
       <c r="N36" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="C37" t="n">
         <v>17.9</v>
       </c>
-      <c r="C37" t="n">
-        <v>17.97</v>
-      </c>
       <c r="D37" t="n">
-        <v>17.82</v>
+        <v>17.44</v>
       </c>
       <c r="E37" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="F37" t="n">
         <v>12</v>
@@ -2175,69 +2175,69 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>69.79000000000001</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>70.48999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>69.43000000000001</v>
+        <v>69.53</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M37" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="N37" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.74</v>
+        <v>17.84</v>
       </c>
       <c r="C38" t="n">
-        <v>17.82</v>
+        <v>17.88</v>
       </c>
       <c r="D38" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="E38" t="n">
         <v>12.2</v>
       </c>
       <c r="F38" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>70.81999999999999</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>70.98</v>
+        <v>70.3</v>
       </c>
       <c r="J38" t="n">
-        <v>70.54000000000001</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M38" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N38" t="n">
         <v>6162</v>
@@ -2247,69 +2247,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.68</v>
+        <v>17.9</v>
       </c>
       <c r="C39" t="n">
-        <v>17.71</v>
+        <v>17.97</v>
       </c>
       <c r="D39" t="n">
-        <v>17.64</v>
+        <v>17.82</v>
       </c>
       <c r="E39" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="F39" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>71.42</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>71.8</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>71.13</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
         <v>1.5</v>
-      </c>
-      <c r="M39" t="n">
-        <v>2</v>
       </c>
       <c r="N39" t="n">
         <v>6162</v>
       </c>
-      <c r="O39" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>17.74</v>
       </c>
       <c r="C40" t="n">
-        <v>17.78</v>
+        <v>17.82</v>
       </c>
       <c r="D40" t="n">
-        <v>17.68</v>
+        <v>17.7</v>
       </c>
       <c r="E40" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="F40" t="n">
         <v>12.2</v>
@@ -2318,60 +2316,60 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>71.53</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>72.06999999999999</v>
+        <v>70.98</v>
       </c>
       <c r="J40" t="n">
-        <v>70.67</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N40" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>18.17</v>
+        <v>17.68</v>
       </c>
       <c r="C41" t="n">
-        <v>18.45</v>
+        <v>17.71</v>
       </c>
       <c r="D41" t="n">
-        <v>17.85</v>
+        <v>17.64</v>
       </c>
       <c r="E41" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="F41" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>67.5</v>
+        <v>71.42</v>
       </c>
       <c r="I41" t="n">
-        <v>70.09</v>
+        <v>71.8</v>
       </c>
       <c r="J41" t="n">
-        <v>65.53</v>
+        <v>71.13</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2383,333 +2381,335 @@
         <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>6152</v>
-      </c>
-      <c r="O41" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19.12</v>
+        <v>17.74</v>
       </c>
       <c r="C42" t="n">
-        <v>19.48</v>
+        <v>17.78</v>
       </c>
       <c r="D42" t="n">
-        <v>18.59</v>
+        <v>17.68</v>
       </c>
       <c r="E42" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="F42" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>62.25</v>
+        <v>71.53</v>
       </c>
       <c r="I42" t="n">
-        <v>64.8</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>60.27</v>
+        <v>70.67</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="M42" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>6180</v>
+        <v>6152</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.89</v>
+        <v>18.17</v>
       </c>
       <c r="C43" t="n">
-        <v>20.2</v>
+        <v>18.45</v>
       </c>
       <c r="D43" t="n">
-        <v>19.54</v>
+        <v>17.85</v>
       </c>
       <c r="E43" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="F43" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>58.12</v>
+        <v>67.5</v>
       </c>
       <c r="I43" t="n">
-        <v>59.88</v>
+        <v>70.09</v>
       </c>
       <c r="J43" t="n">
-        <v>56.65</v>
+        <v>65.53</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N43" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20.59</v>
+        <v>19.12</v>
       </c>
       <c r="C44" t="n">
-        <v>21.02</v>
+        <v>19.48</v>
       </c>
       <c r="D44" t="n">
-        <v>20.23</v>
+        <v>18.59</v>
       </c>
       <c r="E44" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="F44" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>55.26</v>
+        <v>62.25</v>
       </c>
       <c r="I44" t="n">
-        <v>56.46</v>
+        <v>64.8</v>
       </c>
       <c r="J44" t="n">
-        <v>54.02</v>
+        <v>60.27</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="M44" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="N44" t="n">
-        <v>6200</v>
+        <v>6180</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21.34</v>
+        <v>19.89</v>
       </c>
       <c r="C45" t="n">
-        <v>21.65</v>
+        <v>20.2</v>
       </c>
       <c r="D45" t="n">
-        <v>20.98</v>
+        <v>19.54</v>
       </c>
       <c r="E45" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F45" t="n">
         <v>11.1</v>
       </c>
-      <c r="F45" t="n">
-        <v>11</v>
-      </c>
       <c r="G45" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>52.89</v>
+        <v>58.12</v>
       </c>
       <c r="I45" t="n">
-        <v>53.97</v>
+        <v>59.88</v>
       </c>
       <c r="J45" t="n">
-        <v>51.51</v>
+        <v>56.65</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="M45" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="N45" t="n">
-        <v>6220</v>
+        <v>6190</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22.22</v>
+        <v>20.59</v>
       </c>
       <c r="C46" t="n">
-        <v>22.72</v>
+        <v>21.02</v>
       </c>
       <c r="D46" t="n">
-        <v>21.71</v>
+        <v>20.23</v>
       </c>
       <c r="E46" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="F46" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="G46" t="n">
-        <v>210</v>
+        <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>50.44</v>
+        <v>55.26</v>
       </c>
       <c r="I46" t="n">
-        <v>51.7</v>
+        <v>56.46</v>
       </c>
       <c r="J46" t="n">
-        <v>49.53</v>
+        <v>54.02</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N46" t="n">
-        <v>6240</v>
+        <v>6200</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>22.94</v>
+        <v>21.34</v>
       </c>
       <c r="C47" t="n">
-        <v>23.82</v>
+        <v>21.65</v>
       </c>
       <c r="D47" t="n">
-        <v>22.29</v>
+        <v>20.98</v>
       </c>
       <c r="E47" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="F47" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G47" t="n">
-        <v>355</v>
+        <v>63</v>
       </c>
       <c r="H47" t="n">
-        <v>46.37</v>
+        <v>52.89</v>
       </c>
       <c r="I47" t="n">
-        <v>49.68</v>
+        <v>53.97</v>
       </c>
       <c r="J47" t="n">
-        <v>44.22</v>
+        <v>51.51</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M47" t="n">
         <v>2.7</v>
       </c>
-      <c r="M47" t="n">
-        <v>3.8</v>
-      </c>
       <c r="N47" t="n">
-        <v>6250</v>
+        <v>6220</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>23.12</v>
+        <v>22.22</v>
       </c>
       <c r="C48" t="n">
-        <v>24.14</v>
+        <v>22.72</v>
       </c>
       <c r="D48" t="n">
-        <v>22.72</v>
+        <v>21.71</v>
       </c>
       <c r="E48" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="F48" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="G48" t="n">
-        <v>344</v>
+        <v>210</v>
       </c>
       <c r="H48" t="n">
-        <v>45.59</v>
+        <v>50.44</v>
       </c>
       <c r="I48" t="n">
-        <v>46.9</v>
+        <v>51.7</v>
       </c>
       <c r="J48" t="n">
-        <v>43.18</v>
+        <v>49.53</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="M48" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N48" t="n">
         <v>6240</v>
@@ -2719,94 +2719,94 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>22.76</v>
+        <v>22.94</v>
       </c>
       <c r="C49" t="n">
-        <v>23.63</v>
+        <v>23.82</v>
       </c>
       <c r="D49" t="n">
-        <v>22.08</v>
+        <v>22.29</v>
       </c>
       <c r="E49" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="F49" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="G49" t="n">
-        <v>462</v>
+        <v>355</v>
       </c>
       <c r="H49" t="n">
-        <v>47.51</v>
+        <v>46.37</v>
       </c>
       <c r="I49" t="n">
-        <v>49.36</v>
+        <v>49.68</v>
       </c>
       <c r="J49" t="n">
-        <v>46.08</v>
+        <v>44.22</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N49" t="n">
-        <v>6240</v>
+        <v>6250</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>22.55</v>
+        <v>23.12</v>
       </c>
       <c r="C50" t="n">
-        <v>23.29</v>
+        <v>24.14</v>
       </c>
       <c r="D50" t="n">
-        <v>21.68</v>
+        <v>22.72</v>
       </c>
       <c r="E50" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="F50" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="G50" t="n">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="H50" t="n">
-        <v>47.88</v>
+        <v>45.59</v>
       </c>
       <c r="I50" t="n">
-        <v>50.32</v>
+        <v>46.9</v>
       </c>
       <c r="J50" t="n">
-        <v>46.13</v>
+        <v>43.18</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M50" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N50" t="n">
-        <v>6220</v>
+        <v>6240</v>
       </c>
       <c r="O50" t="n">
         <v>3.7</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,317 +508,317 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.63</v>
+        <v>21.39</v>
       </c>
       <c r="C2" t="n">
-        <v>23.93</v>
+        <v>21.69</v>
       </c>
       <c r="D2" t="n">
-        <v>23.26</v>
+        <v>21.12</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="F2" t="n">
-        <v>9.9</v>
+        <v>10.7</v>
       </c>
       <c r="G2" t="n">
-        <v>334</v>
+        <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>42.8</v>
+        <v>51.61</v>
       </c>
       <c r="I2" t="n">
-        <v>44.12</v>
+        <v>53.03</v>
       </c>
       <c r="J2" t="n">
-        <v>41.98</v>
+        <v>50.01</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.27</v>
+        <v>22.33</v>
       </c>
       <c r="C3" t="n">
-        <v>23.64</v>
+        <v>22.66</v>
       </c>
       <c r="D3" t="n">
-        <v>22.89</v>
+        <v>21.95</v>
       </c>
       <c r="E3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F3" t="n">
         <v>9.6</v>
       </c>
-      <c r="F3" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="G3" t="n">
-        <v>326</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>42.52</v>
+        <v>46.23</v>
       </c>
       <c r="I3" t="n">
-        <v>43.12</v>
+        <v>48.69</v>
       </c>
       <c r="J3" t="n">
-        <v>41.91</v>
+        <v>44.45</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="N3" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.93</v>
+        <v>22.97</v>
       </c>
       <c r="C4" t="n">
-        <v>23.35</v>
+        <v>23.49</v>
       </c>
       <c r="D4" t="n">
-        <v>22.54</v>
+        <v>22.63</v>
       </c>
       <c r="E4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="F4" t="n">
         <v>9.4</v>
       </c>
       <c r="G4" t="n">
-        <v>393</v>
+        <v>72</v>
       </c>
       <c r="H4" t="n">
-        <v>43.56</v>
+        <v>43.28</v>
       </c>
       <c r="I4" t="n">
-        <v>44.91</v>
+        <v>44.43</v>
       </c>
       <c r="J4" t="n">
-        <v>42.28</v>
+        <v>41.95</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>1.4</v>
       </c>
       <c r="N4" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.23</v>
+        <v>23.37</v>
       </c>
       <c r="C5" t="n">
-        <v>22.76</v>
+        <v>23.93</v>
       </c>
       <c r="D5" t="n">
-        <v>21.86</v>
+        <v>23.11</v>
       </c>
       <c r="E5" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="G5" t="n">
-        <v>383</v>
+        <v>271</v>
       </c>
       <c r="H5" t="n">
-        <v>45.63</v>
+        <v>42.7</v>
       </c>
       <c r="I5" t="n">
-        <v>47.01</v>
+        <v>44.12</v>
       </c>
       <c r="J5" t="n">
-        <v>44.24</v>
+        <v>41.98</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N5" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.57</v>
+        <v>23.27</v>
       </c>
       <c r="C6" t="n">
-        <v>22.64</v>
+        <v>23.64</v>
       </c>
       <c r="D6" t="n">
-        <v>20.71</v>
+        <v>22.89</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="F6" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>373</v>
+        <v>326</v>
       </c>
       <c r="H6" t="n">
-        <v>48.34</v>
+        <v>42.52</v>
       </c>
       <c r="I6" t="n">
-        <v>51.45</v>
+        <v>43.12</v>
       </c>
       <c r="J6" t="n">
-        <v>45.03</v>
+        <v>41.91</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N6" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.3</v>
+        <v>22.93</v>
       </c>
       <c r="C7" t="n">
-        <v>20.76</v>
+        <v>23.35</v>
       </c>
       <c r="D7" t="n">
-        <v>19.87</v>
+        <v>22.54</v>
       </c>
       <c r="E7" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="G7" t="n">
-        <v>231</v>
+        <v>393</v>
       </c>
       <c r="H7" t="n">
-        <v>53.23</v>
+        <v>43.56</v>
       </c>
       <c r="I7" t="n">
-        <v>56.41</v>
+        <v>44.91</v>
       </c>
       <c r="J7" t="n">
-        <v>51.05</v>
+        <v>42.28</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N7" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.38</v>
+        <v>22.23</v>
       </c>
       <c r="C8" t="n">
-        <v>19.85</v>
+        <v>22.76</v>
       </c>
       <c r="D8" t="n">
-        <v>18.89</v>
+        <v>21.86</v>
       </c>
       <c r="E8" t="n">
-        <v>11.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>383</v>
       </c>
       <c r="H8" t="n">
-        <v>61.37</v>
+        <v>45.63</v>
       </c>
       <c r="I8" t="n">
-        <v>65.44</v>
+        <v>47.01</v>
       </c>
       <c r="J8" t="n">
-        <v>57.45</v>
+        <v>44.24</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -827,327 +827,327 @@
         <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="N8" t="n">
-        <v>6152</v>
+        <v>6180</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.52</v>
+        <v>21.57</v>
       </c>
       <c r="C9" t="n">
-        <v>18.87</v>
+        <v>22.64</v>
       </c>
       <c r="D9" t="n">
-        <v>18.23</v>
+        <v>20.71</v>
       </c>
       <c r="E9" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>34</v>
+        <v>373</v>
       </c>
       <c r="H9" t="n">
-        <v>67.5</v>
+        <v>48.34</v>
       </c>
       <c r="I9" t="n">
-        <v>70.43000000000001</v>
+        <v>51.45</v>
       </c>
       <c r="J9" t="n">
-        <v>65.33</v>
+        <v>45.03</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N9" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.89</v>
+        <v>20.3</v>
       </c>
       <c r="C10" t="n">
-        <v>18.27</v>
+        <v>20.76</v>
       </c>
       <c r="D10" t="n">
-        <v>17.53</v>
+        <v>19.87</v>
       </c>
       <c r="E10" t="n">
-        <v>13.1</v>
+        <v>10.3</v>
       </c>
       <c r="F10" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>231</v>
       </c>
       <c r="H10" t="n">
-        <v>74.15000000000001</v>
+        <v>53.23</v>
       </c>
       <c r="I10" t="n">
-        <v>77.34999999999999</v>
+        <v>56.41</v>
       </c>
       <c r="J10" t="n">
-        <v>70.23999999999999</v>
+        <v>51.05</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N10" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.34</v>
+        <v>19.38</v>
       </c>
       <c r="C11" t="n">
-        <v>17.48</v>
+        <v>19.85</v>
       </c>
       <c r="D11" t="n">
-        <v>17.19</v>
+        <v>18.89</v>
       </c>
       <c r="E11" t="n">
-        <v>13.3</v>
+        <v>11.6</v>
       </c>
       <c r="F11" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H11" t="n">
-        <v>78.27</v>
+        <v>61.37</v>
       </c>
       <c r="I11" t="n">
-        <v>79.16</v>
+        <v>65.44</v>
       </c>
       <c r="J11" t="n">
-        <v>77.5</v>
+        <v>57.45</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.62</v>
+        <v>18.52</v>
       </c>
       <c r="C12" t="n">
-        <v>17.85</v>
+        <v>18.87</v>
       </c>
       <c r="D12" t="n">
-        <v>17.33</v>
+        <v>18.23</v>
       </c>
       <c r="E12" t="n">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="F12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H12" t="n">
-        <v>74.13</v>
+        <v>67.5</v>
       </c>
       <c r="I12" t="n">
-        <v>77.06</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>71.3</v>
+        <v>65.33</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.72</v>
+        <v>17.89</v>
       </c>
       <c r="C13" t="n">
-        <v>18.84</v>
+        <v>18.27</v>
       </c>
       <c r="D13" t="n">
-        <v>17.46</v>
+        <v>17.53</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="F13" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>71.95999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>74.59999999999999</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>65.83</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18.99</v>
+        <v>17.34</v>
       </c>
       <c r="C14" t="n">
-        <v>19.05</v>
+        <v>17.48</v>
       </c>
       <c r="D14" t="n">
-        <v>18.9</v>
+        <v>17.19</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5</v>
+        <v>13.3</v>
       </c>
       <c r="F14" t="n">
-        <v>11.3</v>
+        <v>13.1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>62.56</v>
+        <v>78.27</v>
       </c>
       <c r="I14" t="n">
-        <v>63.18</v>
+        <v>79.16</v>
       </c>
       <c r="J14" t="n">
-        <v>61.89</v>
+        <v>77.5</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N14" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.33</v>
+        <v>17.62</v>
       </c>
       <c r="C15" t="n">
-        <v>19.55</v>
+        <v>17.85</v>
       </c>
       <c r="D15" t="n">
-        <v>19.01</v>
+        <v>17.33</v>
       </c>
       <c r="E15" t="n">
-        <v>11.4</v>
+        <v>12.8</v>
       </c>
       <c r="F15" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>60.72</v>
+        <v>74.13</v>
       </c>
       <c r="I15" t="n">
-        <v>62.8</v>
+        <v>77.06</v>
       </c>
       <c r="J15" t="n">
-        <v>59.1</v>
+        <v>71.3</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1156,54 +1156,54 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19.52</v>
+        <v>17.72</v>
       </c>
       <c r="C16" t="n">
-        <v>19.58</v>
+        <v>18.84</v>
       </c>
       <c r="D16" t="n">
-        <v>19.46</v>
+        <v>17.46</v>
       </c>
       <c r="E16" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F16" t="n">
-        <v>11.2</v>
+        <v>12.1</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>60.01</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>60.64</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>59.58</v>
+        <v>65.83</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>6152</v>
@@ -1213,35 +1213,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.62</v>
+        <v>18.99</v>
       </c>
       <c r="C17" t="n">
-        <v>19.71</v>
+        <v>19.05</v>
       </c>
       <c r="D17" t="n">
-        <v>19.49</v>
+        <v>18.9</v>
       </c>
       <c r="E17" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F17" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>60.63</v>
+        <v>62.56</v>
       </c>
       <c r="I17" t="n">
-        <v>61.71</v>
+        <v>63.18</v>
       </c>
       <c r="J17" t="n">
-        <v>59.73</v>
+        <v>61.89</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1260,129 +1260,129 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19.79</v>
+        <v>19.33</v>
       </c>
       <c r="C18" t="n">
-        <v>20.01</v>
+        <v>19.55</v>
       </c>
       <c r="D18" t="n">
-        <v>19.61</v>
+        <v>19.01</v>
       </c>
       <c r="E18" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F18" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>60.18</v>
+        <v>60.72</v>
       </c>
       <c r="I18" t="n">
-        <v>61.23</v>
+        <v>62.8</v>
       </c>
       <c r="J18" t="n">
-        <v>59.04</v>
+        <v>59.1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="N18" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20.19</v>
+        <v>19.52</v>
       </c>
       <c r="C19" t="n">
-        <v>20.36</v>
+        <v>19.58</v>
       </c>
       <c r="D19" t="n">
-        <v>20.01</v>
+        <v>19.46</v>
       </c>
       <c r="E19" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F19" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>58.19</v>
+        <v>60.01</v>
       </c>
       <c r="I19" t="n">
-        <v>59.14</v>
+        <v>60.64</v>
       </c>
       <c r="J19" t="n">
-        <v>57.54</v>
+        <v>59.58</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="N19" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20.44</v>
+        <v>19.62</v>
       </c>
       <c r="C20" t="n">
-        <v>20.64</v>
+        <v>19.71</v>
       </c>
       <c r="D20" t="n">
-        <v>20.37</v>
+        <v>19.49</v>
       </c>
       <c r="E20" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F20" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>57.96</v>
+        <v>60.63</v>
       </c>
       <c r="I20" t="n">
-        <v>58.31</v>
+        <v>61.71</v>
       </c>
       <c r="J20" t="n">
-        <v>57.52</v>
+        <v>59.73</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1394,42 +1394,42 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.99</v>
+        <v>19.79</v>
       </c>
       <c r="C21" t="n">
-        <v>21.3</v>
+        <v>20.01</v>
       </c>
       <c r="D21" t="n">
-        <v>20.64</v>
+        <v>19.61</v>
       </c>
       <c r="E21" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F21" t="n">
         <v>11.6</v>
       </c>
-      <c r="F21" t="n">
-        <v>11.5</v>
-      </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>55.76</v>
+        <v>60.18</v>
       </c>
       <c r="I21" t="n">
-        <v>57.26</v>
+        <v>61.23</v>
       </c>
       <c r="J21" t="n">
-        <v>54.28</v>
+        <v>59.04</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1438,186 +1438,186 @@
         <v>0.2</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N21" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21.82</v>
+        <v>20.19</v>
       </c>
       <c r="C22" t="n">
-        <v>22.25</v>
+        <v>20.36</v>
       </c>
       <c r="D22" t="n">
-        <v>21.38</v>
+        <v>20.01</v>
       </c>
       <c r="E22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F22" t="n">
         <v>11.4</v>
       </c>
-      <c r="F22" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>52.03</v>
+        <v>58.19</v>
       </c>
       <c r="I22" t="n">
-        <v>53.83</v>
+        <v>59.14</v>
       </c>
       <c r="J22" t="n">
-        <v>50.23</v>
+        <v>57.54</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N22" t="n">
-        <v>6180</v>
+        <v>6132</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22.61</v>
+        <v>20.44</v>
       </c>
       <c r="C23" t="n">
-        <v>22.85</v>
+        <v>20.64</v>
       </c>
       <c r="D23" t="n">
-        <v>22.34</v>
+        <v>20.37</v>
       </c>
       <c r="E23" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G23" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>49.28</v>
+        <v>57.96</v>
       </c>
       <c r="I23" t="n">
-        <v>50.37</v>
+        <v>58.31</v>
       </c>
       <c r="J23" t="n">
-        <v>48.38</v>
+        <v>57.52</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23.26</v>
+        <v>20.99</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>21.3</v>
       </c>
       <c r="D24" t="n">
-        <v>22.73</v>
+        <v>20.64</v>
       </c>
       <c r="E24" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F24" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="G24" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>47.55</v>
+        <v>55.76</v>
       </c>
       <c r="I24" t="n">
-        <v>48.93</v>
+        <v>57.26</v>
       </c>
       <c r="J24" t="n">
-        <v>45.68</v>
+        <v>54.28</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N24" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.81</v>
+        <v>21.82</v>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>22.25</v>
       </c>
       <c r="D25" t="n">
-        <v>21.97</v>
+        <v>21.38</v>
       </c>
       <c r="E25" t="n">
         <v>11.4</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="G25" t="n">
-        <v>373</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>49.12</v>
+        <v>52.03</v>
       </c>
       <c r="I25" t="n">
-        <v>52.45</v>
+        <v>53.83</v>
       </c>
       <c r="J25" t="n">
-        <v>45.39</v>
+        <v>50.23</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1626,195 +1626,195 @@
         <v>0.7</v>
       </c>
       <c r="M25" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21.82</v>
+        <v>22.61</v>
       </c>
       <c r="C26" t="n">
-        <v>21.95</v>
+        <v>22.85</v>
       </c>
       <c r="D26" t="n">
-        <v>21.73</v>
+        <v>22.34</v>
       </c>
       <c r="E26" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F26" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="H26" t="n">
-        <v>52.7</v>
+        <v>49.28</v>
       </c>
       <c r="I26" t="n">
-        <v>52.97</v>
+        <v>50.37</v>
       </c>
       <c r="J26" t="n">
-        <v>52.47</v>
+        <v>48.38</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="N26" t="n">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.74</v>
+        <v>23.26</v>
       </c>
       <c r="C27" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>21.56</v>
+        <v>22.73</v>
       </c>
       <c r="E27" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="F27" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="G27" t="n">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="H27" t="n">
-        <v>52.76</v>
+        <v>47.55</v>
       </c>
       <c r="I27" t="n">
-        <v>53.57</v>
+        <v>48.93</v>
       </c>
       <c r="J27" t="n">
-        <v>52.06</v>
+        <v>45.68</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21.42</v>
+        <v>22.81</v>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>20.92</v>
+        <v>21.97</v>
       </c>
       <c r="E28" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>218</v>
+        <v>373</v>
       </c>
       <c r="H28" t="n">
-        <v>54.49</v>
+        <v>49.12</v>
       </c>
       <c r="I28" t="n">
-        <v>56.38</v>
+        <v>52.45</v>
       </c>
       <c r="J28" t="n">
-        <v>52.2</v>
+        <v>45.39</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M28" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N28" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21.35</v>
+        <v>21.82</v>
       </c>
       <c r="C29" t="n">
-        <v>22.22</v>
+        <v>21.95</v>
       </c>
       <c r="D29" t="n">
-        <v>20.87</v>
+        <v>21.73</v>
       </c>
       <c r="E29" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F29" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G29" t="n">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>55.07</v>
+        <v>52.7</v>
       </c>
       <c r="I29" t="n">
-        <v>56.71</v>
+        <v>52.97</v>
       </c>
       <c r="J29" t="n">
-        <v>52.16</v>
+        <v>52.47</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M29" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="N29" t="n">
         <v>6190</v>
@@ -1824,252 +1824,252 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21.1</v>
+        <v>21.74</v>
       </c>
       <c r="C30" t="n">
-        <v>21.69</v>
+        <v>21.95</v>
       </c>
       <c r="D30" t="n">
-        <v>20.51</v>
+        <v>21.56</v>
       </c>
       <c r="E30" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="F30" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G30" t="n">
-        <v>480</v>
+        <v>165</v>
       </c>
       <c r="H30" t="n">
-        <v>55.96</v>
+        <v>52.76</v>
       </c>
       <c r="I30" t="n">
-        <v>58.01</v>
+        <v>53.57</v>
       </c>
       <c r="J30" t="n">
-        <v>53.81</v>
+        <v>52.06</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="N30" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20.15</v>
+        <v>21.42</v>
       </c>
       <c r="C31" t="n">
-        <v>20.85</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
-        <v>19.57</v>
+        <v>20.92</v>
       </c>
       <c r="E31" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="F31" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G31" t="n">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="H31" t="n">
-        <v>60.77</v>
+        <v>54.49</v>
       </c>
       <c r="I31" t="n">
-        <v>64.81</v>
+        <v>56.38</v>
       </c>
       <c r="J31" t="n">
-        <v>56.73</v>
+        <v>52.2</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M31" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19.37</v>
+        <v>21.35</v>
       </c>
       <c r="C32" t="n">
-        <v>19.79</v>
+        <v>22.22</v>
       </c>
       <c r="D32" t="n">
-        <v>18.91</v>
+        <v>20.87</v>
       </c>
       <c r="E32" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F32" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G32" t="n">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="H32" t="n">
-        <v>65.04000000000001</v>
+        <v>55.07</v>
       </c>
       <c r="I32" t="n">
-        <v>66.98999999999999</v>
+        <v>56.71</v>
       </c>
       <c r="J32" t="n">
-        <v>63.19</v>
+        <v>52.16</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M32" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N32" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>18.41</v>
+        <v>21.1</v>
       </c>
       <c r="C33" t="n">
-        <v>18.85</v>
+        <v>21.69</v>
       </c>
       <c r="D33" t="n">
-        <v>18.05</v>
+        <v>20.51</v>
       </c>
       <c r="E33" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F33" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G33" t="n">
-        <v>76</v>
+        <v>480</v>
       </c>
       <c r="H33" t="n">
-        <v>69.37</v>
+        <v>55.96</v>
       </c>
       <c r="I33" t="n">
-        <v>71.67</v>
+        <v>58.01</v>
       </c>
       <c r="J33" t="n">
-        <v>67.22</v>
+        <v>53.81</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M33" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>6170</v>
+        <v>6210</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.66</v>
+        <v>20.15</v>
       </c>
       <c r="C34" t="n">
-        <v>17.95</v>
+        <v>20.85</v>
       </c>
       <c r="D34" t="n">
-        <v>17.51</v>
+        <v>19.57</v>
       </c>
       <c r="E34" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="F34" t="n">
-        <v>12.6</v>
+        <v>11.6</v>
       </c>
       <c r="G34" t="n">
-        <v>10</v>
+        <v>266</v>
       </c>
       <c r="H34" t="n">
-        <v>73.31</v>
+        <v>60.77</v>
       </c>
       <c r="I34" t="n">
-        <v>74.14</v>
+        <v>64.81</v>
       </c>
       <c r="J34" t="n">
-        <v>72.19</v>
+        <v>56.73</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="N34" t="n">
-        <v>6162</v>
+        <v>6200</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.6</v>
+        <v>19.37</v>
       </c>
       <c r="C35" t="n">
-        <v>17.68</v>
+        <v>19.79</v>
       </c>
       <c r="D35" t="n">
-        <v>17.49</v>
+        <v>18.91</v>
       </c>
       <c r="E35" t="n">
         <v>12.4</v>
@@ -2078,110 +2078,110 @@
         <v>12.3</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="H35" t="n">
-        <v>72.5</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>73.76000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>71.78</v>
+        <v>63.19</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="N35" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.53</v>
+        <v>18.41</v>
       </c>
       <c r="C36" t="n">
-        <v>17.62</v>
+        <v>18.85</v>
       </c>
       <c r="D36" t="n">
-        <v>17.45</v>
+        <v>18.05</v>
       </c>
       <c r="E36" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F36" t="n">
         <v>12.4</v>
       </c>
-      <c r="F36" t="n">
-        <v>12.2</v>
-      </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H36" t="n">
-        <v>72.33</v>
+        <v>69.37</v>
       </c>
       <c r="I36" t="n">
-        <v>72.88</v>
+        <v>71.67</v>
       </c>
       <c r="J36" t="n">
-        <v>71.93000000000001</v>
+        <v>67.22</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="N36" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.64</v>
+        <v>17.66</v>
       </c>
       <c r="C37" t="n">
-        <v>17.9</v>
+        <v>17.95</v>
       </c>
       <c r="D37" t="n">
-        <v>17.44</v>
+        <v>17.51</v>
       </c>
       <c r="E37" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H37" t="n">
-        <v>71.73999999999999</v>
+        <v>73.31</v>
       </c>
       <c r="I37" t="n">
-        <v>73.59999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="J37" t="n">
-        <v>69.53</v>
+        <v>72.19</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2190,499 +2190,499 @@
         <v>0.3</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="N37" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.84</v>
+        <v>17.6</v>
       </c>
       <c r="C38" t="n">
-        <v>17.88</v>
+        <v>17.68</v>
       </c>
       <c r="D38" t="n">
-        <v>17.8</v>
+        <v>17.49</v>
       </c>
       <c r="E38" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F38" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>70.06999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I38" t="n">
-        <v>70.3</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>69.65000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="N38" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.9</v>
+        <v>17.53</v>
       </c>
       <c r="C39" t="n">
-        <v>17.97</v>
+        <v>17.62</v>
       </c>
       <c r="D39" t="n">
-        <v>17.82</v>
+        <v>17.45</v>
       </c>
       <c r="E39" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="F39" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>69.79000000000001</v>
+        <v>72.33</v>
       </c>
       <c r="I39" t="n">
-        <v>70.48999999999999</v>
+        <v>72.88</v>
       </c>
       <c r="J39" t="n">
-        <v>69.43000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M39" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N39" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.74</v>
+        <v>17.64</v>
       </c>
       <c r="C40" t="n">
-        <v>17.82</v>
+        <v>17.9</v>
       </c>
       <c r="D40" t="n">
-        <v>17.7</v>
+        <v>17.44</v>
       </c>
       <c r="E40" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F40" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>70.81999999999999</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>70.98</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>70.54000000000001</v>
+        <v>69.53</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M40" t="n">
         <v>1.4</v>
       </c>
       <c r="N40" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.68</v>
+        <v>17.84</v>
       </c>
       <c r="C41" t="n">
-        <v>17.71</v>
+        <v>17.88</v>
       </c>
       <c r="D41" t="n">
-        <v>17.64</v>
+        <v>17.8</v>
       </c>
       <c r="E41" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F41" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>71.42</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>71.8</v>
+        <v>70.3</v>
       </c>
       <c r="J41" t="n">
-        <v>71.13</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N41" t="n">
         <v>6162</v>
       </c>
-      <c r="O41" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.74</v>
+        <v>17.9</v>
       </c>
       <c r="C42" t="n">
-        <v>17.78</v>
+        <v>17.97</v>
       </c>
       <c r="D42" t="n">
-        <v>17.68</v>
+        <v>17.82</v>
       </c>
       <c r="E42" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F42" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>71.53</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>72.06999999999999</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>70.67</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N42" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18.17</v>
+        <v>17.74</v>
       </c>
       <c r="C43" t="n">
-        <v>18.45</v>
+        <v>17.82</v>
       </c>
       <c r="D43" t="n">
-        <v>17.85</v>
+        <v>17.7</v>
       </c>
       <c r="E43" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="F43" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>67.5</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>70.09</v>
+        <v>70.98</v>
       </c>
       <c r="J43" t="n">
-        <v>65.53</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N43" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.12</v>
+        <v>17.68</v>
       </c>
       <c r="C44" t="n">
-        <v>19.48</v>
+        <v>17.71</v>
       </c>
       <c r="D44" t="n">
-        <v>18.59</v>
+        <v>17.64</v>
       </c>
       <c r="E44" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="F44" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>62.25</v>
+        <v>71.42</v>
       </c>
       <c r="I44" t="n">
-        <v>64.8</v>
+        <v>71.8</v>
       </c>
       <c r="J44" t="n">
-        <v>60.27</v>
+        <v>71.13</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>6180</v>
-      </c>
-      <c r="O44" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.89</v>
+        <v>17.74</v>
       </c>
       <c r="C45" t="n">
-        <v>20.2</v>
+        <v>17.78</v>
       </c>
       <c r="D45" t="n">
-        <v>19.54</v>
+        <v>17.68</v>
       </c>
       <c r="E45" t="n">
-        <v>11.2</v>
+        <v>12.4</v>
       </c>
       <c r="F45" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>58.12</v>
+        <v>71.53</v>
       </c>
       <c r="I45" t="n">
-        <v>59.88</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>56.65</v>
+        <v>70.67</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="M45" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20.59</v>
+        <v>18.17</v>
       </c>
       <c r="C46" t="n">
-        <v>21.02</v>
+        <v>18.45</v>
       </c>
       <c r="D46" t="n">
-        <v>20.23</v>
+        <v>17.85</v>
       </c>
       <c r="E46" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="F46" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="G46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>55.26</v>
+        <v>67.5</v>
       </c>
       <c r="I46" t="n">
-        <v>56.46</v>
+        <v>70.09</v>
       </c>
       <c r="J46" t="n">
-        <v>54.02</v>
+        <v>65.53</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M46" t="n">
         <v>2</v>
       </c>
-      <c r="M46" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N46" t="n">
-        <v>6200</v>
+        <v>6152</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21.34</v>
+        <v>19.12</v>
       </c>
       <c r="C47" t="n">
-        <v>21.65</v>
+        <v>19.48</v>
       </c>
       <c r="D47" t="n">
-        <v>20.98</v>
+        <v>18.59</v>
       </c>
       <c r="E47" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="G47" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>52.89</v>
+        <v>62.25</v>
       </c>
       <c r="I47" t="n">
-        <v>53.97</v>
+        <v>64.8</v>
       </c>
       <c r="J47" t="n">
-        <v>51.51</v>
+        <v>60.27</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="M47" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="N47" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.22</v>
+        <v>19.89</v>
       </c>
       <c r="C48" t="n">
-        <v>22.72</v>
+        <v>20.2</v>
       </c>
       <c r="D48" t="n">
-        <v>21.71</v>
+        <v>19.54</v>
       </c>
       <c r="E48" t="n">
         <v>11.2</v>
@@ -2691,122 +2691,122 @@
         <v>11.1</v>
       </c>
       <c r="G48" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>50.44</v>
+        <v>58.12</v>
       </c>
       <c r="I48" t="n">
-        <v>51.7</v>
+        <v>59.88</v>
       </c>
       <c r="J48" t="n">
-        <v>49.53</v>
+        <v>56.65</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="M48" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="N48" t="n">
-        <v>6240</v>
+        <v>6190</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>22.94</v>
+        <v>20.59</v>
       </c>
       <c r="C49" t="n">
-        <v>23.82</v>
+        <v>21.02</v>
       </c>
       <c r="D49" t="n">
-        <v>22.29</v>
+        <v>20.23</v>
       </c>
       <c r="E49" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="F49" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G49" t="n">
-        <v>355</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>46.37</v>
+        <v>55.26</v>
       </c>
       <c r="I49" t="n">
-        <v>49.68</v>
+        <v>56.46</v>
       </c>
       <c r="J49" t="n">
-        <v>44.22</v>
+        <v>54.02</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N49" t="n">
-        <v>6250</v>
+        <v>6200</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.12</v>
+        <v>21.34</v>
       </c>
       <c r="C50" t="n">
-        <v>24.14</v>
+        <v>21.65</v>
       </c>
       <c r="D50" t="n">
-        <v>22.72</v>
+        <v>20.98</v>
       </c>
       <c r="E50" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F50" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G50" t="n">
-        <v>344</v>
+        <v>63</v>
       </c>
       <c r="H50" t="n">
-        <v>45.59</v>
+        <v>52.89</v>
       </c>
       <c r="I50" t="n">
-        <v>46.9</v>
+        <v>53.97</v>
       </c>
       <c r="J50" t="n">
-        <v>43.18</v>
+        <v>51.51</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M50" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="N50" t="n">
-        <v>6240</v>
+        <v>6220</v>
       </c>
       <c r="O50" t="n">
         <v>3.7</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,279 +508,279 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.39</v>
+        <v>18.07</v>
       </c>
       <c r="C2" t="n">
-        <v>21.69</v>
+        <v>18.13</v>
       </c>
       <c r="D2" t="n">
-        <v>21.12</v>
+        <v>18.02</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9</v>
+        <v>13.3</v>
       </c>
       <c r="F2" t="n">
-        <v>10.7</v>
+        <v>13.3</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>51.61</v>
+        <v>74.61</v>
       </c>
       <c r="I2" t="n">
-        <v>53.03</v>
+        <v>74.84</v>
       </c>
       <c r="J2" t="n">
-        <v>50.01</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="N2" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.33</v>
+        <v>18.6</v>
       </c>
       <c r="C3" t="n">
-        <v>22.66</v>
+        <v>19.26</v>
       </c>
       <c r="D3" t="n">
-        <v>21.95</v>
+        <v>18.22</v>
       </c>
       <c r="E3" t="n">
-        <v>9.9</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>46.23</v>
+        <v>70.7</v>
       </c>
       <c r="I3" t="n">
-        <v>48.69</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>44.45</v>
+        <v>65.41</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.97</v>
+        <v>20.29</v>
       </c>
       <c r="C4" t="n">
-        <v>23.49</v>
+        <v>21.69</v>
       </c>
       <c r="D4" t="n">
-        <v>22.63</v>
+        <v>19.3</v>
       </c>
       <c r="E4" t="n">
-        <v>9.5</v>
+        <v>11.6</v>
       </c>
       <c r="F4" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="G4" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>43.28</v>
+        <v>58.46</v>
       </c>
       <c r="I4" t="n">
-        <v>44.43</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>41.95</v>
+        <v>50.01</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.37</v>
+        <v>22.33</v>
       </c>
       <c r="C5" t="n">
-        <v>23.93</v>
+        <v>22.66</v>
       </c>
       <c r="D5" t="n">
-        <v>23.11</v>
+        <v>21.95</v>
       </c>
       <c r="E5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="F5" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="G5" t="n">
-        <v>271</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
-        <v>42.7</v>
+        <v>46.23</v>
       </c>
       <c r="I5" t="n">
-        <v>44.12</v>
+        <v>48.69</v>
       </c>
       <c r="J5" t="n">
-        <v>41.98</v>
+        <v>44.45</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="N5" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.27</v>
+        <v>22.97</v>
       </c>
       <c r="C6" t="n">
-        <v>23.64</v>
+        <v>23.49</v>
       </c>
       <c r="D6" t="n">
-        <v>22.89</v>
+        <v>22.63</v>
       </c>
       <c r="E6" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G6" t="n">
-        <v>326</v>
+        <v>72</v>
       </c>
       <c r="H6" t="n">
-        <v>42.52</v>
+        <v>43.28</v>
       </c>
       <c r="I6" t="n">
-        <v>43.12</v>
+        <v>44.43</v>
       </c>
       <c r="J6" t="n">
-        <v>41.91</v>
+        <v>41.95</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N6" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.93</v>
+        <v>23.37</v>
       </c>
       <c r="C7" t="n">
-        <v>23.35</v>
+        <v>23.93</v>
       </c>
       <c r="D7" t="n">
-        <v>22.54</v>
+        <v>23.11</v>
       </c>
       <c r="E7" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="G7" t="n">
-        <v>393</v>
+        <v>271</v>
       </c>
       <c r="H7" t="n">
-        <v>43.56</v>
+        <v>42.7</v>
       </c>
       <c r="I7" t="n">
-        <v>44.91</v>
+        <v>44.12</v>
       </c>
       <c r="J7" t="n">
-        <v>42.28</v>
+        <v>41.98</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N7" t="n">
         <v>6190</v>
@@ -790,35 +790,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.23</v>
+        <v>23.27</v>
       </c>
       <c r="C8" t="n">
-        <v>22.76</v>
+        <v>23.64</v>
       </c>
       <c r="D8" t="n">
-        <v>21.86</v>
+        <v>22.89</v>
       </c>
       <c r="E8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="F8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="H8" t="n">
-        <v>45.63</v>
+        <v>42.52</v>
       </c>
       <c r="I8" t="n">
-        <v>47.01</v>
+        <v>43.12</v>
       </c>
       <c r="J8" t="n">
-        <v>44.24</v>
+        <v>41.91</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -827,336 +827,336 @@
         <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="N8" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.57</v>
+        <v>22.93</v>
       </c>
       <c r="C9" t="n">
-        <v>22.64</v>
+        <v>23.35</v>
       </c>
       <c r="D9" t="n">
-        <v>20.71</v>
+        <v>22.54</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G9" t="n">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="H9" t="n">
-        <v>48.34</v>
+        <v>43.56</v>
       </c>
       <c r="I9" t="n">
-        <v>51.45</v>
+        <v>44.91</v>
       </c>
       <c r="J9" t="n">
-        <v>45.03</v>
+        <v>42.28</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N9" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20.3</v>
+        <v>22.23</v>
       </c>
       <c r="C10" t="n">
-        <v>20.76</v>
+        <v>22.76</v>
       </c>
       <c r="D10" t="n">
-        <v>19.87</v>
+        <v>21.86</v>
       </c>
       <c r="E10" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>231</v>
+        <v>383</v>
       </c>
       <c r="H10" t="n">
-        <v>53.23</v>
+        <v>45.63</v>
       </c>
       <c r="I10" t="n">
-        <v>56.41</v>
+        <v>47.01</v>
       </c>
       <c r="J10" t="n">
-        <v>51.05</v>
+        <v>44.24</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="N10" t="n">
-        <v>6170</v>
+        <v>6180</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.38</v>
+        <v>21.57</v>
       </c>
       <c r="C11" t="n">
-        <v>19.85</v>
+        <v>22.64</v>
       </c>
       <c r="D11" t="n">
-        <v>18.89</v>
+        <v>20.71</v>
       </c>
       <c r="E11" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>110</v>
+        <v>373</v>
       </c>
       <c r="H11" t="n">
-        <v>61.37</v>
+        <v>48.34</v>
       </c>
       <c r="I11" t="n">
-        <v>65.44</v>
+        <v>51.45</v>
       </c>
       <c r="J11" t="n">
-        <v>57.45</v>
+        <v>45.03</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="N11" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.52</v>
+        <v>20.3</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87</v>
+        <v>20.76</v>
       </c>
       <c r="D12" t="n">
-        <v>18.23</v>
+        <v>19.87</v>
       </c>
       <c r="E12" t="n">
-        <v>12.2</v>
+        <v>10.3</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>34</v>
+        <v>231</v>
       </c>
       <c r="H12" t="n">
-        <v>67.5</v>
+        <v>53.23</v>
       </c>
       <c r="I12" t="n">
-        <v>70.43000000000001</v>
+        <v>56.41</v>
       </c>
       <c r="J12" t="n">
-        <v>65.33</v>
+        <v>51.05</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N12" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.89</v>
+        <v>19.38</v>
       </c>
       <c r="C13" t="n">
-        <v>18.27</v>
+        <v>19.85</v>
       </c>
       <c r="D13" t="n">
-        <v>17.53</v>
+        <v>18.89</v>
       </c>
       <c r="E13" t="n">
-        <v>13.1</v>
+        <v>11.6</v>
       </c>
       <c r="F13" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="H13" t="n">
-        <v>74.15000000000001</v>
+        <v>61.37</v>
       </c>
       <c r="I13" t="n">
-        <v>77.34999999999999</v>
+        <v>65.44</v>
       </c>
       <c r="J13" t="n">
-        <v>70.23999999999999</v>
+        <v>57.45</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.34</v>
+        <v>18.52</v>
       </c>
       <c r="C14" t="n">
-        <v>17.48</v>
+        <v>18.87</v>
       </c>
       <c r="D14" t="n">
-        <v>17.19</v>
+        <v>18.23</v>
       </c>
       <c r="E14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="F14" t="n">
-        <v>13.1</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H14" t="n">
-        <v>78.27</v>
+        <v>67.5</v>
       </c>
       <c r="I14" t="n">
-        <v>79.16</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>77.5</v>
+        <v>65.33</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.62</v>
+        <v>17.89</v>
       </c>
       <c r="C15" t="n">
-        <v>17.85</v>
+        <v>18.27</v>
       </c>
       <c r="D15" t="n">
-        <v>17.33</v>
+        <v>17.53</v>
       </c>
       <c r="E15" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="F15" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>74.13</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>77.06</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>71.3</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>6142</v>
@@ -1166,82 +1166,82 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.72</v>
+        <v>17.34</v>
       </c>
       <c r="C16" t="n">
-        <v>18.84</v>
+        <v>17.48</v>
       </c>
       <c r="D16" t="n">
-        <v>17.46</v>
+        <v>17.19</v>
       </c>
       <c r="E16" t="n">
-        <v>12.4</v>
+        <v>13.3</v>
       </c>
       <c r="F16" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>71.95999999999999</v>
+        <v>78.27</v>
       </c>
       <c r="I16" t="n">
-        <v>74.59999999999999</v>
+        <v>79.16</v>
       </c>
       <c r="J16" t="n">
-        <v>65.83</v>
+        <v>77.5</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N16" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.99</v>
+        <v>17.62</v>
       </c>
       <c r="C17" t="n">
-        <v>19.05</v>
+        <v>17.85</v>
       </c>
       <c r="D17" t="n">
-        <v>18.9</v>
+        <v>17.33</v>
       </c>
       <c r="E17" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="F17" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>62.56</v>
+        <v>74.13</v>
       </c>
       <c r="I17" t="n">
-        <v>63.18</v>
+        <v>77.06</v>
       </c>
       <c r="J17" t="n">
-        <v>61.89</v>
+        <v>71.3</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1253,42 +1253,42 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19.33</v>
+        <v>17.72</v>
       </c>
       <c r="C18" t="n">
-        <v>19.55</v>
+        <v>18.84</v>
       </c>
       <c r="D18" t="n">
-        <v>19.01</v>
+        <v>17.46</v>
       </c>
       <c r="E18" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F18" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>60.72</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>62.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>59.1</v>
+        <v>65.83</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1297,54 +1297,54 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.52</v>
+        <v>18.99</v>
       </c>
       <c r="C19" t="n">
-        <v>19.58</v>
+        <v>19.05</v>
       </c>
       <c r="D19" t="n">
-        <v>19.46</v>
+        <v>18.9</v>
       </c>
       <c r="E19" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="F19" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>60.01</v>
+        <v>62.56</v>
       </c>
       <c r="I19" t="n">
-        <v>60.64</v>
+        <v>63.18</v>
       </c>
       <c r="J19" t="n">
-        <v>59.58</v>
+        <v>61.89</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>6152</v>
@@ -1354,35 +1354,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.62</v>
+        <v>19.33</v>
       </c>
       <c r="C20" t="n">
-        <v>19.71</v>
+        <v>19.55</v>
       </c>
       <c r="D20" t="n">
-        <v>19.49</v>
+        <v>19.01</v>
       </c>
       <c r="E20" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F20" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>60.63</v>
+        <v>60.72</v>
       </c>
       <c r="I20" t="n">
-        <v>61.71</v>
+        <v>62.8</v>
       </c>
       <c r="J20" t="n">
-        <v>59.73</v>
+        <v>59.1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1391,77 +1391,77 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N20" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.79</v>
+        <v>19.52</v>
       </c>
       <c r="C21" t="n">
-        <v>20.01</v>
+        <v>19.58</v>
       </c>
       <c r="D21" t="n">
-        <v>19.61</v>
+        <v>19.46</v>
       </c>
       <c r="E21" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F21" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>60.18</v>
+        <v>60.01</v>
       </c>
       <c r="I21" t="n">
-        <v>61.23</v>
+        <v>60.64</v>
       </c>
       <c r="J21" t="n">
-        <v>59.04</v>
+        <v>59.58</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M21" t="n">
         <v>0.5</v>
       </c>
       <c r="N21" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20.19</v>
+        <v>19.62</v>
       </c>
       <c r="C22" t="n">
-        <v>20.36</v>
+        <v>19.71</v>
       </c>
       <c r="D22" t="n">
-        <v>20.01</v>
+        <v>19.49</v>
       </c>
       <c r="E22" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F22" t="n">
         <v>11.4</v>
@@ -1470,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>58.19</v>
+        <v>60.63</v>
       </c>
       <c r="I22" t="n">
-        <v>59.14</v>
+        <v>61.71</v>
       </c>
       <c r="J22" t="n">
-        <v>57.54</v>
+        <v>59.73</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1485,430 +1485,430 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20.44</v>
+        <v>19.79</v>
       </c>
       <c r="C23" t="n">
-        <v>20.64</v>
+        <v>20.01</v>
       </c>
       <c r="D23" t="n">
-        <v>20.37</v>
+        <v>19.61</v>
       </c>
       <c r="E23" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F23" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>57.96</v>
+        <v>60.18</v>
       </c>
       <c r="I23" t="n">
-        <v>58.31</v>
+        <v>61.23</v>
       </c>
       <c r="J23" t="n">
-        <v>57.52</v>
+        <v>59.04</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N23" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20.99</v>
+        <v>20.19</v>
       </c>
       <c r="C24" t="n">
-        <v>21.3</v>
+        <v>20.36</v>
       </c>
       <c r="D24" t="n">
-        <v>20.64</v>
+        <v>20.01</v>
       </c>
       <c r="E24" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F24" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>55.76</v>
+        <v>58.19</v>
       </c>
       <c r="I24" t="n">
-        <v>57.26</v>
+        <v>59.14</v>
       </c>
       <c r="J24" t="n">
-        <v>54.28</v>
+        <v>57.54</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0.2</v>
       </c>
-      <c r="M24" t="n">
-        <v>0.8</v>
-      </c>
       <c r="N24" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21.82</v>
+        <v>20.44</v>
       </c>
       <c r="C25" t="n">
-        <v>22.25</v>
+        <v>20.64</v>
       </c>
       <c r="D25" t="n">
-        <v>21.38</v>
+        <v>20.37</v>
       </c>
       <c r="E25" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="F25" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>52.03</v>
+        <v>57.96</v>
       </c>
       <c r="I25" t="n">
-        <v>53.83</v>
+        <v>58.31</v>
       </c>
       <c r="J25" t="n">
-        <v>50.23</v>
+        <v>57.52</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22.61</v>
+        <v>20.99</v>
       </c>
       <c r="C26" t="n">
-        <v>22.85</v>
+        <v>21.3</v>
       </c>
       <c r="D26" t="n">
-        <v>22.34</v>
+        <v>20.64</v>
       </c>
       <c r="E26" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G26" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>49.28</v>
+        <v>55.76</v>
       </c>
       <c r="I26" t="n">
-        <v>50.37</v>
+        <v>57.26</v>
       </c>
       <c r="J26" t="n">
-        <v>48.38</v>
+        <v>54.28</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="M26" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="N26" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23.26</v>
+        <v>21.82</v>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>22.25</v>
       </c>
       <c r="D27" t="n">
-        <v>22.73</v>
+        <v>21.38</v>
       </c>
       <c r="E27" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F27" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="G27" t="n">
-        <v>249</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>47.55</v>
+        <v>52.03</v>
       </c>
       <c r="I27" t="n">
-        <v>48.93</v>
+        <v>53.83</v>
       </c>
       <c r="J27" t="n">
-        <v>45.68</v>
+        <v>50.23</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M27" t="n">
         <v>1.1</v>
       </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
       <c r="N27" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22.81</v>
+        <v>22.61</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>22.85</v>
       </c>
       <c r="D28" t="n">
-        <v>21.97</v>
+        <v>22.34</v>
       </c>
       <c r="E28" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="H28" t="n">
-        <v>49.12</v>
+        <v>49.28</v>
       </c>
       <c r="I28" t="n">
-        <v>52.45</v>
+        <v>50.37</v>
       </c>
       <c r="J28" t="n">
-        <v>45.39</v>
+        <v>48.38</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="N28" t="n">
-        <v>6220</v>
+        <v>6200</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21.82</v>
+        <v>23.26</v>
       </c>
       <c r="C29" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>21.73</v>
+        <v>22.73</v>
       </c>
       <c r="E29" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="F29" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="G29" t="n">
-        <v>146</v>
+        <v>249</v>
       </c>
       <c r="H29" t="n">
-        <v>52.7</v>
+        <v>47.55</v>
       </c>
       <c r="I29" t="n">
-        <v>52.97</v>
+        <v>48.93</v>
       </c>
       <c r="J29" t="n">
-        <v>52.47</v>
+        <v>45.68</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21.74</v>
+        <v>22.81</v>
       </c>
       <c r="C30" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>21.56</v>
+        <v>21.97</v>
       </c>
       <c r="E30" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F30" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>165</v>
+        <v>373</v>
       </c>
       <c r="H30" t="n">
-        <v>52.76</v>
+        <v>49.12</v>
       </c>
       <c r="I30" t="n">
-        <v>53.57</v>
+        <v>52.45</v>
       </c>
       <c r="J30" t="n">
-        <v>52.06</v>
+        <v>45.39</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N30" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21.42</v>
+        <v>21.82</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>21.95</v>
       </c>
       <c r="D31" t="n">
-        <v>20.92</v>
+        <v>21.73</v>
       </c>
       <c r="E31" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F31" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G31" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="H31" t="n">
-        <v>54.49</v>
+        <v>52.7</v>
       </c>
       <c r="I31" t="n">
-        <v>56.38</v>
+        <v>52.97</v>
       </c>
       <c r="J31" t="n">
-        <v>52.2</v>
+        <v>52.47</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N31" t="n">
         <v>6190</v>
@@ -1918,44 +1918,44 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21.35</v>
+        <v>21.74</v>
       </c>
       <c r="C32" t="n">
-        <v>22.22</v>
+        <v>21.95</v>
       </c>
       <c r="D32" t="n">
-        <v>20.87</v>
+        <v>21.56</v>
       </c>
       <c r="E32" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="F32" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G32" t="n">
-        <v>238</v>
+        <v>165</v>
       </c>
       <c r="H32" t="n">
-        <v>55.07</v>
+        <v>52.76</v>
       </c>
       <c r="I32" t="n">
-        <v>56.71</v>
+        <v>53.57</v>
       </c>
       <c r="J32" t="n">
-        <v>52.16</v>
+        <v>52.06</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="M32" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="N32" t="n">
         <v>6190</v>
@@ -1965,317 +1965,317 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21.1</v>
+        <v>21.42</v>
       </c>
       <c r="C33" t="n">
-        <v>21.69</v>
+        <v>22</v>
       </c>
       <c r="D33" t="n">
-        <v>20.51</v>
+        <v>20.92</v>
       </c>
       <c r="E33" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F33" t="n">
         <v>11.5</v>
       </c>
       <c r="G33" t="n">
-        <v>480</v>
+        <v>218</v>
       </c>
       <c r="H33" t="n">
-        <v>55.96</v>
+        <v>54.49</v>
       </c>
       <c r="I33" t="n">
-        <v>58.01</v>
+        <v>56.38</v>
       </c>
       <c r="J33" t="n">
-        <v>53.81</v>
+        <v>52.2</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>20.15</v>
+        <v>21.35</v>
       </c>
       <c r="C34" t="n">
-        <v>20.85</v>
+        <v>22.22</v>
       </c>
       <c r="D34" t="n">
-        <v>19.57</v>
+        <v>20.87</v>
       </c>
       <c r="E34" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="F34" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G34" t="n">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="H34" t="n">
-        <v>60.77</v>
+        <v>55.07</v>
       </c>
       <c r="I34" t="n">
-        <v>64.81</v>
+        <v>56.71</v>
       </c>
       <c r="J34" t="n">
-        <v>56.73</v>
+        <v>52.16</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="N34" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.37</v>
+        <v>21.1</v>
       </c>
       <c r="C35" t="n">
-        <v>19.79</v>
+        <v>21.69</v>
       </c>
       <c r="D35" t="n">
-        <v>18.91</v>
+        <v>20.51</v>
       </c>
       <c r="E35" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F35" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G35" t="n">
-        <v>174</v>
+        <v>480</v>
       </c>
       <c r="H35" t="n">
-        <v>65.04000000000001</v>
+        <v>55.96</v>
       </c>
       <c r="I35" t="n">
-        <v>66.98999999999999</v>
+        <v>58.01</v>
       </c>
       <c r="J35" t="n">
-        <v>63.19</v>
+        <v>53.81</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="M35" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>6180</v>
+        <v>6210</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>18.41</v>
+        <v>20.15</v>
       </c>
       <c r="C36" t="n">
-        <v>18.85</v>
+        <v>20.85</v>
       </c>
       <c r="D36" t="n">
-        <v>18.05</v>
+        <v>19.57</v>
       </c>
       <c r="E36" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="F36" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="G36" t="n">
-        <v>76</v>
+        <v>266</v>
       </c>
       <c r="H36" t="n">
-        <v>69.37</v>
+        <v>60.77</v>
       </c>
       <c r="I36" t="n">
-        <v>71.67</v>
+        <v>64.81</v>
       </c>
       <c r="J36" t="n">
-        <v>67.22</v>
+        <v>56.73</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M36" t="n">
         <v>2.3</v>
       </c>
       <c r="N36" t="n">
-        <v>6170</v>
+        <v>6200</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.66</v>
+        <v>19.37</v>
       </c>
       <c r="C37" t="n">
-        <v>17.95</v>
+        <v>19.79</v>
       </c>
       <c r="D37" t="n">
-        <v>17.51</v>
+        <v>18.91</v>
       </c>
       <c r="E37" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="F37" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="G37" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="H37" t="n">
-        <v>73.31</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>74.14</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>72.19</v>
+        <v>63.19</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="N37" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.6</v>
+        <v>18.41</v>
       </c>
       <c r="C38" t="n">
-        <v>17.68</v>
+        <v>18.85</v>
       </c>
       <c r="D38" t="n">
-        <v>17.49</v>
+        <v>18.05</v>
       </c>
       <c r="E38" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F38" t="n">
         <v>12.4</v>
       </c>
-      <c r="F38" t="n">
-        <v>12.3</v>
-      </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H38" t="n">
-        <v>72.5</v>
+        <v>69.37</v>
       </c>
       <c r="I38" t="n">
-        <v>73.76000000000001</v>
+        <v>71.67</v>
       </c>
       <c r="J38" t="n">
-        <v>71.78</v>
+        <v>67.22</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="N38" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.53</v>
+        <v>17.66</v>
       </c>
       <c r="C39" t="n">
-        <v>17.62</v>
+        <v>17.95</v>
       </c>
       <c r="D39" t="n">
-        <v>17.45</v>
+        <v>17.51</v>
       </c>
       <c r="E39" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="F39" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H39" t="n">
-        <v>72.33</v>
+        <v>73.31</v>
       </c>
       <c r="I39" t="n">
-        <v>72.88</v>
+        <v>74.14</v>
       </c>
       <c r="J39" t="n">
-        <v>71.93000000000001</v>
+        <v>72.19</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2284,124 +2284,124 @@
         <v>0.3</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N39" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.64</v>
+        <v>17.6</v>
       </c>
       <c r="C40" t="n">
-        <v>17.9</v>
+        <v>17.68</v>
       </c>
       <c r="D40" t="n">
-        <v>17.44</v>
+        <v>17.49</v>
       </c>
       <c r="E40" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F40" t="n">
         <v>12.3</v>
       </c>
-      <c r="F40" t="n">
-        <v>12</v>
-      </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>71.73999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I40" t="n">
-        <v>73.59999999999999</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>69.53</v>
+        <v>71.78</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="N40" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.84</v>
+        <v>17.53</v>
       </c>
       <c r="C41" t="n">
-        <v>17.88</v>
+        <v>17.62</v>
       </c>
       <c r="D41" t="n">
-        <v>17.8</v>
+        <v>17.45</v>
       </c>
       <c r="E41" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F41" t="n">
         <v>12.2</v>
       </c>
-      <c r="F41" t="n">
-        <v>12</v>
-      </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>70.06999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="I41" t="n">
-        <v>70.3</v>
+        <v>72.88</v>
       </c>
       <c r="J41" t="n">
-        <v>69.65000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M41" t="n">
         <v>0.8</v>
       </c>
-      <c r="M41" t="n">
-        <v>1.3</v>
-      </c>
       <c r="N41" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="C42" t="n">
         <v>17.9</v>
       </c>
-      <c r="C42" t="n">
-        <v>17.97</v>
-      </c>
       <c r="D42" t="n">
-        <v>17.82</v>
+        <v>17.44</v>
       </c>
       <c r="E42" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="F42" t="n">
         <v>12</v>
@@ -2410,69 +2410,69 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>69.79000000000001</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>70.48999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>69.43000000000001</v>
+        <v>69.53</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M42" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="N42" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.74</v>
+        <v>17.84</v>
       </c>
       <c r="C43" t="n">
-        <v>17.82</v>
+        <v>17.88</v>
       </c>
       <c r="D43" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="E43" t="n">
         <v>12.2</v>
       </c>
       <c r="F43" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>70.81999999999999</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>70.98</v>
+        <v>70.3</v>
       </c>
       <c r="J43" t="n">
-        <v>70.54000000000001</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M43" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N43" t="n">
         <v>6162</v>
@@ -2482,69 +2482,67 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17.68</v>
+        <v>17.9</v>
       </c>
       <c r="C44" t="n">
-        <v>17.71</v>
+        <v>17.97</v>
       </c>
       <c r="D44" t="n">
-        <v>17.64</v>
+        <v>17.82</v>
       </c>
       <c r="E44" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="F44" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>71.42</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>71.8</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>71.13</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
         <v>1.5</v>
-      </c>
-      <c r="M44" t="n">
-        <v>2</v>
       </c>
       <c r="N44" t="n">
         <v>6162</v>
       </c>
-      <c r="O44" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>17.74</v>
       </c>
       <c r="C45" t="n">
-        <v>17.78</v>
+        <v>17.82</v>
       </c>
       <c r="D45" t="n">
-        <v>17.68</v>
+        <v>17.7</v>
       </c>
       <c r="E45" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="F45" t="n">
         <v>12.2</v>
@@ -2553,60 +2551,60 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>71.53</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>72.06999999999999</v>
+        <v>70.98</v>
       </c>
       <c r="J45" t="n">
-        <v>70.67</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N45" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18.17</v>
+        <v>17.68</v>
       </c>
       <c r="C46" t="n">
-        <v>18.45</v>
+        <v>17.71</v>
       </c>
       <c r="D46" t="n">
-        <v>17.85</v>
+        <v>17.64</v>
       </c>
       <c r="E46" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="F46" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>67.5</v>
+        <v>71.42</v>
       </c>
       <c r="I46" t="n">
-        <v>70.09</v>
+        <v>71.8</v>
       </c>
       <c r="J46" t="n">
-        <v>65.53</v>
+        <v>71.13</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2618,195 +2616,197 @@
         <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>6152</v>
-      </c>
-      <c r="O46" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>19.12</v>
+        <v>17.74</v>
       </c>
       <c r="C47" t="n">
-        <v>19.48</v>
+        <v>17.78</v>
       </c>
       <c r="D47" t="n">
-        <v>18.59</v>
+        <v>17.68</v>
       </c>
       <c r="E47" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="F47" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>62.25</v>
+        <v>71.53</v>
       </c>
       <c r="I47" t="n">
-        <v>64.8</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>60.27</v>
+        <v>70.67</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>6180</v>
+        <v>6152</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19.89</v>
+        <v>18.17</v>
       </c>
       <c r="C48" t="n">
-        <v>20.2</v>
+        <v>18.45</v>
       </c>
       <c r="D48" t="n">
-        <v>19.54</v>
+        <v>17.85</v>
       </c>
       <c r="E48" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="F48" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>58.12</v>
+        <v>67.5</v>
       </c>
       <c r="I48" t="n">
-        <v>59.88</v>
+        <v>70.09</v>
       </c>
       <c r="J48" t="n">
-        <v>56.65</v>
+        <v>65.53</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M48" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.59</v>
+        <v>19.12</v>
       </c>
       <c r="C49" t="n">
-        <v>21.02</v>
+        <v>19.48</v>
       </c>
       <c r="D49" t="n">
-        <v>20.23</v>
+        <v>18.59</v>
       </c>
       <c r="E49" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>55.26</v>
+        <v>62.25</v>
       </c>
       <c r="I49" t="n">
-        <v>56.46</v>
+        <v>64.8</v>
       </c>
       <c r="J49" t="n">
-        <v>54.02</v>
+        <v>60.27</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="M49" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="N49" t="n">
-        <v>6200</v>
+        <v>6180</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>21.34</v>
+        <v>19.89</v>
       </c>
       <c r="C50" t="n">
-        <v>21.65</v>
+        <v>20.2</v>
       </c>
       <c r="D50" t="n">
-        <v>20.98</v>
+        <v>19.54</v>
       </c>
       <c r="E50" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F50" t="n">
         <v>11.1</v>
       </c>
-      <c r="F50" t="n">
-        <v>11</v>
-      </c>
       <c r="G50" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>52.89</v>
+        <v>58.12</v>
       </c>
       <c r="I50" t="n">
-        <v>53.97</v>
+        <v>59.88</v>
       </c>
       <c r="J50" t="n">
-        <v>51.51</v>
+        <v>56.65</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="M50" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="N50" t="n">
-        <v>6220</v>
+        <v>6190</v>
       </c>
       <c r="O50" t="n">
         <v>3.7</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,373 +508,373 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.07</v>
+        <v>17.63</v>
       </c>
       <c r="C2" t="n">
-        <v>18.13</v>
+        <v>17.67</v>
       </c>
       <c r="D2" t="n">
-        <v>18.02</v>
+        <v>17.6</v>
       </c>
       <c r="E2" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="F2" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>74.61</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>74.84</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>74.34999999999999</v>
+        <v>75.95</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="N2" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.6</v>
+        <v>17.43</v>
       </c>
       <c r="C3" t="n">
-        <v>19.26</v>
+        <v>17.62</v>
       </c>
       <c r="D3" t="n">
-        <v>18.22</v>
+        <v>17.17</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="F3" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>70.7</v>
+        <v>79.34</v>
       </c>
       <c r="I3" t="n">
-        <v>73.79000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="J3" t="n">
-        <v>65.41</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.29</v>
+        <v>17.89</v>
       </c>
       <c r="C4" t="n">
-        <v>21.69</v>
+        <v>18.13</v>
       </c>
       <c r="D4" t="n">
-        <v>19.3</v>
+        <v>17.76</v>
       </c>
       <c r="E4" t="n">
-        <v>11.6</v>
+        <v>13.4</v>
       </c>
       <c r="F4" t="n">
-        <v>10.7</v>
+        <v>13.2</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>58.46</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>64.93000000000001</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>50.01</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="N4" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.33</v>
+        <v>18.6</v>
       </c>
       <c r="C5" t="n">
-        <v>22.66</v>
+        <v>19.26</v>
       </c>
       <c r="D5" t="n">
-        <v>21.95</v>
+        <v>18.22</v>
       </c>
       <c r="E5" t="n">
-        <v>9.9</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>46.23</v>
+        <v>70.7</v>
       </c>
       <c r="I5" t="n">
-        <v>48.69</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>44.45</v>
+        <v>65.41</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.97</v>
+        <v>20.29</v>
       </c>
       <c r="C6" t="n">
-        <v>23.49</v>
+        <v>21.69</v>
       </c>
       <c r="D6" t="n">
-        <v>22.63</v>
+        <v>19.3</v>
       </c>
       <c r="E6" t="n">
-        <v>9.5</v>
+        <v>11.6</v>
       </c>
       <c r="F6" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="G6" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>43.28</v>
+        <v>58.46</v>
       </c>
       <c r="I6" t="n">
-        <v>44.43</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>41.95</v>
+        <v>50.01</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.37</v>
+        <v>22.33</v>
       </c>
       <c r="C7" t="n">
-        <v>23.93</v>
+        <v>22.66</v>
       </c>
       <c r="D7" t="n">
-        <v>23.11</v>
+        <v>21.95</v>
       </c>
       <c r="E7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="F7" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="G7" t="n">
-        <v>271</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
-        <v>42.7</v>
+        <v>46.23</v>
       </c>
       <c r="I7" t="n">
-        <v>44.12</v>
+        <v>48.69</v>
       </c>
       <c r="J7" t="n">
-        <v>41.98</v>
+        <v>44.45</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="N7" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.27</v>
+        <v>22.97</v>
       </c>
       <c r="C8" t="n">
-        <v>23.64</v>
+        <v>23.49</v>
       </c>
       <c r="D8" t="n">
-        <v>22.89</v>
+        <v>22.63</v>
       </c>
       <c r="E8" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G8" t="n">
-        <v>326</v>
+        <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>42.52</v>
+        <v>43.28</v>
       </c>
       <c r="I8" t="n">
-        <v>43.12</v>
+        <v>44.43</v>
       </c>
       <c r="J8" t="n">
-        <v>41.91</v>
+        <v>41.95</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N8" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.93</v>
+        <v>23.37</v>
       </c>
       <c r="C9" t="n">
-        <v>23.35</v>
+        <v>23.93</v>
       </c>
       <c r="D9" t="n">
-        <v>22.54</v>
+        <v>23.11</v>
       </c>
       <c r="E9" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="G9" t="n">
-        <v>393</v>
+        <v>271</v>
       </c>
       <c r="H9" t="n">
-        <v>43.56</v>
+        <v>42.7</v>
       </c>
       <c r="I9" t="n">
-        <v>44.91</v>
+        <v>44.12</v>
       </c>
       <c r="J9" t="n">
-        <v>42.28</v>
+        <v>41.98</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N9" t="n">
         <v>6190</v>
@@ -884,35 +884,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.23</v>
+        <v>23.27</v>
       </c>
       <c r="C10" t="n">
-        <v>22.76</v>
+        <v>23.64</v>
       </c>
       <c r="D10" t="n">
-        <v>21.86</v>
+        <v>22.89</v>
       </c>
       <c r="E10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="F10" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="H10" t="n">
-        <v>45.63</v>
+        <v>42.52</v>
       </c>
       <c r="I10" t="n">
-        <v>47.01</v>
+        <v>43.12</v>
       </c>
       <c r="J10" t="n">
-        <v>44.24</v>
+        <v>41.91</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -921,336 +921,336 @@
         <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="N10" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.57</v>
+        <v>22.93</v>
       </c>
       <c r="C11" t="n">
-        <v>22.64</v>
+        <v>23.35</v>
       </c>
       <c r="D11" t="n">
-        <v>20.71</v>
+        <v>22.54</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G11" t="n">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="H11" t="n">
-        <v>48.34</v>
+        <v>43.56</v>
       </c>
       <c r="I11" t="n">
-        <v>51.45</v>
+        <v>44.91</v>
       </c>
       <c r="J11" t="n">
-        <v>45.03</v>
+        <v>42.28</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N11" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.3</v>
+        <v>22.23</v>
       </c>
       <c r="C12" t="n">
-        <v>20.76</v>
+        <v>22.76</v>
       </c>
       <c r="D12" t="n">
-        <v>19.87</v>
+        <v>21.86</v>
       </c>
       <c r="E12" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>231</v>
+        <v>383</v>
       </c>
       <c r="H12" t="n">
-        <v>53.23</v>
+        <v>45.63</v>
       </c>
       <c r="I12" t="n">
-        <v>56.41</v>
+        <v>47.01</v>
       </c>
       <c r="J12" t="n">
-        <v>51.05</v>
+        <v>44.24</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="N12" t="n">
-        <v>6170</v>
+        <v>6180</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19.38</v>
+        <v>21.57</v>
       </c>
       <c r="C13" t="n">
-        <v>19.85</v>
+        <v>22.64</v>
       </c>
       <c r="D13" t="n">
-        <v>18.89</v>
+        <v>20.71</v>
       </c>
       <c r="E13" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>110</v>
+        <v>373</v>
       </c>
       <c r="H13" t="n">
-        <v>61.37</v>
+        <v>48.34</v>
       </c>
       <c r="I13" t="n">
-        <v>65.44</v>
+        <v>51.45</v>
       </c>
       <c r="J13" t="n">
-        <v>57.45</v>
+        <v>45.03</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="N13" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18.52</v>
+        <v>20.3</v>
       </c>
       <c r="C14" t="n">
-        <v>18.87</v>
+        <v>20.76</v>
       </c>
       <c r="D14" t="n">
-        <v>18.23</v>
+        <v>19.87</v>
       </c>
       <c r="E14" t="n">
-        <v>12.2</v>
+        <v>10.3</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>34</v>
+        <v>231</v>
       </c>
       <c r="H14" t="n">
-        <v>67.5</v>
+        <v>53.23</v>
       </c>
       <c r="I14" t="n">
-        <v>70.43000000000001</v>
+        <v>56.41</v>
       </c>
       <c r="J14" t="n">
-        <v>65.33</v>
+        <v>51.05</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N14" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.89</v>
+        <v>19.38</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27</v>
+        <v>19.85</v>
       </c>
       <c r="D15" t="n">
-        <v>17.53</v>
+        <v>18.89</v>
       </c>
       <c r="E15" t="n">
-        <v>13.1</v>
+        <v>11.6</v>
       </c>
       <c r="F15" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="H15" t="n">
-        <v>74.15000000000001</v>
+        <v>61.37</v>
       </c>
       <c r="I15" t="n">
-        <v>77.34999999999999</v>
+        <v>65.44</v>
       </c>
       <c r="J15" t="n">
-        <v>70.23999999999999</v>
+        <v>57.45</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.34</v>
+        <v>18.52</v>
       </c>
       <c r="C16" t="n">
-        <v>17.48</v>
+        <v>18.87</v>
       </c>
       <c r="D16" t="n">
-        <v>17.19</v>
+        <v>18.23</v>
       </c>
       <c r="E16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="F16" t="n">
-        <v>13.1</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H16" t="n">
-        <v>78.27</v>
+        <v>67.5</v>
       </c>
       <c r="I16" t="n">
-        <v>79.16</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>77.5</v>
+        <v>65.33</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.62</v>
+        <v>17.89</v>
       </c>
       <c r="C17" t="n">
-        <v>17.85</v>
+        <v>18.27</v>
       </c>
       <c r="D17" t="n">
-        <v>17.33</v>
+        <v>17.53</v>
       </c>
       <c r="E17" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="F17" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
-        <v>74.13</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>77.06</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>71.3</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>6142</v>
@@ -1260,82 +1260,82 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.72</v>
+        <v>17.34</v>
       </c>
       <c r="C18" t="n">
-        <v>18.84</v>
+        <v>17.48</v>
       </c>
       <c r="D18" t="n">
-        <v>17.46</v>
+        <v>17.19</v>
       </c>
       <c r="E18" t="n">
-        <v>12.4</v>
+        <v>13.3</v>
       </c>
       <c r="F18" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>71.95999999999999</v>
+        <v>78.27</v>
       </c>
       <c r="I18" t="n">
-        <v>74.59999999999999</v>
+        <v>79.16</v>
       </c>
       <c r="J18" t="n">
-        <v>65.83</v>
+        <v>77.5</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N18" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18.99</v>
+        <v>17.62</v>
       </c>
       <c r="C19" t="n">
-        <v>19.05</v>
+        <v>17.85</v>
       </c>
       <c r="D19" t="n">
-        <v>18.9</v>
+        <v>17.33</v>
       </c>
       <c r="E19" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="F19" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>62.56</v>
+        <v>74.13</v>
       </c>
       <c r="I19" t="n">
-        <v>63.18</v>
+        <v>77.06</v>
       </c>
       <c r="J19" t="n">
-        <v>61.89</v>
+        <v>71.3</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1347,42 +1347,42 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.33</v>
+        <v>17.72</v>
       </c>
       <c r="C20" t="n">
-        <v>19.55</v>
+        <v>18.84</v>
       </c>
       <c r="D20" t="n">
-        <v>19.01</v>
+        <v>17.46</v>
       </c>
       <c r="E20" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F20" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>60.72</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>62.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>59.1</v>
+        <v>65.83</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1391,54 +1391,54 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.52</v>
+        <v>18.99</v>
       </c>
       <c r="C21" t="n">
-        <v>19.58</v>
+        <v>19.05</v>
       </c>
       <c r="D21" t="n">
-        <v>19.46</v>
+        <v>18.9</v>
       </c>
       <c r="E21" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="F21" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>60.01</v>
+        <v>62.56</v>
       </c>
       <c r="I21" t="n">
-        <v>60.64</v>
+        <v>63.18</v>
       </c>
       <c r="J21" t="n">
-        <v>59.58</v>
+        <v>61.89</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>6152</v>
@@ -1448,35 +1448,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.62</v>
+        <v>19.33</v>
       </c>
       <c r="C22" t="n">
-        <v>19.71</v>
+        <v>19.55</v>
       </c>
       <c r="D22" t="n">
-        <v>19.49</v>
+        <v>19.01</v>
       </c>
       <c r="E22" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F22" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>60.63</v>
+        <v>60.72</v>
       </c>
       <c r="I22" t="n">
-        <v>61.71</v>
+        <v>62.8</v>
       </c>
       <c r="J22" t="n">
-        <v>59.73</v>
+        <v>59.1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1485,77 +1485,77 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N22" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.79</v>
+        <v>19.52</v>
       </c>
       <c r="C23" t="n">
-        <v>20.01</v>
+        <v>19.58</v>
       </c>
       <c r="D23" t="n">
-        <v>19.61</v>
+        <v>19.46</v>
       </c>
       <c r="E23" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F23" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>60.18</v>
+        <v>60.01</v>
       </c>
       <c r="I23" t="n">
-        <v>61.23</v>
+        <v>60.64</v>
       </c>
       <c r="J23" t="n">
-        <v>59.04</v>
+        <v>59.58</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M23" t="n">
         <v>0.5</v>
       </c>
       <c r="N23" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20.19</v>
+        <v>19.62</v>
       </c>
       <c r="C24" t="n">
-        <v>20.36</v>
+        <v>19.71</v>
       </c>
       <c r="D24" t="n">
-        <v>20.01</v>
+        <v>19.49</v>
       </c>
       <c r="E24" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F24" t="n">
         <v>11.4</v>
@@ -1564,13 +1564,13 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>58.19</v>
+        <v>60.63</v>
       </c>
       <c r="I24" t="n">
-        <v>59.14</v>
+        <v>61.71</v>
       </c>
       <c r="J24" t="n">
-        <v>57.54</v>
+        <v>59.73</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1579,430 +1579,430 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20.44</v>
+        <v>19.79</v>
       </c>
       <c r="C25" t="n">
-        <v>20.64</v>
+        <v>20.01</v>
       </c>
       <c r="D25" t="n">
-        <v>20.37</v>
+        <v>19.61</v>
       </c>
       <c r="E25" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F25" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>57.96</v>
+        <v>60.18</v>
       </c>
       <c r="I25" t="n">
-        <v>58.31</v>
+        <v>61.23</v>
       </c>
       <c r="J25" t="n">
-        <v>57.52</v>
+        <v>59.04</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N25" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20.99</v>
+        <v>20.19</v>
       </c>
       <c r="C26" t="n">
-        <v>21.3</v>
+        <v>20.36</v>
       </c>
       <c r="D26" t="n">
-        <v>20.64</v>
+        <v>20.01</v>
       </c>
       <c r="E26" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F26" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>55.76</v>
+        <v>58.19</v>
       </c>
       <c r="I26" t="n">
-        <v>57.26</v>
+        <v>59.14</v>
       </c>
       <c r="J26" t="n">
-        <v>54.28</v>
+        <v>57.54</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>0.2</v>
       </c>
-      <c r="M26" t="n">
-        <v>0.8</v>
-      </c>
       <c r="N26" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.82</v>
+        <v>20.44</v>
       </c>
       <c r="C27" t="n">
-        <v>22.25</v>
+        <v>20.64</v>
       </c>
       <c r="D27" t="n">
-        <v>21.38</v>
+        <v>20.37</v>
       </c>
       <c r="E27" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="F27" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>52.03</v>
+        <v>57.96</v>
       </c>
       <c r="I27" t="n">
-        <v>53.83</v>
+        <v>58.31</v>
       </c>
       <c r="J27" t="n">
-        <v>50.23</v>
+        <v>57.52</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22.61</v>
+        <v>20.99</v>
       </c>
       <c r="C28" t="n">
-        <v>22.85</v>
+        <v>21.3</v>
       </c>
       <c r="D28" t="n">
-        <v>22.34</v>
+        <v>20.64</v>
       </c>
       <c r="E28" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G28" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>49.28</v>
+        <v>55.76</v>
       </c>
       <c r="I28" t="n">
-        <v>50.37</v>
+        <v>57.26</v>
       </c>
       <c r="J28" t="n">
-        <v>48.38</v>
+        <v>54.28</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="M28" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="N28" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23.26</v>
+        <v>21.82</v>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>22.25</v>
       </c>
       <c r="D29" t="n">
-        <v>22.73</v>
+        <v>21.38</v>
       </c>
       <c r="E29" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F29" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="G29" t="n">
-        <v>249</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>47.55</v>
+        <v>52.03</v>
       </c>
       <c r="I29" t="n">
-        <v>48.93</v>
+        <v>53.83</v>
       </c>
       <c r="J29" t="n">
-        <v>45.68</v>
+        <v>50.23</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M29" t="n">
         <v>1.1</v>
       </c>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
       <c r="N29" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.81</v>
+        <v>22.61</v>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>22.85</v>
       </c>
       <c r="D30" t="n">
-        <v>21.97</v>
+        <v>22.34</v>
       </c>
       <c r="E30" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F30" t="n">
         <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="H30" t="n">
-        <v>49.12</v>
+        <v>49.28</v>
       </c>
       <c r="I30" t="n">
-        <v>52.45</v>
+        <v>50.37</v>
       </c>
       <c r="J30" t="n">
-        <v>45.39</v>
+        <v>48.38</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="N30" t="n">
-        <v>6220</v>
+        <v>6200</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21.82</v>
+        <v>23.26</v>
       </c>
       <c r="C31" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>21.73</v>
+        <v>22.73</v>
       </c>
       <c r="E31" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="F31" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="G31" t="n">
-        <v>146</v>
+        <v>249</v>
       </c>
       <c r="H31" t="n">
-        <v>52.7</v>
+        <v>47.55</v>
       </c>
       <c r="I31" t="n">
-        <v>52.97</v>
+        <v>48.93</v>
       </c>
       <c r="J31" t="n">
-        <v>52.47</v>
+        <v>45.68</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21.74</v>
+        <v>22.81</v>
       </c>
       <c r="C32" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>21.56</v>
+        <v>21.97</v>
       </c>
       <c r="E32" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F32" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="G32" t="n">
-        <v>165</v>
+        <v>373</v>
       </c>
       <c r="H32" t="n">
-        <v>52.76</v>
+        <v>49.12</v>
       </c>
       <c r="I32" t="n">
-        <v>53.57</v>
+        <v>52.45</v>
       </c>
       <c r="J32" t="n">
-        <v>52.06</v>
+        <v>45.39</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N32" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21.42</v>
+        <v>21.82</v>
       </c>
       <c r="C33" t="n">
-        <v>22</v>
+        <v>21.95</v>
       </c>
       <c r="D33" t="n">
-        <v>20.92</v>
+        <v>21.73</v>
       </c>
       <c r="E33" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F33" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G33" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="H33" t="n">
-        <v>54.49</v>
+        <v>52.7</v>
       </c>
       <c r="I33" t="n">
-        <v>56.38</v>
+        <v>52.97</v>
       </c>
       <c r="J33" t="n">
-        <v>52.2</v>
+        <v>52.47</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N33" t="n">
         <v>6190</v>
@@ -2012,44 +2012,44 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21.35</v>
+        <v>21.74</v>
       </c>
       <c r="C34" t="n">
-        <v>22.22</v>
+        <v>21.95</v>
       </c>
       <c r="D34" t="n">
-        <v>20.87</v>
+        <v>21.56</v>
       </c>
       <c r="E34" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="F34" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G34" t="n">
-        <v>238</v>
+        <v>165</v>
       </c>
       <c r="H34" t="n">
-        <v>55.07</v>
+        <v>52.76</v>
       </c>
       <c r="I34" t="n">
-        <v>56.71</v>
+        <v>53.57</v>
       </c>
       <c r="J34" t="n">
-        <v>52.16</v>
+        <v>52.06</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="M34" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="N34" t="n">
         <v>6190</v>
@@ -2059,317 +2059,317 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>21.1</v>
+        <v>21.42</v>
       </c>
       <c r="C35" t="n">
-        <v>21.69</v>
+        <v>22</v>
       </c>
       <c r="D35" t="n">
-        <v>20.51</v>
+        <v>20.92</v>
       </c>
       <c r="E35" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F35" t="n">
         <v>11.5</v>
       </c>
       <c r="G35" t="n">
-        <v>480</v>
+        <v>218</v>
       </c>
       <c r="H35" t="n">
-        <v>55.96</v>
+        <v>54.49</v>
       </c>
       <c r="I35" t="n">
-        <v>58.01</v>
+        <v>56.38</v>
       </c>
       <c r="J35" t="n">
-        <v>53.81</v>
+        <v>52.2</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>20.15</v>
+        <v>21.35</v>
       </c>
       <c r="C36" t="n">
-        <v>20.85</v>
+        <v>22.22</v>
       </c>
       <c r="D36" t="n">
-        <v>19.57</v>
+        <v>20.87</v>
       </c>
       <c r="E36" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="F36" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G36" t="n">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="H36" t="n">
-        <v>60.77</v>
+        <v>55.07</v>
       </c>
       <c r="I36" t="n">
-        <v>64.81</v>
+        <v>56.71</v>
       </c>
       <c r="J36" t="n">
-        <v>56.73</v>
+        <v>52.16</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M36" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="N36" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.37</v>
+        <v>21.1</v>
       </c>
       <c r="C37" t="n">
-        <v>19.79</v>
+        <v>21.69</v>
       </c>
       <c r="D37" t="n">
-        <v>18.91</v>
+        <v>20.51</v>
       </c>
       <c r="E37" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F37" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G37" t="n">
-        <v>174</v>
+        <v>480</v>
       </c>
       <c r="H37" t="n">
-        <v>65.04000000000001</v>
+        <v>55.96</v>
       </c>
       <c r="I37" t="n">
-        <v>66.98999999999999</v>
+        <v>58.01</v>
       </c>
       <c r="J37" t="n">
-        <v>63.19</v>
+        <v>53.81</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="M37" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>6180</v>
+        <v>6210</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18.41</v>
+        <v>20.15</v>
       </c>
       <c r="C38" t="n">
-        <v>18.85</v>
+        <v>20.85</v>
       </c>
       <c r="D38" t="n">
-        <v>18.05</v>
+        <v>19.57</v>
       </c>
       <c r="E38" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="F38" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="G38" t="n">
-        <v>76</v>
+        <v>266</v>
       </c>
       <c r="H38" t="n">
-        <v>69.37</v>
+        <v>60.77</v>
       </c>
       <c r="I38" t="n">
-        <v>71.67</v>
+        <v>64.81</v>
       </c>
       <c r="J38" t="n">
-        <v>67.22</v>
+        <v>56.73</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M38" t="n">
         <v>2.3</v>
       </c>
       <c r="N38" t="n">
-        <v>6170</v>
+        <v>6200</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.66</v>
+        <v>19.37</v>
       </c>
       <c r="C39" t="n">
-        <v>17.95</v>
+        <v>19.79</v>
       </c>
       <c r="D39" t="n">
-        <v>17.51</v>
+        <v>18.91</v>
       </c>
       <c r="E39" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="F39" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="G39" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="H39" t="n">
-        <v>73.31</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>74.14</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>72.19</v>
+        <v>63.19</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="N39" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.6</v>
+        <v>18.41</v>
       </c>
       <c r="C40" t="n">
-        <v>17.68</v>
+        <v>18.85</v>
       </c>
       <c r="D40" t="n">
-        <v>17.49</v>
+        <v>18.05</v>
       </c>
       <c r="E40" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F40" t="n">
         <v>12.4</v>
       </c>
-      <c r="F40" t="n">
-        <v>12.3</v>
-      </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H40" t="n">
-        <v>72.5</v>
+        <v>69.37</v>
       </c>
       <c r="I40" t="n">
-        <v>73.76000000000001</v>
+        <v>71.67</v>
       </c>
       <c r="J40" t="n">
-        <v>71.78</v>
+        <v>67.22</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="N40" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.53</v>
+        <v>17.66</v>
       </c>
       <c r="C41" t="n">
-        <v>17.62</v>
+        <v>17.95</v>
       </c>
       <c r="D41" t="n">
-        <v>17.45</v>
+        <v>17.51</v>
       </c>
       <c r="E41" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="F41" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H41" t="n">
-        <v>72.33</v>
+        <v>73.31</v>
       </c>
       <c r="I41" t="n">
-        <v>72.88</v>
+        <v>74.14</v>
       </c>
       <c r="J41" t="n">
-        <v>71.93000000000001</v>
+        <v>72.19</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2378,124 +2378,124 @@
         <v>0.3</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N41" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.64</v>
+        <v>17.6</v>
       </c>
       <c r="C42" t="n">
-        <v>17.9</v>
+        <v>17.68</v>
       </c>
       <c r="D42" t="n">
-        <v>17.44</v>
+        <v>17.49</v>
       </c>
       <c r="E42" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F42" t="n">
         <v>12.3</v>
       </c>
-      <c r="F42" t="n">
-        <v>12</v>
-      </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>71.73999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I42" t="n">
-        <v>73.59999999999999</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>69.53</v>
+        <v>71.78</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="N42" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.84</v>
+        <v>17.53</v>
       </c>
       <c r="C43" t="n">
-        <v>17.88</v>
+        <v>17.62</v>
       </c>
       <c r="D43" t="n">
-        <v>17.8</v>
+        <v>17.45</v>
       </c>
       <c r="E43" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F43" t="n">
         <v>12.2</v>
       </c>
-      <c r="F43" t="n">
-        <v>12</v>
-      </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>70.06999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="I43" t="n">
-        <v>70.3</v>
+        <v>72.88</v>
       </c>
       <c r="J43" t="n">
-        <v>69.65000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M43" t="n">
         <v>0.8</v>
       </c>
-      <c r="M43" t="n">
-        <v>1.3</v>
-      </c>
       <c r="N43" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="C44" t="n">
         <v>17.9</v>
       </c>
-      <c r="C44" t="n">
-        <v>17.97</v>
-      </c>
       <c r="D44" t="n">
-        <v>17.82</v>
+        <v>17.44</v>
       </c>
       <c r="E44" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="F44" t="n">
         <v>12</v>
@@ -2504,69 +2504,69 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>69.79000000000001</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>70.48999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>69.43000000000001</v>
+        <v>69.53</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M44" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="N44" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.74</v>
+        <v>17.84</v>
       </c>
       <c r="C45" t="n">
-        <v>17.82</v>
+        <v>17.88</v>
       </c>
       <c r="D45" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="E45" t="n">
         <v>12.2</v>
       </c>
       <c r="F45" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>70.81999999999999</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>70.98</v>
+        <v>70.3</v>
       </c>
       <c r="J45" t="n">
-        <v>70.54000000000001</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M45" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N45" t="n">
         <v>6162</v>
@@ -2576,69 +2576,67 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.68</v>
+        <v>17.9</v>
       </c>
       <c r="C46" t="n">
-        <v>17.71</v>
+        <v>17.97</v>
       </c>
       <c r="D46" t="n">
-        <v>17.64</v>
+        <v>17.82</v>
       </c>
       <c r="E46" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="F46" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>71.42</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>71.8</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>71.13</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
         <v>1.5</v>
-      </c>
-      <c r="M46" t="n">
-        <v>2</v>
       </c>
       <c r="N46" t="n">
         <v>6162</v>
       </c>
-      <c r="O46" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>17.74</v>
       </c>
       <c r="C47" t="n">
-        <v>17.78</v>
+        <v>17.82</v>
       </c>
       <c r="D47" t="n">
-        <v>17.68</v>
+        <v>17.7</v>
       </c>
       <c r="E47" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="F47" t="n">
         <v>12.2</v>
@@ -2647,60 +2645,60 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>71.53</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>72.06999999999999</v>
+        <v>70.98</v>
       </c>
       <c r="J47" t="n">
-        <v>70.67</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N47" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18.17</v>
+        <v>17.68</v>
       </c>
       <c r="C48" t="n">
-        <v>18.45</v>
+        <v>17.71</v>
       </c>
       <c r="D48" t="n">
-        <v>17.85</v>
+        <v>17.64</v>
       </c>
       <c r="E48" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="F48" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>67.5</v>
+        <v>71.42</v>
       </c>
       <c r="I48" t="n">
-        <v>70.09</v>
+        <v>71.8</v>
       </c>
       <c r="J48" t="n">
-        <v>65.53</v>
+        <v>71.13</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2712,101 +2710,103 @@
         <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>6152</v>
-      </c>
-      <c r="O48" t="inlineStr"/>
+        <v>6162</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19.12</v>
+        <v>17.74</v>
       </c>
       <c r="C49" t="n">
-        <v>19.48</v>
+        <v>17.78</v>
       </c>
       <c r="D49" t="n">
-        <v>18.59</v>
+        <v>17.68</v>
       </c>
       <c r="E49" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="F49" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>62.25</v>
+        <v>71.53</v>
       </c>
       <c r="I49" t="n">
-        <v>64.8</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>60.27</v>
+        <v>70.67</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="M49" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>6180</v>
+        <v>6152</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>19.89</v>
+        <v>18.17</v>
       </c>
       <c r="C50" t="n">
-        <v>20.2</v>
+        <v>18.45</v>
       </c>
       <c r="D50" t="n">
-        <v>19.54</v>
+        <v>17.85</v>
       </c>
       <c r="E50" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="F50" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>58.12</v>
+        <v>67.5</v>
       </c>
       <c r="I50" t="n">
-        <v>59.88</v>
+        <v>70.09</v>
       </c>
       <c r="J50" t="n">
-        <v>56.65</v>
+        <v>65.53</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M50" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O50" t="n">
         <v>3.7</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,646 +508,646 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.63</v>
+        <v>15.35</v>
       </c>
       <c r="C2" t="n">
-        <v>17.67</v>
+        <v>15.55</v>
       </c>
       <c r="D2" t="n">
-        <v>17.6</v>
+        <v>15.29</v>
       </c>
       <c r="E2" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="F2" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>76.18000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>76.51000000000001</v>
+        <v>87.12</v>
       </c>
       <c r="J2" t="n">
-        <v>75.95</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="M2" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="N2" t="n">
-        <v>6132</v>
+        <v>6112</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.43</v>
+        <v>15.61</v>
       </c>
       <c r="C3" t="n">
-        <v>17.62</v>
+        <v>16.09</v>
       </c>
       <c r="D3" t="n">
-        <v>17.17</v>
+        <v>15.44</v>
       </c>
       <c r="E3" t="n">
-        <v>13.6</v>
+        <v>12.8</v>
       </c>
       <c r="F3" t="n">
-        <v>13.3</v>
+        <v>12.4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>79.34</v>
+        <v>84.45</v>
       </c>
       <c r="I3" t="n">
-        <v>82.2</v>
+        <v>86.2</v>
       </c>
       <c r="J3" t="n">
-        <v>77.51000000000001</v>
+        <v>79</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="N3" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.89</v>
+        <v>16.78</v>
       </c>
       <c r="C4" t="n">
-        <v>18.13</v>
+        <v>17.16</v>
       </c>
       <c r="D4" t="n">
-        <v>17.76</v>
+        <v>16.31</v>
       </c>
       <c r="E4" t="n">
-        <v>13.4</v>
+        <v>11.9</v>
       </c>
       <c r="F4" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>76.29000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="I4" t="n">
-        <v>78.06999999999999</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>74.34999999999999</v>
+        <v>69.84</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M4" t="n">
         <v>2.2</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.3</v>
-      </c>
       <c r="N4" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.6</v>
+        <v>17.55</v>
       </c>
       <c r="C5" t="n">
-        <v>19.26</v>
+        <v>17.8</v>
       </c>
       <c r="D5" t="n">
-        <v>18.22</v>
+        <v>17.2</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>12.1</v>
       </c>
       <c r="F5" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>70.7</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>73.79000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="J5" t="n">
-        <v>65.41</v>
+        <v>69.28</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="N5" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.29</v>
+        <v>17.63</v>
       </c>
       <c r="C6" t="n">
-        <v>21.69</v>
+        <v>18.08</v>
       </c>
       <c r="D6" t="n">
-        <v>19.3</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="F6" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>58.46</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>64.93000000000001</v>
+        <v>76.55</v>
       </c>
       <c r="J6" t="n">
-        <v>50.01</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="N6" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.33</v>
+        <v>17.46</v>
       </c>
       <c r="C7" t="n">
-        <v>22.66</v>
+        <v>17.67</v>
       </c>
       <c r="D7" t="n">
-        <v>21.95</v>
+        <v>17.22</v>
       </c>
       <c r="E7" t="n">
-        <v>9.9</v>
+        <v>13.2</v>
       </c>
       <c r="F7" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>46.23</v>
+        <v>76.84</v>
       </c>
       <c r="I7" t="n">
-        <v>48.69</v>
+        <v>79.37</v>
       </c>
       <c r="J7" t="n">
-        <v>44.45</v>
+        <v>75.08</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="N7" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.97</v>
+        <v>17.43</v>
       </c>
       <c r="C8" t="n">
-        <v>23.49</v>
+        <v>17.62</v>
       </c>
       <c r="D8" t="n">
-        <v>22.63</v>
+        <v>17.17</v>
       </c>
       <c r="E8" t="n">
-        <v>9.5</v>
+        <v>13.6</v>
       </c>
       <c r="F8" t="n">
-        <v>9.4</v>
+        <v>13.3</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>43.28</v>
+        <v>79.34</v>
       </c>
       <c r="I8" t="n">
-        <v>44.43</v>
+        <v>82.2</v>
       </c>
       <c r="J8" t="n">
-        <v>41.95</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>6180</v>
+        <v>6142</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.37</v>
+        <v>17.89</v>
       </c>
       <c r="C9" t="n">
-        <v>23.93</v>
+        <v>18.13</v>
       </c>
       <c r="D9" t="n">
-        <v>23.11</v>
+        <v>17.76</v>
       </c>
       <c r="E9" t="n">
-        <v>9.699999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="F9" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="G9" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>42.7</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>44.12</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>41.98</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="N9" t="n">
-        <v>6190</v>
+        <v>6142</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.27</v>
+        <v>18.6</v>
       </c>
       <c r="C10" t="n">
-        <v>23.64</v>
+        <v>19.26</v>
       </c>
       <c r="D10" t="n">
-        <v>22.89</v>
+        <v>18.22</v>
       </c>
       <c r="E10" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>9.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="G10" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>42.52</v>
+        <v>70.7</v>
       </c>
       <c r="I10" t="n">
-        <v>43.12</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>41.91</v>
+        <v>65.41</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.93</v>
+        <v>20.29</v>
       </c>
       <c r="C11" t="n">
-        <v>23.35</v>
+        <v>21.69</v>
       </c>
       <c r="D11" t="n">
-        <v>22.54</v>
+        <v>19.3</v>
       </c>
       <c r="E11" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="F11" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="G11" t="n">
-        <v>393</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>43.56</v>
+        <v>58.46</v>
       </c>
       <c r="I11" t="n">
-        <v>44.91</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>42.28</v>
+        <v>50.01</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22.23</v>
+        <v>22.33</v>
       </c>
       <c r="C12" t="n">
-        <v>22.76</v>
+        <v>22.66</v>
       </c>
       <c r="D12" t="n">
-        <v>21.86</v>
+        <v>21.95</v>
       </c>
       <c r="E12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="F12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="G12" t="n">
-        <v>383</v>
+        <v>24</v>
       </c>
       <c r="H12" t="n">
-        <v>45.63</v>
+        <v>46.23</v>
       </c>
       <c r="I12" t="n">
-        <v>47.01</v>
+        <v>48.69</v>
       </c>
       <c r="J12" t="n">
-        <v>44.24</v>
+        <v>44.45</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="N12" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.57</v>
+        <v>22.97</v>
       </c>
       <c r="C13" t="n">
-        <v>22.64</v>
+        <v>23.49</v>
       </c>
       <c r="D13" t="n">
-        <v>20.71</v>
+        <v>22.63</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="F13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G13" t="n">
-        <v>373</v>
+        <v>72</v>
       </c>
       <c r="H13" t="n">
-        <v>48.34</v>
+        <v>43.28</v>
       </c>
       <c r="I13" t="n">
-        <v>51.45</v>
+        <v>44.43</v>
       </c>
       <c r="J13" t="n">
-        <v>45.03</v>
+        <v>41.95</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N13" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20.3</v>
+        <v>23.37</v>
       </c>
       <c r="C14" t="n">
-        <v>20.76</v>
+        <v>23.93</v>
       </c>
       <c r="D14" t="n">
-        <v>19.87</v>
+        <v>23.11</v>
       </c>
       <c r="E14" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G14" t="n">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="H14" t="n">
-        <v>53.23</v>
+        <v>42.7</v>
       </c>
       <c r="I14" t="n">
-        <v>56.41</v>
+        <v>44.12</v>
       </c>
       <c r="J14" t="n">
-        <v>51.05</v>
+        <v>41.98</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="N14" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.38</v>
+        <v>23.27</v>
       </c>
       <c r="C15" t="n">
-        <v>19.85</v>
+        <v>23.64</v>
       </c>
       <c r="D15" t="n">
-        <v>18.89</v>
+        <v>22.89</v>
       </c>
       <c r="E15" t="n">
-        <v>11.6</v>
+        <v>9.6</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>110</v>
+        <v>326</v>
       </c>
       <c r="H15" t="n">
-        <v>61.37</v>
+        <v>42.52</v>
       </c>
       <c r="I15" t="n">
-        <v>65.44</v>
+        <v>43.12</v>
       </c>
       <c r="J15" t="n">
-        <v>57.45</v>
+        <v>41.91</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1156,242 +1156,242 @@
         <v>0.5</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N15" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18.52</v>
+        <v>22.93</v>
       </c>
       <c r="C16" t="n">
-        <v>18.87</v>
+        <v>23.35</v>
       </c>
       <c r="D16" t="n">
-        <v>18.23</v>
+        <v>22.54</v>
       </c>
       <c r="E16" t="n">
-        <v>12.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="G16" t="n">
-        <v>34</v>
+        <v>393</v>
       </c>
       <c r="H16" t="n">
-        <v>67.5</v>
+        <v>43.56</v>
       </c>
       <c r="I16" t="n">
-        <v>70.43000000000001</v>
+        <v>44.91</v>
       </c>
       <c r="J16" t="n">
-        <v>65.33</v>
+        <v>42.28</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N16" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.89</v>
+        <v>22.23</v>
       </c>
       <c r="C17" t="n">
-        <v>18.27</v>
+        <v>22.76</v>
       </c>
       <c r="D17" t="n">
-        <v>17.53</v>
+        <v>21.86</v>
       </c>
       <c r="E17" t="n">
-        <v>13.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>12.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>383</v>
       </c>
       <c r="H17" t="n">
-        <v>74.15000000000001</v>
+        <v>45.63</v>
       </c>
       <c r="I17" t="n">
-        <v>77.34999999999999</v>
+        <v>47.01</v>
       </c>
       <c r="J17" t="n">
-        <v>70.23999999999999</v>
+        <v>44.24</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="N17" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.34</v>
+        <v>21.57</v>
       </c>
       <c r="C18" t="n">
-        <v>17.48</v>
+        <v>22.64</v>
       </c>
       <c r="D18" t="n">
-        <v>17.19</v>
+        <v>20.71</v>
       </c>
       <c r="E18" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>13.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="H18" t="n">
-        <v>78.27</v>
+        <v>48.34</v>
       </c>
       <c r="I18" t="n">
-        <v>79.16</v>
+        <v>51.45</v>
       </c>
       <c r="J18" t="n">
-        <v>77.5</v>
+        <v>45.03</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="N18" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.62</v>
+        <v>20.3</v>
       </c>
       <c r="C19" t="n">
-        <v>17.85</v>
+        <v>20.76</v>
       </c>
       <c r="D19" t="n">
-        <v>17.33</v>
+        <v>19.87</v>
       </c>
       <c r="E19" t="n">
-        <v>12.8</v>
+        <v>10.3</v>
       </c>
       <c r="F19" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="H19" t="n">
-        <v>74.13</v>
+        <v>53.23</v>
       </c>
       <c r="I19" t="n">
-        <v>77.06</v>
+        <v>56.41</v>
       </c>
       <c r="J19" t="n">
-        <v>71.3</v>
+        <v>51.05</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N19" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.72</v>
+        <v>19.38</v>
       </c>
       <c r="C20" t="n">
-        <v>18.84</v>
+        <v>19.85</v>
       </c>
       <c r="D20" t="n">
-        <v>17.46</v>
+        <v>18.89</v>
       </c>
       <c r="E20" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="F20" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H20" t="n">
-        <v>71.95999999999999</v>
+        <v>61.37</v>
       </c>
       <c r="I20" t="n">
-        <v>74.59999999999999</v>
+        <v>65.44</v>
       </c>
       <c r="J20" t="n">
-        <v>65.83</v>
+        <v>57.45</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
         <v>6152</v>
@@ -1401,44 +1401,44 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.99</v>
+        <v>18.52</v>
       </c>
       <c r="C21" t="n">
-        <v>19.05</v>
+        <v>18.87</v>
       </c>
       <c r="D21" t="n">
-        <v>18.9</v>
+        <v>18.23</v>
       </c>
       <c r="E21" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="F21" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H21" t="n">
-        <v>62.56</v>
+        <v>67.5</v>
       </c>
       <c r="I21" t="n">
-        <v>63.18</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>61.89</v>
+        <v>65.33</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>6152</v>
@@ -1448,82 +1448,82 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.33</v>
+        <v>17.89</v>
       </c>
       <c r="C22" t="n">
-        <v>19.55</v>
+        <v>18.27</v>
       </c>
       <c r="D22" t="n">
-        <v>19.01</v>
+        <v>17.53</v>
       </c>
       <c r="E22" t="n">
-        <v>11.4</v>
+        <v>13.1</v>
       </c>
       <c r="F22" t="n">
-        <v>11.3</v>
+        <v>12.6</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>60.72</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>62.8</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>59.1</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.52</v>
+        <v>17.34</v>
       </c>
       <c r="C23" t="n">
-        <v>19.58</v>
+        <v>17.48</v>
       </c>
       <c r="D23" t="n">
-        <v>19.46</v>
+        <v>17.19</v>
       </c>
       <c r="E23" t="n">
-        <v>11.4</v>
+        <v>13.3</v>
       </c>
       <c r="F23" t="n">
-        <v>11.2</v>
+        <v>13.1</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>60.01</v>
+        <v>78.27</v>
       </c>
       <c r="I23" t="n">
-        <v>60.64</v>
+        <v>79.16</v>
       </c>
       <c r="J23" t="n">
-        <v>59.58</v>
+        <v>77.5</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1535,42 +1535,42 @@
         <v>0.5</v>
       </c>
       <c r="N23" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.62</v>
+        <v>17.62</v>
       </c>
       <c r="C24" t="n">
-        <v>19.71</v>
+        <v>17.85</v>
       </c>
       <c r="D24" t="n">
-        <v>19.49</v>
+        <v>17.33</v>
       </c>
       <c r="E24" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="F24" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>60.63</v>
+        <v>74.13</v>
       </c>
       <c r="I24" t="n">
-        <v>61.71</v>
+        <v>77.06</v>
       </c>
       <c r="J24" t="n">
-        <v>59.73</v>
+        <v>71.3</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1582,89 +1582,89 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.79</v>
+        <v>17.72</v>
       </c>
       <c r="C25" t="n">
-        <v>20.01</v>
+        <v>18.84</v>
       </c>
       <c r="D25" t="n">
-        <v>19.61</v>
+        <v>17.46</v>
       </c>
       <c r="E25" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="F25" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>60.18</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>61.23</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>59.04</v>
+        <v>65.83</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20.19</v>
+        <v>18.99</v>
       </c>
       <c r="C26" t="n">
-        <v>20.36</v>
+        <v>19.05</v>
       </c>
       <c r="D26" t="n">
-        <v>20.01</v>
+        <v>18.9</v>
       </c>
       <c r="E26" t="n">
         <v>11.5</v>
       </c>
       <c r="F26" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>58.19</v>
+        <v>62.56</v>
       </c>
       <c r="I26" t="n">
-        <v>59.14</v>
+        <v>63.18</v>
       </c>
       <c r="J26" t="n">
-        <v>57.54</v>
+        <v>61.89</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1673,45 +1673,45 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20.44</v>
+        <v>19.33</v>
       </c>
       <c r="C27" t="n">
-        <v>20.64</v>
+        <v>19.55</v>
       </c>
       <c r="D27" t="n">
-        <v>20.37</v>
+        <v>19.01</v>
       </c>
       <c r="E27" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F27" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>57.96</v>
+        <v>60.72</v>
       </c>
       <c r="I27" t="n">
-        <v>58.31</v>
+        <v>62.8</v>
       </c>
       <c r="J27" t="n">
-        <v>57.52</v>
+        <v>59.1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1720,900 +1720,902 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N27" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20.99</v>
+        <v>19.52</v>
       </c>
       <c r="C28" t="n">
-        <v>21.3</v>
+        <v>19.58</v>
       </c>
       <c r="D28" t="n">
-        <v>20.64</v>
+        <v>19.46</v>
       </c>
       <c r="E28" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F28" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>55.76</v>
+        <v>60.01</v>
       </c>
       <c r="I28" t="n">
-        <v>57.26</v>
+        <v>60.64</v>
       </c>
       <c r="J28" t="n">
-        <v>54.28</v>
+        <v>59.58</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N28" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21.82</v>
+        <v>19.62</v>
       </c>
       <c r="C29" t="n">
-        <v>22.25</v>
+        <v>19.71</v>
       </c>
       <c r="D29" t="n">
-        <v>21.38</v>
+        <v>19.49</v>
       </c>
       <c r="E29" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F29" t="n">
         <v>11.4</v>
       </c>
-      <c r="F29" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>52.03</v>
+        <v>60.63</v>
       </c>
       <c r="I29" t="n">
-        <v>53.83</v>
+        <v>61.71</v>
       </c>
       <c r="J29" t="n">
-        <v>50.23</v>
+        <v>59.73</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6180</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
+        <v>6152</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.61</v>
+        <v>19.79</v>
       </c>
       <c r="C30" t="n">
-        <v>22.85</v>
+        <v>20.01</v>
       </c>
       <c r="D30" t="n">
-        <v>22.34</v>
+        <v>19.61</v>
       </c>
       <c r="E30" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="G30" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>49.28</v>
+        <v>60.18</v>
       </c>
       <c r="I30" t="n">
-        <v>50.37</v>
+        <v>61.23</v>
       </c>
       <c r="J30" t="n">
-        <v>48.38</v>
+        <v>59.04</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="M30" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="N30" t="n">
-        <v>6200</v>
+        <v>6142</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23.26</v>
+        <v>20.19</v>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>20.36</v>
       </c>
       <c r="D31" t="n">
-        <v>22.73</v>
+        <v>20.01</v>
       </c>
       <c r="E31" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="F31" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="G31" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>47.55</v>
+        <v>58.19</v>
       </c>
       <c r="I31" t="n">
-        <v>48.93</v>
+        <v>59.14</v>
       </c>
       <c r="J31" t="n">
-        <v>45.68</v>
+        <v>57.54</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="N31" t="n">
-        <v>6220</v>
+        <v>6132</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22.81</v>
+        <v>20.44</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>20.64</v>
       </c>
       <c r="D32" t="n">
-        <v>21.97</v>
+        <v>20.37</v>
       </c>
       <c r="E32" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G32" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>49.12</v>
+        <v>57.96</v>
       </c>
       <c r="I32" t="n">
-        <v>52.45</v>
+        <v>58.31</v>
       </c>
       <c r="J32" t="n">
-        <v>45.39</v>
+        <v>57.52</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21.82</v>
+        <v>20.99</v>
       </c>
       <c r="C33" t="n">
-        <v>21.95</v>
+        <v>21.3</v>
       </c>
       <c r="D33" t="n">
-        <v>21.73</v>
+        <v>20.64</v>
       </c>
       <c r="E33" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F33" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="G33" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>52.7</v>
+        <v>55.76</v>
       </c>
       <c r="I33" t="n">
-        <v>52.97</v>
+        <v>57.26</v>
       </c>
       <c r="J33" t="n">
-        <v>52.47</v>
+        <v>54.28</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="N33" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21.74</v>
+        <v>21.82</v>
       </c>
       <c r="C34" t="n">
-        <v>21.95</v>
+        <v>22.25</v>
       </c>
       <c r="D34" t="n">
-        <v>21.56</v>
+        <v>21.38</v>
       </c>
       <c r="E34" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F34" t="n">
         <v>11.2</v>
       </c>
       <c r="G34" t="n">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>52.76</v>
+        <v>52.03</v>
       </c>
       <c r="I34" t="n">
-        <v>53.57</v>
+        <v>53.83</v>
       </c>
       <c r="J34" t="n">
-        <v>52.06</v>
+        <v>50.23</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>21.42</v>
+        <v>22.61</v>
       </c>
       <c r="C35" t="n">
-        <v>22</v>
+        <v>22.85</v>
       </c>
       <c r="D35" t="n">
-        <v>20.92</v>
+        <v>22.34</v>
       </c>
       <c r="E35" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="F35" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="H35" t="n">
-        <v>54.49</v>
+        <v>49.28</v>
       </c>
       <c r="I35" t="n">
-        <v>56.38</v>
+        <v>50.37</v>
       </c>
       <c r="J35" t="n">
-        <v>52.2</v>
+        <v>48.38</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N35" t="n">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21.35</v>
+        <v>23.26</v>
       </c>
       <c r="C36" t="n">
-        <v>22.22</v>
+        <v>24</v>
       </c>
       <c r="D36" t="n">
-        <v>20.87</v>
+        <v>22.73</v>
       </c>
       <c r="E36" t="n">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
       <c r="F36" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="G36" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="H36" t="n">
-        <v>55.07</v>
+        <v>47.55</v>
       </c>
       <c r="I36" t="n">
-        <v>56.71</v>
+        <v>48.93</v>
       </c>
       <c r="J36" t="n">
-        <v>52.16</v>
+        <v>45.68</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="M36" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>21.1</v>
+        <v>22.81</v>
       </c>
       <c r="C37" t="n">
-        <v>21.69</v>
+        <v>24</v>
       </c>
       <c r="D37" t="n">
-        <v>20.51</v>
+        <v>21.97</v>
       </c>
       <c r="E37" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F37" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G37" t="n">
-        <v>480</v>
+        <v>373</v>
       </c>
       <c r="H37" t="n">
-        <v>55.96</v>
+        <v>49.12</v>
       </c>
       <c r="I37" t="n">
-        <v>58.01</v>
+        <v>52.45</v>
       </c>
       <c r="J37" t="n">
-        <v>53.81</v>
+        <v>45.39</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="N37" t="n">
-        <v>6210</v>
+        <v>6220</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20.15</v>
+        <v>21.82</v>
       </c>
       <c r="C38" t="n">
-        <v>20.85</v>
+        <v>21.95</v>
       </c>
       <c r="D38" t="n">
-        <v>19.57</v>
+        <v>21.73</v>
       </c>
       <c r="E38" t="n">
-        <v>12.1</v>
+        <v>11.4</v>
       </c>
       <c r="F38" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="G38" t="n">
-        <v>266</v>
+        <v>146</v>
       </c>
       <c r="H38" t="n">
-        <v>60.77</v>
+        <v>52.7</v>
       </c>
       <c r="I38" t="n">
-        <v>64.81</v>
+        <v>52.97</v>
       </c>
       <c r="J38" t="n">
-        <v>56.73</v>
+        <v>52.47</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="M38" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="N38" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>19.37</v>
+        <v>21.74</v>
       </c>
       <c r="C39" t="n">
-        <v>19.79</v>
+        <v>21.95</v>
       </c>
       <c r="D39" t="n">
-        <v>18.91</v>
+        <v>21.56</v>
       </c>
       <c r="E39" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="F39" t="n">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
       <c r="G39" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="H39" t="n">
-        <v>65.04000000000001</v>
+        <v>52.76</v>
       </c>
       <c r="I39" t="n">
-        <v>66.98999999999999</v>
+        <v>53.57</v>
       </c>
       <c r="J39" t="n">
-        <v>63.19</v>
+        <v>52.06</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="M39" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="N39" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>18.41</v>
+        <v>21.42</v>
       </c>
       <c r="C40" t="n">
-        <v>18.85</v>
+        <v>22</v>
       </c>
       <c r="D40" t="n">
-        <v>18.05</v>
+        <v>20.92</v>
       </c>
       <c r="E40" t="n">
-        <v>12.6</v>
+        <v>11.6</v>
       </c>
       <c r="F40" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G40" t="n">
-        <v>76</v>
+        <v>218</v>
       </c>
       <c r="H40" t="n">
-        <v>69.37</v>
+        <v>54.49</v>
       </c>
       <c r="I40" t="n">
-        <v>71.67</v>
+        <v>56.38</v>
       </c>
       <c r="J40" t="n">
-        <v>67.22</v>
+        <v>52.2</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="N40" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.66</v>
+        <v>21.35</v>
       </c>
       <c r="C41" t="n">
-        <v>17.95</v>
+        <v>22.22</v>
       </c>
       <c r="D41" t="n">
-        <v>17.51</v>
+        <v>20.87</v>
       </c>
       <c r="E41" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="F41" t="n">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="G41" t="n">
-        <v>10</v>
+        <v>238</v>
       </c>
       <c r="H41" t="n">
-        <v>73.31</v>
+        <v>55.07</v>
       </c>
       <c r="I41" t="n">
-        <v>74.14</v>
+        <v>56.71</v>
       </c>
       <c r="J41" t="n">
-        <v>72.19</v>
+        <v>52.16</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="N41" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.6</v>
+        <v>21.1</v>
       </c>
       <c r="C42" t="n">
-        <v>17.68</v>
+        <v>21.69</v>
       </c>
       <c r="D42" t="n">
-        <v>17.49</v>
+        <v>20.51</v>
       </c>
       <c r="E42" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F42" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="H42" t="n">
-        <v>72.5</v>
+        <v>55.96</v>
       </c>
       <c r="I42" t="n">
-        <v>73.76000000000001</v>
+        <v>58.01</v>
       </c>
       <c r="J42" t="n">
-        <v>71.78</v>
+        <v>53.81</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>6142</v>
+        <v>6210</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.53</v>
+        <v>20.15</v>
       </c>
       <c r="C43" t="n">
-        <v>17.62</v>
+        <v>20.85</v>
       </c>
       <c r="D43" t="n">
-        <v>17.45</v>
+        <v>19.57</v>
       </c>
       <c r="E43" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F43" t="n">
-        <v>12.2</v>
+        <v>11.6</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="H43" t="n">
-        <v>72.33</v>
+        <v>60.77</v>
       </c>
       <c r="I43" t="n">
-        <v>72.88</v>
+        <v>64.81</v>
       </c>
       <c r="J43" t="n">
-        <v>71.93000000000001</v>
+        <v>56.73</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="N43" t="n">
-        <v>6152</v>
+        <v>6200</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17.64</v>
+        <v>19.37</v>
       </c>
       <c r="C44" t="n">
-        <v>17.9</v>
+        <v>19.79</v>
       </c>
       <c r="D44" t="n">
-        <v>17.44</v>
+        <v>18.91</v>
       </c>
       <c r="E44" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F44" t="n">
         <v>12.3</v>
       </c>
-      <c r="F44" t="n">
-        <v>12</v>
-      </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="H44" t="n">
-        <v>71.73999999999999</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>73.59999999999999</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>69.53</v>
+        <v>63.19</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M44" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="N44" t="n">
-        <v>6152</v>
+        <v>6180</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.84</v>
+        <v>18.41</v>
       </c>
       <c r="C45" t="n">
-        <v>17.88</v>
+        <v>18.85</v>
       </c>
       <c r="D45" t="n">
-        <v>17.8</v>
+        <v>18.05</v>
       </c>
       <c r="E45" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="F45" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H45" t="n">
-        <v>70.06999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="I45" t="n">
-        <v>70.3</v>
+        <v>71.67</v>
       </c>
       <c r="J45" t="n">
-        <v>69.65000000000001</v>
+        <v>67.22</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="M45" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="N45" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.9</v>
+        <v>17.66</v>
       </c>
       <c r="C46" t="n">
-        <v>17.97</v>
+        <v>17.95</v>
       </c>
       <c r="D46" t="n">
-        <v>17.82</v>
+        <v>17.51</v>
       </c>
       <c r="E46" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H46" t="n">
-        <v>69.79000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="I46" t="n">
-        <v>70.48999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="J46" t="n">
-        <v>69.43000000000001</v>
+        <v>72.19</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M46" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="N46" t="n">
         <v>6162</v>
@@ -2623,193 +2625,144 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.74</v>
+        <v>17.6</v>
       </c>
       <c r="C47" t="n">
-        <v>17.82</v>
+        <v>17.68</v>
       </c>
       <c r="D47" t="n">
-        <v>17.7</v>
+        <v>17.49</v>
       </c>
       <c r="E47" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F47" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>70.81999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I47" t="n">
-        <v>70.98</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>70.54000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="N47" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.68</v>
+        <v>17.53</v>
       </c>
       <c r="C48" t="n">
-        <v>17.71</v>
+        <v>17.62</v>
       </c>
       <c r="D48" t="n">
-        <v>17.64</v>
+        <v>17.45</v>
       </c>
       <c r="E48" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F48" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>71.42</v>
+        <v>72.33</v>
       </c>
       <c r="I48" t="n">
-        <v>71.8</v>
+        <v>72.88</v>
       </c>
       <c r="J48" t="n">
-        <v>71.13</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N48" t="n">
-        <v>6162</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.4</v>
-      </c>
+        <v>6152</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.74</v>
+        <v>17.64</v>
       </c>
       <c r="C49" t="n">
-        <v>17.78</v>
+        <v>17.9</v>
       </c>
       <c r="D49" t="n">
-        <v>17.68</v>
+        <v>17.44</v>
       </c>
       <c r="E49" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F49" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>71.53</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>72.06999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>70.67</v>
+        <v>69.53</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N49" t="n">
         <v>6152</v>
       </c>
-      <c r="O49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-10-15 22:00:00</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="C50" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="D50" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="E50" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F50" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="I50" t="n">
-        <v>70.09</v>
-      </c>
-      <c r="J50" t="n">
-        <v>65.53</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2</v>
-      </c>
-      <c r="N50" t="n">
-        <v>6152</v>
-      </c>
-      <c r="O50" t="n">
-        <v>3.7</v>
+      <c r="O49" t="n">
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,91 +508,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15.35</v>
+        <v>14.52</v>
       </c>
       <c r="C2" t="n">
-        <v>15.55</v>
+        <v>14.56</v>
       </c>
       <c r="D2" t="n">
-        <v>15.29</v>
+        <v>14.47</v>
       </c>
       <c r="E2" t="n">
-        <v>12.8</v>
+        <v>10.1</v>
       </c>
       <c r="F2" t="n">
-        <v>12.4</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H2" t="n">
-        <v>85.76000000000001</v>
+        <v>76.09</v>
       </c>
       <c r="I2" t="n">
-        <v>87.12</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>82.43000000000001</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>1.2</v>
       </c>
       <c r="N2" t="n">
-        <v>6112</v>
+        <v>6122</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.61</v>
+        <v>14.64</v>
       </c>
       <c r="C3" t="n">
-        <v>16.09</v>
+        <v>14.86</v>
       </c>
       <c r="D3" t="n">
-        <v>15.44</v>
+        <v>14.45</v>
       </c>
       <c r="E3" t="n">
-        <v>12.8</v>
+        <v>10.9</v>
       </c>
       <c r="F3" t="n">
-        <v>12.4</v>
+        <v>10.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>84.45</v>
+        <v>79.53</v>
       </c>
       <c r="I3" t="n">
-        <v>86.2</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>79</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="N3" t="n">
         <v>6132</v>
@@ -602,787 +602,787 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.78</v>
+        <v>15.07</v>
       </c>
       <c r="C4" t="n">
-        <v>17.16</v>
+        <v>15.23</v>
       </c>
       <c r="D4" t="n">
-        <v>16.31</v>
+        <v>14.92</v>
       </c>
       <c r="E4" t="n">
-        <v>11.9</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>73.62</v>
+        <v>77.61</v>
       </c>
       <c r="I4" t="n">
-        <v>76.98999999999999</v>
+        <v>78.94</v>
       </c>
       <c r="J4" t="n">
-        <v>69.84</v>
+        <v>76.67</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.55</v>
+        <v>15.37</v>
       </c>
       <c r="C5" t="n">
-        <v>17.8</v>
+        <v>15.49</v>
       </c>
       <c r="D5" t="n">
-        <v>17.2</v>
+        <v>15.25</v>
       </c>
       <c r="E5" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="F5" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>71.04000000000001</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>73.81</v>
+        <v>80.69</v>
       </c>
       <c r="J5" t="n">
-        <v>69.28</v>
+        <v>78.86</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.63</v>
+        <v>15.65</v>
       </c>
       <c r="C6" t="n">
-        <v>18.08</v>
+        <v>15.77</v>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>15.48</v>
       </c>
       <c r="E6" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>73.43000000000001</v>
+        <v>78.64</v>
       </c>
       <c r="I6" t="n">
-        <v>76.55</v>
+        <v>80.7</v>
       </c>
       <c r="J6" t="n">
-        <v>68.51000000000001</v>
+        <v>77.23</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="N6" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.46</v>
+        <v>15.39</v>
       </c>
       <c r="C7" t="n">
-        <v>17.67</v>
+        <v>15.59</v>
       </c>
       <c r="D7" t="n">
-        <v>17.22</v>
+        <v>15.29</v>
       </c>
       <c r="E7" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>76.84</v>
+        <v>84.89</v>
       </c>
       <c r="I7" t="n">
-        <v>79.37</v>
+        <v>87.12</v>
       </c>
       <c r="J7" t="n">
-        <v>75.08</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="N7" t="n">
-        <v>6132</v>
+        <v>6112</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.43</v>
+        <v>15.61</v>
       </c>
       <c r="C8" t="n">
-        <v>17.62</v>
+        <v>16.09</v>
       </c>
       <c r="D8" t="n">
-        <v>17.17</v>
+        <v>15.44</v>
       </c>
       <c r="E8" t="n">
-        <v>13.6</v>
+        <v>12.8</v>
       </c>
       <c r="F8" t="n">
-        <v>13.3</v>
+        <v>12.4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>79.34</v>
+        <v>84.45</v>
       </c>
       <c r="I8" t="n">
-        <v>82.2</v>
+        <v>86.2</v>
       </c>
       <c r="J8" t="n">
-        <v>77.51000000000001</v>
+        <v>79</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="N8" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.89</v>
+        <v>16.78</v>
       </c>
       <c r="C9" t="n">
-        <v>18.13</v>
+        <v>17.16</v>
       </c>
       <c r="D9" t="n">
-        <v>17.76</v>
+        <v>16.31</v>
       </c>
       <c r="E9" t="n">
-        <v>13.4</v>
+        <v>11.9</v>
       </c>
       <c r="F9" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>76.29000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="I9" t="n">
-        <v>78.06999999999999</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>74.34999999999999</v>
+        <v>69.84</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M9" t="n">
         <v>2.2</v>
       </c>
-      <c r="M9" t="n">
-        <v>2.3</v>
-      </c>
       <c r="N9" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18.6</v>
+        <v>17.55</v>
       </c>
       <c r="C10" t="n">
-        <v>19.26</v>
+        <v>17.8</v>
       </c>
       <c r="D10" t="n">
-        <v>18.22</v>
+        <v>17.2</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>12.1</v>
       </c>
       <c r="F10" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>70.7</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>73.79000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="J10" t="n">
-        <v>65.41</v>
+        <v>69.28</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="N10" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20.29</v>
+        <v>17.63</v>
       </c>
       <c r="C11" t="n">
-        <v>21.69</v>
+        <v>18.08</v>
       </c>
       <c r="D11" t="n">
-        <v>19.3</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="F11" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>58.46</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>64.93000000000001</v>
+        <v>76.55</v>
       </c>
       <c r="J11" t="n">
-        <v>50.01</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="N11" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22.33</v>
+        <v>17.46</v>
       </c>
       <c r="C12" t="n">
-        <v>22.66</v>
+        <v>17.67</v>
       </c>
       <c r="D12" t="n">
-        <v>21.95</v>
+        <v>17.22</v>
       </c>
       <c r="E12" t="n">
-        <v>9.9</v>
+        <v>13.2</v>
       </c>
       <c r="F12" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>46.23</v>
+        <v>76.84</v>
       </c>
       <c r="I12" t="n">
-        <v>48.69</v>
+        <v>79.37</v>
       </c>
       <c r="J12" t="n">
-        <v>44.45</v>
+        <v>75.08</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="N12" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22.97</v>
+        <v>17.43</v>
       </c>
       <c r="C13" t="n">
-        <v>23.49</v>
+        <v>17.62</v>
       </c>
       <c r="D13" t="n">
-        <v>22.63</v>
+        <v>17.17</v>
       </c>
       <c r="E13" t="n">
-        <v>9.5</v>
+        <v>13.6</v>
       </c>
       <c r="F13" t="n">
-        <v>9.4</v>
+        <v>13.3</v>
       </c>
       <c r="G13" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>43.28</v>
+        <v>79.34</v>
       </c>
       <c r="I13" t="n">
-        <v>44.43</v>
+        <v>82.2</v>
       </c>
       <c r="J13" t="n">
-        <v>41.95</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>6180</v>
+        <v>6142</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23.37</v>
+        <v>17.89</v>
       </c>
       <c r="C14" t="n">
-        <v>23.93</v>
+        <v>18.13</v>
       </c>
       <c r="D14" t="n">
-        <v>23.11</v>
+        <v>17.76</v>
       </c>
       <c r="E14" t="n">
-        <v>9.699999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="F14" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="G14" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>42.7</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>44.12</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>41.98</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="N14" t="n">
-        <v>6190</v>
+        <v>6142</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23.27</v>
+        <v>18.6</v>
       </c>
       <c r="C15" t="n">
-        <v>23.64</v>
+        <v>19.26</v>
       </c>
       <c r="D15" t="n">
-        <v>22.89</v>
+        <v>18.22</v>
       </c>
       <c r="E15" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>9.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="G15" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>42.52</v>
+        <v>70.7</v>
       </c>
       <c r="I15" t="n">
-        <v>43.12</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>41.91</v>
+        <v>65.41</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22.93</v>
+        <v>20.29</v>
       </c>
       <c r="C16" t="n">
-        <v>23.35</v>
+        <v>21.69</v>
       </c>
       <c r="D16" t="n">
-        <v>22.54</v>
+        <v>19.3</v>
       </c>
       <c r="E16" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="F16" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="G16" t="n">
-        <v>393</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>43.56</v>
+        <v>58.46</v>
       </c>
       <c r="I16" t="n">
-        <v>44.91</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>42.28</v>
+        <v>50.01</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22.23</v>
+        <v>22.33</v>
       </c>
       <c r="C17" t="n">
-        <v>22.76</v>
+        <v>22.66</v>
       </c>
       <c r="D17" t="n">
-        <v>21.86</v>
+        <v>21.95</v>
       </c>
       <c r="E17" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="F17" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="G17" t="n">
-        <v>383</v>
+        <v>24</v>
       </c>
       <c r="H17" t="n">
-        <v>45.63</v>
+        <v>46.23</v>
       </c>
       <c r="I17" t="n">
-        <v>47.01</v>
+        <v>48.69</v>
       </c>
       <c r="J17" t="n">
-        <v>44.24</v>
+        <v>44.45</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="N17" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21.57</v>
+        <v>22.97</v>
       </c>
       <c r="C18" t="n">
-        <v>22.64</v>
+        <v>23.49</v>
       </c>
       <c r="D18" t="n">
-        <v>20.71</v>
+        <v>22.63</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="F18" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G18" t="n">
-        <v>373</v>
+        <v>72</v>
       </c>
       <c r="H18" t="n">
-        <v>48.34</v>
+        <v>43.28</v>
       </c>
       <c r="I18" t="n">
-        <v>51.45</v>
+        <v>44.43</v>
       </c>
       <c r="J18" t="n">
-        <v>45.03</v>
+        <v>41.95</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N18" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20.3</v>
+        <v>23.37</v>
       </c>
       <c r="C19" t="n">
-        <v>20.76</v>
+        <v>23.93</v>
       </c>
       <c r="D19" t="n">
-        <v>19.87</v>
+        <v>23.11</v>
       </c>
       <c r="E19" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G19" t="n">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="H19" t="n">
-        <v>53.23</v>
+        <v>42.7</v>
       </c>
       <c r="I19" t="n">
-        <v>56.41</v>
+        <v>44.12</v>
       </c>
       <c r="J19" t="n">
-        <v>51.05</v>
+        <v>41.98</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="N19" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.38</v>
+        <v>23.27</v>
       </c>
       <c r="C20" t="n">
-        <v>19.85</v>
+        <v>23.64</v>
       </c>
       <c r="D20" t="n">
-        <v>18.89</v>
+        <v>22.89</v>
       </c>
       <c r="E20" t="n">
-        <v>11.6</v>
+        <v>9.6</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>110</v>
+        <v>326</v>
       </c>
       <c r="H20" t="n">
-        <v>61.37</v>
+        <v>42.52</v>
       </c>
       <c r="I20" t="n">
-        <v>65.44</v>
+        <v>43.12</v>
       </c>
       <c r="J20" t="n">
-        <v>57.45</v>
+        <v>41.91</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1391,242 +1391,242 @@
         <v>0.5</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N20" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.52</v>
+        <v>22.93</v>
       </c>
       <c r="C21" t="n">
-        <v>18.87</v>
+        <v>23.35</v>
       </c>
       <c r="D21" t="n">
-        <v>18.23</v>
+        <v>22.54</v>
       </c>
       <c r="E21" t="n">
-        <v>12.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="G21" t="n">
-        <v>34</v>
+        <v>393</v>
       </c>
       <c r="H21" t="n">
-        <v>67.5</v>
+        <v>43.56</v>
       </c>
       <c r="I21" t="n">
-        <v>70.43000000000001</v>
+        <v>44.91</v>
       </c>
       <c r="J21" t="n">
-        <v>65.33</v>
+        <v>42.28</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N21" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.89</v>
+        <v>22.23</v>
       </c>
       <c r="C22" t="n">
-        <v>18.27</v>
+        <v>22.76</v>
       </c>
       <c r="D22" t="n">
-        <v>17.53</v>
+        <v>21.86</v>
       </c>
       <c r="E22" t="n">
-        <v>13.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>12.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>383</v>
       </c>
       <c r="H22" t="n">
-        <v>74.15000000000001</v>
+        <v>45.63</v>
       </c>
       <c r="I22" t="n">
-        <v>77.34999999999999</v>
+        <v>47.01</v>
       </c>
       <c r="J22" t="n">
-        <v>70.23999999999999</v>
+        <v>44.24</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="N22" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.34</v>
+        <v>21.57</v>
       </c>
       <c r="C23" t="n">
-        <v>17.48</v>
+        <v>22.64</v>
       </c>
       <c r="D23" t="n">
-        <v>17.19</v>
+        <v>20.71</v>
       </c>
       <c r="E23" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>13.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="H23" t="n">
-        <v>78.27</v>
+        <v>48.34</v>
       </c>
       <c r="I23" t="n">
-        <v>79.16</v>
+        <v>51.45</v>
       </c>
       <c r="J23" t="n">
-        <v>77.5</v>
+        <v>45.03</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="N23" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.62</v>
+        <v>20.3</v>
       </c>
       <c r="C24" t="n">
-        <v>17.85</v>
+        <v>20.76</v>
       </c>
       <c r="D24" t="n">
-        <v>17.33</v>
+        <v>19.87</v>
       </c>
       <c r="E24" t="n">
-        <v>12.8</v>
+        <v>10.3</v>
       </c>
       <c r="F24" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="H24" t="n">
-        <v>74.13</v>
+        <v>53.23</v>
       </c>
       <c r="I24" t="n">
-        <v>77.06</v>
+        <v>56.41</v>
       </c>
       <c r="J24" t="n">
-        <v>71.3</v>
+        <v>51.05</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N24" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.72</v>
+        <v>19.38</v>
       </c>
       <c r="C25" t="n">
-        <v>18.84</v>
+        <v>19.85</v>
       </c>
       <c r="D25" t="n">
-        <v>17.46</v>
+        <v>18.89</v>
       </c>
       <c r="E25" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="F25" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H25" t="n">
-        <v>71.95999999999999</v>
+        <v>61.37</v>
       </c>
       <c r="I25" t="n">
-        <v>74.59999999999999</v>
+        <v>65.44</v>
       </c>
       <c r="J25" t="n">
-        <v>65.83</v>
+        <v>57.45</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
         <v>6152</v>
@@ -1636,44 +1636,44 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18.99</v>
+        <v>18.52</v>
       </c>
       <c r="C26" t="n">
-        <v>19.05</v>
+        <v>18.87</v>
       </c>
       <c r="D26" t="n">
-        <v>18.9</v>
+        <v>18.23</v>
       </c>
       <c r="E26" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="F26" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H26" t="n">
-        <v>62.56</v>
+        <v>67.5</v>
       </c>
       <c r="I26" t="n">
-        <v>63.18</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>61.89</v>
+        <v>65.33</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>6152</v>
@@ -1683,82 +1683,82 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.33</v>
+        <v>17.89</v>
       </c>
       <c r="C27" t="n">
-        <v>19.55</v>
+        <v>18.27</v>
       </c>
       <c r="D27" t="n">
-        <v>19.01</v>
+        <v>17.53</v>
       </c>
       <c r="E27" t="n">
-        <v>11.4</v>
+        <v>13.1</v>
       </c>
       <c r="F27" t="n">
-        <v>11.3</v>
+        <v>12.6</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>60.72</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>62.8</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>59.1</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.52</v>
+        <v>17.34</v>
       </c>
       <c r="C28" t="n">
-        <v>19.58</v>
+        <v>17.48</v>
       </c>
       <c r="D28" t="n">
-        <v>19.46</v>
+        <v>17.19</v>
       </c>
       <c r="E28" t="n">
-        <v>11.4</v>
+        <v>13.3</v>
       </c>
       <c r="F28" t="n">
-        <v>11.2</v>
+        <v>13.1</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>60.01</v>
+        <v>78.27</v>
       </c>
       <c r="I28" t="n">
-        <v>60.64</v>
+        <v>79.16</v>
       </c>
       <c r="J28" t="n">
-        <v>59.58</v>
+        <v>77.5</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1770,42 +1770,42 @@
         <v>0.5</v>
       </c>
       <c r="N28" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.62</v>
+        <v>17.62</v>
       </c>
       <c r="C29" t="n">
-        <v>19.71</v>
+        <v>17.85</v>
       </c>
       <c r="D29" t="n">
-        <v>19.49</v>
+        <v>17.33</v>
       </c>
       <c r="E29" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="F29" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>60.63</v>
+        <v>74.13</v>
       </c>
       <c r="I29" t="n">
-        <v>61.71</v>
+        <v>77.06</v>
       </c>
       <c r="J29" t="n">
-        <v>59.73</v>
+        <v>71.3</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1817,91 +1817,89 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6152</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.3</v>
-      </c>
+        <v>6142</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.79</v>
+        <v>17.72</v>
       </c>
       <c r="C30" t="n">
-        <v>20.01</v>
+        <v>18.84</v>
       </c>
       <c r="D30" t="n">
-        <v>19.61</v>
+        <v>17.46</v>
       </c>
       <c r="E30" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="F30" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>60.18</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>61.23</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>59.04</v>
+        <v>65.83</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20.19</v>
+        <v>18.99</v>
       </c>
       <c r="C31" t="n">
-        <v>20.36</v>
+        <v>19.05</v>
       </c>
       <c r="D31" t="n">
-        <v>20.01</v>
+        <v>18.9</v>
       </c>
       <c r="E31" t="n">
         <v>11.5</v>
       </c>
       <c r="F31" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>58.19</v>
+        <v>62.56</v>
       </c>
       <c r="I31" t="n">
-        <v>59.14</v>
+        <v>63.18</v>
       </c>
       <c r="J31" t="n">
-        <v>57.54</v>
+        <v>61.89</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1910,45 +1908,45 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>20.44</v>
+        <v>19.33</v>
       </c>
       <c r="C32" t="n">
-        <v>20.64</v>
+        <v>19.55</v>
       </c>
       <c r="D32" t="n">
-        <v>20.37</v>
+        <v>19.01</v>
       </c>
       <c r="E32" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F32" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>57.96</v>
+        <v>60.72</v>
       </c>
       <c r="I32" t="n">
-        <v>58.31</v>
+        <v>62.8</v>
       </c>
       <c r="J32" t="n">
-        <v>57.52</v>
+        <v>59.1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1957,811 +1955,860 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N32" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.99</v>
+        <v>19.52</v>
       </c>
       <c r="C33" t="n">
-        <v>21.3</v>
+        <v>19.58</v>
       </c>
       <c r="D33" t="n">
-        <v>20.64</v>
+        <v>19.46</v>
       </c>
       <c r="E33" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F33" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>55.76</v>
+        <v>60.01</v>
       </c>
       <c r="I33" t="n">
-        <v>57.26</v>
+        <v>60.64</v>
       </c>
       <c r="J33" t="n">
-        <v>54.28</v>
+        <v>59.58</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N33" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21.82</v>
+        <v>19.62</v>
       </c>
       <c r="C34" t="n">
-        <v>22.25</v>
+        <v>19.71</v>
       </c>
       <c r="D34" t="n">
-        <v>21.38</v>
+        <v>19.49</v>
       </c>
       <c r="E34" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F34" t="n">
         <v>11.4</v>
       </c>
-      <c r="F34" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>52.03</v>
+        <v>60.63</v>
       </c>
       <c r="I34" t="n">
-        <v>53.83</v>
+        <v>61.71</v>
       </c>
       <c r="J34" t="n">
-        <v>50.23</v>
+        <v>59.73</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6180</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
+        <v>6152</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.61</v>
+        <v>19.79</v>
       </c>
       <c r="C35" t="n">
-        <v>22.85</v>
+        <v>20.01</v>
       </c>
       <c r="D35" t="n">
-        <v>22.34</v>
+        <v>19.61</v>
       </c>
       <c r="E35" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="G35" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>49.28</v>
+        <v>60.18</v>
       </c>
       <c r="I35" t="n">
-        <v>50.37</v>
+        <v>61.23</v>
       </c>
       <c r="J35" t="n">
-        <v>48.38</v>
+        <v>59.04</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="M35" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="N35" t="n">
-        <v>6200</v>
+        <v>6142</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>23.26</v>
+        <v>20.19</v>
       </c>
       <c r="C36" t="n">
-        <v>24</v>
+        <v>20.36</v>
       </c>
       <c r="D36" t="n">
-        <v>22.73</v>
+        <v>20.01</v>
       </c>
       <c r="E36" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="F36" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="G36" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>47.55</v>
+        <v>58.19</v>
       </c>
       <c r="I36" t="n">
-        <v>48.93</v>
+        <v>59.14</v>
       </c>
       <c r="J36" t="n">
-        <v>45.68</v>
+        <v>57.54</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="N36" t="n">
-        <v>6220</v>
+        <v>6132</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22.81</v>
+        <v>20.44</v>
       </c>
       <c r="C37" t="n">
-        <v>24</v>
+        <v>20.64</v>
       </c>
       <c r="D37" t="n">
-        <v>21.97</v>
+        <v>20.37</v>
       </c>
       <c r="E37" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G37" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>49.12</v>
+        <v>57.96</v>
       </c>
       <c r="I37" t="n">
-        <v>52.45</v>
+        <v>58.31</v>
       </c>
       <c r="J37" t="n">
-        <v>45.39</v>
+        <v>57.52</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>21.82</v>
+        <v>20.99</v>
       </c>
       <c r="C38" t="n">
-        <v>21.95</v>
+        <v>21.3</v>
       </c>
       <c r="D38" t="n">
-        <v>21.73</v>
+        <v>20.64</v>
       </c>
       <c r="E38" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F38" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="G38" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>52.7</v>
+        <v>55.76</v>
       </c>
       <c r="I38" t="n">
-        <v>52.97</v>
+        <v>57.26</v>
       </c>
       <c r="J38" t="n">
-        <v>52.47</v>
+        <v>54.28</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="N38" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>21.74</v>
+        <v>21.82</v>
       </c>
       <c r="C39" t="n">
-        <v>21.95</v>
+        <v>22.25</v>
       </c>
       <c r="D39" t="n">
-        <v>21.56</v>
+        <v>21.38</v>
       </c>
       <c r="E39" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F39" t="n">
         <v>11.2</v>
       </c>
       <c r="G39" t="n">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="H39" t="n">
-        <v>52.76</v>
+        <v>52.03</v>
       </c>
       <c r="I39" t="n">
-        <v>53.57</v>
+        <v>53.83</v>
       </c>
       <c r="J39" t="n">
-        <v>52.06</v>
+        <v>50.23</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M39" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N39" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>21.42</v>
+        <v>22.61</v>
       </c>
       <c r="C40" t="n">
-        <v>22</v>
+        <v>22.85</v>
       </c>
       <c r="D40" t="n">
-        <v>20.92</v>
+        <v>22.34</v>
       </c>
       <c r="E40" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="F40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G40" t="n">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="H40" t="n">
-        <v>54.49</v>
+        <v>49.28</v>
       </c>
       <c r="I40" t="n">
-        <v>56.38</v>
+        <v>50.37</v>
       </c>
       <c r="J40" t="n">
-        <v>52.2</v>
+        <v>48.38</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N40" t="n">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>21.35</v>
+        <v>23.26</v>
       </c>
       <c r="C41" t="n">
-        <v>22.22</v>
+        <v>24</v>
       </c>
       <c r="D41" t="n">
-        <v>20.87</v>
+        <v>22.73</v>
       </c>
       <c r="E41" t="n">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
       <c r="F41" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="G41" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="H41" t="n">
-        <v>55.07</v>
+        <v>47.55</v>
       </c>
       <c r="I41" t="n">
-        <v>56.71</v>
+        <v>48.93</v>
       </c>
       <c r="J41" t="n">
-        <v>52.16</v>
+        <v>45.68</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="M41" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>21.1</v>
+        <v>22.81</v>
       </c>
       <c r="C42" t="n">
-        <v>21.69</v>
+        <v>24</v>
       </c>
       <c r="D42" t="n">
-        <v>20.51</v>
+        <v>21.97</v>
       </c>
       <c r="E42" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G42" t="n">
-        <v>480</v>
+        <v>373</v>
       </c>
       <c r="H42" t="n">
-        <v>55.96</v>
+        <v>49.12</v>
       </c>
       <c r="I42" t="n">
-        <v>58.01</v>
+        <v>52.45</v>
       </c>
       <c r="J42" t="n">
-        <v>53.81</v>
+        <v>45.39</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="N42" t="n">
-        <v>6210</v>
+        <v>6220</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>20.15</v>
+        <v>21.82</v>
       </c>
       <c r="C43" t="n">
-        <v>20.85</v>
+        <v>21.95</v>
       </c>
       <c r="D43" t="n">
-        <v>19.57</v>
+        <v>21.73</v>
       </c>
       <c r="E43" t="n">
-        <v>12.1</v>
+        <v>11.4</v>
       </c>
       <c r="F43" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="G43" t="n">
-        <v>266</v>
+        <v>146</v>
       </c>
       <c r="H43" t="n">
-        <v>60.77</v>
+        <v>52.7</v>
       </c>
       <c r="I43" t="n">
-        <v>64.81</v>
+        <v>52.97</v>
       </c>
       <c r="J43" t="n">
-        <v>56.73</v>
+        <v>52.47</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="M43" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="N43" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.37</v>
+        <v>21.74</v>
       </c>
       <c r="C44" t="n">
-        <v>19.79</v>
+        <v>21.95</v>
       </c>
       <c r="D44" t="n">
-        <v>18.91</v>
+        <v>21.56</v>
       </c>
       <c r="E44" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="F44" t="n">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
       <c r="G44" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="H44" t="n">
-        <v>65.04000000000001</v>
+        <v>52.76</v>
       </c>
       <c r="I44" t="n">
-        <v>66.98999999999999</v>
+        <v>53.57</v>
       </c>
       <c r="J44" t="n">
-        <v>63.19</v>
+        <v>52.06</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="M44" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="N44" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>18.41</v>
+        <v>21.42</v>
       </c>
       <c r="C45" t="n">
-        <v>18.85</v>
+        <v>22</v>
       </c>
       <c r="D45" t="n">
-        <v>18.05</v>
+        <v>20.92</v>
       </c>
       <c r="E45" t="n">
-        <v>12.6</v>
+        <v>11.6</v>
       </c>
       <c r="F45" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G45" t="n">
-        <v>76</v>
+        <v>218</v>
       </c>
       <c r="H45" t="n">
-        <v>69.37</v>
+        <v>54.49</v>
       </c>
       <c r="I45" t="n">
-        <v>71.67</v>
+        <v>56.38</v>
       </c>
       <c r="J45" t="n">
-        <v>67.22</v>
+        <v>52.2</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.66</v>
+        <v>21.35</v>
       </c>
       <c r="C46" t="n">
-        <v>17.95</v>
+        <v>22.22</v>
       </c>
       <c r="D46" t="n">
-        <v>17.51</v>
+        <v>20.87</v>
       </c>
       <c r="E46" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="F46" t="n">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="G46" t="n">
-        <v>10</v>
+        <v>238</v>
       </c>
       <c r="H46" t="n">
-        <v>73.31</v>
+        <v>55.07</v>
       </c>
       <c r="I46" t="n">
-        <v>74.14</v>
+        <v>56.71</v>
       </c>
       <c r="J46" t="n">
-        <v>72.19</v>
+        <v>52.16</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="N46" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.6</v>
+        <v>21.1</v>
       </c>
       <c r="C47" t="n">
-        <v>17.68</v>
+        <v>21.69</v>
       </c>
       <c r="D47" t="n">
-        <v>17.49</v>
+        <v>20.51</v>
       </c>
       <c r="E47" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F47" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="H47" t="n">
-        <v>72.5</v>
+        <v>55.96</v>
       </c>
       <c r="I47" t="n">
-        <v>73.76000000000001</v>
+        <v>58.01</v>
       </c>
       <c r="J47" t="n">
-        <v>71.78</v>
+        <v>53.81</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>6142</v>
+        <v>6210</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.53</v>
+        <v>20.15</v>
       </c>
       <c r="C48" t="n">
-        <v>17.62</v>
+        <v>20.85</v>
       </c>
       <c r="D48" t="n">
-        <v>17.45</v>
+        <v>19.57</v>
       </c>
       <c r="E48" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F48" t="n">
-        <v>12.2</v>
+        <v>11.6</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="H48" t="n">
-        <v>72.33</v>
+        <v>60.77</v>
       </c>
       <c r="I48" t="n">
-        <v>72.88</v>
+        <v>64.81</v>
       </c>
       <c r="J48" t="n">
-        <v>71.93000000000001</v>
+        <v>56.73</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="N48" t="n">
-        <v>6152</v>
+        <v>6200</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.64</v>
+        <v>19.37</v>
       </c>
       <c r="C49" t="n">
-        <v>17.9</v>
+        <v>19.79</v>
       </c>
       <c r="D49" t="n">
-        <v>17.44</v>
+        <v>18.91</v>
       </c>
       <c r="E49" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F49" t="n">
         <v>12.3</v>
       </c>
-      <c r="F49" t="n">
-        <v>12</v>
-      </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="H49" t="n">
-        <v>71.73999999999999</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>73.59999999999999</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>69.53</v>
+        <v>63.19</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="N49" t="n">
-        <v>6152</v>
-      </c>
-      <c r="O49" t="n">
+        <v>6180</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:00:00</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="C50" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="D50" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="E50" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G50" t="n">
+        <v>76</v>
+      </c>
+      <c r="H50" t="n">
+        <v>69.37</v>
+      </c>
+      <c r="I50" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="J50" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N50" t="n">
+        <v>6170</v>
+      </c>
+      <c r="O50" t="n">
         <v>2.4</v>
       </c>
     </row>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,35 +508,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.52</v>
+        <v>15.04</v>
       </c>
       <c r="C2" t="n">
-        <v>14.56</v>
+        <v>15.1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.47</v>
+        <v>14.99</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="H2" t="n">
-        <v>76.09</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>76.48999999999999</v>
+        <v>79.25</v>
       </c>
       <c r="J2" t="n">
-        <v>75.84999999999999</v>
+        <v>79.11</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -545,148 +545,148 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N2" t="n">
-        <v>6122</v>
+        <v>6142</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.64</v>
+        <v>14.79</v>
       </c>
       <c r="C3" t="n">
-        <v>14.86</v>
+        <v>15.1</v>
       </c>
       <c r="D3" t="n">
-        <v>14.45</v>
+        <v>14.32</v>
       </c>
       <c r="E3" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="F3" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="H3" t="n">
-        <v>79.53</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>82.73999999999999</v>
+        <v>83.36</v>
       </c>
       <c r="J3" t="n">
-        <v>76.79000000000001</v>
+        <v>79.05</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N3" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.07</v>
+        <v>14.05</v>
       </c>
       <c r="C4" t="n">
-        <v>15.23</v>
+        <v>14.26</v>
       </c>
       <c r="D4" t="n">
-        <v>14.92</v>
+        <v>13.8</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="F4" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H4" t="n">
-        <v>77.61</v>
+        <v>85.09</v>
       </c>
       <c r="I4" t="n">
-        <v>78.94</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>76.67</v>
+        <v>84.14</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N4" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.37</v>
+        <v>14.11</v>
       </c>
       <c r="C5" t="n">
-        <v>15.49</v>
+        <v>14.56</v>
       </c>
       <c r="D5" t="n">
-        <v>15.25</v>
+        <v>13.7</v>
       </c>
       <c r="E5" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="F5" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>79.81999999999999</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>80.69</v>
+        <v>87.31</v>
       </c>
       <c r="J5" t="n">
-        <v>78.86</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N5" t="n">
         <v>6132</v>
@@ -696,44 +696,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.65</v>
+        <v>14.64</v>
       </c>
       <c r="C6" t="n">
-        <v>15.77</v>
+        <v>14.86</v>
       </c>
       <c r="D6" t="n">
-        <v>15.48</v>
+        <v>14.45</v>
       </c>
       <c r="E6" t="n">
-        <v>11.8</v>
+        <v>10.9</v>
       </c>
       <c r="F6" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>78.64</v>
+        <v>79.53</v>
       </c>
       <c r="I6" t="n">
-        <v>80.7</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>77.23</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="N6" t="n">
         <v>6132</v>
@@ -743,91 +743,91 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.39</v>
+        <v>15.07</v>
       </c>
       <c r="C7" t="n">
-        <v>15.59</v>
+        <v>15.23</v>
       </c>
       <c r="D7" t="n">
-        <v>15.29</v>
+        <v>14.92</v>
       </c>
       <c r="E7" t="n">
-        <v>12.7</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>12.3</v>
+        <v>10.7</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>84.89</v>
+        <v>77.61</v>
       </c>
       <c r="I7" t="n">
-        <v>87.12</v>
+        <v>78.94</v>
       </c>
       <c r="J7" t="n">
-        <v>81.20999999999999</v>
+        <v>76.67</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>6112</v>
+        <v>6132</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.61</v>
+        <v>15.37</v>
       </c>
       <c r="C8" t="n">
-        <v>16.09</v>
+        <v>15.49</v>
       </c>
       <c r="D8" t="n">
-        <v>15.44</v>
+        <v>15.25</v>
       </c>
       <c r="E8" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="F8" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>84.45</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>86.2</v>
+        <v>80.69</v>
       </c>
       <c r="J8" t="n">
-        <v>79</v>
+        <v>78.86</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
         <v>6132</v>
@@ -837,232 +837,232 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.78</v>
+        <v>15.65</v>
       </c>
       <c r="C9" t="n">
-        <v>17.16</v>
+        <v>15.77</v>
       </c>
       <c r="D9" t="n">
-        <v>16.31</v>
+        <v>15.48</v>
       </c>
       <c r="E9" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="F9" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>73.62</v>
+        <v>78.64</v>
       </c>
       <c r="I9" t="n">
-        <v>76.98999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="J9" t="n">
-        <v>69.84</v>
+        <v>77.23</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="N9" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.55</v>
+        <v>15.39</v>
       </c>
       <c r="C10" t="n">
-        <v>17.8</v>
+        <v>15.59</v>
       </c>
       <c r="D10" t="n">
-        <v>17.2</v>
+        <v>15.29</v>
       </c>
       <c r="E10" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="F10" t="n">
-        <v>11.8</v>
+        <v>12.3</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>71.04000000000001</v>
+        <v>84.89</v>
       </c>
       <c r="I10" t="n">
-        <v>73.81</v>
+        <v>87.12</v>
       </c>
       <c r="J10" t="n">
-        <v>69.28</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="N10" t="n">
-        <v>6142</v>
+        <v>6112</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.63</v>
+        <v>15.61</v>
       </c>
       <c r="C11" t="n">
-        <v>18.08</v>
+        <v>16.09</v>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>15.44</v>
       </c>
       <c r="E11" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>73.43000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="I11" t="n">
-        <v>76.55</v>
+        <v>86.2</v>
       </c>
       <c r="J11" t="n">
-        <v>68.51000000000001</v>
+        <v>79</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="N11" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.46</v>
+        <v>16.78</v>
       </c>
       <c r="C12" t="n">
-        <v>17.67</v>
+        <v>17.16</v>
       </c>
       <c r="D12" t="n">
-        <v>17.22</v>
+        <v>16.31</v>
       </c>
       <c r="E12" t="n">
-        <v>13.2</v>
+        <v>11.9</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11.4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>76.84</v>
+        <v>73.62</v>
       </c>
       <c r="I12" t="n">
-        <v>79.37</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>75.08</v>
+        <v>69.84</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N12" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.43</v>
+        <v>17.55</v>
       </c>
       <c r="C13" t="n">
-        <v>17.62</v>
+        <v>17.8</v>
       </c>
       <c r="D13" t="n">
-        <v>17.17</v>
+        <v>17.2</v>
       </c>
       <c r="E13" t="n">
-        <v>13.6</v>
+        <v>12.1</v>
       </c>
       <c r="F13" t="n">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>79.34</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>82.2</v>
+        <v>73.81</v>
       </c>
       <c r="J13" t="n">
-        <v>77.51000000000001</v>
+        <v>69.28</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="N13" t="n">
         <v>6142</v>
@@ -1072,552 +1072,552 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.89</v>
+        <v>17.63</v>
       </c>
       <c r="C14" t="n">
-        <v>18.13</v>
+        <v>18.08</v>
       </c>
       <c r="D14" t="n">
-        <v>17.76</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="n">
-        <v>13.4</v>
+        <v>12.6</v>
       </c>
       <c r="F14" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>76.29000000000001</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>78.06999999999999</v>
+        <v>76.55</v>
       </c>
       <c r="J14" t="n">
-        <v>74.34999999999999</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="N14" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18.6</v>
+        <v>17.46</v>
       </c>
       <c r="C15" t="n">
-        <v>19.26</v>
+        <v>17.67</v>
       </c>
       <c r="D15" t="n">
-        <v>18.22</v>
+        <v>17.22</v>
       </c>
       <c r="E15" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F15" t="n">
         <v>13</v>
       </c>
-      <c r="F15" t="n">
-        <v>12.5</v>
-      </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>70.7</v>
+        <v>76.84</v>
       </c>
       <c r="I15" t="n">
-        <v>73.79000000000001</v>
+        <v>79.37</v>
       </c>
       <c r="J15" t="n">
-        <v>65.41</v>
+        <v>75.08</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="N15" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20.29</v>
+        <v>17.43</v>
       </c>
       <c r="C16" t="n">
-        <v>21.69</v>
+        <v>17.62</v>
       </c>
       <c r="D16" t="n">
-        <v>19.3</v>
+        <v>17.17</v>
       </c>
       <c r="E16" t="n">
-        <v>11.6</v>
+        <v>13.6</v>
       </c>
       <c r="F16" t="n">
-        <v>10.7</v>
+        <v>13.3</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>58.46</v>
+        <v>79.34</v>
       </c>
       <c r="I16" t="n">
-        <v>64.93000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="J16" t="n">
-        <v>50.01</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22.33</v>
+        <v>17.89</v>
       </c>
       <c r="C17" t="n">
-        <v>22.66</v>
+        <v>18.13</v>
       </c>
       <c r="D17" t="n">
-        <v>21.95</v>
+        <v>17.76</v>
       </c>
       <c r="E17" t="n">
-        <v>9.9</v>
+        <v>13.4</v>
       </c>
       <c r="F17" t="n">
-        <v>9.6</v>
+        <v>13.2</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>46.23</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>48.69</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>44.45</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="N17" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22.97</v>
+        <v>18.6</v>
       </c>
       <c r="C18" t="n">
-        <v>23.49</v>
+        <v>19.26</v>
       </c>
       <c r="D18" t="n">
-        <v>22.63</v>
+        <v>18.22</v>
       </c>
       <c r="E18" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="G18" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>43.28</v>
+        <v>70.7</v>
       </c>
       <c r="I18" t="n">
-        <v>44.43</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>41.95</v>
+        <v>65.41</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>6180</v>
+        <v>6152</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.37</v>
+        <v>20.29</v>
       </c>
       <c r="C19" t="n">
-        <v>23.93</v>
+        <v>21.69</v>
       </c>
       <c r="D19" t="n">
-        <v>23.11</v>
+        <v>19.3</v>
       </c>
       <c r="E19" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="F19" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="G19" t="n">
-        <v>271</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>42.7</v>
+        <v>58.46</v>
       </c>
       <c r="I19" t="n">
-        <v>44.12</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>41.98</v>
+        <v>50.01</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23.27</v>
+        <v>22.33</v>
       </c>
       <c r="C20" t="n">
-        <v>23.64</v>
+        <v>22.66</v>
       </c>
       <c r="D20" t="n">
-        <v>22.89</v>
+        <v>21.95</v>
       </c>
       <c r="E20" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F20" t="n">
         <v>9.6</v>
       </c>
-      <c r="F20" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="G20" t="n">
-        <v>326</v>
+        <v>24</v>
       </c>
       <c r="H20" t="n">
-        <v>42.52</v>
+        <v>46.23</v>
       </c>
       <c r="I20" t="n">
-        <v>43.12</v>
+        <v>48.69</v>
       </c>
       <c r="J20" t="n">
-        <v>41.91</v>
+        <v>44.45</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="N20" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.93</v>
+        <v>22.97</v>
       </c>
       <c r="C21" t="n">
-        <v>23.35</v>
+        <v>23.49</v>
       </c>
       <c r="D21" t="n">
-        <v>22.54</v>
+        <v>22.63</v>
       </c>
       <c r="E21" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="F21" t="n">
         <v>9.4</v>
       </c>
       <c r="G21" t="n">
-        <v>393</v>
+        <v>72</v>
       </c>
       <c r="H21" t="n">
-        <v>43.56</v>
+        <v>43.28</v>
       </c>
       <c r="I21" t="n">
-        <v>44.91</v>
+        <v>44.43</v>
       </c>
       <c r="J21" t="n">
-        <v>42.28</v>
+        <v>41.95</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>1.4</v>
       </c>
       <c r="N21" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.23</v>
+        <v>23.37</v>
       </c>
       <c r="C22" t="n">
-        <v>22.76</v>
+        <v>23.93</v>
       </c>
       <c r="D22" t="n">
-        <v>21.86</v>
+        <v>23.11</v>
       </c>
       <c r="E22" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="G22" t="n">
-        <v>383</v>
+        <v>271</v>
       </c>
       <c r="H22" t="n">
-        <v>45.63</v>
+        <v>42.7</v>
       </c>
       <c r="I22" t="n">
-        <v>47.01</v>
+        <v>44.12</v>
       </c>
       <c r="J22" t="n">
-        <v>44.24</v>
+        <v>41.98</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N22" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21.57</v>
+        <v>23.27</v>
       </c>
       <c r="C23" t="n">
-        <v>22.64</v>
+        <v>23.64</v>
       </c>
       <c r="D23" t="n">
-        <v>20.71</v>
+        <v>22.89</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="F23" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>373</v>
+        <v>326</v>
       </c>
       <c r="H23" t="n">
-        <v>48.34</v>
+        <v>42.52</v>
       </c>
       <c r="I23" t="n">
-        <v>51.45</v>
+        <v>43.12</v>
       </c>
       <c r="J23" t="n">
-        <v>45.03</v>
+        <v>41.91</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N23" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20.3</v>
+        <v>22.93</v>
       </c>
       <c r="C24" t="n">
-        <v>20.76</v>
+        <v>23.35</v>
       </c>
       <c r="D24" t="n">
-        <v>19.87</v>
+        <v>22.54</v>
       </c>
       <c r="E24" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="G24" t="n">
-        <v>231</v>
+        <v>393</v>
       </c>
       <c r="H24" t="n">
-        <v>53.23</v>
+        <v>43.56</v>
       </c>
       <c r="I24" t="n">
-        <v>56.41</v>
+        <v>44.91</v>
       </c>
       <c r="J24" t="n">
-        <v>51.05</v>
+        <v>42.28</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.38</v>
+        <v>22.23</v>
       </c>
       <c r="C25" t="n">
-        <v>19.85</v>
+        <v>22.76</v>
       </c>
       <c r="D25" t="n">
-        <v>18.89</v>
+        <v>21.86</v>
       </c>
       <c r="E25" t="n">
-        <v>11.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>110</v>
+        <v>383</v>
       </c>
       <c r="H25" t="n">
-        <v>61.37</v>
+        <v>45.63</v>
       </c>
       <c r="I25" t="n">
-        <v>65.44</v>
+        <v>47.01</v>
       </c>
       <c r="J25" t="n">
-        <v>57.45</v>
+        <v>44.24</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1626,327 +1626,327 @@
         <v>0.5</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="N25" t="n">
-        <v>6152</v>
+        <v>6180</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18.52</v>
+        <v>21.57</v>
       </c>
       <c r="C26" t="n">
-        <v>18.87</v>
+        <v>22.64</v>
       </c>
       <c r="D26" t="n">
-        <v>18.23</v>
+        <v>20.71</v>
       </c>
       <c r="E26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>34</v>
+        <v>373</v>
       </c>
       <c r="H26" t="n">
-        <v>67.5</v>
+        <v>48.34</v>
       </c>
       <c r="I26" t="n">
-        <v>70.43000000000001</v>
+        <v>51.45</v>
       </c>
       <c r="J26" t="n">
-        <v>65.33</v>
+        <v>45.03</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N26" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.89</v>
+        <v>20.3</v>
       </c>
       <c r="C27" t="n">
-        <v>18.27</v>
+        <v>20.76</v>
       </c>
       <c r="D27" t="n">
-        <v>17.53</v>
+        <v>19.87</v>
       </c>
       <c r="E27" t="n">
-        <v>13.1</v>
+        <v>10.3</v>
       </c>
       <c r="F27" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>231</v>
       </c>
       <c r="H27" t="n">
-        <v>74.15000000000001</v>
+        <v>53.23</v>
       </c>
       <c r="I27" t="n">
-        <v>77.34999999999999</v>
+        <v>56.41</v>
       </c>
       <c r="J27" t="n">
-        <v>70.23999999999999</v>
+        <v>51.05</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N27" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17.34</v>
+        <v>19.38</v>
       </c>
       <c r="C28" t="n">
-        <v>17.48</v>
+        <v>19.85</v>
       </c>
       <c r="D28" t="n">
-        <v>17.19</v>
+        <v>18.89</v>
       </c>
       <c r="E28" t="n">
-        <v>13.3</v>
+        <v>11.6</v>
       </c>
       <c r="F28" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H28" t="n">
-        <v>78.27</v>
+        <v>61.37</v>
       </c>
       <c r="I28" t="n">
-        <v>79.16</v>
+        <v>65.44</v>
       </c>
       <c r="J28" t="n">
-        <v>77.5</v>
+        <v>57.45</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.62</v>
+        <v>18.52</v>
       </c>
       <c r="C29" t="n">
-        <v>17.85</v>
+        <v>18.87</v>
       </c>
       <c r="D29" t="n">
-        <v>17.33</v>
+        <v>18.23</v>
       </c>
       <c r="E29" t="n">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="F29" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H29" t="n">
-        <v>74.13</v>
+        <v>67.5</v>
       </c>
       <c r="I29" t="n">
-        <v>77.06</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>71.3</v>
+        <v>65.33</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.72</v>
+        <v>17.89</v>
       </c>
       <c r="C30" t="n">
-        <v>18.84</v>
+        <v>18.27</v>
       </c>
       <c r="D30" t="n">
-        <v>17.46</v>
+        <v>17.53</v>
       </c>
       <c r="E30" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="F30" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>71.95999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>74.59999999999999</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>65.83</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18.99</v>
+        <v>17.34</v>
       </c>
       <c r="C31" t="n">
-        <v>19.05</v>
+        <v>17.48</v>
       </c>
       <c r="D31" t="n">
-        <v>18.9</v>
+        <v>17.19</v>
       </c>
       <c r="E31" t="n">
-        <v>11.5</v>
+        <v>13.3</v>
       </c>
       <c r="F31" t="n">
-        <v>11.3</v>
+        <v>13.1</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>62.56</v>
+        <v>78.27</v>
       </c>
       <c r="I31" t="n">
-        <v>63.18</v>
+        <v>79.16</v>
       </c>
       <c r="J31" t="n">
-        <v>61.89</v>
+        <v>77.5</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N31" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19.33</v>
+        <v>17.62</v>
       </c>
       <c r="C32" t="n">
-        <v>19.55</v>
+        <v>17.85</v>
       </c>
       <c r="D32" t="n">
-        <v>19.01</v>
+        <v>17.33</v>
       </c>
       <c r="E32" t="n">
-        <v>11.4</v>
+        <v>12.8</v>
       </c>
       <c r="F32" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>60.72</v>
+        <v>74.13</v>
       </c>
       <c r="I32" t="n">
-        <v>62.8</v>
+        <v>77.06</v>
       </c>
       <c r="J32" t="n">
-        <v>59.1</v>
+        <v>71.3</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1955,54 +1955,54 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>19.52</v>
+        <v>17.72</v>
       </c>
       <c r="C33" t="n">
-        <v>19.58</v>
+        <v>18.84</v>
       </c>
       <c r="D33" t="n">
-        <v>19.46</v>
+        <v>17.46</v>
       </c>
       <c r="E33" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F33" t="n">
-        <v>11.2</v>
+        <v>12.1</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>60.01</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>60.64</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>59.58</v>
+        <v>65.83</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>6152</v>
@@ -2012,35 +2012,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.62</v>
+        <v>18.99</v>
       </c>
       <c r="C34" t="n">
-        <v>19.71</v>
+        <v>19.05</v>
       </c>
       <c r="D34" t="n">
-        <v>19.49</v>
+        <v>18.9</v>
       </c>
       <c r="E34" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F34" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>60.63</v>
+        <v>62.56</v>
       </c>
       <c r="I34" t="n">
-        <v>61.71</v>
+        <v>63.18</v>
       </c>
       <c r="J34" t="n">
-        <v>59.73</v>
+        <v>61.89</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2054,136 +2054,134 @@
       <c r="N34" t="n">
         <v>6152</v>
       </c>
-      <c r="O34" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.79</v>
+        <v>19.33</v>
       </c>
       <c r="C35" t="n">
-        <v>20.01</v>
+        <v>19.55</v>
       </c>
       <c r="D35" t="n">
-        <v>19.61</v>
+        <v>19.01</v>
       </c>
       <c r="E35" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F35" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>60.18</v>
+        <v>60.72</v>
       </c>
       <c r="I35" t="n">
-        <v>61.23</v>
+        <v>62.8</v>
       </c>
       <c r="J35" t="n">
-        <v>59.04</v>
+        <v>59.1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="N35" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>20.19</v>
+        <v>19.52</v>
       </c>
       <c r="C36" t="n">
-        <v>20.36</v>
+        <v>19.58</v>
       </c>
       <c r="D36" t="n">
-        <v>20.01</v>
+        <v>19.46</v>
       </c>
       <c r="E36" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F36" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>58.19</v>
+        <v>60.01</v>
       </c>
       <c r="I36" t="n">
-        <v>59.14</v>
+        <v>60.64</v>
       </c>
       <c r="J36" t="n">
-        <v>57.54</v>
+        <v>59.58</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="N36" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>20.44</v>
+        <v>19.62</v>
       </c>
       <c r="C37" t="n">
-        <v>20.64</v>
+        <v>19.71</v>
       </c>
       <c r="D37" t="n">
-        <v>20.37</v>
+        <v>19.49</v>
       </c>
       <c r="E37" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F37" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>57.96</v>
+        <v>60.63</v>
       </c>
       <c r="I37" t="n">
-        <v>58.31</v>
+        <v>61.71</v>
       </c>
       <c r="J37" t="n">
-        <v>57.52</v>
+        <v>59.73</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2195,42 +2193,44 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6170</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
+        <v>6152</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20.99</v>
+        <v>19.79</v>
       </c>
       <c r="C38" t="n">
-        <v>21.3</v>
+        <v>20.01</v>
       </c>
       <c r="D38" t="n">
-        <v>20.64</v>
+        <v>19.61</v>
       </c>
       <c r="E38" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F38" t="n">
         <v>11.6</v>
       </c>
-      <c r="F38" t="n">
-        <v>11.5</v>
-      </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>55.76</v>
+        <v>60.18</v>
       </c>
       <c r="I38" t="n">
-        <v>57.26</v>
+        <v>61.23</v>
       </c>
       <c r="J38" t="n">
-        <v>54.28</v>
+        <v>59.04</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2239,186 +2239,186 @@
         <v>0.2</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N38" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>21.82</v>
+        <v>20.19</v>
       </c>
       <c r="C39" t="n">
-        <v>22.25</v>
+        <v>20.36</v>
       </c>
       <c r="D39" t="n">
-        <v>21.38</v>
+        <v>20.01</v>
       </c>
       <c r="E39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F39" t="n">
         <v>11.4</v>
       </c>
-      <c r="F39" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>52.03</v>
+        <v>58.19</v>
       </c>
       <c r="I39" t="n">
-        <v>53.83</v>
+        <v>59.14</v>
       </c>
       <c r="J39" t="n">
-        <v>50.23</v>
+        <v>57.54</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N39" t="n">
-        <v>6180</v>
+        <v>6132</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>22.61</v>
+        <v>20.44</v>
       </c>
       <c r="C40" t="n">
-        <v>22.85</v>
+        <v>20.64</v>
       </c>
       <c r="D40" t="n">
-        <v>22.34</v>
+        <v>20.37</v>
       </c>
       <c r="E40" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G40" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>49.28</v>
+        <v>57.96</v>
       </c>
       <c r="I40" t="n">
-        <v>50.37</v>
+        <v>58.31</v>
       </c>
       <c r="J40" t="n">
-        <v>48.38</v>
+        <v>57.52</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>23.26</v>
+        <v>20.99</v>
       </c>
       <c r="C41" t="n">
-        <v>24</v>
+        <v>21.3</v>
       </c>
       <c r="D41" t="n">
-        <v>22.73</v>
+        <v>20.64</v>
       </c>
       <c r="E41" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F41" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="G41" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>47.55</v>
+        <v>55.76</v>
       </c>
       <c r="I41" t="n">
-        <v>48.93</v>
+        <v>57.26</v>
       </c>
       <c r="J41" t="n">
-        <v>45.68</v>
+        <v>54.28</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N41" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>22.81</v>
+        <v>21.82</v>
       </c>
       <c r="C42" t="n">
-        <v>24</v>
+        <v>22.25</v>
       </c>
       <c r="D42" t="n">
-        <v>21.97</v>
+        <v>21.38</v>
       </c>
       <c r="E42" t="n">
         <v>11.4</v>
       </c>
       <c r="F42" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="G42" t="n">
-        <v>373</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>49.12</v>
+        <v>52.03</v>
       </c>
       <c r="I42" t="n">
-        <v>52.45</v>
+        <v>53.83</v>
       </c>
       <c r="J42" t="n">
-        <v>45.39</v>
+        <v>50.23</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2427,195 +2427,195 @@
         <v>0.7</v>
       </c>
       <c r="M42" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N42" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>21.82</v>
+        <v>22.61</v>
       </c>
       <c r="C43" t="n">
-        <v>21.95</v>
+        <v>22.85</v>
       </c>
       <c r="D43" t="n">
-        <v>21.73</v>
+        <v>22.34</v>
       </c>
       <c r="E43" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F43" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="G43" t="n">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="H43" t="n">
-        <v>52.7</v>
+        <v>49.28</v>
       </c>
       <c r="I43" t="n">
-        <v>52.97</v>
+        <v>50.37</v>
       </c>
       <c r="J43" t="n">
-        <v>52.47</v>
+        <v>48.38</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="M43" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="N43" t="n">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>21.74</v>
+        <v>23.26</v>
       </c>
       <c r="C44" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>21.56</v>
+        <v>22.73</v>
       </c>
       <c r="E44" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="F44" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="G44" t="n">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="H44" t="n">
-        <v>52.76</v>
+        <v>47.55</v>
       </c>
       <c r="I44" t="n">
-        <v>53.57</v>
+        <v>48.93</v>
       </c>
       <c r="J44" t="n">
-        <v>52.06</v>
+        <v>45.68</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="M44" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21.42</v>
+        <v>22.81</v>
       </c>
       <c r="C45" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D45" t="n">
-        <v>20.92</v>
+        <v>21.97</v>
       </c>
       <c r="E45" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F45" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G45" t="n">
-        <v>218</v>
+        <v>373</v>
       </c>
       <c r="H45" t="n">
-        <v>54.49</v>
+        <v>49.12</v>
       </c>
       <c r="I45" t="n">
-        <v>56.38</v>
+        <v>52.45</v>
       </c>
       <c r="J45" t="n">
-        <v>52.2</v>
+        <v>45.39</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N45" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>21.35</v>
+        <v>21.82</v>
       </c>
       <c r="C46" t="n">
-        <v>22.22</v>
+        <v>21.95</v>
       </c>
       <c r="D46" t="n">
-        <v>20.87</v>
+        <v>21.73</v>
       </c>
       <c r="E46" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F46" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G46" t="n">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="H46" t="n">
-        <v>55.07</v>
+        <v>52.7</v>
       </c>
       <c r="I46" t="n">
-        <v>56.71</v>
+        <v>52.97</v>
       </c>
       <c r="J46" t="n">
-        <v>52.16</v>
+        <v>52.47</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M46" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="N46" t="n">
         <v>6190</v>
@@ -2625,188 +2625,188 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21.1</v>
+        <v>21.74</v>
       </c>
       <c r="C47" t="n">
-        <v>21.69</v>
+        <v>21.95</v>
       </c>
       <c r="D47" t="n">
-        <v>20.51</v>
+        <v>21.56</v>
       </c>
       <c r="E47" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="F47" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G47" t="n">
-        <v>480</v>
+        <v>165</v>
       </c>
       <c r="H47" t="n">
-        <v>55.96</v>
+        <v>52.76</v>
       </c>
       <c r="I47" t="n">
-        <v>58.01</v>
+        <v>53.57</v>
       </c>
       <c r="J47" t="n">
-        <v>53.81</v>
+        <v>52.06</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="N47" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>20.15</v>
+        <v>21.42</v>
       </c>
       <c r="C48" t="n">
-        <v>20.85</v>
+        <v>22</v>
       </c>
       <c r="D48" t="n">
-        <v>19.57</v>
+        <v>20.92</v>
       </c>
       <c r="E48" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="F48" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G48" t="n">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="H48" t="n">
-        <v>60.77</v>
+        <v>54.49</v>
       </c>
       <c r="I48" t="n">
-        <v>64.81</v>
+        <v>56.38</v>
       </c>
       <c r="J48" t="n">
-        <v>56.73</v>
+        <v>52.2</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M48" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>6200</v>
+        <v>6190</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19.37</v>
+        <v>21.35</v>
       </c>
       <c r="C49" t="n">
-        <v>19.79</v>
+        <v>22.22</v>
       </c>
       <c r="D49" t="n">
-        <v>18.91</v>
+        <v>20.87</v>
       </c>
       <c r="E49" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F49" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G49" t="n">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="H49" t="n">
-        <v>65.04000000000001</v>
+        <v>55.07</v>
       </c>
       <c r="I49" t="n">
-        <v>66.98999999999999</v>
+        <v>56.71</v>
       </c>
       <c r="J49" t="n">
-        <v>63.19</v>
+        <v>52.16</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M49" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N49" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>18.41</v>
+        <v>21.1</v>
       </c>
       <c r="C50" t="n">
-        <v>18.85</v>
+        <v>21.69</v>
       </c>
       <c r="D50" t="n">
-        <v>18.05</v>
+        <v>20.51</v>
       </c>
       <c r="E50" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F50" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G50" t="n">
-        <v>76</v>
+        <v>480</v>
       </c>
       <c r="H50" t="n">
-        <v>69.37</v>
+        <v>55.96</v>
       </c>
       <c r="I50" t="n">
-        <v>71.67</v>
+        <v>58.01</v>
       </c>
       <c r="J50" t="n">
-        <v>67.22</v>
+        <v>53.81</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M50" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>6170</v>
+        <v>6210</v>
       </c>
       <c r="O50" t="n">
         <v>2.4</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,176 +508,176 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15.04</v>
+        <v>17.6</v>
       </c>
       <c r="C2" t="n">
-        <v>15.1</v>
+        <v>17.71</v>
       </c>
       <c r="D2" t="n">
-        <v>14.99</v>
+        <v>17.41</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="F2" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="G2" t="n">
-        <v>126</v>
+        <v>206</v>
       </c>
       <c r="H2" t="n">
-        <v>79.18000000000001</v>
+        <v>62.54</v>
       </c>
       <c r="I2" t="n">
-        <v>79.25</v>
+        <v>63.45</v>
       </c>
       <c r="J2" t="n">
-        <v>79.11</v>
+        <v>62.08</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.3</v>
-      </c>
       <c r="N2" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.79</v>
+        <v>16.72</v>
       </c>
       <c r="C3" t="n">
-        <v>15.1</v>
+        <v>17.47</v>
       </c>
       <c r="D3" t="n">
-        <v>14.32</v>
+        <v>16.08</v>
       </c>
       <c r="E3" t="n">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="F3" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="H3" t="n">
-        <v>80.70999999999999</v>
+        <v>67.33</v>
       </c>
       <c r="I3" t="n">
-        <v>83.36</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>79.05</v>
+        <v>63.98</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N3" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.05</v>
+        <v>15.83</v>
       </c>
       <c r="C4" t="n">
-        <v>14.26</v>
+        <v>16.23</v>
       </c>
       <c r="D4" t="n">
-        <v>13.8</v>
+        <v>15.45</v>
       </c>
       <c r="E4" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="F4" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="G4" t="n">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="H4" t="n">
-        <v>85.09</v>
+        <v>72.95</v>
       </c>
       <c r="I4" t="n">
-        <v>86.40000000000001</v>
+        <v>75.03</v>
       </c>
       <c r="J4" t="n">
-        <v>84.14</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="M4" t="n">
         <v>1.4</v>
       </c>
       <c r="N4" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.11</v>
+        <v>15.22</v>
       </c>
       <c r="C5" t="n">
-        <v>14.56</v>
+        <v>15.77</v>
       </c>
       <c r="D5" t="n">
-        <v>13.7</v>
+        <v>14.97</v>
       </c>
       <c r="E5" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="H5" t="n">
-        <v>81.01000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="I5" t="n">
-        <v>87.31</v>
+        <v>79.25</v>
       </c>
       <c r="J5" t="n">
-        <v>75.84999999999999</v>
+        <v>74.45</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -686,148 +686,148 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N5" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.64</v>
+        <v>14.79</v>
       </c>
       <c r="C6" t="n">
-        <v>14.86</v>
+        <v>15.1</v>
       </c>
       <c r="D6" t="n">
-        <v>14.45</v>
+        <v>14.32</v>
       </c>
       <c r="E6" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="F6" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="H6" t="n">
-        <v>79.53</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>82.73999999999999</v>
+        <v>83.36</v>
       </c>
       <c r="J6" t="n">
-        <v>76.79000000000001</v>
+        <v>79.05</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N6" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.07</v>
+        <v>14.05</v>
       </c>
       <c r="C7" t="n">
-        <v>15.23</v>
+        <v>14.26</v>
       </c>
       <c r="D7" t="n">
-        <v>14.92</v>
+        <v>13.8</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="F7" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H7" t="n">
-        <v>77.61</v>
+        <v>85.09</v>
       </c>
       <c r="I7" t="n">
-        <v>78.94</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>76.67</v>
+        <v>84.14</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N7" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.37</v>
+        <v>14.11</v>
       </c>
       <c r="C8" t="n">
-        <v>15.49</v>
+        <v>14.56</v>
       </c>
       <c r="D8" t="n">
-        <v>15.25</v>
+        <v>13.7</v>
       </c>
       <c r="E8" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="F8" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H8" t="n">
-        <v>79.81999999999999</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>80.69</v>
+        <v>87.31</v>
       </c>
       <c r="J8" t="n">
-        <v>78.86</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N8" t="n">
         <v>6132</v>
@@ -837,44 +837,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.65</v>
+        <v>14.64</v>
       </c>
       <c r="C9" t="n">
-        <v>15.77</v>
+        <v>14.86</v>
       </c>
       <c r="D9" t="n">
-        <v>15.48</v>
+        <v>14.45</v>
       </c>
       <c r="E9" t="n">
-        <v>11.8</v>
+        <v>10.9</v>
       </c>
       <c r="F9" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>78.64</v>
+        <v>79.53</v>
       </c>
       <c r="I9" t="n">
-        <v>80.7</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>77.23</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="N9" t="n">
         <v>6132</v>
@@ -884,91 +884,91 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.39</v>
+        <v>15.07</v>
       </c>
       <c r="C10" t="n">
-        <v>15.59</v>
+        <v>15.23</v>
       </c>
       <c r="D10" t="n">
-        <v>15.29</v>
+        <v>14.92</v>
       </c>
       <c r="E10" t="n">
-        <v>12.7</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>12.3</v>
+        <v>10.7</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>84.89</v>
+        <v>77.61</v>
       </c>
       <c r="I10" t="n">
-        <v>87.12</v>
+        <v>78.94</v>
       </c>
       <c r="J10" t="n">
-        <v>81.20999999999999</v>
+        <v>76.67</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>6112</v>
+        <v>6132</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15.61</v>
+        <v>15.37</v>
       </c>
       <c r="C11" t="n">
-        <v>16.09</v>
+        <v>15.49</v>
       </c>
       <c r="D11" t="n">
-        <v>15.44</v>
+        <v>15.25</v>
       </c>
       <c r="E11" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="F11" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>84.45</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>86.2</v>
+        <v>80.69</v>
       </c>
       <c r="J11" t="n">
-        <v>79</v>
+        <v>78.86</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
         <v>6132</v>
@@ -978,232 +978,232 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16.78</v>
+        <v>15.65</v>
       </c>
       <c r="C12" t="n">
-        <v>17.16</v>
+        <v>15.77</v>
       </c>
       <c r="D12" t="n">
-        <v>16.31</v>
+        <v>15.48</v>
       </c>
       <c r="E12" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="F12" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>73.62</v>
+        <v>78.64</v>
       </c>
       <c r="I12" t="n">
-        <v>76.98999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="J12" t="n">
-        <v>69.84</v>
+        <v>77.23</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="N12" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.55</v>
+        <v>15.39</v>
       </c>
       <c r="C13" t="n">
-        <v>17.8</v>
+        <v>15.59</v>
       </c>
       <c r="D13" t="n">
-        <v>17.2</v>
+        <v>15.29</v>
       </c>
       <c r="E13" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="F13" t="n">
-        <v>11.8</v>
+        <v>12.3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>71.04000000000001</v>
+        <v>84.89</v>
       </c>
       <c r="I13" t="n">
-        <v>73.81</v>
+        <v>87.12</v>
       </c>
       <c r="J13" t="n">
-        <v>69.28</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="N13" t="n">
-        <v>6142</v>
+        <v>6112</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.63</v>
+        <v>15.61</v>
       </c>
       <c r="C14" t="n">
-        <v>18.08</v>
+        <v>16.09</v>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>15.44</v>
       </c>
       <c r="E14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>73.43000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="I14" t="n">
-        <v>76.55</v>
+        <v>86.2</v>
       </c>
       <c r="J14" t="n">
-        <v>68.51000000000001</v>
+        <v>79</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="N14" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.46</v>
+        <v>16.78</v>
       </c>
       <c r="C15" t="n">
-        <v>17.67</v>
+        <v>17.16</v>
       </c>
       <c r="D15" t="n">
-        <v>17.22</v>
+        <v>16.31</v>
       </c>
       <c r="E15" t="n">
-        <v>13.2</v>
+        <v>11.9</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>11.4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>76.84</v>
+        <v>73.62</v>
       </c>
       <c r="I15" t="n">
-        <v>79.37</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>75.08</v>
+        <v>69.84</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N15" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.43</v>
+        <v>17.55</v>
       </c>
       <c r="C16" t="n">
-        <v>17.62</v>
+        <v>17.8</v>
       </c>
       <c r="D16" t="n">
-        <v>17.17</v>
+        <v>17.2</v>
       </c>
       <c r="E16" t="n">
-        <v>13.6</v>
+        <v>12.1</v>
       </c>
       <c r="F16" t="n">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>79.34</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>82.2</v>
+        <v>73.81</v>
       </c>
       <c r="J16" t="n">
-        <v>77.51000000000001</v>
+        <v>69.28</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="N16" t="n">
         <v>6142</v>
@@ -1213,552 +1213,552 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.89</v>
+        <v>17.63</v>
       </c>
       <c r="C17" t="n">
-        <v>18.13</v>
+        <v>18.08</v>
       </c>
       <c r="D17" t="n">
-        <v>17.76</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="n">
-        <v>13.4</v>
+        <v>12.6</v>
       </c>
       <c r="F17" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>76.29000000000001</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>78.06999999999999</v>
+        <v>76.55</v>
       </c>
       <c r="J17" t="n">
-        <v>74.34999999999999</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="N17" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18.6</v>
+        <v>17.46</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26</v>
+        <v>17.67</v>
       </c>
       <c r="D18" t="n">
-        <v>18.22</v>
+        <v>17.22</v>
       </c>
       <c r="E18" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F18" t="n">
         <v>13</v>
       </c>
-      <c r="F18" t="n">
-        <v>12.5</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>70.7</v>
+        <v>76.84</v>
       </c>
       <c r="I18" t="n">
-        <v>73.79000000000001</v>
+        <v>79.37</v>
       </c>
       <c r="J18" t="n">
-        <v>65.41</v>
+        <v>75.08</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="N18" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20.29</v>
+        <v>17.43</v>
       </c>
       <c r="C19" t="n">
-        <v>21.69</v>
+        <v>17.62</v>
       </c>
       <c r="D19" t="n">
-        <v>19.3</v>
+        <v>17.17</v>
       </c>
       <c r="E19" t="n">
-        <v>11.6</v>
+        <v>13.6</v>
       </c>
       <c r="F19" t="n">
-        <v>10.7</v>
+        <v>13.3</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>58.46</v>
+        <v>79.34</v>
       </c>
       <c r="I19" t="n">
-        <v>64.93000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="J19" t="n">
-        <v>50.01</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.33</v>
+        <v>17.89</v>
       </c>
       <c r="C20" t="n">
-        <v>22.66</v>
+        <v>18.13</v>
       </c>
       <c r="D20" t="n">
-        <v>21.95</v>
+        <v>17.76</v>
       </c>
       <c r="E20" t="n">
-        <v>9.9</v>
+        <v>13.4</v>
       </c>
       <c r="F20" t="n">
-        <v>9.6</v>
+        <v>13.2</v>
       </c>
       <c r="G20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>46.23</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>48.69</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>44.45</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="N20" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.97</v>
+        <v>18.6</v>
       </c>
       <c r="C21" t="n">
-        <v>23.49</v>
+        <v>19.26</v>
       </c>
       <c r="D21" t="n">
-        <v>22.63</v>
+        <v>18.22</v>
       </c>
       <c r="E21" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="G21" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>43.28</v>
+        <v>70.7</v>
       </c>
       <c r="I21" t="n">
-        <v>44.43</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>41.95</v>
+        <v>65.41</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>6180</v>
+        <v>6152</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23.37</v>
+        <v>20.29</v>
       </c>
       <c r="C22" t="n">
-        <v>23.93</v>
+        <v>21.69</v>
       </c>
       <c r="D22" t="n">
-        <v>23.11</v>
+        <v>19.3</v>
       </c>
       <c r="E22" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="F22" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="G22" t="n">
-        <v>271</v>
+        <v>9</v>
       </c>
       <c r="H22" t="n">
-        <v>42.7</v>
+        <v>58.46</v>
       </c>
       <c r="I22" t="n">
-        <v>44.12</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>41.98</v>
+        <v>50.01</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.27</v>
+        <v>22.33</v>
       </c>
       <c r="C23" t="n">
-        <v>23.64</v>
+        <v>22.66</v>
       </c>
       <c r="D23" t="n">
-        <v>22.89</v>
+        <v>21.95</v>
       </c>
       <c r="E23" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F23" t="n">
         <v>9.6</v>
       </c>
-      <c r="F23" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="G23" t="n">
-        <v>326</v>
+        <v>24</v>
       </c>
       <c r="H23" t="n">
-        <v>42.52</v>
+        <v>46.23</v>
       </c>
       <c r="I23" t="n">
-        <v>43.12</v>
+        <v>48.69</v>
       </c>
       <c r="J23" t="n">
-        <v>41.91</v>
+        <v>44.45</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="N23" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22.93</v>
+        <v>22.97</v>
       </c>
       <c r="C24" t="n">
-        <v>23.35</v>
+        <v>23.49</v>
       </c>
       <c r="D24" t="n">
-        <v>22.54</v>
+        <v>22.63</v>
       </c>
       <c r="E24" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="F24" t="n">
         <v>9.4</v>
       </c>
       <c r="G24" t="n">
-        <v>393</v>
+        <v>72</v>
       </c>
       <c r="H24" t="n">
-        <v>43.56</v>
+        <v>43.28</v>
       </c>
       <c r="I24" t="n">
-        <v>44.91</v>
+        <v>44.43</v>
       </c>
       <c r="J24" t="n">
-        <v>42.28</v>
+        <v>41.95</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>1.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.23</v>
+        <v>23.37</v>
       </c>
       <c r="C25" t="n">
-        <v>22.76</v>
+        <v>23.93</v>
       </c>
       <c r="D25" t="n">
-        <v>21.86</v>
+        <v>23.11</v>
       </c>
       <c r="E25" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="G25" t="n">
-        <v>383</v>
+        <v>271</v>
       </c>
       <c r="H25" t="n">
-        <v>45.63</v>
+        <v>42.7</v>
       </c>
       <c r="I25" t="n">
-        <v>47.01</v>
+        <v>44.12</v>
       </c>
       <c r="J25" t="n">
-        <v>44.24</v>
+        <v>41.98</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N25" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21.57</v>
+        <v>23.27</v>
       </c>
       <c r="C26" t="n">
-        <v>22.64</v>
+        <v>23.64</v>
       </c>
       <c r="D26" t="n">
-        <v>20.71</v>
+        <v>22.89</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="F26" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>373</v>
+        <v>326</v>
       </c>
       <c r="H26" t="n">
-        <v>48.34</v>
+        <v>42.52</v>
       </c>
       <c r="I26" t="n">
-        <v>51.45</v>
+        <v>43.12</v>
       </c>
       <c r="J26" t="n">
-        <v>45.03</v>
+        <v>41.91</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N26" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20.3</v>
+        <v>22.93</v>
       </c>
       <c r="C27" t="n">
-        <v>20.76</v>
+        <v>23.35</v>
       </c>
       <c r="D27" t="n">
-        <v>19.87</v>
+        <v>22.54</v>
       </c>
       <c r="E27" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="G27" t="n">
-        <v>231</v>
+        <v>393</v>
       </c>
       <c r="H27" t="n">
-        <v>53.23</v>
+        <v>43.56</v>
       </c>
       <c r="I27" t="n">
-        <v>56.41</v>
+        <v>44.91</v>
       </c>
       <c r="J27" t="n">
-        <v>51.05</v>
+        <v>42.28</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N27" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.38</v>
+        <v>22.23</v>
       </c>
       <c r="C28" t="n">
-        <v>19.85</v>
+        <v>22.76</v>
       </c>
       <c r="D28" t="n">
-        <v>18.89</v>
+        <v>21.86</v>
       </c>
       <c r="E28" t="n">
-        <v>11.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>110</v>
+        <v>383</v>
       </c>
       <c r="H28" t="n">
-        <v>61.37</v>
+        <v>45.63</v>
       </c>
       <c r="I28" t="n">
-        <v>65.44</v>
+        <v>47.01</v>
       </c>
       <c r="J28" t="n">
-        <v>57.45</v>
+        <v>44.24</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1767,327 +1767,327 @@
         <v>0.5</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="N28" t="n">
-        <v>6152</v>
+        <v>6180</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18.52</v>
+        <v>21.57</v>
       </c>
       <c r="C29" t="n">
-        <v>18.87</v>
+        <v>22.64</v>
       </c>
       <c r="D29" t="n">
-        <v>18.23</v>
+        <v>20.71</v>
       </c>
       <c r="E29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>34</v>
+        <v>373</v>
       </c>
       <c r="H29" t="n">
-        <v>67.5</v>
+        <v>48.34</v>
       </c>
       <c r="I29" t="n">
-        <v>70.43000000000001</v>
+        <v>51.45</v>
       </c>
       <c r="J29" t="n">
-        <v>65.33</v>
+        <v>45.03</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N29" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.89</v>
+        <v>20.3</v>
       </c>
       <c r="C30" t="n">
-        <v>18.27</v>
+        <v>20.76</v>
       </c>
       <c r="D30" t="n">
-        <v>17.53</v>
+        <v>19.87</v>
       </c>
       <c r="E30" t="n">
-        <v>13.1</v>
+        <v>10.3</v>
       </c>
       <c r="F30" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>231</v>
       </c>
       <c r="H30" t="n">
-        <v>74.15000000000001</v>
+        <v>53.23</v>
       </c>
       <c r="I30" t="n">
-        <v>77.34999999999999</v>
+        <v>56.41</v>
       </c>
       <c r="J30" t="n">
-        <v>70.23999999999999</v>
+        <v>51.05</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N30" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.34</v>
+        <v>19.38</v>
       </c>
       <c r="C31" t="n">
-        <v>17.48</v>
+        <v>19.85</v>
       </c>
       <c r="D31" t="n">
-        <v>17.19</v>
+        <v>18.89</v>
       </c>
       <c r="E31" t="n">
-        <v>13.3</v>
+        <v>11.6</v>
       </c>
       <c r="F31" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H31" t="n">
-        <v>78.27</v>
+        <v>61.37</v>
       </c>
       <c r="I31" t="n">
-        <v>79.16</v>
+        <v>65.44</v>
       </c>
       <c r="J31" t="n">
-        <v>77.5</v>
+        <v>57.45</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.62</v>
+        <v>18.52</v>
       </c>
       <c r="C32" t="n">
-        <v>17.85</v>
+        <v>18.87</v>
       </c>
       <c r="D32" t="n">
-        <v>17.33</v>
+        <v>18.23</v>
       </c>
       <c r="E32" t="n">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="F32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H32" t="n">
-        <v>74.13</v>
+        <v>67.5</v>
       </c>
       <c r="I32" t="n">
-        <v>77.06</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>71.3</v>
+        <v>65.33</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.72</v>
+        <v>17.89</v>
       </c>
       <c r="C33" t="n">
-        <v>18.84</v>
+        <v>18.27</v>
       </c>
       <c r="D33" t="n">
-        <v>17.46</v>
+        <v>17.53</v>
       </c>
       <c r="E33" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="F33" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>71.95999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>74.59999999999999</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>65.83</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18.99</v>
+        <v>17.34</v>
       </c>
       <c r="C34" t="n">
-        <v>19.05</v>
+        <v>17.48</v>
       </c>
       <c r="D34" t="n">
-        <v>18.9</v>
+        <v>17.19</v>
       </c>
       <c r="E34" t="n">
-        <v>11.5</v>
+        <v>13.3</v>
       </c>
       <c r="F34" t="n">
-        <v>11.3</v>
+        <v>13.1</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>62.56</v>
+        <v>78.27</v>
       </c>
       <c r="I34" t="n">
-        <v>63.18</v>
+        <v>79.16</v>
       </c>
       <c r="J34" t="n">
-        <v>61.89</v>
+        <v>77.5</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N34" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.33</v>
+        <v>17.62</v>
       </c>
       <c r="C35" t="n">
-        <v>19.55</v>
+        <v>17.85</v>
       </c>
       <c r="D35" t="n">
-        <v>19.01</v>
+        <v>17.33</v>
       </c>
       <c r="E35" t="n">
-        <v>11.4</v>
+        <v>12.8</v>
       </c>
       <c r="F35" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>60.72</v>
+        <v>74.13</v>
       </c>
       <c r="I35" t="n">
-        <v>62.8</v>
+        <v>77.06</v>
       </c>
       <c r="J35" t="n">
-        <v>59.1</v>
+        <v>71.3</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2096,54 +2096,54 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19.52</v>
+        <v>17.72</v>
       </c>
       <c r="C36" t="n">
-        <v>19.58</v>
+        <v>18.84</v>
       </c>
       <c r="D36" t="n">
-        <v>19.46</v>
+        <v>17.46</v>
       </c>
       <c r="E36" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F36" t="n">
-        <v>11.2</v>
+        <v>12.1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>60.01</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>60.64</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>59.58</v>
+        <v>65.83</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>6152</v>
@@ -2153,35 +2153,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.62</v>
+        <v>18.99</v>
       </c>
       <c r="C37" t="n">
-        <v>19.71</v>
+        <v>19.05</v>
       </c>
       <c r="D37" t="n">
-        <v>19.49</v>
+        <v>18.9</v>
       </c>
       <c r="E37" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F37" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>60.63</v>
+        <v>62.56</v>
       </c>
       <c r="I37" t="n">
-        <v>61.71</v>
+        <v>63.18</v>
       </c>
       <c r="J37" t="n">
-        <v>59.73</v>
+        <v>61.89</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2195,136 +2195,134 @@
       <c r="N37" t="n">
         <v>6152</v>
       </c>
-      <c r="O37" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>19.79</v>
+        <v>19.33</v>
       </c>
       <c r="C38" t="n">
-        <v>20.01</v>
+        <v>19.55</v>
       </c>
       <c r="D38" t="n">
-        <v>19.61</v>
+        <v>19.01</v>
       </c>
       <c r="E38" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F38" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>60.18</v>
+        <v>60.72</v>
       </c>
       <c r="I38" t="n">
-        <v>61.23</v>
+        <v>62.8</v>
       </c>
       <c r="J38" t="n">
-        <v>59.04</v>
+        <v>59.1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="N38" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20.19</v>
+        <v>19.52</v>
       </c>
       <c r="C39" t="n">
-        <v>20.36</v>
+        <v>19.58</v>
       </c>
       <c r="D39" t="n">
-        <v>20.01</v>
+        <v>19.46</v>
       </c>
       <c r="E39" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F39" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>58.19</v>
+        <v>60.01</v>
       </c>
       <c r="I39" t="n">
-        <v>59.14</v>
+        <v>60.64</v>
       </c>
       <c r="J39" t="n">
-        <v>57.54</v>
+        <v>59.58</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="N39" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20.44</v>
+        <v>19.62</v>
       </c>
       <c r="C40" t="n">
-        <v>20.64</v>
+        <v>19.71</v>
       </c>
       <c r="D40" t="n">
-        <v>20.37</v>
+        <v>19.49</v>
       </c>
       <c r="E40" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F40" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>57.96</v>
+        <v>60.63</v>
       </c>
       <c r="I40" t="n">
-        <v>58.31</v>
+        <v>61.71</v>
       </c>
       <c r="J40" t="n">
-        <v>57.52</v>
+        <v>59.73</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2336,42 +2334,44 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6170</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>6152</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20.99</v>
+        <v>19.79</v>
       </c>
       <c r="C41" t="n">
-        <v>21.3</v>
+        <v>20.01</v>
       </c>
       <c r="D41" t="n">
-        <v>20.64</v>
+        <v>19.61</v>
       </c>
       <c r="E41" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F41" t="n">
         <v>11.6</v>
       </c>
-      <c r="F41" t="n">
-        <v>11.5</v>
-      </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>55.76</v>
+        <v>60.18</v>
       </c>
       <c r="I41" t="n">
-        <v>57.26</v>
+        <v>61.23</v>
       </c>
       <c r="J41" t="n">
-        <v>54.28</v>
+        <v>59.04</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2380,186 +2380,186 @@
         <v>0.2</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N41" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>21.82</v>
+        <v>20.19</v>
       </c>
       <c r="C42" t="n">
-        <v>22.25</v>
+        <v>20.36</v>
       </c>
       <c r="D42" t="n">
-        <v>21.38</v>
+        <v>20.01</v>
       </c>
       <c r="E42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F42" t="n">
         <v>11.4</v>
       </c>
-      <c r="F42" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>52.03</v>
+        <v>58.19</v>
       </c>
       <c r="I42" t="n">
-        <v>53.83</v>
+        <v>59.14</v>
       </c>
       <c r="J42" t="n">
-        <v>50.23</v>
+        <v>57.54</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N42" t="n">
-        <v>6180</v>
+        <v>6132</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22.61</v>
+        <v>20.44</v>
       </c>
       <c r="C43" t="n">
-        <v>22.85</v>
+        <v>20.64</v>
       </c>
       <c r="D43" t="n">
-        <v>22.34</v>
+        <v>20.37</v>
       </c>
       <c r="E43" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G43" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>49.28</v>
+        <v>57.96</v>
       </c>
       <c r="I43" t="n">
-        <v>50.37</v>
+        <v>58.31</v>
       </c>
       <c r="J43" t="n">
-        <v>48.38</v>
+        <v>57.52</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23.26</v>
+        <v>20.99</v>
       </c>
       <c r="C44" t="n">
-        <v>24</v>
+        <v>21.3</v>
       </c>
       <c r="D44" t="n">
-        <v>22.73</v>
+        <v>20.64</v>
       </c>
       <c r="E44" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F44" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="G44" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>47.55</v>
+        <v>55.76</v>
       </c>
       <c r="I44" t="n">
-        <v>48.93</v>
+        <v>57.26</v>
       </c>
       <c r="J44" t="n">
-        <v>45.68</v>
+        <v>54.28</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N44" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>22.81</v>
+        <v>21.82</v>
       </c>
       <c r="C45" t="n">
-        <v>24</v>
+        <v>22.25</v>
       </c>
       <c r="D45" t="n">
-        <v>21.97</v>
+        <v>21.38</v>
       </c>
       <c r="E45" t="n">
         <v>11.4</v>
       </c>
       <c r="F45" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="G45" t="n">
-        <v>373</v>
+        <v>6</v>
       </c>
       <c r="H45" t="n">
-        <v>49.12</v>
+        <v>52.03</v>
       </c>
       <c r="I45" t="n">
-        <v>52.45</v>
+        <v>53.83</v>
       </c>
       <c r="J45" t="n">
-        <v>45.39</v>
+        <v>50.23</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2568,195 +2568,195 @@
         <v>0.7</v>
       </c>
       <c r="M45" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N45" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>21.82</v>
+        <v>22.61</v>
       </c>
       <c r="C46" t="n">
-        <v>21.95</v>
+        <v>22.85</v>
       </c>
       <c r="D46" t="n">
-        <v>21.73</v>
+        <v>22.34</v>
       </c>
       <c r="E46" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F46" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="G46" t="n">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="H46" t="n">
-        <v>52.7</v>
+        <v>49.28</v>
       </c>
       <c r="I46" t="n">
-        <v>52.97</v>
+        <v>50.37</v>
       </c>
       <c r="J46" t="n">
-        <v>52.47</v>
+        <v>48.38</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="M46" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="N46" t="n">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21.74</v>
+        <v>23.26</v>
       </c>
       <c r="C47" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D47" t="n">
-        <v>21.56</v>
+        <v>22.73</v>
       </c>
       <c r="E47" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="F47" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="G47" t="n">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="H47" t="n">
-        <v>52.76</v>
+        <v>47.55</v>
       </c>
       <c r="I47" t="n">
-        <v>53.57</v>
+        <v>48.93</v>
       </c>
       <c r="J47" t="n">
-        <v>52.06</v>
+        <v>45.68</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="M47" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.42</v>
+        <v>22.81</v>
       </c>
       <c r="C48" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D48" t="n">
-        <v>20.92</v>
+        <v>21.97</v>
       </c>
       <c r="E48" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F48" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G48" t="n">
-        <v>218</v>
+        <v>373</v>
       </c>
       <c r="H48" t="n">
-        <v>54.49</v>
+        <v>49.12</v>
       </c>
       <c r="I48" t="n">
-        <v>56.38</v>
+        <v>52.45</v>
       </c>
       <c r="J48" t="n">
-        <v>52.2</v>
+        <v>45.39</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N48" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>21.35</v>
+        <v>21.82</v>
       </c>
       <c r="C49" t="n">
-        <v>22.22</v>
+        <v>21.95</v>
       </c>
       <c r="D49" t="n">
-        <v>20.87</v>
+        <v>21.73</v>
       </c>
       <c r="E49" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F49" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G49" t="n">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="H49" t="n">
-        <v>55.07</v>
+        <v>52.7</v>
       </c>
       <c r="I49" t="n">
-        <v>56.71</v>
+        <v>52.97</v>
       </c>
       <c r="J49" t="n">
-        <v>52.16</v>
+        <v>52.47</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M49" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="N49" t="n">
         <v>6190</v>
@@ -2766,47 +2766,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>21.1</v>
+        <v>21.74</v>
       </c>
       <c r="C50" t="n">
-        <v>21.69</v>
+        <v>21.95</v>
       </c>
       <c r="D50" t="n">
-        <v>20.51</v>
+        <v>21.56</v>
       </c>
       <c r="E50" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="F50" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G50" t="n">
-        <v>480</v>
+        <v>165</v>
       </c>
       <c r="H50" t="n">
-        <v>55.96</v>
+        <v>52.76</v>
       </c>
       <c r="I50" t="n">
-        <v>58.01</v>
+        <v>53.57</v>
       </c>
       <c r="J50" t="n">
-        <v>53.81</v>
+        <v>52.06</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="N50" t="n">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="O50" t="n">
         <v>2.4</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,82 +508,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.6</v>
+        <v>17.81</v>
       </c>
       <c r="C2" t="n">
-        <v>17.71</v>
+        <v>18.11</v>
       </c>
       <c r="D2" t="n">
-        <v>17.41</v>
+        <v>17.56</v>
       </c>
       <c r="E2" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="F2" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="G2" t="n">
-        <v>206</v>
+        <v>85</v>
       </c>
       <c r="H2" t="n">
-        <v>62.54</v>
+        <v>63.74</v>
       </c>
       <c r="I2" t="n">
-        <v>63.45</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>62.08</v>
+        <v>63.46</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N2" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.72</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>17.47</v>
+        <v>18.2</v>
       </c>
       <c r="D3" t="n">
-        <v>16.08</v>
+        <v>17.79</v>
       </c>
       <c r="E3" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="F3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="G3" t="n">
-        <v>260</v>
+        <v>164</v>
       </c>
       <c r="H3" t="n">
-        <v>67.33</v>
+        <v>62.96</v>
       </c>
       <c r="I3" t="n">
-        <v>70.81999999999999</v>
+        <v>64.08</v>
       </c>
       <c r="J3" t="n">
-        <v>63.98</v>
+        <v>61.81</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -595,230 +595,230 @@
         <v>1.3</v>
       </c>
       <c r="N3" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.83</v>
+        <v>18.15</v>
       </c>
       <c r="C4" t="n">
-        <v>16.23</v>
+        <v>18.5</v>
       </c>
       <c r="D4" t="n">
-        <v>15.45</v>
+        <v>17.92</v>
       </c>
       <c r="E4" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="F4" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>173</v>
+        <v>250</v>
       </c>
       <c r="H4" t="n">
-        <v>72.95</v>
+        <v>60.86</v>
       </c>
       <c r="I4" t="n">
-        <v>75.03</v>
+        <v>62.23</v>
       </c>
       <c r="J4" t="n">
-        <v>69.84999999999999</v>
+        <v>59.51</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.22</v>
+        <v>17.71</v>
       </c>
       <c r="C5" t="n">
-        <v>15.77</v>
+        <v>18.05</v>
       </c>
       <c r="D5" t="n">
-        <v>14.97</v>
+        <v>17.31</v>
       </c>
       <c r="E5" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="F5" t="n">
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="G5" t="n">
-        <v>158</v>
+        <v>239</v>
       </c>
       <c r="H5" t="n">
-        <v>77.61</v>
+        <v>61.59</v>
       </c>
       <c r="I5" t="n">
-        <v>79.25</v>
+        <v>63.45</v>
       </c>
       <c r="J5" t="n">
-        <v>74.45</v>
+        <v>59.82</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="N5" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.79</v>
+        <v>16.72</v>
       </c>
       <c r="C6" t="n">
-        <v>15.1</v>
+        <v>17.47</v>
       </c>
       <c r="D6" t="n">
-        <v>14.32</v>
+        <v>16.08</v>
       </c>
       <c r="E6" t="n">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="F6" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="H6" t="n">
-        <v>80.70999999999999</v>
+        <v>67.33</v>
       </c>
       <c r="I6" t="n">
-        <v>83.36</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>79.05</v>
+        <v>63.98</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N6" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.05</v>
+        <v>15.83</v>
       </c>
       <c r="C7" t="n">
-        <v>14.26</v>
+        <v>16.23</v>
       </c>
       <c r="D7" t="n">
-        <v>13.8</v>
+        <v>15.45</v>
       </c>
       <c r="E7" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="F7" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="G7" t="n">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="H7" t="n">
-        <v>85.09</v>
+        <v>72.95</v>
       </c>
       <c r="I7" t="n">
-        <v>86.40000000000001</v>
+        <v>75.03</v>
       </c>
       <c r="J7" t="n">
-        <v>84.14</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="M7" t="n">
         <v>1.4</v>
       </c>
       <c r="N7" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.11</v>
+        <v>15.22</v>
       </c>
       <c r="C8" t="n">
-        <v>14.56</v>
+        <v>15.77</v>
       </c>
       <c r="D8" t="n">
-        <v>13.7</v>
+        <v>14.97</v>
       </c>
       <c r="E8" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="G8" t="n">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="H8" t="n">
-        <v>81.01000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="I8" t="n">
-        <v>87.31</v>
+        <v>79.25</v>
       </c>
       <c r="J8" t="n">
-        <v>75.84999999999999</v>
+        <v>74.45</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -827,148 +827,148 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N8" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.64</v>
+        <v>14.79</v>
       </c>
       <c r="C9" t="n">
-        <v>14.86</v>
+        <v>15.1</v>
       </c>
       <c r="D9" t="n">
-        <v>14.45</v>
+        <v>14.32</v>
       </c>
       <c r="E9" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="F9" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="H9" t="n">
-        <v>79.53</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>82.73999999999999</v>
+        <v>83.36</v>
       </c>
       <c r="J9" t="n">
-        <v>76.79000000000001</v>
+        <v>79.05</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N9" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.07</v>
+        <v>14.05</v>
       </c>
       <c r="C10" t="n">
-        <v>15.23</v>
+        <v>14.26</v>
       </c>
       <c r="D10" t="n">
-        <v>14.92</v>
+        <v>13.8</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="F10" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H10" t="n">
-        <v>77.61</v>
+        <v>85.09</v>
       </c>
       <c r="I10" t="n">
-        <v>78.94</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>76.67</v>
+        <v>84.14</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N10" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15.37</v>
+        <v>14.11</v>
       </c>
       <c r="C11" t="n">
-        <v>15.49</v>
+        <v>14.56</v>
       </c>
       <c r="D11" t="n">
-        <v>15.25</v>
+        <v>13.7</v>
       </c>
       <c r="E11" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="F11" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H11" t="n">
-        <v>79.81999999999999</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>80.69</v>
+        <v>87.31</v>
       </c>
       <c r="J11" t="n">
-        <v>78.86</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N11" t="n">
         <v>6132</v>
@@ -978,44 +978,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.65</v>
+        <v>14.64</v>
       </c>
       <c r="C12" t="n">
-        <v>15.77</v>
+        <v>14.86</v>
       </c>
       <c r="D12" t="n">
-        <v>15.48</v>
+        <v>14.45</v>
       </c>
       <c r="E12" t="n">
-        <v>11.8</v>
+        <v>10.9</v>
       </c>
       <c r="F12" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>78.64</v>
+        <v>79.53</v>
       </c>
       <c r="I12" t="n">
-        <v>80.7</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>77.23</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="N12" t="n">
         <v>6132</v>
@@ -1025,91 +1025,91 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.39</v>
+        <v>15.07</v>
       </c>
       <c r="C13" t="n">
-        <v>15.59</v>
+        <v>15.23</v>
       </c>
       <c r="D13" t="n">
-        <v>15.29</v>
+        <v>14.92</v>
       </c>
       <c r="E13" t="n">
-        <v>12.7</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>12.3</v>
+        <v>10.7</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>84.89</v>
+        <v>77.61</v>
       </c>
       <c r="I13" t="n">
-        <v>87.12</v>
+        <v>78.94</v>
       </c>
       <c r="J13" t="n">
-        <v>81.20999999999999</v>
+        <v>76.67</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>6112</v>
+        <v>6132</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.61</v>
+        <v>15.37</v>
       </c>
       <c r="C14" t="n">
-        <v>16.09</v>
+        <v>15.49</v>
       </c>
       <c r="D14" t="n">
-        <v>15.44</v>
+        <v>15.25</v>
       </c>
       <c r="E14" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="F14" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>84.45</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>86.2</v>
+        <v>80.69</v>
       </c>
       <c r="J14" t="n">
-        <v>79</v>
+        <v>78.86</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
         <v>6132</v>
@@ -1119,232 +1119,232 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.78</v>
+        <v>15.65</v>
       </c>
       <c r="C15" t="n">
-        <v>17.16</v>
+        <v>15.77</v>
       </c>
       <c r="D15" t="n">
-        <v>16.31</v>
+        <v>15.48</v>
       </c>
       <c r="E15" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="F15" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>73.62</v>
+        <v>78.64</v>
       </c>
       <c r="I15" t="n">
-        <v>76.98999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="J15" t="n">
-        <v>69.84</v>
+        <v>77.23</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="N15" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.55</v>
+        <v>15.39</v>
       </c>
       <c r="C16" t="n">
-        <v>17.8</v>
+        <v>15.59</v>
       </c>
       <c r="D16" t="n">
-        <v>17.2</v>
+        <v>15.29</v>
       </c>
       <c r="E16" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="F16" t="n">
-        <v>11.8</v>
+        <v>12.3</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>71.04000000000001</v>
+        <v>84.89</v>
       </c>
       <c r="I16" t="n">
-        <v>73.81</v>
+        <v>87.12</v>
       </c>
       <c r="J16" t="n">
-        <v>69.28</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="M16" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="N16" t="n">
-        <v>6142</v>
+        <v>6112</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.63</v>
+        <v>15.61</v>
       </c>
       <c r="C17" t="n">
-        <v>18.08</v>
+        <v>16.09</v>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>15.44</v>
       </c>
       <c r="E17" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>73.43000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="I17" t="n">
-        <v>76.55</v>
+        <v>86.2</v>
       </c>
       <c r="J17" t="n">
-        <v>68.51000000000001</v>
+        <v>79</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M17" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="N17" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.46</v>
+        <v>16.78</v>
       </c>
       <c r="C18" t="n">
-        <v>17.67</v>
+        <v>17.16</v>
       </c>
       <c r="D18" t="n">
-        <v>17.22</v>
+        <v>16.31</v>
       </c>
       <c r="E18" t="n">
-        <v>13.2</v>
+        <v>11.9</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>11.4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>76.84</v>
+        <v>73.62</v>
       </c>
       <c r="I18" t="n">
-        <v>79.37</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>75.08</v>
+        <v>69.84</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N18" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.43</v>
+        <v>17.55</v>
       </c>
       <c r="C19" t="n">
-        <v>17.62</v>
+        <v>17.8</v>
       </c>
       <c r="D19" t="n">
-        <v>17.17</v>
+        <v>17.2</v>
       </c>
       <c r="E19" t="n">
-        <v>13.6</v>
+        <v>12.1</v>
       </c>
       <c r="F19" t="n">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>79.34</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>82.2</v>
+        <v>73.81</v>
       </c>
       <c r="J19" t="n">
-        <v>77.51000000000001</v>
+        <v>69.28</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="N19" t="n">
         <v>6142</v>
@@ -1354,552 +1354,552 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.89</v>
+        <v>17.63</v>
       </c>
       <c r="C20" t="n">
-        <v>18.13</v>
+        <v>18.08</v>
       </c>
       <c r="D20" t="n">
-        <v>17.76</v>
+        <v>17.4</v>
       </c>
       <c r="E20" t="n">
-        <v>13.4</v>
+        <v>12.6</v>
       </c>
       <c r="F20" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>76.29000000000001</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>78.06999999999999</v>
+        <v>76.55</v>
       </c>
       <c r="J20" t="n">
-        <v>74.34999999999999</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="N20" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.6</v>
+        <v>17.46</v>
       </c>
       <c r="C21" t="n">
-        <v>19.26</v>
+        <v>17.67</v>
       </c>
       <c r="D21" t="n">
-        <v>18.22</v>
+        <v>17.22</v>
       </c>
       <c r="E21" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F21" t="n">
         <v>13</v>
       </c>
-      <c r="F21" t="n">
-        <v>12.5</v>
-      </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>70.7</v>
+        <v>76.84</v>
       </c>
       <c r="I21" t="n">
-        <v>73.79000000000001</v>
+        <v>79.37</v>
       </c>
       <c r="J21" t="n">
-        <v>65.41</v>
+        <v>75.08</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="N21" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20.29</v>
+        <v>17.43</v>
       </c>
       <c r="C22" t="n">
-        <v>21.69</v>
+        <v>17.62</v>
       </c>
       <c r="D22" t="n">
-        <v>19.3</v>
+        <v>17.17</v>
       </c>
       <c r="E22" t="n">
-        <v>11.6</v>
+        <v>13.6</v>
       </c>
       <c r="F22" t="n">
-        <v>10.7</v>
+        <v>13.3</v>
       </c>
       <c r="G22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>58.46</v>
+        <v>79.34</v>
       </c>
       <c r="I22" t="n">
-        <v>64.93000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="J22" t="n">
-        <v>50.01</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22.33</v>
+        <v>17.89</v>
       </c>
       <c r="C23" t="n">
-        <v>22.66</v>
+        <v>18.13</v>
       </c>
       <c r="D23" t="n">
-        <v>21.95</v>
+        <v>17.76</v>
       </c>
       <c r="E23" t="n">
-        <v>9.9</v>
+        <v>13.4</v>
       </c>
       <c r="F23" t="n">
-        <v>9.6</v>
+        <v>13.2</v>
       </c>
       <c r="G23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>46.23</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>48.69</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>44.45</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="N23" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22.97</v>
+        <v>18.6</v>
       </c>
       <c r="C24" t="n">
-        <v>23.49</v>
+        <v>19.26</v>
       </c>
       <c r="D24" t="n">
-        <v>22.63</v>
+        <v>18.22</v>
       </c>
       <c r="E24" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="F24" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="G24" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>43.28</v>
+        <v>70.7</v>
       </c>
       <c r="I24" t="n">
-        <v>44.43</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>41.95</v>
+        <v>65.41</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>6180</v>
+        <v>6152</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>23.37</v>
+        <v>20.29</v>
       </c>
       <c r="C25" t="n">
-        <v>23.93</v>
+        <v>21.69</v>
       </c>
       <c r="D25" t="n">
-        <v>23.11</v>
+        <v>19.3</v>
       </c>
       <c r="E25" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="F25" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="G25" t="n">
-        <v>271</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>42.7</v>
+        <v>58.46</v>
       </c>
       <c r="I25" t="n">
-        <v>44.12</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>41.98</v>
+        <v>50.01</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23.27</v>
+        <v>22.33</v>
       </c>
       <c r="C26" t="n">
-        <v>23.64</v>
+        <v>22.66</v>
       </c>
       <c r="D26" t="n">
-        <v>22.89</v>
+        <v>21.95</v>
       </c>
       <c r="E26" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F26" t="n">
         <v>9.6</v>
       </c>
-      <c r="F26" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="G26" t="n">
-        <v>326</v>
+        <v>24</v>
       </c>
       <c r="H26" t="n">
-        <v>42.52</v>
+        <v>46.23</v>
       </c>
       <c r="I26" t="n">
-        <v>43.12</v>
+        <v>48.69</v>
       </c>
       <c r="J26" t="n">
-        <v>41.91</v>
+        <v>44.45</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="N26" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22.93</v>
+        <v>22.97</v>
       </c>
       <c r="C27" t="n">
-        <v>23.35</v>
+        <v>23.49</v>
       </c>
       <c r="D27" t="n">
-        <v>22.54</v>
+        <v>22.63</v>
       </c>
       <c r="E27" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="F27" t="n">
         <v>9.4</v>
       </c>
       <c r="G27" t="n">
-        <v>393</v>
+        <v>72</v>
       </c>
       <c r="H27" t="n">
-        <v>43.56</v>
+        <v>43.28</v>
       </c>
       <c r="I27" t="n">
-        <v>44.91</v>
+        <v>44.43</v>
       </c>
       <c r="J27" t="n">
-        <v>42.28</v>
+        <v>41.95</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>1.4</v>
       </c>
       <c r="N27" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22.23</v>
+        <v>23.37</v>
       </c>
       <c r="C28" t="n">
-        <v>22.76</v>
+        <v>23.93</v>
       </c>
       <c r="D28" t="n">
-        <v>21.86</v>
+        <v>23.11</v>
       </c>
       <c r="E28" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="G28" t="n">
-        <v>383</v>
+        <v>271</v>
       </c>
       <c r="H28" t="n">
-        <v>45.63</v>
+        <v>42.7</v>
       </c>
       <c r="I28" t="n">
-        <v>47.01</v>
+        <v>44.12</v>
       </c>
       <c r="J28" t="n">
-        <v>44.24</v>
+        <v>41.98</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N28" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21.57</v>
+        <v>23.27</v>
       </c>
       <c r="C29" t="n">
-        <v>22.64</v>
+        <v>23.64</v>
       </c>
       <c r="D29" t="n">
-        <v>20.71</v>
+        <v>22.89</v>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="F29" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>373</v>
+        <v>326</v>
       </c>
       <c r="H29" t="n">
-        <v>48.34</v>
+        <v>42.52</v>
       </c>
       <c r="I29" t="n">
-        <v>51.45</v>
+        <v>43.12</v>
       </c>
       <c r="J29" t="n">
-        <v>45.03</v>
+        <v>41.91</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N29" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20.3</v>
+        <v>22.93</v>
       </c>
       <c r="C30" t="n">
-        <v>20.76</v>
+        <v>23.35</v>
       </c>
       <c r="D30" t="n">
-        <v>19.87</v>
+        <v>22.54</v>
       </c>
       <c r="E30" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="G30" t="n">
-        <v>231</v>
+        <v>393</v>
       </c>
       <c r="H30" t="n">
-        <v>53.23</v>
+        <v>43.56</v>
       </c>
       <c r="I30" t="n">
-        <v>56.41</v>
+        <v>44.91</v>
       </c>
       <c r="J30" t="n">
-        <v>51.05</v>
+        <v>42.28</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N30" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.38</v>
+        <v>22.23</v>
       </c>
       <c r="C31" t="n">
-        <v>19.85</v>
+        <v>22.76</v>
       </c>
       <c r="D31" t="n">
-        <v>18.89</v>
+        <v>21.86</v>
       </c>
       <c r="E31" t="n">
-        <v>11.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>110</v>
+        <v>383</v>
       </c>
       <c r="H31" t="n">
-        <v>61.37</v>
+        <v>45.63</v>
       </c>
       <c r="I31" t="n">
-        <v>65.44</v>
+        <v>47.01</v>
       </c>
       <c r="J31" t="n">
-        <v>57.45</v>
+        <v>44.24</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1908,327 +1908,327 @@
         <v>0.5</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="N31" t="n">
-        <v>6152</v>
+        <v>6180</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18.52</v>
+        <v>21.57</v>
       </c>
       <c r="C32" t="n">
-        <v>18.87</v>
+        <v>22.64</v>
       </c>
       <c r="D32" t="n">
-        <v>18.23</v>
+        <v>20.71</v>
       </c>
       <c r="E32" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>34</v>
+        <v>373</v>
       </c>
       <c r="H32" t="n">
-        <v>67.5</v>
+        <v>48.34</v>
       </c>
       <c r="I32" t="n">
-        <v>70.43000000000001</v>
+        <v>51.45</v>
       </c>
       <c r="J32" t="n">
-        <v>65.33</v>
+        <v>45.03</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N32" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.89</v>
+        <v>20.3</v>
       </c>
       <c r="C33" t="n">
-        <v>18.27</v>
+        <v>20.76</v>
       </c>
       <c r="D33" t="n">
-        <v>17.53</v>
+        <v>19.87</v>
       </c>
       <c r="E33" t="n">
-        <v>13.1</v>
+        <v>10.3</v>
       </c>
       <c r="F33" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>231</v>
       </c>
       <c r="H33" t="n">
-        <v>74.15000000000001</v>
+        <v>53.23</v>
       </c>
       <c r="I33" t="n">
-        <v>77.34999999999999</v>
+        <v>56.41</v>
       </c>
       <c r="J33" t="n">
-        <v>70.23999999999999</v>
+        <v>51.05</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N33" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.34</v>
+        <v>19.38</v>
       </c>
       <c r="C34" t="n">
-        <v>17.48</v>
+        <v>19.85</v>
       </c>
       <c r="D34" t="n">
-        <v>17.19</v>
+        <v>18.89</v>
       </c>
       <c r="E34" t="n">
-        <v>13.3</v>
+        <v>11.6</v>
       </c>
       <c r="F34" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H34" t="n">
-        <v>78.27</v>
+        <v>61.37</v>
       </c>
       <c r="I34" t="n">
-        <v>79.16</v>
+        <v>65.44</v>
       </c>
       <c r="J34" t="n">
-        <v>77.5</v>
+        <v>57.45</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.62</v>
+        <v>18.52</v>
       </c>
       <c r="C35" t="n">
-        <v>17.85</v>
+        <v>18.87</v>
       </c>
       <c r="D35" t="n">
-        <v>17.33</v>
+        <v>18.23</v>
       </c>
       <c r="E35" t="n">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="F35" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>74.13</v>
+        <v>67.5</v>
       </c>
       <c r="I35" t="n">
-        <v>77.06</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>71.3</v>
+        <v>65.33</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.72</v>
+        <v>17.89</v>
       </c>
       <c r="C36" t="n">
-        <v>18.84</v>
+        <v>18.27</v>
       </c>
       <c r="D36" t="n">
-        <v>17.46</v>
+        <v>17.53</v>
       </c>
       <c r="E36" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="F36" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H36" t="n">
-        <v>71.95999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>74.59999999999999</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>65.83</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18.99</v>
+        <v>17.34</v>
       </c>
       <c r="C37" t="n">
-        <v>19.05</v>
+        <v>17.48</v>
       </c>
       <c r="D37" t="n">
-        <v>18.9</v>
+        <v>17.19</v>
       </c>
       <c r="E37" t="n">
-        <v>11.5</v>
+        <v>13.3</v>
       </c>
       <c r="F37" t="n">
-        <v>11.3</v>
+        <v>13.1</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>62.56</v>
+        <v>78.27</v>
       </c>
       <c r="I37" t="n">
-        <v>63.18</v>
+        <v>79.16</v>
       </c>
       <c r="J37" t="n">
-        <v>61.89</v>
+        <v>77.5</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N37" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>19.33</v>
+        <v>17.62</v>
       </c>
       <c r="C38" t="n">
-        <v>19.55</v>
+        <v>17.85</v>
       </c>
       <c r="D38" t="n">
-        <v>19.01</v>
+        <v>17.33</v>
       </c>
       <c r="E38" t="n">
-        <v>11.4</v>
+        <v>12.8</v>
       </c>
       <c r="F38" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>60.72</v>
+        <v>74.13</v>
       </c>
       <c r="I38" t="n">
-        <v>62.8</v>
+        <v>77.06</v>
       </c>
       <c r="J38" t="n">
-        <v>59.1</v>
+        <v>71.3</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2237,54 +2237,54 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>19.52</v>
+        <v>17.72</v>
       </c>
       <c r="C39" t="n">
-        <v>19.58</v>
+        <v>18.84</v>
       </c>
       <c r="D39" t="n">
-        <v>19.46</v>
+        <v>17.46</v>
       </c>
       <c r="E39" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F39" t="n">
-        <v>11.2</v>
+        <v>12.1</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>60.01</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>60.64</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>59.58</v>
+        <v>65.83</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>6152</v>
@@ -2294,35 +2294,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19.62</v>
+        <v>18.99</v>
       </c>
       <c r="C40" t="n">
-        <v>19.71</v>
+        <v>19.05</v>
       </c>
       <c r="D40" t="n">
-        <v>19.49</v>
+        <v>18.9</v>
       </c>
       <c r="E40" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F40" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>60.63</v>
+        <v>62.56</v>
       </c>
       <c r="I40" t="n">
-        <v>61.71</v>
+        <v>63.18</v>
       </c>
       <c r="J40" t="n">
-        <v>59.73</v>
+        <v>61.89</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2336,136 +2336,134 @@
       <c r="N40" t="n">
         <v>6152</v>
       </c>
-      <c r="O40" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>19.79</v>
+        <v>19.33</v>
       </c>
       <c r="C41" t="n">
-        <v>20.01</v>
+        <v>19.55</v>
       </c>
       <c r="D41" t="n">
-        <v>19.61</v>
+        <v>19.01</v>
       </c>
       <c r="E41" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F41" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>60.18</v>
+        <v>60.72</v>
       </c>
       <c r="I41" t="n">
-        <v>61.23</v>
+        <v>62.8</v>
       </c>
       <c r="J41" t="n">
-        <v>59.04</v>
+        <v>59.1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="N41" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>20.19</v>
+        <v>19.52</v>
       </c>
       <c r="C42" t="n">
-        <v>20.36</v>
+        <v>19.58</v>
       </c>
       <c r="D42" t="n">
-        <v>20.01</v>
+        <v>19.46</v>
       </c>
       <c r="E42" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F42" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>58.19</v>
+        <v>60.01</v>
       </c>
       <c r="I42" t="n">
-        <v>59.14</v>
+        <v>60.64</v>
       </c>
       <c r="J42" t="n">
-        <v>57.54</v>
+        <v>59.58</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="N42" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>20.44</v>
+        <v>19.62</v>
       </c>
       <c r="C43" t="n">
-        <v>20.64</v>
+        <v>19.71</v>
       </c>
       <c r="D43" t="n">
-        <v>20.37</v>
+        <v>19.49</v>
       </c>
       <c r="E43" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F43" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>57.96</v>
+        <v>60.63</v>
       </c>
       <c r="I43" t="n">
-        <v>58.31</v>
+        <v>61.71</v>
       </c>
       <c r="J43" t="n">
-        <v>57.52</v>
+        <v>59.73</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2477,42 +2475,44 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>6170</v>
-      </c>
-      <c r="O43" t="inlineStr"/>
+        <v>6152</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20.99</v>
+        <v>19.79</v>
       </c>
       <c r="C44" t="n">
-        <v>21.3</v>
+        <v>20.01</v>
       </c>
       <c r="D44" t="n">
-        <v>20.64</v>
+        <v>19.61</v>
       </c>
       <c r="E44" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F44" t="n">
         <v>11.6</v>
       </c>
-      <c r="F44" t="n">
-        <v>11.5</v>
-      </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>55.76</v>
+        <v>60.18</v>
       </c>
       <c r="I44" t="n">
-        <v>57.26</v>
+        <v>61.23</v>
       </c>
       <c r="J44" t="n">
-        <v>54.28</v>
+        <v>59.04</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2521,186 +2521,186 @@
         <v>0.2</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N44" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21.82</v>
+        <v>20.19</v>
       </c>
       <c r="C45" t="n">
-        <v>22.25</v>
+        <v>20.36</v>
       </c>
       <c r="D45" t="n">
-        <v>21.38</v>
+        <v>20.01</v>
       </c>
       <c r="E45" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F45" t="n">
         <v>11.4</v>
       </c>
-      <c r="F45" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>52.03</v>
+        <v>58.19</v>
       </c>
       <c r="I45" t="n">
-        <v>53.83</v>
+        <v>59.14</v>
       </c>
       <c r="J45" t="n">
-        <v>50.23</v>
+        <v>57.54</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N45" t="n">
-        <v>6180</v>
+        <v>6132</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22.61</v>
+        <v>20.44</v>
       </c>
       <c r="C46" t="n">
-        <v>22.85</v>
+        <v>20.64</v>
       </c>
       <c r="D46" t="n">
-        <v>22.34</v>
+        <v>20.37</v>
       </c>
       <c r="E46" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="F46" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G46" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>49.28</v>
+        <v>57.96</v>
       </c>
       <c r="I46" t="n">
-        <v>50.37</v>
+        <v>58.31</v>
       </c>
       <c r="J46" t="n">
-        <v>48.38</v>
+        <v>57.52</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.26</v>
+        <v>20.99</v>
       </c>
       <c r="C47" t="n">
-        <v>24</v>
+        <v>21.3</v>
       </c>
       <c r="D47" t="n">
-        <v>22.73</v>
+        <v>20.64</v>
       </c>
       <c r="E47" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F47" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>47.55</v>
+        <v>55.76</v>
       </c>
       <c r="I47" t="n">
-        <v>48.93</v>
+        <v>57.26</v>
       </c>
       <c r="J47" t="n">
-        <v>45.68</v>
+        <v>54.28</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N47" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.81</v>
+        <v>21.82</v>
       </c>
       <c r="C48" t="n">
-        <v>24</v>
+        <v>22.25</v>
       </c>
       <c r="D48" t="n">
-        <v>21.97</v>
+        <v>21.38</v>
       </c>
       <c r="E48" t="n">
         <v>11.4</v>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="G48" t="n">
-        <v>373</v>
+        <v>6</v>
       </c>
       <c r="H48" t="n">
-        <v>49.12</v>
+        <v>52.03</v>
       </c>
       <c r="I48" t="n">
-        <v>52.45</v>
+        <v>53.83</v>
       </c>
       <c r="J48" t="n">
-        <v>45.39</v>
+        <v>50.23</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2709,104 +2709,104 @@
         <v>0.7</v>
       </c>
       <c r="M48" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>21.82</v>
+        <v>22.61</v>
       </c>
       <c r="C49" t="n">
-        <v>21.95</v>
+        <v>22.85</v>
       </c>
       <c r="D49" t="n">
-        <v>21.73</v>
+        <v>22.34</v>
       </c>
       <c r="E49" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F49" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="G49" t="n">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="H49" t="n">
-        <v>52.7</v>
+        <v>49.28</v>
       </c>
       <c r="I49" t="n">
-        <v>52.97</v>
+        <v>50.37</v>
       </c>
       <c r="J49" t="n">
-        <v>52.47</v>
+        <v>48.38</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="M49" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="N49" t="n">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>21.74</v>
+        <v>23.26</v>
       </c>
       <c r="C50" t="n">
-        <v>21.95</v>
+        <v>24</v>
       </c>
       <c r="D50" t="n">
-        <v>21.56</v>
+        <v>22.73</v>
       </c>
       <c r="E50" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="F50" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="G50" t="n">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="H50" t="n">
-        <v>52.76</v>
+        <v>47.55</v>
       </c>
       <c r="I50" t="n">
-        <v>53.57</v>
+        <v>48.93</v>
       </c>
       <c r="J50" t="n">
-        <v>52.06</v>
+        <v>45.68</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="M50" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O50" t="n">
         <v>2.4</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,138 +508,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.81</v>
+        <v>17.03</v>
       </c>
       <c r="C2" t="n">
-        <v>18.11</v>
+        <v>17.08</v>
       </c>
       <c r="D2" t="n">
-        <v>17.56</v>
+        <v>16.98</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="F2" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="G2" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>63.74</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>64.15000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="J2" t="n">
-        <v>63.46</v>
+        <v>68.62</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="N2" t="n">
-        <v>6152</v>
+        <v>6122</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>17.26</v>
       </c>
       <c r="C3" t="n">
-        <v>18.2</v>
+        <v>17.41</v>
       </c>
       <c r="D3" t="n">
-        <v>17.79</v>
+        <v>17.13</v>
       </c>
       <c r="E3" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="F3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>62.96</v>
+        <v>65.97</v>
       </c>
       <c r="I3" t="n">
-        <v>64.08</v>
+        <v>68.3</v>
       </c>
       <c r="J3" t="n">
-        <v>61.81</v>
+        <v>62.44</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N3" t="n">
-        <v>6162</v>
+        <v>6132</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.15</v>
+        <v>17.57</v>
       </c>
       <c r="C4" t="n">
-        <v>18.5</v>
+        <v>18.11</v>
       </c>
       <c r="D4" t="n">
-        <v>17.92</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="H4" t="n">
-        <v>60.86</v>
+        <v>63.38</v>
       </c>
       <c r="I4" t="n">
-        <v>62.23</v>
+        <v>64.3</v>
       </c>
       <c r="J4" t="n">
-        <v>59.51</v>
+        <v>61.77</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="N4" t="n">
         <v>6142</v>
@@ -649,317 +649,317 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.71</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>18.05</v>
+        <v>18.2</v>
       </c>
       <c r="D5" t="n">
-        <v>17.31</v>
+        <v>17.79</v>
       </c>
       <c r="E5" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="F5" t="n">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="G5" t="n">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="H5" t="n">
-        <v>61.59</v>
+        <v>62.96</v>
       </c>
       <c r="I5" t="n">
-        <v>63.45</v>
+        <v>64.08</v>
       </c>
       <c r="J5" t="n">
-        <v>59.82</v>
+        <v>61.81</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N5" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.72</v>
+        <v>18.15</v>
       </c>
       <c r="C6" t="n">
-        <v>17.47</v>
+        <v>18.5</v>
       </c>
       <c r="D6" t="n">
-        <v>16.08</v>
+        <v>17.92</v>
       </c>
       <c r="E6" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="H6" t="n">
-        <v>67.33</v>
+        <v>60.86</v>
       </c>
       <c r="I6" t="n">
-        <v>70.81999999999999</v>
+        <v>62.23</v>
       </c>
       <c r="J6" t="n">
-        <v>63.98</v>
+        <v>59.51</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.83</v>
+        <v>17.71</v>
       </c>
       <c r="C7" t="n">
-        <v>16.23</v>
+        <v>18.05</v>
       </c>
       <c r="D7" t="n">
-        <v>15.45</v>
+        <v>17.31</v>
       </c>
       <c r="E7" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="F7" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="G7" t="n">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="H7" t="n">
-        <v>72.95</v>
+        <v>61.59</v>
       </c>
       <c r="I7" t="n">
-        <v>75.03</v>
+        <v>63.45</v>
       </c>
       <c r="J7" t="n">
-        <v>69.84999999999999</v>
+        <v>59.82</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.22</v>
+        <v>16.72</v>
       </c>
       <c r="C8" t="n">
-        <v>15.77</v>
+        <v>17.47</v>
       </c>
       <c r="D8" t="n">
-        <v>14.97</v>
+        <v>16.08</v>
       </c>
       <c r="E8" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="F8" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>158</v>
+        <v>260</v>
       </c>
       <c r="H8" t="n">
-        <v>77.61</v>
+        <v>67.33</v>
       </c>
       <c r="I8" t="n">
-        <v>79.25</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>74.45</v>
+        <v>63.98</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N8" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.79</v>
+        <v>15.83</v>
       </c>
       <c r="C9" t="n">
-        <v>15.1</v>
+        <v>16.23</v>
       </c>
       <c r="D9" t="n">
-        <v>14.32</v>
+        <v>15.45</v>
       </c>
       <c r="E9" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="F9" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="G9" t="n">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="H9" t="n">
-        <v>80.70999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="I9" t="n">
-        <v>83.36</v>
+        <v>75.03</v>
       </c>
       <c r="J9" t="n">
-        <v>79.05</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M9" t="n">
         <v>1.4</v>
       </c>
       <c r="N9" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.05</v>
+        <v>15.22</v>
       </c>
       <c r="C10" t="n">
-        <v>14.26</v>
+        <v>15.77</v>
       </c>
       <c r="D10" t="n">
-        <v>13.8</v>
+        <v>14.97</v>
       </c>
       <c r="E10" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F10" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="G10" t="n">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="H10" t="n">
-        <v>85.09</v>
+        <v>77.61</v>
       </c>
       <c r="I10" t="n">
-        <v>86.40000000000001</v>
+        <v>79.25</v>
       </c>
       <c r="J10" t="n">
-        <v>84.14</v>
+        <v>74.45</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>1.4</v>
       </c>
       <c r="N10" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14.11</v>
+        <v>14.79</v>
       </c>
       <c r="C11" t="n">
-        <v>14.56</v>
+        <v>15.1</v>
       </c>
       <c r="D11" t="n">
-        <v>13.7</v>
+        <v>14.32</v>
       </c>
       <c r="E11" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="G11" t="n">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="H11" t="n">
-        <v>81.01000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>87.31</v>
+        <v>83.36</v>
       </c>
       <c r="J11" t="n">
-        <v>75.84999999999999</v>
+        <v>79.05</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -968,101 +968,101 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N11" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.64</v>
+        <v>14.05</v>
       </c>
       <c r="C12" t="n">
-        <v>14.86</v>
+        <v>14.26</v>
       </c>
       <c r="D12" t="n">
-        <v>14.45</v>
+        <v>13.8</v>
       </c>
       <c r="E12" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="F12" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="H12" t="n">
-        <v>79.53</v>
+        <v>85.09</v>
       </c>
       <c r="I12" t="n">
-        <v>82.73999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>76.79000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N12" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.07</v>
+        <v>14.11</v>
       </c>
       <c r="C13" t="n">
-        <v>15.23</v>
+        <v>14.56</v>
       </c>
       <c r="D13" t="n">
-        <v>14.92</v>
+        <v>13.7</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="F13" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H13" t="n">
-        <v>77.61</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>78.94</v>
+        <v>87.31</v>
       </c>
       <c r="J13" t="n">
-        <v>76.67</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N13" t="n">
         <v>6132</v>
@@ -1072,44 +1072,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.37</v>
+        <v>14.64</v>
       </c>
       <c r="C14" t="n">
-        <v>15.49</v>
+        <v>14.86</v>
       </c>
       <c r="D14" t="n">
-        <v>15.25</v>
+        <v>14.45</v>
       </c>
       <c r="E14" t="n">
-        <v>11.8</v>
+        <v>10.9</v>
       </c>
       <c r="F14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>79.81999999999999</v>
+        <v>79.53</v>
       </c>
       <c r="I14" t="n">
-        <v>80.69</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>78.86</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N14" t="n">
         <v>6132</v>
@@ -1119,44 +1119,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.65</v>
+        <v>15.07</v>
       </c>
       <c r="C15" t="n">
-        <v>15.77</v>
+        <v>15.23</v>
       </c>
       <c r="D15" t="n">
-        <v>15.48</v>
+        <v>14.92</v>
       </c>
       <c r="E15" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>11.6</v>
+        <v>10.7</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>78.64</v>
+        <v>77.61</v>
       </c>
       <c r="I15" t="n">
-        <v>80.7</v>
+        <v>78.94</v>
       </c>
       <c r="J15" t="n">
-        <v>77.23</v>
+        <v>76.67</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>6132</v>
@@ -1166,91 +1166,91 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.39</v>
+        <v>15.37</v>
       </c>
       <c r="C16" t="n">
-        <v>15.59</v>
+        <v>15.49</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29</v>
+        <v>15.25</v>
       </c>
       <c r="E16" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="F16" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>84.89</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>87.12</v>
+        <v>80.69</v>
       </c>
       <c r="J16" t="n">
-        <v>81.20999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>6112</v>
+        <v>6132</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.61</v>
+        <v>15.65</v>
       </c>
       <c r="C17" t="n">
-        <v>16.09</v>
+        <v>15.77</v>
       </c>
       <c r="D17" t="n">
-        <v>15.44</v>
+        <v>15.48</v>
       </c>
       <c r="E17" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="F17" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>84.45</v>
+        <v>78.64</v>
       </c>
       <c r="I17" t="n">
-        <v>86.2</v>
+        <v>80.7</v>
       </c>
       <c r="J17" t="n">
-        <v>79</v>
+        <v>77.23</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="N17" t="n">
         <v>6132</v>
@@ -1260,138 +1260,138 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.78</v>
+        <v>15.39</v>
       </c>
       <c r="C18" t="n">
-        <v>17.16</v>
+        <v>15.59</v>
       </c>
       <c r="D18" t="n">
-        <v>16.31</v>
+        <v>15.29</v>
       </c>
       <c r="E18" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="F18" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>73.62</v>
+        <v>84.89</v>
       </c>
       <c r="I18" t="n">
-        <v>76.98999999999999</v>
+        <v>87.12</v>
       </c>
       <c r="J18" t="n">
-        <v>69.84</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="N18" t="n">
-        <v>6122</v>
+        <v>6112</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.55</v>
+        <v>15.61</v>
       </c>
       <c r="C19" t="n">
-        <v>17.8</v>
+        <v>16.09</v>
       </c>
       <c r="D19" t="n">
-        <v>17.2</v>
+        <v>15.44</v>
       </c>
       <c r="E19" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="F19" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>71.04000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="I19" t="n">
-        <v>73.81</v>
+        <v>86.2</v>
       </c>
       <c r="J19" t="n">
-        <v>69.28</v>
+        <v>79</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="N19" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.63</v>
+        <v>16.78</v>
       </c>
       <c r="C20" t="n">
-        <v>18.08</v>
+        <v>17.16</v>
       </c>
       <c r="D20" t="n">
-        <v>17.4</v>
+        <v>16.31</v>
       </c>
       <c r="E20" t="n">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>73.43000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="I20" t="n">
-        <v>76.55</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>68.51000000000001</v>
+        <v>69.84</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="N20" t="n">
         <v>6122</v>
@@ -1401,82 +1401,82 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.46</v>
+        <v>17.55</v>
       </c>
       <c r="C21" t="n">
-        <v>17.67</v>
+        <v>17.8</v>
       </c>
       <c r="D21" t="n">
-        <v>17.22</v>
+        <v>17.2</v>
       </c>
       <c r="E21" t="n">
-        <v>13.2</v>
+        <v>12.1</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>76.84</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>79.37</v>
+        <v>73.81</v>
       </c>
       <c r="J21" t="n">
-        <v>75.08</v>
+        <v>69.28</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="N21" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.43</v>
+        <v>17.63</v>
       </c>
       <c r="C22" t="n">
-        <v>17.62</v>
+        <v>18.08</v>
       </c>
       <c r="D22" t="n">
-        <v>17.17</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="F22" t="n">
-        <v>13.3</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>79.34</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>82.2</v>
+        <v>76.55</v>
       </c>
       <c r="J22" t="n">
-        <v>77.51000000000001</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1485,383 +1485,383 @@
         <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="N22" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.89</v>
+        <v>17.46</v>
       </c>
       <c r="C23" t="n">
-        <v>18.13</v>
+        <v>17.67</v>
       </c>
       <c r="D23" t="n">
-        <v>17.76</v>
+        <v>17.22</v>
       </c>
       <c r="E23" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="F23" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>76.29000000000001</v>
+        <v>76.84</v>
       </c>
       <c r="I23" t="n">
-        <v>78.06999999999999</v>
+        <v>79.37</v>
       </c>
       <c r="J23" t="n">
-        <v>74.34999999999999</v>
+        <v>75.08</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="N23" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18.6</v>
+        <v>17.43</v>
       </c>
       <c r="C24" t="n">
-        <v>19.26</v>
+        <v>17.62</v>
       </c>
       <c r="D24" t="n">
-        <v>18.22</v>
+        <v>17.17</v>
       </c>
       <c r="E24" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="F24" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>70.7</v>
+        <v>79.34</v>
       </c>
       <c r="I24" t="n">
-        <v>73.79000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="J24" t="n">
-        <v>65.41</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20.29</v>
+        <v>17.89</v>
       </c>
       <c r="C25" t="n">
-        <v>21.69</v>
+        <v>18.13</v>
       </c>
       <c r="D25" t="n">
-        <v>19.3</v>
+        <v>17.76</v>
       </c>
       <c r="E25" t="n">
-        <v>11.6</v>
+        <v>13.4</v>
       </c>
       <c r="F25" t="n">
-        <v>10.7</v>
+        <v>13.2</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>58.46</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>64.93000000000001</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>50.01</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="N25" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22.33</v>
+        <v>18.6</v>
       </c>
       <c r="C26" t="n">
-        <v>22.66</v>
+        <v>19.26</v>
       </c>
       <c r="D26" t="n">
-        <v>21.95</v>
+        <v>18.22</v>
       </c>
       <c r="E26" t="n">
-        <v>9.9</v>
+        <v>13</v>
       </c>
       <c r="F26" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="G26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>46.23</v>
+        <v>70.7</v>
       </c>
       <c r="I26" t="n">
-        <v>48.69</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>44.45</v>
+        <v>65.41</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22.97</v>
+        <v>20.29</v>
       </c>
       <c r="C27" t="n">
-        <v>23.49</v>
+        <v>21.69</v>
       </c>
       <c r="D27" t="n">
-        <v>22.63</v>
+        <v>19.3</v>
       </c>
       <c r="E27" t="n">
-        <v>9.5</v>
+        <v>11.6</v>
       </c>
       <c r="F27" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="G27" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>43.28</v>
+        <v>58.46</v>
       </c>
       <c r="I27" t="n">
-        <v>44.43</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>41.95</v>
+        <v>50.01</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="M27" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23.37</v>
+        <v>22.33</v>
       </c>
       <c r="C28" t="n">
-        <v>23.93</v>
+        <v>22.66</v>
       </c>
       <c r="D28" t="n">
-        <v>23.11</v>
+        <v>21.95</v>
       </c>
       <c r="E28" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="F28" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="G28" t="n">
-        <v>271</v>
+        <v>24</v>
       </c>
       <c r="H28" t="n">
-        <v>42.7</v>
+        <v>46.23</v>
       </c>
       <c r="I28" t="n">
-        <v>44.12</v>
+        <v>48.69</v>
       </c>
       <c r="J28" t="n">
-        <v>41.98</v>
+        <v>44.45</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="N28" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23.27</v>
+        <v>22.97</v>
       </c>
       <c r="C29" t="n">
-        <v>23.64</v>
+        <v>23.49</v>
       </c>
       <c r="D29" t="n">
-        <v>22.89</v>
+        <v>22.63</v>
       </c>
       <c r="E29" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F29" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G29" t="n">
-        <v>326</v>
+        <v>72</v>
       </c>
       <c r="H29" t="n">
-        <v>42.52</v>
+        <v>43.28</v>
       </c>
       <c r="I29" t="n">
-        <v>43.12</v>
+        <v>44.43</v>
       </c>
       <c r="J29" t="n">
-        <v>41.91</v>
+        <v>41.95</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N29" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.93</v>
+        <v>23.37</v>
       </c>
       <c r="C30" t="n">
-        <v>23.35</v>
+        <v>23.93</v>
       </c>
       <c r="D30" t="n">
-        <v>22.54</v>
+        <v>23.11</v>
       </c>
       <c r="E30" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="G30" t="n">
-        <v>393</v>
+        <v>271</v>
       </c>
       <c r="H30" t="n">
-        <v>43.56</v>
+        <v>42.7</v>
       </c>
       <c r="I30" t="n">
-        <v>44.91</v>
+        <v>44.12</v>
       </c>
       <c r="J30" t="n">
-        <v>42.28</v>
+        <v>41.98</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N30" t="n">
         <v>6190</v>
@@ -1871,35 +1871,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22.23</v>
+        <v>23.27</v>
       </c>
       <c r="C31" t="n">
-        <v>22.76</v>
+        <v>23.64</v>
       </c>
       <c r="D31" t="n">
-        <v>21.86</v>
+        <v>22.89</v>
       </c>
       <c r="E31" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="F31" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="H31" t="n">
-        <v>45.63</v>
+        <v>42.52</v>
       </c>
       <c r="I31" t="n">
-        <v>47.01</v>
+        <v>43.12</v>
       </c>
       <c r="J31" t="n">
-        <v>44.24</v>
+        <v>41.91</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1908,336 +1908,336 @@
         <v>0.5</v>
       </c>
       <c r="M31" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="N31" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21.57</v>
+        <v>22.93</v>
       </c>
       <c r="C32" t="n">
-        <v>22.64</v>
+        <v>23.35</v>
       </c>
       <c r="D32" t="n">
-        <v>20.71</v>
+        <v>22.54</v>
       </c>
       <c r="E32" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G32" t="n">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="H32" t="n">
-        <v>48.34</v>
+        <v>43.56</v>
       </c>
       <c r="I32" t="n">
-        <v>51.45</v>
+        <v>44.91</v>
       </c>
       <c r="J32" t="n">
-        <v>45.03</v>
+        <v>42.28</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N32" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.3</v>
+        <v>22.23</v>
       </c>
       <c r="C33" t="n">
-        <v>20.76</v>
+        <v>22.76</v>
       </c>
       <c r="D33" t="n">
-        <v>19.87</v>
+        <v>21.86</v>
       </c>
       <c r="E33" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>231</v>
+        <v>383</v>
       </c>
       <c r="H33" t="n">
-        <v>53.23</v>
+        <v>45.63</v>
       </c>
       <c r="I33" t="n">
-        <v>56.41</v>
+        <v>47.01</v>
       </c>
       <c r="J33" t="n">
-        <v>51.05</v>
+        <v>44.24</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="N33" t="n">
-        <v>6170</v>
+        <v>6180</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.38</v>
+        <v>21.57</v>
       </c>
       <c r="C34" t="n">
-        <v>19.85</v>
+        <v>22.64</v>
       </c>
       <c r="D34" t="n">
-        <v>18.89</v>
+        <v>20.71</v>
       </c>
       <c r="E34" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>110</v>
+        <v>373</v>
       </c>
       <c r="H34" t="n">
-        <v>61.37</v>
+        <v>48.34</v>
       </c>
       <c r="I34" t="n">
-        <v>65.44</v>
+        <v>51.45</v>
       </c>
       <c r="J34" t="n">
-        <v>57.45</v>
+        <v>45.03</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="N34" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>18.52</v>
+        <v>20.3</v>
       </c>
       <c r="C35" t="n">
-        <v>18.87</v>
+        <v>20.76</v>
       </c>
       <c r="D35" t="n">
-        <v>18.23</v>
+        <v>19.87</v>
       </c>
       <c r="E35" t="n">
-        <v>12.2</v>
+        <v>10.3</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G35" t="n">
-        <v>34</v>
+        <v>231</v>
       </c>
       <c r="H35" t="n">
-        <v>67.5</v>
+        <v>53.23</v>
       </c>
       <c r="I35" t="n">
-        <v>70.43000000000001</v>
+        <v>56.41</v>
       </c>
       <c r="J35" t="n">
-        <v>65.33</v>
+        <v>51.05</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N35" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.89</v>
+        <v>19.38</v>
       </c>
       <c r="C36" t="n">
-        <v>18.27</v>
+        <v>19.85</v>
       </c>
       <c r="D36" t="n">
-        <v>17.53</v>
+        <v>18.89</v>
       </c>
       <c r="E36" t="n">
-        <v>13.1</v>
+        <v>11.6</v>
       </c>
       <c r="F36" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="G36" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="H36" t="n">
-        <v>74.15000000000001</v>
+        <v>61.37</v>
       </c>
       <c r="I36" t="n">
-        <v>77.34999999999999</v>
+        <v>65.44</v>
       </c>
       <c r="J36" t="n">
-        <v>70.23999999999999</v>
+        <v>57.45</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.34</v>
+        <v>18.52</v>
       </c>
       <c r="C37" t="n">
-        <v>17.48</v>
+        <v>18.87</v>
       </c>
       <c r="D37" t="n">
-        <v>17.19</v>
+        <v>18.23</v>
       </c>
       <c r="E37" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="F37" t="n">
-        <v>13.1</v>
+        <v>12</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H37" t="n">
-        <v>78.27</v>
+        <v>67.5</v>
       </c>
       <c r="I37" t="n">
-        <v>79.16</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>77.5</v>
+        <v>65.33</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.62</v>
+        <v>17.89</v>
       </c>
       <c r="C38" t="n">
-        <v>17.85</v>
+        <v>18.27</v>
       </c>
       <c r="D38" t="n">
-        <v>17.33</v>
+        <v>17.53</v>
       </c>
       <c r="E38" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="F38" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H38" t="n">
-        <v>74.13</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>77.06</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>71.3</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
         <v>6142</v>
@@ -2247,82 +2247,82 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.72</v>
+        <v>17.34</v>
       </c>
       <c r="C39" t="n">
-        <v>18.84</v>
+        <v>17.48</v>
       </c>
       <c r="D39" t="n">
-        <v>17.46</v>
+        <v>17.19</v>
       </c>
       <c r="E39" t="n">
-        <v>12.4</v>
+        <v>13.3</v>
       </c>
       <c r="F39" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>71.95999999999999</v>
+        <v>78.27</v>
       </c>
       <c r="I39" t="n">
-        <v>74.59999999999999</v>
+        <v>79.16</v>
       </c>
       <c r="J39" t="n">
-        <v>65.83</v>
+        <v>77.5</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N39" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>18.99</v>
+        <v>17.62</v>
       </c>
       <c r="C40" t="n">
-        <v>19.05</v>
+        <v>17.85</v>
       </c>
       <c r="D40" t="n">
-        <v>18.9</v>
+        <v>17.33</v>
       </c>
       <c r="E40" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="F40" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>62.56</v>
+        <v>74.13</v>
       </c>
       <c r="I40" t="n">
-        <v>63.18</v>
+        <v>77.06</v>
       </c>
       <c r="J40" t="n">
-        <v>61.89</v>
+        <v>71.3</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2334,42 +2334,42 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>19.33</v>
+        <v>17.72</v>
       </c>
       <c r="C41" t="n">
-        <v>19.55</v>
+        <v>18.84</v>
       </c>
       <c r="D41" t="n">
-        <v>19.01</v>
+        <v>17.46</v>
       </c>
       <c r="E41" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F41" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>60.72</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>62.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>59.1</v>
+        <v>65.83</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2378,54 +2378,54 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19.52</v>
+        <v>18.99</v>
       </c>
       <c r="C42" t="n">
-        <v>19.58</v>
+        <v>19.05</v>
       </c>
       <c r="D42" t="n">
-        <v>19.46</v>
+        <v>18.9</v>
       </c>
       <c r="E42" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="F42" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>60.01</v>
+        <v>62.56</v>
       </c>
       <c r="I42" t="n">
-        <v>60.64</v>
+        <v>63.18</v>
       </c>
       <c r="J42" t="n">
-        <v>59.58</v>
+        <v>61.89</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>6152</v>
@@ -2435,35 +2435,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.62</v>
+        <v>19.33</v>
       </c>
       <c r="C43" t="n">
-        <v>19.71</v>
+        <v>19.55</v>
       </c>
       <c r="D43" t="n">
-        <v>19.49</v>
+        <v>19.01</v>
       </c>
       <c r="E43" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F43" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>60.63</v>
+        <v>60.72</v>
       </c>
       <c r="I43" t="n">
-        <v>61.71</v>
+        <v>62.8</v>
       </c>
       <c r="J43" t="n">
-        <v>59.73</v>
+        <v>59.1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2472,79 +2472,77 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N43" t="n">
-        <v>6152</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.3</v>
-      </c>
+        <v>6132</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.79</v>
+        <v>19.52</v>
       </c>
       <c r="C44" t="n">
-        <v>20.01</v>
+        <v>19.58</v>
       </c>
       <c r="D44" t="n">
-        <v>19.61</v>
+        <v>19.46</v>
       </c>
       <c r="E44" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F44" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>60.18</v>
+        <v>60.01</v>
       </c>
       <c r="I44" t="n">
-        <v>61.23</v>
+        <v>60.64</v>
       </c>
       <c r="J44" t="n">
-        <v>59.04</v>
+        <v>59.58</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M44" t="n">
         <v>0.5</v>
       </c>
       <c r="N44" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>20.19</v>
+        <v>19.62</v>
       </c>
       <c r="C45" t="n">
-        <v>20.36</v>
+        <v>19.71</v>
       </c>
       <c r="D45" t="n">
-        <v>20.01</v>
+        <v>19.49</v>
       </c>
       <c r="E45" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F45" t="n">
         <v>11.4</v>
@@ -2553,13 +2551,13 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>58.19</v>
+        <v>60.63</v>
       </c>
       <c r="I45" t="n">
-        <v>59.14</v>
+        <v>61.71</v>
       </c>
       <c r="J45" t="n">
-        <v>57.54</v>
+        <v>59.73</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2568,245 +2566,247 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6132</v>
-      </c>
-      <c r="O45" t="inlineStr"/>
+        <v>6152</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20.44</v>
+        <v>19.79</v>
       </c>
       <c r="C46" t="n">
-        <v>20.64</v>
+        <v>20.01</v>
       </c>
       <c r="D46" t="n">
-        <v>20.37</v>
+        <v>19.61</v>
       </c>
       <c r="E46" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F46" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>57.96</v>
+        <v>60.18</v>
       </c>
       <c r="I46" t="n">
-        <v>58.31</v>
+        <v>61.23</v>
       </c>
       <c r="J46" t="n">
-        <v>57.52</v>
+        <v>59.04</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N46" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20.99</v>
+        <v>20.19</v>
       </c>
       <c r="C47" t="n">
-        <v>21.3</v>
+        <v>20.36</v>
       </c>
       <c r="D47" t="n">
-        <v>20.64</v>
+        <v>20.01</v>
       </c>
       <c r="E47" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F47" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>55.76</v>
+        <v>58.19</v>
       </c>
       <c r="I47" t="n">
-        <v>57.26</v>
+        <v>59.14</v>
       </c>
       <c r="J47" t="n">
-        <v>54.28</v>
+        <v>57.54</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>0.2</v>
       </c>
-      <c r="M47" t="n">
-        <v>0.8</v>
-      </c>
       <c r="N47" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.82</v>
+        <v>20.44</v>
       </c>
       <c r="C48" t="n">
-        <v>22.25</v>
+        <v>20.64</v>
       </c>
       <c r="D48" t="n">
-        <v>21.38</v>
+        <v>20.37</v>
       </c>
       <c r="E48" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="F48" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>52.03</v>
+        <v>57.96</v>
       </c>
       <c r="I48" t="n">
-        <v>53.83</v>
+        <v>58.31</v>
       </c>
       <c r="J48" t="n">
-        <v>50.23</v>
+        <v>57.52</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>22.61</v>
+        <v>20.99</v>
       </c>
       <c r="C49" t="n">
-        <v>22.85</v>
+        <v>21.3</v>
       </c>
       <c r="D49" t="n">
-        <v>22.34</v>
+        <v>20.64</v>
       </c>
       <c r="E49" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G49" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>49.28</v>
+        <v>55.76</v>
       </c>
       <c r="I49" t="n">
-        <v>50.37</v>
+        <v>57.26</v>
       </c>
       <c r="J49" t="n">
-        <v>48.38</v>
+        <v>54.28</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="M49" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="N49" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.26</v>
+        <v>21.82</v>
       </c>
       <c r="C50" t="n">
-        <v>24</v>
+        <v>22.25</v>
       </c>
       <c r="D50" t="n">
-        <v>22.73</v>
+        <v>21.38</v>
       </c>
       <c r="E50" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F50" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="G50" t="n">
-        <v>249</v>
+        <v>6</v>
       </c>
       <c r="H50" t="n">
-        <v>47.55</v>
+        <v>52.03</v>
       </c>
       <c r="I50" t="n">
-        <v>48.93</v>
+        <v>53.83</v>
       </c>
       <c r="J50" t="n">
-        <v>45.68</v>
+        <v>50.23</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M50" t="n">
         <v>1.1</v>
       </c>
-      <c r="M50" t="n">
-        <v>2</v>
-      </c>
       <c r="N50" t="n">
-        <v>6220</v>
+        <v>6180</v>
       </c>
       <c r="O50" t="n">
         <v>2.4</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,91 +508,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.03</v>
+        <v>16.23</v>
       </c>
       <c r="C2" t="n">
-        <v>17.08</v>
+        <v>16.37</v>
       </c>
       <c r="D2" t="n">
-        <v>16.98</v>
+        <v>16.09</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="F2" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>68.95999999999999</v>
+        <v>73.47</v>
       </c>
       <c r="I2" t="n">
-        <v>69.3</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>68.62</v>
+        <v>72.33</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N2" t="n">
-        <v>6122</v>
+        <v>6112</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.26</v>
+        <v>16.37</v>
       </c>
       <c r="C3" t="n">
-        <v>17.41</v>
+        <v>16.48</v>
       </c>
       <c r="D3" t="n">
-        <v>17.13</v>
+        <v>16.29</v>
       </c>
       <c r="E3" t="n">
-        <v>10.7</v>
+        <v>11.6</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>65.97</v>
+        <v>74.02</v>
       </c>
       <c r="I3" t="n">
-        <v>68.3</v>
+        <v>74.88</v>
       </c>
       <c r="J3" t="n">
-        <v>62.44</v>
+        <v>72.13</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="N3" t="n">
         <v>6132</v>
@@ -602,138 +602,138 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.57</v>
+        <v>16.84</v>
       </c>
       <c r="C4" t="n">
-        <v>18.11</v>
+        <v>17.08</v>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.57</v>
       </c>
       <c r="E4" t="n">
-        <v>10.4</v>
+        <v>11.3</v>
       </c>
       <c r="F4" t="n">
-        <v>9.800000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>63.38</v>
+        <v>70.64</v>
       </c>
       <c r="I4" t="n">
-        <v>64.3</v>
+        <v>72.89</v>
       </c>
       <c r="J4" t="n">
-        <v>61.77</v>
+        <v>68.62</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="N4" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>17.26</v>
       </c>
       <c r="C5" t="n">
-        <v>18.2</v>
+        <v>17.41</v>
       </c>
       <c r="D5" t="n">
-        <v>17.79</v>
+        <v>17.13</v>
       </c>
       <c r="E5" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="F5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>62.96</v>
+        <v>65.97</v>
       </c>
       <c r="I5" t="n">
-        <v>64.08</v>
+        <v>68.3</v>
       </c>
       <c r="J5" t="n">
-        <v>61.81</v>
+        <v>62.44</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N5" t="n">
-        <v>6162</v>
+        <v>6132</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.15</v>
+        <v>17.57</v>
       </c>
       <c r="C6" t="n">
-        <v>18.5</v>
+        <v>18.11</v>
       </c>
       <c r="D6" t="n">
-        <v>17.92</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="H6" t="n">
-        <v>60.86</v>
+        <v>63.38</v>
       </c>
       <c r="I6" t="n">
-        <v>62.23</v>
+        <v>64.3</v>
       </c>
       <c r="J6" t="n">
-        <v>59.51</v>
+        <v>61.77</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="N6" t="n">
         <v>6142</v>
@@ -743,317 +743,317 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.71</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>18.05</v>
+        <v>18.2</v>
       </c>
       <c r="D7" t="n">
-        <v>17.31</v>
+        <v>17.79</v>
       </c>
       <c r="E7" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="F7" t="n">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="G7" t="n">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="H7" t="n">
-        <v>61.59</v>
+        <v>62.96</v>
       </c>
       <c r="I7" t="n">
-        <v>63.45</v>
+        <v>64.08</v>
       </c>
       <c r="J7" t="n">
-        <v>59.82</v>
+        <v>61.81</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N7" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.72</v>
+        <v>18.15</v>
       </c>
       <c r="C8" t="n">
-        <v>17.47</v>
+        <v>18.5</v>
       </c>
       <c r="D8" t="n">
-        <v>16.08</v>
+        <v>17.92</v>
       </c>
       <c r="E8" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="H8" t="n">
-        <v>67.33</v>
+        <v>60.86</v>
       </c>
       <c r="I8" t="n">
-        <v>70.81999999999999</v>
+        <v>62.23</v>
       </c>
       <c r="J8" t="n">
-        <v>63.98</v>
+        <v>59.51</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.83</v>
+        <v>17.71</v>
       </c>
       <c r="C9" t="n">
-        <v>16.23</v>
+        <v>18.05</v>
       </c>
       <c r="D9" t="n">
-        <v>15.45</v>
+        <v>17.31</v>
       </c>
       <c r="E9" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="F9" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="G9" t="n">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="H9" t="n">
-        <v>72.95</v>
+        <v>61.59</v>
       </c>
       <c r="I9" t="n">
-        <v>75.03</v>
+        <v>63.45</v>
       </c>
       <c r="J9" t="n">
-        <v>69.84999999999999</v>
+        <v>59.82</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.22</v>
+        <v>16.72</v>
       </c>
       <c r="C10" t="n">
-        <v>15.77</v>
+        <v>17.47</v>
       </c>
       <c r="D10" t="n">
-        <v>14.97</v>
+        <v>16.08</v>
       </c>
       <c r="E10" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="F10" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>158</v>
+        <v>260</v>
       </c>
       <c r="H10" t="n">
-        <v>77.61</v>
+        <v>67.33</v>
       </c>
       <c r="I10" t="n">
-        <v>79.25</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>74.45</v>
+        <v>63.98</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N10" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14.79</v>
+        <v>15.83</v>
       </c>
       <c r="C11" t="n">
-        <v>15.1</v>
+        <v>16.23</v>
       </c>
       <c r="D11" t="n">
-        <v>14.32</v>
+        <v>15.45</v>
       </c>
       <c r="E11" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="F11" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="G11" t="n">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="H11" t="n">
-        <v>80.70999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="I11" t="n">
-        <v>83.36</v>
+        <v>75.03</v>
       </c>
       <c r="J11" t="n">
-        <v>79.05</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M11" t="n">
         <v>1.4</v>
       </c>
       <c r="N11" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.05</v>
+        <v>15.22</v>
       </c>
       <c r="C12" t="n">
-        <v>14.26</v>
+        <v>15.77</v>
       </c>
       <c r="D12" t="n">
-        <v>13.8</v>
+        <v>14.97</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F12" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="G12" t="n">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="H12" t="n">
-        <v>85.09</v>
+        <v>77.61</v>
       </c>
       <c r="I12" t="n">
-        <v>86.40000000000001</v>
+        <v>79.25</v>
       </c>
       <c r="J12" t="n">
-        <v>84.14</v>
+        <v>74.45</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>1.4</v>
       </c>
       <c r="N12" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14.11</v>
+        <v>14.79</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56</v>
+        <v>15.1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.7</v>
+        <v>14.32</v>
       </c>
       <c r="E13" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="G13" t="n">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="H13" t="n">
-        <v>81.01000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>87.31</v>
+        <v>83.36</v>
       </c>
       <c r="J13" t="n">
-        <v>75.84999999999999</v>
+        <v>79.05</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1062,101 +1062,101 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N13" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.64</v>
+        <v>14.05</v>
       </c>
       <c r="C14" t="n">
-        <v>14.86</v>
+        <v>14.26</v>
       </c>
       <c r="D14" t="n">
-        <v>14.45</v>
+        <v>13.8</v>
       </c>
       <c r="E14" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="F14" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="H14" t="n">
-        <v>79.53</v>
+        <v>85.09</v>
       </c>
       <c r="I14" t="n">
-        <v>82.73999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>76.79000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N14" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.07</v>
+        <v>14.11</v>
       </c>
       <c r="C15" t="n">
-        <v>15.23</v>
+        <v>14.56</v>
       </c>
       <c r="D15" t="n">
-        <v>14.92</v>
+        <v>13.7</v>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="F15" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H15" t="n">
-        <v>77.61</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>78.94</v>
+        <v>87.31</v>
       </c>
       <c r="J15" t="n">
-        <v>76.67</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N15" t="n">
         <v>6132</v>
@@ -1166,44 +1166,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.37</v>
+        <v>14.64</v>
       </c>
       <c r="C16" t="n">
-        <v>15.49</v>
+        <v>14.86</v>
       </c>
       <c r="D16" t="n">
-        <v>15.25</v>
+        <v>14.45</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8</v>
+        <v>10.9</v>
       </c>
       <c r="F16" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>79.81999999999999</v>
+        <v>79.53</v>
       </c>
       <c r="I16" t="n">
-        <v>80.69</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>78.86</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N16" t="n">
         <v>6132</v>
@@ -1213,44 +1213,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.65</v>
+        <v>15.07</v>
       </c>
       <c r="C17" t="n">
-        <v>15.77</v>
+        <v>15.23</v>
       </c>
       <c r="D17" t="n">
-        <v>15.48</v>
+        <v>14.92</v>
       </c>
       <c r="E17" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>11.6</v>
+        <v>10.7</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>78.64</v>
+        <v>77.61</v>
       </c>
       <c r="I17" t="n">
-        <v>80.7</v>
+        <v>78.94</v>
       </c>
       <c r="J17" t="n">
-        <v>77.23</v>
+        <v>76.67</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>6132</v>
@@ -1260,91 +1260,91 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15.39</v>
+        <v>15.37</v>
       </c>
       <c r="C18" t="n">
-        <v>15.59</v>
+        <v>15.49</v>
       </c>
       <c r="D18" t="n">
-        <v>15.29</v>
+        <v>15.25</v>
       </c>
       <c r="E18" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="F18" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>84.89</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>87.12</v>
+        <v>80.69</v>
       </c>
       <c r="J18" t="n">
-        <v>81.20999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>6112</v>
+        <v>6132</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15.61</v>
+        <v>15.65</v>
       </c>
       <c r="C19" t="n">
-        <v>16.09</v>
+        <v>15.77</v>
       </c>
       <c r="D19" t="n">
-        <v>15.44</v>
+        <v>15.48</v>
       </c>
       <c r="E19" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="F19" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>84.45</v>
+        <v>78.64</v>
       </c>
       <c r="I19" t="n">
-        <v>86.2</v>
+        <v>80.7</v>
       </c>
       <c r="J19" t="n">
-        <v>79</v>
+        <v>77.23</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="N19" t="n">
         <v>6132</v>
@@ -1354,138 +1354,138 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.78</v>
+        <v>15.39</v>
       </c>
       <c r="C20" t="n">
-        <v>17.16</v>
+        <v>15.59</v>
       </c>
       <c r="D20" t="n">
-        <v>16.31</v>
+        <v>15.29</v>
       </c>
       <c r="E20" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="F20" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>73.62</v>
+        <v>84.89</v>
       </c>
       <c r="I20" t="n">
-        <v>76.98999999999999</v>
+        <v>87.12</v>
       </c>
       <c r="J20" t="n">
-        <v>69.84</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="N20" t="n">
-        <v>6122</v>
+        <v>6112</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.55</v>
+        <v>15.61</v>
       </c>
       <c r="C21" t="n">
-        <v>17.8</v>
+        <v>16.09</v>
       </c>
       <c r="D21" t="n">
-        <v>17.2</v>
+        <v>15.44</v>
       </c>
       <c r="E21" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="F21" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>71.04000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="I21" t="n">
-        <v>73.81</v>
+        <v>86.2</v>
       </c>
       <c r="J21" t="n">
-        <v>69.28</v>
+        <v>79</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="M21" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="N21" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.63</v>
+        <v>16.78</v>
       </c>
       <c r="C22" t="n">
-        <v>18.08</v>
+        <v>17.16</v>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>16.31</v>
       </c>
       <c r="E22" t="n">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>73.43000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="I22" t="n">
-        <v>76.55</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>68.51000000000001</v>
+        <v>69.84</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="N22" t="n">
         <v>6122</v>
@@ -1495,82 +1495,82 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.46</v>
+        <v>17.55</v>
       </c>
       <c r="C23" t="n">
-        <v>17.67</v>
+        <v>17.8</v>
       </c>
       <c r="D23" t="n">
-        <v>17.22</v>
+        <v>17.2</v>
       </c>
       <c r="E23" t="n">
-        <v>13.2</v>
+        <v>12.1</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>76.84</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>79.37</v>
+        <v>73.81</v>
       </c>
       <c r="J23" t="n">
-        <v>75.08</v>
+        <v>69.28</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="N23" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.43</v>
+        <v>17.63</v>
       </c>
       <c r="C24" t="n">
-        <v>17.62</v>
+        <v>18.08</v>
       </c>
       <c r="D24" t="n">
-        <v>17.17</v>
+        <v>17.4</v>
       </c>
       <c r="E24" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="F24" t="n">
-        <v>13.3</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>79.34</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>82.2</v>
+        <v>76.55</v>
       </c>
       <c r="J24" t="n">
-        <v>77.51000000000001</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1579,383 +1579,383 @@
         <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.89</v>
+        <v>17.46</v>
       </c>
       <c r="C25" t="n">
-        <v>18.13</v>
+        <v>17.67</v>
       </c>
       <c r="D25" t="n">
-        <v>17.76</v>
+        <v>17.22</v>
       </c>
       <c r="E25" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="F25" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>76.29000000000001</v>
+        <v>76.84</v>
       </c>
       <c r="I25" t="n">
-        <v>78.06999999999999</v>
+        <v>79.37</v>
       </c>
       <c r="J25" t="n">
-        <v>74.34999999999999</v>
+        <v>75.08</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="N25" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18.6</v>
+        <v>17.43</v>
       </c>
       <c r="C26" t="n">
-        <v>19.26</v>
+        <v>17.62</v>
       </c>
       <c r="D26" t="n">
-        <v>18.22</v>
+        <v>17.17</v>
       </c>
       <c r="E26" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="F26" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>70.7</v>
+        <v>79.34</v>
       </c>
       <c r="I26" t="n">
-        <v>73.79000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="J26" t="n">
-        <v>65.41</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20.29</v>
+        <v>17.89</v>
       </c>
       <c r="C27" t="n">
-        <v>21.69</v>
+        <v>18.13</v>
       </c>
       <c r="D27" t="n">
-        <v>19.3</v>
+        <v>17.76</v>
       </c>
       <c r="E27" t="n">
-        <v>11.6</v>
+        <v>13.4</v>
       </c>
       <c r="F27" t="n">
-        <v>10.7</v>
+        <v>13.2</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>58.46</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>64.93000000000001</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>50.01</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="N27" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22.33</v>
+        <v>18.6</v>
       </c>
       <c r="C28" t="n">
-        <v>22.66</v>
+        <v>19.26</v>
       </c>
       <c r="D28" t="n">
-        <v>21.95</v>
+        <v>18.22</v>
       </c>
       <c r="E28" t="n">
-        <v>9.9</v>
+        <v>13</v>
       </c>
       <c r="F28" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="G28" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>46.23</v>
+        <v>70.7</v>
       </c>
       <c r="I28" t="n">
-        <v>48.69</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>44.45</v>
+        <v>65.41</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22.97</v>
+        <v>20.29</v>
       </c>
       <c r="C29" t="n">
-        <v>23.49</v>
+        <v>21.69</v>
       </c>
       <c r="D29" t="n">
-        <v>22.63</v>
+        <v>19.3</v>
       </c>
       <c r="E29" t="n">
-        <v>9.5</v>
+        <v>11.6</v>
       </c>
       <c r="F29" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="G29" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>43.28</v>
+        <v>58.46</v>
       </c>
       <c r="I29" t="n">
-        <v>44.43</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>41.95</v>
+        <v>50.01</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23.37</v>
+        <v>22.33</v>
       </c>
       <c r="C30" t="n">
-        <v>23.93</v>
+        <v>22.66</v>
       </c>
       <c r="D30" t="n">
-        <v>23.11</v>
+        <v>21.95</v>
       </c>
       <c r="E30" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="F30" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="G30" t="n">
-        <v>271</v>
+        <v>24</v>
       </c>
       <c r="H30" t="n">
-        <v>42.7</v>
+        <v>46.23</v>
       </c>
       <c r="I30" t="n">
-        <v>44.12</v>
+        <v>48.69</v>
       </c>
       <c r="J30" t="n">
-        <v>41.98</v>
+        <v>44.45</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="M30" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="N30" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23.27</v>
+        <v>22.97</v>
       </c>
       <c r="C31" t="n">
-        <v>23.64</v>
+        <v>23.49</v>
       </c>
       <c r="D31" t="n">
-        <v>22.89</v>
+        <v>22.63</v>
       </c>
       <c r="E31" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F31" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G31" t="n">
-        <v>326</v>
+        <v>72</v>
       </c>
       <c r="H31" t="n">
-        <v>42.52</v>
+        <v>43.28</v>
       </c>
       <c r="I31" t="n">
-        <v>43.12</v>
+        <v>44.43</v>
       </c>
       <c r="J31" t="n">
-        <v>41.91</v>
+        <v>41.95</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N31" t="n">
-        <v>6190</v>
+        <v>6180</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22.93</v>
+        <v>23.37</v>
       </c>
       <c r="C32" t="n">
-        <v>23.35</v>
+        <v>23.93</v>
       </c>
       <c r="D32" t="n">
-        <v>22.54</v>
+        <v>23.11</v>
       </c>
       <c r="E32" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="G32" t="n">
-        <v>393</v>
+        <v>271</v>
       </c>
       <c r="H32" t="n">
-        <v>43.56</v>
+        <v>42.7</v>
       </c>
       <c r="I32" t="n">
-        <v>44.91</v>
+        <v>44.12</v>
       </c>
       <c r="J32" t="n">
-        <v>42.28</v>
+        <v>41.98</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N32" t="n">
         <v>6190</v>
@@ -1965,35 +1965,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.23</v>
+        <v>23.27</v>
       </c>
       <c r="C33" t="n">
-        <v>22.76</v>
+        <v>23.64</v>
       </c>
       <c r="D33" t="n">
-        <v>21.86</v>
+        <v>22.89</v>
       </c>
       <c r="E33" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="F33" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="H33" t="n">
-        <v>45.63</v>
+        <v>42.52</v>
       </c>
       <c r="I33" t="n">
-        <v>47.01</v>
+        <v>43.12</v>
       </c>
       <c r="J33" t="n">
-        <v>44.24</v>
+        <v>41.91</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2002,336 +2002,336 @@
         <v>0.5</v>
       </c>
       <c r="M33" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="N33" t="n">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21.57</v>
+        <v>22.93</v>
       </c>
       <c r="C34" t="n">
-        <v>22.64</v>
+        <v>23.35</v>
       </c>
       <c r="D34" t="n">
-        <v>20.71</v>
+        <v>22.54</v>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G34" t="n">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="H34" t="n">
-        <v>48.34</v>
+        <v>43.56</v>
       </c>
       <c r="I34" t="n">
-        <v>51.45</v>
+        <v>44.91</v>
       </c>
       <c r="J34" t="n">
-        <v>45.03</v>
+        <v>42.28</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N34" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>20.3</v>
+        <v>22.23</v>
       </c>
       <c r="C35" t="n">
-        <v>20.76</v>
+        <v>22.76</v>
       </c>
       <c r="D35" t="n">
-        <v>19.87</v>
+        <v>21.86</v>
       </c>
       <c r="E35" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>231</v>
+        <v>383</v>
       </c>
       <c r="H35" t="n">
-        <v>53.23</v>
+        <v>45.63</v>
       </c>
       <c r="I35" t="n">
-        <v>56.41</v>
+        <v>47.01</v>
       </c>
       <c r="J35" t="n">
-        <v>51.05</v>
+        <v>44.24</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M35" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="N35" t="n">
-        <v>6170</v>
+        <v>6180</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19.38</v>
+        <v>21.57</v>
       </c>
       <c r="C36" t="n">
-        <v>19.85</v>
+        <v>22.64</v>
       </c>
       <c r="D36" t="n">
-        <v>18.89</v>
+        <v>20.71</v>
       </c>
       <c r="E36" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>110</v>
+        <v>373</v>
       </c>
       <c r="H36" t="n">
-        <v>61.37</v>
+        <v>48.34</v>
       </c>
       <c r="I36" t="n">
-        <v>65.44</v>
+        <v>51.45</v>
       </c>
       <c r="J36" t="n">
-        <v>57.45</v>
+        <v>45.03</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="N36" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18.52</v>
+        <v>20.3</v>
       </c>
       <c r="C37" t="n">
-        <v>18.87</v>
+        <v>20.76</v>
       </c>
       <c r="D37" t="n">
-        <v>18.23</v>
+        <v>19.87</v>
       </c>
       <c r="E37" t="n">
-        <v>12.2</v>
+        <v>10.3</v>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
-        <v>34</v>
+        <v>231</v>
       </c>
       <c r="H37" t="n">
-        <v>67.5</v>
+        <v>53.23</v>
       </c>
       <c r="I37" t="n">
-        <v>70.43000000000001</v>
+        <v>56.41</v>
       </c>
       <c r="J37" t="n">
-        <v>65.33</v>
+        <v>51.05</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N37" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.89</v>
+        <v>19.38</v>
       </c>
       <c r="C38" t="n">
-        <v>18.27</v>
+        <v>19.85</v>
       </c>
       <c r="D38" t="n">
-        <v>17.53</v>
+        <v>18.89</v>
       </c>
       <c r="E38" t="n">
-        <v>13.1</v>
+        <v>11.6</v>
       </c>
       <c r="F38" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="G38" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="H38" t="n">
-        <v>74.15000000000001</v>
+        <v>61.37</v>
       </c>
       <c r="I38" t="n">
-        <v>77.34999999999999</v>
+        <v>65.44</v>
       </c>
       <c r="J38" t="n">
-        <v>70.23999999999999</v>
+        <v>57.45</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.34</v>
+        <v>18.52</v>
       </c>
       <c r="C39" t="n">
-        <v>17.48</v>
+        <v>18.87</v>
       </c>
       <c r="D39" t="n">
-        <v>17.19</v>
+        <v>18.23</v>
       </c>
       <c r="E39" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="F39" t="n">
-        <v>13.1</v>
+        <v>12</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H39" t="n">
-        <v>78.27</v>
+        <v>67.5</v>
       </c>
       <c r="I39" t="n">
-        <v>79.16</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>77.5</v>
+        <v>65.33</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.62</v>
+        <v>17.89</v>
       </c>
       <c r="C40" t="n">
-        <v>17.85</v>
+        <v>18.27</v>
       </c>
       <c r="D40" t="n">
-        <v>17.33</v>
+        <v>17.53</v>
       </c>
       <c r="E40" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="F40" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>74.13</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>77.06</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>71.3</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
         <v>6142</v>
@@ -2341,82 +2341,82 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.72</v>
+        <v>17.34</v>
       </c>
       <c r="C41" t="n">
-        <v>18.84</v>
+        <v>17.48</v>
       </c>
       <c r="D41" t="n">
-        <v>17.46</v>
+        <v>17.19</v>
       </c>
       <c r="E41" t="n">
-        <v>12.4</v>
+        <v>13.3</v>
       </c>
       <c r="F41" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>71.95999999999999</v>
+        <v>78.27</v>
       </c>
       <c r="I41" t="n">
-        <v>74.59999999999999</v>
+        <v>79.16</v>
       </c>
       <c r="J41" t="n">
-        <v>65.83</v>
+        <v>77.5</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N41" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18.99</v>
+        <v>17.62</v>
       </c>
       <c r="C42" t="n">
-        <v>19.05</v>
+        <v>17.85</v>
       </c>
       <c r="D42" t="n">
-        <v>18.9</v>
+        <v>17.33</v>
       </c>
       <c r="E42" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="F42" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>62.56</v>
+        <v>74.13</v>
       </c>
       <c r="I42" t="n">
-        <v>63.18</v>
+        <v>77.06</v>
       </c>
       <c r="J42" t="n">
-        <v>61.89</v>
+        <v>71.3</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2428,42 +2428,42 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.33</v>
+        <v>17.72</v>
       </c>
       <c r="C43" t="n">
-        <v>19.55</v>
+        <v>18.84</v>
       </c>
       <c r="D43" t="n">
-        <v>19.01</v>
+        <v>17.46</v>
       </c>
       <c r="E43" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F43" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>60.72</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>62.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>59.1</v>
+        <v>65.83</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2472,54 +2472,54 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.52</v>
+        <v>18.99</v>
       </c>
       <c r="C44" t="n">
-        <v>19.58</v>
+        <v>19.05</v>
       </c>
       <c r="D44" t="n">
-        <v>19.46</v>
+        <v>18.9</v>
       </c>
       <c r="E44" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="F44" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>60.01</v>
+        <v>62.56</v>
       </c>
       <c r="I44" t="n">
-        <v>60.64</v>
+        <v>63.18</v>
       </c>
       <c r="J44" t="n">
-        <v>59.58</v>
+        <v>61.89</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>6152</v>
@@ -2529,35 +2529,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.62</v>
+        <v>19.33</v>
       </c>
       <c r="C45" t="n">
-        <v>19.71</v>
+        <v>19.55</v>
       </c>
       <c r="D45" t="n">
-        <v>19.49</v>
+        <v>19.01</v>
       </c>
       <c r="E45" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F45" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>60.63</v>
+        <v>60.72</v>
       </c>
       <c r="I45" t="n">
-        <v>61.71</v>
+        <v>62.8</v>
       </c>
       <c r="J45" t="n">
-        <v>59.73</v>
+        <v>59.1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2566,79 +2566,77 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N45" t="n">
-        <v>6152</v>
-      </c>
-      <c r="O45" t="n">
-        <v>2.3</v>
-      </c>
+        <v>6132</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.79</v>
+        <v>19.52</v>
       </c>
       <c r="C46" t="n">
-        <v>20.01</v>
+        <v>19.58</v>
       </c>
       <c r="D46" t="n">
-        <v>19.61</v>
+        <v>19.46</v>
       </c>
       <c r="E46" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F46" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>60.18</v>
+        <v>60.01</v>
       </c>
       <c r="I46" t="n">
-        <v>61.23</v>
+        <v>60.64</v>
       </c>
       <c r="J46" t="n">
-        <v>59.04</v>
+        <v>59.58</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M46" t="n">
         <v>0.5</v>
       </c>
       <c r="N46" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20.19</v>
+        <v>19.62</v>
       </c>
       <c r="C47" t="n">
-        <v>20.36</v>
+        <v>19.71</v>
       </c>
       <c r="D47" t="n">
-        <v>20.01</v>
+        <v>19.49</v>
       </c>
       <c r="E47" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F47" t="n">
         <v>11.4</v>
@@ -2647,13 +2645,13 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>58.19</v>
+        <v>60.63</v>
       </c>
       <c r="I47" t="n">
-        <v>59.14</v>
+        <v>61.71</v>
       </c>
       <c r="J47" t="n">
-        <v>57.54</v>
+        <v>59.73</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2662,151 +2660,153 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>6132</v>
-      </c>
-      <c r="O47" t="inlineStr"/>
+        <v>6152</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>20.44</v>
+        <v>19.79</v>
       </c>
       <c r="C48" t="n">
-        <v>20.64</v>
+        <v>20.01</v>
       </c>
       <c r="D48" t="n">
-        <v>20.37</v>
+        <v>19.61</v>
       </c>
       <c r="E48" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F48" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>57.96</v>
+        <v>60.18</v>
       </c>
       <c r="I48" t="n">
-        <v>58.31</v>
+        <v>61.23</v>
       </c>
       <c r="J48" t="n">
-        <v>57.52</v>
+        <v>59.04</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N48" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.99</v>
+        <v>20.19</v>
       </c>
       <c r="C49" t="n">
-        <v>21.3</v>
+        <v>20.36</v>
       </c>
       <c r="D49" t="n">
-        <v>20.64</v>
+        <v>20.01</v>
       </c>
       <c r="E49" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F49" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>55.76</v>
+        <v>58.19</v>
       </c>
       <c r="I49" t="n">
-        <v>57.26</v>
+        <v>59.14</v>
       </c>
       <c r="J49" t="n">
-        <v>54.28</v>
+        <v>57.54</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>0.2</v>
       </c>
-      <c r="M49" t="n">
-        <v>0.8</v>
-      </c>
       <c r="N49" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>21.82</v>
+        <v>20.44</v>
       </c>
       <c r="C50" t="n">
-        <v>22.25</v>
+        <v>20.64</v>
       </c>
       <c r="D50" t="n">
-        <v>21.38</v>
+        <v>20.37</v>
       </c>
       <c r="E50" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="F50" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>52.03</v>
+        <v>57.96</v>
       </c>
       <c r="I50" t="n">
-        <v>53.83</v>
+        <v>58.31</v>
       </c>
       <c r="J50" t="n">
-        <v>50.23</v>
+        <v>57.52</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O50" t="n">
         <v>2.4</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,44 +508,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.23</v>
+        <v>15.75</v>
       </c>
       <c r="C2" t="n">
-        <v>16.37</v>
+        <v>15.77</v>
       </c>
       <c r="D2" t="n">
-        <v>16.09</v>
+        <v>15.72</v>
       </c>
       <c r="E2" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="F2" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>73.47</v>
+        <v>80.33</v>
       </c>
       <c r="I2" t="n">
-        <v>74.68000000000001</v>
+        <v>80.62</v>
       </c>
       <c r="J2" t="n">
-        <v>72.33</v>
+        <v>80.16</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
         <v>6112</v>
@@ -555,467 +555,467 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.37</v>
+        <v>16.09</v>
       </c>
       <c r="C3" t="n">
-        <v>16.48</v>
+        <v>16.59</v>
       </c>
       <c r="D3" t="n">
-        <v>16.29</v>
+        <v>15.76</v>
       </c>
       <c r="E3" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="F3" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>74.02</v>
+        <v>76.7</v>
       </c>
       <c r="I3" t="n">
-        <v>74.88</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>72.13</v>
+        <v>72.89</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N3" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.84</v>
+        <v>16.2</v>
       </c>
       <c r="C4" t="n">
-        <v>17.08</v>
+        <v>16.53</v>
       </c>
       <c r="D4" t="n">
-        <v>16.57</v>
+        <v>15.84</v>
       </c>
       <c r="E4" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="F4" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>70.64</v>
+        <v>77.2</v>
       </c>
       <c r="I4" t="n">
-        <v>72.89</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>68.62</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="N4" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.26</v>
+        <v>16.03</v>
       </c>
       <c r="C5" t="n">
-        <v>17.41</v>
+        <v>16.12</v>
       </c>
       <c r="D5" t="n">
-        <v>17.13</v>
+        <v>15.93</v>
       </c>
       <c r="E5" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>65.97</v>
+        <v>77.56</v>
       </c>
       <c r="I5" t="n">
-        <v>68.3</v>
+        <v>79.16</v>
       </c>
       <c r="J5" t="n">
-        <v>62.44</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="N5" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.57</v>
+        <v>15.79</v>
       </c>
       <c r="C6" t="n">
-        <v>18.11</v>
+        <v>15.92</v>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>15.7</v>
       </c>
       <c r="E6" t="n">
-        <v>10.4</v>
+        <v>11.9</v>
       </c>
       <c r="F6" t="n">
-        <v>9.800000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>63.38</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>64.3</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>61.77</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="N6" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>15.9</v>
       </c>
       <c r="C7" t="n">
-        <v>18.2</v>
+        <v>16.37</v>
       </c>
       <c r="D7" t="n">
-        <v>17.79</v>
+        <v>15.67</v>
       </c>
       <c r="E7" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="F7" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="G7" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>62.96</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>64.08</v>
+        <v>78.44</v>
       </c>
       <c r="J7" t="n">
-        <v>61.81</v>
+        <v>72.33</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N7" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.15</v>
+        <v>16.37</v>
       </c>
       <c r="C8" t="n">
-        <v>18.5</v>
+        <v>16.48</v>
       </c>
       <c r="D8" t="n">
-        <v>17.92</v>
+        <v>16.29</v>
       </c>
       <c r="E8" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="G8" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>60.86</v>
+        <v>74.02</v>
       </c>
       <c r="I8" t="n">
-        <v>62.23</v>
+        <v>74.88</v>
       </c>
       <c r="J8" t="n">
-        <v>59.51</v>
+        <v>72.13</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="N8" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.71</v>
+        <v>16.84</v>
       </c>
       <c r="C9" t="n">
-        <v>18.05</v>
+        <v>17.08</v>
       </c>
       <c r="D9" t="n">
-        <v>17.31</v>
+        <v>16.57</v>
       </c>
       <c r="E9" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
       <c r="F9" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="G9" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>61.59</v>
+        <v>70.64</v>
       </c>
       <c r="I9" t="n">
-        <v>63.45</v>
+        <v>72.89</v>
       </c>
       <c r="J9" t="n">
-        <v>59.82</v>
+        <v>68.62</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N9" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.72</v>
+        <v>17.26</v>
       </c>
       <c r="C10" t="n">
-        <v>17.47</v>
+        <v>17.41</v>
       </c>
       <c r="D10" t="n">
-        <v>16.08</v>
+        <v>17.13</v>
       </c>
       <c r="E10" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="F10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>260</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>67.33</v>
+        <v>65.97</v>
       </c>
       <c r="I10" t="n">
-        <v>70.81999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="J10" t="n">
-        <v>63.98</v>
+        <v>62.44</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N10" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15.83</v>
+        <v>17.57</v>
       </c>
       <c r="C11" t="n">
-        <v>16.23</v>
+        <v>18.11</v>
       </c>
       <c r="D11" t="n">
-        <v>15.45</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F11" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H11" t="n">
-        <v>72.95</v>
+        <v>63.38</v>
       </c>
       <c r="I11" t="n">
-        <v>75.03</v>
+        <v>64.3</v>
       </c>
       <c r="J11" t="n">
-        <v>69.84999999999999</v>
+        <v>61.77</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N11" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.22</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>15.77</v>
+        <v>18.2</v>
       </c>
       <c r="D12" t="n">
-        <v>14.97</v>
+        <v>17.79</v>
       </c>
       <c r="E12" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="F12" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="G12" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H12" t="n">
-        <v>77.61</v>
+        <v>62.96</v>
       </c>
       <c r="I12" t="n">
-        <v>79.25</v>
+        <v>64.08</v>
       </c>
       <c r="J12" t="n">
-        <v>74.45</v>
+        <v>61.81</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N12" t="n">
         <v>6162</v>
@@ -1025,44 +1025,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14.79</v>
+        <v>18.15</v>
       </c>
       <c r="C13" t="n">
-        <v>15.1</v>
+        <v>18.5</v>
       </c>
       <c r="D13" t="n">
-        <v>14.32</v>
+        <v>17.92</v>
       </c>
       <c r="E13" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="F13" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="H13" t="n">
-        <v>80.70999999999999</v>
+        <v>60.86</v>
       </c>
       <c r="I13" t="n">
-        <v>83.36</v>
+        <v>62.23</v>
       </c>
       <c r="J13" t="n">
-        <v>79.05</v>
+        <v>59.51</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
         <v>6142</v>
@@ -1072,138 +1072,138 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.05</v>
+        <v>17.71</v>
       </c>
       <c r="C14" t="n">
-        <v>14.26</v>
+        <v>18.05</v>
       </c>
       <c r="D14" t="n">
-        <v>13.8</v>
+        <v>17.31</v>
       </c>
       <c r="E14" t="n">
-        <v>11.4</v>
+        <v>10.1</v>
       </c>
       <c r="F14" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="G14" t="n">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="H14" t="n">
-        <v>85.09</v>
+        <v>61.59</v>
       </c>
       <c r="I14" t="n">
-        <v>86.40000000000001</v>
+        <v>63.45</v>
       </c>
       <c r="J14" t="n">
-        <v>84.14</v>
+        <v>59.82</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.11</v>
+        <v>16.72</v>
       </c>
       <c r="C15" t="n">
-        <v>14.56</v>
+        <v>17.47</v>
       </c>
       <c r="D15" t="n">
-        <v>13.7</v>
+        <v>16.08</v>
       </c>
       <c r="E15" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>31</v>
+        <v>260</v>
       </c>
       <c r="H15" t="n">
-        <v>81.01000000000001</v>
+        <v>67.33</v>
       </c>
       <c r="I15" t="n">
-        <v>87.31</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>75.84999999999999</v>
+        <v>63.98</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M15" t="n">
         <v>1.3</v>
       </c>
       <c r="N15" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14.64</v>
+        <v>15.83</v>
       </c>
       <c r="C16" t="n">
-        <v>14.86</v>
+        <v>16.23</v>
       </c>
       <c r="D16" t="n">
-        <v>14.45</v>
+        <v>15.45</v>
       </c>
       <c r="E16" t="n">
         <v>10.9</v>
       </c>
       <c r="F16" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>173</v>
       </c>
       <c r="H16" t="n">
-        <v>79.53</v>
+        <v>72.95</v>
       </c>
       <c r="I16" t="n">
-        <v>82.73999999999999</v>
+        <v>75.03</v>
       </c>
       <c r="J16" t="n">
-        <v>76.79000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N16" t="n">
         <v>6132</v>
@@ -1213,232 +1213,232 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.07</v>
+        <v>15.22</v>
       </c>
       <c r="C17" t="n">
-        <v>15.23</v>
+        <v>15.77</v>
       </c>
       <c r="D17" t="n">
-        <v>14.92</v>
+        <v>14.97</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="F17" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H17" t="n">
         <v>77.61</v>
       </c>
       <c r="I17" t="n">
-        <v>78.94</v>
+        <v>79.25</v>
       </c>
       <c r="J17" t="n">
-        <v>76.67</v>
+        <v>74.45</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N17" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15.37</v>
+        <v>14.79</v>
       </c>
       <c r="C18" t="n">
-        <v>15.49</v>
+        <v>15.1</v>
       </c>
       <c r="D18" t="n">
-        <v>15.25</v>
+        <v>14.32</v>
       </c>
       <c r="E18" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F18" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H18" t="n">
-        <v>79.81999999999999</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>80.69</v>
+        <v>83.36</v>
       </c>
       <c r="J18" t="n">
-        <v>78.86</v>
+        <v>79.05</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N18" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15.65</v>
+        <v>14.05</v>
       </c>
       <c r="C19" t="n">
-        <v>15.77</v>
+        <v>14.26</v>
       </c>
       <c r="D19" t="n">
-        <v>15.48</v>
+        <v>13.8</v>
       </c>
       <c r="E19" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F19" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H19" t="n">
-        <v>78.64</v>
+        <v>85.09</v>
       </c>
       <c r="I19" t="n">
-        <v>80.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>77.23</v>
+        <v>84.14</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.39</v>
+        <v>14.11</v>
       </c>
       <c r="C20" t="n">
-        <v>15.59</v>
+        <v>14.56</v>
       </c>
       <c r="D20" t="n">
-        <v>15.29</v>
+        <v>13.7</v>
       </c>
       <c r="E20" t="n">
-        <v>12.7</v>
+        <v>10.7</v>
       </c>
       <c r="F20" t="n">
-        <v>12.3</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H20" t="n">
-        <v>84.89</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>87.12</v>
+        <v>87.31</v>
       </c>
       <c r="J20" t="n">
-        <v>81.20999999999999</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N20" t="n">
-        <v>6112</v>
+        <v>6132</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.61</v>
+        <v>14.64</v>
       </c>
       <c r="C21" t="n">
-        <v>16.09</v>
+        <v>14.86</v>
       </c>
       <c r="D21" t="n">
-        <v>15.44</v>
+        <v>14.45</v>
       </c>
       <c r="E21" t="n">
-        <v>12.8</v>
+        <v>10.9</v>
       </c>
       <c r="F21" t="n">
-        <v>12.4</v>
+        <v>10.5</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>84.45</v>
+        <v>79.53</v>
       </c>
       <c r="I21" t="n">
-        <v>86.2</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>79</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="N21" t="n">
         <v>6132</v>
@@ -1448,787 +1448,789 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.78</v>
+        <v>15.07</v>
       </c>
       <c r="C22" t="n">
-        <v>17.16</v>
+        <v>15.23</v>
       </c>
       <c r="D22" t="n">
-        <v>16.31</v>
+        <v>14.92</v>
       </c>
       <c r="E22" t="n">
-        <v>11.9</v>
+        <v>11</v>
       </c>
       <c r="F22" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>73.62</v>
+        <v>77.61</v>
       </c>
       <c r="I22" t="n">
-        <v>76.98999999999999</v>
+        <v>78.94</v>
       </c>
       <c r="J22" t="n">
-        <v>69.84</v>
+        <v>76.67</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="M22" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.55</v>
+        <v>15.37</v>
       </c>
       <c r="C23" t="n">
-        <v>17.8</v>
+        <v>15.49</v>
       </c>
       <c r="D23" t="n">
-        <v>17.2</v>
+        <v>15.25</v>
       </c>
       <c r="E23" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="F23" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>71.04000000000001</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>73.81</v>
+        <v>80.69</v>
       </c>
       <c r="J23" t="n">
-        <v>69.28</v>
+        <v>78.86</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="M23" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.63</v>
+        <v>15.65</v>
       </c>
       <c r="C24" t="n">
-        <v>18.08</v>
+        <v>15.77</v>
       </c>
       <c r="D24" t="n">
-        <v>17.4</v>
+        <v>15.48</v>
       </c>
       <c r="E24" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>73.43000000000001</v>
+        <v>78.64</v>
       </c>
       <c r="I24" t="n">
-        <v>76.55</v>
+        <v>80.7</v>
       </c>
       <c r="J24" t="n">
-        <v>68.51000000000001</v>
+        <v>77.23</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="M24" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="N24" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.46</v>
+        <v>15.39</v>
       </c>
       <c r="C25" t="n">
-        <v>17.67</v>
+        <v>15.59</v>
       </c>
       <c r="D25" t="n">
-        <v>17.22</v>
+        <v>15.29</v>
       </c>
       <c r="E25" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>76.84</v>
+        <v>84.89</v>
       </c>
       <c r="I25" t="n">
-        <v>79.37</v>
+        <v>87.12</v>
       </c>
       <c r="J25" t="n">
-        <v>75.08</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M25" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="N25" t="n">
-        <v>6132</v>
+        <v>6112</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17.43</v>
+        <v>15.61</v>
       </c>
       <c r="C26" t="n">
-        <v>17.62</v>
+        <v>16.09</v>
       </c>
       <c r="D26" t="n">
-        <v>17.17</v>
+        <v>15.44</v>
       </c>
       <c r="E26" t="n">
-        <v>13.6</v>
+        <v>12.8</v>
       </c>
       <c r="F26" t="n">
-        <v>13.3</v>
+        <v>12.4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>79.34</v>
+        <v>84.45</v>
       </c>
       <c r="I26" t="n">
-        <v>82.2</v>
+        <v>86.2</v>
       </c>
       <c r="J26" t="n">
-        <v>77.51000000000001</v>
+        <v>79</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="N26" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.89</v>
+        <v>16.78</v>
       </c>
       <c r="C27" t="n">
-        <v>18.13</v>
+        <v>17.16</v>
       </c>
       <c r="D27" t="n">
-        <v>17.76</v>
+        <v>16.31</v>
       </c>
       <c r="E27" t="n">
-        <v>13.4</v>
+        <v>11.9</v>
       </c>
       <c r="F27" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>76.29000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="I27" t="n">
-        <v>78.06999999999999</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>74.34999999999999</v>
+        <v>69.84</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M27" t="n">
         <v>2.2</v>
       </c>
-      <c r="M27" t="n">
-        <v>2.3</v>
-      </c>
       <c r="N27" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.6</v>
+        <v>17.55</v>
       </c>
       <c r="C28" t="n">
-        <v>19.26</v>
+        <v>17.8</v>
       </c>
       <c r="D28" t="n">
-        <v>18.22</v>
+        <v>17.2</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>12.1</v>
       </c>
       <c r="F28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>70.7</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>73.79000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="J28" t="n">
-        <v>65.41</v>
+        <v>69.28</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="N28" t="n">
-        <v>6152</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
+        <v>6142</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>20.29</v>
+        <v>17.63</v>
       </c>
       <c r="C29" t="n">
-        <v>21.69</v>
+        <v>18.08</v>
       </c>
       <c r="D29" t="n">
-        <v>19.3</v>
+        <v>17.4</v>
       </c>
       <c r="E29" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="F29" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>58.46</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>64.93000000000001</v>
+        <v>76.55</v>
       </c>
       <c r="J29" t="n">
-        <v>50.01</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="N29" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.33</v>
+        <v>17.46</v>
       </c>
       <c r="C30" t="n">
-        <v>22.66</v>
+        <v>17.67</v>
       </c>
       <c r="D30" t="n">
-        <v>21.95</v>
+        <v>17.22</v>
       </c>
       <c r="E30" t="n">
-        <v>9.9</v>
+        <v>13.2</v>
       </c>
       <c r="F30" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>46.23</v>
+        <v>76.84</v>
       </c>
       <c r="I30" t="n">
-        <v>48.69</v>
+        <v>79.37</v>
       </c>
       <c r="J30" t="n">
-        <v>44.45</v>
+        <v>75.08</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="N30" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22.97</v>
+        <v>17.43</v>
       </c>
       <c r="C31" t="n">
-        <v>23.49</v>
+        <v>17.62</v>
       </c>
       <c r="D31" t="n">
-        <v>22.63</v>
+        <v>17.17</v>
       </c>
       <c r="E31" t="n">
-        <v>9.5</v>
+        <v>13.6</v>
       </c>
       <c r="F31" t="n">
-        <v>9.4</v>
+        <v>13.3</v>
       </c>
       <c r="G31" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>43.28</v>
+        <v>79.34</v>
       </c>
       <c r="I31" t="n">
-        <v>44.43</v>
+        <v>82.2</v>
       </c>
       <c r="J31" t="n">
-        <v>41.95</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>6180</v>
+        <v>6142</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23.37</v>
+        <v>17.89</v>
       </c>
       <c r="C32" t="n">
-        <v>23.93</v>
+        <v>18.13</v>
       </c>
       <c r="D32" t="n">
-        <v>23.11</v>
+        <v>17.76</v>
       </c>
       <c r="E32" t="n">
-        <v>9.699999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="F32" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="G32" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>42.7</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>44.12</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>41.98</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="M32" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="N32" t="n">
-        <v>6190</v>
+        <v>6142</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23.27</v>
+        <v>18.6</v>
       </c>
       <c r="C33" t="n">
-        <v>23.64</v>
+        <v>19.26</v>
       </c>
       <c r="D33" t="n">
-        <v>22.89</v>
+        <v>18.22</v>
       </c>
       <c r="E33" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="F33" t="n">
-        <v>9.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="G33" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>42.52</v>
+        <v>70.7</v>
       </c>
       <c r="I33" t="n">
-        <v>43.12</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>41.91</v>
+        <v>65.41</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22.93</v>
+        <v>20.29</v>
       </c>
       <c r="C34" t="n">
-        <v>23.35</v>
+        <v>21.69</v>
       </c>
       <c r="D34" t="n">
-        <v>22.54</v>
+        <v>19.3</v>
       </c>
       <c r="E34" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="F34" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="G34" t="n">
-        <v>393</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
-        <v>43.56</v>
+        <v>58.46</v>
       </c>
       <c r="I34" t="n">
-        <v>44.91</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>42.28</v>
+        <v>50.01</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="M34" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.23</v>
+        <v>22.33</v>
       </c>
       <c r="C35" t="n">
-        <v>22.76</v>
+        <v>22.66</v>
       </c>
       <c r="D35" t="n">
-        <v>21.86</v>
+        <v>21.95</v>
       </c>
       <c r="E35" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="F35" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="G35" t="n">
-        <v>383</v>
+        <v>24</v>
       </c>
       <c r="H35" t="n">
-        <v>45.63</v>
+        <v>46.23</v>
       </c>
       <c r="I35" t="n">
-        <v>47.01</v>
+        <v>48.69</v>
       </c>
       <c r="J35" t="n">
-        <v>44.24</v>
+        <v>44.45</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="M35" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="N35" t="n">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21.57</v>
+        <v>22.97</v>
       </c>
       <c r="C36" t="n">
-        <v>22.64</v>
+        <v>23.49</v>
       </c>
       <c r="D36" t="n">
-        <v>20.71</v>
+        <v>22.63</v>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="F36" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G36" t="n">
-        <v>373</v>
+        <v>72</v>
       </c>
       <c r="H36" t="n">
-        <v>48.34</v>
+        <v>43.28</v>
       </c>
       <c r="I36" t="n">
-        <v>51.45</v>
+        <v>44.43</v>
       </c>
       <c r="J36" t="n">
-        <v>45.03</v>
+        <v>41.95</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N36" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>20.3</v>
+        <v>23.37</v>
       </c>
       <c r="C37" t="n">
-        <v>20.76</v>
+        <v>23.93</v>
       </c>
       <c r="D37" t="n">
-        <v>19.87</v>
+        <v>23.11</v>
       </c>
       <c r="E37" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G37" t="n">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="H37" t="n">
-        <v>53.23</v>
+        <v>42.7</v>
       </c>
       <c r="I37" t="n">
-        <v>56.41</v>
+        <v>44.12</v>
       </c>
       <c r="J37" t="n">
-        <v>51.05</v>
+        <v>41.98</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="N37" t="n">
-        <v>6170</v>
+        <v>6190</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>19.38</v>
+        <v>23.27</v>
       </c>
       <c r="C38" t="n">
-        <v>19.85</v>
+        <v>23.64</v>
       </c>
       <c r="D38" t="n">
-        <v>18.89</v>
+        <v>22.89</v>
       </c>
       <c r="E38" t="n">
-        <v>11.6</v>
+        <v>9.6</v>
       </c>
       <c r="F38" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>110</v>
+        <v>326</v>
       </c>
       <c r="H38" t="n">
-        <v>61.37</v>
+        <v>42.52</v>
       </c>
       <c r="I38" t="n">
-        <v>65.44</v>
+        <v>43.12</v>
       </c>
       <c r="J38" t="n">
-        <v>57.45</v>
+        <v>41.91</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2237,242 +2239,242 @@
         <v>0.5</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N38" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>18.52</v>
+        <v>22.93</v>
       </c>
       <c r="C39" t="n">
-        <v>18.87</v>
+        <v>23.35</v>
       </c>
       <c r="D39" t="n">
-        <v>18.23</v>
+        <v>22.54</v>
       </c>
       <c r="E39" t="n">
-        <v>12.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="G39" t="n">
-        <v>34</v>
+        <v>393</v>
       </c>
       <c r="H39" t="n">
-        <v>67.5</v>
+        <v>43.56</v>
       </c>
       <c r="I39" t="n">
-        <v>70.43000000000001</v>
+        <v>44.91</v>
       </c>
       <c r="J39" t="n">
-        <v>65.33</v>
+        <v>42.28</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N39" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.89</v>
+        <v>22.23</v>
       </c>
       <c r="C40" t="n">
-        <v>18.27</v>
+        <v>22.76</v>
       </c>
       <c r="D40" t="n">
-        <v>17.53</v>
+        <v>21.86</v>
       </c>
       <c r="E40" t="n">
-        <v>13.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>12.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>7</v>
+        <v>383</v>
       </c>
       <c r="H40" t="n">
-        <v>74.15000000000001</v>
+        <v>45.63</v>
       </c>
       <c r="I40" t="n">
-        <v>77.34999999999999</v>
+        <v>47.01</v>
       </c>
       <c r="J40" t="n">
-        <v>70.23999999999999</v>
+        <v>44.24</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="N40" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.34</v>
+        <v>21.57</v>
       </c>
       <c r="C41" t="n">
-        <v>17.48</v>
+        <v>22.64</v>
       </c>
       <c r="D41" t="n">
-        <v>17.19</v>
+        <v>20.71</v>
       </c>
       <c r="E41" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>13.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="H41" t="n">
-        <v>78.27</v>
+        <v>48.34</v>
       </c>
       <c r="I41" t="n">
-        <v>79.16</v>
+        <v>51.45</v>
       </c>
       <c r="J41" t="n">
-        <v>77.5</v>
+        <v>45.03</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="N41" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.62</v>
+        <v>20.3</v>
       </c>
       <c r="C42" t="n">
-        <v>17.85</v>
+        <v>20.76</v>
       </c>
       <c r="D42" t="n">
-        <v>17.33</v>
+        <v>19.87</v>
       </c>
       <c r="E42" t="n">
-        <v>12.8</v>
+        <v>10.3</v>
       </c>
       <c r="F42" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="H42" t="n">
-        <v>74.13</v>
+        <v>53.23</v>
       </c>
       <c r="I42" t="n">
-        <v>77.06</v>
+        <v>56.41</v>
       </c>
       <c r="J42" t="n">
-        <v>71.3</v>
+        <v>51.05</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N42" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.72</v>
+        <v>19.38</v>
       </c>
       <c r="C43" t="n">
-        <v>18.84</v>
+        <v>19.85</v>
       </c>
       <c r="D43" t="n">
-        <v>17.46</v>
+        <v>18.89</v>
       </c>
       <c r="E43" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="F43" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H43" t="n">
-        <v>71.95999999999999</v>
+        <v>61.37</v>
       </c>
       <c r="I43" t="n">
-        <v>74.59999999999999</v>
+        <v>65.44</v>
       </c>
       <c r="J43" t="n">
-        <v>65.83</v>
+        <v>57.45</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N43" t="n">
         <v>6152</v>
@@ -2482,44 +2484,44 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.99</v>
+        <v>18.52</v>
       </c>
       <c r="C44" t="n">
-        <v>19.05</v>
+        <v>18.87</v>
       </c>
       <c r="D44" t="n">
-        <v>18.9</v>
+        <v>18.23</v>
       </c>
       <c r="E44" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="F44" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H44" t="n">
-        <v>62.56</v>
+        <v>67.5</v>
       </c>
       <c r="I44" t="n">
-        <v>63.18</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>61.89</v>
+        <v>65.33</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
         <v>6152</v>
@@ -2529,82 +2531,82 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.33</v>
+        <v>17.89</v>
       </c>
       <c r="C45" t="n">
-        <v>19.55</v>
+        <v>18.27</v>
       </c>
       <c r="D45" t="n">
-        <v>19.01</v>
+        <v>17.53</v>
       </c>
       <c r="E45" t="n">
-        <v>11.4</v>
+        <v>13.1</v>
       </c>
       <c r="F45" t="n">
-        <v>11.3</v>
+        <v>12.6</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>60.72</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>62.8</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>59.1</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.52</v>
+        <v>17.34</v>
       </c>
       <c r="C46" t="n">
-        <v>19.58</v>
+        <v>17.48</v>
       </c>
       <c r="D46" t="n">
-        <v>19.46</v>
+        <v>17.19</v>
       </c>
       <c r="E46" t="n">
-        <v>11.4</v>
+        <v>13.3</v>
       </c>
       <c r="F46" t="n">
-        <v>11.2</v>
+        <v>13.1</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>60.01</v>
+        <v>78.27</v>
       </c>
       <c r="I46" t="n">
-        <v>60.64</v>
+        <v>79.16</v>
       </c>
       <c r="J46" t="n">
-        <v>59.58</v>
+        <v>77.5</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2616,42 +2618,42 @@
         <v>0.5</v>
       </c>
       <c r="N46" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>19.62</v>
+        <v>17.62</v>
       </c>
       <c r="C47" t="n">
-        <v>19.71</v>
+        <v>17.85</v>
       </c>
       <c r="D47" t="n">
-        <v>19.49</v>
+        <v>17.33</v>
       </c>
       <c r="E47" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="F47" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>60.63</v>
+        <v>74.13</v>
       </c>
       <c r="I47" t="n">
-        <v>61.71</v>
+        <v>77.06</v>
       </c>
       <c r="J47" t="n">
-        <v>59.73</v>
+        <v>71.3</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2663,91 +2665,89 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>6152</v>
-      </c>
-      <c r="O47" t="n">
-        <v>2.3</v>
-      </c>
+        <v>6142</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19.79</v>
+        <v>17.72</v>
       </c>
       <c r="C48" t="n">
-        <v>20.01</v>
+        <v>18.84</v>
       </c>
       <c r="D48" t="n">
-        <v>19.61</v>
+        <v>17.46</v>
       </c>
       <c r="E48" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="F48" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>60.18</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>61.23</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>59.04</v>
+        <v>65.83</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6142</v>
+        <v>6152</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.19</v>
+        <v>18.99</v>
       </c>
       <c r="C49" t="n">
-        <v>20.36</v>
+        <v>19.05</v>
       </c>
       <c r="D49" t="n">
-        <v>20.01</v>
+        <v>18.9</v>
       </c>
       <c r="E49" t="n">
         <v>11.5</v>
       </c>
       <c r="F49" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>58.19</v>
+        <v>62.56</v>
       </c>
       <c r="I49" t="n">
-        <v>59.14</v>
+        <v>63.18</v>
       </c>
       <c r="J49" t="n">
-        <v>57.54</v>
+        <v>61.89</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2756,45 +2756,45 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>20.44</v>
+        <v>19.33</v>
       </c>
       <c r="C50" t="n">
-        <v>20.64</v>
+        <v>19.55</v>
       </c>
       <c r="D50" t="n">
-        <v>20.37</v>
+        <v>19.01</v>
       </c>
       <c r="E50" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F50" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>57.96</v>
+        <v>60.72</v>
       </c>
       <c r="I50" t="n">
-        <v>58.31</v>
+        <v>62.8</v>
       </c>
       <c r="J50" t="n">
-        <v>57.52</v>
+        <v>59.1</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2803,13 +2803,13 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N50" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O50" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,44 +508,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15.75</v>
+        <v>16.33</v>
       </c>
       <c r="C2" t="n">
-        <v>15.77</v>
+        <v>16.46</v>
       </c>
       <c r="D2" t="n">
-        <v>15.72</v>
+        <v>16.2</v>
       </c>
       <c r="E2" t="n">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="F2" t="n">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>80.33</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>80.62</v>
+        <v>77.45</v>
       </c>
       <c r="J2" t="n">
-        <v>80.16</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.8</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.1</v>
       </c>
       <c r="N2" t="n">
         <v>6112</v>
@@ -555,44 +555,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.09</v>
+        <v>15.62</v>
       </c>
       <c r="C3" t="n">
-        <v>16.59</v>
+        <v>16.07</v>
       </c>
       <c r="D3" t="n">
-        <v>15.76</v>
+        <v>15.35</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="F3" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>76.7</v>
+        <v>85.33</v>
       </c>
       <c r="I3" t="n">
-        <v>80.06999999999999</v>
+        <v>89.23</v>
       </c>
       <c r="J3" t="n">
-        <v>72.89</v>
+        <v>79.03</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>6122</v>
@@ -602,44 +602,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.2</v>
+        <v>15.25</v>
       </c>
       <c r="C4" t="n">
-        <v>16.53</v>
+        <v>15.35</v>
       </c>
       <c r="D4" t="n">
-        <v>15.84</v>
+        <v>15.06</v>
       </c>
       <c r="E4" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="F4" t="n">
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>77.2</v>
+        <v>89.16</v>
       </c>
       <c r="I4" t="n">
-        <v>80.54000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="J4" t="n">
-        <v>73.31999999999999</v>
+        <v>87.77</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>6122</v>
@@ -649,44 +649,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.03</v>
+        <v>15.2</v>
       </c>
       <c r="C5" t="n">
-        <v>16.12</v>
+        <v>15.32</v>
       </c>
       <c r="D5" t="n">
-        <v>15.93</v>
+        <v>15.08</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="F5" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>77.56</v>
+        <v>88.42</v>
       </c>
       <c r="I5" t="n">
-        <v>79.16</v>
+        <v>89.37</v>
       </c>
       <c r="J5" t="n">
-        <v>76.79000000000001</v>
+        <v>87.13</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>6122</v>
@@ -696,44 +696,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.79</v>
+        <v>15.53</v>
       </c>
       <c r="C6" t="n">
-        <v>15.92</v>
+        <v>15.66</v>
       </c>
       <c r="D6" t="n">
-        <v>15.7</v>
+        <v>15.45</v>
       </c>
       <c r="E6" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="F6" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>78.34999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>78.65000000000001</v>
+        <v>86.58</v>
       </c>
       <c r="J6" t="n">
-        <v>77.79000000000001</v>
+        <v>83.42</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>6122</v>
@@ -743,44 +743,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.9</v>
+        <v>15.66</v>
       </c>
       <c r="C7" t="n">
-        <v>16.37</v>
+        <v>15.73</v>
       </c>
       <c r="D7" t="n">
-        <v>15.67</v>
+        <v>15.62</v>
       </c>
       <c r="E7" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>76.45999999999999</v>
+        <v>82.52</v>
       </c>
       <c r="I7" t="n">
-        <v>78.44</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>72.33</v>
+        <v>82.33</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
         <v>6122</v>
@@ -790,223 +790,223 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.37</v>
+        <v>15.72</v>
       </c>
       <c r="C8" t="n">
-        <v>16.48</v>
+        <v>15.77</v>
       </c>
       <c r="D8" t="n">
-        <v>16.29</v>
+        <v>15.65</v>
       </c>
       <c r="E8" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="F8" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>74.02</v>
+        <v>81.17</v>
       </c>
       <c r="I8" t="n">
-        <v>74.88</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>72.13</v>
+        <v>80.16</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.84</v>
+        <v>16.09</v>
       </c>
       <c r="C9" t="n">
-        <v>17.08</v>
+        <v>16.59</v>
       </c>
       <c r="D9" t="n">
-        <v>16.57</v>
+        <v>15.76</v>
       </c>
       <c r="E9" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="F9" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>70.64</v>
+        <v>76.7</v>
       </c>
       <c r="I9" t="n">
+        <v>80.06999999999999</v>
+      </c>
+      <c r="J9" t="n">
         <v>72.89</v>
       </c>
-      <c r="J9" t="n">
-        <v>68.62</v>
-      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N9" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.26</v>
+        <v>16.2</v>
       </c>
       <c r="C10" t="n">
-        <v>17.41</v>
+        <v>16.53</v>
       </c>
       <c r="D10" t="n">
-        <v>17.13</v>
+        <v>15.84</v>
       </c>
       <c r="E10" t="n">
-        <v>10.7</v>
+        <v>12.1</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>11.6</v>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>65.97</v>
+        <v>77.2</v>
       </c>
       <c r="I10" t="n">
-        <v>68.3</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>62.44</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N10" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.57</v>
+        <v>16.03</v>
       </c>
       <c r="C11" t="n">
-        <v>18.11</v>
+        <v>16.12</v>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>15.93</v>
       </c>
       <c r="E11" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>9.800000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>63.38</v>
+        <v>77.56</v>
       </c>
       <c r="I11" t="n">
-        <v>64.3</v>
+        <v>79.16</v>
       </c>
       <c r="J11" t="n">
-        <v>61.77</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="N11" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>15.79</v>
       </c>
       <c r="C12" t="n">
-        <v>18.2</v>
+        <v>15.92</v>
       </c>
       <c r="D12" t="n">
-        <v>17.79</v>
+        <v>15.7</v>
       </c>
       <c r="E12" t="n">
-        <v>10.6</v>
+        <v>11.9</v>
       </c>
       <c r="F12" t="n">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
       <c r="G12" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>62.96</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>64.08</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>61.81</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1018,192 +1018,192 @@
         <v>1.3</v>
       </c>
       <c r="N12" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18.15</v>
+        <v>15.9</v>
       </c>
       <c r="C13" t="n">
-        <v>18.5</v>
+        <v>16.37</v>
       </c>
       <c r="D13" t="n">
-        <v>17.92</v>
+        <v>15.67</v>
       </c>
       <c r="E13" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="G13" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>60.86</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>62.23</v>
+        <v>78.44</v>
       </c>
       <c r="J13" t="n">
-        <v>59.51</v>
+        <v>72.33</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N13" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.71</v>
+        <v>16.37</v>
       </c>
       <c r="C14" t="n">
-        <v>18.05</v>
+        <v>16.48</v>
       </c>
       <c r="D14" t="n">
-        <v>17.31</v>
+        <v>16.29</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1</v>
+        <v>11.6</v>
       </c>
       <c r="F14" t="n">
-        <v>9.9</v>
+        <v>11.3</v>
       </c>
       <c r="G14" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>61.59</v>
+        <v>74.02</v>
       </c>
       <c r="I14" t="n">
-        <v>63.45</v>
+        <v>74.88</v>
       </c>
       <c r="J14" t="n">
-        <v>59.82</v>
+        <v>72.13</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="N14" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.72</v>
+        <v>16.84</v>
       </c>
       <c r="C15" t="n">
-        <v>17.47</v>
+        <v>17.08</v>
       </c>
       <c r="D15" t="n">
-        <v>16.08</v>
+        <v>16.57</v>
       </c>
       <c r="E15" t="n">
-        <v>10.4</v>
+        <v>11.3</v>
       </c>
       <c r="F15" t="n">
-        <v>9.800000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="G15" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>67.33</v>
+        <v>70.64</v>
       </c>
       <c r="I15" t="n">
-        <v>70.81999999999999</v>
+        <v>72.89</v>
       </c>
       <c r="J15" t="n">
-        <v>63.98</v>
+        <v>68.62</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="N15" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.83</v>
+        <v>17.26</v>
       </c>
       <c r="C16" t="n">
-        <v>16.23</v>
+        <v>17.41</v>
       </c>
       <c r="D16" t="n">
-        <v>15.45</v>
+        <v>17.13</v>
       </c>
       <c r="E16" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="F16" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>173</v>
+        <v>11</v>
       </c>
       <c r="H16" t="n">
-        <v>72.95</v>
+        <v>65.97</v>
       </c>
       <c r="I16" t="n">
-        <v>75.03</v>
+        <v>68.3</v>
       </c>
       <c r="J16" t="n">
-        <v>69.84999999999999</v>
+        <v>62.44</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="N16" t="n">
         <v>6132</v>
@@ -1213,138 +1213,138 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.22</v>
+        <v>17.57</v>
       </c>
       <c r="C17" t="n">
-        <v>15.77</v>
+        <v>18.11</v>
       </c>
       <c r="D17" t="n">
-        <v>14.97</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="F17" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="H17" t="n">
-        <v>77.61</v>
+        <v>63.38</v>
       </c>
       <c r="I17" t="n">
-        <v>79.25</v>
+        <v>64.3</v>
       </c>
       <c r="J17" t="n">
-        <v>74.45</v>
+        <v>61.77</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N17" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14.79</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>15.1</v>
+        <v>18.2</v>
       </c>
       <c r="D18" t="n">
-        <v>14.32</v>
+        <v>17.79</v>
       </c>
       <c r="E18" t="n">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
       <c r="F18" t="n">
-        <v>11.2</v>
+        <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="H18" t="n">
-        <v>80.70999999999999</v>
+        <v>62.96</v>
       </c>
       <c r="I18" t="n">
-        <v>83.36</v>
+        <v>64.08</v>
       </c>
       <c r="J18" t="n">
-        <v>79.05</v>
+        <v>61.81</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N18" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14.05</v>
+        <v>18.15</v>
       </c>
       <c r="C19" t="n">
-        <v>14.26</v>
+        <v>18.5</v>
       </c>
       <c r="D19" t="n">
-        <v>13.8</v>
+        <v>17.92</v>
       </c>
       <c r="E19" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="F19" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="H19" t="n">
-        <v>85.09</v>
+        <v>60.86</v>
       </c>
       <c r="I19" t="n">
-        <v>86.40000000000001</v>
+        <v>62.23</v>
       </c>
       <c r="J19" t="n">
-        <v>84.14</v>
+        <v>59.51</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M19" t="n">
         <v>1.1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.4</v>
       </c>
       <c r="N19" t="n">
         <v>6142</v>
@@ -1354,138 +1354,138 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14.11</v>
+        <v>17.71</v>
       </c>
       <c r="C20" t="n">
-        <v>14.56</v>
+        <v>18.05</v>
       </c>
       <c r="D20" t="n">
-        <v>13.7</v>
+        <v>17.31</v>
       </c>
       <c r="E20" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="G20" t="n">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="H20" t="n">
-        <v>81.01000000000001</v>
+        <v>61.59</v>
       </c>
       <c r="I20" t="n">
-        <v>87.31</v>
+        <v>63.45</v>
       </c>
       <c r="J20" t="n">
-        <v>75.84999999999999</v>
+        <v>59.82</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="N20" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.64</v>
+        <v>16.72</v>
       </c>
       <c r="C21" t="n">
-        <v>14.86</v>
+        <v>17.47</v>
       </c>
       <c r="D21" t="n">
-        <v>14.45</v>
+        <v>16.08</v>
       </c>
       <c r="E21" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F21" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="H21" t="n">
-        <v>79.53</v>
+        <v>67.33</v>
       </c>
       <c r="I21" t="n">
-        <v>82.73999999999999</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>76.79000000000001</v>
+        <v>63.98</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="N21" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15.07</v>
+        <v>15.83</v>
       </c>
       <c r="C22" t="n">
-        <v>15.23</v>
+        <v>16.23</v>
       </c>
       <c r="D22" t="n">
-        <v>14.92</v>
+        <v>15.45</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="F22" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="H22" t="n">
-        <v>77.61</v>
+        <v>72.95</v>
       </c>
       <c r="I22" t="n">
-        <v>78.94</v>
+        <v>75.03</v>
       </c>
       <c r="J22" t="n">
-        <v>76.67</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N22" t="n">
         <v>6132</v>
@@ -1495,185 +1495,185 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15.37</v>
+        <v>15.22</v>
       </c>
       <c r="C23" t="n">
-        <v>15.49</v>
+        <v>15.77</v>
       </c>
       <c r="D23" t="n">
-        <v>15.25</v>
+        <v>14.97</v>
       </c>
       <c r="E23" t="n">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="F23" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H23" t="n">
-        <v>79.81999999999999</v>
+        <v>77.61</v>
       </c>
       <c r="I23" t="n">
-        <v>80.69</v>
+        <v>79.25</v>
       </c>
       <c r="J23" t="n">
-        <v>78.86</v>
+        <v>74.45</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N23" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.65</v>
+        <v>14.79</v>
       </c>
       <c r="C24" t="n">
-        <v>15.77</v>
+        <v>15.1</v>
       </c>
       <c r="D24" t="n">
-        <v>15.48</v>
+        <v>14.32</v>
       </c>
       <c r="E24" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F24" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H24" t="n">
-        <v>78.64</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>80.7</v>
+        <v>83.36</v>
       </c>
       <c r="J24" t="n">
-        <v>77.23</v>
+        <v>79.05</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15.39</v>
+        <v>14.05</v>
       </c>
       <c r="C25" t="n">
-        <v>15.59</v>
+        <v>14.26</v>
       </c>
       <c r="D25" t="n">
-        <v>15.29</v>
+        <v>13.8</v>
       </c>
       <c r="E25" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="F25" t="n">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H25" t="n">
-        <v>84.89</v>
+        <v>85.09</v>
       </c>
       <c r="I25" t="n">
-        <v>87.12</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>81.20999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="M25" t="n">
         <v>1.4</v>
       </c>
       <c r="N25" t="n">
-        <v>6112</v>
+        <v>6142</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15.61</v>
+        <v>14.11</v>
       </c>
       <c r="C26" t="n">
-        <v>16.09</v>
+        <v>14.56</v>
       </c>
       <c r="D26" t="n">
-        <v>15.44</v>
+        <v>13.7</v>
       </c>
       <c r="E26" t="n">
-        <v>12.8</v>
+        <v>10.7</v>
       </c>
       <c r="F26" t="n">
-        <v>12.4</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H26" t="n">
-        <v>84.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>86.2</v>
+        <v>87.31</v>
       </c>
       <c r="J26" t="n">
-        <v>79</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N26" t="n">
         <v>6132</v>
@@ -1683,187 +1683,185 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.78</v>
+        <v>14.64</v>
       </c>
       <c r="C27" t="n">
-        <v>17.16</v>
+        <v>14.86</v>
       </c>
       <c r="D27" t="n">
-        <v>16.31</v>
+        <v>14.45</v>
       </c>
       <c r="E27" t="n">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="F27" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>73.62</v>
+        <v>79.53</v>
       </c>
       <c r="I27" t="n">
-        <v>76.98999999999999</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>69.84</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="N27" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17.55</v>
+        <v>15.07</v>
       </c>
       <c r="C28" t="n">
-        <v>17.8</v>
+        <v>15.23</v>
       </c>
       <c r="D28" t="n">
-        <v>17.2</v>
+        <v>14.92</v>
       </c>
       <c r="E28" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>71.04000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="I28" t="n">
-        <v>73.81</v>
+        <v>78.94</v>
       </c>
       <c r="J28" t="n">
-        <v>69.28</v>
+        <v>76.67</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M28" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>6142</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.6</v>
-      </c>
+        <v>6132</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.63</v>
+        <v>15.37</v>
       </c>
       <c r="C29" t="n">
-        <v>18.08</v>
+        <v>15.49</v>
       </c>
       <c r="D29" t="n">
-        <v>17.4</v>
+        <v>15.25</v>
       </c>
       <c r="E29" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>73.43000000000001</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>76.55</v>
+        <v>80.69</v>
       </c>
       <c r="J29" t="n">
-        <v>68.51000000000001</v>
+        <v>78.86</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="M29" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.46</v>
+        <v>15.65</v>
       </c>
       <c r="C30" t="n">
-        <v>17.67</v>
+        <v>15.77</v>
       </c>
       <c r="D30" t="n">
-        <v>17.22</v>
+        <v>15.48</v>
       </c>
       <c r="E30" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>11.6</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>76.84</v>
+        <v>78.64</v>
       </c>
       <c r="I30" t="n">
-        <v>79.37</v>
+        <v>80.7</v>
       </c>
       <c r="J30" t="n">
-        <v>75.08</v>
+        <v>77.23</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="M30" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="N30" t="n">
         <v>6132</v>
@@ -1873,693 +1871,695 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.43</v>
+        <v>15.39</v>
       </c>
       <c r="C31" t="n">
-        <v>17.62</v>
+        <v>15.59</v>
       </c>
       <c r="D31" t="n">
-        <v>17.17</v>
+        <v>15.29</v>
       </c>
       <c r="E31" t="n">
-        <v>13.6</v>
+        <v>12.7</v>
       </c>
       <c r="F31" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>79.34</v>
+        <v>84.89</v>
       </c>
       <c r="I31" t="n">
-        <v>82.2</v>
+        <v>87.12</v>
       </c>
       <c r="J31" t="n">
-        <v>77.51000000000001</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N31" t="n">
-        <v>6142</v>
+        <v>6112</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.89</v>
+        <v>15.61</v>
       </c>
       <c r="C32" t="n">
-        <v>18.13</v>
+        <v>16.09</v>
       </c>
       <c r="D32" t="n">
-        <v>17.76</v>
+        <v>15.44</v>
       </c>
       <c r="E32" t="n">
-        <v>13.4</v>
+        <v>12.8</v>
       </c>
       <c r="F32" t="n">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>76.29000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="I32" t="n">
-        <v>78.06999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="J32" t="n">
-        <v>74.34999999999999</v>
+        <v>79</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="M32" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="N32" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>18.6</v>
+        <v>16.78</v>
       </c>
       <c r="C33" t="n">
-        <v>19.26</v>
+        <v>17.16</v>
       </c>
       <c r="D33" t="n">
-        <v>18.22</v>
+        <v>16.31</v>
       </c>
       <c r="E33" t="n">
-        <v>13</v>
+        <v>11.9</v>
       </c>
       <c r="F33" t="n">
-        <v>12.5</v>
+        <v>11.4</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>70.7</v>
+        <v>73.62</v>
       </c>
       <c r="I33" t="n">
-        <v>73.79000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>65.41</v>
+        <v>69.84</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="N33" t="n">
-        <v>6152</v>
+        <v>6122</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>20.29</v>
+        <v>17.55</v>
       </c>
       <c r="C34" t="n">
-        <v>21.69</v>
+        <v>17.8</v>
       </c>
       <c r="D34" t="n">
-        <v>19.3</v>
+        <v>17.2</v>
       </c>
       <c r="E34" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="F34" t="n">
-        <v>10.7</v>
+        <v>11.8</v>
       </c>
       <c r="G34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>58.46</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>64.93000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="J34" t="n">
-        <v>50.01</v>
+        <v>69.28</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="N34" t="n">
-        <v>6162</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
+        <v>6142</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.33</v>
+        <v>17.63</v>
       </c>
       <c r="C35" t="n">
-        <v>22.66</v>
+        <v>18.08</v>
       </c>
       <c r="D35" t="n">
-        <v>21.95</v>
+        <v>17.4</v>
       </c>
       <c r="E35" t="n">
-        <v>9.9</v>
+        <v>12.6</v>
       </c>
       <c r="F35" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>46.23</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>48.69</v>
+        <v>76.55</v>
       </c>
       <c r="J35" t="n">
-        <v>44.45</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M35" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="N35" t="n">
-        <v>6170</v>
+        <v>6122</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>22.97</v>
+        <v>17.46</v>
       </c>
       <c r="C36" t="n">
-        <v>23.49</v>
+        <v>17.67</v>
       </c>
       <c r="D36" t="n">
-        <v>22.63</v>
+        <v>17.22</v>
       </c>
       <c r="E36" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="F36" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="G36" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>43.28</v>
+        <v>76.84</v>
       </c>
       <c r="I36" t="n">
-        <v>44.43</v>
+        <v>79.37</v>
       </c>
       <c r="J36" t="n">
-        <v>41.95</v>
+        <v>75.08</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="N36" t="n">
-        <v>6180</v>
+        <v>6132</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>23.37</v>
+        <v>17.43</v>
       </c>
       <c r="C37" t="n">
-        <v>23.93</v>
+        <v>17.62</v>
       </c>
       <c r="D37" t="n">
-        <v>23.11</v>
+        <v>17.17</v>
       </c>
       <c r="E37" t="n">
-        <v>9.699999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="F37" t="n">
-        <v>9.5</v>
+        <v>13.3</v>
       </c>
       <c r="G37" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>42.7</v>
+        <v>79.34</v>
       </c>
       <c r="I37" t="n">
-        <v>44.12</v>
+        <v>82.2</v>
       </c>
       <c r="J37" t="n">
-        <v>41.98</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M37" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>6190</v>
+        <v>6142</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>23.27</v>
+        <v>17.89</v>
       </c>
       <c r="C38" t="n">
-        <v>23.64</v>
+        <v>18.13</v>
       </c>
       <c r="D38" t="n">
-        <v>22.89</v>
+        <v>17.76</v>
       </c>
       <c r="E38" t="n">
-        <v>9.6</v>
+        <v>13.4</v>
       </c>
       <c r="F38" t="n">
-        <v>9.300000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="G38" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>42.52</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>43.12</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>41.91</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="N38" t="n">
-        <v>6190</v>
+        <v>6142</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>22.93</v>
+        <v>18.6</v>
       </c>
       <c r="C39" t="n">
-        <v>23.35</v>
+        <v>19.26</v>
       </c>
       <c r="D39" t="n">
-        <v>22.54</v>
+        <v>18.22</v>
       </c>
       <c r="E39" t="n">
-        <v>9.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="F39" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="G39" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>43.56</v>
+        <v>70.7</v>
       </c>
       <c r="I39" t="n">
-        <v>44.91</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>42.28</v>
+        <v>65.41</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="M39" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>22.23</v>
+        <v>20.29</v>
       </c>
       <c r="C40" t="n">
-        <v>22.76</v>
+        <v>21.69</v>
       </c>
       <c r="D40" t="n">
-        <v>21.86</v>
+        <v>19.3</v>
       </c>
       <c r="E40" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="F40" t="n">
-        <v>9.300000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G40" t="n">
-        <v>383</v>
+        <v>9</v>
       </c>
       <c r="H40" t="n">
-        <v>45.63</v>
+        <v>58.46</v>
       </c>
       <c r="I40" t="n">
-        <v>47.01</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>44.24</v>
+        <v>50.01</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="M40" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>21.57</v>
+        <v>22.33</v>
       </c>
       <c r="C41" t="n">
-        <v>22.64</v>
+        <v>22.66</v>
       </c>
       <c r="D41" t="n">
-        <v>20.71</v>
+        <v>21.95</v>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="F41" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="G41" t="n">
-        <v>373</v>
+        <v>24</v>
       </c>
       <c r="H41" t="n">
-        <v>48.34</v>
+        <v>46.23</v>
       </c>
       <c r="I41" t="n">
-        <v>51.45</v>
+        <v>48.69</v>
       </c>
       <c r="J41" t="n">
-        <v>45.03</v>
+        <v>44.45</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="M41" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="N41" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>20.3</v>
+        <v>22.97</v>
       </c>
       <c r="C42" t="n">
-        <v>20.76</v>
+        <v>23.49</v>
       </c>
       <c r="D42" t="n">
-        <v>19.87</v>
+        <v>22.63</v>
       </c>
       <c r="E42" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="G42" t="n">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="H42" t="n">
-        <v>53.23</v>
+        <v>43.28</v>
       </c>
       <c r="I42" t="n">
-        <v>56.41</v>
+        <v>44.43</v>
       </c>
       <c r="J42" t="n">
-        <v>51.05</v>
+        <v>41.95</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N42" t="n">
-        <v>6170</v>
+        <v>6180</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.38</v>
+        <v>23.37</v>
       </c>
       <c r="C43" t="n">
-        <v>19.85</v>
+        <v>23.93</v>
       </c>
       <c r="D43" t="n">
-        <v>18.89</v>
+        <v>23.11</v>
       </c>
       <c r="E43" t="n">
-        <v>11.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="G43" t="n">
-        <v>110</v>
+        <v>271</v>
       </c>
       <c r="H43" t="n">
-        <v>61.37</v>
+        <v>42.7</v>
       </c>
       <c r="I43" t="n">
-        <v>65.44</v>
+        <v>44.12</v>
       </c>
       <c r="J43" t="n">
-        <v>57.45</v>
+        <v>41.98</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="N43" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.52</v>
+        <v>23.27</v>
       </c>
       <c r="C44" t="n">
-        <v>18.87</v>
+        <v>23.64</v>
       </c>
       <c r="D44" t="n">
-        <v>18.23</v>
+        <v>22.89</v>
       </c>
       <c r="E44" t="n">
-        <v>12.2</v>
+        <v>9.6</v>
       </c>
       <c r="F44" t="n">
-        <v>12</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="H44" t="n">
-        <v>67.5</v>
+        <v>42.52</v>
       </c>
       <c r="I44" t="n">
-        <v>70.43000000000001</v>
+        <v>43.12</v>
       </c>
       <c r="J44" t="n">
-        <v>65.33</v>
+        <v>41.91</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N44" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.89</v>
+        <v>22.93</v>
       </c>
       <c r="C45" t="n">
-        <v>18.27</v>
+        <v>23.35</v>
       </c>
       <c r="D45" t="n">
-        <v>17.53</v>
+        <v>22.54</v>
       </c>
       <c r="E45" t="n">
-        <v>13.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>12.6</v>
+        <v>9.4</v>
       </c>
       <c r="G45" t="n">
-        <v>7</v>
+        <v>393</v>
       </c>
       <c r="H45" t="n">
-        <v>74.15000000000001</v>
+        <v>43.56</v>
       </c>
       <c r="I45" t="n">
-        <v>77.34999999999999</v>
+        <v>44.91</v>
       </c>
       <c r="J45" t="n">
-        <v>70.23999999999999</v>
+        <v>42.28</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2568,195 +2568,195 @@
         <v>0.6</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N45" t="n">
-        <v>6142</v>
+        <v>6190</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.34</v>
+        <v>22.23</v>
       </c>
       <c r="C46" t="n">
-        <v>17.48</v>
+        <v>22.76</v>
       </c>
       <c r="D46" t="n">
-        <v>17.19</v>
+        <v>21.86</v>
       </c>
       <c r="E46" t="n">
-        <v>13.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>13.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="H46" t="n">
-        <v>78.27</v>
+        <v>45.63</v>
       </c>
       <c r="I46" t="n">
-        <v>79.16</v>
+        <v>47.01</v>
       </c>
       <c r="J46" t="n">
-        <v>77.5</v>
+        <v>44.24</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="M46" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="N46" t="n">
-        <v>6132</v>
+        <v>6180</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.62</v>
+        <v>21.57</v>
       </c>
       <c r="C47" t="n">
-        <v>17.85</v>
+        <v>22.64</v>
       </c>
       <c r="D47" t="n">
-        <v>17.33</v>
+        <v>20.71</v>
       </c>
       <c r="E47" t="n">
-        <v>12.8</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>12.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="H47" t="n">
-        <v>74.13</v>
+        <v>48.34</v>
       </c>
       <c r="I47" t="n">
-        <v>77.06</v>
+        <v>51.45</v>
       </c>
       <c r="J47" t="n">
-        <v>71.3</v>
+        <v>45.03</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N47" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.72</v>
+        <v>20.3</v>
       </c>
       <c r="C48" t="n">
-        <v>18.84</v>
+        <v>20.76</v>
       </c>
       <c r="D48" t="n">
-        <v>17.46</v>
+        <v>19.87</v>
       </c>
       <c r="E48" t="n">
-        <v>12.4</v>
+        <v>10.3</v>
       </c>
       <c r="F48" t="n">
-        <v>12.1</v>
+        <v>10</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="H48" t="n">
-        <v>71.95999999999999</v>
+        <v>53.23</v>
       </c>
       <c r="I48" t="n">
-        <v>74.59999999999999</v>
+        <v>56.41</v>
       </c>
       <c r="J48" t="n">
-        <v>65.83</v>
+        <v>51.05</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N48" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>18.99</v>
+        <v>19.38</v>
       </c>
       <c r="C49" t="n">
-        <v>19.05</v>
+        <v>19.85</v>
       </c>
       <c r="D49" t="n">
-        <v>18.9</v>
+        <v>18.89</v>
       </c>
       <c r="E49" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F49" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H49" t="n">
-        <v>62.56</v>
+        <v>61.37</v>
       </c>
       <c r="I49" t="n">
-        <v>63.18</v>
+        <v>65.44</v>
       </c>
       <c r="J49" t="n">
-        <v>61.89</v>
+        <v>57.45</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N49" t="n">
         <v>6152</v>
@@ -2766,47 +2766,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>19.33</v>
+        <v>18.52</v>
       </c>
       <c r="C50" t="n">
-        <v>19.55</v>
+        <v>18.87</v>
       </c>
       <c r="D50" t="n">
-        <v>19.01</v>
+        <v>18.23</v>
       </c>
       <c r="E50" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="F50" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H50" t="n">
-        <v>60.72</v>
+        <v>67.5</v>
       </c>
       <c r="I50" t="n">
-        <v>62.8</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>59.1</v>
+        <v>65.33</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O50" t="n">
         <v>2.3</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,373 +508,373 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.33</v>
+        <v>22.35</v>
       </c>
       <c r="C2" t="n">
-        <v>16.46</v>
+        <v>22.6</v>
       </c>
       <c r="D2" t="n">
-        <v>16.2</v>
+        <v>22.16</v>
       </c>
       <c r="E2" t="n">
-        <v>11.9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>11.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>31</v>
+        <v>411</v>
       </c>
       <c r="H2" t="n">
-        <v>75.79000000000001</v>
+        <v>46.16</v>
       </c>
       <c r="I2" t="n">
-        <v>77.45</v>
+        <v>47.21</v>
       </c>
       <c r="J2" t="n">
-        <v>74.06999999999999</v>
+        <v>45.53</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>6112</v>
+        <v>6210</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.62</v>
+        <v>22.58</v>
       </c>
       <c r="C3" t="n">
-        <v>16.07</v>
+        <v>23.47</v>
       </c>
       <c r="D3" t="n">
-        <v>15.35</v>
+        <v>21.83</v>
       </c>
       <c r="E3" t="n">
-        <v>12.9</v>
+        <v>10.1</v>
       </c>
       <c r="F3" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>815</v>
       </c>
       <c r="H3" t="n">
-        <v>85.33</v>
+        <v>45.81</v>
       </c>
       <c r="I3" t="n">
-        <v>89.23</v>
+        <v>48.66</v>
       </c>
       <c r="J3" t="n">
-        <v>79.03</v>
+        <v>43.93</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="N3" t="n">
-        <v>6122</v>
+        <v>6220</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.25</v>
+        <v>21.31</v>
       </c>
       <c r="C4" t="n">
-        <v>15.35</v>
+        <v>22.4</v>
       </c>
       <c r="D4" t="n">
-        <v>15.06</v>
+        <v>20.2</v>
       </c>
       <c r="E4" t="n">
-        <v>13.3</v>
+        <v>10.4</v>
       </c>
       <c r="F4" t="n">
-        <v>13.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>689</v>
       </c>
       <c r="H4" t="n">
-        <v>89.16</v>
+        <v>50.33</v>
       </c>
       <c r="I4" t="n">
-        <v>91.05</v>
+        <v>56.08</v>
       </c>
       <c r="J4" t="n">
-        <v>87.77</v>
+        <v>47.33</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>6122</v>
+        <v>6190</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.2</v>
+        <v>18.91</v>
       </c>
       <c r="C5" t="n">
-        <v>15.32</v>
+        <v>19.91</v>
       </c>
       <c r="D5" t="n">
-        <v>15.08</v>
+        <v>18.4</v>
       </c>
       <c r="E5" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="F5" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="H5" t="n">
-        <v>88.42</v>
+        <v>60.58</v>
       </c>
       <c r="I5" t="n">
-        <v>89.37</v>
+        <v>63.06</v>
       </c>
       <c r="J5" t="n">
-        <v>87.13</v>
+        <v>55.94</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N5" t="n">
-        <v>6122</v>
+        <v>6162</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.53</v>
+        <v>17.94</v>
       </c>
       <c r="C6" t="n">
-        <v>15.66</v>
+        <v>18.46</v>
       </c>
       <c r="D6" t="n">
-        <v>15.45</v>
+        <v>17.55</v>
       </c>
       <c r="E6" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="F6" t="n">
-        <v>12.7</v>
+        <v>11.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H6" t="n">
-        <v>85.40000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>86.58</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>83.42</v>
+        <v>64.44</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>6122</v>
+        <v>6152</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.66</v>
+        <v>17.55</v>
       </c>
       <c r="C7" t="n">
-        <v>15.73</v>
+        <v>17.81</v>
       </c>
       <c r="D7" t="n">
-        <v>15.62</v>
+        <v>17.2</v>
       </c>
       <c r="E7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="F7" t="n">
-        <v>12.5</v>
+        <v>10.9</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H7" t="n">
-        <v>82.52</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>82.76000000000001</v>
+        <v>69.95</v>
       </c>
       <c r="J7" t="n">
-        <v>82.33</v>
+        <v>65.48</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N7" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.72</v>
+        <v>16.64</v>
       </c>
       <c r="C8" t="n">
-        <v>15.77</v>
+        <v>17.06</v>
       </c>
       <c r="D8" t="n">
-        <v>15.65</v>
+        <v>16.2</v>
       </c>
       <c r="E8" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.3</v>
+        <v>11.4</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H8" t="n">
-        <v>81.17</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>82.40000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="J8" t="n">
-        <v>80.16</v>
+        <v>70.3</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N8" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.09</v>
+        <v>15.62</v>
       </c>
       <c r="C9" t="n">
-        <v>16.59</v>
+        <v>16.07</v>
       </c>
       <c r="D9" t="n">
-        <v>15.76</v>
+        <v>15.35</v>
       </c>
       <c r="E9" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="F9" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>76.7</v>
+        <v>85.33</v>
       </c>
       <c r="I9" t="n">
-        <v>80.06999999999999</v>
+        <v>89.23</v>
       </c>
       <c r="J9" t="n">
-        <v>72.89</v>
+        <v>79.03</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>6122</v>
@@ -884,44 +884,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.2</v>
+        <v>15.25</v>
       </c>
       <c r="C10" t="n">
-        <v>16.53</v>
+        <v>15.35</v>
       </c>
       <c r="D10" t="n">
-        <v>15.84</v>
+        <v>15.06</v>
       </c>
       <c r="E10" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="F10" t="n">
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>77.2</v>
+        <v>89.16</v>
       </c>
       <c r="I10" t="n">
-        <v>80.54000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="J10" t="n">
-        <v>73.31999999999999</v>
+        <v>87.77</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>6122</v>
@@ -931,44 +931,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16.03</v>
+        <v>15.2</v>
       </c>
       <c r="C11" t="n">
-        <v>16.12</v>
+        <v>15.32</v>
       </c>
       <c r="D11" t="n">
-        <v>15.93</v>
+        <v>15.08</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="F11" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>77.56</v>
+        <v>88.42</v>
       </c>
       <c r="I11" t="n">
-        <v>79.16</v>
+        <v>89.37</v>
       </c>
       <c r="J11" t="n">
-        <v>76.79000000000001</v>
+        <v>87.13</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>6122</v>
@@ -978,44 +978,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.79</v>
+        <v>15.53</v>
       </c>
       <c r="C12" t="n">
-        <v>15.92</v>
+        <v>15.66</v>
       </c>
       <c r="D12" t="n">
-        <v>15.7</v>
+        <v>15.45</v>
       </c>
       <c r="E12" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="F12" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>78.34999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>78.65000000000001</v>
+        <v>86.58</v>
       </c>
       <c r="J12" t="n">
-        <v>77.79000000000001</v>
+        <v>83.42</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>6122</v>
@@ -1025,44 +1025,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.9</v>
+        <v>15.66</v>
       </c>
       <c r="C13" t="n">
-        <v>16.37</v>
+        <v>15.73</v>
       </c>
       <c r="D13" t="n">
-        <v>15.67</v>
+        <v>15.62</v>
       </c>
       <c r="E13" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="F13" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>76.45999999999999</v>
+        <v>82.52</v>
       </c>
       <c r="I13" t="n">
-        <v>78.44</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>72.33</v>
+        <v>82.33</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
         <v>6122</v>
@@ -1072,223 +1072,223 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.37</v>
+        <v>15.72</v>
       </c>
       <c r="C14" t="n">
-        <v>16.48</v>
+        <v>15.77</v>
       </c>
       <c r="D14" t="n">
-        <v>16.29</v>
+        <v>15.65</v>
       </c>
       <c r="E14" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>74.02</v>
+        <v>81.17</v>
       </c>
       <c r="I14" t="n">
-        <v>74.88</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>72.13</v>
+        <v>80.16</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.84</v>
+        <v>16.09</v>
       </c>
       <c r="C15" t="n">
-        <v>17.08</v>
+        <v>16.59</v>
       </c>
       <c r="D15" t="n">
-        <v>16.57</v>
+        <v>15.76</v>
       </c>
       <c r="E15" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="F15" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>70.64</v>
+        <v>76.7</v>
       </c>
       <c r="I15" t="n">
+        <v>80.06999999999999</v>
+      </c>
+      <c r="J15" t="n">
         <v>72.89</v>
       </c>
-      <c r="J15" t="n">
-        <v>68.62</v>
-      </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N15" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.26</v>
+        <v>16.2</v>
       </c>
       <c r="C16" t="n">
-        <v>17.41</v>
+        <v>16.53</v>
       </c>
       <c r="D16" t="n">
-        <v>17.13</v>
+        <v>15.84</v>
       </c>
       <c r="E16" t="n">
-        <v>10.7</v>
+        <v>12.1</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>11.6</v>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>65.97</v>
+        <v>77.2</v>
       </c>
       <c r="I16" t="n">
-        <v>68.3</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>62.44</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N16" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.57</v>
+        <v>16.03</v>
       </c>
       <c r="C17" t="n">
-        <v>18.11</v>
+        <v>16.12</v>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>15.93</v>
       </c>
       <c r="E17" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>9.800000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="G17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>63.38</v>
+        <v>77.56</v>
       </c>
       <c r="I17" t="n">
-        <v>64.3</v>
+        <v>79.16</v>
       </c>
       <c r="J17" t="n">
-        <v>61.77</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="N17" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>15.79</v>
       </c>
       <c r="C18" t="n">
-        <v>18.2</v>
+        <v>15.92</v>
       </c>
       <c r="D18" t="n">
-        <v>17.79</v>
+        <v>15.7</v>
       </c>
       <c r="E18" t="n">
-        <v>10.6</v>
+        <v>11.9</v>
       </c>
       <c r="F18" t="n">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
       <c r="G18" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>62.96</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>64.08</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>61.81</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1300,192 +1300,192 @@
         <v>1.3</v>
       </c>
       <c r="N18" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18.15</v>
+        <v>15.9</v>
       </c>
       <c r="C19" t="n">
-        <v>18.5</v>
+        <v>16.37</v>
       </c>
       <c r="D19" t="n">
-        <v>17.92</v>
+        <v>15.67</v>
       </c>
       <c r="E19" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="G19" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>60.86</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>62.23</v>
+        <v>78.44</v>
       </c>
       <c r="J19" t="n">
-        <v>59.51</v>
+        <v>72.33</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.71</v>
+        <v>16.37</v>
       </c>
       <c r="C20" t="n">
-        <v>18.05</v>
+        <v>16.48</v>
       </c>
       <c r="D20" t="n">
-        <v>17.31</v>
+        <v>16.29</v>
       </c>
       <c r="E20" t="n">
-        <v>10.1</v>
+        <v>11.6</v>
       </c>
       <c r="F20" t="n">
-        <v>9.9</v>
+        <v>11.3</v>
       </c>
       <c r="G20" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>61.59</v>
+        <v>74.02</v>
       </c>
       <c r="I20" t="n">
-        <v>63.45</v>
+        <v>74.88</v>
       </c>
       <c r="J20" t="n">
-        <v>59.82</v>
+        <v>72.13</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="N20" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.72</v>
+        <v>16.84</v>
       </c>
       <c r="C21" t="n">
-        <v>17.47</v>
+        <v>17.08</v>
       </c>
       <c r="D21" t="n">
-        <v>16.08</v>
+        <v>16.57</v>
       </c>
       <c r="E21" t="n">
-        <v>10.4</v>
+        <v>11.3</v>
       </c>
       <c r="F21" t="n">
-        <v>9.800000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="G21" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>67.33</v>
+        <v>70.64</v>
       </c>
       <c r="I21" t="n">
-        <v>70.81999999999999</v>
+        <v>72.89</v>
       </c>
       <c r="J21" t="n">
-        <v>63.98</v>
+        <v>68.62</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="N21" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15.83</v>
+        <v>17.26</v>
       </c>
       <c r="C22" t="n">
-        <v>16.23</v>
+        <v>17.41</v>
       </c>
       <c r="D22" t="n">
-        <v>15.45</v>
+        <v>17.13</v>
       </c>
       <c r="E22" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="F22" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>173</v>
+        <v>11</v>
       </c>
       <c r="H22" t="n">
-        <v>72.95</v>
+        <v>65.97</v>
       </c>
       <c r="I22" t="n">
-        <v>75.03</v>
+        <v>68.3</v>
       </c>
       <c r="J22" t="n">
-        <v>69.84999999999999</v>
+        <v>62.44</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="N22" t="n">
         <v>6132</v>
@@ -1495,138 +1495,138 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15.22</v>
+        <v>17.57</v>
       </c>
       <c r="C23" t="n">
-        <v>15.77</v>
+        <v>18.11</v>
       </c>
       <c r="D23" t="n">
-        <v>14.97</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="F23" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="H23" t="n">
-        <v>77.61</v>
+        <v>63.38</v>
       </c>
       <c r="I23" t="n">
-        <v>79.25</v>
+        <v>64.3</v>
       </c>
       <c r="J23" t="n">
-        <v>74.45</v>
+        <v>61.77</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N23" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14.79</v>
+        <v>18</v>
       </c>
       <c r="C24" t="n">
-        <v>15.1</v>
+        <v>18.2</v>
       </c>
       <c r="D24" t="n">
-        <v>14.32</v>
+        <v>17.79</v>
       </c>
       <c r="E24" t="n">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
       <c r="F24" t="n">
-        <v>11.2</v>
+        <v>10.5</v>
       </c>
       <c r="G24" t="n">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="H24" t="n">
-        <v>80.70999999999999</v>
+        <v>62.96</v>
       </c>
       <c r="I24" t="n">
-        <v>83.36</v>
+        <v>64.08</v>
       </c>
       <c r="J24" t="n">
-        <v>79.05</v>
+        <v>61.81</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N24" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14.05</v>
+        <v>18.15</v>
       </c>
       <c r="C25" t="n">
-        <v>14.26</v>
+        <v>18.5</v>
       </c>
       <c r="D25" t="n">
-        <v>13.8</v>
+        <v>17.92</v>
       </c>
       <c r="E25" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="F25" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="H25" t="n">
-        <v>85.09</v>
+        <v>60.86</v>
       </c>
       <c r="I25" t="n">
-        <v>86.40000000000001</v>
+        <v>62.23</v>
       </c>
       <c r="J25" t="n">
-        <v>84.14</v>
+        <v>59.51</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M25" t="n">
         <v>1.1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.4</v>
       </c>
       <c r="N25" t="n">
         <v>6142</v>
@@ -1636,138 +1636,138 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14.11</v>
+        <v>17.71</v>
       </c>
       <c r="C26" t="n">
-        <v>14.56</v>
+        <v>18.05</v>
       </c>
       <c r="D26" t="n">
-        <v>13.7</v>
+        <v>17.31</v>
       </c>
       <c r="E26" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="G26" t="n">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="H26" t="n">
-        <v>81.01000000000001</v>
+        <v>61.59</v>
       </c>
       <c r="I26" t="n">
-        <v>87.31</v>
+        <v>63.45</v>
       </c>
       <c r="J26" t="n">
-        <v>75.84999999999999</v>
+        <v>59.82</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="M26" t="n">
-        <v>1.3</v>
-      </c>
       <c r="N26" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.64</v>
+        <v>16.72</v>
       </c>
       <c r="C27" t="n">
-        <v>14.86</v>
+        <v>17.47</v>
       </c>
       <c r="D27" t="n">
-        <v>14.45</v>
+        <v>16.08</v>
       </c>
       <c r="E27" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F27" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="H27" t="n">
-        <v>79.53</v>
+        <v>67.33</v>
       </c>
       <c r="I27" t="n">
-        <v>82.73999999999999</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>76.79000000000001</v>
+        <v>63.98</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="N27" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15.07</v>
+        <v>15.83</v>
       </c>
       <c r="C28" t="n">
-        <v>15.23</v>
+        <v>16.23</v>
       </c>
       <c r="D28" t="n">
-        <v>14.92</v>
+        <v>15.45</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="F28" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="H28" t="n">
-        <v>77.61</v>
+        <v>72.95</v>
       </c>
       <c r="I28" t="n">
-        <v>78.94</v>
+        <v>75.03</v>
       </c>
       <c r="J28" t="n">
-        <v>76.67</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N28" t="n">
         <v>6132</v>
@@ -1777,185 +1777,185 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15.37</v>
+        <v>15.22</v>
       </c>
       <c r="C29" t="n">
-        <v>15.49</v>
+        <v>15.77</v>
       </c>
       <c r="D29" t="n">
-        <v>15.25</v>
+        <v>14.97</v>
       </c>
       <c r="E29" t="n">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="F29" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H29" t="n">
-        <v>79.81999999999999</v>
+        <v>77.61</v>
       </c>
       <c r="I29" t="n">
-        <v>80.69</v>
+        <v>79.25</v>
       </c>
       <c r="J29" t="n">
-        <v>78.86</v>
+        <v>74.45</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N29" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15.65</v>
+        <v>14.79</v>
       </c>
       <c r="C30" t="n">
-        <v>15.77</v>
+        <v>15.1</v>
       </c>
       <c r="D30" t="n">
-        <v>15.48</v>
+        <v>14.32</v>
       </c>
       <c r="E30" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F30" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H30" t="n">
-        <v>78.64</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>80.7</v>
+        <v>83.36</v>
       </c>
       <c r="J30" t="n">
-        <v>77.23</v>
+        <v>79.05</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N30" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>15.39</v>
+        <v>14.05</v>
       </c>
       <c r="C31" t="n">
-        <v>15.59</v>
+        <v>14.26</v>
       </c>
       <c r="D31" t="n">
-        <v>15.29</v>
+        <v>13.8</v>
       </c>
       <c r="E31" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="F31" t="n">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H31" t="n">
-        <v>84.89</v>
+        <v>85.09</v>
       </c>
       <c r="I31" t="n">
-        <v>87.12</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>81.20999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="M31" t="n">
         <v>1.4</v>
       </c>
       <c r="N31" t="n">
-        <v>6112</v>
+        <v>6142</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>15.61</v>
+        <v>14.11</v>
       </c>
       <c r="C32" t="n">
-        <v>16.09</v>
+        <v>14.56</v>
       </c>
       <c r="D32" t="n">
-        <v>15.44</v>
+        <v>13.7</v>
       </c>
       <c r="E32" t="n">
-        <v>12.8</v>
+        <v>10.7</v>
       </c>
       <c r="F32" t="n">
-        <v>12.4</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>84.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>86.2</v>
+        <v>87.31</v>
       </c>
       <c r="J32" t="n">
-        <v>79</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N32" t="n">
         <v>6132</v>
@@ -1965,187 +1965,185 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.78</v>
+        <v>14.64</v>
       </c>
       <c r="C33" t="n">
-        <v>17.16</v>
+        <v>14.86</v>
       </c>
       <c r="D33" t="n">
-        <v>16.31</v>
+        <v>14.45</v>
       </c>
       <c r="E33" t="n">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="F33" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>73.62</v>
+        <v>79.53</v>
       </c>
       <c r="I33" t="n">
-        <v>76.98999999999999</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>69.84</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="N33" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.55</v>
+        <v>15.07</v>
       </c>
       <c r="C34" t="n">
-        <v>17.8</v>
+        <v>15.23</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>14.92</v>
       </c>
       <c r="E34" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="F34" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>71.04000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="I34" t="n">
-        <v>73.81</v>
+        <v>78.94</v>
       </c>
       <c r="J34" t="n">
-        <v>69.28</v>
+        <v>76.67</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M34" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>6142</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.6</v>
-      </c>
+        <v>6132</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.63</v>
+        <v>15.37</v>
       </c>
       <c r="C35" t="n">
-        <v>18.08</v>
+        <v>15.49</v>
       </c>
       <c r="D35" t="n">
-        <v>17.4</v>
+        <v>15.25</v>
       </c>
       <c r="E35" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>73.43000000000001</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>76.55</v>
+        <v>80.69</v>
       </c>
       <c r="J35" t="n">
-        <v>68.51000000000001</v>
+        <v>78.86</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="M35" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.46</v>
+        <v>15.65</v>
       </c>
       <c r="C36" t="n">
-        <v>17.67</v>
+        <v>15.77</v>
       </c>
       <c r="D36" t="n">
-        <v>17.22</v>
+        <v>15.48</v>
       </c>
       <c r="E36" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="F36" t="n">
-        <v>13</v>
+        <v>11.6</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>76.84</v>
+        <v>78.64</v>
       </c>
       <c r="I36" t="n">
-        <v>79.37</v>
+        <v>80.7</v>
       </c>
       <c r="J36" t="n">
-        <v>75.08</v>
+        <v>77.23</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="M36" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="N36" t="n">
         <v>6132</v>
@@ -2155,658 +2153,660 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.43</v>
+        <v>15.39</v>
       </c>
       <c r="C37" t="n">
-        <v>17.62</v>
+        <v>15.59</v>
       </c>
       <c r="D37" t="n">
-        <v>17.17</v>
+        <v>15.29</v>
       </c>
       <c r="E37" t="n">
-        <v>13.6</v>
+        <v>12.7</v>
       </c>
       <c r="F37" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>79.34</v>
+        <v>84.89</v>
       </c>
       <c r="I37" t="n">
-        <v>82.2</v>
+        <v>87.12</v>
       </c>
       <c r="J37" t="n">
-        <v>77.51000000000001</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N37" t="n">
-        <v>6142</v>
+        <v>6112</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.89</v>
+        <v>15.61</v>
       </c>
       <c r="C38" t="n">
-        <v>18.13</v>
+        <v>16.09</v>
       </c>
       <c r="D38" t="n">
-        <v>17.76</v>
+        <v>15.44</v>
       </c>
       <c r="E38" t="n">
-        <v>13.4</v>
+        <v>12.8</v>
       </c>
       <c r="F38" t="n">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>76.29000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="I38" t="n">
-        <v>78.06999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="J38" t="n">
-        <v>74.34999999999999</v>
+        <v>79</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="M38" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="N38" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>18.6</v>
+        <v>16.78</v>
       </c>
       <c r="C39" t="n">
-        <v>19.26</v>
+        <v>17.16</v>
       </c>
       <c r="D39" t="n">
-        <v>18.22</v>
+        <v>16.31</v>
       </c>
       <c r="E39" t="n">
-        <v>13</v>
+        <v>11.9</v>
       </c>
       <c r="F39" t="n">
-        <v>12.5</v>
+        <v>11.4</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>70.7</v>
+        <v>73.62</v>
       </c>
       <c r="I39" t="n">
-        <v>73.79000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>65.41</v>
+        <v>69.84</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="N39" t="n">
-        <v>6152</v>
+        <v>6122</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20.29</v>
+        <v>17.55</v>
       </c>
       <c r="C40" t="n">
-        <v>21.69</v>
+        <v>17.8</v>
       </c>
       <c r="D40" t="n">
-        <v>19.3</v>
+        <v>17.2</v>
       </c>
       <c r="E40" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="F40" t="n">
-        <v>10.7</v>
+        <v>11.8</v>
       </c>
       <c r="G40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>58.46</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>64.93000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="J40" t="n">
-        <v>50.01</v>
+        <v>69.28</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="N40" t="n">
-        <v>6162</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>6142</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>22.33</v>
+        <v>17.63</v>
       </c>
       <c r="C41" t="n">
-        <v>22.66</v>
+        <v>18.08</v>
       </c>
       <c r="D41" t="n">
-        <v>21.95</v>
+        <v>17.4</v>
       </c>
       <c r="E41" t="n">
-        <v>9.9</v>
+        <v>12.6</v>
       </c>
       <c r="F41" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="G41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>46.23</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>48.69</v>
+        <v>76.55</v>
       </c>
       <c r="J41" t="n">
-        <v>44.45</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M41" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="N41" t="n">
-        <v>6170</v>
+        <v>6122</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>22.97</v>
+        <v>17.46</v>
       </c>
       <c r="C42" t="n">
-        <v>23.49</v>
+        <v>17.67</v>
       </c>
       <c r="D42" t="n">
-        <v>22.63</v>
+        <v>17.22</v>
       </c>
       <c r="E42" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="F42" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="G42" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>43.28</v>
+        <v>76.84</v>
       </c>
       <c r="I42" t="n">
-        <v>44.43</v>
+        <v>79.37</v>
       </c>
       <c r="J42" t="n">
-        <v>41.95</v>
+        <v>75.08</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="N42" t="n">
-        <v>6180</v>
+        <v>6132</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>23.37</v>
+        <v>17.43</v>
       </c>
       <c r="C43" t="n">
-        <v>23.93</v>
+        <v>17.62</v>
       </c>
       <c r="D43" t="n">
-        <v>23.11</v>
+        <v>17.17</v>
       </c>
       <c r="E43" t="n">
-        <v>9.699999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="F43" t="n">
-        <v>9.5</v>
+        <v>13.3</v>
       </c>
       <c r="G43" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>42.7</v>
+        <v>79.34</v>
       </c>
       <c r="I43" t="n">
-        <v>44.12</v>
+        <v>82.2</v>
       </c>
       <c r="J43" t="n">
-        <v>41.98</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N43" t="n">
-        <v>6190</v>
+        <v>6142</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23.27</v>
+        <v>17.89</v>
       </c>
       <c r="C44" t="n">
-        <v>23.64</v>
+        <v>18.13</v>
       </c>
       <c r="D44" t="n">
-        <v>22.89</v>
+        <v>17.76</v>
       </c>
       <c r="E44" t="n">
-        <v>9.6</v>
+        <v>13.4</v>
       </c>
       <c r="F44" t="n">
-        <v>9.300000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="G44" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>42.52</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>43.12</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>41.91</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="N44" t="n">
-        <v>6190</v>
+        <v>6142</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>22.93</v>
+        <v>18.6</v>
       </c>
       <c r="C45" t="n">
-        <v>23.35</v>
+        <v>19.26</v>
       </c>
       <c r="D45" t="n">
-        <v>22.54</v>
+        <v>18.22</v>
       </c>
       <c r="E45" t="n">
-        <v>9.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="F45" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="G45" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>43.56</v>
+        <v>70.7</v>
       </c>
       <c r="I45" t="n">
-        <v>44.91</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>42.28</v>
+        <v>65.41</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="M45" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22.23</v>
+        <v>20.29</v>
       </c>
       <c r="C46" t="n">
-        <v>22.76</v>
+        <v>21.69</v>
       </c>
       <c r="D46" t="n">
-        <v>21.86</v>
+        <v>19.3</v>
       </c>
       <c r="E46" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="F46" t="n">
-        <v>9.300000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G46" t="n">
-        <v>383</v>
+        <v>9</v>
       </c>
       <c r="H46" t="n">
-        <v>45.63</v>
+        <v>58.46</v>
       </c>
       <c r="I46" t="n">
-        <v>47.01</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>44.24</v>
+        <v>50.01</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="M46" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21.57</v>
+        <v>22.33</v>
       </c>
       <c r="C47" t="n">
-        <v>22.64</v>
+        <v>22.66</v>
       </c>
       <c r="D47" t="n">
-        <v>20.71</v>
+        <v>21.95</v>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="F47" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="G47" t="n">
-        <v>373</v>
+        <v>24</v>
       </c>
       <c r="H47" t="n">
-        <v>48.34</v>
+        <v>46.23</v>
       </c>
       <c r="I47" t="n">
-        <v>51.45</v>
+        <v>48.69</v>
       </c>
       <c r="J47" t="n">
-        <v>45.03</v>
+        <v>44.45</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="M47" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="N47" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>20.3</v>
+        <v>22.97</v>
       </c>
       <c r="C48" t="n">
-        <v>20.76</v>
+        <v>23.49</v>
       </c>
       <c r="D48" t="n">
-        <v>19.87</v>
+        <v>22.63</v>
       </c>
       <c r="E48" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="G48" t="n">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="H48" t="n">
-        <v>53.23</v>
+        <v>43.28</v>
       </c>
       <c r="I48" t="n">
-        <v>56.41</v>
+        <v>44.43</v>
       </c>
       <c r="J48" t="n">
-        <v>51.05</v>
+        <v>41.95</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N48" t="n">
-        <v>6170</v>
+        <v>6180</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19.38</v>
+        <v>23.37</v>
       </c>
       <c r="C49" t="n">
-        <v>19.85</v>
+        <v>23.93</v>
       </c>
       <c r="D49" t="n">
-        <v>18.89</v>
+        <v>23.11</v>
       </c>
       <c r="E49" t="n">
-        <v>11.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="G49" t="n">
-        <v>110</v>
+        <v>271</v>
       </c>
       <c r="H49" t="n">
-        <v>61.37</v>
+        <v>42.7</v>
       </c>
       <c r="I49" t="n">
-        <v>65.44</v>
+        <v>44.12</v>
       </c>
       <c r="J49" t="n">
-        <v>57.45</v>
+        <v>41.98</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="N49" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>18.52</v>
+        <v>23.27</v>
       </c>
       <c r="C50" t="n">
-        <v>18.87</v>
+        <v>23.64</v>
       </c>
       <c r="D50" t="n">
-        <v>18.23</v>
+        <v>22.89</v>
       </c>
       <c r="E50" t="n">
-        <v>12.2</v>
+        <v>9.6</v>
       </c>
       <c r="F50" t="n">
-        <v>12</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="H50" t="n">
-        <v>67.5</v>
+        <v>42.52</v>
       </c>
       <c r="I50" t="n">
-        <v>70.43000000000001</v>
+        <v>43.12</v>
       </c>
       <c r="J50" t="n">
-        <v>65.33</v>
+        <v>41.91</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N50" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O50" t="n">
         <v>2.3</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,505 +508,505 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.35</v>
+        <v>19.9</v>
       </c>
       <c r="C2" t="n">
-        <v>22.6</v>
+        <v>19.92</v>
       </c>
       <c r="D2" t="n">
-        <v>22.16</v>
+        <v>19.89</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="F2" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G2" t="n">
-        <v>411</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
-        <v>46.16</v>
+        <v>54.7</v>
       </c>
       <c r="I2" t="n">
-        <v>47.21</v>
+        <v>54.82</v>
       </c>
       <c r="J2" t="n">
-        <v>45.53</v>
+        <v>54.53</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="N2" t="n">
-        <v>6210</v>
+        <v>6152</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 13:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.58</v>
+        <v>19.91</v>
       </c>
       <c r="C3" t="n">
-        <v>23.47</v>
+        <v>19.98</v>
       </c>
       <c r="D3" t="n">
-        <v>21.83</v>
+        <v>19.83</v>
       </c>
       <c r="E3" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="F3" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="G3" t="n">
-        <v>815</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>45.81</v>
+        <v>54.74</v>
       </c>
       <c r="I3" t="n">
-        <v>48.66</v>
+        <v>54.92</v>
       </c>
       <c r="J3" t="n">
-        <v>43.93</v>
+        <v>54.61</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>6220</v>
+        <v>6162</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 12:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.31</v>
+        <v>20.31</v>
       </c>
       <c r="C4" t="n">
-        <v>22.4</v>
+        <v>20.99</v>
       </c>
       <c r="D4" t="n">
-        <v>20.2</v>
+        <v>19.97</v>
       </c>
       <c r="E4" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="F4" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="G4" t="n">
-        <v>689</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>50.33</v>
+        <v>53.29</v>
       </c>
       <c r="I4" t="n">
-        <v>56.08</v>
+        <v>54.84</v>
       </c>
       <c r="J4" t="n">
-        <v>47.33</v>
+        <v>51.22</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19 11:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.91</v>
+        <v>21.38</v>
       </c>
       <c r="C5" t="n">
-        <v>19.91</v>
+        <v>21.67</v>
       </c>
       <c r="D5" t="n">
-        <v>18.4</v>
+        <v>20.91</v>
       </c>
       <c r="E5" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="F5" t="n">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>305</v>
+        <v>213</v>
       </c>
       <c r="H5" t="n">
-        <v>60.58</v>
+        <v>49.67</v>
       </c>
       <c r="I5" t="n">
-        <v>63.06</v>
+        <v>50.93</v>
       </c>
       <c r="J5" t="n">
-        <v>55.94</v>
+        <v>48.59</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.94</v>
+        <v>21.78</v>
       </c>
       <c r="C6" t="n">
-        <v>18.46</v>
+        <v>22.31</v>
       </c>
       <c r="D6" t="n">
-        <v>17.55</v>
+        <v>21.39</v>
       </c>
       <c r="E6" t="n">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="F6" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="H6" t="n">
-        <v>67.54000000000001</v>
+        <v>48.06</v>
       </c>
       <c r="I6" t="n">
-        <v>70.20999999999999</v>
+        <v>48.87</v>
       </c>
       <c r="J6" t="n">
-        <v>64.44</v>
+        <v>46.24</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>6152</v>
+        <v>6210</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.55</v>
+        <v>22.97</v>
       </c>
       <c r="C7" t="n">
-        <v>17.81</v>
+        <v>24.27</v>
       </c>
       <c r="D7" t="n">
-        <v>17.2</v>
+        <v>22.16</v>
       </c>
       <c r="E7" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="F7" t="n">
-        <v>10.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>95</v>
+        <v>747</v>
       </c>
       <c r="H7" t="n">
-        <v>68.43000000000001</v>
+        <v>44.85</v>
       </c>
       <c r="I7" t="n">
-        <v>69.95</v>
+        <v>47.21</v>
       </c>
       <c r="J7" t="n">
-        <v>65.48</v>
+        <v>41.93</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
+        <v>4.3</v>
       </c>
       <c r="N7" t="n">
-        <v>6132</v>
+        <v>6220</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.64</v>
+        <v>22.58</v>
       </c>
       <c r="C8" t="n">
-        <v>17.06</v>
+        <v>23.47</v>
       </c>
       <c r="D8" t="n">
-        <v>16.2</v>
+        <v>21.83</v>
       </c>
       <c r="E8" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="F8" t="n">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
       <c r="G8" t="n">
-        <v>44</v>
+        <v>815</v>
       </c>
       <c r="H8" t="n">
-        <v>72.79000000000001</v>
+        <v>45.81</v>
       </c>
       <c r="I8" t="n">
-        <v>77.45</v>
+        <v>48.66</v>
       </c>
       <c r="J8" t="n">
-        <v>70.3</v>
+        <v>43.93</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="N8" t="n">
-        <v>6132</v>
+        <v>6220</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.62</v>
+        <v>21.31</v>
       </c>
       <c r="C9" t="n">
-        <v>16.07</v>
+        <v>22.4</v>
       </c>
       <c r="D9" t="n">
-        <v>15.35</v>
+        <v>20.2</v>
       </c>
       <c r="E9" t="n">
-        <v>12.9</v>
+        <v>10.4</v>
       </c>
       <c r="F9" t="n">
-        <v>12.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>689</v>
       </c>
       <c r="H9" t="n">
-        <v>85.33</v>
+        <v>50.33</v>
       </c>
       <c r="I9" t="n">
-        <v>89.23</v>
+        <v>56.08</v>
       </c>
       <c r="J9" t="n">
-        <v>79.03</v>
+        <v>47.33</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="N9" t="n">
-        <v>6122</v>
+        <v>6190</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.25</v>
+        <v>18.91</v>
       </c>
       <c r="C10" t="n">
-        <v>15.35</v>
+        <v>19.91</v>
       </c>
       <c r="D10" t="n">
-        <v>15.06</v>
+        <v>18.4</v>
       </c>
       <c r="E10" t="n">
-        <v>13.3</v>
+        <v>10.9</v>
       </c>
       <c r="F10" t="n">
-        <v>13.2</v>
+        <v>10.6</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="H10" t="n">
-        <v>89.16</v>
+        <v>60.58</v>
       </c>
       <c r="I10" t="n">
-        <v>91.05</v>
+        <v>63.06</v>
       </c>
       <c r="J10" t="n">
-        <v>87.77</v>
+        <v>55.94</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N10" t="n">
-        <v>6122</v>
+        <v>6162</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15.2</v>
+        <v>17.94</v>
       </c>
       <c r="C11" t="n">
-        <v>15.32</v>
+        <v>18.46</v>
       </c>
       <c r="D11" t="n">
-        <v>15.08</v>
+        <v>17.55</v>
       </c>
       <c r="E11" t="n">
-        <v>13.1</v>
+        <v>11.6</v>
       </c>
       <c r="F11" t="n">
-        <v>13.1</v>
+        <v>11.2</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H11" t="n">
-        <v>88.42</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>89.37</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>87.13</v>
+        <v>64.44</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>6122</v>
+        <v>6152</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.53</v>
+        <v>17.55</v>
       </c>
       <c r="C12" t="n">
-        <v>15.66</v>
+        <v>17.81</v>
       </c>
       <c r="D12" t="n">
-        <v>15.45</v>
+        <v>17.2</v>
       </c>
       <c r="E12" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="F12" t="n">
-        <v>12.7</v>
+        <v>10.9</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H12" t="n">
-        <v>85.40000000000001</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>86.58</v>
+        <v>69.95</v>
       </c>
       <c r="J12" t="n">
-        <v>83.42</v>
+        <v>65.48</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1015,45 +1015,45 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N12" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.66</v>
+        <v>16.64</v>
       </c>
       <c r="C13" t="n">
-        <v>15.73</v>
+        <v>17.06</v>
       </c>
       <c r="D13" t="n">
-        <v>15.62</v>
+        <v>16.2</v>
       </c>
       <c r="E13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="F13" t="n">
-        <v>12.5</v>
+        <v>11.4</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H13" t="n">
-        <v>82.52</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>82.76000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="J13" t="n">
-        <v>82.33</v>
+        <v>70.3</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1062,54 +1062,54 @@
         <v>0.3</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N13" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.72</v>
+        <v>15.62</v>
       </c>
       <c r="C14" t="n">
-        <v>15.77</v>
+        <v>16.07</v>
       </c>
       <c r="D14" t="n">
-        <v>15.65</v>
+        <v>15.35</v>
       </c>
       <c r="E14" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F14" t="n">
         <v>12.4</v>
       </c>
-      <c r="F14" t="n">
-        <v>12.3</v>
-      </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>81.17</v>
+        <v>85.33</v>
       </c>
       <c r="I14" t="n">
-        <v>82.40000000000001</v>
+        <v>89.23</v>
       </c>
       <c r="J14" t="n">
-        <v>80.16</v>
+        <v>79.03</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>6122</v>
@@ -1119,44 +1119,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.09</v>
+        <v>15.25</v>
       </c>
       <c r="C15" t="n">
-        <v>16.59</v>
+        <v>15.35</v>
       </c>
       <c r="D15" t="n">
-        <v>15.76</v>
+        <v>15.06</v>
       </c>
       <c r="E15" t="n">
-        <v>11.9</v>
+        <v>13.3</v>
       </c>
       <c r="F15" t="n">
-        <v>11.4</v>
+        <v>13.2</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>76.7</v>
+        <v>89.16</v>
       </c>
       <c r="I15" t="n">
-        <v>80.06999999999999</v>
+        <v>91.05</v>
       </c>
       <c r="J15" t="n">
-        <v>72.89</v>
+        <v>87.77</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>6122</v>
@@ -1166,44 +1166,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.2</v>
+        <v>15.2</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53</v>
+        <v>15.32</v>
       </c>
       <c r="D16" t="n">
-        <v>15.84</v>
+        <v>15.08</v>
       </c>
       <c r="E16" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="F16" t="n">
-        <v>11.6</v>
+        <v>13.1</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>77.2</v>
+        <v>88.42</v>
       </c>
       <c r="I16" t="n">
-        <v>80.54000000000001</v>
+        <v>89.37</v>
       </c>
       <c r="J16" t="n">
-        <v>73.31999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>6122</v>
@@ -1213,44 +1213,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.03</v>
+        <v>15.53</v>
       </c>
       <c r="C17" t="n">
-        <v>16.12</v>
+        <v>15.66</v>
       </c>
       <c r="D17" t="n">
-        <v>15.93</v>
+        <v>15.45</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="F17" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>77.56</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>79.16</v>
+        <v>86.58</v>
       </c>
       <c r="J17" t="n">
-        <v>76.79000000000001</v>
+        <v>83.42</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>6122</v>
@@ -1260,44 +1260,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15.79</v>
+        <v>15.66</v>
       </c>
       <c r="C18" t="n">
-        <v>15.92</v>
+        <v>15.73</v>
       </c>
       <c r="D18" t="n">
-        <v>15.7</v>
+        <v>15.62</v>
       </c>
       <c r="E18" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="F18" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>78.34999999999999</v>
+        <v>82.52</v>
       </c>
       <c r="I18" t="n">
-        <v>78.65000000000001</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>77.79000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="n">
         <v>6122</v>
@@ -1307,44 +1307,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15.9</v>
+        <v>15.72</v>
       </c>
       <c r="C19" t="n">
-        <v>16.37</v>
+        <v>15.77</v>
       </c>
       <c r="D19" t="n">
-        <v>15.67</v>
+        <v>15.65</v>
       </c>
       <c r="E19" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="F19" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>76.45999999999999</v>
+        <v>81.17</v>
       </c>
       <c r="I19" t="n">
-        <v>78.44</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>72.33</v>
+        <v>80.16</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
         <v>6122</v>
@@ -1354,467 +1354,467 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.37</v>
+        <v>16.09</v>
       </c>
       <c r="C20" t="n">
-        <v>16.48</v>
+        <v>16.59</v>
       </c>
       <c r="D20" t="n">
-        <v>16.29</v>
+        <v>15.76</v>
       </c>
       <c r="E20" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="F20" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>74.02</v>
+        <v>76.7</v>
       </c>
       <c r="I20" t="n">
-        <v>74.88</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>72.13</v>
+        <v>72.89</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N20" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.84</v>
+        <v>16.2</v>
       </c>
       <c r="C21" t="n">
-        <v>17.08</v>
+        <v>16.53</v>
       </c>
       <c r="D21" t="n">
-        <v>16.57</v>
+        <v>15.84</v>
       </c>
       <c r="E21" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="F21" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>70.64</v>
+        <v>77.2</v>
       </c>
       <c r="I21" t="n">
-        <v>72.89</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>68.62</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="N21" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.26</v>
+        <v>16.03</v>
       </c>
       <c r="C22" t="n">
-        <v>17.41</v>
+        <v>16.12</v>
       </c>
       <c r="D22" t="n">
-        <v>17.13</v>
+        <v>15.93</v>
       </c>
       <c r="E22" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="G22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>65.97</v>
+        <v>77.56</v>
       </c>
       <c r="I22" t="n">
-        <v>68.3</v>
+        <v>79.16</v>
       </c>
       <c r="J22" t="n">
-        <v>62.44</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="N22" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.57</v>
+        <v>15.79</v>
       </c>
       <c r="C23" t="n">
-        <v>18.11</v>
+        <v>15.92</v>
       </c>
       <c r="D23" t="n">
-        <v>17.4</v>
+        <v>15.7</v>
       </c>
       <c r="E23" t="n">
-        <v>10.4</v>
+        <v>11.9</v>
       </c>
       <c r="F23" t="n">
-        <v>9.800000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>63.38</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>64.3</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>61.77</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="N23" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18</v>
+        <v>15.9</v>
       </c>
       <c r="C24" t="n">
-        <v>18.2</v>
+        <v>16.37</v>
       </c>
       <c r="D24" t="n">
-        <v>17.79</v>
+        <v>15.67</v>
       </c>
       <c r="E24" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="F24" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="G24" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>62.96</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>64.08</v>
+        <v>78.44</v>
       </c>
       <c r="J24" t="n">
-        <v>61.81</v>
+        <v>72.33</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18.15</v>
+        <v>16.37</v>
       </c>
       <c r="C25" t="n">
-        <v>18.5</v>
+        <v>16.48</v>
       </c>
       <c r="D25" t="n">
-        <v>17.92</v>
+        <v>16.29</v>
       </c>
       <c r="E25" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="G25" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>60.86</v>
+        <v>74.02</v>
       </c>
       <c r="I25" t="n">
-        <v>62.23</v>
+        <v>74.88</v>
       </c>
       <c r="J25" t="n">
-        <v>59.51</v>
+        <v>72.13</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="N25" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17.71</v>
+        <v>16.84</v>
       </c>
       <c r="C26" t="n">
-        <v>18.05</v>
+        <v>17.08</v>
       </c>
       <c r="D26" t="n">
-        <v>17.31</v>
+        <v>16.57</v>
       </c>
       <c r="E26" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
       <c r="F26" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="G26" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>61.59</v>
+        <v>70.64</v>
       </c>
       <c r="I26" t="n">
-        <v>63.45</v>
+        <v>72.89</v>
       </c>
       <c r="J26" t="n">
-        <v>59.82</v>
+        <v>68.62</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N26" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.72</v>
+        <v>17.26</v>
       </c>
       <c r="C27" t="n">
-        <v>17.47</v>
+        <v>17.41</v>
       </c>
       <c r="D27" t="n">
-        <v>16.08</v>
+        <v>17.13</v>
       </c>
       <c r="E27" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="F27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>260</v>
+        <v>11</v>
       </c>
       <c r="H27" t="n">
-        <v>67.33</v>
+        <v>65.97</v>
       </c>
       <c r="I27" t="n">
-        <v>70.81999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="J27" t="n">
-        <v>63.98</v>
+        <v>62.44</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N27" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15.83</v>
+        <v>17.57</v>
       </c>
       <c r="C28" t="n">
-        <v>16.23</v>
+        <v>18.11</v>
       </c>
       <c r="D28" t="n">
-        <v>15.45</v>
+        <v>17.4</v>
       </c>
       <c r="E28" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F28" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H28" t="n">
-        <v>72.95</v>
+        <v>63.38</v>
       </c>
       <c r="I28" t="n">
-        <v>75.03</v>
+        <v>64.3</v>
       </c>
       <c r="J28" t="n">
-        <v>69.84999999999999</v>
+        <v>61.77</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N28" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15.22</v>
+        <v>18</v>
       </c>
       <c r="C29" t="n">
-        <v>15.77</v>
+        <v>18.2</v>
       </c>
       <c r="D29" t="n">
-        <v>14.97</v>
+        <v>17.79</v>
       </c>
       <c r="E29" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="F29" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="G29" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H29" t="n">
-        <v>77.61</v>
+        <v>62.96</v>
       </c>
       <c r="I29" t="n">
-        <v>79.25</v>
+        <v>64.08</v>
       </c>
       <c r="J29" t="n">
-        <v>74.45</v>
+        <v>61.81</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N29" t="n">
         <v>6162</v>
@@ -1824,44 +1824,44 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>14.79</v>
+        <v>18.15</v>
       </c>
       <c r="C30" t="n">
-        <v>15.1</v>
+        <v>18.5</v>
       </c>
       <c r="D30" t="n">
-        <v>14.32</v>
+        <v>17.92</v>
       </c>
       <c r="E30" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="F30" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="H30" t="n">
-        <v>80.70999999999999</v>
+        <v>60.86</v>
       </c>
       <c r="I30" t="n">
-        <v>83.36</v>
+        <v>62.23</v>
       </c>
       <c r="J30" t="n">
-        <v>79.05</v>
+        <v>59.51</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
         <v>6142</v>
@@ -1871,138 +1871,138 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>14.05</v>
+        <v>17.71</v>
       </c>
       <c r="C31" t="n">
-        <v>14.26</v>
+        <v>18.05</v>
       </c>
       <c r="D31" t="n">
-        <v>13.8</v>
+        <v>17.31</v>
       </c>
       <c r="E31" t="n">
-        <v>11.4</v>
+        <v>10.1</v>
       </c>
       <c r="F31" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="G31" t="n">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="H31" t="n">
-        <v>85.09</v>
+        <v>61.59</v>
       </c>
       <c r="I31" t="n">
-        <v>86.40000000000001</v>
+        <v>63.45</v>
       </c>
       <c r="J31" t="n">
-        <v>84.14</v>
+        <v>59.82</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>14.11</v>
+        <v>16.72</v>
       </c>
       <c r="C32" t="n">
-        <v>14.56</v>
+        <v>17.47</v>
       </c>
       <c r="D32" t="n">
-        <v>13.7</v>
+        <v>16.08</v>
       </c>
       <c r="E32" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>31</v>
+        <v>260</v>
       </c>
       <c r="H32" t="n">
-        <v>81.01000000000001</v>
+        <v>67.33</v>
       </c>
       <c r="I32" t="n">
-        <v>87.31</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>75.84999999999999</v>
+        <v>63.98</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M32" t="n">
         <v>1.3</v>
       </c>
       <c r="N32" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.64</v>
+        <v>15.83</v>
       </c>
       <c r="C33" t="n">
-        <v>14.86</v>
+        <v>16.23</v>
       </c>
       <c r="D33" t="n">
-        <v>14.45</v>
+        <v>15.45</v>
       </c>
       <c r="E33" t="n">
         <v>10.9</v>
       </c>
       <c r="F33" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>173</v>
       </c>
       <c r="H33" t="n">
-        <v>79.53</v>
+        <v>72.95</v>
       </c>
       <c r="I33" t="n">
-        <v>82.73999999999999</v>
+        <v>75.03</v>
       </c>
       <c r="J33" t="n">
-        <v>76.79000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N33" t="n">
         <v>6132</v>
@@ -2012,232 +2012,232 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15.07</v>
+        <v>15.22</v>
       </c>
       <c r="C34" t="n">
-        <v>15.23</v>
+        <v>15.77</v>
       </c>
       <c r="D34" t="n">
-        <v>14.92</v>
+        <v>14.97</v>
       </c>
       <c r="E34" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="F34" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H34" t="n">
         <v>77.61</v>
       </c>
       <c r="I34" t="n">
-        <v>78.94</v>
+        <v>79.25</v>
       </c>
       <c r="J34" t="n">
-        <v>76.67</v>
+        <v>74.45</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N34" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15.37</v>
+        <v>14.79</v>
       </c>
       <c r="C35" t="n">
-        <v>15.49</v>
+        <v>15.1</v>
       </c>
       <c r="D35" t="n">
-        <v>15.25</v>
+        <v>14.32</v>
       </c>
       <c r="E35" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F35" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H35" t="n">
-        <v>79.81999999999999</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>80.69</v>
+        <v>83.36</v>
       </c>
       <c r="J35" t="n">
-        <v>78.86</v>
+        <v>79.05</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N35" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.65</v>
+        <v>14.05</v>
       </c>
       <c r="C36" t="n">
-        <v>15.77</v>
+        <v>14.26</v>
       </c>
       <c r="D36" t="n">
-        <v>15.48</v>
+        <v>13.8</v>
       </c>
       <c r="E36" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F36" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H36" t="n">
-        <v>78.64</v>
+        <v>85.09</v>
       </c>
       <c r="I36" t="n">
-        <v>80.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>77.23</v>
+        <v>84.14</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M36" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N36" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15.39</v>
+        <v>14.11</v>
       </c>
       <c r="C37" t="n">
-        <v>15.59</v>
+        <v>14.56</v>
       </c>
       <c r="D37" t="n">
-        <v>15.29</v>
+        <v>13.7</v>
       </c>
       <c r="E37" t="n">
-        <v>12.7</v>
+        <v>10.7</v>
       </c>
       <c r="F37" t="n">
-        <v>12.3</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H37" t="n">
-        <v>84.89</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>87.12</v>
+        <v>87.31</v>
       </c>
       <c r="J37" t="n">
-        <v>81.20999999999999</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N37" t="n">
-        <v>6112</v>
+        <v>6132</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>15.61</v>
+        <v>14.64</v>
       </c>
       <c r="C38" t="n">
-        <v>16.09</v>
+        <v>14.86</v>
       </c>
       <c r="D38" t="n">
-        <v>15.44</v>
+        <v>14.45</v>
       </c>
       <c r="E38" t="n">
-        <v>12.8</v>
+        <v>10.9</v>
       </c>
       <c r="F38" t="n">
-        <v>12.4</v>
+        <v>10.5</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H38" t="n">
-        <v>84.45</v>
+        <v>79.53</v>
       </c>
       <c r="I38" t="n">
-        <v>86.2</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>79</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="N38" t="n">
         <v>6132</v>
@@ -2247,566 +2247,566 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.78</v>
+        <v>15.07</v>
       </c>
       <c r="C39" t="n">
-        <v>17.16</v>
+        <v>15.23</v>
       </c>
       <c r="D39" t="n">
-        <v>16.31</v>
+        <v>14.92</v>
       </c>
       <c r="E39" t="n">
-        <v>11.9</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>73.62</v>
+        <v>77.61</v>
       </c>
       <c r="I39" t="n">
-        <v>76.98999999999999</v>
+        <v>78.94</v>
       </c>
       <c r="J39" t="n">
-        <v>69.84</v>
+        <v>76.67</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="M39" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.55</v>
+        <v>15.37</v>
       </c>
       <c r="C40" t="n">
-        <v>17.8</v>
+        <v>15.49</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>15.25</v>
       </c>
       <c r="E40" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="F40" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>71.04000000000001</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>73.81</v>
+        <v>80.69</v>
       </c>
       <c r="J40" t="n">
-        <v>69.28</v>
+        <v>78.86</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="M40" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="N40" t="n">
-        <v>6142</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.6</v>
-      </c>
+        <v>6132</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.63</v>
+        <v>15.65</v>
       </c>
       <c r="C41" t="n">
-        <v>18.08</v>
+        <v>15.77</v>
       </c>
       <c r="D41" t="n">
-        <v>17.4</v>
+        <v>15.48</v>
       </c>
       <c r="E41" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F41" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>73.43000000000001</v>
+        <v>78.64</v>
       </c>
       <c r="I41" t="n">
-        <v>76.55</v>
+        <v>80.7</v>
       </c>
       <c r="J41" t="n">
-        <v>68.51000000000001</v>
+        <v>77.23</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="M41" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="N41" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.46</v>
+        <v>15.39</v>
       </c>
       <c r="C42" t="n">
-        <v>17.67</v>
+        <v>15.59</v>
       </c>
       <c r="D42" t="n">
-        <v>17.22</v>
+        <v>15.29</v>
       </c>
       <c r="E42" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="F42" t="n">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>76.84</v>
+        <v>84.89</v>
       </c>
       <c r="I42" t="n">
-        <v>79.37</v>
+        <v>87.12</v>
       </c>
       <c r="J42" t="n">
-        <v>75.08</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M42" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="N42" t="n">
-        <v>6132</v>
+        <v>6112</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.43</v>
+        <v>15.61</v>
       </c>
       <c r="C43" t="n">
-        <v>17.62</v>
+        <v>16.09</v>
       </c>
       <c r="D43" t="n">
-        <v>17.17</v>
+        <v>15.44</v>
       </c>
       <c r="E43" t="n">
-        <v>13.6</v>
+        <v>12.8</v>
       </c>
       <c r="F43" t="n">
-        <v>13.3</v>
+        <v>12.4</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>79.34</v>
+        <v>84.45</v>
       </c>
       <c r="I43" t="n">
-        <v>82.2</v>
+        <v>86.2</v>
       </c>
       <c r="J43" t="n">
-        <v>77.51000000000001</v>
+        <v>79</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="N43" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17.89</v>
+        <v>16.78</v>
       </c>
       <c r="C44" t="n">
-        <v>18.13</v>
+        <v>17.16</v>
       </c>
       <c r="D44" t="n">
-        <v>17.76</v>
+        <v>16.31</v>
       </c>
       <c r="E44" t="n">
-        <v>13.4</v>
+        <v>11.9</v>
       </c>
       <c r="F44" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>76.29000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="I44" t="n">
-        <v>78.06999999999999</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>74.34999999999999</v>
+        <v>69.84</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M44" t="n">
         <v>2.2</v>
       </c>
-      <c r="M44" t="n">
-        <v>2.3</v>
-      </c>
       <c r="N44" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>18.6</v>
+        <v>17.55</v>
       </c>
       <c r="C45" t="n">
-        <v>19.26</v>
+        <v>17.8</v>
       </c>
       <c r="D45" t="n">
-        <v>18.22</v>
+        <v>17.2</v>
       </c>
       <c r="E45" t="n">
-        <v>13</v>
+        <v>12.1</v>
       </c>
       <c r="F45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>70.7</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>73.79000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="J45" t="n">
-        <v>65.41</v>
+        <v>69.28</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="N45" t="n">
-        <v>6152</v>
-      </c>
-      <c r="O45" t="inlineStr"/>
+        <v>6142</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20.29</v>
+        <v>17.63</v>
       </c>
       <c r="C46" t="n">
-        <v>21.69</v>
+        <v>18.08</v>
       </c>
       <c r="D46" t="n">
-        <v>19.3</v>
+        <v>17.4</v>
       </c>
       <c r="E46" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="F46" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>58.46</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>64.93000000000001</v>
+        <v>76.55</v>
       </c>
       <c r="J46" t="n">
-        <v>50.01</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="N46" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>22.33</v>
+        <v>17.46</v>
       </c>
       <c r="C47" t="n">
-        <v>22.66</v>
+        <v>17.67</v>
       </c>
       <c r="D47" t="n">
-        <v>21.95</v>
+        <v>17.22</v>
       </c>
       <c r="E47" t="n">
-        <v>9.9</v>
+        <v>13.2</v>
       </c>
       <c r="F47" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="G47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>46.23</v>
+        <v>76.84</v>
       </c>
       <c r="I47" t="n">
-        <v>48.69</v>
+        <v>79.37</v>
       </c>
       <c r="J47" t="n">
-        <v>44.45</v>
+        <v>75.08</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M47" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="N47" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.97</v>
+        <v>17.43</v>
       </c>
       <c r="C48" t="n">
-        <v>23.49</v>
+        <v>17.62</v>
       </c>
       <c r="D48" t="n">
-        <v>22.63</v>
+        <v>17.17</v>
       </c>
       <c r="E48" t="n">
-        <v>9.5</v>
+        <v>13.6</v>
       </c>
       <c r="F48" t="n">
-        <v>9.4</v>
+        <v>13.3</v>
       </c>
       <c r="G48" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>43.28</v>
+        <v>79.34</v>
       </c>
       <c r="I48" t="n">
-        <v>44.43</v>
+        <v>82.2</v>
       </c>
       <c r="J48" t="n">
-        <v>41.95</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M48" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>6180</v>
+        <v>6142</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>23.37</v>
+        <v>17.89</v>
       </c>
       <c r="C49" t="n">
-        <v>23.93</v>
+        <v>18.13</v>
       </c>
       <c r="D49" t="n">
-        <v>23.11</v>
+        <v>17.76</v>
       </c>
       <c r="E49" t="n">
-        <v>9.699999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="F49" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="G49" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>42.7</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>44.12</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>41.98</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="M49" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="N49" t="n">
-        <v>6190</v>
+        <v>6142</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.27</v>
+        <v>18.6</v>
       </c>
       <c r="C50" t="n">
-        <v>23.64</v>
+        <v>19.26</v>
       </c>
       <c r="D50" t="n">
-        <v>22.89</v>
+        <v>18.22</v>
       </c>
       <c r="E50" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="F50" t="n">
-        <v>9.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="G50" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>42.52</v>
+        <v>70.7</v>
       </c>
       <c r="I50" t="n">
-        <v>43.12</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>41.91</v>
+        <v>65.41</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="M50" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O50" t="n">
         <v>2.3</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,317 +508,317 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 19:00:00</t>
+          <t>2026-10-19 21:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.9</v>
+        <v>19.97</v>
       </c>
       <c r="C2" t="n">
-        <v>19.92</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>19.89</v>
+        <v>19.94</v>
       </c>
       <c r="E2" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="F2" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>54.7</v>
+        <v>55.74</v>
       </c>
       <c r="I2" t="n">
-        <v>54.82</v>
+        <v>55.91</v>
       </c>
       <c r="J2" t="n">
-        <v>54.53</v>
+        <v>55.55</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="N2" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-19 20:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.91</v>
+        <v>19.56</v>
       </c>
       <c r="C3" t="n">
-        <v>19.98</v>
+        <v>19.96</v>
       </c>
       <c r="D3" t="n">
-        <v>19.83</v>
+        <v>19.34</v>
       </c>
       <c r="E3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F3" t="n">
         <v>10.3</v>
       </c>
-      <c r="F3" t="n">
-        <v>10.2</v>
-      </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>54.74</v>
+        <v>56.91</v>
       </c>
       <c r="I3" t="n">
-        <v>54.92</v>
+        <v>57.67</v>
       </c>
       <c r="J3" t="n">
-        <v>54.61</v>
+        <v>55.82</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N3" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.31</v>
+        <v>19.8</v>
       </c>
       <c r="C4" t="n">
-        <v>20.99</v>
+        <v>19.92</v>
       </c>
       <c r="D4" t="n">
-        <v>19.97</v>
+        <v>19.62</v>
       </c>
       <c r="E4" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F4" t="n">
         <v>10.2</v>
       </c>
-      <c r="F4" t="n">
-        <v>10.1</v>
-      </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>53.29</v>
+        <v>55.22</v>
       </c>
       <c r="I4" t="n">
-        <v>54.84</v>
+        <v>56.29</v>
       </c>
       <c r="J4" t="n">
-        <v>51.22</v>
+        <v>54.46</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N4" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.38</v>
+        <v>19.91</v>
       </c>
       <c r="C5" t="n">
-        <v>21.67</v>
+        <v>19.98</v>
       </c>
       <c r="D5" t="n">
-        <v>20.91</v>
+        <v>19.83</v>
       </c>
       <c r="E5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F5" t="n">
         <v>10.2</v>
       </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
       <c r="G5" t="n">
-        <v>213</v>
+        <v>17</v>
       </c>
       <c r="H5" t="n">
-        <v>49.67</v>
+        <v>54.74</v>
       </c>
       <c r="I5" t="n">
-        <v>50.93</v>
+        <v>54.92</v>
       </c>
       <c r="J5" t="n">
-        <v>48.59</v>
+        <v>54.61</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.78</v>
+        <v>20.31</v>
       </c>
       <c r="C6" t="n">
-        <v>22.31</v>
+        <v>20.99</v>
       </c>
       <c r="D6" t="n">
-        <v>21.39</v>
+        <v>19.97</v>
       </c>
       <c r="E6" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F6" t="n">
         <v>10.1</v>
       </c>
-      <c r="F6" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="G6" t="n">
-        <v>323</v>
+        <v>40</v>
       </c>
       <c r="H6" t="n">
-        <v>48.06</v>
+        <v>53.29</v>
       </c>
       <c r="I6" t="n">
-        <v>48.87</v>
+        <v>54.84</v>
       </c>
       <c r="J6" t="n">
-        <v>46.24</v>
+        <v>51.22</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>6210</v>
+        <v>6170</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.97</v>
+        <v>21.38</v>
       </c>
       <c r="C7" t="n">
-        <v>24.27</v>
+        <v>21.67</v>
       </c>
       <c r="D7" t="n">
-        <v>22.16</v>
+        <v>20.91</v>
       </c>
       <c r="E7" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F7" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>747</v>
+        <v>213</v>
       </c>
       <c r="H7" t="n">
-        <v>44.85</v>
+        <v>49.67</v>
       </c>
       <c r="I7" t="n">
-        <v>47.21</v>
+        <v>50.93</v>
       </c>
       <c r="J7" t="n">
-        <v>41.93</v>
+        <v>48.59</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
-        <v>4.3</v>
-      </c>
       <c r="N7" t="n">
-        <v>6220</v>
+        <v>6190</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19 13:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.58</v>
+        <v>21.78</v>
       </c>
       <c r="C8" t="n">
-        <v>23.47</v>
+        <v>22.31</v>
       </c>
       <c r="D8" t="n">
-        <v>21.83</v>
+        <v>21.39</v>
       </c>
       <c r="E8" t="n">
         <v>10.1</v>
       </c>
       <c r="F8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>815</v>
+        <v>323</v>
       </c>
       <c r="H8" t="n">
-        <v>45.81</v>
+        <v>48.06</v>
       </c>
       <c r="I8" t="n">
-        <v>48.66</v>
+        <v>48.87</v>
       </c>
       <c r="J8" t="n">
-        <v>43.93</v>
+        <v>46.24</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -827,383 +827,383 @@
         <v>2.7</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>6220</v>
+        <v>6210</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19 12:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.31</v>
+        <v>22.97</v>
       </c>
       <c r="C9" t="n">
-        <v>22.4</v>
+        <v>24.27</v>
       </c>
       <c r="D9" t="n">
-        <v>20.2</v>
+        <v>22.16</v>
       </c>
       <c r="E9" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="F9" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>689</v>
+        <v>747</v>
       </c>
       <c r="H9" t="n">
-        <v>50.33</v>
+        <v>44.85</v>
       </c>
       <c r="I9" t="n">
-        <v>56.08</v>
+        <v>47.21</v>
       </c>
       <c r="J9" t="n">
-        <v>47.33</v>
+        <v>41.93</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19 11:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18.91</v>
+        <v>22.58</v>
       </c>
       <c r="C10" t="n">
-        <v>19.91</v>
+        <v>23.47</v>
       </c>
       <c r="D10" t="n">
-        <v>18.4</v>
+        <v>21.83</v>
       </c>
       <c r="E10" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="F10" t="n">
-        <v>10.6</v>
+        <v>9.6</v>
       </c>
       <c r="G10" t="n">
-        <v>305</v>
+        <v>815</v>
       </c>
       <c r="H10" t="n">
-        <v>60.58</v>
+        <v>45.81</v>
       </c>
       <c r="I10" t="n">
-        <v>63.06</v>
+        <v>48.66</v>
       </c>
       <c r="J10" t="n">
-        <v>55.94</v>
+        <v>43.93</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="N10" t="n">
-        <v>6162</v>
+        <v>6220</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.94</v>
+        <v>21.31</v>
       </c>
       <c r="C11" t="n">
-        <v>18.46</v>
+        <v>22.4</v>
       </c>
       <c r="D11" t="n">
-        <v>17.55</v>
+        <v>20.2</v>
       </c>
       <c r="E11" t="n">
-        <v>11.6</v>
+        <v>10.4</v>
       </c>
       <c r="F11" t="n">
-        <v>11.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>189</v>
+        <v>689</v>
       </c>
       <c r="H11" t="n">
-        <v>67.54000000000001</v>
+        <v>50.33</v>
       </c>
       <c r="I11" t="n">
-        <v>70.20999999999999</v>
+        <v>56.08</v>
       </c>
       <c r="J11" t="n">
-        <v>64.44</v>
+        <v>47.33</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="N11" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.55</v>
+        <v>18.91</v>
       </c>
       <c r="C12" t="n">
-        <v>17.81</v>
+        <v>19.91</v>
       </c>
       <c r="D12" t="n">
-        <v>17.2</v>
+        <v>18.4</v>
       </c>
       <c r="E12" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="F12" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="G12" t="n">
-        <v>95</v>
+        <v>305</v>
       </c>
       <c r="H12" t="n">
-        <v>68.43000000000001</v>
+        <v>60.58</v>
       </c>
       <c r="I12" t="n">
-        <v>69.95</v>
+        <v>63.06</v>
       </c>
       <c r="J12" t="n">
-        <v>65.48</v>
+        <v>55.94</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="N12" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.64</v>
+        <v>17.94</v>
       </c>
       <c r="C13" t="n">
-        <v>17.06</v>
+        <v>18.46</v>
       </c>
       <c r="D13" t="n">
-        <v>16.2</v>
+        <v>17.55</v>
       </c>
       <c r="E13" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F13" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G13" t="n">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="H13" t="n">
-        <v>72.79000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>77.45</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>70.3</v>
+        <v>64.44</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.62</v>
+        <v>17.55</v>
       </c>
       <c r="C14" t="n">
-        <v>16.07</v>
+        <v>17.81</v>
       </c>
       <c r="D14" t="n">
-        <v>15.35</v>
+        <v>17.2</v>
       </c>
       <c r="E14" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="F14" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="H14" t="n">
-        <v>85.33</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>89.23</v>
+        <v>69.95</v>
       </c>
       <c r="J14" t="n">
-        <v>79.03</v>
+        <v>65.48</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N14" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.25</v>
+        <v>16.64</v>
       </c>
       <c r="C15" t="n">
-        <v>15.35</v>
+        <v>17.06</v>
       </c>
       <c r="D15" t="n">
-        <v>15.06</v>
+        <v>16.2</v>
       </c>
       <c r="E15" t="n">
-        <v>13.3</v>
+        <v>11.5</v>
       </c>
       <c r="F15" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H15" t="n">
-        <v>89.16</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>91.05</v>
+        <v>77.45</v>
       </c>
       <c r="J15" t="n">
-        <v>87.77</v>
+        <v>70.3</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N15" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.2</v>
+        <v>15.62</v>
       </c>
       <c r="C16" t="n">
-        <v>15.32</v>
+        <v>16.07</v>
       </c>
       <c r="D16" t="n">
-        <v>15.08</v>
+        <v>15.35</v>
       </c>
       <c r="E16" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="F16" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>88.42</v>
+        <v>85.33</v>
       </c>
       <c r="I16" t="n">
-        <v>89.37</v>
+        <v>89.23</v>
       </c>
       <c r="J16" t="n">
-        <v>87.13</v>
+        <v>79.03</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>6122</v>
@@ -1213,35 +1213,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.53</v>
+        <v>15.25</v>
       </c>
       <c r="C17" t="n">
-        <v>15.66</v>
+        <v>15.35</v>
       </c>
       <c r="D17" t="n">
-        <v>15.45</v>
+        <v>15.06</v>
       </c>
       <c r="E17" t="n">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
       <c r="F17" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>85.40000000000001</v>
+        <v>89.16</v>
       </c>
       <c r="I17" t="n">
-        <v>86.58</v>
+        <v>91.05</v>
       </c>
       <c r="J17" t="n">
-        <v>83.42</v>
+        <v>87.77</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1260,44 +1260,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15.66</v>
+        <v>15.2</v>
       </c>
       <c r="C18" t="n">
-        <v>15.73</v>
+        <v>15.32</v>
       </c>
       <c r="D18" t="n">
-        <v>15.62</v>
+        <v>15.08</v>
       </c>
       <c r="E18" t="n">
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
       <c r="F18" t="n">
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>82.52</v>
+        <v>88.42</v>
       </c>
       <c r="I18" t="n">
-        <v>82.76000000000001</v>
+        <v>89.37</v>
       </c>
       <c r="J18" t="n">
-        <v>82.33</v>
+        <v>87.13</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>6122</v>
@@ -1307,44 +1307,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15.72</v>
+        <v>15.53</v>
       </c>
       <c r="C19" t="n">
-        <v>15.77</v>
+        <v>15.66</v>
       </c>
       <c r="D19" t="n">
-        <v>15.65</v>
+        <v>15.45</v>
       </c>
       <c r="E19" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="F19" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>81.17</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>82.40000000000001</v>
+        <v>86.58</v>
       </c>
       <c r="J19" t="n">
-        <v>80.16</v>
+        <v>83.42</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>6122</v>
@@ -1354,44 +1354,44 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.09</v>
+        <v>15.66</v>
       </c>
       <c r="C20" t="n">
-        <v>16.59</v>
+        <v>15.73</v>
       </c>
       <c r="D20" t="n">
-        <v>15.76</v>
+        <v>15.62</v>
       </c>
       <c r="E20" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="F20" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>76.7</v>
+        <v>82.52</v>
       </c>
       <c r="I20" t="n">
-        <v>80.06999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>72.89</v>
+        <v>82.33</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
         <v>6122</v>
@@ -1401,35 +1401,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.2</v>
+        <v>15.72</v>
       </c>
       <c r="C21" t="n">
-        <v>16.53</v>
+        <v>15.77</v>
       </c>
       <c r="D21" t="n">
-        <v>15.84</v>
+        <v>15.65</v>
       </c>
       <c r="E21" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="F21" t="n">
-        <v>11.6</v>
+        <v>12.3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>77.2</v>
+        <v>81.17</v>
       </c>
       <c r="I21" t="n">
-        <v>80.54000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>73.31999999999999</v>
+        <v>80.16</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0.6</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
         <v>6122</v>
@@ -1448,44 +1448,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.03</v>
+        <v>16.09</v>
       </c>
       <c r="C22" t="n">
-        <v>16.12</v>
+        <v>16.59</v>
       </c>
       <c r="D22" t="n">
-        <v>15.93</v>
+        <v>15.76</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="F22" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>77.56</v>
+        <v>76.7</v>
       </c>
       <c r="I22" t="n">
-        <v>79.16</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>76.79000000000001</v>
+        <v>72.89</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N22" t="n">
         <v>6122</v>
@@ -1495,41 +1495,41 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15.79</v>
+        <v>16.2</v>
       </c>
       <c r="C23" t="n">
-        <v>15.92</v>
+        <v>16.53</v>
       </c>
       <c r="D23" t="n">
-        <v>15.7</v>
+        <v>15.84</v>
       </c>
       <c r="E23" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="F23" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>78.34999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="I23" t="n">
-        <v>78.65000000000001</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>77.79000000000001</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M23" t="n">
         <v>1.3</v>
@@ -1542,44 +1542,44 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.9</v>
+        <v>16.03</v>
       </c>
       <c r="C24" t="n">
-        <v>16.37</v>
+        <v>16.12</v>
       </c>
       <c r="D24" t="n">
-        <v>15.67</v>
+        <v>15.93</v>
       </c>
       <c r="E24" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>76.45999999999999</v>
+        <v>77.56</v>
       </c>
       <c r="I24" t="n">
-        <v>78.44</v>
+        <v>79.16</v>
       </c>
       <c r="J24" t="n">
-        <v>72.33</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="N24" t="n">
         <v>6122</v>
@@ -1589,138 +1589,138 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16.37</v>
+        <v>15.79</v>
       </c>
       <c r="C25" t="n">
-        <v>16.48</v>
+        <v>15.92</v>
       </c>
       <c r="D25" t="n">
-        <v>16.29</v>
+        <v>15.7</v>
       </c>
       <c r="E25" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="F25" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>74.02</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>74.88</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>72.13</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="N25" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16.84</v>
+        <v>15.9</v>
       </c>
       <c r="C26" t="n">
-        <v>17.08</v>
+        <v>16.37</v>
       </c>
       <c r="D26" t="n">
-        <v>16.57</v>
+        <v>15.67</v>
       </c>
       <c r="E26" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F26" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>70.64</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>72.89</v>
+        <v>78.44</v>
       </c>
       <c r="J26" t="n">
-        <v>68.62</v>
+        <v>72.33</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N26" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.26</v>
+        <v>16.37</v>
       </c>
       <c r="C27" t="n">
-        <v>17.41</v>
+        <v>16.48</v>
       </c>
       <c r="D27" t="n">
-        <v>17.13</v>
+        <v>16.29</v>
       </c>
       <c r="E27" t="n">
-        <v>10.7</v>
+        <v>11.6</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="G27" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>65.97</v>
+        <v>74.02</v>
       </c>
       <c r="I27" t="n">
-        <v>68.3</v>
+        <v>74.88</v>
       </c>
       <c r="J27" t="n">
-        <v>62.44</v>
+        <v>72.13</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="N27" t="n">
         <v>6132</v>
@@ -1730,138 +1730,138 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17.57</v>
+        <v>16.84</v>
       </c>
       <c r="C28" t="n">
-        <v>18.11</v>
+        <v>17.08</v>
       </c>
       <c r="D28" t="n">
-        <v>17.4</v>
+        <v>16.57</v>
       </c>
       <c r="E28" t="n">
-        <v>10.4</v>
+        <v>11.3</v>
       </c>
       <c r="F28" t="n">
-        <v>9.800000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="G28" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>63.38</v>
+        <v>70.64</v>
       </c>
       <c r="I28" t="n">
-        <v>64.3</v>
+        <v>72.89</v>
       </c>
       <c r="J28" t="n">
-        <v>61.77</v>
+        <v>68.62</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="N28" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18</v>
+        <v>17.26</v>
       </c>
       <c r="C29" t="n">
-        <v>18.2</v>
+        <v>17.41</v>
       </c>
       <c r="D29" t="n">
-        <v>17.79</v>
+        <v>17.13</v>
       </c>
       <c r="E29" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="F29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="H29" t="n">
-        <v>62.96</v>
+        <v>65.97</v>
       </c>
       <c r="I29" t="n">
-        <v>64.08</v>
+        <v>68.3</v>
       </c>
       <c r="J29" t="n">
-        <v>61.81</v>
+        <v>62.44</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N29" t="n">
-        <v>6162</v>
+        <v>6132</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>18.15</v>
+        <v>17.57</v>
       </c>
       <c r="C30" t="n">
-        <v>18.5</v>
+        <v>18.11</v>
       </c>
       <c r="D30" t="n">
-        <v>17.92</v>
+        <v>17.4</v>
       </c>
       <c r="E30" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="H30" t="n">
-        <v>60.86</v>
+        <v>63.38</v>
       </c>
       <c r="I30" t="n">
-        <v>62.23</v>
+        <v>64.3</v>
       </c>
       <c r="J30" t="n">
-        <v>59.51</v>
+        <v>61.77</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="N30" t="n">
         <v>6142</v>
@@ -1871,317 +1871,317 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.71</v>
+        <v>18</v>
       </c>
       <c r="C31" t="n">
-        <v>18.05</v>
+        <v>18.2</v>
       </c>
       <c r="D31" t="n">
-        <v>17.31</v>
+        <v>17.79</v>
       </c>
       <c r="E31" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="F31" t="n">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="G31" t="n">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="H31" t="n">
-        <v>61.59</v>
+        <v>62.96</v>
       </c>
       <c r="I31" t="n">
-        <v>63.45</v>
+        <v>64.08</v>
       </c>
       <c r="J31" t="n">
-        <v>59.82</v>
+        <v>61.81</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N31" t="n">
-        <v>6170</v>
+        <v>6162</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.72</v>
+        <v>18.15</v>
       </c>
       <c r="C32" t="n">
-        <v>17.47</v>
+        <v>18.5</v>
       </c>
       <c r="D32" t="n">
-        <v>16.08</v>
+        <v>17.92</v>
       </c>
       <c r="E32" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F32" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="H32" t="n">
-        <v>67.33</v>
+        <v>60.86</v>
       </c>
       <c r="I32" t="n">
-        <v>70.81999999999999</v>
+        <v>62.23</v>
       </c>
       <c r="J32" t="n">
-        <v>63.98</v>
+        <v>59.51</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15.83</v>
+        <v>17.71</v>
       </c>
       <c r="C33" t="n">
-        <v>16.23</v>
+        <v>18.05</v>
       </c>
       <c r="D33" t="n">
-        <v>15.45</v>
+        <v>17.31</v>
       </c>
       <c r="E33" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="F33" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="G33" t="n">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="H33" t="n">
-        <v>72.95</v>
+        <v>61.59</v>
       </c>
       <c r="I33" t="n">
-        <v>75.03</v>
+        <v>63.45</v>
       </c>
       <c r="J33" t="n">
-        <v>69.84999999999999</v>
+        <v>59.82</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="M33" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15.22</v>
+        <v>16.72</v>
       </c>
       <c r="C34" t="n">
-        <v>15.77</v>
+        <v>17.47</v>
       </c>
       <c r="D34" t="n">
-        <v>14.97</v>
+        <v>16.08</v>
       </c>
       <c r="E34" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="F34" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>158</v>
+        <v>260</v>
       </c>
       <c r="H34" t="n">
-        <v>77.61</v>
+        <v>67.33</v>
       </c>
       <c r="I34" t="n">
-        <v>79.25</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>74.45</v>
+        <v>63.98</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M34" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N34" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>14.79</v>
+        <v>15.83</v>
       </c>
       <c r="C35" t="n">
-        <v>15.1</v>
+        <v>16.23</v>
       </c>
       <c r="D35" t="n">
-        <v>14.32</v>
+        <v>15.45</v>
       </c>
       <c r="E35" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="F35" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="G35" t="n">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="H35" t="n">
-        <v>80.70999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="I35" t="n">
-        <v>83.36</v>
+        <v>75.03</v>
       </c>
       <c r="J35" t="n">
-        <v>79.05</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M35" t="n">
         <v>1.4</v>
       </c>
       <c r="N35" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>14.05</v>
+        <v>15.22</v>
       </c>
       <c r="C36" t="n">
-        <v>14.26</v>
+        <v>15.77</v>
       </c>
       <c r="D36" t="n">
-        <v>13.8</v>
+        <v>14.97</v>
       </c>
       <c r="E36" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="F36" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="G36" t="n">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="H36" t="n">
-        <v>85.09</v>
+        <v>77.61</v>
       </c>
       <c r="I36" t="n">
-        <v>86.40000000000001</v>
+        <v>79.25</v>
       </c>
       <c r="J36" t="n">
-        <v>84.14</v>
+        <v>74.45</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>1.4</v>
       </c>
       <c r="N36" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>14.11</v>
+        <v>14.79</v>
       </c>
       <c r="C37" t="n">
-        <v>14.56</v>
+        <v>15.1</v>
       </c>
       <c r="D37" t="n">
-        <v>13.7</v>
+        <v>14.32</v>
       </c>
       <c r="E37" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="G37" t="n">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="H37" t="n">
-        <v>81.01000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>87.31</v>
+        <v>83.36</v>
       </c>
       <c r="J37" t="n">
-        <v>75.84999999999999</v>
+        <v>79.05</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2190,101 +2190,101 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N37" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14.64</v>
+        <v>14.05</v>
       </c>
       <c r="C38" t="n">
-        <v>14.86</v>
+        <v>14.26</v>
       </c>
       <c r="D38" t="n">
-        <v>14.45</v>
+        <v>13.8</v>
       </c>
       <c r="E38" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="F38" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="G38" t="n">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="H38" t="n">
-        <v>79.53</v>
+        <v>85.09</v>
       </c>
       <c r="I38" t="n">
-        <v>82.73999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>76.79000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N38" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>15.07</v>
+        <v>14.11</v>
       </c>
       <c r="C39" t="n">
-        <v>15.23</v>
+        <v>14.56</v>
       </c>
       <c r="D39" t="n">
-        <v>14.92</v>
+        <v>13.7</v>
       </c>
       <c r="E39" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="F39" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H39" t="n">
-        <v>77.61</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>78.94</v>
+        <v>87.31</v>
       </c>
       <c r="J39" t="n">
-        <v>76.67</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N39" t="n">
         <v>6132</v>
@@ -2294,44 +2294,44 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15.37</v>
+        <v>14.64</v>
       </c>
       <c r="C40" t="n">
-        <v>15.49</v>
+        <v>14.86</v>
       </c>
       <c r="D40" t="n">
-        <v>15.25</v>
+        <v>14.45</v>
       </c>
       <c r="E40" t="n">
-        <v>11.8</v>
+        <v>10.9</v>
       </c>
       <c r="F40" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H40" t="n">
-        <v>79.81999999999999</v>
+        <v>79.53</v>
       </c>
       <c r="I40" t="n">
-        <v>80.69</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>78.86</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N40" t="n">
         <v>6132</v>
@@ -2341,44 +2341,44 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.65</v>
+        <v>15.07</v>
       </c>
       <c r="C41" t="n">
-        <v>15.77</v>
+        <v>15.23</v>
       </c>
       <c r="D41" t="n">
-        <v>15.48</v>
+        <v>14.92</v>
       </c>
       <c r="E41" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="F41" t="n">
-        <v>11.6</v>
+        <v>10.7</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>78.64</v>
+        <v>77.61</v>
       </c>
       <c r="I41" t="n">
-        <v>80.7</v>
+        <v>78.94</v>
       </c>
       <c r="J41" t="n">
-        <v>77.23</v>
+        <v>76.67</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="M41" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
         <v>6132</v>
@@ -2388,91 +2388,91 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.39</v>
+        <v>15.37</v>
       </c>
       <c r="C42" t="n">
-        <v>15.59</v>
+        <v>15.49</v>
       </c>
       <c r="D42" t="n">
-        <v>15.29</v>
+        <v>15.25</v>
       </c>
       <c r="E42" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="F42" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>84.89</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>87.12</v>
+        <v>80.69</v>
       </c>
       <c r="J42" t="n">
-        <v>81.20999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M42" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N42" t="n">
-        <v>6112</v>
+        <v>6132</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15.61</v>
+        <v>15.65</v>
       </c>
       <c r="C43" t="n">
-        <v>16.09</v>
+        <v>15.77</v>
       </c>
       <c r="D43" t="n">
-        <v>15.44</v>
+        <v>15.48</v>
       </c>
       <c r="E43" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="F43" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>84.45</v>
+        <v>78.64</v>
       </c>
       <c r="I43" t="n">
-        <v>86.2</v>
+        <v>80.7</v>
       </c>
       <c r="J43" t="n">
-        <v>79</v>
+        <v>77.23</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="M43" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="N43" t="n">
         <v>6132</v>
@@ -2482,140 +2482,138 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.78</v>
+        <v>15.39</v>
       </c>
       <c r="C44" t="n">
-        <v>17.16</v>
+        <v>15.59</v>
       </c>
       <c r="D44" t="n">
-        <v>16.31</v>
+        <v>15.29</v>
       </c>
       <c r="E44" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="F44" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>73.62</v>
+        <v>84.89</v>
       </c>
       <c r="I44" t="n">
-        <v>76.98999999999999</v>
+        <v>87.12</v>
       </c>
       <c r="J44" t="n">
-        <v>69.84</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="M44" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="N44" t="n">
-        <v>6122</v>
+        <v>6112</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.55</v>
+        <v>15.61</v>
       </c>
       <c r="C45" t="n">
-        <v>17.8</v>
+        <v>16.09</v>
       </c>
       <c r="D45" t="n">
-        <v>17.2</v>
+        <v>15.44</v>
       </c>
       <c r="E45" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="F45" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>71.04000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="I45" t="n">
-        <v>73.81</v>
+        <v>86.2</v>
       </c>
       <c r="J45" t="n">
-        <v>69.28</v>
+        <v>79</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="M45" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="N45" t="n">
-        <v>6142</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.6</v>
-      </c>
+        <v>6132</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.63</v>
+        <v>16.78</v>
       </c>
       <c r="C46" t="n">
-        <v>18.08</v>
+        <v>17.16</v>
       </c>
       <c r="D46" t="n">
-        <v>17.4</v>
+        <v>16.31</v>
       </c>
       <c r="E46" t="n">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>73.43000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="I46" t="n">
-        <v>76.55</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>68.51000000000001</v>
+        <v>69.84</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M46" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="N46" t="n">
         <v>6122</v>
@@ -2625,82 +2623,84 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.46</v>
+        <v>17.55</v>
       </c>
       <c r="C47" t="n">
-        <v>17.67</v>
+        <v>17.8</v>
       </c>
       <c r="D47" t="n">
-        <v>17.22</v>
+        <v>17.2</v>
       </c>
       <c r="E47" t="n">
-        <v>13.2</v>
+        <v>12.1</v>
       </c>
       <c r="F47" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>76.84</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>79.37</v>
+        <v>73.81</v>
       </c>
       <c r="J47" t="n">
-        <v>75.08</v>
+        <v>69.28</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="N47" t="n">
-        <v>6132</v>
-      </c>
-      <c r="O47" t="inlineStr"/>
+        <v>6142</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.43</v>
+        <v>17.63</v>
       </c>
       <c r="C48" t="n">
-        <v>17.62</v>
+        <v>18.08</v>
       </c>
       <c r="D48" t="n">
-        <v>17.17</v>
+        <v>17.4</v>
       </c>
       <c r="E48" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="F48" t="n">
-        <v>13.3</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>79.34</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>82.2</v>
+        <v>76.55</v>
       </c>
       <c r="J48" t="n">
-        <v>77.51000000000001</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2709,104 +2709,104 @@
         <v>1.8</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="N48" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.89</v>
+        <v>17.46</v>
       </c>
       <c r="C49" t="n">
-        <v>18.13</v>
+        <v>17.67</v>
       </c>
       <c r="D49" t="n">
-        <v>17.76</v>
+        <v>17.22</v>
       </c>
       <c r="E49" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="F49" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>76.29000000000001</v>
+        <v>76.84</v>
       </c>
       <c r="I49" t="n">
-        <v>78.06999999999999</v>
+        <v>79.37</v>
       </c>
       <c r="J49" t="n">
-        <v>74.34999999999999</v>
+        <v>75.08</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="N49" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>18.6</v>
+        <v>17.43</v>
       </c>
       <c r="C50" t="n">
-        <v>19.26</v>
+        <v>17.62</v>
       </c>
       <c r="D50" t="n">
-        <v>18.22</v>
+        <v>17.17</v>
       </c>
       <c r="E50" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="F50" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>70.7</v>
+        <v>79.34</v>
       </c>
       <c r="I50" t="n">
-        <v>73.79000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="J50" t="n">
-        <v>65.41</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O50" t="n">
         <v>2.3</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,984 +508,984 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 21:00:00</t>
+          <t>2026-10-20 03:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.97</v>
+        <v>17.05</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>17.22</v>
       </c>
       <c r="D2" t="n">
-        <v>19.94</v>
+        <v>16.88</v>
       </c>
       <c r="E2" t="n">
-        <v>10.6</v>
+        <v>12.5</v>
       </c>
       <c r="F2" t="n">
-        <v>10.6</v>
+        <v>12.5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>55.74</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>55.91</v>
+        <v>76.7</v>
       </c>
       <c r="J2" t="n">
-        <v>55.55</v>
+        <v>74.67</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>6132</v>
+        <v>6102</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 20:00:00</t>
+          <t>2026-10-20 02:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.56</v>
+        <v>17.59</v>
       </c>
       <c r="C3" t="n">
-        <v>19.96</v>
+        <v>17.8</v>
       </c>
       <c r="D3" t="n">
-        <v>19.34</v>
+        <v>17.29</v>
       </c>
       <c r="E3" t="n">
-        <v>10.6</v>
+        <v>12.7</v>
       </c>
       <c r="F3" t="n">
-        <v>10.3</v>
+        <v>12.5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>56.91</v>
+        <v>73.83</v>
       </c>
       <c r="I3" t="n">
-        <v>57.67</v>
+        <v>74.95</v>
       </c>
       <c r="J3" t="n">
-        <v>55.82</v>
+        <v>72.36</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 19:00:00</t>
+          <t>2026-10-20 01:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.8</v>
+        <v>18.24</v>
       </c>
       <c r="C4" t="n">
-        <v>19.92</v>
+        <v>18.59</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62</v>
+        <v>17.84</v>
       </c>
       <c r="E4" t="n">
-        <v>10.3</v>
+        <v>11.8</v>
       </c>
       <c r="F4" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>55.22</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>56.29</v>
+        <v>71.14</v>
       </c>
       <c r="J4" t="n">
-        <v>54.46</v>
+        <v>63.93</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6152</v>
+        <v>6092</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-20 00:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.91</v>
+        <v>18.68</v>
       </c>
       <c r="C5" t="n">
-        <v>19.98</v>
+        <v>18.93</v>
       </c>
       <c r="D5" t="n">
-        <v>19.83</v>
+        <v>18.52</v>
       </c>
       <c r="E5" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
       <c r="F5" t="n">
-        <v>10.2</v>
+        <v>11.2</v>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>54.74</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>54.92</v>
+        <v>65.87</v>
       </c>
       <c r="J5" t="n">
-        <v>54.61</v>
+        <v>61.94</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-19 23:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.31</v>
+        <v>19.43</v>
       </c>
       <c r="C6" t="n">
-        <v>20.99</v>
+        <v>19.64</v>
       </c>
       <c r="D6" t="n">
-        <v>19.97</v>
+        <v>19.01</v>
       </c>
       <c r="E6" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="F6" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="G6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>53.29</v>
+        <v>60.1</v>
       </c>
       <c r="I6" t="n">
-        <v>54.84</v>
+        <v>60.96</v>
       </c>
       <c r="J6" t="n">
-        <v>51.22</v>
+        <v>59.25</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-19 22:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.38</v>
+        <v>20.1</v>
       </c>
       <c r="C7" t="n">
-        <v>21.67</v>
+        <v>20.3</v>
       </c>
       <c r="D7" t="n">
-        <v>20.91</v>
+        <v>19.77</v>
       </c>
       <c r="E7" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="G7" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>49.67</v>
+        <v>56.64</v>
       </c>
       <c r="I7" t="n">
-        <v>50.93</v>
+        <v>58.8</v>
       </c>
       <c r="J7" t="n">
-        <v>48.59</v>
+        <v>55.68</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="n">
-        <v>6190</v>
+        <v>6112</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00:00</t>
+          <t>2026-10-19 21:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.78</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>22.31</v>
+        <v>20.17</v>
       </c>
       <c r="D8" t="n">
-        <v>21.39</v>
+        <v>19.94</v>
       </c>
       <c r="E8" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="F8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="G8" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>48.06</v>
+        <v>55.69</v>
       </c>
       <c r="I8" t="n">
-        <v>48.87</v>
+        <v>55.96</v>
       </c>
       <c r="J8" t="n">
-        <v>46.24</v>
+        <v>55.41</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="N8" t="n">
-        <v>6210</v>
+        <v>6142</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 20:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.97</v>
+        <v>19.56</v>
       </c>
       <c r="C9" t="n">
-        <v>24.27</v>
+        <v>19.96</v>
       </c>
       <c r="D9" t="n">
-        <v>22.16</v>
+        <v>19.34</v>
       </c>
       <c r="E9" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="F9" t="n">
-        <v>9.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="G9" t="n">
-        <v>747</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>44.85</v>
+        <v>56.91</v>
       </c>
       <c r="I9" t="n">
-        <v>47.21</v>
+        <v>57.67</v>
       </c>
       <c r="J9" t="n">
-        <v>41.93</v>
+        <v>55.82</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="N9" t="n">
-        <v>6220</v>
+        <v>6142</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19 13:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.58</v>
+        <v>19.8</v>
       </c>
       <c r="C10" t="n">
-        <v>23.47</v>
+        <v>19.92</v>
       </c>
       <c r="D10" t="n">
-        <v>21.83</v>
+        <v>19.62</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="F10" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="G10" t="n">
-        <v>815</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>45.81</v>
+        <v>55.22</v>
       </c>
       <c r="I10" t="n">
-        <v>48.66</v>
+        <v>56.29</v>
       </c>
       <c r="J10" t="n">
-        <v>43.93</v>
+        <v>54.46</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="N10" t="n">
-        <v>6220</v>
+        <v>6152</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19 12:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.31</v>
+        <v>19.91</v>
       </c>
       <c r="C11" t="n">
-        <v>22.4</v>
+        <v>19.98</v>
       </c>
       <c r="D11" t="n">
-        <v>20.2</v>
+        <v>19.83</v>
       </c>
       <c r="E11" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F11" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G11" t="n">
-        <v>689</v>
+        <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>50.33</v>
+        <v>54.74</v>
       </c>
       <c r="I11" t="n">
-        <v>56.08</v>
+        <v>54.92</v>
       </c>
       <c r="J11" t="n">
-        <v>47.33</v>
+        <v>54.61</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19 11:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.91</v>
+        <v>20.31</v>
       </c>
       <c r="C12" t="n">
-        <v>19.91</v>
+        <v>20.99</v>
       </c>
       <c r="D12" t="n">
-        <v>18.4</v>
+        <v>19.97</v>
       </c>
       <c r="E12" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="F12" t="n">
-        <v>10.6</v>
+        <v>10.1</v>
       </c>
       <c r="G12" t="n">
-        <v>305</v>
+        <v>40</v>
       </c>
       <c r="H12" t="n">
-        <v>60.58</v>
+        <v>53.29</v>
       </c>
       <c r="I12" t="n">
-        <v>63.06</v>
+        <v>54.84</v>
       </c>
       <c r="J12" t="n">
-        <v>55.94</v>
+        <v>51.22</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.94</v>
+        <v>21.38</v>
       </c>
       <c r="C13" t="n">
-        <v>18.46</v>
+        <v>21.67</v>
       </c>
       <c r="D13" t="n">
-        <v>17.55</v>
+        <v>20.91</v>
       </c>
       <c r="E13" t="n">
-        <v>11.6</v>
+        <v>10.2</v>
       </c>
       <c r="F13" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="H13" t="n">
-        <v>67.54000000000001</v>
+        <v>49.67</v>
       </c>
       <c r="I13" t="n">
-        <v>70.20999999999999</v>
+        <v>50.93</v>
       </c>
       <c r="J13" t="n">
-        <v>64.44</v>
+        <v>48.59</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.55</v>
+        <v>21.78</v>
       </c>
       <c r="C14" t="n">
-        <v>17.81</v>
+        <v>22.31</v>
       </c>
       <c r="D14" t="n">
-        <v>17.2</v>
+        <v>21.39</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="F14" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="H14" t="n">
-        <v>68.43000000000001</v>
+        <v>48.06</v>
       </c>
       <c r="I14" t="n">
-        <v>69.95</v>
+        <v>48.87</v>
       </c>
       <c r="J14" t="n">
-        <v>65.48</v>
+        <v>46.24</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>6132</v>
+        <v>6210</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.64</v>
+        <v>22.97</v>
       </c>
       <c r="C15" t="n">
-        <v>17.06</v>
+        <v>24.27</v>
       </c>
       <c r="D15" t="n">
-        <v>16.2</v>
+        <v>22.16</v>
       </c>
       <c r="E15" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="F15" t="n">
-        <v>11.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>44</v>
+        <v>747</v>
       </c>
       <c r="H15" t="n">
-        <v>72.79000000000001</v>
+        <v>44.85</v>
       </c>
       <c r="I15" t="n">
-        <v>77.45</v>
+        <v>47.21</v>
       </c>
       <c r="J15" t="n">
-        <v>70.3</v>
+        <v>41.93</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>6132</v>
+        <v>6220</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.62</v>
+        <v>22.58</v>
       </c>
       <c r="C16" t="n">
-        <v>16.07</v>
+        <v>23.47</v>
       </c>
       <c r="D16" t="n">
-        <v>15.35</v>
+        <v>21.83</v>
       </c>
       <c r="E16" t="n">
-        <v>12.9</v>
+        <v>10.1</v>
       </c>
       <c r="F16" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>815</v>
       </c>
       <c r="H16" t="n">
-        <v>85.33</v>
+        <v>45.81</v>
       </c>
       <c r="I16" t="n">
-        <v>89.23</v>
+        <v>48.66</v>
       </c>
       <c r="J16" t="n">
-        <v>79.03</v>
+        <v>43.93</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="N16" t="n">
-        <v>6122</v>
+        <v>6220</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.25</v>
+        <v>21.31</v>
       </c>
       <c r="C17" t="n">
-        <v>15.35</v>
+        <v>22.4</v>
       </c>
       <c r="D17" t="n">
-        <v>15.06</v>
+        <v>20.2</v>
       </c>
       <c r="E17" t="n">
-        <v>13.3</v>
+        <v>10.4</v>
       </c>
       <c r="F17" t="n">
-        <v>13.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>689</v>
       </c>
       <c r="H17" t="n">
-        <v>89.16</v>
+        <v>50.33</v>
       </c>
       <c r="I17" t="n">
-        <v>91.05</v>
+        <v>56.08</v>
       </c>
       <c r="J17" t="n">
-        <v>87.77</v>
+        <v>47.33</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N17" t="n">
-        <v>6122</v>
+        <v>6190</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15.2</v>
+        <v>18.91</v>
       </c>
       <c r="C18" t="n">
-        <v>15.32</v>
+        <v>19.91</v>
       </c>
       <c r="D18" t="n">
-        <v>15.08</v>
+        <v>18.4</v>
       </c>
       <c r="E18" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="F18" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="H18" t="n">
-        <v>88.42</v>
+        <v>60.58</v>
       </c>
       <c r="I18" t="n">
-        <v>89.37</v>
+        <v>63.06</v>
       </c>
       <c r="J18" t="n">
-        <v>87.13</v>
+        <v>55.94</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N18" t="n">
-        <v>6122</v>
+        <v>6162</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15.53</v>
+        <v>17.94</v>
       </c>
       <c r="C19" t="n">
-        <v>15.66</v>
+        <v>18.46</v>
       </c>
       <c r="D19" t="n">
-        <v>15.45</v>
+        <v>17.55</v>
       </c>
       <c r="E19" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="F19" t="n">
-        <v>12.7</v>
+        <v>11.2</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H19" t="n">
-        <v>85.40000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>86.58</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>83.42</v>
+        <v>64.44</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>6122</v>
+        <v>6152</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.66</v>
+        <v>17.55</v>
       </c>
       <c r="C20" t="n">
-        <v>15.73</v>
+        <v>17.81</v>
       </c>
       <c r="D20" t="n">
-        <v>15.62</v>
+        <v>17.2</v>
       </c>
       <c r="E20" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="F20" t="n">
-        <v>12.5</v>
+        <v>10.9</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H20" t="n">
-        <v>82.52</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>82.76000000000001</v>
+        <v>69.95</v>
       </c>
       <c r="J20" t="n">
-        <v>82.33</v>
+        <v>65.48</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N20" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.72</v>
+        <v>16.64</v>
       </c>
       <c r="C21" t="n">
-        <v>15.77</v>
+        <v>17.06</v>
       </c>
       <c r="D21" t="n">
-        <v>15.65</v>
+        <v>16.2</v>
       </c>
       <c r="E21" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="F21" t="n">
-        <v>12.3</v>
+        <v>11.4</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H21" t="n">
-        <v>81.17</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>82.40000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="J21" t="n">
-        <v>80.16</v>
+        <v>70.3</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N21" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.09</v>
+        <v>15.62</v>
       </c>
       <c r="C22" t="n">
-        <v>16.59</v>
+        <v>16.07</v>
       </c>
       <c r="D22" t="n">
-        <v>15.76</v>
+        <v>15.35</v>
       </c>
       <c r="E22" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="F22" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H22" t="n">
-        <v>76.7</v>
+        <v>85.33</v>
       </c>
       <c r="I22" t="n">
-        <v>80.06999999999999</v>
+        <v>89.23</v>
       </c>
       <c r="J22" t="n">
-        <v>72.89</v>
+        <v>79.03</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>6122</v>
@@ -1495,44 +1495,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.2</v>
+        <v>15.25</v>
       </c>
       <c r="C23" t="n">
-        <v>16.53</v>
+        <v>15.35</v>
       </c>
       <c r="D23" t="n">
-        <v>15.84</v>
+        <v>15.06</v>
       </c>
       <c r="E23" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="F23" t="n">
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>77.2</v>
+        <v>89.16</v>
       </c>
       <c r="I23" t="n">
-        <v>80.54000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="J23" t="n">
-        <v>73.31999999999999</v>
+        <v>87.77</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>6122</v>
@@ -1542,44 +1542,44 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.03</v>
+        <v>15.2</v>
       </c>
       <c r="C24" t="n">
-        <v>16.12</v>
+        <v>15.32</v>
       </c>
       <c r="D24" t="n">
-        <v>15.93</v>
+        <v>15.08</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="F24" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>77.56</v>
+        <v>88.42</v>
       </c>
       <c r="I24" t="n">
-        <v>79.16</v>
+        <v>89.37</v>
       </c>
       <c r="J24" t="n">
-        <v>76.79000000000001</v>
+        <v>87.13</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>6122</v>
@@ -1589,44 +1589,44 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15.79</v>
+        <v>15.53</v>
       </c>
       <c r="C25" t="n">
-        <v>15.92</v>
+        <v>15.66</v>
       </c>
       <c r="D25" t="n">
-        <v>15.7</v>
+        <v>15.45</v>
       </c>
       <c r="E25" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="F25" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>78.34999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>78.65000000000001</v>
+        <v>86.58</v>
       </c>
       <c r="J25" t="n">
-        <v>77.79000000000001</v>
+        <v>83.42</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>6122</v>
@@ -1636,44 +1636,44 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15.9</v>
+        <v>15.66</v>
       </c>
       <c r="C26" t="n">
-        <v>16.37</v>
+        <v>15.73</v>
       </c>
       <c r="D26" t="n">
-        <v>15.67</v>
+        <v>15.62</v>
       </c>
       <c r="E26" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="F26" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>76.45999999999999</v>
+        <v>82.52</v>
       </c>
       <c r="I26" t="n">
-        <v>78.44</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>72.33</v>
+        <v>82.33</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N26" t="n">
         <v>6122</v>
@@ -1683,223 +1683,225 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.37</v>
+        <v>15.72</v>
       </c>
       <c r="C27" t="n">
-        <v>16.48</v>
+        <v>15.77</v>
       </c>
       <c r="D27" t="n">
-        <v>16.29</v>
+        <v>15.65</v>
       </c>
       <c r="E27" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="F27" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>74.02</v>
+        <v>81.17</v>
       </c>
       <c r="I27" t="n">
-        <v>74.88</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>72.13</v>
+        <v>80.16</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16.84</v>
+        <v>16.09</v>
       </c>
       <c r="C28" t="n">
-        <v>17.08</v>
+        <v>16.59</v>
       </c>
       <c r="D28" t="n">
-        <v>16.57</v>
+        <v>15.76</v>
       </c>
       <c r="E28" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="F28" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>70.64</v>
+        <v>76.7</v>
       </c>
       <c r="I28" t="n">
+        <v>80.06999999999999</v>
+      </c>
+      <c r="J28" t="n">
         <v>72.89</v>
       </c>
-      <c r="J28" t="n">
-        <v>68.62</v>
-      </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N28" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.26</v>
+        <v>16.2</v>
       </c>
       <c r="C29" t="n">
-        <v>17.41</v>
+        <v>16.53</v>
       </c>
       <c r="D29" t="n">
-        <v>17.13</v>
+        <v>15.84</v>
       </c>
       <c r="E29" t="n">
-        <v>10.7</v>
+        <v>12.1</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>11.6</v>
       </c>
       <c r="G29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>65.97</v>
+        <v>77.2</v>
       </c>
       <c r="I29" t="n">
-        <v>68.3</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>62.44</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N29" t="n">
-        <v>6132</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
+        <v>6122</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.57</v>
+        <v>16.03</v>
       </c>
       <c r="C30" t="n">
-        <v>18.11</v>
+        <v>16.12</v>
       </c>
       <c r="D30" t="n">
-        <v>17.4</v>
+        <v>15.93</v>
       </c>
       <c r="E30" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>9.800000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>63.38</v>
+        <v>77.56</v>
       </c>
       <c r="I30" t="n">
-        <v>64.3</v>
+        <v>79.16</v>
       </c>
       <c r="J30" t="n">
-        <v>61.77</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="M30" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="N30" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18</v>
+        <v>15.79</v>
       </c>
       <c r="C31" t="n">
-        <v>18.2</v>
+        <v>15.92</v>
       </c>
       <c r="D31" t="n">
-        <v>17.79</v>
+        <v>15.7</v>
       </c>
       <c r="E31" t="n">
-        <v>10.6</v>
+        <v>11.9</v>
       </c>
       <c r="F31" t="n">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
       <c r="G31" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>62.96</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>64.08</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>61.81</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1911,192 +1913,192 @@
         <v>1.3</v>
       </c>
       <c r="N31" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18.15</v>
+        <v>15.9</v>
       </c>
       <c r="C32" t="n">
-        <v>18.5</v>
+        <v>16.37</v>
       </c>
       <c r="D32" t="n">
-        <v>17.92</v>
+        <v>15.67</v>
       </c>
       <c r="E32" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="G32" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>60.86</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>62.23</v>
+        <v>78.44</v>
       </c>
       <c r="J32" t="n">
-        <v>59.51</v>
+        <v>72.33</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N32" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.71</v>
+        <v>16.37</v>
       </c>
       <c r="C33" t="n">
-        <v>18.05</v>
+        <v>16.48</v>
       </c>
       <c r="D33" t="n">
-        <v>17.31</v>
+        <v>16.29</v>
       </c>
       <c r="E33" t="n">
-        <v>10.1</v>
+        <v>11.6</v>
       </c>
       <c r="F33" t="n">
-        <v>9.9</v>
+        <v>11.3</v>
       </c>
       <c r="G33" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>61.59</v>
+        <v>74.02</v>
       </c>
       <c r="I33" t="n">
-        <v>63.45</v>
+        <v>74.88</v>
       </c>
       <c r="J33" t="n">
-        <v>59.82</v>
+        <v>72.13</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="N33" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.72</v>
+        <v>16.84</v>
       </c>
       <c r="C34" t="n">
-        <v>17.47</v>
+        <v>17.08</v>
       </c>
       <c r="D34" t="n">
-        <v>16.08</v>
+        <v>16.57</v>
       </c>
       <c r="E34" t="n">
-        <v>10.4</v>
+        <v>11.3</v>
       </c>
       <c r="F34" t="n">
-        <v>9.800000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="G34" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>67.33</v>
+        <v>70.64</v>
       </c>
       <c r="I34" t="n">
-        <v>70.81999999999999</v>
+        <v>72.89</v>
       </c>
       <c r="J34" t="n">
-        <v>63.98</v>
+        <v>68.62</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="N34" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15.83</v>
+        <v>17.26</v>
       </c>
       <c r="C35" t="n">
-        <v>16.23</v>
+        <v>17.41</v>
       </c>
       <c r="D35" t="n">
-        <v>15.45</v>
+        <v>17.13</v>
       </c>
       <c r="E35" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="F35" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="G35" t="n">
-        <v>173</v>
+        <v>11</v>
       </c>
       <c r="H35" t="n">
-        <v>72.95</v>
+        <v>65.97</v>
       </c>
       <c r="I35" t="n">
-        <v>75.03</v>
+        <v>68.3</v>
       </c>
       <c r="J35" t="n">
-        <v>69.84999999999999</v>
+        <v>62.44</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M35" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="N35" t="n">
         <v>6132</v>
@@ -2106,138 +2108,138 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.22</v>
+        <v>17.57</v>
       </c>
       <c r="C36" t="n">
-        <v>15.77</v>
+        <v>18.11</v>
       </c>
       <c r="D36" t="n">
-        <v>14.97</v>
+        <v>17.4</v>
       </c>
       <c r="E36" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="F36" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="H36" t="n">
-        <v>77.61</v>
+        <v>63.38</v>
       </c>
       <c r="I36" t="n">
-        <v>79.25</v>
+        <v>64.3</v>
       </c>
       <c r="J36" t="n">
-        <v>74.45</v>
+        <v>61.77</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N36" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>14.79</v>
+        <v>18</v>
       </c>
       <c r="C37" t="n">
-        <v>15.1</v>
+        <v>18.2</v>
       </c>
       <c r="D37" t="n">
-        <v>14.32</v>
+        <v>17.79</v>
       </c>
       <c r="E37" t="n">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
       <c r="F37" t="n">
-        <v>11.2</v>
+        <v>10.5</v>
       </c>
       <c r="G37" t="n">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="H37" t="n">
-        <v>80.70999999999999</v>
+        <v>62.96</v>
       </c>
       <c r="I37" t="n">
-        <v>83.36</v>
+        <v>64.08</v>
       </c>
       <c r="J37" t="n">
-        <v>79.05</v>
+        <v>61.81</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N37" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14.05</v>
+        <v>18.15</v>
       </c>
       <c r="C38" t="n">
-        <v>14.26</v>
+        <v>18.5</v>
       </c>
       <c r="D38" t="n">
-        <v>13.8</v>
+        <v>17.92</v>
       </c>
       <c r="E38" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="F38" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="G38" t="n">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="H38" t="n">
-        <v>85.09</v>
+        <v>60.86</v>
       </c>
       <c r="I38" t="n">
-        <v>86.40000000000001</v>
+        <v>62.23</v>
       </c>
       <c r="J38" t="n">
-        <v>84.14</v>
+        <v>59.51</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M38" t="n">
         <v>1.1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.4</v>
       </c>
       <c r="N38" t="n">
         <v>6142</v>
@@ -2247,138 +2249,138 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>14.11</v>
+        <v>17.71</v>
       </c>
       <c r="C39" t="n">
-        <v>14.56</v>
+        <v>18.05</v>
       </c>
       <c r="D39" t="n">
-        <v>13.7</v>
+        <v>17.31</v>
       </c>
       <c r="E39" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="G39" t="n">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="H39" t="n">
-        <v>81.01000000000001</v>
+        <v>61.59</v>
       </c>
       <c r="I39" t="n">
-        <v>87.31</v>
+        <v>63.45</v>
       </c>
       <c r="J39" t="n">
-        <v>75.84999999999999</v>
+        <v>59.82</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="M39" t="n">
-        <v>1.3</v>
-      </c>
       <c r="N39" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>14.64</v>
+        <v>16.72</v>
       </c>
       <c r="C40" t="n">
-        <v>14.86</v>
+        <v>17.47</v>
       </c>
       <c r="D40" t="n">
-        <v>14.45</v>
+        <v>16.08</v>
       </c>
       <c r="E40" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F40" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="H40" t="n">
-        <v>79.53</v>
+        <v>67.33</v>
       </c>
       <c r="I40" t="n">
-        <v>82.73999999999999</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>76.79000000000001</v>
+        <v>63.98</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="N40" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.07</v>
+        <v>15.83</v>
       </c>
       <c r="C41" t="n">
-        <v>15.23</v>
+        <v>16.23</v>
       </c>
       <c r="D41" t="n">
-        <v>14.92</v>
+        <v>15.45</v>
       </c>
       <c r="E41" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="F41" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="H41" t="n">
-        <v>77.61</v>
+        <v>72.95</v>
       </c>
       <c r="I41" t="n">
-        <v>78.94</v>
+        <v>75.03</v>
       </c>
       <c r="J41" t="n">
-        <v>76.67</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N41" t="n">
         <v>6132</v>
@@ -2388,185 +2390,185 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.37</v>
+        <v>15.22</v>
       </c>
       <c r="C42" t="n">
-        <v>15.49</v>
+        <v>15.77</v>
       </c>
       <c r="D42" t="n">
-        <v>15.25</v>
+        <v>14.97</v>
       </c>
       <c r="E42" t="n">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="F42" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H42" t="n">
-        <v>79.81999999999999</v>
+        <v>77.61</v>
       </c>
       <c r="I42" t="n">
-        <v>80.69</v>
+        <v>79.25</v>
       </c>
       <c r="J42" t="n">
-        <v>78.86</v>
+        <v>74.45</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N42" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15.65</v>
+        <v>14.79</v>
       </c>
       <c r="C43" t="n">
-        <v>15.77</v>
+        <v>15.1</v>
       </c>
       <c r="D43" t="n">
-        <v>15.48</v>
+        <v>14.32</v>
       </c>
       <c r="E43" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F43" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H43" t="n">
-        <v>78.64</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>80.7</v>
+        <v>83.36</v>
       </c>
       <c r="J43" t="n">
-        <v>77.23</v>
+        <v>79.05</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N43" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>15.39</v>
+        <v>14.05</v>
       </c>
       <c r="C44" t="n">
-        <v>15.59</v>
+        <v>14.26</v>
       </c>
       <c r="D44" t="n">
-        <v>15.29</v>
+        <v>13.8</v>
       </c>
       <c r="E44" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="F44" t="n">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H44" t="n">
-        <v>84.89</v>
+        <v>85.09</v>
       </c>
       <c r="I44" t="n">
-        <v>87.12</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>81.20999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="M44" t="n">
         <v>1.4</v>
       </c>
       <c r="N44" t="n">
-        <v>6112</v>
+        <v>6142</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15.61</v>
+        <v>14.11</v>
       </c>
       <c r="C45" t="n">
-        <v>16.09</v>
+        <v>14.56</v>
       </c>
       <c r="D45" t="n">
-        <v>15.44</v>
+        <v>13.7</v>
       </c>
       <c r="E45" t="n">
-        <v>12.8</v>
+        <v>10.7</v>
       </c>
       <c r="F45" t="n">
-        <v>12.4</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H45" t="n">
-        <v>84.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>86.2</v>
+        <v>87.31</v>
       </c>
       <c r="J45" t="n">
-        <v>79</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N45" t="n">
         <v>6132</v>
@@ -2576,187 +2578,185 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16.78</v>
+        <v>14.64</v>
       </c>
       <c r="C46" t="n">
-        <v>17.16</v>
+        <v>14.86</v>
       </c>
       <c r="D46" t="n">
-        <v>16.31</v>
+        <v>14.45</v>
       </c>
       <c r="E46" t="n">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="F46" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H46" t="n">
-        <v>73.62</v>
+        <v>79.53</v>
       </c>
       <c r="I46" t="n">
-        <v>76.98999999999999</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>69.84</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="N46" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.55</v>
+        <v>15.07</v>
       </c>
       <c r="C47" t="n">
-        <v>17.8</v>
+        <v>15.23</v>
       </c>
       <c r="D47" t="n">
-        <v>17.2</v>
+        <v>14.92</v>
       </c>
       <c r="E47" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="F47" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>71.04000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="I47" t="n">
-        <v>73.81</v>
+        <v>78.94</v>
       </c>
       <c r="J47" t="n">
-        <v>69.28</v>
+        <v>76.67</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M47" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>6142</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.6</v>
-      </c>
+        <v>6132</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.63</v>
+        <v>15.37</v>
       </c>
       <c r="C48" t="n">
-        <v>18.08</v>
+        <v>15.49</v>
       </c>
       <c r="D48" t="n">
-        <v>17.4</v>
+        <v>15.25</v>
       </c>
       <c r="E48" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>73.43000000000001</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>76.55</v>
+        <v>80.69</v>
       </c>
       <c r="J48" t="n">
-        <v>68.51000000000001</v>
+        <v>78.86</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="M48" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.46</v>
+        <v>15.65</v>
       </c>
       <c r="C49" t="n">
-        <v>17.67</v>
+        <v>15.77</v>
       </c>
       <c r="D49" t="n">
-        <v>17.22</v>
+        <v>15.48</v>
       </c>
       <c r="E49" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="F49" t="n">
-        <v>13</v>
+        <v>11.6</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>76.84</v>
+        <v>78.64</v>
       </c>
       <c r="I49" t="n">
-        <v>79.37</v>
+        <v>80.7</v>
       </c>
       <c r="J49" t="n">
-        <v>75.08</v>
+        <v>77.23</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="M49" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="N49" t="n">
         <v>6132</v>
@@ -2766,50 +2766,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>17.43</v>
+        <v>15.39</v>
       </c>
       <c r="C50" t="n">
-        <v>17.62</v>
+        <v>15.59</v>
       </c>
       <c r="D50" t="n">
-        <v>17.17</v>
+        <v>15.29</v>
       </c>
       <c r="E50" t="n">
-        <v>13.6</v>
+        <v>12.7</v>
       </c>
       <c r="F50" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>79.34</v>
+        <v>84.89</v>
       </c>
       <c r="I50" t="n">
-        <v>82.2</v>
+        <v>87.12</v>
       </c>
       <c r="J50" t="n">
-        <v>77.51000000000001</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N50" t="n">
-        <v>6142</v>
+        <v>6112</v>
       </c>
       <c r="O50" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,35 +508,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 03:00:00</t>
+          <t>2026-10-20 08:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.05</v>
+        <v>17.49</v>
       </c>
       <c r="C2" t="n">
-        <v>17.22</v>
+        <v>17.57</v>
       </c>
       <c r="D2" t="n">
-        <v>16.88</v>
+        <v>17.45</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="F2" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
-        <v>75.90000000000001</v>
+        <v>74.72</v>
       </c>
       <c r="I2" t="n">
-        <v>76.7</v>
+        <v>75.61</v>
       </c>
       <c r="J2" t="n">
-        <v>74.67</v>
+        <v>73.23</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -555,35 +555,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00:00</t>
+          <t>2026-10-20 07:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.59</v>
+        <v>16.92</v>
       </c>
       <c r="C3" t="n">
-        <v>17.8</v>
+        <v>17.33</v>
       </c>
       <c r="D3" t="n">
-        <v>17.29</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="n">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="F3" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>73.83</v>
+        <v>74.87</v>
       </c>
       <c r="I3" t="n">
-        <v>74.95</v>
+        <v>75.66</v>
       </c>
       <c r="J3" t="n">
-        <v>72.36</v>
+        <v>74.08</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -595,42 +595,42 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6122</v>
+        <v>6092</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 01:00:00</t>
+          <t>2026-10-20 06:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.24</v>
+        <v>16.75</v>
       </c>
       <c r="C4" t="n">
-        <v>18.59</v>
+        <v>16.84</v>
       </c>
       <c r="D4" t="n">
-        <v>17.84</v>
+        <v>16.64</v>
       </c>
       <c r="E4" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="F4" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>66.76000000000001</v>
+        <v>74.86</v>
       </c>
       <c r="I4" t="n">
-        <v>71.14</v>
+        <v>75.98</v>
       </c>
       <c r="J4" t="n">
-        <v>63.93</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -642,42 +642,42 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6092</v>
+        <v>6102</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:00:00</t>
+          <t>2026-10-20 05:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.68</v>
+        <v>16.83</v>
       </c>
       <c r="C5" t="n">
-        <v>18.93</v>
+        <v>17.01</v>
       </c>
       <c r="D5" t="n">
-        <v>18.52</v>
+        <v>16.66</v>
       </c>
       <c r="E5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F5" t="n">
         <v>11.7</v>
       </c>
-      <c r="F5" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>64.40000000000001</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>65.87</v>
+        <v>75.19</v>
       </c>
       <c r="J5" t="n">
-        <v>61.94</v>
+        <v>72.06</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -689,42 +689,42 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6122</v>
+        <v>6082</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19 23:00:00</t>
+          <t>2026-10-20 04:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.43</v>
+        <v>16.74</v>
       </c>
       <c r="C6" t="n">
-        <v>19.64</v>
+        <v>16.99</v>
       </c>
       <c r="D6" t="n">
-        <v>19.01</v>
+        <v>16.45</v>
       </c>
       <c r="E6" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="F6" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>60.1</v>
+        <v>74.84</v>
       </c>
       <c r="I6" t="n">
-        <v>60.96</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>59.25</v>
+        <v>72.64</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -736,51 +736,51 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6132</v>
+        <v>6112</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19 22:00:00</t>
+          <t>2026-10-20 03:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.1</v>
+        <v>16.86</v>
       </c>
       <c r="C7" t="n">
-        <v>20.3</v>
+        <v>17.22</v>
       </c>
       <c r="D7" t="n">
-        <v>19.77</v>
+        <v>16.71</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="F7" t="n">
-        <v>10.9</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>56.64</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>58.8</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>55.68</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>6112</v>
@@ -790,834 +790,834 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19 21:00:00</t>
+          <t>2026-10-20 02:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>17.59</v>
       </c>
       <c r="C8" t="n">
-        <v>20.17</v>
+        <v>17.8</v>
       </c>
       <c r="D8" t="n">
-        <v>19.94</v>
+        <v>17.29</v>
       </c>
       <c r="E8" t="n">
-        <v>10.6</v>
+        <v>12.7</v>
       </c>
       <c r="F8" t="n">
-        <v>10.6</v>
+        <v>12.5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>55.69</v>
+        <v>73.83</v>
       </c>
       <c r="I8" t="n">
-        <v>55.96</v>
+        <v>74.95</v>
       </c>
       <c r="J8" t="n">
-        <v>55.41</v>
+        <v>72.36</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19 20:00:00</t>
+          <t>2026-10-20 01:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.56</v>
+        <v>18.24</v>
       </c>
       <c r="C9" t="n">
-        <v>19.96</v>
+        <v>18.59</v>
       </c>
       <c r="D9" t="n">
-        <v>19.34</v>
+        <v>17.84</v>
       </c>
       <c r="E9" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="F9" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>56.91</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>57.67</v>
+        <v>71.14</v>
       </c>
       <c r="J9" t="n">
-        <v>55.82</v>
+        <v>63.93</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6142</v>
+        <v>6092</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19 19:00:00</t>
+          <t>2026-10-20 00:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19.8</v>
+        <v>18.68</v>
       </c>
       <c r="C10" t="n">
-        <v>19.92</v>
+        <v>18.93</v>
       </c>
       <c r="D10" t="n">
-        <v>19.62</v>
+        <v>18.52</v>
       </c>
       <c r="E10" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
       <c r="F10" t="n">
-        <v>10.2</v>
+        <v>11.2</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>55.22</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>56.29</v>
+        <v>65.87</v>
       </c>
       <c r="J10" t="n">
-        <v>54.46</v>
+        <v>61.94</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6152</v>
+        <v>6122</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-19 23:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.91</v>
+        <v>19.43</v>
       </c>
       <c r="C11" t="n">
-        <v>19.98</v>
+        <v>19.64</v>
       </c>
       <c r="D11" t="n">
-        <v>19.83</v>
+        <v>19.01</v>
       </c>
       <c r="E11" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="F11" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="G11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>54.74</v>
+        <v>60.1</v>
       </c>
       <c r="I11" t="n">
-        <v>54.92</v>
+        <v>60.96</v>
       </c>
       <c r="J11" t="n">
-        <v>54.61</v>
+        <v>59.25</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6162</v>
+        <v>6132</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-19 22:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.31</v>
+        <v>20.1</v>
       </c>
       <c r="C12" t="n">
-        <v>20.99</v>
+        <v>20.3</v>
       </c>
       <c r="D12" t="n">
-        <v>19.97</v>
+        <v>19.77</v>
       </c>
       <c r="E12" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="G12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>53.29</v>
+        <v>56.64</v>
       </c>
       <c r="I12" t="n">
-        <v>54.84</v>
+        <v>58.8</v>
       </c>
       <c r="J12" t="n">
-        <v>51.22</v>
+        <v>55.68</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="N12" t="n">
-        <v>6170</v>
+        <v>6112</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-19 21:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.38</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>21.67</v>
+        <v>20.17</v>
       </c>
       <c r="D13" t="n">
-        <v>20.91</v>
+        <v>19.94</v>
       </c>
       <c r="E13" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="G13" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>49.67</v>
+        <v>55.69</v>
       </c>
       <c r="I13" t="n">
-        <v>50.93</v>
+        <v>55.96</v>
       </c>
       <c r="J13" t="n">
-        <v>48.59</v>
+        <v>55.41</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="N13" t="n">
-        <v>6190</v>
+        <v>6142</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00:00</t>
+          <t>2026-10-19 20:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.78</v>
+        <v>19.56</v>
       </c>
       <c r="C14" t="n">
-        <v>22.31</v>
+        <v>19.96</v>
       </c>
       <c r="D14" t="n">
-        <v>21.39</v>
+        <v>19.34</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="F14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="G14" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>48.06</v>
+        <v>56.91</v>
       </c>
       <c r="I14" t="n">
-        <v>48.87</v>
+        <v>57.67</v>
       </c>
       <c r="J14" t="n">
-        <v>46.24</v>
+        <v>55.82</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="N14" t="n">
-        <v>6210</v>
+        <v>6142</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.97</v>
+        <v>19.8</v>
       </c>
       <c r="C15" t="n">
-        <v>24.27</v>
+        <v>19.92</v>
       </c>
       <c r="D15" t="n">
-        <v>22.16</v>
+        <v>19.62</v>
       </c>
       <c r="E15" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="F15" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G15" t="n">
-        <v>747</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>44.85</v>
+        <v>55.22</v>
       </c>
       <c r="I15" t="n">
-        <v>47.21</v>
+        <v>56.29</v>
       </c>
       <c r="J15" t="n">
-        <v>41.93</v>
+        <v>54.46</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="N15" t="n">
-        <v>6220</v>
+        <v>6152</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-19 13:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22.58</v>
+        <v>19.91</v>
       </c>
       <c r="C16" t="n">
-        <v>23.47</v>
+        <v>19.98</v>
       </c>
       <c r="D16" t="n">
-        <v>21.83</v>
+        <v>19.83</v>
       </c>
       <c r="E16" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="F16" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="G16" t="n">
-        <v>815</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>45.81</v>
+        <v>54.74</v>
       </c>
       <c r="I16" t="n">
-        <v>48.66</v>
+        <v>54.92</v>
       </c>
       <c r="J16" t="n">
-        <v>43.93</v>
+        <v>54.61</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>6220</v>
+        <v>6162</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-19 12:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21.31</v>
+        <v>20.31</v>
       </c>
       <c r="C17" t="n">
-        <v>22.4</v>
+        <v>20.99</v>
       </c>
       <c r="D17" t="n">
-        <v>20.2</v>
+        <v>19.97</v>
       </c>
       <c r="E17" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="F17" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="G17" t="n">
-        <v>689</v>
+        <v>40</v>
       </c>
       <c r="H17" t="n">
-        <v>50.33</v>
+        <v>53.29</v>
       </c>
       <c r="I17" t="n">
-        <v>56.08</v>
+        <v>54.84</v>
       </c>
       <c r="J17" t="n">
-        <v>47.33</v>
+        <v>51.22</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-19 11:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18.91</v>
+        <v>21.38</v>
       </c>
       <c r="C18" t="n">
-        <v>19.91</v>
+        <v>21.67</v>
       </c>
       <c r="D18" t="n">
-        <v>18.4</v>
+        <v>20.91</v>
       </c>
       <c r="E18" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="F18" t="n">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>305</v>
+        <v>213</v>
       </c>
       <c r="H18" t="n">
-        <v>60.58</v>
+        <v>49.67</v>
       </c>
       <c r="I18" t="n">
-        <v>63.06</v>
+        <v>50.93</v>
       </c>
       <c r="J18" t="n">
-        <v>55.94</v>
+        <v>48.59</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.94</v>
+        <v>21.78</v>
       </c>
       <c r="C19" t="n">
-        <v>18.46</v>
+        <v>22.31</v>
       </c>
       <c r="D19" t="n">
-        <v>17.55</v>
+        <v>21.39</v>
       </c>
       <c r="E19" t="n">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="F19" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="H19" t="n">
-        <v>67.54000000000001</v>
+        <v>48.06</v>
       </c>
       <c r="I19" t="n">
-        <v>70.20999999999999</v>
+        <v>48.87</v>
       </c>
       <c r="J19" t="n">
-        <v>64.44</v>
+        <v>46.24</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>6152</v>
+        <v>6210</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.55</v>
+        <v>22.97</v>
       </c>
       <c r="C20" t="n">
-        <v>17.81</v>
+        <v>24.27</v>
       </c>
       <c r="D20" t="n">
-        <v>17.2</v>
+        <v>22.16</v>
       </c>
       <c r="E20" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="F20" t="n">
-        <v>10.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>95</v>
+        <v>747</v>
       </c>
       <c r="H20" t="n">
-        <v>68.43000000000001</v>
+        <v>44.85</v>
       </c>
       <c r="I20" t="n">
-        <v>69.95</v>
+        <v>47.21</v>
       </c>
       <c r="J20" t="n">
-        <v>65.48</v>
+        <v>41.93</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2</v>
+        <v>4.3</v>
       </c>
       <c r="N20" t="n">
-        <v>6132</v>
+        <v>6220</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.64</v>
+        <v>22.58</v>
       </c>
       <c r="C21" t="n">
-        <v>17.06</v>
+        <v>23.47</v>
       </c>
       <c r="D21" t="n">
-        <v>16.2</v>
+        <v>21.83</v>
       </c>
       <c r="E21" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="F21" t="n">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
       <c r="G21" t="n">
-        <v>44</v>
+        <v>815</v>
       </c>
       <c r="H21" t="n">
-        <v>72.79000000000001</v>
+        <v>45.81</v>
       </c>
       <c r="I21" t="n">
-        <v>77.45</v>
+        <v>48.66</v>
       </c>
       <c r="J21" t="n">
-        <v>70.3</v>
+        <v>43.93</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="N21" t="n">
-        <v>6132</v>
+        <v>6220</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15.62</v>
+        <v>21.31</v>
       </c>
       <c r="C22" t="n">
-        <v>16.07</v>
+        <v>22.4</v>
       </c>
       <c r="D22" t="n">
-        <v>15.35</v>
+        <v>20.2</v>
       </c>
       <c r="E22" t="n">
-        <v>12.9</v>
+        <v>10.4</v>
       </c>
       <c r="F22" t="n">
-        <v>12.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>689</v>
       </c>
       <c r="H22" t="n">
-        <v>85.33</v>
+        <v>50.33</v>
       </c>
       <c r="I22" t="n">
-        <v>89.23</v>
+        <v>56.08</v>
       </c>
       <c r="J22" t="n">
-        <v>79.03</v>
+        <v>47.33</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="N22" t="n">
-        <v>6122</v>
+        <v>6190</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15.25</v>
+        <v>18.91</v>
       </c>
       <c r="C23" t="n">
-        <v>15.35</v>
+        <v>19.91</v>
       </c>
       <c r="D23" t="n">
-        <v>15.06</v>
+        <v>18.4</v>
       </c>
       <c r="E23" t="n">
-        <v>13.3</v>
+        <v>10.9</v>
       </c>
       <c r="F23" t="n">
-        <v>13.2</v>
+        <v>10.6</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="H23" t="n">
-        <v>89.16</v>
+        <v>60.58</v>
       </c>
       <c r="I23" t="n">
-        <v>91.05</v>
+        <v>63.06</v>
       </c>
       <c r="J23" t="n">
-        <v>87.77</v>
+        <v>55.94</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N23" t="n">
-        <v>6122</v>
+        <v>6162</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.2</v>
+        <v>17.94</v>
       </c>
       <c r="C24" t="n">
-        <v>15.32</v>
+        <v>18.46</v>
       </c>
       <c r="D24" t="n">
-        <v>15.08</v>
+        <v>17.55</v>
       </c>
       <c r="E24" t="n">
-        <v>13.1</v>
+        <v>11.6</v>
       </c>
       <c r="F24" t="n">
-        <v>13.1</v>
+        <v>11.2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H24" t="n">
-        <v>88.42</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>89.37</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>87.13</v>
+        <v>64.44</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>6122</v>
+        <v>6152</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15.53</v>
+        <v>17.55</v>
       </c>
       <c r="C25" t="n">
-        <v>15.66</v>
+        <v>17.81</v>
       </c>
       <c r="D25" t="n">
-        <v>15.45</v>
+        <v>17.2</v>
       </c>
       <c r="E25" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="F25" t="n">
-        <v>12.7</v>
+        <v>10.9</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H25" t="n">
-        <v>85.40000000000001</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>86.58</v>
+        <v>69.95</v>
       </c>
       <c r="J25" t="n">
-        <v>83.42</v>
+        <v>65.48</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1626,45 +1626,45 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N25" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15.66</v>
+        <v>16.64</v>
       </c>
       <c r="C26" t="n">
-        <v>15.73</v>
+        <v>17.06</v>
       </c>
       <c r="D26" t="n">
-        <v>15.62</v>
+        <v>16.2</v>
       </c>
       <c r="E26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="F26" t="n">
-        <v>12.5</v>
+        <v>11.4</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H26" t="n">
-        <v>82.52</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>82.76000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="J26" t="n">
-        <v>82.33</v>
+        <v>70.3</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1673,54 +1673,54 @@
         <v>0.3</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N26" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15.72</v>
+        <v>15.62</v>
       </c>
       <c r="C27" t="n">
-        <v>15.77</v>
+        <v>16.07</v>
       </c>
       <c r="D27" t="n">
-        <v>15.65</v>
+        <v>15.35</v>
       </c>
       <c r="E27" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F27" t="n">
         <v>12.4</v>
       </c>
-      <c r="F27" t="n">
-        <v>12.3</v>
-      </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H27" t="n">
-        <v>81.17</v>
+        <v>85.33</v>
       </c>
       <c r="I27" t="n">
-        <v>82.40000000000001</v>
+        <v>89.23</v>
       </c>
       <c r="J27" t="n">
-        <v>80.16</v>
+        <v>79.03</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>6122</v>
@@ -1730,44 +1730,44 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16.09</v>
+        <v>15.25</v>
       </c>
       <c r="C28" t="n">
-        <v>16.59</v>
+        <v>15.35</v>
       </c>
       <c r="D28" t="n">
-        <v>15.76</v>
+        <v>15.06</v>
       </c>
       <c r="E28" t="n">
-        <v>11.9</v>
+        <v>13.3</v>
       </c>
       <c r="F28" t="n">
-        <v>11.4</v>
+        <v>13.2</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>76.7</v>
+        <v>89.16</v>
       </c>
       <c r="I28" t="n">
-        <v>80.06999999999999</v>
+        <v>91.05</v>
       </c>
       <c r="J28" t="n">
-        <v>72.89</v>
+        <v>87.77</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>6122</v>
@@ -1777,93 +1777,91 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>16.2</v>
+        <v>15.2</v>
       </c>
       <c r="C29" t="n">
-        <v>16.53</v>
+        <v>15.32</v>
       </c>
       <c r="D29" t="n">
-        <v>15.84</v>
+        <v>15.08</v>
       </c>
       <c r="E29" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="F29" t="n">
-        <v>11.6</v>
+        <v>13.1</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>77.2</v>
+        <v>88.42</v>
       </c>
       <c r="I29" t="n">
-        <v>80.54000000000001</v>
+        <v>89.37</v>
       </c>
       <c r="J29" t="n">
-        <v>73.31999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>6122</v>
       </c>
-      <c r="O29" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>16.03</v>
+        <v>15.53</v>
       </c>
       <c r="C30" t="n">
-        <v>16.12</v>
+        <v>15.66</v>
       </c>
       <c r="D30" t="n">
-        <v>15.93</v>
+        <v>15.45</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="F30" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>77.56</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>79.16</v>
+        <v>86.58</v>
       </c>
       <c r="J30" t="n">
-        <v>76.79000000000001</v>
+        <v>83.42</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>6122</v>
@@ -1873,44 +1871,44 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>15.79</v>
+        <v>15.66</v>
       </c>
       <c r="C31" t="n">
-        <v>15.92</v>
+        <v>15.73</v>
       </c>
       <c r="D31" t="n">
-        <v>15.7</v>
+        <v>15.62</v>
       </c>
       <c r="E31" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="F31" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>78.34999999999999</v>
+        <v>82.52</v>
       </c>
       <c r="I31" t="n">
-        <v>78.65000000000001</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>77.79000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="n">
         <v>6122</v>
@@ -1920,44 +1918,44 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>15.9</v>
+        <v>15.72</v>
       </c>
       <c r="C32" t="n">
-        <v>16.37</v>
+        <v>15.77</v>
       </c>
       <c r="D32" t="n">
-        <v>15.67</v>
+        <v>15.65</v>
       </c>
       <c r="E32" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="F32" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>76.45999999999999</v>
+        <v>81.17</v>
       </c>
       <c r="I32" t="n">
-        <v>78.44</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>72.33</v>
+        <v>80.16</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="M32" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
         <v>6122</v>
@@ -1967,467 +1965,469 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.37</v>
+        <v>16.09</v>
       </c>
       <c r="C33" t="n">
-        <v>16.48</v>
+        <v>16.59</v>
       </c>
       <c r="D33" t="n">
-        <v>16.29</v>
+        <v>15.76</v>
       </c>
       <c r="E33" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="F33" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>74.02</v>
+        <v>76.7</v>
       </c>
       <c r="I33" t="n">
-        <v>74.88</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>72.13</v>
+        <v>72.89</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M33" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N33" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.84</v>
+        <v>16.2</v>
       </c>
       <c r="C34" t="n">
-        <v>17.08</v>
+        <v>16.53</v>
       </c>
       <c r="D34" t="n">
-        <v>16.57</v>
+        <v>15.84</v>
       </c>
       <c r="E34" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="F34" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>70.64</v>
+        <v>77.2</v>
       </c>
       <c r="I34" t="n">
-        <v>72.89</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>68.62</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="N34" t="n">
-        <v>6132</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
+        <v>6122</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.26</v>
+        <v>16.03</v>
       </c>
       <c r="C35" t="n">
-        <v>17.41</v>
+        <v>16.12</v>
       </c>
       <c r="D35" t="n">
-        <v>17.13</v>
+        <v>15.93</v>
       </c>
       <c r="E35" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="G35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>65.97</v>
+        <v>77.56</v>
       </c>
       <c r="I35" t="n">
-        <v>68.3</v>
+        <v>79.16</v>
       </c>
       <c r="J35" t="n">
-        <v>62.44</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="M35" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="N35" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.57</v>
+        <v>15.79</v>
       </c>
       <c r="C36" t="n">
-        <v>18.11</v>
+        <v>15.92</v>
       </c>
       <c r="D36" t="n">
-        <v>17.4</v>
+        <v>15.7</v>
       </c>
       <c r="E36" t="n">
-        <v>10.4</v>
+        <v>11.9</v>
       </c>
       <c r="F36" t="n">
-        <v>9.800000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="G36" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>63.38</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>64.3</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>61.77</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="M36" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="N36" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18</v>
+        <v>15.9</v>
       </c>
       <c r="C37" t="n">
-        <v>18.2</v>
+        <v>16.37</v>
       </c>
       <c r="D37" t="n">
-        <v>17.79</v>
+        <v>15.67</v>
       </c>
       <c r="E37" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="F37" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="G37" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>62.96</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>64.08</v>
+        <v>78.44</v>
       </c>
       <c r="J37" t="n">
-        <v>61.81</v>
+        <v>72.33</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="M37" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N37" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18.15</v>
+        <v>16.37</v>
       </c>
       <c r="C38" t="n">
-        <v>18.5</v>
+        <v>16.48</v>
       </c>
       <c r="D38" t="n">
-        <v>17.92</v>
+        <v>16.29</v>
       </c>
       <c r="E38" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="G38" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>60.86</v>
+        <v>74.02</v>
       </c>
       <c r="I38" t="n">
-        <v>62.23</v>
+        <v>74.88</v>
       </c>
       <c r="J38" t="n">
-        <v>59.51</v>
+        <v>72.13</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="N38" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.71</v>
+        <v>16.84</v>
       </c>
       <c r="C39" t="n">
-        <v>18.05</v>
+        <v>17.08</v>
       </c>
       <c r="D39" t="n">
-        <v>17.31</v>
+        <v>16.57</v>
       </c>
       <c r="E39" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
       <c r="F39" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="G39" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>61.59</v>
+        <v>70.64</v>
       </c>
       <c r="I39" t="n">
-        <v>63.45</v>
+        <v>72.89</v>
       </c>
       <c r="J39" t="n">
-        <v>59.82</v>
+        <v>68.62</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N39" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.72</v>
+        <v>17.26</v>
       </c>
       <c r="C40" t="n">
-        <v>17.47</v>
+        <v>17.41</v>
       </c>
       <c r="D40" t="n">
-        <v>16.08</v>
+        <v>17.13</v>
       </c>
       <c r="E40" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="F40" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G40" t="n">
-        <v>260</v>
+        <v>11</v>
       </c>
       <c r="H40" t="n">
-        <v>67.33</v>
+        <v>65.97</v>
       </c>
       <c r="I40" t="n">
-        <v>70.81999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="J40" t="n">
-        <v>63.98</v>
+        <v>62.44</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M40" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N40" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.83</v>
+        <v>17.57</v>
       </c>
       <c r="C41" t="n">
-        <v>16.23</v>
+        <v>18.11</v>
       </c>
       <c r="D41" t="n">
-        <v>15.45</v>
+        <v>17.4</v>
       </c>
       <c r="E41" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F41" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H41" t="n">
-        <v>72.95</v>
+        <v>63.38</v>
       </c>
       <c r="I41" t="n">
-        <v>75.03</v>
+        <v>64.3</v>
       </c>
       <c r="J41" t="n">
-        <v>69.84999999999999</v>
+        <v>61.77</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="M41" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N41" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.22</v>
+        <v>18</v>
       </c>
       <c r="C42" t="n">
-        <v>15.77</v>
+        <v>18.2</v>
       </c>
       <c r="D42" t="n">
-        <v>14.97</v>
+        <v>17.79</v>
       </c>
       <c r="E42" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="F42" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="G42" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H42" t="n">
-        <v>77.61</v>
+        <v>62.96</v>
       </c>
       <c r="I42" t="n">
-        <v>79.25</v>
+        <v>64.08</v>
       </c>
       <c r="J42" t="n">
-        <v>74.45</v>
+        <v>61.81</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M42" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N42" t="n">
         <v>6162</v>
@@ -2437,44 +2437,44 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>14.79</v>
+        <v>18.15</v>
       </c>
       <c r="C43" t="n">
-        <v>15.1</v>
+        <v>18.5</v>
       </c>
       <c r="D43" t="n">
-        <v>14.32</v>
+        <v>17.92</v>
       </c>
       <c r="E43" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="F43" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="G43" t="n">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="H43" t="n">
-        <v>80.70999999999999</v>
+        <v>60.86</v>
       </c>
       <c r="I43" t="n">
-        <v>83.36</v>
+        <v>62.23</v>
       </c>
       <c r="J43" t="n">
-        <v>79.05</v>
+        <v>59.51</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M43" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N43" t="n">
         <v>6142</v>
@@ -2484,138 +2484,138 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>14.05</v>
+        <v>17.71</v>
       </c>
       <c r="C44" t="n">
-        <v>14.26</v>
+        <v>18.05</v>
       </c>
       <c r="D44" t="n">
-        <v>13.8</v>
+        <v>17.31</v>
       </c>
       <c r="E44" t="n">
-        <v>11.4</v>
+        <v>10.1</v>
       </c>
       <c r="F44" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="G44" t="n">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="H44" t="n">
-        <v>85.09</v>
+        <v>61.59</v>
       </c>
       <c r="I44" t="n">
-        <v>86.40000000000001</v>
+        <v>63.45</v>
       </c>
       <c r="J44" t="n">
-        <v>84.14</v>
+        <v>59.82</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="M44" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>14.11</v>
+        <v>16.72</v>
       </c>
       <c r="C45" t="n">
-        <v>14.56</v>
+        <v>17.47</v>
       </c>
       <c r="D45" t="n">
-        <v>13.7</v>
+        <v>16.08</v>
       </c>
       <c r="E45" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>31</v>
+        <v>260</v>
       </c>
       <c r="H45" t="n">
-        <v>81.01000000000001</v>
+        <v>67.33</v>
       </c>
       <c r="I45" t="n">
-        <v>87.31</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>75.84999999999999</v>
+        <v>63.98</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M45" t="n">
         <v>1.3</v>
       </c>
       <c r="N45" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>14.64</v>
+        <v>15.83</v>
       </c>
       <c r="C46" t="n">
-        <v>14.86</v>
+        <v>16.23</v>
       </c>
       <c r="D46" t="n">
-        <v>14.45</v>
+        <v>15.45</v>
       </c>
       <c r="E46" t="n">
         <v>10.9</v>
       </c>
       <c r="F46" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>173</v>
       </c>
       <c r="H46" t="n">
-        <v>79.53</v>
+        <v>72.95</v>
       </c>
       <c r="I46" t="n">
-        <v>82.73999999999999</v>
+        <v>75.03</v>
       </c>
       <c r="J46" t="n">
-        <v>76.79000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N46" t="n">
         <v>6132</v>
@@ -2625,188 +2625,188 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>15.07</v>
+        <v>15.22</v>
       </c>
       <c r="C47" t="n">
-        <v>15.23</v>
+        <v>15.77</v>
       </c>
       <c r="D47" t="n">
-        <v>14.92</v>
+        <v>14.97</v>
       </c>
       <c r="E47" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="F47" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H47" t="n">
         <v>77.61</v>
       </c>
       <c r="I47" t="n">
-        <v>78.94</v>
+        <v>79.25</v>
       </c>
       <c r="J47" t="n">
-        <v>76.67</v>
+        <v>74.45</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N47" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>15.37</v>
+        <v>14.79</v>
       </c>
       <c r="C48" t="n">
-        <v>15.49</v>
+        <v>15.1</v>
       </c>
       <c r="D48" t="n">
-        <v>15.25</v>
+        <v>14.32</v>
       </c>
       <c r="E48" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F48" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H48" t="n">
-        <v>79.81999999999999</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>80.69</v>
+        <v>83.36</v>
       </c>
       <c r="J48" t="n">
-        <v>78.86</v>
+        <v>79.05</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N48" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>15.65</v>
+        <v>14.05</v>
       </c>
       <c r="C49" t="n">
-        <v>15.77</v>
+        <v>14.26</v>
       </c>
       <c r="D49" t="n">
-        <v>15.48</v>
+        <v>13.8</v>
       </c>
       <c r="E49" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="F49" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H49" t="n">
-        <v>78.64</v>
+        <v>85.09</v>
       </c>
       <c r="I49" t="n">
-        <v>80.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>77.23</v>
+        <v>84.14</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M49" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N49" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>15.39</v>
+        <v>14.11</v>
       </c>
       <c r="C50" t="n">
-        <v>15.59</v>
+        <v>14.56</v>
       </c>
       <c r="D50" t="n">
-        <v>15.29</v>
+        <v>13.7</v>
       </c>
       <c r="E50" t="n">
-        <v>12.7</v>
+        <v>10.7</v>
       </c>
       <c r="F50" t="n">
-        <v>12.3</v>
+        <v>10</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H50" t="n">
-        <v>84.89</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>87.12</v>
+        <v>87.31</v>
       </c>
       <c r="J50" t="n">
-        <v>81.20999999999999</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N50" t="n">
-        <v>6112</v>
+        <v>6132</v>
       </c>
       <c r="O50" t="n">
         <v>1.6</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,223 +508,223 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 08:00:00</t>
+          <t>2026-10-20 13:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.49</v>
+        <v>24.99</v>
       </c>
       <c r="C2" t="n">
-        <v>17.57</v>
+        <v>25.05</v>
       </c>
       <c r="D2" t="n">
-        <v>17.45</v>
+        <v>24.91</v>
       </c>
       <c r="E2" t="n">
-        <v>12.8</v>
+        <v>11.5</v>
       </c>
       <c r="F2" t="n">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>297</v>
       </c>
       <c r="H2" t="n">
-        <v>74.72</v>
+        <v>43.81</v>
       </c>
       <c r="I2" t="n">
-        <v>75.61</v>
+        <v>43.82</v>
       </c>
       <c r="J2" t="n">
-        <v>73.23</v>
+        <v>43.79</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>6102</v>
+        <v>6162</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 07:00:00</t>
+          <t>2026-10-20 12:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.92</v>
+        <v>24.81</v>
       </c>
       <c r="C3" t="n">
-        <v>17.33</v>
+        <v>25.08</v>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>24.53</v>
       </c>
       <c r="E3" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="F3" t="n">
-        <v>12.1</v>
+        <v>11.2</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>373</v>
       </c>
       <c r="H3" t="n">
-        <v>74.87</v>
+        <v>43.89</v>
       </c>
       <c r="I3" t="n">
-        <v>75.66</v>
+        <v>44.75</v>
       </c>
       <c r="J3" t="n">
-        <v>74.08</v>
+        <v>43.04</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>6092</v>
+        <v>6162</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00:00</t>
+          <t>2026-10-20 11:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.75</v>
+        <v>23.48</v>
       </c>
       <c r="C4" t="n">
-        <v>16.84</v>
+        <v>24.58</v>
       </c>
       <c r="D4" t="n">
-        <v>16.64</v>
+        <v>22.73</v>
       </c>
       <c r="E4" t="n">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="F4" t="n">
-        <v>11.9</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>519</v>
       </c>
       <c r="H4" t="n">
-        <v>74.86</v>
+        <v>47.14</v>
       </c>
       <c r="I4" t="n">
-        <v>75.98</v>
+        <v>49.9</v>
       </c>
       <c r="J4" t="n">
-        <v>73.98999999999999</v>
+        <v>43.67</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>6102</v>
+        <v>6162</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 05:00:00</t>
+          <t>2026-10-20 10:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.83</v>
+        <v>21.96</v>
       </c>
       <c r="C5" t="n">
-        <v>17.01</v>
+        <v>22.96</v>
       </c>
       <c r="D5" t="n">
-        <v>16.66</v>
+        <v>21.26</v>
       </c>
       <c r="E5" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="F5" t="n">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="H5" t="n">
-        <v>73.56999999999999</v>
+        <v>52.22</v>
       </c>
       <c r="I5" t="n">
-        <v>75.19</v>
+        <v>54.36</v>
       </c>
       <c r="J5" t="n">
-        <v>72.06</v>
+        <v>49</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>6082</v>
+        <v>6152</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20 04:00:00</t>
+          <t>2026-10-20 09:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.74</v>
+        <v>20.32</v>
       </c>
       <c r="C6" t="n">
-        <v>16.99</v>
+        <v>21.66</v>
       </c>
       <c r="D6" t="n">
-        <v>16.45</v>
+        <v>19.17</v>
       </c>
       <c r="E6" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F6" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="H6" t="n">
-        <v>74.84</v>
+        <v>60.55</v>
       </c>
       <c r="I6" t="n">
-        <v>77.06999999999999</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>72.64</v>
+        <v>55.76</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -733,45 +733,45 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N6" t="n">
-        <v>6112</v>
+        <v>6142</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20 03:00:00</t>
+          <t>2026-10-20 08:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.86</v>
+        <v>18.15</v>
       </c>
       <c r="C7" t="n">
-        <v>17.22</v>
+        <v>19.16</v>
       </c>
       <c r="D7" t="n">
-        <v>16.71</v>
+        <v>17.45</v>
       </c>
       <c r="E7" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="H7" t="n">
-        <v>75.81999999999999</v>
+        <v>70.59</v>
       </c>
       <c r="I7" t="n">
-        <v>77.26000000000001</v>
+        <v>75.61</v>
       </c>
       <c r="J7" t="n">
-        <v>74.54000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -780,45 +780,45 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N7" t="n">
-        <v>6112</v>
+        <v>6122</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00:00</t>
+          <t>2026-10-20 07:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.59</v>
+        <v>16.92</v>
       </c>
       <c r="C8" t="n">
-        <v>17.8</v>
+        <v>17.33</v>
       </c>
       <c r="D8" t="n">
-        <v>17.29</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="n">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="F8" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
-        <v>73.83</v>
+        <v>74.87</v>
       </c>
       <c r="I8" t="n">
-        <v>74.95</v>
+        <v>75.66</v>
       </c>
       <c r="J8" t="n">
-        <v>72.36</v>
+        <v>74.08</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -830,42 +830,42 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>6122</v>
+        <v>6092</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20 01:00:00</t>
+          <t>2026-10-20 06:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.24</v>
+        <v>16.75</v>
       </c>
       <c r="C9" t="n">
-        <v>18.59</v>
+        <v>16.84</v>
       </c>
       <c r="D9" t="n">
-        <v>17.84</v>
+        <v>16.64</v>
       </c>
       <c r="E9" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="F9" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>66.76000000000001</v>
+        <v>74.86</v>
       </c>
       <c r="I9" t="n">
-        <v>71.14</v>
+        <v>75.98</v>
       </c>
       <c r="J9" t="n">
-        <v>63.93</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -877,42 +877,42 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6092</v>
+        <v>6102</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20 00:00:00</t>
+          <t>2026-10-20 05:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18.68</v>
+        <v>16.83</v>
       </c>
       <c r="C10" t="n">
-        <v>18.93</v>
+        <v>17.01</v>
       </c>
       <c r="D10" t="n">
-        <v>18.52</v>
+        <v>16.66</v>
       </c>
       <c r="E10" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F10" t="n">
         <v>11.7</v>
       </c>
-      <c r="F10" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>64.40000000000001</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>65.87</v>
+        <v>75.19</v>
       </c>
       <c r="J10" t="n">
-        <v>61.94</v>
+        <v>72.06</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -924,42 +924,42 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6122</v>
+        <v>6082</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19 23:00:00</t>
+          <t>2026-10-20 04:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.43</v>
+        <v>16.74</v>
       </c>
       <c r="C11" t="n">
-        <v>19.64</v>
+        <v>16.99</v>
       </c>
       <c r="D11" t="n">
-        <v>19.01</v>
+        <v>16.45</v>
       </c>
       <c r="E11" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="F11" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>60.1</v>
+        <v>74.84</v>
       </c>
       <c r="I11" t="n">
-        <v>60.96</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>59.25</v>
+        <v>72.64</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -971,51 +971,51 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6132</v>
+        <v>6112</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19 22:00:00</t>
+          <t>2026-10-20 03:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.1</v>
+        <v>16.86</v>
       </c>
       <c r="C12" t="n">
-        <v>20.3</v>
+        <v>17.22</v>
       </c>
       <c r="D12" t="n">
-        <v>19.77</v>
+        <v>16.71</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="F12" t="n">
-        <v>10.9</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>56.64</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>58.8</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>55.68</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>6112</v>
@@ -1025,834 +1025,834 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19 21:00:00</t>
+          <t>2026-10-20 02:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>17.59</v>
       </c>
       <c r="C13" t="n">
-        <v>20.17</v>
+        <v>17.8</v>
       </c>
       <c r="D13" t="n">
-        <v>19.94</v>
+        <v>17.29</v>
       </c>
       <c r="E13" t="n">
-        <v>10.6</v>
+        <v>12.7</v>
       </c>
       <c r="F13" t="n">
-        <v>10.6</v>
+        <v>12.5</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>55.69</v>
+        <v>73.83</v>
       </c>
       <c r="I13" t="n">
-        <v>55.96</v>
+        <v>74.95</v>
       </c>
       <c r="J13" t="n">
-        <v>55.41</v>
+        <v>72.36</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-19 20:00:00</t>
+          <t>2026-10-20 01:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19.56</v>
+        <v>18.24</v>
       </c>
       <c r="C14" t="n">
-        <v>19.96</v>
+        <v>18.59</v>
       </c>
       <c r="D14" t="n">
-        <v>19.34</v>
+        <v>17.84</v>
       </c>
       <c r="E14" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="F14" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>56.91</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>57.67</v>
+        <v>71.14</v>
       </c>
       <c r="J14" t="n">
-        <v>55.82</v>
+        <v>63.93</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6142</v>
+        <v>6092</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-19 19:00:00</t>
+          <t>2026-10-20 00:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.8</v>
+        <v>18.68</v>
       </c>
       <c r="C15" t="n">
-        <v>19.92</v>
+        <v>18.93</v>
       </c>
       <c r="D15" t="n">
-        <v>19.62</v>
+        <v>18.52</v>
       </c>
       <c r="E15" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
       <c r="F15" t="n">
-        <v>10.2</v>
+        <v>11.2</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>55.22</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>56.29</v>
+        <v>65.87</v>
       </c>
       <c r="J15" t="n">
-        <v>54.46</v>
+        <v>61.94</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6152</v>
+        <v>6122</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-19 23:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19.91</v>
+        <v>19.43</v>
       </c>
       <c r="C16" t="n">
-        <v>19.98</v>
+        <v>19.64</v>
       </c>
       <c r="D16" t="n">
-        <v>19.83</v>
+        <v>19.01</v>
       </c>
       <c r="E16" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="F16" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>54.74</v>
+        <v>60.1</v>
       </c>
       <c r="I16" t="n">
-        <v>54.92</v>
+        <v>60.96</v>
       </c>
       <c r="J16" t="n">
-        <v>54.61</v>
+        <v>59.25</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>6162</v>
+        <v>6132</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-19 22:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.31</v>
+        <v>20.1</v>
       </c>
       <c r="C17" t="n">
-        <v>20.99</v>
+        <v>20.3</v>
       </c>
       <c r="D17" t="n">
-        <v>19.97</v>
+        <v>19.77</v>
       </c>
       <c r="E17" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="G17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>53.29</v>
+        <v>56.64</v>
       </c>
       <c r="I17" t="n">
-        <v>54.84</v>
+        <v>58.8</v>
       </c>
       <c r="J17" t="n">
-        <v>51.22</v>
+        <v>55.68</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="N17" t="n">
-        <v>6170</v>
+        <v>6112</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-19 21:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21.38</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>21.67</v>
+        <v>20.17</v>
       </c>
       <c r="D18" t="n">
-        <v>20.91</v>
+        <v>19.94</v>
       </c>
       <c r="E18" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="G18" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>49.67</v>
+        <v>55.69</v>
       </c>
       <c r="I18" t="n">
-        <v>50.93</v>
+        <v>55.96</v>
       </c>
       <c r="J18" t="n">
-        <v>48.59</v>
+        <v>55.41</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="N18" t="n">
-        <v>6190</v>
+        <v>6142</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00:00</t>
+          <t>2026-10-19 20:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21.78</v>
+        <v>19.56</v>
       </c>
       <c r="C19" t="n">
-        <v>22.31</v>
+        <v>19.96</v>
       </c>
       <c r="D19" t="n">
-        <v>21.39</v>
+        <v>19.34</v>
       </c>
       <c r="E19" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="F19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="G19" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>48.06</v>
+        <v>56.91</v>
       </c>
       <c r="I19" t="n">
-        <v>48.87</v>
+        <v>57.67</v>
       </c>
       <c r="J19" t="n">
-        <v>46.24</v>
+        <v>55.82</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6210</v>
+        <v>6142</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.97</v>
+        <v>19.8</v>
       </c>
       <c r="C20" t="n">
-        <v>24.27</v>
+        <v>19.92</v>
       </c>
       <c r="D20" t="n">
-        <v>22.16</v>
+        <v>19.62</v>
       </c>
       <c r="E20" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="F20" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G20" t="n">
-        <v>747</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>44.85</v>
+        <v>55.22</v>
       </c>
       <c r="I20" t="n">
-        <v>47.21</v>
+        <v>56.29</v>
       </c>
       <c r="J20" t="n">
-        <v>41.93</v>
+        <v>54.46</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="M20" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="N20" t="n">
-        <v>6220</v>
+        <v>6152</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-19 13:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.58</v>
+        <v>19.91</v>
       </c>
       <c r="C21" t="n">
-        <v>23.47</v>
+        <v>19.98</v>
       </c>
       <c r="D21" t="n">
-        <v>21.83</v>
+        <v>19.83</v>
       </c>
       <c r="E21" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="F21" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="G21" t="n">
-        <v>815</v>
+        <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>45.81</v>
+        <v>54.74</v>
       </c>
       <c r="I21" t="n">
-        <v>48.66</v>
+        <v>54.92</v>
       </c>
       <c r="J21" t="n">
-        <v>43.93</v>
+        <v>54.61</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="M21" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>6220</v>
+        <v>6162</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-19 12:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21.31</v>
+        <v>20.31</v>
       </c>
       <c r="C22" t="n">
-        <v>22.4</v>
+        <v>20.99</v>
       </c>
       <c r="D22" t="n">
-        <v>20.2</v>
+        <v>19.97</v>
       </c>
       <c r="E22" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="F22" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="G22" t="n">
-        <v>689</v>
+        <v>40</v>
       </c>
       <c r="H22" t="n">
-        <v>50.33</v>
+        <v>53.29</v>
       </c>
       <c r="I22" t="n">
-        <v>56.08</v>
+        <v>54.84</v>
       </c>
       <c r="J22" t="n">
-        <v>47.33</v>
+        <v>51.22</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-19 11:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18.91</v>
+        <v>21.38</v>
       </c>
       <c r="C23" t="n">
-        <v>19.91</v>
+        <v>21.67</v>
       </c>
       <c r="D23" t="n">
-        <v>18.4</v>
+        <v>20.91</v>
       </c>
       <c r="E23" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="F23" t="n">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>305</v>
+        <v>213</v>
       </c>
       <c r="H23" t="n">
-        <v>60.58</v>
+        <v>49.67</v>
       </c>
       <c r="I23" t="n">
-        <v>63.06</v>
+        <v>50.93</v>
       </c>
       <c r="J23" t="n">
-        <v>55.94</v>
+        <v>48.59</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.94</v>
+        <v>21.78</v>
       </c>
       <c r="C24" t="n">
-        <v>18.46</v>
+        <v>22.31</v>
       </c>
       <c r="D24" t="n">
-        <v>17.55</v>
+        <v>21.39</v>
       </c>
       <c r="E24" t="n">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="F24" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="H24" t="n">
-        <v>67.54000000000001</v>
+        <v>48.06</v>
       </c>
       <c r="I24" t="n">
-        <v>70.20999999999999</v>
+        <v>48.87</v>
       </c>
       <c r="J24" t="n">
-        <v>64.44</v>
+        <v>46.24</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>6152</v>
+        <v>6210</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.55</v>
+        <v>22.97</v>
       </c>
       <c r="C25" t="n">
-        <v>17.81</v>
+        <v>24.27</v>
       </c>
       <c r="D25" t="n">
-        <v>17.2</v>
+        <v>22.16</v>
       </c>
       <c r="E25" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="F25" t="n">
-        <v>10.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>95</v>
+        <v>747</v>
       </c>
       <c r="H25" t="n">
-        <v>68.43000000000001</v>
+        <v>44.85</v>
       </c>
       <c r="I25" t="n">
-        <v>69.95</v>
+        <v>47.21</v>
       </c>
       <c r="J25" t="n">
-        <v>65.48</v>
+        <v>41.93</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2</v>
+        <v>4.3</v>
       </c>
       <c r="N25" t="n">
-        <v>6132</v>
+        <v>6220</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16.64</v>
+        <v>22.58</v>
       </c>
       <c r="C26" t="n">
-        <v>17.06</v>
+        <v>23.47</v>
       </c>
       <c r="D26" t="n">
-        <v>16.2</v>
+        <v>21.83</v>
       </c>
       <c r="E26" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="F26" t="n">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
       <c r="G26" t="n">
-        <v>44</v>
+        <v>815</v>
       </c>
       <c r="H26" t="n">
-        <v>72.79000000000001</v>
+        <v>45.81</v>
       </c>
       <c r="I26" t="n">
-        <v>77.45</v>
+        <v>48.66</v>
       </c>
       <c r="J26" t="n">
-        <v>70.3</v>
+        <v>43.93</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>6132</v>
+        <v>6220</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15.62</v>
+        <v>21.31</v>
       </c>
       <c r="C27" t="n">
-        <v>16.07</v>
+        <v>22.4</v>
       </c>
       <c r="D27" t="n">
-        <v>15.35</v>
+        <v>20.2</v>
       </c>
       <c r="E27" t="n">
-        <v>12.9</v>
+        <v>10.4</v>
       </c>
       <c r="F27" t="n">
-        <v>12.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>8</v>
+        <v>689</v>
       </c>
       <c r="H27" t="n">
-        <v>85.33</v>
+        <v>50.33</v>
       </c>
       <c r="I27" t="n">
-        <v>89.23</v>
+        <v>56.08</v>
       </c>
       <c r="J27" t="n">
-        <v>79.03</v>
+        <v>47.33</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="N27" t="n">
-        <v>6122</v>
+        <v>6190</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15.25</v>
+        <v>18.91</v>
       </c>
       <c r="C28" t="n">
-        <v>15.35</v>
+        <v>19.91</v>
       </c>
       <c r="D28" t="n">
-        <v>15.06</v>
+        <v>18.4</v>
       </c>
       <c r="E28" t="n">
-        <v>13.3</v>
+        <v>10.9</v>
       </c>
       <c r="F28" t="n">
-        <v>13.2</v>
+        <v>10.6</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="H28" t="n">
-        <v>89.16</v>
+        <v>60.58</v>
       </c>
       <c r="I28" t="n">
-        <v>91.05</v>
+        <v>63.06</v>
       </c>
       <c r="J28" t="n">
-        <v>87.77</v>
+        <v>55.94</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N28" t="n">
-        <v>6122</v>
+        <v>6162</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15.2</v>
+        <v>17.94</v>
       </c>
       <c r="C29" t="n">
-        <v>15.32</v>
+        <v>18.46</v>
       </c>
       <c r="D29" t="n">
-        <v>15.08</v>
+        <v>17.55</v>
       </c>
       <c r="E29" t="n">
-        <v>13.1</v>
+        <v>11.6</v>
       </c>
       <c r="F29" t="n">
-        <v>13.1</v>
+        <v>11.2</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H29" t="n">
-        <v>88.42</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>89.37</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>87.13</v>
+        <v>64.44</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>6122</v>
+        <v>6152</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15.53</v>
+        <v>17.55</v>
       </c>
       <c r="C30" t="n">
-        <v>15.66</v>
+        <v>17.81</v>
       </c>
       <c r="D30" t="n">
-        <v>15.45</v>
+        <v>17.2</v>
       </c>
       <c r="E30" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="F30" t="n">
-        <v>12.7</v>
+        <v>10.9</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H30" t="n">
-        <v>85.40000000000001</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>86.58</v>
+        <v>69.95</v>
       </c>
       <c r="J30" t="n">
-        <v>83.42</v>
+        <v>65.48</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1861,45 +1861,45 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N30" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>15.66</v>
+        <v>16.64</v>
       </c>
       <c r="C31" t="n">
-        <v>15.73</v>
+        <v>17.06</v>
       </c>
       <c r="D31" t="n">
-        <v>15.62</v>
+        <v>16.2</v>
       </c>
       <c r="E31" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="F31" t="n">
-        <v>12.5</v>
+        <v>11.4</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H31" t="n">
-        <v>82.52</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>82.76000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="J31" t="n">
-        <v>82.33</v>
+        <v>70.3</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1908,54 +1908,54 @@
         <v>0.3</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N31" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>15.72</v>
+        <v>15.62</v>
       </c>
       <c r="C32" t="n">
-        <v>15.77</v>
+        <v>16.07</v>
       </c>
       <c r="D32" t="n">
-        <v>15.65</v>
+        <v>15.35</v>
       </c>
       <c r="E32" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F32" t="n">
         <v>12.4</v>
       </c>
-      <c r="F32" t="n">
-        <v>12.3</v>
-      </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>81.17</v>
+        <v>85.33</v>
       </c>
       <c r="I32" t="n">
-        <v>82.40000000000001</v>
+        <v>89.23</v>
       </c>
       <c r="J32" t="n">
-        <v>80.16</v>
+        <v>79.03</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
         <v>6122</v>
@@ -1965,44 +1965,44 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.09</v>
+        <v>15.25</v>
       </c>
       <c r="C33" t="n">
-        <v>16.59</v>
+        <v>15.35</v>
       </c>
       <c r="D33" t="n">
-        <v>15.76</v>
+        <v>15.06</v>
       </c>
       <c r="E33" t="n">
-        <v>11.9</v>
+        <v>13.3</v>
       </c>
       <c r="F33" t="n">
-        <v>11.4</v>
+        <v>13.2</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>76.7</v>
+        <v>89.16</v>
       </c>
       <c r="I33" t="n">
-        <v>80.06999999999999</v>
+        <v>91.05</v>
       </c>
       <c r="J33" t="n">
-        <v>72.89</v>
+        <v>87.77</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>6122</v>
@@ -2012,93 +2012,91 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.2</v>
+        <v>15.2</v>
       </c>
       <c r="C34" t="n">
-        <v>16.53</v>
+        <v>15.32</v>
       </c>
       <c r="D34" t="n">
-        <v>15.84</v>
+        <v>15.08</v>
       </c>
       <c r="E34" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="F34" t="n">
-        <v>11.6</v>
+        <v>13.1</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>77.2</v>
+        <v>88.42</v>
       </c>
       <c r="I34" t="n">
-        <v>80.54000000000001</v>
+        <v>89.37</v>
       </c>
       <c r="J34" t="n">
-        <v>73.31999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>6122</v>
       </c>
-      <c r="O34" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16.03</v>
+        <v>15.53</v>
       </c>
       <c r="C35" t="n">
-        <v>16.12</v>
+        <v>15.66</v>
       </c>
       <c r="D35" t="n">
-        <v>15.93</v>
+        <v>15.45</v>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="F35" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>77.56</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>79.16</v>
+        <v>86.58</v>
       </c>
       <c r="J35" t="n">
-        <v>76.79000000000001</v>
+        <v>83.42</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>6122</v>
@@ -2108,44 +2106,44 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.79</v>
+        <v>15.66</v>
       </c>
       <c r="C36" t="n">
-        <v>15.92</v>
+        <v>15.73</v>
       </c>
       <c r="D36" t="n">
-        <v>15.7</v>
+        <v>15.62</v>
       </c>
       <c r="E36" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="F36" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>78.34999999999999</v>
+        <v>82.52</v>
       </c>
       <c r="I36" t="n">
-        <v>78.65000000000001</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>77.79000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="M36" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
         <v>6122</v>
@@ -2155,44 +2153,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15.9</v>
+        <v>15.72</v>
       </c>
       <c r="C37" t="n">
-        <v>16.37</v>
+        <v>15.77</v>
       </c>
       <c r="D37" t="n">
-        <v>15.67</v>
+        <v>15.65</v>
       </c>
       <c r="E37" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="F37" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>76.45999999999999</v>
+        <v>81.17</v>
       </c>
       <c r="I37" t="n">
-        <v>78.44</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>72.33</v>
+        <v>80.16</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N37" t="n">
         <v>6122</v>
@@ -2202,467 +2200,469 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.37</v>
+        <v>16.09</v>
       </c>
       <c r="C38" t="n">
-        <v>16.48</v>
+        <v>16.59</v>
       </c>
       <c r="D38" t="n">
-        <v>16.29</v>
+        <v>15.76</v>
       </c>
       <c r="E38" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="F38" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>74.02</v>
+        <v>76.7</v>
       </c>
       <c r="I38" t="n">
-        <v>74.88</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>72.13</v>
+        <v>72.89</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M38" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N38" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.84</v>
+        <v>16.2</v>
       </c>
       <c r="C39" t="n">
-        <v>17.08</v>
+        <v>16.53</v>
       </c>
       <c r="D39" t="n">
-        <v>16.57</v>
+        <v>15.84</v>
       </c>
       <c r="E39" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="F39" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>70.64</v>
+        <v>77.2</v>
       </c>
       <c r="I39" t="n">
-        <v>72.89</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>68.62</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="N39" t="n">
-        <v>6132</v>
-      </c>
-      <c r="O39" t="inlineStr"/>
+        <v>6122</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.26</v>
+        <v>16.03</v>
       </c>
       <c r="C40" t="n">
-        <v>17.41</v>
+        <v>16.12</v>
       </c>
       <c r="D40" t="n">
-        <v>17.13</v>
+        <v>15.93</v>
       </c>
       <c r="E40" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="G40" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>65.97</v>
+        <v>77.56</v>
       </c>
       <c r="I40" t="n">
-        <v>68.3</v>
+        <v>79.16</v>
       </c>
       <c r="J40" t="n">
-        <v>62.44</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="M40" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="N40" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.57</v>
+        <v>15.79</v>
       </c>
       <c r="C41" t="n">
-        <v>18.11</v>
+        <v>15.92</v>
       </c>
       <c r="D41" t="n">
-        <v>17.4</v>
+        <v>15.7</v>
       </c>
       <c r="E41" t="n">
-        <v>10.4</v>
+        <v>11.9</v>
       </c>
       <c r="F41" t="n">
-        <v>9.800000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="G41" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>63.38</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>64.3</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>61.77</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="M41" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="N41" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18</v>
+        <v>15.9</v>
       </c>
       <c r="C42" t="n">
-        <v>18.2</v>
+        <v>16.37</v>
       </c>
       <c r="D42" t="n">
-        <v>17.79</v>
+        <v>15.67</v>
       </c>
       <c r="E42" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="F42" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="G42" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>62.96</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>64.08</v>
+        <v>78.44</v>
       </c>
       <c r="J42" t="n">
-        <v>61.81</v>
+        <v>72.33</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="M42" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N42" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18.15</v>
+        <v>16.37</v>
       </c>
       <c r="C43" t="n">
-        <v>18.5</v>
+        <v>16.48</v>
       </c>
       <c r="D43" t="n">
-        <v>17.92</v>
+        <v>16.29</v>
       </c>
       <c r="E43" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="G43" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>60.86</v>
+        <v>74.02</v>
       </c>
       <c r="I43" t="n">
-        <v>62.23</v>
+        <v>74.88</v>
       </c>
       <c r="J43" t="n">
-        <v>59.51</v>
+        <v>72.13</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="N43" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17.71</v>
+        <v>16.84</v>
       </c>
       <c r="C44" t="n">
-        <v>18.05</v>
+        <v>17.08</v>
       </c>
       <c r="D44" t="n">
-        <v>17.31</v>
+        <v>16.57</v>
       </c>
       <c r="E44" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
       <c r="F44" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="G44" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>61.59</v>
+        <v>70.64</v>
       </c>
       <c r="I44" t="n">
-        <v>63.45</v>
+        <v>72.89</v>
       </c>
       <c r="J44" t="n">
-        <v>59.82</v>
+        <v>68.62</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N44" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.72</v>
+        <v>17.26</v>
       </c>
       <c r="C45" t="n">
-        <v>17.47</v>
+        <v>17.41</v>
       </c>
       <c r="D45" t="n">
-        <v>16.08</v>
+        <v>17.13</v>
       </c>
       <c r="E45" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="F45" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
-        <v>260</v>
+        <v>11</v>
       </c>
       <c r="H45" t="n">
-        <v>67.33</v>
+        <v>65.97</v>
       </c>
       <c r="I45" t="n">
-        <v>70.81999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="J45" t="n">
-        <v>63.98</v>
+        <v>62.44</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M45" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N45" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15.83</v>
+        <v>17.57</v>
       </c>
       <c r="C46" t="n">
-        <v>16.23</v>
+        <v>18.11</v>
       </c>
       <c r="D46" t="n">
-        <v>15.45</v>
+        <v>17.4</v>
       </c>
       <c r="E46" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F46" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H46" t="n">
-        <v>72.95</v>
+        <v>63.38</v>
       </c>
       <c r="I46" t="n">
-        <v>75.03</v>
+        <v>64.3</v>
       </c>
       <c r="J46" t="n">
-        <v>69.84999999999999</v>
+        <v>61.77</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="M46" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N46" t="n">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>15.22</v>
+        <v>18</v>
       </c>
       <c r="C47" t="n">
-        <v>15.77</v>
+        <v>18.2</v>
       </c>
       <c r="D47" t="n">
-        <v>14.97</v>
+        <v>17.79</v>
       </c>
       <c r="E47" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="F47" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="G47" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H47" t="n">
-        <v>77.61</v>
+        <v>62.96</v>
       </c>
       <c r="I47" t="n">
-        <v>79.25</v>
+        <v>64.08</v>
       </c>
       <c r="J47" t="n">
-        <v>74.45</v>
+        <v>61.81</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M47" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N47" t="n">
         <v>6162</v>
@@ -2672,44 +2672,44 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>14.79</v>
+        <v>18.15</v>
       </c>
       <c r="C48" t="n">
-        <v>15.1</v>
+        <v>18.5</v>
       </c>
       <c r="D48" t="n">
-        <v>14.32</v>
+        <v>17.92</v>
       </c>
       <c r="E48" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="F48" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="G48" t="n">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="H48" t="n">
-        <v>80.70999999999999</v>
+        <v>60.86</v>
       </c>
       <c r="I48" t="n">
-        <v>83.36</v>
+        <v>62.23</v>
       </c>
       <c r="J48" t="n">
-        <v>79.05</v>
+        <v>59.51</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M48" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N48" t="n">
         <v>6142</v>
@@ -2719,94 +2719,94 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>14.05</v>
+        <v>17.71</v>
       </c>
       <c r="C49" t="n">
-        <v>14.26</v>
+        <v>18.05</v>
       </c>
       <c r="D49" t="n">
-        <v>13.8</v>
+        <v>17.31</v>
       </c>
       <c r="E49" t="n">
-        <v>11.4</v>
+        <v>10.1</v>
       </c>
       <c r="F49" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="G49" t="n">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="H49" t="n">
-        <v>85.09</v>
+        <v>61.59</v>
       </c>
       <c r="I49" t="n">
-        <v>86.40000000000001</v>
+        <v>63.45</v>
       </c>
       <c r="J49" t="n">
-        <v>84.14</v>
+        <v>59.82</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="M49" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>14.11</v>
+        <v>16.72</v>
       </c>
       <c r="C50" t="n">
-        <v>14.56</v>
+        <v>17.47</v>
       </c>
       <c r="D50" t="n">
-        <v>13.7</v>
+        <v>16.08</v>
       </c>
       <c r="E50" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="F50" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>31</v>
+        <v>260</v>
       </c>
       <c r="H50" t="n">
-        <v>81.01000000000001</v>
+        <v>67.33</v>
       </c>
       <c r="I50" t="n">
-        <v>87.31</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>75.84999999999999</v>
+        <v>63.98</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M50" t="n">
         <v>1.3</v>
       </c>
       <c r="N50" t="n">
-        <v>6132</v>
+        <v>6170</v>
       </c>
       <c r="O50" t="n">
         <v>1.6</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,411 +508,411 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 13:00:00</t>
+          <t>2026-10-20 17:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.99</v>
+        <v>26.24</v>
       </c>
       <c r="C2" t="n">
-        <v>25.05</v>
+        <v>26.34</v>
       </c>
       <c r="D2" t="n">
-        <v>24.91</v>
+        <v>26.14</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5</v>
+        <v>12.6</v>
       </c>
       <c r="F2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="G2" t="n">
-        <v>297</v>
+        <v>138</v>
       </c>
       <c r="H2" t="n">
-        <v>43.81</v>
+        <v>43.39</v>
       </c>
       <c r="I2" t="n">
-        <v>43.82</v>
+        <v>43.49</v>
       </c>
       <c r="J2" t="n">
-        <v>43.79</v>
+        <v>43.23</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="N2" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 12:00:00</t>
+          <t>2026-10-20 16:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.81</v>
+        <v>26.66</v>
       </c>
       <c r="C3" t="n">
-        <v>25.08</v>
+        <v>26.95</v>
       </c>
       <c r="D3" t="n">
-        <v>24.53</v>
+        <v>26.15</v>
       </c>
       <c r="E3" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="F3" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="G3" t="n">
-        <v>373</v>
+        <v>229</v>
       </c>
       <c r="H3" t="n">
-        <v>43.89</v>
+        <v>42.04</v>
       </c>
       <c r="I3" t="n">
-        <v>44.75</v>
+        <v>43.28</v>
       </c>
       <c r="J3" t="n">
-        <v>43.04</v>
+        <v>41.15</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="M3" t="n">
         <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00:00</t>
+          <t>2026-10-20 15:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.48</v>
+        <v>27.13</v>
       </c>
       <c r="C4" t="n">
-        <v>24.58</v>
+        <v>27.72</v>
       </c>
       <c r="D4" t="n">
-        <v>22.73</v>
+        <v>26.66</v>
       </c>
       <c r="E4" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>11.9</v>
       </c>
       <c r="G4" t="n">
-        <v>519</v>
+        <v>368</v>
       </c>
       <c r="H4" t="n">
-        <v>47.14</v>
+        <v>40.38</v>
       </c>
       <c r="I4" t="n">
-        <v>49.9</v>
+        <v>41.51</v>
       </c>
       <c r="J4" t="n">
-        <v>43.67</v>
+        <v>39.08</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 10:00:00</t>
+          <t>2026-10-20 14:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.96</v>
+        <v>26.77</v>
       </c>
       <c r="C5" t="n">
-        <v>22.96</v>
+        <v>27.91</v>
       </c>
       <c r="D5" t="n">
-        <v>21.26</v>
+        <v>25.49</v>
       </c>
       <c r="E5" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="F5" t="n">
-        <v>11.2</v>
+        <v>12.1</v>
       </c>
       <c r="G5" t="n">
-        <v>298</v>
+        <v>508</v>
       </c>
       <c r="H5" t="n">
-        <v>52.22</v>
+        <v>41.64</v>
       </c>
       <c r="I5" t="n">
-        <v>54.36</v>
+        <v>44.08</v>
       </c>
       <c r="J5" t="n">
-        <v>49</v>
+        <v>39.72</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="N5" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20 09:00:00</t>
+          <t>2026-10-20 13:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.32</v>
+        <v>25.07</v>
       </c>
       <c r="C6" t="n">
-        <v>21.66</v>
+        <v>25.85</v>
       </c>
       <c r="D6" t="n">
-        <v>19.17</v>
+        <v>24.61</v>
       </c>
       <c r="E6" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="F6" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="G6" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
-        <v>60.55</v>
+        <v>44.5</v>
       </c>
       <c r="I6" t="n">
-        <v>64.51000000000001</v>
+        <v>45.61</v>
       </c>
       <c r="J6" t="n">
-        <v>55.76</v>
+        <v>43.09</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>6142</v>
+        <v>6170</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20 08:00:00</t>
+          <t>2026-10-20 12:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.15</v>
+        <v>24.81</v>
       </c>
       <c r="C7" t="n">
-        <v>19.16</v>
+        <v>25.08</v>
       </c>
       <c r="D7" t="n">
-        <v>17.45</v>
+        <v>24.53</v>
       </c>
       <c r="E7" t="n">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="F7" t="n">
-        <v>12.1</v>
+        <v>11.2</v>
       </c>
       <c r="G7" t="n">
-        <v>111</v>
+        <v>373</v>
       </c>
       <c r="H7" t="n">
-        <v>70.59</v>
+        <v>43.89</v>
       </c>
       <c r="I7" t="n">
-        <v>75.61</v>
+        <v>44.75</v>
       </c>
       <c r="J7" t="n">
-        <v>65.56999999999999</v>
+        <v>43.04</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>6122</v>
+        <v>6162</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20 07:00:00</t>
+          <t>2026-10-20 11:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.92</v>
+        <v>23.48</v>
       </c>
       <c r="C8" t="n">
-        <v>17.33</v>
+        <v>24.58</v>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>22.73</v>
       </c>
       <c r="E8" t="n">
-        <v>12.3</v>
+        <v>11.3</v>
       </c>
       <c r="F8" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>17</v>
+        <v>519</v>
       </c>
       <c r="H8" t="n">
-        <v>74.87</v>
+        <v>47.14</v>
       </c>
       <c r="I8" t="n">
-        <v>75.66</v>
+        <v>49.9</v>
       </c>
       <c r="J8" t="n">
-        <v>74.08</v>
+        <v>43.67</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>6092</v>
+        <v>6162</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00:00</t>
+          <t>2026-10-20 10:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.75</v>
+        <v>21.96</v>
       </c>
       <c r="C9" t="n">
-        <v>16.84</v>
+        <v>22.96</v>
       </c>
       <c r="D9" t="n">
-        <v>16.64</v>
+        <v>21.26</v>
       </c>
       <c r="E9" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="F9" t="n">
-        <v>11.9</v>
+        <v>11.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="H9" t="n">
-        <v>74.86</v>
+        <v>52.22</v>
       </c>
       <c r="I9" t="n">
-        <v>75.98</v>
+        <v>54.36</v>
       </c>
       <c r="J9" t="n">
-        <v>73.98999999999999</v>
+        <v>49</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>6102</v>
+        <v>6152</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20 05:00:00</t>
+          <t>2026-10-20 09:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.83</v>
+        <v>20.32</v>
       </c>
       <c r="C10" t="n">
-        <v>17.01</v>
+        <v>21.66</v>
       </c>
       <c r="D10" t="n">
-        <v>16.66</v>
+        <v>19.17</v>
       </c>
       <c r="E10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F10" t="n">
         <v>11.9</v>
       </c>
-      <c r="F10" t="n">
-        <v>11.7</v>
-      </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="H10" t="n">
-        <v>73.56999999999999</v>
+        <v>60.55</v>
       </c>
       <c r="I10" t="n">
-        <v>75.19</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>72.06</v>
+        <v>55.76</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -921,45 +921,45 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N10" t="n">
-        <v>6082</v>
+        <v>6142</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20 04:00:00</t>
+          <t>2026-10-20 08:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16.74</v>
+        <v>18.15</v>
       </c>
       <c r="C11" t="n">
-        <v>16.99</v>
+        <v>19.16</v>
       </c>
       <c r="D11" t="n">
-        <v>16.45</v>
+        <v>17.45</v>
       </c>
       <c r="E11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F11" t="n">
         <v>12.1</v>
       </c>
-      <c r="F11" t="n">
-        <v>11.8</v>
-      </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="H11" t="n">
-        <v>74.84</v>
+        <v>70.59</v>
       </c>
       <c r="I11" t="n">
-        <v>77.06999999999999</v>
+        <v>75.61</v>
       </c>
       <c r="J11" t="n">
-        <v>72.64</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -968,45 +968,45 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N11" t="n">
-        <v>6112</v>
+        <v>6122</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20 03:00:00</t>
+          <t>2026-10-20 07:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16.86</v>
+        <v>16.92</v>
       </c>
       <c r="C12" t="n">
-        <v>17.22</v>
+        <v>17.33</v>
       </c>
       <c r="D12" t="n">
-        <v>16.71</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>75.81999999999999</v>
+        <v>74.87</v>
       </c>
       <c r="I12" t="n">
-        <v>77.26000000000001</v>
+        <v>75.66</v>
       </c>
       <c r="J12" t="n">
-        <v>74.54000000000001</v>
+        <v>74.08</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1018,42 +1018,42 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6112</v>
+        <v>6092</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00:00</t>
+          <t>2026-10-20 06:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.59</v>
+        <v>16.75</v>
       </c>
       <c r="C13" t="n">
-        <v>17.8</v>
+        <v>16.84</v>
       </c>
       <c r="D13" t="n">
-        <v>17.29</v>
+        <v>16.64</v>
       </c>
       <c r="E13" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="F13" t="n">
-        <v>12.5</v>
+        <v>11.9</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>73.83</v>
+        <v>74.86</v>
       </c>
       <c r="I13" t="n">
-        <v>74.95</v>
+        <v>75.98</v>
       </c>
       <c r="J13" t="n">
-        <v>72.36</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1065,42 +1065,42 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6122</v>
+        <v>6102</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20 01:00:00</t>
+          <t>2026-10-20 05:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18.24</v>
+        <v>16.83</v>
       </c>
       <c r="C14" t="n">
-        <v>18.59</v>
+        <v>17.01</v>
       </c>
       <c r="D14" t="n">
-        <v>17.84</v>
+        <v>16.66</v>
       </c>
       <c r="E14" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="F14" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>66.76000000000001</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>71.14</v>
+        <v>75.19</v>
       </c>
       <c r="J14" t="n">
-        <v>63.93</v>
+        <v>72.06</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1112,42 +1112,42 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6092</v>
+        <v>6082</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20 00:00:00</t>
+          <t>2026-10-20 04:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18.68</v>
+        <v>16.74</v>
       </c>
       <c r="C15" t="n">
-        <v>18.93</v>
+        <v>16.99</v>
       </c>
       <c r="D15" t="n">
-        <v>18.52</v>
+        <v>16.45</v>
       </c>
       <c r="E15" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="F15" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>64.40000000000001</v>
+        <v>74.84</v>
       </c>
       <c r="I15" t="n">
-        <v>65.87</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>61.94</v>
+        <v>72.64</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1159,42 +1159,42 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6122</v>
+        <v>6112</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-19 23:00:00</t>
+          <t>2026-10-20 03:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19.43</v>
+        <v>16.86</v>
       </c>
       <c r="C16" t="n">
-        <v>19.64</v>
+        <v>17.22</v>
       </c>
       <c r="D16" t="n">
-        <v>19.01</v>
+        <v>16.71</v>
       </c>
       <c r="E16" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="F16" t="n">
-        <v>11.1</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>60.1</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>60.96</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>59.25</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1206,521 +1206,521 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>6132</v>
+        <v>6112</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-19 22:00:00</t>
+          <t>2026-10-20 02:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.1</v>
+        <v>17.59</v>
       </c>
       <c r="C17" t="n">
-        <v>20.3</v>
+        <v>17.8</v>
       </c>
       <c r="D17" t="n">
-        <v>19.77</v>
+        <v>17.29</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>12.7</v>
       </c>
       <c r="F17" t="n">
-        <v>10.9</v>
+        <v>12.5</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>56.64</v>
+        <v>73.83</v>
       </c>
       <c r="I17" t="n">
-        <v>58.8</v>
+        <v>74.95</v>
       </c>
       <c r="J17" t="n">
-        <v>55.68</v>
+        <v>72.36</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6112</v>
+        <v>6122</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-19 21:00:00</t>
+          <t>2026-10-20 01:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>18.24</v>
       </c>
       <c r="C18" t="n">
-        <v>20.17</v>
+        <v>18.59</v>
       </c>
       <c r="D18" t="n">
-        <v>19.94</v>
+        <v>17.84</v>
       </c>
       <c r="E18" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="F18" t="n">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>55.69</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>55.96</v>
+        <v>71.14</v>
       </c>
       <c r="J18" t="n">
-        <v>55.41</v>
+        <v>63.93</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6142</v>
+        <v>6092</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-19 20:00:00</t>
+          <t>2026-10-20 00:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.56</v>
+        <v>18.68</v>
       </c>
       <c r="C19" t="n">
-        <v>19.96</v>
+        <v>18.93</v>
       </c>
       <c r="D19" t="n">
-        <v>19.34</v>
+        <v>18.52</v>
       </c>
       <c r="E19" t="n">
-        <v>10.6</v>
+        <v>11.7</v>
       </c>
       <c r="F19" t="n">
-        <v>10.3</v>
+        <v>11.2</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>56.91</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>57.67</v>
+        <v>65.87</v>
       </c>
       <c r="J19" t="n">
-        <v>55.82</v>
+        <v>61.94</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-19 19:00:00</t>
+          <t>2026-10-19 23:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.8</v>
+        <v>19.43</v>
       </c>
       <c r="C20" t="n">
-        <v>19.92</v>
+        <v>19.64</v>
       </c>
       <c r="D20" t="n">
-        <v>19.62</v>
+        <v>19.01</v>
       </c>
       <c r="E20" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="F20" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>55.22</v>
+        <v>60.1</v>
       </c>
       <c r="I20" t="n">
-        <v>56.29</v>
+        <v>60.96</v>
       </c>
       <c r="J20" t="n">
-        <v>54.46</v>
+        <v>59.25</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-19 22:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.91</v>
+        <v>20.1</v>
       </c>
       <c r="C21" t="n">
-        <v>19.98</v>
+        <v>20.3</v>
       </c>
       <c r="D21" t="n">
-        <v>19.83</v>
+        <v>19.77</v>
       </c>
       <c r="E21" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="G21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>54.74</v>
+        <v>56.64</v>
       </c>
       <c r="I21" t="n">
-        <v>54.92</v>
+        <v>58.8</v>
       </c>
       <c r="J21" t="n">
-        <v>54.61</v>
+        <v>55.68</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="N21" t="n">
-        <v>6162</v>
+        <v>6112</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-19 21:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20.31</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>20.99</v>
+        <v>20.17</v>
       </c>
       <c r="D22" t="n">
-        <v>19.97</v>
+        <v>19.94</v>
       </c>
       <c r="E22" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="F22" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="G22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>53.29</v>
+        <v>55.69</v>
       </c>
       <c r="I22" t="n">
-        <v>54.84</v>
+        <v>55.96</v>
       </c>
       <c r="J22" t="n">
-        <v>51.22</v>
+        <v>55.41</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="N22" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-19 20:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21.38</v>
+        <v>19.56</v>
       </c>
       <c r="C23" t="n">
-        <v>21.67</v>
+        <v>19.96</v>
       </c>
       <c r="D23" t="n">
-        <v>20.91</v>
+        <v>19.34</v>
       </c>
       <c r="E23" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="G23" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>49.67</v>
+        <v>56.91</v>
       </c>
       <c r="I23" t="n">
-        <v>50.93</v>
+        <v>57.67</v>
       </c>
       <c r="J23" t="n">
-        <v>48.59</v>
+        <v>55.82</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="N23" t="n">
-        <v>6190</v>
+        <v>6142</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21.78</v>
+        <v>19.8</v>
       </c>
       <c r="C24" t="n">
-        <v>22.31</v>
+        <v>19.92</v>
       </c>
       <c r="D24" t="n">
-        <v>21.39</v>
+        <v>19.62</v>
       </c>
       <c r="E24" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="F24" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="G24" t="n">
-        <v>323</v>
+        <v>10</v>
       </c>
       <c r="H24" t="n">
-        <v>48.06</v>
+        <v>55.22</v>
       </c>
       <c r="I24" t="n">
-        <v>48.87</v>
+        <v>56.29</v>
       </c>
       <c r="J24" t="n">
-        <v>46.24</v>
+        <v>54.46</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6210</v>
+        <v>6152</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.97</v>
+        <v>19.91</v>
       </c>
       <c r="C25" t="n">
-        <v>24.27</v>
+        <v>19.98</v>
       </c>
       <c r="D25" t="n">
-        <v>22.16</v>
+        <v>19.83</v>
       </c>
       <c r="E25" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="F25" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G25" t="n">
-        <v>747</v>
+        <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>44.85</v>
+        <v>54.74</v>
       </c>
       <c r="I25" t="n">
-        <v>47.21</v>
+        <v>54.92</v>
       </c>
       <c r="J25" t="n">
-        <v>41.93</v>
+        <v>54.61</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="M25" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>6220</v>
+        <v>6162</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-19 13:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22.58</v>
+        <v>20.31</v>
       </c>
       <c r="C26" t="n">
-        <v>23.47</v>
+        <v>20.99</v>
       </c>
       <c r="D26" t="n">
-        <v>21.83</v>
+        <v>19.97</v>
       </c>
       <c r="E26" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F26" t="n">
         <v>10.1</v>
       </c>
-      <c r="F26" t="n">
-        <v>9.6</v>
-      </c>
       <c r="G26" t="n">
-        <v>815</v>
+        <v>40</v>
       </c>
       <c r="H26" t="n">
-        <v>45.81</v>
+        <v>53.29</v>
       </c>
       <c r="I26" t="n">
-        <v>48.66</v>
+        <v>54.84</v>
       </c>
       <c r="J26" t="n">
-        <v>43.93</v>
+        <v>51.22</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19 12:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.31</v>
+        <v>21.38</v>
       </c>
       <c r="C27" t="n">
-        <v>22.4</v>
+        <v>21.67</v>
       </c>
       <c r="D27" t="n">
-        <v>20.2</v>
+        <v>20.91</v>
       </c>
       <c r="E27" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="F27" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>689</v>
+        <v>213</v>
       </c>
       <c r="H27" t="n">
-        <v>50.33</v>
+        <v>49.67</v>
       </c>
       <c r="I27" t="n">
-        <v>56.08</v>
+        <v>50.93</v>
       </c>
       <c r="J27" t="n">
-        <v>47.33</v>
+        <v>48.59</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
         <v>6190</v>
@@ -1730,223 +1730,223 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-19 11:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.91</v>
+        <v>21.78</v>
       </c>
       <c r="C28" t="n">
-        <v>19.91</v>
+        <v>22.31</v>
       </c>
       <c r="D28" t="n">
-        <v>18.4</v>
+        <v>21.39</v>
       </c>
       <c r="E28" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="F28" t="n">
-        <v>10.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="H28" t="n">
-        <v>60.58</v>
+        <v>48.06</v>
       </c>
       <c r="I28" t="n">
-        <v>63.06</v>
+        <v>48.87</v>
       </c>
       <c r="J28" t="n">
-        <v>55.94</v>
+        <v>46.24</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="M28" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6162</v>
+        <v>6210</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.94</v>
+        <v>22.97</v>
       </c>
       <c r="C29" t="n">
-        <v>18.46</v>
+        <v>24.27</v>
       </c>
       <c r="D29" t="n">
-        <v>17.55</v>
+        <v>22.16</v>
       </c>
       <c r="E29" t="n">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="F29" t="n">
-        <v>11.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>189</v>
+        <v>747</v>
       </c>
       <c r="H29" t="n">
-        <v>67.54000000000001</v>
+        <v>44.85</v>
       </c>
       <c r="I29" t="n">
-        <v>70.20999999999999</v>
+        <v>47.21</v>
       </c>
       <c r="J29" t="n">
-        <v>64.44</v>
+        <v>41.93</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>6152</v>
+        <v>6220</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.55</v>
+        <v>22.58</v>
       </c>
       <c r="C30" t="n">
-        <v>17.81</v>
+        <v>23.47</v>
       </c>
       <c r="D30" t="n">
-        <v>17.2</v>
+        <v>21.83</v>
       </c>
       <c r="E30" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="F30" t="n">
-        <v>10.9</v>
+        <v>9.6</v>
       </c>
       <c r="G30" t="n">
-        <v>95</v>
+        <v>815</v>
       </c>
       <c r="H30" t="n">
-        <v>68.43000000000001</v>
+        <v>45.81</v>
       </c>
       <c r="I30" t="n">
-        <v>69.95</v>
+        <v>48.66</v>
       </c>
       <c r="J30" t="n">
-        <v>65.48</v>
+        <v>43.93</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="N30" t="n">
-        <v>6132</v>
+        <v>6220</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16.64</v>
+        <v>21.31</v>
       </c>
       <c r="C31" t="n">
-        <v>17.06</v>
+        <v>22.4</v>
       </c>
       <c r="D31" t="n">
-        <v>16.2</v>
+        <v>20.2</v>
       </c>
       <c r="E31" t="n">
-        <v>11.5</v>
+        <v>10.4</v>
       </c>
       <c r="F31" t="n">
-        <v>11.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>44</v>
+        <v>689</v>
       </c>
       <c r="H31" t="n">
-        <v>72.79000000000001</v>
+        <v>50.33</v>
       </c>
       <c r="I31" t="n">
-        <v>77.45</v>
+        <v>56.08</v>
       </c>
       <c r="J31" t="n">
-        <v>70.3</v>
+        <v>47.33</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="N31" t="n">
-        <v>6132</v>
+        <v>6190</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>15.62</v>
+        <v>18.91</v>
       </c>
       <c r="C32" t="n">
-        <v>16.07</v>
+        <v>19.91</v>
       </c>
       <c r="D32" t="n">
-        <v>15.35</v>
+        <v>18.4</v>
       </c>
       <c r="E32" t="n">
-        <v>12.9</v>
+        <v>10.9</v>
       </c>
       <c r="F32" t="n">
-        <v>12.4</v>
+        <v>10.6</v>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="H32" t="n">
-        <v>85.33</v>
+        <v>60.58</v>
       </c>
       <c r="I32" t="n">
-        <v>89.23</v>
+        <v>63.06</v>
       </c>
       <c r="J32" t="n">
-        <v>79.03</v>
+        <v>55.94</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1955,92 +1955,92 @@
         <v>0.4</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N32" t="n">
-        <v>6122</v>
+        <v>6162</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15.25</v>
+        <v>17.94</v>
       </c>
       <c r="C33" t="n">
-        <v>15.35</v>
+        <v>18.46</v>
       </c>
       <c r="D33" t="n">
-        <v>15.06</v>
+        <v>17.55</v>
       </c>
       <c r="E33" t="n">
-        <v>13.3</v>
+        <v>11.6</v>
       </c>
       <c r="F33" t="n">
-        <v>13.2</v>
+        <v>11.2</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H33" t="n">
-        <v>89.16</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>91.05</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>87.77</v>
+        <v>64.44</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>6122</v>
+        <v>6152</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15.2</v>
+        <v>17.55</v>
       </c>
       <c r="C34" t="n">
-        <v>15.32</v>
+        <v>17.81</v>
       </c>
       <c r="D34" t="n">
-        <v>15.08</v>
+        <v>17.2</v>
       </c>
       <c r="E34" t="n">
-        <v>13.1</v>
+        <v>11.5</v>
       </c>
       <c r="F34" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H34" t="n">
-        <v>88.42</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>89.37</v>
+        <v>69.95</v>
       </c>
       <c r="J34" t="n">
-        <v>87.13</v>
+        <v>65.48</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2049,101 +2049,101 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N34" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15.53</v>
+        <v>16.64</v>
       </c>
       <c r="C35" t="n">
-        <v>15.66</v>
+        <v>17.06</v>
       </c>
       <c r="D35" t="n">
-        <v>15.45</v>
+        <v>16.2</v>
       </c>
       <c r="E35" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="F35" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H35" t="n">
-        <v>85.40000000000001</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>86.58</v>
+        <v>77.45</v>
       </c>
       <c r="J35" t="n">
-        <v>83.42</v>
+        <v>70.3</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N35" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.66</v>
+        <v>15.62</v>
       </c>
       <c r="C36" t="n">
-        <v>15.73</v>
+        <v>16.07</v>
       </c>
       <c r="D36" t="n">
-        <v>15.62</v>
+        <v>15.35</v>
       </c>
       <c r="E36" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="F36" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H36" t="n">
-        <v>82.52</v>
+        <v>85.33</v>
       </c>
       <c r="I36" t="n">
-        <v>82.76000000000001</v>
+        <v>89.23</v>
       </c>
       <c r="J36" t="n">
-        <v>82.33</v>
+        <v>79.03</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>6122</v>
@@ -2153,44 +2153,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15.72</v>
+        <v>15.25</v>
       </c>
       <c r="C37" t="n">
-        <v>15.77</v>
+        <v>15.35</v>
       </c>
       <c r="D37" t="n">
-        <v>15.65</v>
+        <v>15.06</v>
       </c>
       <c r="E37" t="n">
-        <v>12.4</v>
+        <v>13.3</v>
       </c>
       <c r="F37" t="n">
-        <v>12.3</v>
+        <v>13.2</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>81.17</v>
+        <v>89.16</v>
       </c>
       <c r="I37" t="n">
-        <v>82.40000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="J37" t="n">
-        <v>80.16</v>
+        <v>87.77</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>6122</v>
@@ -2200,44 +2200,44 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.09</v>
+        <v>15.2</v>
       </c>
       <c r="C38" t="n">
-        <v>16.59</v>
+        <v>15.32</v>
       </c>
       <c r="D38" t="n">
-        <v>15.76</v>
+        <v>15.08</v>
       </c>
       <c r="E38" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="F38" t="n">
-        <v>11.4</v>
+        <v>13.1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>76.7</v>
+        <v>88.42</v>
       </c>
       <c r="I38" t="n">
-        <v>80.06999999999999</v>
+        <v>89.37</v>
       </c>
       <c r="J38" t="n">
-        <v>72.89</v>
+        <v>87.13</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>6122</v>
@@ -2247,93 +2247,91 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.2</v>
+        <v>15.53</v>
       </c>
       <c r="C39" t="n">
-        <v>16.53</v>
+        <v>15.66</v>
       </c>
       <c r="D39" t="n">
-        <v>15.84</v>
+        <v>15.45</v>
       </c>
       <c r="E39" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="F39" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>77.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>80.54000000000001</v>
+        <v>86.58</v>
       </c>
       <c r="J39" t="n">
-        <v>73.31999999999999</v>
+        <v>83.42</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>6122</v>
       </c>
-      <c r="O39" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.03</v>
+        <v>15.66</v>
       </c>
       <c r="C40" t="n">
-        <v>16.12</v>
+        <v>15.73</v>
       </c>
       <c r="D40" t="n">
-        <v>15.93</v>
+        <v>15.62</v>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="F40" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>77.56</v>
+        <v>82.52</v>
       </c>
       <c r="I40" t="n">
-        <v>79.16</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>76.79000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="N40" t="n">
         <v>6122</v>
@@ -2343,44 +2341,44 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.79</v>
+        <v>15.72</v>
       </c>
       <c r="C41" t="n">
-        <v>15.92</v>
+        <v>15.77</v>
       </c>
       <c r="D41" t="n">
-        <v>15.7</v>
+        <v>15.65</v>
       </c>
       <c r="E41" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="F41" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>78.34999999999999</v>
+        <v>81.17</v>
       </c>
       <c r="I41" t="n">
-        <v>78.65000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>77.79000000000001</v>
+        <v>80.16</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M41" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N41" t="n">
         <v>6122</v>
@@ -2390,41 +2388,41 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.9</v>
+        <v>16.09</v>
       </c>
       <c r="C42" t="n">
-        <v>16.37</v>
+        <v>16.59</v>
       </c>
       <c r="D42" t="n">
-        <v>15.67</v>
+        <v>15.76</v>
       </c>
       <c r="E42" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="F42" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>76.45999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="I42" t="n">
-        <v>78.44</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>72.33</v>
+        <v>72.89</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="M42" t="n">
         <v>1.4</v>
@@ -2437,176 +2435,178 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16.37</v>
+        <v>16.2</v>
       </c>
       <c r="C43" t="n">
-        <v>16.48</v>
+        <v>16.53</v>
       </c>
       <c r="D43" t="n">
-        <v>16.29</v>
+        <v>15.84</v>
       </c>
       <c r="E43" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F43" t="n">
         <v>11.6</v>
       </c>
-      <c r="F43" t="n">
-        <v>11.3</v>
-      </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>74.02</v>
+        <v>77.2</v>
       </c>
       <c r="I43" t="n">
-        <v>74.88</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>72.13</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M43" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="N43" t="n">
-        <v>6132</v>
-      </c>
-      <c r="O43" t="inlineStr"/>
+        <v>6122</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.84</v>
+        <v>16.03</v>
       </c>
       <c r="C44" t="n">
-        <v>17.08</v>
+        <v>16.12</v>
       </c>
       <c r="D44" t="n">
-        <v>16.57</v>
+        <v>15.93</v>
       </c>
       <c r="E44" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="F44" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>70.64</v>
+        <v>77.56</v>
       </c>
       <c r="I44" t="n">
-        <v>72.89</v>
+        <v>79.16</v>
       </c>
       <c r="J44" t="n">
-        <v>68.62</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M44" t="n">
         <v>0.2</v>
       </c>
       <c r="N44" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.26</v>
+        <v>15.79</v>
       </c>
       <c r="C45" t="n">
-        <v>17.41</v>
+        <v>15.92</v>
       </c>
       <c r="D45" t="n">
-        <v>17.13</v>
+        <v>15.7</v>
       </c>
       <c r="E45" t="n">
-        <v>10.7</v>
+        <v>11.9</v>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="G45" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>65.97</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>68.3</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>62.44</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M45" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N45" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.57</v>
+        <v>15.9</v>
       </c>
       <c r="C46" t="n">
-        <v>18.11</v>
+        <v>16.37</v>
       </c>
       <c r="D46" t="n">
-        <v>17.4</v>
+        <v>15.67</v>
       </c>
       <c r="E46" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="F46" t="n">
-        <v>9.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="G46" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>63.38</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>64.3</v>
+        <v>78.44</v>
       </c>
       <c r="J46" t="n">
-        <v>61.77</v>
+        <v>72.33</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2615,168 +2615,168 @@
         <v>1.2</v>
       </c>
       <c r="M46" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N46" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>18</v>
+        <v>16.37</v>
       </c>
       <c r="C47" t="n">
-        <v>18.2</v>
+        <v>16.48</v>
       </c>
       <c r="D47" t="n">
-        <v>17.79</v>
+        <v>16.29</v>
       </c>
       <c r="E47" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="F47" t="n">
-        <v>10.5</v>
+        <v>11.3</v>
       </c>
       <c r="G47" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>62.96</v>
+        <v>74.02</v>
       </c>
       <c r="I47" t="n">
-        <v>64.08</v>
+        <v>74.88</v>
       </c>
       <c r="J47" t="n">
-        <v>61.81</v>
+        <v>72.13</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="N47" t="n">
-        <v>6162</v>
+        <v>6132</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18.15</v>
+        <v>16.84</v>
       </c>
       <c r="C48" t="n">
-        <v>18.5</v>
+        <v>17.08</v>
       </c>
       <c r="D48" t="n">
-        <v>17.92</v>
+        <v>16.57</v>
       </c>
       <c r="E48" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="G48" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>60.86</v>
+        <v>70.64</v>
       </c>
       <c r="I48" t="n">
-        <v>62.23</v>
+        <v>72.89</v>
       </c>
       <c r="J48" t="n">
-        <v>59.51</v>
+        <v>68.62</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N48" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.71</v>
+        <v>17.26</v>
       </c>
       <c r="C49" t="n">
-        <v>18.05</v>
+        <v>17.41</v>
       </c>
       <c r="D49" t="n">
-        <v>17.31</v>
+        <v>17.13</v>
       </c>
       <c r="E49" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="F49" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="G49" t="n">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="H49" t="n">
-        <v>61.59</v>
+        <v>65.97</v>
       </c>
       <c r="I49" t="n">
-        <v>63.45</v>
+        <v>68.3</v>
       </c>
       <c r="J49" t="n">
-        <v>59.82</v>
+        <v>62.44</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N49" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>16.72</v>
+        <v>17.57</v>
       </c>
       <c r="C50" t="n">
-        <v>17.47</v>
+        <v>18.11</v>
       </c>
       <c r="D50" t="n">
-        <v>16.08</v>
+        <v>17.4</v>
       </c>
       <c r="E50" t="n">
         <v>10.4</v>
@@ -2785,28 +2785,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>260</v>
+        <v>55</v>
       </c>
       <c r="H50" t="n">
-        <v>67.33</v>
+        <v>63.38</v>
       </c>
       <c r="I50" t="n">
-        <v>70.81999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="J50" t="n">
-        <v>63.98</v>
+        <v>61.77</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="M50" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="N50" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O50" t="n">
         <v>1.6</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,232 +508,232 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 17:00:00</t>
+          <t>2026-10-20 20:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.24</v>
+        <v>23.79</v>
       </c>
       <c r="C2" t="n">
-        <v>26.34</v>
+        <v>23.82</v>
       </c>
       <c r="D2" t="n">
-        <v>26.14</v>
+        <v>23.78</v>
       </c>
       <c r="E2" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="F2" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="G2" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>43.39</v>
+        <v>51.01</v>
       </c>
       <c r="I2" t="n">
-        <v>43.49</v>
+        <v>51.15</v>
       </c>
       <c r="J2" t="n">
-        <v>43.23</v>
+        <v>50.87</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="N2" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 16:00:00</t>
+          <t>2026-10-20 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.66</v>
+        <v>24.27</v>
       </c>
       <c r="C3" t="n">
-        <v>26.95</v>
+        <v>24.74</v>
       </c>
       <c r="D3" t="n">
-        <v>26.15</v>
+        <v>23.84</v>
       </c>
       <c r="E3" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="F3" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="G3" t="n">
-        <v>229</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>42.04</v>
+        <v>49.32</v>
       </c>
       <c r="I3" t="n">
-        <v>43.28</v>
+        <v>50.77</v>
       </c>
       <c r="J3" t="n">
-        <v>41.15</v>
+        <v>47.94</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="N3" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 15:00:00</t>
+          <t>2026-10-20 18:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.13</v>
+        <v>25.12</v>
       </c>
       <c r="C4" t="n">
-        <v>27.72</v>
+        <v>25.39</v>
       </c>
       <c r="D4" t="n">
-        <v>26.66</v>
+        <v>24.84</v>
       </c>
       <c r="E4" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="F4" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="G4" t="n">
-        <v>368</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
-        <v>40.38</v>
+        <v>46.99</v>
       </c>
       <c r="I4" t="n">
-        <v>41.51</v>
+        <v>47.92</v>
       </c>
       <c r="J4" t="n">
-        <v>39.08</v>
+        <v>45.97</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="N4" t="n">
-        <v>6180</v>
+        <v>6152</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 14:00:00</t>
+          <t>2026-10-20 17:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.77</v>
+        <v>25.86</v>
       </c>
       <c r="C5" t="n">
-        <v>27.91</v>
+        <v>26.34</v>
       </c>
       <c r="D5" t="n">
-        <v>25.49</v>
+        <v>25.5</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="F5" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
       <c r="G5" t="n">
-        <v>508</v>
+        <v>91</v>
       </c>
       <c r="H5" t="n">
-        <v>41.64</v>
+        <v>44.61</v>
       </c>
       <c r="I5" t="n">
-        <v>44.08</v>
+        <v>45.71</v>
       </c>
       <c r="J5" t="n">
-        <v>39.72</v>
+        <v>43.23</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20 13:00:00</t>
+          <t>2026-10-20 16:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.07</v>
+        <v>26.66</v>
       </c>
       <c r="C6" t="n">
-        <v>25.85</v>
+        <v>26.95</v>
       </c>
       <c r="D6" t="n">
-        <v>24.61</v>
+        <v>26.15</v>
       </c>
       <c r="E6" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="F6" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="H6" t="n">
-        <v>44.5</v>
+        <v>42.04</v>
       </c>
       <c r="I6" t="n">
-        <v>45.61</v>
+        <v>43.28</v>
       </c>
       <c r="J6" t="n">
-        <v>43.09</v>
+        <v>41.15</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N6" t="n">
         <v>6170</v>
@@ -743,317 +743,317 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20 12:00:00</t>
+          <t>2026-10-20 15:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.81</v>
+        <v>27.13</v>
       </c>
       <c r="C7" t="n">
-        <v>25.08</v>
+        <v>27.72</v>
       </c>
       <c r="D7" t="n">
-        <v>24.53</v>
+        <v>26.66</v>
       </c>
       <c r="E7" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="F7" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="G7" t="n">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="H7" t="n">
-        <v>43.89</v>
+        <v>40.38</v>
       </c>
       <c r="I7" t="n">
-        <v>44.75</v>
+        <v>41.51</v>
       </c>
       <c r="J7" t="n">
-        <v>43.04</v>
+        <v>39.08</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="N7" t="n">
-        <v>6162</v>
+        <v>6180</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00:00</t>
+          <t>2026-10-20 14:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.48</v>
+        <v>26.77</v>
       </c>
       <c r="C8" t="n">
-        <v>24.58</v>
+        <v>27.91</v>
       </c>
       <c r="D8" t="n">
-        <v>22.73</v>
+        <v>25.49</v>
       </c>
       <c r="E8" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>12.1</v>
       </c>
       <c r="G8" t="n">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="H8" t="n">
-        <v>47.14</v>
+        <v>41.64</v>
       </c>
       <c r="I8" t="n">
-        <v>49.9</v>
+        <v>44.08</v>
       </c>
       <c r="J8" t="n">
-        <v>43.67</v>
+        <v>39.72</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:00:00</t>
+          <t>2026-10-20 13:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.96</v>
+        <v>25.07</v>
       </c>
       <c r="C9" t="n">
-        <v>22.96</v>
+        <v>25.85</v>
       </c>
       <c r="D9" t="n">
-        <v>21.26</v>
+        <v>24.61</v>
       </c>
       <c r="E9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F9" t="n">
         <v>11.5</v>
       </c>
-      <c r="F9" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G9" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H9" t="n">
-        <v>52.22</v>
+        <v>44.5</v>
       </c>
       <c r="I9" t="n">
-        <v>54.36</v>
+        <v>45.61</v>
       </c>
       <c r="J9" t="n">
-        <v>49</v>
+        <v>43.09</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20 09:00:00</t>
+          <t>2026-10-20 12:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20.32</v>
+        <v>24.81</v>
       </c>
       <c r="C10" t="n">
-        <v>21.66</v>
+        <v>25.08</v>
       </c>
       <c r="D10" t="n">
-        <v>19.17</v>
+        <v>24.53</v>
       </c>
       <c r="E10" t="n">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="F10" t="n">
-        <v>11.9</v>
+        <v>11.2</v>
       </c>
       <c r="G10" t="n">
-        <v>289</v>
+        <v>373</v>
       </c>
       <c r="H10" t="n">
-        <v>60.55</v>
+        <v>43.89</v>
       </c>
       <c r="I10" t="n">
-        <v>64.51000000000001</v>
+        <v>44.75</v>
       </c>
       <c r="J10" t="n">
-        <v>55.76</v>
+        <v>43.04</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20 08:00:00</t>
+          <t>2026-10-20 11:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18.15</v>
+        <v>23.48</v>
       </c>
       <c r="C11" t="n">
-        <v>19.16</v>
+        <v>24.58</v>
       </c>
       <c r="D11" t="n">
-        <v>17.45</v>
+        <v>22.73</v>
       </c>
       <c r="E11" t="n">
-        <v>12.6</v>
+        <v>11.3</v>
       </c>
       <c r="F11" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>111</v>
+        <v>519</v>
       </c>
       <c r="H11" t="n">
-        <v>70.59</v>
+        <v>47.14</v>
       </c>
       <c r="I11" t="n">
-        <v>75.61</v>
+        <v>49.9</v>
       </c>
       <c r="J11" t="n">
-        <v>65.56999999999999</v>
+        <v>43.67</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>6122</v>
+        <v>6162</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20 07:00:00</t>
+          <t>2026-10-20 10:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16.92</v>
+        <v>21.96</v>
       </c>
       <c r="C12" t="n">
-        <v>17.33</v>
+        <v>22.96</v>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>21.26</v>
       </c>
       <c r="E12" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="F12" t="n">
-        <v>12.1</v>
+        <v>11.2</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>298</v>
       </c>
       <c r="H12" t="n">
-        <v>74.87</v>
+        <v>52.22</v>
       </c>
       <c r="I12" t="n">
-        <v>75.66</v>
+        <v>54.36</v>
       </c>
       <c r="J12" t="n">
-        <v>74.08</v>
+        <v>49</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>6092</v>
+        <v>6152</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00:00</t>
+          <t>2026-10-20 09:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.75</v>
+        <v>20.32</v>
       </c>
       <c r="C13" t="n">
-        <v>16.84</v>
+        <v>21.66</v>
       </c>
       <c r="D13" t="n">
-        <v>16.64</v>
+        <v>19.17</v>
       </c>
       <c r="E13" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F13" t="n">
         <v>11.9</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="H13" t="n">
-        <v>74.86</v>
+        <v>60.55</v>
       </c>
       <c r="I13" t="n">
-        <v>75.98</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>73.98999999999999</v>
+        <v>55.76</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1062,45 +1062,45 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N13" t="n">
-        <v>6102</v>
+        <v>6142</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20 05:00:00</t>
+          <t>2026-10-20 08:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.83</v>
+        <v>18.15</v>
       </c>
       <c r="C14" t="n">
-        <v>17.01</v>
+        <v>19.16</v>
       </c>
       <c r="D14" t="n">
-        <v>16.66</v>
+        <v>17.45</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9</v>
+        <v>12.6</v>
       </c>
       <c r="F14" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="H14" t="n">
-        <v>73.56999999999999</v>
+        <v>70.59</v>
       </c>
       <c r="I14" t="n">
-        <v>75.19</v>
+        <v>75.61</v>
       </c>
       <c r="J14" t="n">
-        <v>72.06</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1109,45 +1109,45 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N14" t="n">
-        <v>6082</v>
+        <v>6122</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20 04:00:00</t>
+          <t>2026-10-20 07:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.74</v>
+        <v>16.92</v>
       </c>
       <c r="C15" t="n">
-        <v>16.99</v>
+        <v>17.33</v>
       </c>
       <c r="D15" t="n">
-        <v>16.45</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F15" t="n">
         <v>12.1</v>
       </c>
-      <c r="F15" t="n">
-        <v>11.8</v>
-      </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>74.84</v>
+        <v>74.87</v>
       </c>
       <c r="I15" t="n">
-        <v>77.06999999999999</v>
+        <v>75.66</v>
       </c>
       <c r="J15" t="n">
-        <v>72.64</v>
+        <v>74.08</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1159,42 +1159,42 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6112</v>
+        <v>6092</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20 03:00:00</t>
+          <t>2026-10-20 06:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.86</v>
+        <v>16.75</v>
       </c>
       <c r="C16" t="n">
-        <v>17.22</v>
+        <v>16.84</v>
       </c>
       <c r="D16" t="n">
-        <v>16.71</v>
+        <v>16.64</v>
       </c>
       <c r="E16" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>75.81999999999999</v>
+        <v>74.86</v>
       </c>
       <c r="I16" t="n">
-        <v>77.26000000000001</v>
+        <v>75.98</v>
       </c>
       <c r="J16" t="n">
-        <v>74.54000000000001</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1206,42 +1206,42 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>6112</v>
+        <v>6102</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00:00</t>
+          <t>2026-10-20 05:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.59</v>
+        <v>16.83</v>
       </c>
       <c r="C17" t="n">
-        <v>17.8</v>
+        <v>17.01</v>
       </c>
       <c r="D17" t="n">
-        <v>17.29</v>
+        <v>16.66</v>
       </c>
       <c r="E17" t="n">
-        <v>12.7</v>
+        <v>11.9</v>
       </c>
       <c r="F17" t="n">
-        <v>12.5</v>
+        <v>11.7</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>73.83</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>74.95</v>
+        <v>75.19</v>
       </c>
       <c r="J17" t="n">
-        <v>72.36</v>
+        <v>72.06</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1253,42 +1253,42 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6122</v>
+        <v>6082</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20 01:00:00</t>
+          <t>2026-10-20 04:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18.24</v>
+        <v>16.74</v>
       </c>
       <c r="C18" t="n">
-        <v>18.59</v>
+        <v>16.99</v>
       </c>
       <c r="D18" t="n">
-        <v>17.84</v>
+        <v>16.45</v>
       </c>
       <c r="E18" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F18" t="n">
         <v>11.8</v>
       </c>
-      <c r="F18" t="n">
-        <v>11.3</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>66.76000000000001</v>
+        <v>74.84</v>
       </c>
       <c r="I18" t="n">
-        <v>71.14</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>63.93</v>
+        <v>72.64</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1300,42 +1300,42 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6092</v>
+        <v>6112</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20 00:00:00</t>
+          <t>2026-10-20 03:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18.68</v>
+        <v>16.86</v>
       </c>
       <c r="C19" t="n">
-        <v>18.93</v>
+        <v>17.22</v>
       </c>
       <c r="D19" t="n">
-        <v>18.52</v>
+        <v>16.71</v>
       </c>
       <c r="E19" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="F19" t="n">
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>64.40000000000001</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>65.87</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>61.94</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1347,42 +1347,42 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6122</v>
+        <v>6112</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-19 23:00:00</t>
+          <t>2026-10-20 02:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.43</v>
+        <v>17.59</v>
       </c>
       <c r="C20" t="n">
-        <v>19.64</v>
+        <v>17.8</v>
       </c>
       <c r="D20" t="n">
-        <v>19.01</v>
+        <v>17.29</v>
       </c>
       <c r="E20" t="n">
-        <v>11.3</v>
+        <v>12.7</v>
       </c>
       <c r="F20" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>60.1</v>
+        <v>73.83</v>
       </c>
       <c r="I20" t="n">
-        <v>60.96</v>
+        <v>74.95</v>
       </c>
       <c r="J20" t="n">
-        <v>59.25</v>
+        <v>72.36</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1394,747 +1394,747 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-19 22:00:00</t>
+          <t>2026-10-20 01:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.1</v>
+        <v>18.24</v>
       </c>
       <c r="C21" t="n">
-        <v>20.3</v>
+        <v>18.59</v>
       </c>
       <c r="D21" t="n">
-        <v>19.77</v>
+        <v>17.84</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="F21" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>56.64</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>58.8</v>
+        <v>71.14</v>
       </c>
       <c r="J21" t="n">
-        <v>55.68</v>
+        <v>63.93</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6112</v>
+        <v>6092</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-19 21:00:00</t>
+          <t>2026-10-20 00:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>18.68</v>
       </c>
       <c r="C22" t="n">
-        <v>20.17</v>
+        <v>18.93</v>
       </c>
       <c r="D22" t="n">
-        <v>19.94</v>
+        <v>18.52</v>
       </c>
       <c r="E22" t="n">
-        <v>10.6</v>
+        <v>11.7</v>
       </c>
       <c r="F22" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>55.69</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>55.96</v>
+        <v>65.87</v>
       </c>
       <c r="J22" t="n">
-        <v>55.41</v>
+        <v>61.94</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-19 20:00:00</t>
+          <t>2026-10-19 23:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.56</v>
+        <v>19.43</v>
       </c>
       <c r="C23" t="n">
-        <v>19.96</v>
+        <v>19.64</v>
       </c>
       <c r="D23" t="n">
-        <v>19.34</v>
+        <v>19.01</v>
       </c>
       <c r="E23" t="n">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="F23" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>56.91</v>
+        <v>60.1</v>
       </c>
       <c r="I23" t="n">
-        <v>57.67</v>
+        <v>60.96</v>
       </c>
       <c r="J23" t="n">
-        <v>55.82</v>
+        <v>59.25</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-19 19:00:00</t>
+          <t>2026-10-19 22:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="C24" t="n">
-        <v>19.92</v>
+        <v>20.3</v>
       </c>
       <c r="D24" t="n">
-        <v>19.62</v>
+        <v>19.77</v>
       </c>
       <c r="E24" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>55.22</v>
+        <v>56.64</v>
       </c>
       <c r="I24" t="n">
-        <v>56.29</v>
+        <v>58.8</v>
       </c>
       <c r="J24" t="n">
-        <v>54.46</v>
+        <v>55.68</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="N24" t="n">
-        <v>6152</v>
+        <v>6112</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-19 21:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.91</v>
+        <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>19.98</v>
+        <v>20.17</v>
       </c>
       <c r="D25" t="n">
-        <v>19.83</v>
+        <v>19.94</v>
       </c>
       <c r="E25" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="F25" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="G25" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>54.74</v>
+        <v>55.69</v>
       </c>
       <c r="I25" t="n">
-        <v>54.92</v>
+        <v>55.96</v>
       </c>
       <c r="J25" t="n">
-        <v>54.61</v>
+        <v>55.41</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="N25" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-19 20:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20.31</v>
+        <v>19.56</v>
       </c>
       <c r="C26" t="n">
-        <v>20.99</v>
+        <v>19.96</v>
       </c>
       <c r="D26" t="n">
-        <v>19.97</v>
+        <v>19.34</v>
       </c>
       <c r="E26" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="F26" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="G26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>53.29</v>
+        <v>56.91</v>
       </c>
       <c r="I26" t="n">
-        <v>54.84</v>
+        <v>57.67</v>
       </c>
       <c r="J26" t="n">
-        <v>51.22</v>
+        <v>55.82</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N26" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.38</v>
+        <v>19.8</v>
       </c>
       <c r="C27" t="n">
-        <v>21.67</v>
+        <v>19.92</v>
       </c>
       <c r="D27" t="n">
-        <v>20.91</v>
+        <v>19.62</v>
       </c>
       <c r="E27" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F27" t="n">
         <v>10.2</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>10</v>
       </c>
-      <c r="G27" t="n">
-        <v>213</v>
-      </c>
       <c r="H27" t="n">
-        <v>49.67</v>
+        <v>55.22</v>
       </c>
       <c r="I27" t="n">
-        <v>50.93</v>
+        <v>56.29</v>
       </c>
       <c r="J27" t="n">
-        <v>48.59</v>
+        <v>54.46</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="N27" t="n">
-        <v>6190</v>
+        <v>6152</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21.78</v>
+        <v>19.91</v>
       </c>
       <c r="C28" t="n">
-        <v>22.31</v>
+        <v>19.98</v>
       </c>
       <c r="D28" t="n">
-        <v>21.39</v>
+        <v>19.83</v>
       </c>
       <c r="E28" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="F28" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="G28" t="n">
-        <v>323</v>
+        <v>17</v>
       </c>
       <c r="H28" t="n">
-        <v>48.06</v>
+        <v>54.74</v>
       </c>
       <c r="I28" t="n">
-        <v>48.87</v>
+        <v>54.92</v>
       </c>
       <c r="J28" t="n">
-        <v>46.24</v>
+        <v>54.61</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>6210</v>
+        <v>6162</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22.97</v>
+        <v>20.31</v>
       </c>
       <c r="C29" t="n">
-        <v>24.27</v>
+        <v>20.99</v>
       </c>
       <c r="D29" t="n">
-        <v>22.16</v>
+        <v>19.97</v>
       </c>
       <c r="E29" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F29" t="n">
         <v>10.1</v>
       </c>
-      <c r="F29" t="n">
-        <v>9.699999999999999</v>
-      </c>
       <c r="G29" t="n">
-        <v>747</v>
+        <v>40</v>
       </c>
       <c r="H29" t="n">
-        <v>44.85</v>
+        <v>53.29</v>
       </c>
       <c r="I29" t="n">
-        <v>47.21</v>
+        <v>54.84</v>
       </c>
       <c r="J29" t="n">
-        <v>41.93</v>
+        <v>51.22</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-19 13:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.58</v>
+        <v>21.38</v>
       </c>
       <c r="C30" t="n">
-        <v>23.47</v>
+        <v>21.67</v>
       </c>
       <c r="D30" t="n">
-        <v>21.83</v>
+        <v>20.91</v>
       </c>
       <c r="E30" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F30" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>815</v>
+        <v>213</v>
       </c>
       <c r="H30" t="n">
-        <v>45.81</v>
+        <v>49.67</v>
       </c>
       <c r="I30" t="n">
-        <v>48.66</v>
+        <v>50.93</v>
       </c>
       <c r="J30" t="n">
-        <v>43.93</v>
+        <v>48.59</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>6220</v>
+        <v>6190</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-19 12:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21.31</v>
+        <v>21.78</v>
       </c>
       <c r="C31" t="n">
-        <v>22.4</v>
+        <v>22.31</v>
       </c>
       <c r="D31" t="n">
-        <v>20.2</v>
+        <v>21.39</v>
       </c>
       <c r="E31" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="F31" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>689</v>
+        <v>323</v>
       </c>
       <c r="H31" t="n">
-        <v>50.33</v>
+        <v>48.06</v>
       </c>
       <c r="I31" t="n">
-        <v>56.08</v>
+        <v>48.87</v>
       </c>
       <c r="J31" t="n">
-        <v>47.33</v>
+        <v>46.24</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="M31" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>6190</v>
+        <v>6210</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-19 11:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18.91</v>
+        <v>22.97</v>
       </c>
       <c r="C32" t="n">
-        <v>19.91</v>
+        <v>24.27</v>
       </c>
       <c r="D32" t="n">
-        <v>18.4</v>
+        <v>22.16</v>
       </c>
       <c r="E32" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="F32" t="n">
-        <v>10.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>305</v>
+        <v>747</v>
       </c>
       <c r="H32" t="n">
-        <v>60.58</v>
+        <v>44.85</v>
       </c>
       <c r="I32" t="n">
-        <v>63.06</v>
+        <v>47.21</v>
       </c>
       <c r="J32" t="n">
-        <v>55.94</v>
+        <v>41.93</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>6162</v>
+        <v>6220</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.94</v>
+        <v>22.58</v>
       </c>
       <c r="C33" t="n">
-        <v>18.46</v>
+        <v>23.47</v>
       </c>
       <c r="D33" t="n">
-        <v>17.55</v>
+        <v>21.83</v>
       </c>
       <c r="E33" t="n">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="F33" t="n">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
       <c r="G33" t="n">
-        <v>189</v>
+        <v>815</v>
       </c>
       <c r="H33" t="n">
-        <v>67.54000000000001</v>
+        <v>45.81</v>
       </c>
       <c r="I33" t="n">
-        <v>70.20999999999999</v>
+        <v>48.66</v>
       </c>
       <c r="J33" t="n">
-        <v>64.44</v>
+        <v>43.93</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>6152</v>
+        <v>6220</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.55</v>
+        <v>21.31</v>
       </c>
       <c r="C34" t="n">
-        <v>17.81</v>
+        <v>22.4</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>20.2</v>
       </c>
       <c r="E34" t="n">
-        <v>11.5</v>
+        <v>10.4</v>
       </c>
       <c r="F34" t="n">
-        <v>10.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>95</v>
+        <v>689</v>
       </c>
       <c r="H34" t="n">
-        <v>68.43000000000001</v>
+        <v>50.33</v>
       </c>
       <c r="I34" t="n">
-        <v>69.95</v>
+        <v>56.08</v>
       </c>
       <c r="J34" t="n">
-        <v>65.48</v>
+        <v>47.33</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="N34" t="n">
-        <v>6132</v>
+        <v>6190</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16.64</v>
+        <v>18.91</v>
       </c>
       <c r="C35" t="n">
-        <v>17.06</v>
+        <v>19.91</v>
       </c>
       <c r="D35" t="n">
-        <v>16.2</v>
+        <v>18.4</v>
       </c>
       <c r="E35" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="F35" t="n">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
       <c r="G35" t="n">
-        <v>44</v>
+        <v>305</v>
       </c>
       <c r="H35" t="n">
-        <v>72.79000000000001</v>
+        <v>60.58</v>
       </c>
       <c r="I35" t="n">
-        <v>77.45</v>
+        <v>63.06</v>
       </c>
       <c r="J35" t="n">
-        <v>70.3</v>
+        <v>55.94</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="N35" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.62</v>
+        <v>17.94</v>
       </c>
       <c r="C36" t="n">
-        <v>16.07</v>
+        <v>18.46</v>
       </c>
       <c r="D36" t="n">
-        <v>15.35</v>
+        <v>17.55</v>
       </c>
       <c r="E36" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="F36" t="n">
-        <v>12.4</v>
+        <v>11.2</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="H36" t="n">
-        <v>85.33</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>89.23</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>79.03</v>
+        <v>64.44</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2143,45 +2143,45 @@
         <v>0.4</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>6122</v>
+        <v>6152</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15.25</v>
+        <v>17.55</v>
       </c>
       <c r="C37" t="n">
-        <v>15.35</v>
+        <v>17.81</v>
       </c>
       <c r="D37" t="n">
-        <v>15.06</v>
+        <v>17.2</v>
       </c>
       <c r="E37" t="n">
-        <v>13.3</v>
+        <v>11.5</v>
       </c>
       <c r="F37" t="n">
-        <v>13.2</v>
+        <v>10.9</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H37" t="n">
-        <v>89.16</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>91.05</v>
+        <v>69.95</v>
       </c>
       <c r="J37" t="n">
-        <v>87.77</v>
+        <v>65.48</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2190,101 +2190,101 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N37" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>15.2</v>
+        <v>16.64</v>
       </c>
       <c r="C38" t="n">
-        <v>15.32</v>
+        <v>17.06</v>
       </c>
       <c r="D38" t="n">
-        <v>15.08</v>
+        <v>16.2</v>
       </c>
       <c r="E38" t="n">
-        <v>13.1</v>
+        <v>11.5</v>
       </c>
       <c r="F38" t="n">
-        <v>13.1</v>
+        <v>11.4</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H38" t="n">
-        <v>88.42</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>89.37</v>
+        <v>77.45</v>
       </c>
       <c r="J38" t="n">
-        <v>87.13</v>
+        <v>70.3</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N38" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>15.53</v>
+        <v>15.62</v>
       </c>
       <c r="C39" t="n">
-        <v>15.66</v>
+        <v>16.07</v>
       </c>
       <c r="D39" t="n">
-        <v>15.45</v>
+        <v>15.35</v>
       </c>
       <c r="E39" t="n">
         <v>12.9</v>
       </c>
       <c r="F39" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H39" t="n">
-        <v>85.40000000000001</v>
+        <v>85.33</v>
       </c>
       <c r="I39" t="n">
-        <v>86.58</v>
+        <v>89.23</v>
       </c>
       <c r="J39" t="n">
-        <v>83.42</v>
+        <v>79.03</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
         <v>6122</v>
@@ -2294,44 +2294,44 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15.66</v>
+        <v>15.25</v>
       </c>
       <c r="C40" t="n">
-        <v>15.73</v>
+        <v>15.35</v>
       </c>
       <c r="D40" t="n">
-        <v>15.62</v>
+        <v>15.06</v>
       </c>
       <c r="E40" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="F40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>82.52</v>
+        <v>89.16</v>
       </c>
       <c r="I40" t="n">
-        <v>82.76000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="J40" t="n">
-        <v>82.33</v>
+        <v>87.77</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>6122</v>
@@ -2341,44 +2341,44 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.72</v>
+        <v>15.2</v>
       </c>
       <c r="C41" t="n">
-        <v>15.77</v>
+        <v>15.32</v>
       </c>
       <c r="D41" t="n">
-        <v>15.65</v>
+        <v>15.08</v>
       </c>
       <c r="E41" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="F41" t="n">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>81.17</v>
+        <v>88.42</v>
       </c>
       <c r="I41" t="n">
-        <v>82.40000000000001</v>
+        <v>89.37</v>
       </c>
       <c r="J41" t="n">
-        <v>80.16</v>
+        <v>87.13</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>6122</v>
@@ -2388,44 +2388,44 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16.09</v>
+        <v>15.53</v>
       </c>
       <c r="C42" t="n">
-        <v>16.59</v>
+        <v>15.66</v>
       </c>
       <c r="D42" t="n">
-        <v>15.76</v>
+        <v>15.45</v>
       </c>
       <c r="E42" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="F42" t="n">
-        <v>11.4</v>
+        <v>12.7</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>76.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>80.06999999999999</v>
+        <v>86.58</v>
       </c>
       <c r="J42" t="n">
-        <v>72.89</v>
+        <v>83.42</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>6122</v>
@@ -2435,93 +2435,91 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16.2</v>
+        <v>15.66</v>
       </c>
       <c r="C43" t="n">
-        <v>16.53</v>
+        <v>15.73</v>
       </c>
       <c r="D43" t="n">
-        <v>15.84</v>
+        <v>15.62</v>
       </c>
       <c r="E43" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
       <c r="F43" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>77.2</v>
+        <v>82.52</v>
       </c>
       <c r="I43" t="n">
-        <v>80.54000000000001</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>73.31999999999999</v>
+        <v>82.33</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="M43" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N43" t="n">
         <v>6122</v>
       </c>
-      <c r="O43" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.03</v>
+        <v>15.72</v>
       </c>
       <c r="C44" t="n">
-        <v>16.12</v>
+        <v>15.77</v>
       </c>
       <c r="D44" t="n">
-        <v>15.93</v>
+        <v>15.65</v>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="F44" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>77.56</v>
+        <v>81.17</v>
       </c>
       <c r="I44" t="n">
-        <v>79.16</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>76.79000000000001</v>
+        <v>80.16</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="N44" t="n">
         <v>6122</v>
@@ -2531,44 +2529,44 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15.79</v>
+        <v>16.09</v>
       </c>
       <c r="C45" t="n">
-        <v>15.92</v>
+        <v>16.59</v>
       </c>
       <c r="D45" t="n">
-        <v>15.7</v>
+        <v>15.76</v>
       </c>
       <c r="E45" t="n">
         <v>11.9</v>
       </c>
       <c r="F45" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>78.34999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="I45" t="n">
-        <v>78.65000000000001</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>77.79000000000001</v>
+        <v>72.89</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M45" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N45" t="n">
         <v>6122</v>
@@ -2578,235 +2576,237 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15.9</v>
+        <v>16.2</v>
       </c>
       <c r="C46" t="n">
-        <v>16.37</v>
+        <v>16.53</v>
       </c>
       <c r="D46" t="n">
-        <v>15.67</v>
+        <v>15.84</v>
       </c>
       <c r="E46" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F46" t="n">
         <v>11.6</v>
       </c>
-      <c r="F46" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>76.45999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="I46" t="n">
-        <v>78.44</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>72.33</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="M46" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N46" t="n">
         <v>6122</v>
       </c>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.37</v>
+        <v>16.03</v>
       </c>
       <c r="C47" t="n">
-        <v>16.48</v>
+        <v>16.12</v>
       </c>
       <c r="D47" t="n">
-        <v>16.29</v>
+        <v>15.93</v>
       </c>
       <c r="E47" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="F47" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>74.02</v>
+        <v>77.56</v>
       </c>
       <c r="I47" t="n">
-        <v>74.88</v>
+        <v>79.16</v>
       </c>
       <c r="J47" t="n">
-        <v>72.13</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M47" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="N47" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16.84</v>
+        <v>15.79</v>
       </c>
       <c r="C48" t="n">
-        <v>17.08</v>
+        <v>15.92</v>
       </c>
       <c r="D48" t="n">
-        <v>16.57</v>
+        <v>15.7</v>
       </c>
       <c r="E48" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="F48" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>70.64</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>72.89</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>68.62</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="N48" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.26</v>
+        <v>15.9</v>
       </c>
       <c r="C49" t="n">
-        <v>17.41</v>
+        <v>16.37</v>
       </c>
       <c r="D49" t="n">
-        <v>17.13</v>
+        <v>15.67</v>
       </c>
       <c r="E49" t="n">
-        <v>10.7</v>
+        <v>11.6</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="G49" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>65.97</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>68.3</v>
+        <v>78.44</v>
       </c>
       <c r="J49" t="n">
-        <v>62.44</v>
+        <v>72.33</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="M49" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N49" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>17.57</v>
+        <v>16.37</v>
       </c>
       <c r="C50" t="n">
-        <v>18.11</v>
+        <v>16.48</v>
       </c>
       <c r="D50" t="n">
-        <v>17.4</v>
+        <v>16.29</v>
       </c>
       <c r="E50" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="F50" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="G50" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>63.38</v>
+        <v>74.02</v>
       </c>
       <c r="I50" t="n">
-        <v>64.3</v>
+        <v>74.88</v>
       </c>
       <c r="J50" t="n">
-        <v>61.77</v>
+        <v>72.13</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
         <v>1.7</v>
       </c>
       <c r="N50" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O50" t="n">
         <v>1.6</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,44 +508,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 20:00:00</t>
+          <t>2026-10-20 22:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.79</v>
+        <v>21.54</v>
       </c>
       <c r="C2" t="n">
-        <v>23.82</v>
+        <v>21.85</v>
       </c>
       <c r="D2" t="n">
-        <v>23.78</v>
+        <v>21.3</v>
       </c>
       <c r="E2" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="F2" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>51.01</v>
+        <v>59.25</v>
       </c>
       <c r="I2" t="n">
-        <v>51.15</v>
+        <v>59.85</v>
       </c>
       <c r="J2" t="n">
-        <v>50.87</v>
+        <v>58.39</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.3</v>
       </c>
       <c r="N2" t="n">
         <v>6132</v>
@@ -555,440 +555,440 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 19:00:00</t>
+          <t>2026-10-20 21:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.27</v>
+        <v>22.75</v>
       </c>
       <c r="C3" t="n">
-        <v>24.74</v>
+        <v>23.07</v>
       </c>
       <c r="D3" t="n">
-        <v>23.84</v>
+        <v>22.23</v>
       </c>
       <c r="E3" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="F3" t="n">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>49.32</v>
+        <v>55.42</v>
       </c>
       <c r="I3" t="n">
-        <v>50.77</v>
+        <v>57</v>
       </c>
       <c r="J3" t="n">
-        <v>47.94</v>
+        <v>54.24</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="N3" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 18:00:00</t>
+          <t>2026-10-20 20:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.12</v>
+        <v>23.5</v>
       </c>
       <c r="C4" t="n">
-        <v>25.39</v>
+        <v>23.82</v>
       </c>
       <c r="D4" t="n">
-        <v>24.84</v>
+        <v>23.14</v>
       </c>
       <c r="E4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" t="n">
         <v>12.8</v>
       </c>
-      <c r="F4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>46.99</v>
+        <v>52.31</v>
       </c>
       <c r="I4" t="n">
-        <v>47.92</v>
+        <v>54</v>
       </c>
       <c r="J4" t="n">
-        <v>45.97</v>
+        <v>50.87</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="N4" t="n">
-        <v>6152</v>
+        <v>6132</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 17:00:00</t>
+          <t>2026-10-20 19:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.86</v>
+        <v>24.27</v>
       </c>
       <c r="C5" t="n">
-        <v>26.34</v>
+        <v>24.74</v>
       </c>
       <c r="D5" t="n">
-        <v>25.5</v>
+        <v>23.84</v>
       </c>
       <c r="E5" t="n">
         <v>12.7</v>
       </c>
       <c r="F5" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="G5" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>44.61</v>
+        <v>49.32</v>
       </c>
       <c r="I5" t="n">
-        <v>45.71</v>
+        <v>50.77</v>
       </c>
       <c r="J5" t="n">
-        <v>43.23</v>
+        <v>47.94</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="N5" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20 16:00:00</t>
+          <t>2026-10-20 18:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.66</v>
+        <v>25.12</v>
       </c>
       <c r="C6" t="n">
-        <v>26.95</v>
+        <v>25.39</v>
       </c>
       <c r="D6" t="n">
-        <v>26.15</v>
+        <v>24.84</v>
       </c>
       <c r="E6" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="F6" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="G6" t="n">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
-        <v>42.04</v>
+        <v>46.99</v>
       </c>
       <c r="I6" t="n">
-        <v>43.28</v>
+        <v>47.92</v>
       </c>
       <c r="J6" t="n">
-        <v>41.15</v>
+        <v>45.97</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="N6" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20 15:00:00</t>
+          <t>2026-10-20 17:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.13</v>
+        <v>25.86</v>
       </c>
       <c r="C7" t="n">
-        <v>27.72</v>
+        <v>26.34</v>
       </c>
       <c r="D7" t="n">
-        <v>26.66</v>
+        <v>25.5</v>
       </c>
       <c r="E7" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F7" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="G7" t="n">
-        <v>368</v>
+        <v>91</v>
       </c>
       <c r="H7" t="n">
-        <v>40.38</v>
+        <v>44.61</v>
       </c>
       <c r="I7" t="n">
-        <v>41.51</v>
+        <v>45.71</v>
       </c>
       <c r="J7" t="n">
-        <v>39.08</v>
+        <v>43.23</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="N7" t="n">
-        <v>6180</v>
+        <v>6162</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20 14:00:00</t>
+          <t>2026-10-20 16:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.77</v>
+        <v>26.66</v>
       </c>
       <c r="C8" t="n">
-        <v>27.91</v>
+        <v>26.95</v>
       </c>
       <c r="D8" t="n">
-        <v>25.49</v>
+        <v>26.15</v>
       </c>
       <c r="E8" t="n">
         <v>12.4</v>
       </c>
       <c r="F8" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="G8" t="n">
-        <v>508</v>
+        <v>229</v>
       </c>
       <c r="H8" t="n">
-        <v>41.64</v>
+        <v>42.04</v>
       </c>
       <c r="I8" t="n">
-        <v>44.08</v>
+        <v>43.28</v>
       </c>
       <c r="J8" t="n">
-        <v>39.72</v>
+        <v>41.15</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>6190</v>
+        <v>6170</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:00:00</t>
+          <t>2026-10-20 15:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.07</v>
+        <v>27.13</v>
       </c>
       <c r="C9" t="n">
-        <v>25.85</v>
+        <v>27.72</v>
       </c>
       <c r="D9" t="n">
-        <v>24.61</v>
+        <v>26.66</v>
       </c>
       <c r="E9" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F9" t="n">
         <v>11.9</v>
       </c>
-      <c r="F9" t="n">
-        <v>11.5</v>
-      </c>
       <c r="G9" t="n">
-        <v>300</v>
+        <v>368</v>
       </c>
       <c r="H9" t="n">
-        <v>44.5</v>
+        <v>40.38</v>
       </c>
       <c r="I9" t="n">
-        <v>45.61</v>
+        <v>41.51</v>
       </c>
       <c r="J9" t="n">
-        <v>43.09</v>
+        <v>39.08</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="N9" t="n">
-        <v>6170</v>
+        <v>6180</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20 12:00:00</t>
+          <t>2026-10-20 14:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.81</v>
+        <v>26.77</v>
       </c>
       <c r="C10" t="n">
-        <v>25.08</v>
+        <v>27.91</v>
       </c>
       <c r="D10" t="n">
-        <v>24.53</v>
+        <v>25.49</v>
       </c>
       <c r="E10" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="F10" t="n">
-        <v>11.2</v>
+        <v>12.1</v>
       </c>
       <c r="G10" t="n">
-        <v>373</v>
+        <v>508</v>
       </c>
       <c r="H10" t="n">
-        <v>43.89</v>
+        <v>41.64</v>
       </c>
       <c r="I10" t="n">
-        <v>44.75</v>
+        <v>44.08</v>
       </c>
       <c r="J10" t="n">
-        <v>43.04</v>
+        <v>39.72</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>6162</v>
+        <v>6190</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00:00</t>
+          <t>2026-10-20 13:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23.48</v>
+        <v>25.07</v>
       </c>
       <c r="C11" t="n">
-        <v>24.58</v>
+        <v>25.85</v>
       </c>
       <c r="D11" t="n">
-        <v>22.73</v>
+        <v>24.61</v>
       </c>
       <c r="E11" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G11" t="n">
-        <v>519</v>
+        <v>300</v>
       </c>
       <c r="H11" t="n">
-        <v>47.14</v>
+        <v>44.5</v>
       </c>
       <c r="I11" t="n">
-        <v>49.9</v>
+        <v>45.61</v>
       </c>
       <c r="J11" t="n">
-        <v>43.67</v>
+        <v>43.09</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
         <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20 10:00:00</t>
+          <t>2026-10-20 12:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21.96</v>
+        <v>24.81</v>
       </c>
       <c r="C12" t="n">
-        <v>22.96</v>
+        <v>25.08</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26</v>
+        <v>24.53</v>
       </c>
       <c r="E12" t="n">
         <v>11.5</v>
@@ -997,157 +997,157 @@
         <v>11.2</v>
       </c>
       <c r="G12" t="n">
-        <v>298</v>
+        <v>373</v>
       </c>
       <c r="H12" t="n">
-        <v>52.22</v>
+        <v>43.89</v>
       </c>
       <c r="I12" t="n">
-        <v>54.36</v>
+        <v>44.75</v>
       </c>
       <c r="J12" t="n">
-        <v>49</v>
+        <v>43.04</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20 09:00:00</t>
+          <t>2026-10-20 11:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20.32</v>
+        <v>23.48</v>
       </c>
       <c r="C13" t="n">
-        <v>21.66</v>
+        <v>24.58</v>
       </c>
       <c r="D13" t="n">
-        <v>19.17</v>
+        <v>22.73</v>
       </c>
       <c r="E13" t="n">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
       <c r="F13" t="n">
-        <v>11.9</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>289</v>
+        <v>519</v>
       </c>
       <c r="H13" t="n">
-        <v>60.55</v>
+        <v>47.14</v>
       </c>
       <c r="I13" t="n">
-        <v>64.51000000000001</v>
+        <v>49.9</v>
       </c>
       <c r="J13" t="n">
-        <v>55.76</v>
+        <v>43.67</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>6142</v>
+        <v>6162</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20 08:00:00</t>
+          <t>2026-10-20 10:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18.15</v>
+        <v>21.96</v>
       </c>
       <c r="C14" t="n">
-        <v>19.16</v>
+        <v>22.96</v>
       </c>
       <c r="D14" t="n">
-        <v>17.45</v>
+        <v>21.26</v>
       </c>
       <c r="E14" t="n">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="F14" t="n">
-        <v>12.1</v>
+        <v>11.2</v>
       </c>
       <c r="G14" t="n">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="H14" t="n">
-        <v>70.59</v>
+        <v>52.22</v>
       </c>
       <c r="I14" t="n">
-        <v>75.61</v>
+        <v>54.36</v>
       </c>
       <c r="J14" t="n">
-        <v>65.56999999999999</v>
+        <v>49</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>6122</v>
+        <v>6152</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20 07:00:00</t>
+          <t>2026-10-20 09:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.92</v>
+        <v>20.32</v>
       </c>
       <c r="C15" t="n">
-        <v>17.33</v>
+        <v>21.66</v>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>19.17</v>
       </c>
       <c r="E15" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F15" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="G15" t="n">
-        <v>17</v>
+        <v>289</v>
       </c>
       <c r="H15" t="n">
-        <v>74.87</v>
+        <v>60.55</v>
       </c>
       <c r="I15" t="n">
-        <v>75.66</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>74.08</v>
+        <v>55.76</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1156,45 +1156,45 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N15" t="n">
-        <v>6092</v>
+        <v>6142</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00:00</t>
+          <t>2026-10-20 08:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.75</v>
+        <v>18.15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.84</v>
+        <v>19.16</v>
       </c>
       <c r="D16" t="n">
-        <v>16.64</v>
+        <v>17.45</v>
       </c>
       <c r="E16" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F16" t="n">
         <v>12.1</v>
       </c>
-      <c r="F16" t="n">
-        <v>11.9</v>
-      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="H16" t="n">
-        <v>74.86</v>
+        <v>70.59</v>
       </c>
       <c r="I16" t="n">
-        <v>75.98</v>
+        <v>75.61</v>
       </c>
       <c r="J16" t="n">
-        <v>73.98999999999999</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1203,45 +1203,45 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N16" t="n">
-        <v>6102</v>
+        <v>6122</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20 05:00:00</t>
+          <t>2026-10-20 07:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.83</v>
+        <v>16.92</v>
       </c>
       <c r="C17" t="n">
-        <v>17.01</v>
+        <v>17.33</v>
       </c>
       <c r="D17" t="n">
-        <v>16.66</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="F17" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H17" t="n">
-        <v>73.56999999999999</v>
+        <v>74.87</v>
       </c>
       <c r="I17" t="n">
-        <v>75.19</v>
+        <v>75.66</v>
       </c>
       <c r="J17" t="n">
-        <v>72.06</v>
+        <v>74.08</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1253,42 +1253,42 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6082</v>
+        <v>6092</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20 04:00:00</t>
+          <t>2026-10-20 06:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.74</v>
+        <v>16.75</v>
       </c>
       <c r="C18" t="n">
-        <v>16.99</v>
+        <v>16.84</v>
       </c>
       <c r="D18" t="n">
-        <v>16.45</v>
+        <v>16.64</v>
       </c>
       <c r="E18" t="n">
         <v>12.1</v>
       </c>
       <c r="F18" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>74.84</v>
+        <v>74.86</v>
       </c>
       <c r="I18" t="n">
-        <v>77.06999999999999</v>
+        <v>75.98</v>
       </c>
       <c r="J18" t="n">
-        <v>72.64</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1300,42 +1300,42 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6112</v>
+        <v>6102</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20 03:00:00</t>
+          <t>2026-10-20 05:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16.86</v>
+        <v>16.83</v>
       </c>
       <c r="C19" t="n">
-        <v>17.22</v>
+        <v>17.01</v>
       </c>
       <c r="D19" t="n">
-        <v>16.71</v>
+        <v>16.66</v>
       </c>
       <c r="E19" t="n">
-        <v>12.4</v>
+        <v>11.9</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>75.81999999999999</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>77.26000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="J19" t="n">
-        <v>74.54000000000001</v>
+        <v>72.06</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1347,42 +1347,42 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6112</v>
+        <v>6082</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00:00</t>
+          <t>2026-10-20 04:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.59</v>
+        <v>16.74</v>
       </c>
       <c r="C20" t="n">
-        <v>17.8</v>
+        <v>16.99</v>
       </c>
       <c r="D20" t="n">
-        <v>17.29</v>
+        <v>16.45</v>
       </c>
       <c r="E20" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="F20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>73.83</v>
+        <v>74.84</v>
       </c>
       <c r="I20" t="n">
-        <v>74.95</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>72.36</v>
+        <v>72.64</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1394,42 +1394,42 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6122</v>
+        <v>6112</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20 01:00:00</t>
+          <t>2026-10-20 03:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.24</v>
+        <v>16.86</v>
       </c>
       <c r="C21" t="n">
-        <v>18.59</v>
+        <v>17.22</v>
       </c>
       <c r="D21" t="n">
-        <v>17.84</v>
+        <v>16.71</v>
       </c>
       <c r="E21" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="F21" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>66.76000000000001</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>71.14</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>63.93</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1441,42 +1441,42 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6092</v>
+        <v>6112</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20 00:00:00</t>
+          <t>2026-10-20 02:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18.68</v>
+        <v>17.59</v>
       </c>
       <c r="C22" t="n">
-        <v>18.93</v>
+        <v>17.8</v>
       </c>
       <c r="D22" t="n">
-        <v>18.52</v>
+        <v>17.29</v>
       </c>
       <c r="E22" t="n">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
       <c r="F22" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>64.40000000000001</v>
+        <v>73.83</v>
       </c>
       <c r="I22" t="n">
-        <v>65.87</v>
+        <v>74.95</v>
       </c>
       <c r="J22" t="n">
-        <v>61.94</v>
+        <v>72.36</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1495,35 +1495,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-19 23:00:00</t>
+          <t>2026-10-20 01:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.43</v>
+        <v>18.24</v>
       </c>
       <c r="C23" t="n">
-        <v>19.64</v>
+        <v>18.59</v>
       </c>
       <c r="D23" t="n">
-        <v>19.01</v>
+        <v>17.84</v>
       </c>
       <c r="E23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F23" t="n">
         <v>11.3</v>
       </c>
-      <c r="F23" t="n">
-        <v>11.1</v>
-      </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>60.1</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>60.96</v>
+        <v>71.14</v>
       </c>
       <c r="J23" t="n">
-        <v>59.25</v>
+        <v>63.93</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1535,465 +1535,465 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>6132</v>
+        <v>6092</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-19 22:00:00</t>
+          <t>2026-10-20 00:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20.1</v>
+        <v>18.68</v>
       </c>
       <c r="C24" t="n">
-        <v>20.3</v>
+        <v>18.93</v>
       </c>
       <c r="D24" t="n">
-        <v>19.77</v>
+        <v>18.52</v>
       </c>
       <c r="E24" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="F24" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>56.64</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>58.8</v>
+        <v>65.87</v>
       </c>
       <c r="J24" t="n">
-        <v>55.68</v>
+        <v>61.94</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6112</v>
+        <v>6122</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-19 21:00:00</t>
+          <t>2026-10-19 23:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20</v>
+        <v>19.43</v>
       </c>
       <c r="C25" t="n">
-        <v>20.17</v>
+        <v>19.64</v>
       </c>
       <c r="D25" t="n">
-        <v>19.94</v>
+        <v>19.01</v>
       </c>
       <c r="E25" t="n">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="F25" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>55.69</v>
+        <v>60.1</v>
       </c>
       <c r="I25" t="n">
-        <v>55.96</v>
+        <v>60.96</v>
       </c>
       <c r="J25" t="n">
-        <v>55.41</v>
+        <v>59.25</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6142</v>
+        <v>6132</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-19 20:00:00</t>
+          <t>2026-10-19 22:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19.56</v>
+        <v>20.1</v>
       </c>
       <c r="C26" t="n">
-        <v>19.96</v>
+        <v>20.3</v>
       </c>
       <c r="D26" t="n">
-        <v>19.34</v>
+        <v>19.77</v>
       </c>
       <c r="E26" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="F26" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>56.91</v>
+        <v>56.64</v>
       </c>
       <c r="I26" t="n">
-        <v>57.67</v>
+        <v>58.8</v>
       </c>
       <c r="J26" t="n">
-        <v>55.82</v>
+        <v>55.68</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="N26" t="n">
-        <v>6142</v>
+        <v>6112</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19 19:00:00</t>
+          <t>2026-10-19 21:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="C27" t="n">
-        <v>19.92</v>
+        <v>20.17</v>
       </c>
       <c r="D27" t="n">
-        <v>19.62</v>
+        <v>19.94</v>
       </c>
       <c r="E27" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="F27" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>55.22</v>
+        <v>55.69</v>
       </c>
       <c r="I27" t="n">
-        <v>56.29</v>
+        <v>55.96</v>
       </c>
       <c r="J27" t="n">
-        <v>54.46</v>
+        <v>55.41</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="M27" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="N27" t="n">
-        <v>6152</v>
+        <v>6142</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-19 20:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.91</v>
+        <v>19.56</v>
       </c>
       <c r="C28" t="n">
-        <v>19.98</v>
+        <v>19.96</v>
       </c>
       <c r="D28" t="n">
-        <v>19.83</v>
+        <v>19.34</v>
       </c>
       <c r="E28" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F28" t="n">
         <v>10.3</v>
       </c>
-      <c r="F28" t="n">
-        <v>10.2</v>
-      </c>
       <c r="G28" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>54.74</v>
+        <v>56.91</v>
       </c>
       <c r="I28" t="n">
-        <v>54.92</v>
+        <v>57.67</v>
       </c>
       <c r="J28" t="n">
-        <v>54.61</v>
+        <v>55.82</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N28" t="n">
-        <v>6162</v>
+        <v>6142</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>20.31</v>
+        <v>19.8</v>
       </c>
       <c r="C29" t="n">
-        <v>20.99</v>
+        <v>19.92</v>
       </c>
       <c r="D29" t="n">
-        <v>19.97</v>
+        <v>19.62</v>
       </c>
       <c r="E29" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F29" t="n">
         <v>10.2</v>
       </c>
-      <c r="F29" t="n">
-        <v>10.1</v>
-      </c>
       <c r="G29" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H29" t="n">
-        <v>53.29</v>
+        <v>55.22</v>
       </c>
       <c r="I29" t="n">
-        <v>54.84</v>
+        <v>56.29</v>
       </c>
       <c r="J29" t="n">
-        <v>51.22</v>
+        <v>54.46</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="N29" t="n">
-        <v>6170</v>
+        <v>6152</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21.38</v>
+        <v>19.91</v>
       </c>
       <c r="C30" t="n">
-        <v>21.67</v>
+        <v>19.98</v>
       </c>
       <c r="D30" t="n">
-        <v>20.91</v>
+        <v>19.83</v>
       </c>
       <c r="E30" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F30" t="n">
         <v>10.2</v>
       </c>
-      <c r="F30" t="n">
-        <v>10</v>
-      </c>
       <c r="G30" t="n">
-        <v>213</v>
+        <v>17</v>
       </c>
       <c r="H30" t="n">
-        <v>49.67</v>
+        <v>54.74</v>
       </c>
       <c r="I30" t="n">
-        <v>50.93</v>
+        <v>54.92</v>
       </c>
       <c r="J30" t="n">
-        <v>48.59</v>
+        <v>54.61</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21.78</v>
+        <v>20.31</v>
       </c>
       <c r="C31" t="n">
-        <v>22.31</v>
+        <v>20.99</v>
       </c>
       <c r="D31" t="n">
-        <v>21.39</v>
+        <v>19.97</v>
       </c>
       <c r="E31" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F31" t="n">
         <v>10.1</v>
       </c>
-      <c r="F31" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="G31" t="n">
-        <v>323</v>
+        <v>40</v>
       </c>
       <c r="H31" t="n">
-        <v>48.06</v>
+        <v>53.29</v>
       </c>
       <c r="I31" t="n">
-        <v>48.87</v>
+        <v>54.84</v>
       </c>
       <c r="J31" t="n">
-        <v>46.24</v>
+        <v>51.22</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>6210</v>
+        <v>6170</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22.97</v>
+        <v>21.38</v>
       </c>
       <c r="C32" t="n">
-        <v>24.27</v>
+        <v>21.67</v>
       </c>
       <c r="D32" t="n">
-        <v>22.16</v>
+        <v>20.91</v>
       </c>
       <c r="E32" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F32" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>747</v>
+        <v>213</v>
       </c>
       <c r="H32" t="n">
-        <v>44.85</v>
+        <v>49.67</v>
       </c>
       <c r="I32" t="n">
-        <v>47.21</v>
+        <v>50.93</v>
       </c>
       <c r="J32" t="n">
-        <v>41.93</v>
+        <v>48.59</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M32" t="n">
         <v>3</v>
       </c>
-      <c r="M32" t="n">
-        <v>4.3</v>
-      </c>
       <c r="N32" t="n">
-        <v>6220</v>
+        <v>6190</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-19 13:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.58</v>
+        <v>21.78</v>
       </c>
       <c r="C33" t="n">
-        <v>23.47</v>
+        <v>22.31</v>
       </c>
       <c r="D33" t="n">
-        <v>21.83</v>
+        <v>21.39</v>
       </c>
       <c r="E33" t="n">
         <v>10.1</v>
       </c>
       <c r="F33" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>815</v>
+        <v>323</v>
       </c>
       <c r="H33" t="n">
-        <v>45.81</v>
+        <v>48.06</v>
       </c>
       <c r="I33" t="n">
-        <v>48.66</v>
+        <v>48.87</v>
       </c>
       <c r="J33" t="n">
-        <v>43.93</v>
+        <v>46.24</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2002,383 +2002,383 @@
         <v>2.7</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>6220</v>
+        <v>6210</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-19 12:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21.31</v>
+        <v>22.97</v>
       </c>
       <c r="C34" t="n">
-        <v>22.4</v>
+        <v>24.27</v>
       </c>
       <c r="D34" t="n">
-        <v>20.2</v>
+        <v>22.16</v>
       </c>
       <c r="E34" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="F34" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>689</v>
+        <v>747</v>
       </c>
       <c r="H34" t="n">
-        <v>50.33</v>
+        <v>44.85</v>
       </c>
       <c r="I34" t="n">
-        <v>56.08</v>
+        <v>47.21</v>
       </c>
       <c r="J34" t="n">
-        <v>47.33</v>
+        <v>41.93</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-19 11:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>18.91</v>
+        <v>22.58</v>
       </c>
       <c r="C35" t="n">
-        <v>19.91</v>
+        <v>23.47</v>
       </c>
       <c r="D35" t="n">
-        <v>18.4</v>
+        <v>21.83</v>
       </c>
       <c r="E35" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="F35" t="n">
-        <v>10.6</v>
+        <v>9.6</v>
       </c>
       <c r="G35" t="n">
-        <v>305</v>
+        <v>815</v>
       </c>
       <c r="H35" t="n">
-        <v>60.58</v>
+        <v>45.81</v>
       </c>
       <c r="I35" t="n">
-        <v>63.06</v>
+        <v>48.66</v>
       </c>
       <c r="J35" t="n">
-        <v>55.94</v>
+        <v>43.93</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="N35" t="n">
-        <v>6162</v>
+        <v>6220</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.94</v>
+        <v>21.31</v>
       </c>
       <c r="C36" t="n">
-        <v>18.46</v>
+        <v>22.4</v>
       </c>
       <c r="D36" t="n">
-        <v>17.55</v>
+        <v>20.2</v>
       </c>
       <c r="E36" t="n">
-        <v>11.6</v>
+        <v>10.4</v>
       </c>
       <c r="F36" t="n">
-        <v>11.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>189</v>
+        <v>689</v>
       </c>
       <c r="H36" t="n">
-        <v>67.54000000000001</v>
+        <v>50.33</v>
       </c>
       <c r="I36" t="n">
-        <v>70.20999999999999</v>
+        <v>56.08</v>
       </c>
       <c r="J36" t="n">
-        <v>64.44</v>
+        <v>47.33</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="N36" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.55</v>
+        <v>18.91</v>
       </c>
       <c r="C37" t="n">
-        <v>17.81</v>
+        <v>19.91</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>18.4</v>
       </c>
       <c r="E37" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="F37" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="G37" t="n">
-        <v>95</v>
+        <v>305</v>
       </c>
       <c r="H37" t="n">
-        <v>68.43000000000001</v>
+        <v>60.58</v>
       </c>
       <c r="I37" t="n">
-        <v>69.95</v>
+        <v>63.06</v>
       </c>
       <c r="J37" t="n">
-        <v>65.48</v>
+        <v>55.94</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="N37" t="n">
-        <v>6132</v>
+        <v>6162</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.64</v>
+        <v>17.94</v>
       </c>
       <c r="C38" t="n">
-        <v>17.06</v>
+        <v>18.46</v>
       </c>
       <c r="D38" t="n">
-        <v>16.2</v>
+        <v>17.55</v>
       </c>
       <c r="E38" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F38" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G38" t="n">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="H38" t="n">
-        <v>72.79000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>77.45</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>70.3</v>
+        <v>64.44</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>6132</v>
+        <v>6152</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>15.62</v>
+        <v>17.55</v>
       </c>
       <c r="C39" t="n">
-        <v>16.07</v>
+        <v>17.81</v>
       </c>
       <c r="D39" t="n">
-        <v>15.35</v>
+        <v>17.2</v>
       </c>
       <c r="E39" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="F39" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="G39" t="n">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="H39" t="n">
-        <v>85.33</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>89.23</v>
+        <v>69.95</v>
       </c>
       <c r="J39" t="n">
-        <v>79.03</v>
+        <v>65.48</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N39" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15.25</v>
+        <v>16.64</v>
       </c>
       <c r="C40" t="n">
-        <v>15.35</v>
+        <v>17.06</v>
       </c>
       <c r="D40" t="n">
-        <v>15.06</v>
+        <v>16.2</v>
       </c>
       <c r="E40" t="n">
-        <v>13.3</v>
+        <v>11.5</v>
       </c>
       <c r="F40" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H40" t="n">
-        <v>89.16</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>91.05</v>
+        <v>77.45</v>
       </c>
       <c r="J40" t="n">
-        <v>87.77</v>
+        <v>70.3</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N40" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.2</v>
+        <v>15.62</v>
       </c>
       <c r="C41" t="n">
-        <v>15.32</v>
+        <v>16.07</v>
       </c>
       <c r="D41" t="n">
-        <v>15.08</v>
+        <v>15.35</v>
       </c>
       <c r="E41" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="F41" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H41" t="n">
-        <v>88.42</v>
+        <v>85.33</v>
       </c>
       <c r="I41" t="n">
-        <v>89.37</v>
+        <v>89.23</v>
       </c>
       <c r="J41" t="n">
-        <v>87.13</v>
+        <v>79.03</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
         <v>6122</v>
@@ -2388,35 +2388,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.53</v>
+        <v>15.25</v>
       </c>
       <c r="C42" t="n">
-        <v>15.66</v>
+        <v>15.35</v>
       </c>
       <c r="D42" t="n">
-        <v>15.45</v>
+        <v>15.06</v>
       </c>
       <c r="E42" t="n">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
       <c r="F42" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>85.40000000000001</v>
+        <v>89.16</v>
       </c>
       <c r="I42" t="n">
-        <v>86.58</v>
+        <v>91.05</v>
       </c>
       <c r="J42" t="n">
-        <v>83.42</v>
+        <v>87.77</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2435,44 +2435,44 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15.66</v>
+        <v>15.2</v>
       </c>
       <c r="C43" t="n">
-        <v>15.73</v>
+        <v>15.32</v>
       </c>
       <c r="D43" t="n">
-        <v>15.62</v>
+        <v>15.08</v>
       </c>
       <c r="E43" t="n">
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
       <c r="F43" t="n">
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>82.52</v>
+        <v>88.42</v>
       </c>
       <c r="I43" t="n">
-        <v>82.76000000000001</v>
+        <v>89.37</v>
       </c>
       <c r="J43" t="n">
-        <v>82.33</v>
+        <v>87.13</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>6122</v>
@@ -2482,44 +2482,44 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>15.72</v>
+        <v>15.53</v>
       </c>
       <c r="C44" t="n">
-        <v>15.77</v>
+        <v>15.66</v>
       </c>
       <c r="D44" t="n">
-        <v>15.65</v>
+        <v>15.45</v>
       </c>
       <c r="E44" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="F44" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>81.17</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>82.40000000000001</v>
+        <v>86.58</v>
       </c>
       <c r="J44" t="n">
-        <v>80.16</v>
+        <v>83.42</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>6122</v>
@@ -2529,44 +2529,44 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.09</v>
+        <v>15.66</v>
       </c>
       <c r="C45" t="n">
-        <v>16.59</v>
+        <v>15.73</v>
       </c>
       <c r="D45" t="n">
-        <v>15.76</v>
+        <v>15.62</v>
       </c>
       <c r="E45" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="F45" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>76.7</v>
+        <v>82.52</v>
       </c>
       <c r="I45" t="n">
-        <v>80.06999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>72.89</v>
+        <v>82.33</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="M45" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N45" t="n">
         <v>6122</v>
@@ -2576,35 +2576,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16.2</v>
+        <v>15.72</v>
       </c>
       <c r="C46" t="n">
-        <v>16.53</v>
+        <v>15.77</v>
       </c>
       <c r="D46" t="n">
-        <v>15.84</v>
+        <v>15.65</v>
       </c>
       <c r="E46" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="F46" t="n">
-        <v>11.6</v>
+        <v>12.3</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>77.2</v>
+        <v>81.17</v>
       </c>
       <c r="I46" t="n">
-        <v>80.54000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>73.31999999999999</v>
+        <v>80.16</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2613,56 +2613,54 @@
         <v>0.6</v>
       </c>
       <c r="M46" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N46" t="n">
         <v>6122</v>
       </c>
-      <c r="O46" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.03</v>
+        <v>16.09</v>
       </c>
       <c r="C47" t="n">
-        <v>16.12</v>
+        <v>16.59</v>
       </c>
       <c r="D47" t="n">
-        <v>15.93</v>
+        <v>15.76</v>
       </c>
       <c r="E47" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="F47" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>77.56</v>
+        <v>76.7</v>
       </c>
       <c r="I47" t="n">
-        <v>79.16</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>76.79000000000001</v>
+        <v>72.89</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N47" t="n">
         <v>6122</v>
@@ -2672,41 +2670,41 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>15.79</v>
+        <v>16.2</v>
       </c>
       <c r="C48" t="n">
-        <v>15.92</v>
+        <v>16.53</v>
       </c>
       <c r="D48" t="n">
-        <v>15.7</v>
+        <v>15.84</v>
       </c>
       <c r="E48" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="F48" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>78.34999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="I48" t="n">
-        <v>78.65000000000001</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>77.79000000000001</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M48" t="n">
         <v>1.3</v>
@@ -2714,49 +2712,51 @@
       <c r="N48" t="n">
         <v>6122</v>
       </c>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>15.9</v>
+        <v>16.03</v>
       </c>
       <c r="C49" t="n">
-        <v>16.37</v>
+        <v>16.12</v>
       </c>
       <c r="D49" t="n">
-        <v>15.67</v>
+        <v>15.93</v>
       </c>
       <c r="E49" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>76.45999999999999</v>
+        <v>77.56</v>
       </c>
       <c r="I49" t="n">
-        <v>78.44</v>
+        <v>79.16</v>
       </c>
       <c r="J49" t="n">
-        <v>72.33</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="M49" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="N49" t="n">
         <v>6122</v>
@@ -2766,47 +2766,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>16.37</v>
+        <v>15.79</v>
       </c>
       <c r="C50" t="n">
-        <v>16.48</v>
+        <v>15.92</v>
       </c>
       <c r="D50" t="n">
-        <v>16.29</v>
+        <v>15.7</v>
       </c>
       <c r="E50" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="F50" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>74.02</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>74.88</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>72.13</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M50" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="N50" t="n">
-        <v>6132</v>
+        <v>6122</v>
       </c>
       <c r="O50" t="n">
         <v>1.6</v>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,561 +508,561 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 22:00:00</t>
+          <t>2026-10-21 04:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.54</v>
+        <v>18.33</v>
       </c>
       <c r="C2" t="n">
-        <v>21.85</v>
+        <v>18.38</v>
       </c>
       <c r="D2" t="n">
-        <v>21.3</v>
+        <v>18.29</v>
       </c>
       <c r="E2" t="n">
-        <v>13.1</v>
+        <v>14.5</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>14.4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>59.25</v>
+        <v>79.06</v>
       </c>
       <c r="I2" t="n">
-        <v>59.85</v>
+        <v>79.12</v>
       </c>
       <c r="J2" t="n">
-        <v>58.39</v>
+        <v>78.97</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="n">
-        <v>6132</v>
+        <v>6112</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:00:00</t>
+          <t>2026-10-21 03:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.75</v>
+        <v>18.02</v>
       </c>
       <c r="C3" t="n">
-        <v>23.07</v>
+        <v>18.2</v>
       </c>
       <c r="D3" t="n">
-        <v>22.23</v>
+        <v>17.63</v>
       </c>
       <c r="E3" t="n">
-        <v>13.2</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>55.42</v>
+        <v>78.34</v>
       </c>
       <c r="I3" t="n">
-        <v>57</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>54.24</v>
+        <v>77.64</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="N3" t="n">
-        <v>6132</v>
+        <v>6092</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 20:00:00</t>
+          <t>2026-10-21 02:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.5</v>
+        <v>16.92</v>
       </c>
       <c r="C4" t="n">
-        <v>23.82</v>
+        <v>17.53</v>
       </c>
       <c r="D4" t="n">
-        <v>23.14</v>
+        <v>16.5</v>
       </c>
       <c r="E4" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F4" t="n">
         <v>13</v>
       </c>
-      <c r="F4" t="n">
-        <v>12.8</v>
-      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>52.31</v>
+        <v>80.12</v>
       </c>
       <c r="I4" t="n">
-        <v>54</v>
+        <v>82.41</v>
       </c>
       <c r="J4" t="n">
-        <v>50.87</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="N4" t="n">
-        <v>6132</v>
+        <v>6092</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 19:00:00</t>
+          <t>2026-10-21 01:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.27</v>
+        <v>15.88</v>
       </c>
       <c r="C5" t="n">
-        <v>24.74</v>
+        <v>16.25</v>
       </c>
       <c r="D5" t="n">
-        <v>23.84</v>
+        <v>15.27</v>
       </c>
       <c r="E5" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F5" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>49.32</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>50.77</v>
+        <v>85.31</v>
       </c>
       <c r="J5" t="n">
-        <v>47.94</v>
+        <v>80.92</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="N5" t="n">
-        <v>6142</v>
+        <v>6112</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20 18:00:00</t>
+          <t>2026-10-21 00:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.12</v>
+        <v>16.91</v>
       </c>
       <c r="C6" t="n">
-        <v>25.39</v>
+        <v>17.84</v>
       </c>
       <c r="D6" t="n">
-        <v>24.84</v>
+        <v>16.18</v>
       </c>
       <c r="E6" t="n">
         <v>12.8</v>
       </c>
       <c r="F6" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>46.99</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>47.92</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>45.97</v>
+        <v>73.23</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="N6" t="n">
-        <v>6152</v>
+        <v>6102</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20 17:00:00</t>
+          <t>2026-10-20 23:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.86</v>
+        <v>18.54</v>
       </c>
       <c r="C7" t="n">
-        <v>26.34</v>
+        <v>19.29</v>
       </c>
       <c r="D7" t="n">
-        <v>25.5</v>
+        <v>17.65</v>
       </c>
       <c r="E7" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F7" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="G7" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>44.61</v>
+        <v>69.75</v>
       </c>
       <c r="I7" t="n">
-        <v>45.71</v>
+        <v>73.11</v>
       </c>
       <c r="J7" t="n">
-        <v>43.23</v>
+        <v>66.94</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="N7" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20 16:00:00</t>
+          <t>2026-10-20 22:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.66</v>
+        <v>20.74</v>
       </c>
       <c r="C8" t="n">
-        <v>26.95</v>
+        <v>21.85</v>
       </c>
       <c r="D8" t="n">
-        <v>26.15</v>
+        <v>19.51</v>
       </c>
       <c r="E8" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="F8" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="G8" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>42.04</v>
+        <v>61.67</v>
       </c>
       <c r="I8" t="n">
-        <v>43.28</v>
+        <v>65.73</v>
       </c>
       <c r="J8" t="n">
-        <v>41.15</v>
+        <v>58.39</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="N8" t="n">
-        <v>6170</v>
+        <v>6122</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20 15:00:00</t>
+          <t>2026-10-20 21:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.13</v>
+        <v>22.75</v>
       </c>
       <c r="C9" t="n">
-        <v>27.72</v>
+        <v>23.07</v>
       </c>
       <c r="D9" t="n">
-        <v>26.66</v>
+        <v>22.23</v>
       </c>
       <c r="E9" t="n">
-        <v>12.3</v>
+        <v>13.2</v>
       </c>
       <c r="F9" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="G9" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>40.38</v>
+        <v>55.42</v>
       </c>
       <c r="I9" t="n">
-        <v>41.51</v>
+        <v>57</v>
       </c>
       <c r="J9" t="n">
-        <v>39.08</v>
+        <v>54.24</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="N9" t="n">
-        <v>6180</v>
+        <v>6132</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20 14:00:00</t>
+          <t>2026-10-20 20:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26.77</v>
+        <v>23.5</v>
       </c>
       <c r="C10" t="n">
-        <v>27.91</v>
+        <v>23.82</v>
       </c>
       <c r="D10" t="n">
-        <v>25.49</v>
+        <v>23.14</v>
       </c>
       <c r="E10" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="G10" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>41.64</v>
+        <v>52.31</v>
       </c>
       <c r="I10" t="n">
-        <v>44.08</v>
+        <v>54</v>
       </c>
       <c r="J10" t="n">
-        <v>39.72</v>
+        <v>50.87</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>0.3</v>
       </c>
       <c r="N10" t="n">
-        <v>6190</v>
+        <v>6132</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20 13:00:00</t>
+          <t>2026-10-20 19:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25.07</v>
+        <v>24.27</v>
       </c>
       <c r="C11" t="n">
-        <v>25.85</v>
+        <v>24.74</v>
       </c>
       <c r="D11" t="n">
-        <v>24.61</v>
+        <v>23.84</v>
       </c>
       <c r="E11" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="F11" t="n">
-        <v>11.5</v>
+        <v>12.6</v>
       </c>
       <c r="G11" t="n">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>44.5</v>
+        <v>49.32</v>
       </c>
       <c r="I11" t="n">
-        <v>45.61</v>
+        <v>50.77</v>
       </c>
       <c r="J11" t="n">
-        <v>43.09</v>
+        <v>47.94</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="N11" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20 12:00:00</t>
+          <t>2026-10-20 18:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.81</v>
+        <v>25.12</v>
       </c>
       <c r="C12" t="n">
-        <v>25.08</v>
+        <v>25.39</v>
       </c>
       <c r="D12" t="n">
-        <v>24.53</v>
+        <v>24.84</v>
       </c>
       <c r="E12" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="F12" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="G12" t="n">
-        <v>373</v>
+        <v>32</v>
       </c>
       <c r="H12" t="n">
-        <v>43.89</v>
+        <v>46.99</v>
       </c>
       <c r="I12" t="n">
-        <v>44.75</v>
+        <v>47.92</v>
       </c>
       <c r="J12" t="n">
-        <v>43.04</v>
+        <v>45.97</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="N12" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00:00</t>
+          <t>2026-10-20 17:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.48</v>
+        <v>25.86</v>
       </c>
       <c r="C13" t="n">
-        <v>24.58</v>
+        <v>26.34</v>
       </c>
       <c r="D13" t="n">
-        <v>22.73</v>
+        <v>25.5</v>
       </c>
       <c r="E13" t="n">
-        <v>11.3</v>
+        <v>12.7</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="G13" t="n">
-        <v>519</v>
+        <v>91</v>
       </c>
       <c r="H13" t="n">
-        <v>47.14</v>
+        <v>44.61</v>
       </c>
       <c r="I13" t="n">
-        <v>49.9</v>
+        <v>45.71</v>
       </c>
       <c r="J13" t="n">
-        <v>43.67</v>
+        <v>43.23</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M13" t="n">
         <v>2.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.6</v>
       </c>
       <c r="N13" t="n">
         <v>6162</v>
@@ -1072,364 +1072,364 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20 10:00:00</t>
+          <t>2026-10-20 16:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.96</v>
+        <v>26.66</v>
       </c>
       <c r="C14" t="n">
-        <v>22.96</v>
+        <v>26.95</v>
       </c>
       <c r="D14" t="n">
-        <v>21.26</v>
+        <v>26.15</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="G14" t="n">
-        <v>298</v>
+        <v>229</v>
       </c>
       <c r="H14" t="n">
-        <v>52.22</v>
+        <v>42.04</v>
       </c>
       <c r="I14" t="n">
-        <v>54.36</v>
+        <v>43.28</v>
       </c>
       <c r="J14" t="n">
-        <v>49</v>
+        <v>41.15</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20 09:00:00</t>
+          <t>2026-10-20 15:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20.32</v>
+        <v>27.13</v>
       </c>
       <c r="C15" t="n">
-        <v>21.66</v>
+        <v>27.72</v>
       </c>
       <c r="D15" t="n">
-        <v>19.17</v>
+        <v>26.66</v>
       </c>
       <c r="E15" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F15" t="n">
         <v>11.9</v>
       </c>
       <c r="G15" t="n">
-        <v>289</v>
+        <v>368</v>
       </c>
       <c r="H15" t="n">
-        <v>60.55</v>
+        <v>40.38</v>
       </c>
       <c r="I15" t="n">
-        <v>64.51000000000001</v>
+        <v>41.51</v>
       </c>
       <c r="J15" t="n">
-        <v>55.76</v>
+        <v>39.08</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20 08:00:00</t>
+          <t>2026-10-20 14:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18.15</v>
+        <v>26.77</v>
       </c>
       <c r="C16" t="n">
-        <v>19.16</v>
+        <v>27.91</v>
       </c>
       <c r="D16" t="n">
-        <v>17.45</v>
+        <v>25.49</v>
       </c>
       <c r="E16" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="F16" t="n">
         <v>12.1</v>
       </c>
       <c r="G16" t="n">
-        <v>111</v>
+        <v>508</v>
       </c>
       <c r="H16" t="n">
-        <v>70.59</v>
+        <v>41.64</v>
       </c>
       <c r="I16" t="n">
-        <v>75.61</v>
+        <v>44.08</v>
       </c>
       <c r="J16" t="n">
-        <v>65.56999999999999</v>
+        <v>39.72</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>6122</v>
+        <v>6190</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20 07:00:00</t>
+          <t>2026-10-20 13:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.92</v>
+        <v>25.07</v>
       </c>
       <c r="C17" t="n">
-        <v>17.33</v>
+        <v>25.85</v>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>24.61</v>
       </c>
       <c r="E17" t="n">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="F17" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="G17" t="n">
-        <v>17</v>
+        <v>300</v>
       </c>
       <c r="H17" t="n">
-        <v>74.87</v>
+        <v>44.5</v>
       </c>
       <c r="I17" t="n">
-        <v>75.66</v>
+        <v>45.61</v>
       </c>
       <c r="J17" t="n">
-        <v>74.08</v>
+        <v>43.09</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>6092</v>
+        <v>6170</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00:00</t>
+          <t>2026-10-20 12:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.75</v>
+        <v>24.81</v>
       </c>
       <c r="C18" t="n">
-        <v>16.84</v>
+        <v>25.08</v>
       </c>
       <c r="D18" t="n">
-        <v>16.64</v>
+        <v>24.53</v>
       </c>
       <c r="E18" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="F18" t="n">
-        <v>11.9</v>
+        <v>11.2</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="H18" t="n">
-        <v>74.86</v>
+        <v>43.89</v>
       </c>
       <c r="I18" t="n">
-        <v>75.98</v>
+        <v>44.75</v>
       </c>
       <c r="J18" t="n">
-        <v>73.98999999999999</v>
+        <v>43.04</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>6102</v>
+        <v>6162</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20 05:00:00</t>
+          <t>2026-10-20 11:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16.83</v>
+        <v>23.48</v>
       </c>
       <c r="C19" t="n">
-        <v>17.01</v>
+        <v>24.58</v>
       </c>
       <c r="D19" t="n">
-        <v>16.66</v>
+        <v>22.73</v>
       </c>
       <c r="E19" t="n">
-        <v>11.9</v>
+        <v>11.3</v>
       </c>
       <c r="F19" t="n">
-        <v>11.7</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>519</v>
       </c>
       <c r="H19" t="n">
-        <v>73.56999999999999</v>
+        <v>47.14</v>
       </c>
       <c r="I19" t="n">
-        <v>75.19</v>
+        <v>49.9</v>
       </c>
       <c r="J19" t="n">
-        <v>72.06</v>
+        <v>43.67</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>6082</v>
+        <v>6162</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20 04:00:00</t>
+          <t>2026-10-20 10:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.74</v>
+        <v>21.96</v>
       </c>
       <c r="C20" t="n">
-        <v>16.99</v>
+        <v>22.96</v>
       </c>
       <c r="D20" t="n">
-        <v>16.45</v>
+        <v>21.26</v>
       </c>
       <c r="E20" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="F20" t="n">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="H20" t="n">
-        <v>74.84</v>
+        <v>52.22</v>
       </c>
       <c r="I20" t="n">
-        <v>77.06999999999999</v>
+        <v>54.36</v>
       </c>
       <c r="J20" t="n">
-        <v>72.64</v>
+        <v>49</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>6112</v>
+        <v>6152</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20 03:00:00</t>
+          <t>2026-10-20 09:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.86</v>
+        <v>20.32</v>
       </c>
       <c r="C21" t="n">
-        <v>17.22</v>
+        <v>21.66</v>
       </c>
       <c r="D21" t="n">
-        <v>16.71</v>
+        <v>19.17</v>
       </c>
       <c r="E21" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="H21" t="n">
-        <v>75.81999999999999</v>
+        <v>60.55</v>
       </c>
       <c r="I21" t="n">
-        <v>77.26000000000001</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>74.54000000000001</v>
+        <v>55.76</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1438,45 +1438,45 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N21" t="n">
-        <v>6112</v>
+        <v>6142</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00:00</t>
+          <t>2026-10-20 08:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.59</v>
+        <v>18.15</v>
       </c>
       <c r="C22" t="n">
-        <v>17.8</v>
+        <v>19.16</v>
       </c>
       <c r="D22" t="n">
-        <v>17.29</v>
+        <v>17.45</v>
       </c>
       <c r="E22" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="F22" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="H22" t="n">
-        <v>73.83</v>
+        <v>70.59</v>
       </c>
       <c r="I22" t="n">
-        <v>74.95</v>
+        <v>75.61</v>
       </c>
       <c r="J22" t="n">
-        <v>72.36</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N22" t="n">
         <v>6122</v>
@@ -1495,35 +1495,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20 01:00:00</t>
+          <t>2026-10-20 07:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18.24</v>
+        <v>16.92</v>
       </c>
       <c r="C23" t="n">
-        <v>18.59</v>
+        <v>17.33</v>
       </c>
       <c r="D23" t="n">
-        <v>17.84</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="n">
-        <v>11.8</v>
+        <v>12.3</v>
       </c>
       <c r="F23" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>66.76000000000001</v>
+        <v>74.87</v>
       </c>
       <c r="I23" t="n">
-        <v>71.14</v>
+        <v>75.66</v>
       </c>
       <c r="J23" t="n">
-        <v>63.93</v>
+        <v>74.08</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1542,35 +1542,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-20 00:00:00</t>
+          <t>2026-10-20 06:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18.68</v>
+        <v>16.75</v>
       </c>
       <c r="C24" t="n">
-        <v>18.93</v>
+        <v>16.84</v>
       </c>
       <c r="D24" t="n">
-        <v>18.52</v>
+        <v>16.64</v>
       </c>
       <c r="E24" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="F24" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>64.40000000000001</v>
+        <v>74.86</v>
       </c>
       <c r="I24" t="n">
-        <v>65.87</v>
+        <v>75.98</v>
       </c>
       <c r="J24" t="n">
-        <v>61.94</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1582,42 +1582,42 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6122</v>
+        <v>6102</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-19 23:00:00</t>
+          <t>2026-10-20 05:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.43</v>
+        <v>16.83</v>
       </c>
       <c r="C25" t="n">
-        <v>19.64</v>
+        <v>17.01</v>
       </c>
       <c r="D25" t="n">
-        <v>19.01</v>
+        <v>16.66</v>
       </c>
       <c r="E25" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="F25" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>60.1</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>60.96</v>
+        <v>75.19</v>
       </c>
       <c r="J25" t="n">
-        <v>59.25</v>
+        <v>72.06</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1629,51 +1629,51 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6132</v>
+        <v>6082</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-19 22:00:00</t>
+          <t>2026-10-20 04:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20.1</v>
+        <v>16.74</v>
       </c>
       <c r="C26" t="n">
-        <v>20.3</v>
+        <v>16.99</v>
       </c>
       <c r="D26" t="n">
-        <v>19.77</v>
+        <v>16.45</v>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>12.1</v>
       </c>
       <c r="F26" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>56.64</v>
+        <v>74.84</v>
       </c>
       <c r="I26" t="n">
-        <v>58.8</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>55.68</v>
+        <v>72.64</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>6112</v>
@@ -1683,984 +1683,986 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19 21:00:00</t>
+          <t>2026-10-20 03:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20</v>
+        <v>16.86</v>
       </c>
       <c r="C27" t="n">
-        <v>20.17</v>
+        <v>17.22</v>
       </c>
       <c r="D27" t="n">
-        <v>19.94</v>
+        <v>16.71</v>
       </c>
       <c r="E27" t="n">
-        <v>10.6</v>
+        <v>12.4</v>
       </c>
       <c r="F27" t="n">
-        <v>10.6</v>
+        <v>12</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>55.69</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>55.96</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>55.41</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6142</v>
+        <v>6112</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-19 20:00:00</t>
+          <t>2026-10-20 02:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.56</v>
+        <v>17.59</v>
       </c>
       <c r="C28" t="n">
-        <v>19.96</v>
+        <v>17.8</v>
       </c>
       <c r="D28" t="n">
-        <v>19.34</v>
+        <v>17.29</v>
       </c>
       <c r="E28" t="n">
-        <v>10.6</v>
+        <v>12.7</v>
       </c>
       <c r="F28" t="n">
-        <v>10.3</v>
+        <v>12.5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>56.91</v>
+        <v>73.83</v>
       </c>
       <c r="I28" t="n">
-        <v>57.67</v>
+        <v>74.95</v>
       </c>
       <c r="J28" t="n">
-        <v>55.82</v>
+        <v>72.36</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-19 19:00:00</t>
+          <t>2026-10-20 01:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.8</v>
+        <v>18.24</v>
       </c>
       <c r="C29" t="n">
-        <v>19.92</v>
+        <v>18.59</v>
       </c>
       <c r="D29" t="n">
-        <v>19.62</v>
+        <v>17.84</v>
       </c>
       <c r="E29" t="n">
-        <v>10.3</v>
+        <v>11.8</v>
       </c>
       <c r="F29" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>55.22</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>56.29</v>
+        <v>71.14</v>
       </c>
       <c r="J29" t="n">
-        <v>54.46</v>
+        <v>63.93</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6152</v>
+        <v>6092</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-20 00:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.91</v>
+        <v>18.68</v>
       </c>
       <c r="C30" t="n">
-        <v>19.98</v>
+        <v>18.93</v>
       </c>
       <c r="D30" t="n">
-        <v>19.83</v>
+        <v>18.52</v>
       </c>
       <c r="E30" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
       <c r="F30" t="n">
-        <v>10.2</v>
+        <v>11.2</v>
       </c>
       <c r="G30" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>54.74</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>54.92</v>
+        <v>65.87</v>
       </c>
       <c r="J30" t="n">
-        <v>54.61</v>
+        <v>61.94</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6162</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
+        <v>6122</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-19 23:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20.31</v>
+        <v>19.43</v>
       </c>
       <c r="C31" t="n">
-        <v>20.99</v>
+        <v>19.64</v>
       </c>
       <c r="D31" t="n">
-        <v>19.97</v>
+        <v>19.01</v>
       </c>
       <c r="E31" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="F31" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="G31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>53.29</v>
+        <v>60.1</v>
       </c>
       <c r="I31" t="n">
-        <v>54.84</v>
+        <v>60.96</v>
       </c>
       <c r="J31" t="n">
-        <v>51.22</v>
+        <v>59.25</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6170</v>
+        <v>6132</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-19 22:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21.38</v>
+        <v>20.1</v>
       </c>
       <c r="C32" t="n">
-        <v>21.67</v>
+        <v>20.3</v>
       </c>
       <c r="D32" t="n">
-        <v>20.91</v>
+        <v>19.77</v>
       </c>
       <c r="E32" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="G32" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>49.67</v>
+        <v>56.64</v>
       </c>
       <c r="I32" t="n">
-        <v>50.93</v>
+        <v>58.8</v>
       </c>
       <c r="J32" t="n">
-        <v>48.59</v>
+        <v>55.68</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="N32" t="n">
-        <v>6190</v>
+        <v>6112</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00:00</t>
+          <t>2026-10-19 21:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21.78</v>
+        <v>20</v>
       </c>
       <c r="C33" t="n">
-        <v>22.31</v>
+        <v>20.17</v>
       </c>
       <c r="D33" t="n">
-        <v>21.39</v>
+        <v>19.94</v>
       </c>
       <c r="E33" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="F33" t="n">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="G33" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>48.06</v>
+        <v>55.69</v>
       </c>
       <c r="I33" t="n">
-        <v>48.87</v>
+        <v>55.96</v>
       </c>
       <c r="J33" t="n">
-        <v>46.24</v>
+        <v>55.41</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="N33" t="n">
-        <v>6210</v>
+        <v>6142</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 20:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22.97</v>
+        <v>19.56</v>
       </c>
       <c r="C34" t="n">
-        <v>24.27</v>
+        <v>19.96</v>
       </c>
       <c r="D34" t="n">
-        <v>22.16</v>
+        <v>19.34</v>
       </c>
       <c r="E34" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="F34" t="n">
-        <v>9.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="G34" t="n">
-        <v>747</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>44.85</v>
+        <v>56.91</v>
       </c>
       <c r="I34" t="n">
-        <v>47.21</v>
+        <v>57.67</v>
       </c>
       <c r="J34" t="n">
-        <v>41.93</v>
+        <v>55.82</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="M34" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="N34" t="n">
-        <v>6220</v>
+        <v>6142</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-19 13:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.58</v>
+        <v>19.8</v>
       </c>
       <c r="C35" t="n">
-        <v>23.47</v>
+        <v>19.92</v>
       </c>
       <c r="D35" t="n">
-        <v>21.83</v>
+        <v>19.62</v>
       </c>
       <c r="E35" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="F35" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="G35" t="n">
-        <v>815</v>
+        <v>10</v>
       </c>
       <c r="H35" t="n">
-        <v>45.81</v>
+        <v>55.22</v>
       </c>
       <c r="I35" t="n">
-        <v>48.66</v>
+        <v>56.29</v>
       </c>
       <c r="J35" t="n">
-        <v>43.93</v>
+        <v>54.46</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="M35" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="N35" t="n">
-        <v>6220</v>
+        <v>6152</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-19 12:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21.31</v>
+        <v>19.91</v>
       </c>
       <c r="C36" t="n">
-        <v>22.4</v>
+        <v>19.98</v>
       </c>
       <c r="D36" t="n">
-        <v>20.2</v>
+        <v>19.83</v>
       </c>
       <c r="E36" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F36" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G36" t="n">
-        <v>689</v>
+        <v>17</v>
       </c>
       <c r="H36" t="n">
-        <v>50.33</v>
+        <v>54.74</v>
       </c>
       <c r="I36" t="n">
-        <v>56.08</v>
+        <v>54.92</v>
       </c>
       <c r="J36" t="n">
-        <v>47.33</v>
+        <v>54.61</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="M36" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>6190</v>
+        <v>6162</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-19 11:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18.91</v>
+        <v>20.31</v>
       </c>
       <c r="C37" t="n">
-        <v>19.91</v>
+        <v>20.99</v>
       </c>
       <c r="D37" t="n">
-        <v>18.4</v>
+        <v>19.97</v>
       </c>
       <c r="E37" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="F37" t="n">
-        <v>10.6</v>
+        <v>10.1</v>
       </c>
       <c r="G37" t="n">
-        <v>305</v>
+        <v>40</v>
       </c>
       <c r="H37" t="n">
-        <v>60.58</v>
+        <v>53.29</v>
       </c>
       <c r="I37" t="n">
-        <v>63.06</v>
+        <v>54.84</v>
       </c>
       <c r="J37" t="n">
-        <v>55.94</v>
+        <v>51.22</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="M37" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>6162</v>
+        <v>6170</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.94</v>
+        <v>21.38</v>
       </c>
       <c r="C38" t="n">
-        <v>18.46</v>
+        <v>21.67</v>
       </c>
       <c r="D38" t="n">
-        <v>17.55</v>
+        <v>20.91</v>
       </c>
       <c r="E38" t="n">
-        <v>11.6</v>
+        <v>10.2</v>
       </c>
       <c r="F38" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="G38" t="n">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="H38" t="n">
-        <v>67.54000000000001</v>
+        <v>49.67</v>
       </c>
       <c r="I38" t="n">
-        <v>70.20999999999999</v>
+        <v>50.93</v>
       </c>
       <c r="J38" t="n">
-        <v>64.44</v>
+        <v>48.59</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>6152</v>
+        <v>6190</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.55</v>
+        <v>21.78</v>
       </c>
       <c r="C39" t="n">
-        <v>17.81</v>
+        <v>22.31</v>
       </c>
       <c r="D39" t="n">
-        <v>17.2</v>
+        <v>21.39</v>
       </c>
       <c r="E39" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="F39" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="H39" t="n">
-        <v>68.43000000000001</v>
+        <v>48.06</v>
       </c>
       <c r="I39" t="n">
-        <v>69.95</v>
+        <v>48.87</v>
       </c>
       <c r="J39" t="n">
-        <v>65.48</v>
+        <v>46.24</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>6132</v>
+        <v>6210</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.64</v>
+        <v>22.97</v>
       </c>
       <c r="C40" t="n">
-        <v>17.06</v>
+        <v>24.27</v>
       </c>
       <c r="D40" t="n">
-        <v>16.2</v>
+        <v>22.16</v>
       </c>
       <c r="E40" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="F40" t="n">
-        <v>11.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>44</v>
+        <v>747</v>
       </c>
       <c r="H40" t="n">
-        <v>72.79000000000001</v>
+        <v>44.85</v>
       </c>
       <c r="I40" t="n">
-        <v>77.45</v>
+        <v>47.21</v>
       </c>
       <c r="J40" t="n">
-        <v>70.3</v>
+        <v>41.93</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="N40" t="n">
-        <v>6132</v>
+        <v>6220</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.62</v>
+        <v>22.58</v>
       </c>
       <c r="C41" t="n">
-        <v>16.07</v>
+        <v>23.47</v>
       </c>
       <c r="D41" t="n">
-        <v>15.35</v>
+        <v>21.83</v>
       </c>
       <c r="E41" t="n">
-        <v>12.9</v>
+        <v>10.1</v>
       </c>
       <c r="F41" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="G41" t="n">
-        <v>8</v>
+        <v>815</v>
       </c>
       <c r="H41" t="n">
-        <v>85.33</v>
+        <v>45.81</v>
       </c>
       <c r="I41" t="n">
-        <v>89.23</v>
+        <v>48.66</v>
       </c>
       <c r="J41" t="n">
-        <v>79.03</v>
+        <v>43.93</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="N41" t="n">
-        <v>6122</v>
+        <v>6220</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.25</v>
+        <v>21.31</v>
       </c>
       <c r="C42" t="n">
-        <v>15.35</v>
+        <v>22.4</v>
       </c>
       <c r="D42" t="n">
-        <v>15.06</v>
+        <v>20.2</v>
       </c>
       <c r="E42" t="n">
-        <v>13.3</v>
+        <v>10.4</v>
       </c>
       <c r="F42" t="n">
-        <v>13.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>689</v>
       </c>
       <c r="H42" t="n">
-        <v>89.16</v>
+        <v>50.33</v>
       </c>
       <c r="I42" t="n">
-        <v>91.05</v>
+        <v>56.08</v>
       </c>
       <c r="J42" t="n">
-        <v>87.77</v>
+        <v>47.33</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N42" t="n">
-        <v>6122</v>
+        <v>6190</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15.2</v>
+        <v>18.91</v>
       </c>
       <c r="C43" t="n">
-        <v>15.32</v>
+        <v>19.91</v>
       </c>
       <c r="D43" t="n">
-        <v>15.08</v>
+        <v>18.4</v>
       </c>
       <c r="E43" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="F43" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="H43" t="n">
-        <v>88.42</v>
+        <v>60.58</v>
       </c>
       <c r="I43" t="n">
-        <v>89.37</v>
+        <v>63.06</v>
       </c>
       <c r="J43" t="n">
-        <v>87.13</v>
+        <v>55.94</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N43" t="n">
-        <v>6122</v>
+        <v>6162</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>15.53</v>
+        <v>17.94</v>
       </c>
       <c r="C44" t="n">
-        <v>15.66</v>
+        <v>18.46</v>
       </c>
       <c r="D44" t="n">
-        <v>15.45</v>
+        <v>17.55</v>
       </c>
       <c r="E44" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="F44" t="n">
-        <v>12.7</v>
+        <v>11.2</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H44" t="n">
-        <v>85.40000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>86.58</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>83.42</v>
+        <v>64.44</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N44" t="n">
-        <v>6122</v>
+        <v>6152</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15.66</v>
+        <v>17.55</v>
       </c>
       <c r="C45" t="n">
-        <v>15.73</v>
+        <v>17.81</v>
       </c>
       <c r="D45" t="n">
-        <v>15.62</v>
+        <v>17.2</v>
       </c>
       <c r="E45" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="F45" t="n">
-        <v>12.5</v>
+        <v>10.9</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H45" t="n">
-        <v>82.52</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>82.76000000000001</v>
+        <v>69.95</v>
       </c>
       <c r="J45" t="n">
-        <v>82.33</v>
+        <v>65.48</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="N45" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15.72</v>
+        <v>16.64</v>
       </c>
       <c r="C46" t="n">
-        <v>15.77</v>
+        <v>17.06</v>
       </c>
       <c r="D46" t="n">
-        <v>15.65</v>
+        <v>16.2</v>
       </c>
       <c r="E46" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="F46" t="n">
-        <v>12.3</v>
+        <v>11.4</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H46" t="n">
-        <v>81.17</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>82.40000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="J46" t="n">
-        <v>80.16</v>
+        <v>70.3</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="M46" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N46" t="n">
-        <v>6122</v>
+        <v>6132</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.09</v>
+        <v>15.62</v>
       </c>
       <c r="C47" t="n">
-        <v>16.59</v>
+        <v>16.07</v>
       </c>
       <c r="D47" t="n">
-        <v>15.76</v>
+        <v>15.35</v>
       </c>
       <c r="E47" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="F47" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H47" t="n">
-        <v>76.7</v>
+        <v>85.33</v>
       </c>
       <c r="I47" t="n">
-        <v>80.06999999999999</v>
+        <v>89.23</v>
       </c>
       <c r="J47" t="n">
-        <v>72.89</v>
+        <v>79.03</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="M47" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
         <v>6122</v>
@@ -2670,93 +2672,91 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16.2</v>
+        <v>15.25</v>
       </c>
       <c r="C48" t="n">
-        <v>16.53</v>
+        <v>15.35</v>
       </c>
       <c r="D48" t="n">
-        <v>15.84</v>
+        <v>15.06</v>
       </c>
       <c r="E48" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="F48" t="n">
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>77.2</v>
+        <v>89.16</v>
       </c>
       <c r="I48" t="n">
-        <v>80.54000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="J48" t="n">
-        <v>73.31999999999999</v>
+        <v>87.77</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>6122</v>
       </c>
-      <c r="O48" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16.03</v>
+        <v>15.2</v>
       </c>
       <c r="C49" t="n">
-        <v>16.12</v>
+        <v>15.32</v>
       </c>
       <c r="D49" t="n">
-        <v>15.93</v>
+        <v>15.08</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="F49" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>77.56</v>
+        <v>88.42</v>
       </c>
       <c r="I49" t="n">
-        <v>79.16</v>
+        <v>89.37</v>
       </c>
       <c r="J49" t="n">
-        <v>76.79000000000001</v>
+        <v>87.13</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>6122</v>
@@ -2766,50 +2766,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>15.79</v>
+        <v>15.53</v>
       </c>
       <c r="C50" t="n">
-        <v>15.92</v>
+        <v>15.66</v>
       </c>
       <c r="D50" t="n">
-        <v>15.7</v>
+        <v>15.45</v>
       </c>
       <c r="E50" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="F50" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>78.34999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>78.65000000000001</v>
+        <v>86.58</v>
       </c>
       <c r="J50" t="n">
-        <v>77.79000000000001</v>
+        <v>83.42</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>6122</v>
       </c>
       <c r="O50" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>

--- a/00002646_station_data.xlsx
+++ b/00002646_station_data.xlsx
@@ -508,317 +508,317 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21 04:00:00</t>
+          <t>2026-10-21 10:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.33</v>
+        <v>24.23</v>
       </c>
       <c r="C2" t="n">
-        <v>18.38</v>
+        <v>24.33</v>
       </c>
       <c r="D2" t="n">
-        <v>18.29</v>
+        <v>24.1</v>
       </c>
       <c r="E2" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="F2" t="n">
-        <v>14.4</v>
+        <v>13.4</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="H2" t="n">
-        <v>79.06</v>
+        <v>52.35</v>
       </c>
       <c r="I2" t="n">
-        <v>79.12</v>
+        <v>52.55</v>
       </c>
       <c r="J2" t="n">
-        <v>78.97</v>
+        <v>51.97</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="n">
-        <v>6112</v>
+        <v>6132</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21 03:00:00</t>
+          <t>2026-10-21 09:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.02</v>
+        <v>23.28</v>
       </c>
       <c r="C3" t="n">
-        <v>18.2</v>
+        <v>24.05</v>
       </c>
       <c r="D3" t="n">
-        <v>17.63</v>
+        <v>22.38</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="F3" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="H3" t="n">
-        <v>78.34</v>
+        <v>55.2</v>
       </c>
       <c r="I3" t="n">
-        <v>78.79000000000001</v>
+        <v>57.77</v>
       </c>
       <c r="J3" t="n">
-        <v>77.64</v>
+        <v>52.69</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N3" t="n">
-        <v>6092</v>
+        <v>6132</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21 02:00:00</t>
+          <t>2026-10-21 08:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.92</v>
+        <v>21.84</v>
       </c>
       <c r="C4" t="n">
-        <v>17.53</v>
+        <v>22.4</v>
       </c>
       <c r="D4" t="n">
-        <v>16.5</v>
+        <v>21.12</v>
       </c>
       <c r="E4" t="n">
-        <v>13.3</v>
+        <v>13.9</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="H4" t="n">
-        <v>80.12</v>
+        <v>61.61</v>
       </c>
       <c r="I4" t="n">
-        <v>82.41</v>
+        <v>65.91</v>
       </c>
       <c r="J4" t="n">
-        <v>78.56999999999999</v>
+        <v>57.94</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>6092</v>
+        <v>6102</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21 01:00:00</t>
+          <t>2026-10-21 07:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.88</v>
+        <v>20.08</v>
       </c>
       <c r="C5" t="n">
-        <v>16.25</v>
+        <v>20.89</v>
       </c>
       <c r="D5" t="n">
-        <v>15.27</v>
+        <v>19.6</v>
       </c>
       <c r="E5" t="n">
-        <v>12.8</v>
+        <v>14.4</v>
       </c>
       <c r="F5" t="n">
-        <v>12.3</v>
+        <v>14.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H5" t="n">
-        <v>82.81999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>85.31</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>80.92</v>
+        <v>66.62</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="N5" t="n">
-        <v>6112</v>
+        <v>6122</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21 00:00:00</t>
+          <t>2026-10-21 06:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.91</v>
+        <v>19.52</v>
       </c>
       <c r="C6" t="n">
-        <v>17.84</v>
+        <v>19.69</v>
       </c>
       <c r="D6" t="n">
-        <v>16.18</v>
+        <v>19.18</v>
       </c>
       <c r="E6" t="n">
-        <v>12.8</v>
+        <v>14.2</v>
       </c>
       <c r="F6" t="n">
-        <v>12.4</v>
+        <v>14.1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>77.48999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="I6" t="n">
-        <v>81.31999999999999</v>
+        <v>74.34</v>
       </c>
       <c r="J6" t="n">
-        <v>73.23</v>
+        <v>71.33</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="N6" t="n">
-        <v>6102</v>
+        <v>6112</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20 23:00:00</t>
+          <t>2026-10-21 05:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.54</v>
+        <v>18.68</v>
       </c>
       <c r="C7" t="n">
-        <v>19.29</v>
+        <v>19.08</v>
       </c>
       <c r="D7" t="n">
-        <v>17.65</v>
+        <v>18.04</v>
       </c>
       <c r="E7" t="n">
-        <v>12.8</v>
+        <v>14.4</v>
       </c>
       <c r="F7" t="n">
-        <v>12.3</v>
+        <v>14.2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>69.75</v>
+        <v>76.89</v>
       </c>
       <c r="I7" t="n">
-        <v>73.11</v>
+        <v>79.73</v>
       </c>
       <c r="J7" t="n">
-        <v>66.94</v>
+        <v>75.08</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N7" t="n">
-        <v>6122</v>
+        <v>6112</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20 22:00:00</t>
+          <t>2026-10-21 04:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20.74</v>
+        <v>18.63</v>
       </c>
       <c r="C8" t="n">
-        <v>21.85</v>
+        <v>18.98</v>
       </c>
       <c r="D8" t="n">
-        <v>19.51</v>
+        <v>18.29</v>
       </c>
       <c r="E8" t="n">
-        <v>12.9</v>
+        <v>14.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.7</v>
+        <v>14.4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>61.67</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>65.73</v>
+        <v>79.12</v>
       </c>
       <c r="J8" t="n">
-        <v>58.39</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -827,524 +827,524 @@
         <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="N8" t="n">
-        <v>6122</v>
+        <v>6112</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:00:00</t>
+          <t>2026-10-21 03:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.75</v>
+        <v>18.02</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07</v>
+        <v>18.2</v>
       </c>
       <c r="D9" t="n">
-        <v>22.23</v>
+        <v>17.63</v>
       </c>
       <c r="E9" t="n">
-        <v>13.2</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>55.42</v>
+        <v>78.34</v>
       </c>
       <c r="I9" t="n">
-        <v>57</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>54.24</v>
+        <v>77.64</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="N9" t="n">
-        <v>6132</v>
+        <v>6092</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20 20:00:00</t>
+          <t>2026-10-21 02:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.5</v>
+        <v>16.92</v>
       </c>
       <c r="C10" t="n">
-        <v>23.82</v>
+        <v>17.53</v>
       </c>
       <c r="D10" t="n">
-        <v>23.14</v>
+        <v>16.5</v>
       </c>
       <c r="E10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F10" t="n">
         <v>13</v>
       </c>
-      <c r="F10" t="n">
-        <v>12.8</v>
-      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>52.31</v>
+        <v>80.12</v>
       </c>
       <c r="I10" t="n">
-        <v>54</v>
+        <v>82.41</v>
       </c>
       <c r="J10" t="n">
-        <v>50.87</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="N10" t="n">
-        <v>6132</v>
+        <v>6092</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20 19:00:00</t>
+          <t>2026-10-21 01:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24.27</v>
+        <v>15.88</v>
       </c>
       <c r="C11" t="n">
-        <v>24.74</v>
+        <v>16.25</v>
       </c>
       <c r="D11" t="n">
-        <v>23.84</v>
+        <v>15.27</v>
       </c>
       <c r="E11" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F11" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>49.32</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>50.77</v>
+        <v>85.31</v>
       </c>
       <c r="J11" t="n">
-        <v>47.94</v>
+        <v>80.92</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="N11" t="n">
-        <v>6142</v>
+        <v>6112</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20 18:00:00</t>
+          <t>2026-10-21 00:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25.12</v>
+        <v>16.91</v>
       </c>
       <c r="C12" t="n">
-        <v>25.39</v>
+        <v>17.84</v>
       </c>
       <c r="D12" t="n">
-        <v>24.84</v>
+        <v>16.18</v>
       </c>
       <c r="E12" t="n">
         <v>12.8</v>
       </c>
       <c r="F12" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="G12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>46.99</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>47.92</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>45.97</v>
+        <v>73.23</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="N12" t="n">
-        <v>6152</v>
+        <v>6102</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20 17:00:00</t>
+          <t>2026-10-20 23:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.86</v>
+        <v>18.54</v>
       </c>
       <c r="C13" t="n">
-        <v>26.34</v>
+        <v>19.29</v>
       </c>
       <c r="D13" t="n">
-        <v>25.5</v>
+        <v>17.65</v>
       </c>
       <c r="E13" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F13" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="G13" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>44.61</v>
+        <v>69.75</v>
       </c>
       <c r="I13" t="n">
-        <v>45.71</v>
+        <v>73.11</v>
       </c>
       <c r="J13" t="n">
-        <v>43.23</v>
+        <v>66.94</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="N13" t="n">
-        <v>6162</v>
+        <v>6122</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20 16:00:00</t>
+          <t>2026-10-20 22:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.66</v>
+        <v>20.74</v>
       </c>
       <c r="C14" t="n">
-        <v>26.95</v>
+        <v>21.85</v>
       </c>
       <c r="D14" t="n">
-        <v>26.15</v>
+        <v>19.51</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="F14" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="G14" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>42.04</v>
+        <v>61.67</v>
       </c>
       <c r="I14" t="n">
-        <v>43.28</v>
+        <v>65.73</v>
       </c>
       <c r="J14" t="n">
-        <v>41.15</v>
+        <v>58.39</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="N14" t="n">
-        <v>6170</v>
+        <v>6122</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20 15:00:00</t>
+          <t>2026-10-20 21:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.13</v>
+        <v>22.75</v>
       </c>
       <c r="C15" t="n">
-        <v>27.72</v>
+        <v>23.07</v>
       </c>
       <c r="D15" t="n">
-        <v>26.66</v>
+        <v>22.23</v>
       </c>
       <c r="E15" t="n">
-        <v>12.3</v>
+        <v>13.2</v>
       </c>
       <c r="F15" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="G15" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>40.38</v>
+        <v>55.42</v>
       </c>
       <c r="I15" t="n">
-        <v>41.51</v>
+        <v>57</v>
       </c>
       <c r="J15" t="n">
-        <v>39.08</v>
+        <v>54.24</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="N15" t="n">
-        <v>6180</v>
+        <v>6132</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20 14:00:00</t>
+          <t>2026-10-20 20:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.77</v>
+        <v>23.5</v>
       </c>
       <c r="C16" t="n">
-        <v>27.91</v>
+        <v>23.82</v>
       </c>
       <c r="D16" t="n">
-        <v>25.49</v>
+        <v>23.14</v>
       </c>
       <c r="E16" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="G16" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>41.64</v>
+        <v>52.31</v>
       </c>
       <c r="I16" t="n">
-        <v>44.08</v>
+        <v>54</v>
       </c>
       <c r="J16" t="n">
-        <v>39.72</v>
+        <v>50.87</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>0.3</v>
       </c>
       <c r="N16" t="n">
-        <v>6190</v>
+        <v>6132</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20 13:00:00</t>
+          <t>2026-10-20 19:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25.07</v>
+        <v>24.27</v>
       </c>
       <c r="C17" t="n">
-        <v>25.85</v>
+        <v>24.74</v>
       </c>
       <c r="D17" t="n">
-        <v>24.61</v>
+        <v>23.84</v>
       </c>
       <c r="E17" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="F17" t="n">
-        <v>11.5</v>
+        <v>12.6</v>
       </c>
       <c r="G17" t="n">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>44.5</v>
+        <v>49.32</v>
       </c>
       <c r="I17" t="n">
-        <v>45.61</v>
+        <v>50.77</v>
       </c>
       <c r="J17" t="n">
-        <v>43.09</v>
+        <v>47.94</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="N17" t="n">
-        <v>6170</v>
+        <v>6142</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20 12:00:00</t>
+          <t>2026-10-20 18:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24.81</v>
+        <v>25.12</v>
       </c>
       <c r="C18" t="n">
-        <v>25.08</v>
+        <v>25.39</v>
       </c>
       <c r="D18" t="n">
-        <v>24.53</v>
+        <v>24.84</v>
       </c>
       <c r="E18" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="F18" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="G18" t="n">
-        <v>373</v>
+        <v>32</v>
       </c>
       <c r="H18" t="n">
-        <v>43.89</v>
+        <v>46.99</v>
       </c>
       <c r="I18" t="n">
-        <v>44.75</v>
+        <v>47.92</v>
       </c>
       <c r="J18" t="n">
-        <v>43.04</v>
+        <v>45.97</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="N18" t="n">
-        <v>6162</v>
+        <v>6152</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00:00</t>
+          <t>2026-10-20 17:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.48</v>
+        <v>25.86</v>
       </c>
       <c r="C19" t="n">
-        <v>24.58</v>
+        <v>26.34</v>
       </c>
       <c r="D19" t="n">
-        <v>22.73</v>
+        <v>25.5</v>
       </c>
       <c r="E19" t="n">
-        <v>11.3</v>
+        <v>12.7</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="G19" t="n">
-        <v>519</v>
+        <v>91</v>
       </c>
       <c r="H19" t="n">
-        <v>47.14</v>
+        <v>44.61</v>
       </c>
       <c r="I19" t="n">
-        <v>49.9</v>
+        <v>45.71</v>
       </c>
       <c r="J19" t="n">
-        <v>43.67</v>
+        <v>43.23</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M19" t="n">
         <v>2.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.6</v>
       </c>
       <c r="N19" t="n">
         <v>6162</v>
@@ -1354,364 +1354,364 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20 10:00:00</t>
+          <t>2026-10-20 16:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.96</v>
+        <v>26.66</v>
       </c>
       <c r="C20" t="n">
-        <v>22.96</v>
+        <v>26.95</v>
       </c>
       <c r="D20" t="n">
-        <v>21.26</v>
+        <v>26.15</v>
       </c>
       <c r="E20" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="F20" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="G20" t="n">
-        <v>298</v>
+        <v>229</v>
       </c>
       <c r="H20" t="n">
-        <v>52.22</v>
+        <v>42.04</v>
       </c>
       <c r="I20" t="n">
-        <v>54.36</v>
+        <v>43.28</v>
       </c>
       <c r="J20" t="n">
-        <v>49</v>
+        <v>41.15</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>6152</v>
+        <v>6170</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20 09:00:00</t>
+          <t>2026-10-20 15:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.32</v>
+        <v>27.13</v>
       </c>
       <c r="C21" t="n">
-        <v>21.66</v>
+        <v>27.72</v>
       </c>
       <c r="D21" t="n">
-        <v>19.17</v>
+        <v>26.66</v>
       </c>
       <c r="E21" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F21" t="n">
         <v>11.9</v>
       </c>
       <c r="G21" t="n">
-        <v>289</v>
+        <v>368</v>
       </c>
       <c r="H21" t="n">
-        <v>60.55</v>
+        <v>40.38</v>
       </c>
       <c r="I21" t="n">
-        <v>64.51000000000001</v>
+        <v>41.51</v>
       </c>
       <c r="J21" t="n">
-        <v>55.76</v>
+        <v>39.08</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1</v>
+        <v>4.7</v>
       </c>
       <c r="N21" t="n">
-        <v>6142</v>
+        <v>6180</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20 08:00:00</t>
+          <t>2026-10-20 14:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18.15</v>
+        <v>26.77</v>
       </c>
       <c r="C22" t="n">
-        <v>19.16</v>
+        <v>27.91</v>
       </c>
       <c r="D22" t="n">
-        <v>17.45</v>
+        <v>25.49</v>
       </c>
       <c r="E22" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="F22" t="n">
         <v>12.1</v>
       </c>
       <c r="G22" t="n">
-        <v>111</v>
+        <v>508</v>
       </c>
       <c r="H22" t="n">
-        <v>70.59</v>
+        <v>41.64</v>
       </c>
       <c r="I22" t="n">
-        <v>75.61</v>
+        <v>44.08</v>
       </c>
       <c r="J22" t="n">
-        <v>65.56999999999999</v>
+        <v>39.72</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>6122</v>
+        <v>6190</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20 07:00:00</t>
+          <t>2026-10-20 13:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.92</v>
+        <v>25.07</v>
       </c>
       <c r="C23" t="n">
-        <v>17.33</v>
+        <v>25.85</v>
       </c>
       <c r="D23" t="n">
-        <v>16.7</v>
+        <v>24.61</v>
       </c>
       <c r="E23" t="n">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="F23" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="G23" t="n">
-        <v>17</v>
+        <v>300</v>
       </c>
       <c r="H23" t="n">
-        <v>74.87</v>
+        <v>44.5</v>
       </c>
       <c r="I23" t="n">
-        <v>75.66</v>
+        <v>45.61</v>
       </c>
       <c r="J23" t="n">
-        <v>74.08</v>
+        <v>43.09</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>6092</v>
+        <v>6170</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00:00</t>
+          <t>2026-10-20 12:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.75</v>
+        <v>24.81</v>
       </c>
       <c r="C24" t="n">
-        <v>16.84</v>
+        <v>25.08</v>
       </c>
       <c r="D24" t="n">
-        <v>16.64</v>
+        <v>24.53</v>
       </c>
       <c r="E24" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="F24" t="n">
-        <v>11.9</v>
+        <v>11.2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="H24" t="n">
-        <v>74.86</v>
+        <v>43.89</v>
       </c>
       <c r="I24" t="n">
-        <v>75.98</v>
+        <v>44.75</v>
       </c>
       <c r="J24" t="n">
-        <v>73.98999999999999</v>
+        <v>43.04</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>6102</v>
+        <v>6162</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-20 05:00:00</t>
+          <t>2026-10-20 11:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16.83</v>
+        <v>23.48</v>
       </c>
       <c r="C25" t="n">
-        <v>17.01</v>
+        <v>24.58</v>
       </c>
       <c r="D25" t="n">
-        <v>16.66</v>
+        <v>22.73</v>
       </c>
       <c r="E25" t="n">
-        <v>11.9</v>
+        <v>11.3</v>
       </c>
       <c r="F25" t="n">
-        <v>11.7</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>519</v>
       </c>
       <c r="H25" t="n">
-        <v>73.56999999999999</v>
+        <v>47.14</v>
       </c>
       <c r="I25" t="n">
-        <v>75.19</v>
+        <v>49.9</v>
       </c>
       <c r="J25" t="n">
-        <v>72.06</v>
+        <v>43.67</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>6082</v>
+        <v>6162</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-20 04:00:00</t>
+          <t>2026-10-20 10:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16.74</v>
+        <v>21.96</v>
       </c>
       <c r="C26" t="n">
-        <v>16.99</v>
+        <v>22.96</v>
       </c>
       <c r="D26" t="n">
-        <v>16.45</v>
+        <v>21.26</v>
       </c>
       <c r="E26" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="F26" t="n">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="H26" t="n">
-        <v>74.84</v>
+        <v>52.22</v>
       </c>
       <c r="I26" t="n">
-        <v>77.06999999999999</v>
+        <v>54.36</v>
       </c>
       <c r="J26" t="n">
-        <v>72.64</v>
+        <v>49</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>6112</v>
+        <v>6152</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-20 03:00:00</t>
+          <t>2026-10-20 09:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.86</v>
+        <v>20.32</v>
       </c>
       <c r="C27" t="n">
-        <v>17.22</v>
+        <v>21.66</v>
       </c>
       <c r="D27" t="n">
-        <v>16.71</v>
+        <v>19.17</v>
       </c>
       <c r="E27" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="H27" t="n">
-        <v>75.81999999999999</v>
+        <v>60.55</v>
       </c>
       <c r="I27" t="n">
-        <v>77.26000000000001</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>74.54000000000001</v>
+        <v>55.76</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1720,45 +1720,45 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N27" t="n">
-        <v>6112</v>
+        <v>6142</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00:00</t>
+          <t>2026-10-20 08:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17.59</v>
+        <v>18.15</v>
       </c>
       <c r="C28" t="n">
-        <v>17.8</v>
+        <v>19.16</v>
       </c>
       <c r="D28" t="n">
-        <v>17.29</v>
+        <v>17.45</v>
       </c>
       <c r="E28" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="F28" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="H28" t="n">
-        <v>73.83</v>
+        <v>70.59</v>
       </c>
       <c r="I28" t="n">
-        <v>74.95</v>
+        <v>75.61</v>
       </c>
       <c r="J28" t="n">
-        <v>72.36</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N28" t="n">
         <v>6122</v>
@@ -1777,35 +1777,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20 01:00:00</t>
+          <t>2026-10-20 07:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18.24</v>
+        <v>16.92</v>
       </c>
       <c r="C29" t="n">
-        <v>18.59</v>
+        <v>17.33</v>
       </c>
       <c r="D29" t="n">
-        <v>17.84</v>
+        <v>16.7</v>
       </c>
       <c r="E29" t="n">
-        <v>11.8</v>
+        <v>12.3</v>
       </c>
       <c r="F29" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>66.76000000000001</v>
+        <v>74.87</v>
       </c>
       <c r="I29" t="n">
-        <v>71.14</v>
+        <v>75.66</v>
       </c>
       <c r="J29" t="n">
-        <v>63.93</v>
+        <v>74.08</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1824,35 +1824,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-20 00:00:00</t>
+          <t>2026-10-20 06:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>18.68</v>
+        <v>16.75</v>
       </c>
       <c r="C30" t="n">
-        <v>18.93</v>
+        <v>16.84</v>
       </c>
       <c r="D30" t="n">
-        <v>18.52</v>
+        <v>16.64</v>
       </c>
       <c r="E30" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="F30" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>64.40000000000001</v>
+        <v>74.86</v>
       </c>
       <c r="I30" t="n">
-        <v>65.87</v>
+        <v>75.98</v>
       </c>
       <c r="J30" t="n">
-        <v>61.94</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1864,44 +1864,42 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6122</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3</v>
-      </c>
+        <v>6102</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-19 23:00:00</t>
+          <t>2026-10-20 05:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.43</v>
+        <v>16.83</v>
       </c>
       <c r="C31" t="n">
-        <v>19.64</v>
+        <v>17.01</v>
       </c>
       <c r="D31" t="n">
-        <v>19.01</v>
+        <v>16.66</v>
       </c>
       <c r="E31" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="F31" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>60.1</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>60.96</v>
+        <v>75.19</v>
       </c>
       <c r="J31" t="n">
-        <v>59.25</v>
+        <v>72.06</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1913,51 +1911,51 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6132</v>
+        <v>6082</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-19 22:00:00</t>
+          <t>2026-10-20 04:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>20.1</v>
+        <v>16.74</v>
       </c>
       <c r="C32" t="n">
-        <v>20.3</v>
+        <v>16.99</v>
       </c>
       <c r="D32" t="n">
-        <v>19.77</v>
+        <v>16.45</v>
       </c>
       <c r="E32" t="n">
-        <v>11</v>
+        <v>12.1</v>
       </c>
       <c r="F32" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>56.64</v>
+        <v>74.84</v>
       </c>
       <c r="I32" t="n">
-        <v>58.8</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>55.68</v>
+        <v>72.64</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>6112</v>
@@ -1967,846 +1965,848 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-19 21:00:00</t>
+          <t>2026-10-20 03:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20</v>
+        <v>16.86</v>
       </c>
       <c r="C33" t="n">
-        <v>20.17</v>
+        <v>17.22</v>
       </c>
       <c r="D33" t="n">
-        <v>19.94</v>
+        <v>16.71</v>
       </c>
       <c r="E33" t="n">
-        <v>10.6</v>
+        <v>12.4</v>
       </c>
       <c r="F33" t="n">
-        <v>10.6</v>
+        <v>12</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>55.69</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>55.96</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>55.41</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>6142</v>
+        <v>6112</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-19 20:00:00</t>
+          <t>2026-10-20 02:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.56</v>
+        <v>17.59</v>
       </c>
       <c r="C34" t="n">
-        <v>19.96</v>
+        <v>17.8</v>
       </c>
       <c r="D34" t="n">
-        <v>19.34</v>
+        <v>17.29</v>
       </c>
       <c r="E34" t="n">
-        <v>10.6</v>
+        <v>12.7</v>
       </c>
       <c r="F34" t="n">
-        <v>10.3</v>
+        <v>12.5</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>56.91</v>
+        <v>73.83</v>
       </c>
       <c r="I34" t="n">
-        <v>57.67</v>
+        <v>74.95</v>
       </c>
       <c r="J34" t="n">
-        <v>55.82</v>
+        <v>72.36</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6142</v>
+        <v>6122</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-19 19:00:00</t>
+          <t>2026-10-20 01:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.8</v>
+        <v>18.24</v>
       </c>
       <c r="C35" t="n">
-        <v>19.92</v>
+        <v>18.59</v>
       </c>
       <c r="D35" t="n">
-        <v>19.62</v>
+        <v>17.84</v>
       </c>
       <c r="E35" t="n">
-        <v>10.3</v>
+        <v>11.8</v>
       </c>
       <c r="F35" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="G35" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>55.22</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>56.29</v>
+        <v>71.14</v>
       </c>
       <c r="J35" t="n">
-        <v>54.46</v>
+        <v>63.93</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6152</v>
+        <v>6092</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-20 00:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19.91</v>
+        <v>18.68</v>
       </c>
       <c r="C36" t="n">
-        <v>19.98</v>
+        <v>18.93</v>
       </c>
       <c r="D36" t="n">
-        <v>19.83</v>
+        <v>18.52</v>
       </c>
       <c r="E36" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
       <c r="F36" t="n">
-        <v>10.2</v>
+        <v>11.2</v>
       <